--- a/Src/Assets/StreamingAssets/Common/Tables/Tables/Hero&Enemy.xlsx
+++ b/Src/Assets/StreamingAssets/Common/Tables/Tables/Hero&Enemy.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1273" uniqueCount="844">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1278" uniqueCount="847">
   <si>
     <t>Key</t>
   </si>
@@ -1470,6 +1470,15 @@
     <t>受伤叠加一层复仇，造成伤害失去一点复仇，幼狼死亡获得三点复仇，其他狼死亡获得两点复仇。你每有一层复仇，伤害+1，有复仇时为高攻击欲望。</t>
   </si>
   <si>
+    <t>Leader Catch</t>
+  </si>
+  <si>
+    <t>擒贼先擒王</t>
+  </si>
+  <si>
+    <t>当场上所有类型为Boss和Elite的单位全部死亡时，玩家赢得此局游戏。</t>
+  </si>
+  <si>
     <t>MaxHP</t>
   </si>
   <si>
@@ -1488,7 +1497,7 @@
     <t>【熔铸】第9回合，你击杀场上所有存活的青铜小鬼，并获得它们的资源，你每击杀一个青铜小鬼，你的伤害*2，攻击力+0.5。</t>
   </si>
   <si>
-    <t>["MoltenCast"]</t>
+    <t>["MoltenCast", "Leader Catch"]</t>
   </si>
   <si>
     <t>Boss</t>
@@ -1518,7 +1527,7 @@
     <t>【播种】从第2回合起每隔3回合，你失去3点血量，召唤两个小树领。【枝繁叶茂】若你连续4回合未受到伤害，你回复5点血量，然后重置此技能计数。</t>
   </si>
   <si>
-    <t>["Sow", "LushGrowth"]</t>
+    <t>["Sow", "LushGrowth", "Leader Catch"]</t>
   </si>
   <si>
     <t>FormlessWater</t>
@@ -1640,7 +1649,7 @@
     <t>【死亡化身】第4回合起，你每隔4回合进入一次'生命收割'状态。'生命收割'状态下你不受到任何伤害，且伤害*4。该状态持续3回合。若你在一次'生命收割'状态下未能击杀任何目标，你下回合眩晕。</t>
   </si>
   <si>
-    <t>["DeathIncarnate"]</t>
+    <t>["DeathIncarnate", "Leader Catch"]</t>
   </si>
   <si>
     <t>Imp</t>
@@ -1774,7 +1783,7 @@
     <t>【崩坏】当你是场上血量最多的角色时，你每回合失去2点血量。【地狱集结】每隔5回合，你召唤3个堕落天使。场上最多同时存在7个堕落天使。【奋不顾身】当你的血量小于20时，你失去【地狱集结】，获得【你死我活】。</t>
   </si>
   <si>
-    <t>["Collapse", "HellGather", "DesperateStruggle", "LifeOrDeath"]</t>
+    <t>["Collapse", "HellGather", "DesperateStruggle", "LifeOrDeath", "Leader Catch"]</t>
   </si>
   <si>
     <t>FallenAngel</t>
@@ -1849,7 +1858,7 @@
     <t>【图腾召唤】每三回合随机召唤一个图腾，场上有空余格子时为低攻击欲望，场上没有空余格子时为高攻击欲望。</t>
   </si>
   <si>
-    <t>["TotemCall"]</t>
+    <t>["TotemCall", "Leader Catch"]</t>
   </si>
   <si>
     <t>Follower</t>
@@ -2083,7 +2092,7 @@
     </r>
   </si>
   <si>
-    <t>["WolfHowl", "Bloodlust"]</t>
+    <t>["WolfHowl", "Bloodlust", "Leader Catch"]</t>
   </si>
   <si>
     <t>SixEarMacaque</t>
@@ -2165,7 +2174,7 @@
     </r>
   </si>
   <si>
-    <t>["WellEquipped"]</t>
+    <t>["WellEquipped", "Leader Catch"]</t>
   </si>
   <si>
     <t>Troll</t>
@@ -3425,27 +3434,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <u/>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11.25"/>
-      <color rgb="FFF9FAFB"/>
-      <name val="Segoe UI"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11.25"/>
-      <color rgb="FFF9FAFB"/>
-      <name val="Segoe UI"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <i/>
       <sz val="11.25"/>
       <color rgb="FFFF0000"/>
@@ -3468,6 +3456,27 @@
     <font>
       <sz val="11.25"/>
       <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11.25"/>
+      <color rgb="FFF9FAFB"/>
+      <name val="Segoe UI"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11.25"/>
+      <color rgb="FFF9FAFB"/>
+      <name val="Segoe UI"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <u/>
+      <sz val="10"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -4700,7 +4709,7 @@
     <col min="1" max="1" width="22.8166666666667" style="10" customWidth="1"/>
     <col min="2" max="2" width="21.4916666666667" style="10" customWidth="1"/>
     <col min="3" max="3" width="8.25" style="10"/>
-    <col min="4" max="4" width="15.2166666666667" style="10" customWidth="1"/>
+    <col min="4" max="4" width="15.2083333333333" style="10" customWidth="1"/>
     <col min="5" max="5" width="14" style="10" customWidth="1"/>
     <col min="6" max="6" width="23.675" style="10" customWidth="1"/>
     <col min="7" max="7" width="8.70833333333333" style="10" customWidth="1"/>
@@ -5624,13 +5633,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H86"/>
+  <dimension ref="A1:H87"/>
   <sheetFormatPr defaultColWidth="8.25" defaultRowHeight="14" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="1" width="28.3166666666667" style="10" customWidth="1"/>
     <col min="2" max="2" width="23.9333333333333" style="10" customWidth="1"/>
     <col min="3" max="3" width="16.9083333333333" style="10" customWidth="1"/>
-    <col min="4" max="4" width="15.7833333333333" style="10" customWidth="1"/>
+    <col min="4" max="4" width="15.7916666666667" style="10" customWidth="1"/>
     <col min="5" max="5" width="13.2416666666667" style="10" customWidth="1"/>
     <col min="6" max="6" width="25.975" style="10" customWidth="1"/>
     <col min="7" max="16382" width="8.25" style="10"/>
@@ -5737,7 +5746,7 @@
         <v>11</v>
       </c>
       <c r="H4" s="32">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5" ht="39" spans="1:8">
@@ -5763,7 +5772,7 @@
         <v>11</v>
       </c>
       <c r="H5" s="34">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6" ht="26" spans="1:8">
@@ -7869,6 +7878,32 @@
         <v>11</v>
       </c>
       <c r="H86" s="32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" ht="44" customHeight="1" spans="1:8">
+      <c r="A87" s="34" t="s">
+        <v>345</v>
+      </c>
+      <c r="B87" s="34" t="s">
+        <v>345</v>
+      </c>
+      <c r="C87" s="34" t="s">
+        <v>346</v>
+      </c>
+      <c r="D87" s="34" t="b">
+        <v>1</v>
+      </c>
+      <c r="E87" s="34">
+        <v>1</v>
+      </c>
+      <c r="F87" s="35" t="s">
+        <v>347</v>
+      </c>
+      <c r="G87" s="34" t="s">
+        <v>11</v>
+      </c>
+      <c r="H87" s="34">
         <v>0</v>
       </c>
     </row>
@@ -7909,1255 +7944,1255 @@
         <v>5</v>
       </c>
       <c r="E1" s="12" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="F1" s="13" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="G1" s="13" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="14" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="B2" s="15" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="C2" s="16" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="D2" s="16" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="E2" s="16">
         <v>40</v>
       </c>
       <c r="F2" s="17" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="G2" s="17" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3" s="18" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="B3" s="19" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="C3" s="20" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="D3" s="20" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="E3" s="20">
         <v>8</v>
       </c>
       <c r="F3" s="21" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="G3" s="21" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4" s="14" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="B4" s="15" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="C4" s="16" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="D4" s="16" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="E4" s="16">
         <v>30</v>
       </c>
       <c r="F4" s="17" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="G4" s="17" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5" s="18" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="B5" s="19" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="C5" s="20" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="D5" s="20" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="E5" s="20">
         <v>10</v>
       </c>
       <c r="F5" s="21" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="G5" s="21" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6" s="14" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="B6" s="15" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="C6" s="16" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="D6" s="16" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="E6" s="16">
         <v>25</v>
       </c>
       <c r="F6" s="17" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="G6" s="17" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7" s="18" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="B7" s="19" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="C7" s="20" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="D7" s="20" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="E7" s="20">
         <v>35</v>
       </c>
       <c r="F7" s="21" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="G7" s="21" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8" s="22" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="B8" s="23" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="C8" s="24" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="D8" s="24" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="E8" s="24">
         <v>50</v>
       </c>
       <c r="F8" s="25" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="G8" s="25" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9" s="26" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="B9" s="27" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="C9" s="28" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="D9" s="28" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="E9" s="28">
         <v>55</v>
       </c>
       <c r="F9" s="29" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="G9" s="29" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
     </row>
     <row r="10" ht="17" spans="1:7">
       <c r="A10" s="22" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="B10" s="23" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="C10" s="24" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="D10" s="24" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="E10" s="24">
         <v>35</v>
       </c>
       <c r="F10" s="25" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="G10" s="25" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11" s="26" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="B11" s="27" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="C11" s="28" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="D11" s="28" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="E11" s="28">
         <v>30</v>
       </c>
       <c r="F11" s="29" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="G11" s="29" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12" s="22" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="B12" s="23" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="C12" s="24" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="D12" s="24" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="E12" s="24">
         <v>40</v>
       </c>
       <c r="F12" s="25" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="G12" s="25" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13" s="26" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="B13" s="27" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="C13" s="28" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="D13" s="28" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="E13" s="28">
         <v>4</v>
       </c>
       <c r="F13" s="29" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="G13" s="29" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14" s="22" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="B14" s="23" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="C14" s="24" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="D14" s="24" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="E14" s="24">
         <v>30</v>
       </c>
       <c r="F14" s="25" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="G14" s="25" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15" s="26" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="B15" s="27" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="C15" s="28" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="D15" s="28" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="E15" s="28">
         <v>70</v>
       </c>
       <c r="F15" s="29" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="G15" s="29" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
     </row>
     <row r="16" spans="1:7">
       <c r="A16" s="22" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="B16" s="23" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="C16" s="24" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="D16" s="24" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="E16" s="24">
         <v>60</v>
       </c>
       <c r="F16" s="25" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="G16" s="25" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
     </row>
     <row r="17" spans="1:7">
       <c r="A17" s="26" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="B17" s="27" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="C17" s="28" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="D17" s="28" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="E17" s="28">
         <v>30</v>
       </c>
       <c r="F17" s="29" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="G17" s="29" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
     </row>
     <row r="18" spans="1:7">
       <c r="A18" s="22" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="B18" s="23" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="C18" s="24" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="D18" s="24" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="E18" s="24">
         <v>30</v>
       </c>
       <c r="F18" s="25" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="G18" s="25" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
     </row>
     <row r="19" spans="1:7">
       <c r="A19" s="26" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="B19" s="27" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="C19" s="28" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="D19" s="28" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="E19" s="28">
         <v>30</v>
       </c>
       <c r="F19" s="29" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="G19" s="29" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
     </row>
     <row r="20" ht="17" spans="1:7">
       <c r="A20" s="22" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="B20" s="23" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="C20" s="24" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="D20" s="24" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="E20" s="24">
         <v>20</v>
       </c>
       <c r="F20" s="25" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="G20" s="25" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
     </row>
     <row r="21" spans="1:7">
       <c r="A21" s="26" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="B21" s="27" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="C21" s="28" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="D21" s="28" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="E21" s="28">
         <v>100</v>
       </c>
       <c r="F21" s="29" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="G21" s="29" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
     </row>
     <row r="22" spans="1:7">
       <c r="A22" s="22" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="B22" s="23" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="C22" s="24" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="D22" s="24" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="E22" s="24">
         <v>10</v>
       </c>
       <c r="F22" s="25" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="G22" s="25" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
     </row>
     <row r="23" spans="1:7">
       <c r="A23" s="26" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="B23" s="27" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="C23" s="28" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="D23" s="28" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="E23" s="28">
         <v>20</v>
       </c>
       <c r="F23" s="29" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="G23" s="29" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
     </row>
     <row r="24" spans="1:7">
       <c r="A24" s="22" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="B24" s="23" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="C24" s="24" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="D24" s="24" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="E24" s="24">
         <v>20</v>
       </c>
       <c r="F24" s="25" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="G24" s="25" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
     </row>
     <row r="25" spans="1:7">
       <c r="A25" s="26" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="B25" s="27" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="C25" s="28" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="D25" s="28" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="E25" s="28">
         <v>35</v>
       </c>
       <c r="F25" s="29" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="G25" s="29" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
     </row>
     <row r="26" spans="1:7">
       <c r="A26" s="22" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="B26" s="23" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="C26" s="24" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="D26" s="24" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="E26" s="24">
         <v>50</v>
       </c>
       <c r="F26" s="25" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="G26" s="25" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
     </row>
     <row r="27" spans="1:7">
       <c r="A27" s="26" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="B27" s="27" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="C27" s="28" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="D27" s="28" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="E27" s="28">
         <v>20</v>
       </c>
       <c r="F27" s="29" t="s">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c r="G27" s="29" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
     </row>
     <row r="28" spans="1:7">
       <c r="A28" s="22" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="B28" s="23" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="C28" s="24" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="D28" s="24" t="s">
-        <v>457</v>
+        <v>460</v>
       </c>
       <c r="E28" s="24">
         <v>5</v>
       </c>
       <c r="F28" s="25" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="G28" s="25" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
     </row>
     <row r="29" spans="1:7">
       <c r="A29" s="26" t="s">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="B29" s="27" t="s">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="C29" s="28" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="D29" s="28" t="s">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="E29" s="28">
         <v>20</v>
       </c>
       <c r="F29" s="29" t="s">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="G29" s="29" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
     </row>
     <row r="30" spans="1:7">
       <c r="A30" s="22" t="s">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="B30" s="23" t="s">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="C30" s="24" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="D30" s="24" t="s">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="E30" s="24">
         <v>15</v>
       </c>
       <c r="F30" s="25" t="s">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="G30" s="25" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
     </row>
     <row r="31" spans="1:7">
       <c r="A31" s="26" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="B31" s="27" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="C31" s="28" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="D31" s="28" t="s">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="E31" s="28">
         <v>15</v>
       </c>
       <c r="F31" s="29" t="s">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="G31" s="29" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
     </row>
     <row r="32" ht="17" spans="1:7">
       <c r="A32" s="22" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="B32" s="23" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="C32" s="24" t="s">
-        <v>472</v>
+        <v>475</v>
       </c>
       <c r="D32" s="24" t="s">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="E32" s="24">
         <v>15</v>
       </c>
       <c r="F32" s="25" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="G32" s="25" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
     </row>
     <row r="33" spans="1:7">
       <c r="A33" s="26" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="B33" s="27" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="C33" s="28" t="s">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="D33" s="28" t="s">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="E33" s="28">
         <v>5</v>
       </c>
       <c r="F33" s="29" t="s">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="G33" s="29" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
     </row>
     <row r="34" spans="1:7">
       <c r="A34" s="22" t="s">
-        <v>479</v>
+        <v>482</v>
       </c>
       <c r="B34" s="23" t="s">
-        <v>479</v>
+        <v>482</v>
       </c>
       <c r="C34" s="24" t="s">
-        <v>480</v>
+        <v>483</v>
       </c>
       <c r="D34" s="24" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="E34" s="24">
         <v>25</v>
       </c>
       <c r="F34" s="25" t="s">
-        <v>482</v>
+        <v>485</v>
       </c>
       <c r="G34" s="25" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
     </row>
     <row r="35" spans="1:7">
       <c r="A35" s="26" t="s">
-        <v>483</v>
+        <v>486</v>
       </c>
       <c r="B35" s="27" t="s">
-        <v>483</v>
+        <v>486</v>
       </c>
       <c r="C35" s="28" t="s">
-        <v>484</v>
+        <v>487</v>
       </c>
       <c r="D35" s="28" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="E35" s="28">
         <v>10</v>
       </c>
       <c r="F35" s="29" t="s">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="G35" s="29" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
     </row>
     <row r="36" spans="1:7">
       <c r="A36" s="22" t="s">
-        <v>487</v>
+        <v>490</v>
       </c>
       <c r="B36" s="23" t="s">
-        <v>487</v>
+        <v>490</v>
       </c>
       <c r="C36" s="24" t="s">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="D36" s="24" t="s">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="E36" s="24">
         <v>8</v>
       </c>
       <c r="F36" s="25" t="s">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="G36" s="25" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
     </row>
     <row r="37" spans="1:7">
       <c r="A37" s="26" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="B37" s="27" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="C37" s="28" t="s">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="D37" s="28" t="s">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="E37" s="28">
         <v>100</v>
       </c>
       <c r="F37" s="29" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="G37" s="29" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
     </row>
     <row r="38" spans="1:7">
       <c r="A38" s="22" t="s">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="B38" s="23" t="s">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="C38" s="24" t="s">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="D38" s="24" t="s">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="E38" s="24">
         <v>20</v>
       </c>
       <c r="F38" s="25" t="s">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="G38" s="25" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
     </row>
     <row r="39" ht="17" spans="1:7">
       <c r="A39" s="18" t="s">
-        <v>499</v>
+        <v>502</v>
       </c>
       <c r="B39" s="19" t="s">
-        <v>499</v>
+        <v>502</v>
       </c>
       <c r="C39" s="20" t="s">
-        <v>500</v>
+        <v>503</v>
       </c>
       <c r="D39" s="20" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="E39" s="20">
         <v>10</v>
       </c>
       <c r="F39" s="21" t="s">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="G39" s="21" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
     </row>
     <row r="40" spans="1:7">
       <c r="A40" s="14" t="s">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="B40" s="15" t="s">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="C40" s="16" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="D40" s="16" t="s">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="E40" s="16">
         <v>10</v>
       </c>
       <c r="F40" s="17" t="s">
-        <v>506</v>
+        <v>509</v>
       </c>
       <c r="G40" s="17" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
     </row>
     <row r="41" spans="1:7">
       <c r="A41" s="18" t="s">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="B41" s="19" t="s">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="C41" s="20" t="s">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="D41" s="20" t="s">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="E41" s="20">
         <v>12</v>
       </c>
       <c r="F41" s="21" t="s">
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="G41" s="21" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
     </row>
     <row r="42" ht="17" spans="1:7">
       <c r="A42" s="14" t="s">
-        <v>511</v>
+        <v>514</v>
       </c>
       <c r="B42" s="15" t="s">
-        <v>511</v>
+        <v>514</v>
       </c>
       <c r="C42" s="16" t="s">
-        <v>512</v>
+        <v>515</v>
       </c>
       <c r="D42" s="16" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="E42" s="16">
         <v>15</v>
       </c>
       <c r="F42" s="17" t="s">
-        <v>514</v>
+        <v>517</v>
       </c>
       <c r="G42" s="17" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
     </row>
     <row r="43" spans="1:7">
       <c r="A43" s="18" t="s">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="B43" s="19" t="s">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="C43" s="20" t="s">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="D43" s="20" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="E43" s="20">
         <v>25</v>
       </c>
       <c r="F43" s="21" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="G43" s="21" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
     </row>
     <row r="44" spans="1:7">
       <c r="A44" s="14" t="s">
-        <v>517</v>
+        <v>520</v>
       </c>
       <c r="B44" s="15" t="s">
-        <v>517</v>
+        <v>520</v>
       </c>
       <c r="C44" s="16" t="s">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="D44" s="16" t="s">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="E44" s="16">
         <v>3</v>
       </c>
       <c r="F44" s="17" t="s">
-        <v>520</v>
+        <v>523</v>
       </c>
       <c r="G44" s="17" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
     </row>
     <row r="45" spans="1:7">
       <c r="A45" s="18" t="s">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="B45" s="19" t="s">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="C45" s="20" t="s">
-        <v>522</v>
+        <v>525</v>
       </c>
       <c r="D45" s="20" t="s">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="E45" s="20">
         <v>2</v>
       </c>
       <c r="F45" s="21" t="s">
-        <v>524</v>
+        <v>527</v>
       </c>
       <c r="G45" s="21" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
     </row>
     <row r="46" spans="1:7">
       <c r="A46" s="14" t="s">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="B46" s="15" t="s">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="C46" s="16" t="s">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="D46" s="16" t="s">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="E46" s="16">
         <v>6</v>
       </c>
       <c r="F46" s="17" t="s">
-        <v>528</v>
+        <v>531</v>
       </c>
       <c r="G46" s="17" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
     </row>
     <row r="47" spans="1:7">
       <c r="A47" s="18" t="s">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="B47" s="19" t="s">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="C47" s="20" t="s">
-        <v>530</v>
+        <v>533</v>
       </c>
       <c r="D47" s="20" t="s">
-        <v>531</v>
+        <v>534</v>
       </c>
       <c r="E47" s="20">
         <v>4</v>
       </c>
       <c r="F47" s="21" t="s">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="G47" s="21" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
     </row>
     <row r="48" spans="1:7">
       <c r="A48" s="14" t="s">
-        <v>533</v>
+        <v>536</v>
       </c>
       <c r="B48" s="15" t="s">
-        <v>533</v>
+        <v>536</v>
       </c>
       <c r="C48" s="16" t="s">
-        <v>534</v>
+        <v>537</v>
       </c>
       <c r="D48" s="16" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="E48" s="16">
         <v>3</v>
       </c>
       <c r="F48" s="17" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="G48" s="17" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
     </row>
     <row r="49" spans="1:7">
       <c r="A49" s="18" t="s">
-        <v>535</v>
+        <v>538</v>
       </c>
       <c r="B49" s="19" t="s">
-        <v>535</v>
+        <v>538</v>
       </c>
       <c r="C49" s="20" t="s">
-        <v>536</v>
+        <v>539</v>
       </c>
       <c r="D49" s="20" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
       <c r="E49" s="20">
         <v>4</v>
       </c>
       <c r="F49" s="21" t="s">
-        <v>538</v>
+        <v>541</v>
       </c>
       <c r="G49" s="21" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
     </row>
     <row r="50" spans="1:7">
       <c r="A50" s="14" t="s">
-        <v>539</v>
+        <v>542</v>
       </c>
       <c r="B50" s="15" t="s">
-        <v>539</v>
+        <v>542</v>
       </c>
       <c r="C50" s="16" t="s">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="D50" s="16" t="s">
-        <v>541</v>
+        <v>544</v>
       </c>
       <c r="E50" s="16">
         <v>4</v>
       </c>
       <c r="F50" s="17" t="s">
-        <v>542</v>
+        <v>545</v>
       </c>
       <c r="G50" s="17" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
     </row>
     <row r="51" spans="1:7">
       <c r="A51" s="18" t="s">
-        <v>543</v>
+        <v>546</v>
       </c>
       <c r="B51" s="19" t="s">
-        <v>543</v>
+        <v>546</v>
       </c>
       <c r="C51" s="20" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="D51" s="20" t="s">
-        <v>545</v>
+        <v>548</v>
       </c>
       <c r="E51" s="20">
         <v>6</v>
       </c>
       <c r="F51" s="21" t="s">
-        <v>546</v>
+        <v>549</v>
       </c>
       <c r="G51" s="21" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
     </row>
     <row r="52" spans="1:7">
       <c r="A52" s="14" t="s">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="B52" s="15" t="s">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="C52" s="16" t="s">
-        <v>548</v>
+        <v>551</v>
       </c>
       <c r="D52" s="16" t="s">
-        <v>549</v>
+        <v>552</v>
       </c>
       <c r="E52" s="16">
         <v>2</v>
       </c>
       <c r="F52" s="17" t="s">
-        <v>550</v>
+        <v>553</v>
       </c>
       <c r="G52" s="17" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
     </row>
     <row r="53" spans="1:7">
       <c r="A53" s="18" t="s">
-        <v>551</v>
+        <v>554</v>
       </c>
       <c r="B53" s="19" t="s">
-        <v>551</v>
+        <v>554</v>
       </c>
       <c r="C53" s="20" t="s">
-        <v>552</v>
+        <v>555</v>
       </c>
       <c r="D53" s="20" t="s">
-        <v>553</v>
+        <v>556</v>
       </c>
       <c r="E53" s="20">
         <v>2</v>
       </c>
       <c r="F53" s="21" t="s">
-        <v>554</v>
+        <v>557</v>
       </c>
       <c r="G53" s="21" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
     </row>
     <row r="54" spans="1:7">
       <c r="A54" s="14" t="s">
-        <v>555</v>
+        <v>558</v>
       </c>
       <c r="B54" s="15" t="s">
-        <v>555</v>
+        <v>558</v>
       </c>
       <c r="C54" s="16" t="s">
-        <v>556</v>
+        <v>559</v>
       </c>
       <c r="D54" s="16" t="s">
-        <v>557</v>
+        <v>560</v>
       </c>
       <c r="E54" s="16">
         <v>4</v>
       </c>
       <c r="F54" s="17" t="s">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="G54" s="17" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
     </row>
     <row r="55" spans="1:7">
       <c r="A55" s="18" t="s">
-        <v>559</v>
+        <v>562</v>
       </c>
       <c r="B55" s="19" t="s">
-        <v>559</v>
+        <v>562</v>
       </c>
       <c r="C55" s="20" t="s">
-        <v>560</v>
+        <v>563</v>
       </c>
       <c r="D55" s="20" t="s">
-        <v>561</v>
+        <v>564</v>
       </c>
       <c r="E55" s="20">
         <v>3</v>
       </c>
       <c r="F55" s="21" t="s">
-        <v>562</v>
+        <v>565</v>
       </c>
       <c r="G55" s="21" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
     </row>
   </sheetData>
@@ -9196,1424 +9231,1424 @@
         <v>5</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="2" t="s">
-        <v>563</v>
+        <v>566</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>564</v>
+        <v>567</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>565</v>
+        <v>568</v>
       </c>
       <c r="D2" s="4"/>
       <c r="E2" s="5">
         <v>25</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>566</v>
+        <v>569</v>
       </c>
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="6" t="s">
-        <v>567</v>
+        <v>570</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>567</v>
+        <v>570</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>568</v>
+        <v>571</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>569</v>
+        <v>572</v>
       </c>
       <c r="E3" s="5">
         <v>12</v>
       </c>
       <c r="F3" s="7" t="s">
-        <v>570</v>
+        <v>573</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="8" t="s">
-        <v>571</v>
+        <v>574</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>571</v>
+        <v>574</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>572</v>
+        <v>575</v>
       </c>
       <c r="D4" s="4"/>
       <c r="E4" s="5">
         <v>20</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>573</v>
+        <v>576</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="6" t="s">
-        <v>574</v>
+        <v>577</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>574</v>
+        <v>577</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>575</v>
+        <v>578</v>
       </c>
       <c r="D5" s="4"/>
       <c r="E5" s="5">
         <v>40</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>576</v>
+        <v>579</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="6" t="s">
-        <v>577</v>
+        <v>580</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>577</v>
+        <v>580</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>578</v>
+        <v>581</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>579</v>
+        <v>582</v>
       </c>
       <c r="E6" s="5">
         <v>20</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>580</v>
+        <v>583</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="6" t="s">
-        <v>581</v>
+        <v>584</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>581</v>
+        <v>584</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>582</v>
+        <v>585</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>583</v>
+        <v>586</v>
       </c>
       <c r="E7" s="5">
         <v>15</v>
       </c>
       <c r="F7" s="7" t="s">
-        <v>584</v>
+        <v>587</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="6" t="s">
-        <v>585</v>
+        <v>588</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>585</v>
+        <v>588</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>586</v>
+        <v>589</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>587</v>
+        <v>590</v>
       </c>
       <c r="E8" s="5">
         <v>40</v>
       </c>
       <c r="F8" s="7" t="s">
-        <v>588</v>
+        <v>591</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="6" t="s">
-        <v>589</v>
+        <v>592</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>589</v>
+        <v>592</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>590</v>
+        <v>593</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>591</v>
+        <v>594</v>
       </c>
       <c r="E9" s="5">
         <v>15</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>592</v>
+        <v>595</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="6" t="s">
-        <v>593</v>
+        <v>596</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>593</v>
+        <v>596</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>594</v>
+        <v>597</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>595</v>
+        <v>598</v>
       </c>
       <c r="E10" s="5">
         <v>15</v>
       </c>
       <c r="F10" s="7" t="s">
-        <v>596</v>
+        <v>599</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="6" t="s">
-        <v>597</v>
+        <v>600</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>597</v>
+        <v>600</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>598</v>
+        <v>601</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>599</v>
+        <v>602</v>
       </c>
       <c r="E11" s="5">
         <v>30</v>
       </c>
       <c r="F11" s="7" t="s">
-        <v>600</v>
+        <v>603</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="6" t="s">
-        <v>601</v>
+        <v>604</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>601</v>
+        <v>604</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>602</v>
+        <v>605</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>603</v>
+        <v>606</v>
       </c>
       <c r="E12" s="5">
         <v>15</v>
       </c>
       <c r="F12" s="7" t="s">
-        <v>604</v>
+        <v>607</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="6" t="s">
-        <v>605</v>
+        <v>608</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>605</v>
+        <v>608</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>607</v>
+        <v>610</v>
       </c>
       <c r="E13" s="5">
         <v>15</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>608</v>
+        <v>611</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="6" t="s">
-        <v>609</v>
+        <v>612</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>609</v>
+        <v>612</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>610</v>
+        <v>613</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>611</v>
+        <v>614</v>
       </c>
       <c r="E14" s="5">
         <v>20</v>
       </c>
       <c r="F14" s="7" t="s">
-        <v>612</v>
+        <v>615</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="6" t="s">
-        <v>613</v>
+        <v>616</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>613</v>
+        <v>616</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>614</v>
+        <v>617</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>615</v>
+        <v>618</v>
       </c>
       <c r="E15" s="5">
         <v>20</v>
       </c>
       <c r="F15" s="7" t="s">
-        <v>616</v>
+        <v>619</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="6" t="s">
-        <v>617</v>
+        <v>620</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>617</v>
+        <v>620</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>618</v>
+        <v>621</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>619</v>
+        <v>622</v>
       </c>
       <c r="E16" s="5">
         <v>15</v>
       </c>
       <c r="F16" s="7" t="s">
-        <v>620</v>
+        <v>623</v>
       </c>
     </row>
     <row r="17" spans="1:6">
       <c r="A17" s="6" t="s">
-        <v>621</v>
+        <v>624</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>621</v>
+        <v>624</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>622</v>
+        <v>625</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>623</v>
+        <v>626</v>
       </c>
       <c r="E17" s="5">
         <v>20</v>
       </c>
       <c r="F17" s="7" t="s">
-        <v>624</v>
+        <v>627</v>
       </c>
     </row>
     <row r="18" spans="1:6">
       <c r="A18" s="6" t="s">
-        <v>625</v>
+        <v>628</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>625</v>
+        <v>628</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>626</v>
+        <v>629</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>627</v>
+        <v>630</v>
       </c>
       <c r="E18" s="5">
         <v>12</v>
       </c>
       <c r="F18" s="7" t="s">
-        <v>628</v>
+        <v>631</v>
       </c>
     </row>
     <row r="19" spans="1:6">
       <c r="A19" s="6" t="s">
-        <v>629</v>
+        <v>632</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>629</v>
+        <v>632</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>630</v>
+        <v>633</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>631</v>
+        <v>634</v>
       </c>
       <c r="E19" s="5">
         <v>15</v>
       </c>
       <c r="F19" s="7" t="s">
-        <v>632</v>
+        <v>635</v>
       </c>
     </row>
     <row r="20" spans="1:6">
       <c r="A20" s="6" t="s">
-        <v>633</v>
+        <v>636</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>633</v>
+        <v>636</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>634</v>
+        <v>637</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>635</v>
+        <v>638</v>
       </c>
       <c r="E20" s="5">
         <v>12</v>
       </c>
       <c r="F20" s="7" t="s">
-        <v>636</v>
+        <v>639</v>
       </c>
     </row>
     <row r="21" spans="1:6">
       <c r="A21" s="6" t="s">
-        <v>637</v>
+        <v>640</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>637</v>
+        <v>640</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>638</v>
+        <v>641</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>639</v>
+        <v>642</v>
       </c>
       <c r="E21" s="5">
         <v>20</v>
       </c>
       <c r="F21" s="7" t="s">
-        <v>640</v>
+        <v>643</v>
       </c>
     </row>
     <row r="22" spans="1:6">
       <c r="A22" s="6" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>642</v>
+        <v>645</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>643</v>
+        <v>646</v>
       </c>
       <c r="E22" s="5">
         <v>15</v>
       </c>
       <c r="F22" s="7" t="s">
-        <v>644</v>
+        <v>647</v>
       </c>
     </row>
     <row r="23" spans="1:6">
       <c r="A23" s="6" t="s">
-        <v>645</v>
+        <v>648</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>645</v>
+        <v>648</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>646</v>
+        <v>649</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>647</v>
+        <v>650</v>
       </c>
       <c r="E23" s="5">
         <v>15</v>
       </c>
       <c r="F23" s="7" t="s">
-        <v>648</v>
+        <v>651</v>
       </c>
     </row>
     <row r="24" spans="1:6">
       <c r="A24" s="6" t="s">
-        <v>649</v>
+        <v>652</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>649</v>
+        <v>652</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>650</v>
+        <v>653</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>651</v>
+        <v>654</v>
       </c>
       <c r="E24" s="5">
         <v>15</v>
       </c>
       <c r="F24" s="7" t="s">
-        <v>652</v>
+        <v>655</v>
       </c>
     </row>
     <row r="25" spans="1:6">
       <c r="A25" s="6" t="s">
-        <v>653</v>
+        <v>656</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>653</v>
+        <v>656</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>654</v>
+        <v>657</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>655</v>
+        <v>658</v>
       </c>
       <c r="E25" s="5">
         <v>15</v>
       </c>
       <c r="F25" s="7" t="s">
-        <v>656</v>
+        <v>659</v>
       </c>
     </row>
     <row r="26" spans="1:6">
       <c r="A26" s="6" t="s">
-        <v>657</v>
+        <v>660</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>657</v>
+        <v>660</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>658</v>
+        <v>661</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>659</v>
+        <v>662</v>
       </c>
       <c r="E26" s="5">
         <v>15</v>
       </c>
       <c r="F26" s="7" t="s">
-        <v>660</v>
+        <v>663</v>
       </c>
     </row>
     <row r="27" spans="1:6">
       <c r="A27" s="6" t="s">
-        <v>661</v>
+        <v>664</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>661</v>
+        <v>664</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>662</v>
+        <v>665</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>663</v>
+        <v>666</v>
       </c>
       <c r="E27" s="5">
         <v>15</v>
       </c>
       <c r="F27" s="7" t="s">
-        <v>664</v>
+        <v>667</v>
       </c>
     </row>
     <row r="28" spans="1:6">
       <c r="A28" s="6" t="s">
-        <v>665</v>
+        <v>668</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>665</v>
+        <v>668</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>666</v>
+        <v>669</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>667</v>
+        <v>670</v>
       </c>
       <c r="E28" s="5">
         <v>3</v>
       </c>
       <c r="F28" s="7" t="s">
-        <v>478</v>
+        <v>481</v>
       </c>
     </row>
     <row r="29" spans="1:6">
       <c r="A29" s="6" t="s">
-        <v>668</v>
+        <v>671</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>668</v>
+        <v>671</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>669</v>
+        <v>672</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>670</v>
+        <v>673</v>
       </c>
       <c r="E29" s="5">
         <v>18</v>
       </c>
       <c r="F29" s="7" t="s">
-        <v>671</v>
+        <v>674</v>
       </c>
     </row>
     <row r="30" spans="1:6">
       <c r="A30" s="6" t="s">
-        <v>672</v>
+        <v>675</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>672</v>
+        <v>675</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>673</v>
+        <v>676</v>
       </c>
       <c r="D30" s="5" t="s">
-        <v>674</v>
+        <v>677</v>
       </c>
       <c r="E30" s="5">
         <v>15</v>
       </c>
       <c r="F30" s="7" t="s">
-        <v>675</v>
+        <v>678</v>
       </c>
     </row>
     <row r="31" spans="1:6">
       <c r="A31" s="6" t="s">
-        <v>676</v>
+        <v>679</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>676</v>
+        <v>679</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>677</v>
+        <v>680</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>678</v>
+        <v>681</v>
       </c>
       <c r="E31" s="5">
         <v>15</v>
       </c>
       <c r="F31" s="7" t="s">
-        <v>679</v>
+        <v>682</v>
       </c>
     </row>
     <row r="32" spans="1:6">
       <c r="A32" s="6" t="s">
-        <v>680</v>
+        <v>683</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>680</v>
+        <v>683</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>681</v>
+        <v>684</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>682</v>
+        <v>685</v>
       </c>
       <c r="E32" s="5">
         <v>15</v>
       </c>
       <c r="F32" s="7" t="s">
-        <v>683</v>
+        <v>686</v>
       </c>
     </row>
     <row r="33" spans="1:6">
       <c r="A33" s="6" t="s">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>685</v>
+        <v>688</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>686</v>
+        <v>689</v>
       </c>
       <c r="E33" s="5">
         <v>18</v>
       </c>
       <c r="F33" s="7" t="s">
-        <v>687</v>
+        <v>690</v>
       </c>
     </row>
     <row r="34" spans="1:6">
       <c r="A34" s="6" t="s">
-        <v>688</v>
+        <v>691</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>688</v>
+        <v>691</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>689</v>
+        <v>692</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>690</v>
+        <v>693</v>
       </c>
       <c r="E34" s="5">
         <v>20</v>
       </c>
       <c r="F34" s="7" t="s">
-        <v>691</v>
+        <v>694</v>
       </c>
     </row>
     <row r="35" spans="1:6">
       <c r="A35" s="6" t="s">
-        <v>692</v>
+        <v>695</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>692</v>
+        <v>695</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>693</v>
+        <v>696</v>
       </c>
       <c r="D35" s="5" t="s">
-        <v>694</v>
+        <v>697</v>
       </c>
       <c r="E35" s="5">
         <v>15</v>
       </c>
       <c r="F35" s="7" t="s">
-        <v>695</v>
+        <v>698</v>
       </c>
     </row>
     <row r="36" spans="1:6">
       <c r="A36" s="6" t="s">
-        <v>696</v>
+        <v>699</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>696</v>
+        <v>699</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>697</v>
+        <v>700</v>
       </c>
       <c r="D36" s="5" t="s">
-        <v>698</v>
+        <v>701</v>
       </c>
       <c r="E36" s="5">
         <v>18</v>
       </c>
       <c r="F36" s="7" t="s">
-        <v>699</v>
+        <v>702</v>
       </c>
     </row>
     <row r="37" spans="1:6">
       <c r="A37" s="6" t="s">
-        <v>700</v>
+        <v>703</v>
       </c>
       <c r="B37" s="6" t="s">
-        <v>700</v>
+        <v>703</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>701</v>
+        <v>704</v>
       </c>
       <c r="D37" s="5" t="s">
-        <v>702</v>
+        <v>705</v>
       </c>
       <c r="E37" s="5">
         <v>15</v>
       </c>
       <c r="F37" s="7" t="s">
-        <v>703</v>
+        <v>706</v>
       </c>
     </row>
     <row r="38" spans="1:6">
       <c r="A38" s="6" t="s">
-        <v>704</v>
+        <v>707</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>704</v>
+        <v>707</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>705</v>
+        <v>708</v>
       </c>
       <c r="D38" s="5" t="s">
-        <v>706</v>
+        <v>709</v>
       </c>
       <c r="E38" s="5">
         <v>15</v>
       </c>
       <c r="F38" s="7" t="s">
-        <v>707</v>
+        <v>710</v>
       </c>
     </row>
     <row r="39" spans="1:6">
       <c r="A39" s="6" t="s">
-        <v>708</v>
+        <v>711</v>
       </c>
       <c r="B39" s="6" t="s">
-        <v>708</v>
+        <v>711</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>709</v>
+        <v>712</v>
       </c>
       <c r="D39" s="5" t="s">
-        <v>710</v>
+        <v>713</v>
       </c>
       <c r="E39" s="5">
         <v>15</v>
       </c>
       <c r="F39" s="7" t="s">
-        <v>711</v>
+        <v>714</v>
       </c>
     </row>
     <row r="40" spans="1:6">
       <c r="A40" s="6" t="s">
-        <v>712</v>
+        <v>715</v>
       </c>
       <c r="B40" s="6" t="s">
-        <v>712</v>
+        <v>715</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>713</v>
+        <v>716</v>
       </c>
       <c r="D40" s="5" t="s">
-        <v>714</v>
+        <v>717</v>
       </c>
       <c r="E40" s="5">
         <v>15</v>
       </c>
       <c r="F40" s="7" t="s">
-        <v>715</v>
+        <v>718</v>
       </c>
     </row>
     <row r="41" spans="1:6">
       <c r="A41" s="6" t="s">
-        <v>716</v>
+        <v>719</v>
       </c>
       <c r="B41" s="6" t="s">
-        <v>716</v>
+        <v>719</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>717</v>
+        <v>720</v>
       </c>
       <c r="D41" s="5" t="s">
-        <v>718</v>
+        <v>721</v>
       </c>
       <c r="E41" s="5">
         <v>15</v>
       </c>
       <c r="F41" s="7" t="s">
-        <v>719</v>
+        <v>722</v>
       </c>
     </row>
     <row r="42" spans="1:6">
       <c r="A42" s="6" t="s">
-        <v>720</v>
+        <v>723</v>
       </c>
       <c r="B42" s="6" t="s">
-        <v>720</v>
+        <v>723</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>721</v>
+        <v>724</v>
       </c>
       <c r="D42" s="5" t="s">
-        <v>722</v>
+        <v>725</v>
       </c>
       <c r="E42" s="5">
         <v>15</v>
       </c>
       <c r="F42" s="7" t="s">
-        <v>723</v>
+        <v>726</v>
       </c>
     </row>
     <row r="43" spans="1:6">
       <c r="A43" s="6" t="s">
-        <v>724</v>
+        <v>727</v>
       </c>
       <c r="B43" s="6" t="s">
-        <v>724</v>
+        <v>727</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>725</v>
+        <v>728</v>
       </c>
       <c r="D43" s="5" t="s">
-        <v>726</v>
+        <v>729</v>
       </c>
       <c r="E43" s="5">
         <v>18</v>
       </c>
       <c r="F43" s="7" t="s">
-        <v>727</v>
+        <v>730</v>
       </c>
     </row>
     <row r="44" spans="1:6">
       <c r="A44" s="6" t="s">
-        <v>728</v>
+        <v>731</v>
       </c>
       <c r="B44" s="6" t="s">
-        <v>728</v>
+        <v>731</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>729</v>
+        <v>732</v>
       </c>
       <c r="D44" s="5" t="s">
-        <v>730</v>
+        <v>733</v>
       </c>
       <c r="E44" s="5">
         <v>15</v>
       </c>
       <c r="F44" s="7" t="s">
-        <v>731</v>
+        <v>734</v>
       </c>
     </row>
     <row r="45" spans="1:6">
       <c r="A45" s="6" t="s">
-        <v>732</v>
+        <v>735</v>
       </c>
       <c r="B45" s="6" t="s">
-        <v>732</v>
+        <v>735</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>733</v>
+        <v>736</v>
       </c>
       <c r="D45" s="5" t="s">
-        <v>734</v>
+        <v>737</v>
       </c>
       <c r="E45" s="5">
         <v>10000000</v>
       </c>
       <c r="F45" s="7" t="s">
-        <v>735</v>
+        <v>738</v>
       </c>
     </row>
     <row r="46" spans="1:6">
       <c r="A46" s="6" t="s">
-        <v>736</v>
+        <v>739</v>
       </c>
       <c r="B46" s="6" t="s">
-        <v>736</v>
+        <v>739</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>737</v>
+        <v>740</v>
       </c>
       <c r="D46" s="5" t="s">
-        <v>738</v>
+        <v>741</v>
       </c>
       <c r="E46" s="5">
         <v>15</v>
       </c>
       <c r="F46" s="7" t="s">
-        <v>739</v>
+        <v>742</v>
       </c>
     </row>
     <row r="47" spans="1:6">
       <c r="A47" s="6" t="s">
-        <v>740</v>
+        <v>743</v>
       </c>
       <c r="B47" s="6" t="s">
-        <v>740</v>
+        <v>743</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>741</v>
+        <v>744</v>
       </c>
       <c r="D47" s="5" t="s">
-        <v>742</v>
+        <v>745</v>
       </c>
       <c r="E47" s="5">
         <v>15</v>
       </c>
       <c r="F47" s="7" t="s">
-        <v>743</v>
+        <v>746</v>
       </c>
     </row>
     <row r="48" spans="1:6">
       <c r="A48" s="6" t="s">
-        <v>744</v>
+        <v>747</v>
       </c>
       <c r="B48" s="6" t="s">
-        <v>744</v>
+        <v>747</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>745</v>
+        <v>748</v>
       </c>
       <c r="D48" s="5" t="s">
-        <v>746</v>
+        <v>749</v>
       </c>
       <c r="E48" s="5">
         <v>12</v>
       </c>
       <c r="F48" s="7" t="s">
-        <v>747</v>
+        <v>750</v>
       </c>
     </row>
     <row r="49" spans="1:6">
       <c r="A49" s="6" t="s">
-        <v>748</v>
+        <v>751</v>
       </c>
       <c r="B49" s="6" t="s">
-        <v>748</v>
+        <v>751</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>749</v>
+        <v>752</v>
       </c>
       <c r="D49" s="5" t="s">
-        <v>750</v>
+        <v>753</v>
       </c>
       <c r="E49" s="5">
         <v>15</v>
       </c>
       <c r="F49" s="7" t="s">
-        <v>751</v>
+        <v>754</v>
       </c>
     </row>
     <row r="50" spans="1:6">
       <c r="A50" s="6" t="s">
-        <v>752</v>
+        <v>755</v>
       </c>
       <c r="B50" s="6" t="s">
-        <v>752</v>
+        <v>755</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>753</v>
+        <v>756</v>
       </c>
       <c r="D50" s="5" t="s">
-        <v>754</v>
+        <v>757</v>
       </c>
       <c r="E50" s="5">
         <v>40</v>
       </c>
       <c r="F50" s="7" t="s">
-        <v>755</v>
+        <v>758</v>
       </c>
     </row>
     <row r="51" spans="1:6">
       <c r="A51" s="6" t="s">
-        <v>756</v>
+        <v>759</v>
       </c>
       <c r="B51" s="6" t="s">
-        <v>756</v>
+        <v>759</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>757</v>
+        <v>760</v>
       </c>
       <c r="D51" s="5" t="s">
-        <v>758</v>
+        <v>761</v>
       </c>
       <c r="E51" s="5">
         <v>50</v>
       </c>
       <c r="F51" s="7" t="s">
-        <v>759</v>
+        <v>762</v>
       </c>
     </row>
     <row r="52" spans="1:6">
       <c r="A52" s="6" t="s">
-        <v>760</v>
+        <v>763</v>
       </c>
       <c r="B52" s="6" t="s">
-        <v>760</v>
+        <v>763</v>
       </c>
       <c r="C52" s="5" t="s">
-        <v>761</v>
+        <v>764</v>
       </c>
       <c r="D52" s="5" t="s">
-        <v>762</v>
+        <v>765</v>
       </c>
       <c r="E52" s="5">
         <v>18</v>
       </c>
       <c r="F52" s="7" t="s">
-        <v>763</v>
+        <v>766</v>
       </c>
     </row>
     <row r="53" spans="1:6">
       <c r="A53" s="6" t="s">
-        <v>764</v>
+        <v>767</v>
       </c>
       <c r="B53" s="6" t="s">
-        <v>764</v>
+        <v>767</v>
       </c>
       <c r="C53" s="5" t="s">
-        <v>765</v>
+        <v>768</v>
       </c>
       <c r="D53" s="5" t="s">
-        <v>766</v>
+        <v>769</v>
       </c>
       <c r="E53" s="5">
         <v>15</v>
       </c>
       <c r="F53" s="7" t="s">
-        <v>767</v>
+        <v>770</v>
       </c>
     </row>
     <row r="54" spans="1:6">
       <c r="A54" s="6" t="s">
-        <v>768</v>
+        <v>771</v>
       </c>
       <c r="B54" s="6" t="s">
-        <v>768</v>
+        <v>771</v>
       </c>
       <c r="C54" s="5" t="s">
-        <v>769</v>
+        <v>772</v>
       </c>
       <c r="D54" s="5" t="s">
-        <v>770</v>
+        <v>773</v>
       </c>
       <c r="E54" s="5">
         <v>20</v>
       </c>
       <c r="F54" s="7" t="s">
-        <v>771</v>
+        <v>774</v>
       </c>
     </row>
     <row r="55" spans="1:6">
       <c r="A55" s="6" t="s">
-        <v>772</v>
+        <v>775</v>
       </c>
       <c r="B55" s="6" t="s">
-        <v>772</v>
+        <v>775</v>
       </c>
       <c r="C55" s="5" t="s">
-        <v>773</v>
+        <v>776</v>
       </c>
       <c r="D55" s="5" t="s">
-        <v>774</v>
+        <v>777</v>
       </c>
       <c r="E55" s="5">
         <v>12</v>
       </c>
       <c r="F55" s="7" t="s">
-        <v>775</v>
+        <v>778</v>
       </c>
     </row>
     <row r="56" spans="1:6">
       <c r="A56" s="6" t="s">
-        <v>776</v>
+        <v>779</v>
       </c>
       <c r="B56" s="6" t="s">
-        <v>776</v>
+        <v>779</v>
       </c>
       <c r="C56" s="5" t="s">
-        <v>777</v>
+        <v>780</v>
       </c>
       <c r="D56" s="5" t="s">
-        <v>778</v>
+        <v>781</v>
       </c>
       <c r="E56" s="5">
         <v>20</v>
       </c>
       <c r="F56" s="7" t="s">
-        <v>779</v>
+        <v>782</v>
       </c>
     </row>
     <row r="57" spans="1:6">
       <c r="A57" s="6" t="s">
-        <v>780</v>
+        <v>783</v>
       </c>
       <c r="B57" s="6" t="s">
-        <v>780</v>
+        <v>783</v>
       </c>
       <c r="C57" s="5" t="s">
-        <v>781</v>
+        <v>784</v>
       </c>
       <c r="D57" s="5" t="s">
-        <v>782</v>
+        <v>785</v>
       </c>
       <c r="E57" s="5">
         <v>20</v>
       </c>
       <c r="F57" s="7" t="s">
-        <v>783</v>
+        <v>786</v>
       </c>
     </row>
     <row r="58" spans="1:6">
       <c r="A58" s="6" t="s">
-        <v>784</v>
+        <v>787</v>
       </c>
       <c r="B58" s="6" t="s">
-        <v>784</v>
+        <v>787</v>
       </c>
       <c r="C58" s="5" t="s">
-        <v>785</v>
+        <v>788</v>
       </c>
       <c r="D58" s="5" t="s">
-        <v>786</v>
+        <v>789</v>
       </c>
       <c r="E58" s="5">
         <v>15</v>
       </c>
       <c r="F58" s="7" t="s">
-        <v>787</v>
+        <v>790</v>
       </c>
     </row>
     <row r="59" spans="1:6">
       <c r="A59" s="6" t="s">
-        <v>788</v>
+        <v>791</v>
       </c>
       <c r="B59" s="6" t="s">
-        <v>788</v>
+        <v>791</v>
       </c>
       <c r="C59" s="5" t="s">
-        <v>789</v>
+        <v>792</v>
       </c>
       <c r="D59" s="5" t="s">
-        <v>790</v>
+        <v>793</v>
       </c>
       <c r="E59" s="5">
         <v>15</v>
       </c>
       <c r="F59" s="7" t="s">
-        <v>791</v>
+        <v>794</v>
       </c>
     </row>
     <row r="60" spans="1:6">
       <c r="A60" s="6" t="s">
-        <v>792</v>
+        <v>795</v>
       </c>
       <c r="B60" s="6" t="s">
-        <v>792</v>
+        <v>795</v>
       </c>
       <c r="C60" s="5" t="s">
-        <v>793</v>
+        <v>796</v>
       </c>
       <c r="D60" s="5" t="s">
-        <v>794</v>
+        <v>797</v>
       </c>
       <c r="E60" s="5">
         <v>40</v>
       </c>
       <c r="F60" s="7" t="s">
-        <v>795</v>
+        <v>798</v>
       </c>
     </row>
     <row r="61" spans="1:6">
       <c r="A61" s="6" t="s">
-        <v>796</v>
+        <v>799</v>
       </c>
       <c r="B61" s="6" t="s">
-        <v>796</v>
+        <v>799</v>
       </c>
       <c r="C61" s="5" t="s">
-        <v>797</v>
+        <v>800</v>
       </c>
       <c r="D61" s="5" t="s">
-        <v>798</v>
+        <v>801</v>
       </c>
       <c r="E61" s="5">
         <v>15</v>
       </c>
       <c r="F61" s="7" t="s">
-        <v>799</v>
+        <v>802</v>
       </c>
     </row>
     <row r="62" spans="1:6">
       <c r="A62" s="6" t="s">
-        <v>800</v>
+        <v>803</v>
       </c>
       <c r="B62" s="6" t="s">
-        <v>800</v>
+        <v>803</v>
       </c>
       <c r="C62" s="5" t="s">
-        <v>801</v>
+        <v>804</v>
       </c>
       <c r="D62" s="5" t="s">
-        <v>802</v>
+        <v>805</v>
       </c>
       <c r="E62" s="5">
         <v>20</v>
       </c>
       <c r="F62" s="7" t="s">
-        <v>803</v>
+        <v>806</v>
       </c>
     </row>
     <row r="63" spans="1:6">
       <c r="A63" s="6" t="s">
-        <v>804</v>
+        <v>807</v>
       </c>
       <c r="B63" s="6" t="s">
-        <v>804</v>
+        <v>807</v>
       </c>
       <c r="C63" s="5" t="s">
-        <v>805</v>
+        <v>808</v>
       </c>
       <c r="D63" s="5" t="s">
-        <v>806</v>
+        <v>809</v>
       </c>
       <c r="E63" s="5">
         <v>20</v>
       </c>
       <c r="F63" s="7" t="s">
-        <v>807</v>
+        <v>810</v>
       </c>
     </row>
     <row r="64" ht="26" spans="1:6">
       <c r="A64" s="6" t="s">
-        <v>808</v>
+        <v>811</v>
       </c>
       <c r="B64" s="6" t="s">
-        <v>808</v>
+        <v>811</v>
       </c>
       <c r="C64" s="5" t="s">
-        <v>809</v>
+        <v>812</v>
       </c>
       <c r="D64" s="5" t="s">
-        <v>810</v>
+        <v>813</v>
       </c>
       <c r="E64" s="5">
         <v>15</v>
       </c>
       <c r="F64" s="7" t="s">
-        <v>811</v>
+        <v>814</v>
       </c>
     </row>
     <row r="65" spans="1:6">
       <c r="A65" s="6" t="s">
-        <v>812</v>
+        <v>815</v>
       </c>
       <c r="B65" s="6" t="s">
-        <v>812</v>
+        <v>815</v>
       </c>
       <c r="C65" s="5" t="s">
-        <v>813</v>
+        <v>816</v>
       </c>
       <c r="D65" s="5" t="s">
-        <v>814</v>
+        <v>817</v>
       </c>
       <c r="E65" s="5">
         <v>20</v>
       </c>
       <c r="F65" s="7" t="s">
-        <v>815</v>
+        <v>818</v>
       </c>
     </row>
     <row r="66" spans="1:6">
       <c r="A66" s="6" t="s">
-        <v>816</v>
+        <v>819</v>
       </c>
       <c r="B66" s="6" t="s">
-        <v>816</v>
+        <v>819</v>
       </c>
       <c r="C66" s="5" t="s">
-        <v>817</v>
+        <v>820</v>
       </c>
       <c r="D66" s="5" t="s">
-        <v>818</v>
+        <v>821</v>
       </c>
       <c r="E66" s="5">
         <v>6</v>
       </c>
       <c r="F66" s="7" t="s">
-        <v>819</v>
+        <v>822</v>
       </c>
     </row>
     <row r="67" spans="1:6">
       <c r="A67" s="6" t="s">
-        <v>820</v>
+        <v>823</v>
       </c>
       <c r="B67" s="6" t="s">
-        <v>820</v>
+        <v>823</v>
       </c>
       <c r="C67" s="5" t="s">
-        <v>821</v>
+        <v>824</v>
       </c>
       <c r="D67" s="5" t="s">
-        <v>822</v>
+        <v>825</v>
       </c>
       <c r="E67" s="5">
         <v>20</v>
       </c>
       <c r="F67" s="7" t="s">
-        <v>823</v>
+        <v>826</v>
       </c>
     </row>
     <row r="68" spans="1:6">
       <c r="A68" s="6" t="s">
-        <v>824</v>
+        <v>827</v>
       </c>
       <c r="B68" s="6" t="s">
-        <v>824</v>
+        <v>827</v>
       </c>
       <c r="C68" s="5" t="s">
-        <v>825</v>
+        <v>828</v>
       </c>
       <c r="D68" s="5" t="s">
-        <v>826</v>
+        <v>829</v>
       </c>
       <c r="E68" s="5">
         <v>18</v>
       </c>
       <c r="F68" s="7" t="s">
-        <v>827</v>
+        <v>830</v>
       </c>
     </row>
     <row r="69" spans="1:6">
       <c r="A69" s="6" t="s">
-        <v>828</v>
+        <v>831</v>
       </c>
       <c r="B69" s="6" t="s">
-        <v>828</v>
+        <v>831</v>
       </c>
       <c r="C69" s="5" t="s">
-        <v>829</v>
+        <v>832</v>
       </c>
       <c r="D69" s="5" t="s">
-        <v>830</v>
+        <v>833</v>
       </c>
       <c r="E69" s="5">
         <v>12</v>
       </c>
       <c r="F69" s="7" t="s">
-        <v>831</v>
+        <v>834</v>
       </c>
     </row>
     <row r="70" spans="1:6">
       <c r="A70" s="6" t="s">
-        <v>832</v>
+        <v>835</v>
       </c>
       <c r="B70" s="6" t="s">
-        <v>832</v>
+        <v>835</v>
       </c>
       <c r="C70" s="5" t="s">
-        <v>833</v>
+        <v>836</v>
       </c>
       <c r="D70" s="5" t="s">
-        <v>834</v>
+        <v>837</v>
       </c>
       <c r="E70" s="5">
         <v>18</v>
       </c>
       <c r="F70" s="7" t="s">
-        <v>835</v>
+        <v>838</v>
       </c>
     </row>
     <row r="71" spans="1:6">
       <c r="A71" s="6" t="s">
-        <v>836</v>
+        <v>839</v>
       </c>
       <c r="B71" s="6" t="s">
-        <v>836</v>
+        <v>839</v>
       </c>
       <c r="C71" s="5" t="s">
-        <v>837</v>
+        <v>840</v>
       </c>
       <c r="D71" s="5" t="s">
-        <v>838</v>
+        <v>841</v>
       </c>
       <c r="E71" s="5">
         <v>6</v>
       </c>
       <c r="F71" s="7" t="s">
-        <v>839</v>
+        <v>842</v>
       </c>
     </row>
     <row r="72" spans="1:6">
       <c r="A72" s="6" t="s">
-        <v>840</v>
+        <v>843</v>
       </c>
       <c r="B72" s="6" t="s">
-        <v>840</v>
+        <v>843</v>
       </c>
       <c r="C72" s="5" t="s">
-        <v>841</v>
+        <v>844</v>
       </c>
       <c r="D72" s="5" t="s">
-        <v>842</v>
+        <v>845</v>
       </c>
       <c r="E72" s="5">
         <v>15</v>
       </c>
       <c r="F72" s="7" t="s">
-        <v>843</v>
+        <v>846</v>
       </c>
     </row>
     <row r="75" spans="1:6">

--- a/Src/Assets/StreamingAssets/Common/Tables/Tables/Hero&Enemy.xlsx
+++ b/Src/Assets/StreamingAssets/Common/Tables/Tables/Hero&Enemy.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1278" uniqueCount="847">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1278" uniqueCount="848">
   <si>
     <t>Key</t>
   </si>
@@ -1298,6 +1298,9 @@
     <t>你的攻击造成伤害时，你回复等量生命值。</t>
   </si>
   <si>
+    <t>获得伤害*3算子</t>
+  </si>
+  <si>
     <t>Clone Technique</t>
   </si>
   <si>
@@ -1530,7 +1533,7 @@
     <t>["Sow", "LushGrowth", "Leader Catch"]</t>
   </si>
   <si>
-    <t>FormlessWater</t>
+    <t>IntangibleWater</t>
   </si>
   <si>
     <t>无形之水</t>
@@ -3434,6 +3437,14 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <u/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <i/>
       <sz val="11.25"/>
       <color rgb="FFFF0000"/>
@@ -3470,14 +3481,6 @@
       <sz val="11.25"/>
       <color rgb="FFF9FAFB"/>
       <name val="Segoe UI"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <u/>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="宋体"/>
       <charset val="134"/>
     </font>
   </fonts>
@@ -5824,7 +5827,7 @@
         <v>11</v>
       </c>
       <c r="H7" s="34">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" ht="65" spans="1:8">
@@ -7450,13 +7453,13 @@
         <v>22</v>
       </c>
       <c r="D70" s="32" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E70" s="32">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F70" s="33" t="s">
-        <v>23</v>
+        <v>303</v>
       </c>
       <c r="G70" s="32" t="s">
         <v>11</v>
@@ -7467,13 +7470,13 @@
     </row>
     <row r="71" ht="91" spans="1:8">
       <c r="A71" s="34" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B71" s="34" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C71" s="34" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="D71" s="34" t="b">
         <v>0</v>
@@ -7482,7 +7485,7 @@
         <v>0</v>
       </c>
       <c r="F71" s="35" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="G71" s="34" t="s">
         <v>11</v>
@@ -7493,13 +7496,13 @@
     </row>
     <row r="72" ht="39" spans="1:8">
       <c r="A72" s="32" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B72" s="32" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="C72" s="32" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="D72" s="32" t="b">
         <v>0</v>
@@ -7508,7 +7511,7 @@
         <v>0</v>
       </c>
       <c r="F72" s="33" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="G72" s="32" t="s">
         <v>11</v>
@@ -7519,13 +7522,13 @@
     </row>
     <row r="73" spans="1:8">
       <c r="A73" s="34" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B73" s="34" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C73" s="34" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="D73" s="34" t="b">
         <v>0</v>
@@ -7534,7 +7537,7 @@
         <v>0</v>
       </c>
       <c r="F73" s="35" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="G73" s="34" t="s">
         <v>11</v>
@@ -7545,13 +7548,13 @@
     </row>
     <row r="74" ht="17" spans="1:8">
       <c r="A74" s="32" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B74" s="32" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C74" s="32" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="D74" s="32" t="b">
         <v>0</v>
@@ -7560,7 +7563,7 @@
         <v>0</v>
       </c>
       <c r="F74" s="33" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="G74" s="32" t="s">
         <v>11</v>
@@ -7571,13 +7574,13 @@
     </row>
     <row r="75" spans="1:8">
       <c r="A75" s="34" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B75" s="34" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C75" s="34" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="D75" s="34" t="b">
         <v>0</v>
@@ -7586,7 +7589,7 @@
         <v>0</v>
       </c>
       <c r="F75" s="35" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="G75" s="34" t="s">
         <v>11</v>
@@ -7597,10 +7600,10 @@
     </row>
     <row r="76" spans="1:8">
       <c r="A76" s="32" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B76" s="32" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="C76" s="32" t="s">
         <v>25</v>
@@ -7623,13 +7626,13 @@
     </row>
     <row r="77" ht="26" spans="1:8">
       <c r="A77" s="34" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B77" s="34" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C77" s="34" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="D77" s="34" t="b">
         <v>0</v>
@@ -7638,7 +7641,7 @@
         <v>0</v>
       </c>
       <c r="F77" s="35" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="G77" s="34" t="s">
         <v>11</v>
@@ -7649,13 +7652,13 @@
     </row>
     <row r="78" ht="26" spans="1:8">
       <c r="A78" s="32" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B78" s="32" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="C78" s="32" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="D78" s="32" t="b">
         <v>0</v>
@@ -7664,7 +7667,7 @@
         <v>0</v>
       </c>
       <c r="F78" s="33" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="G78" s="32" t="s">
         <v>11</v>
@@ -7675,13 +7678,13 @@
     </row>
     <row r="79" ht="65" spans="1:8">
       <c r="A79" s="34" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B79" s="34" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C79" s="34" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="D79" s="34" t="b">
         <v>0</v>
@@ -7690,7 +7693,7 @@
         <v>0</v>
       </c>
       <c r="F79" s="35" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="G79" s="34" t="s">
         <v>11</v>
@@ -7701,13 +7704,13 @@
     </row>
     <row r="80" ht="26" spans="1:8">
       <c r="A80" s="32" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B80" s="32" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C80" s="32" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="D80" s="32" t="b">
         <v>0</v>
@@ -7716,7 +7719,7 @@
         <v>0</v>
       </c>
       <c r="F80" s="33" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="G80" s="32" t="s">
         <v>11</v>
@@ -7727,13 +7730,13 @@
     </row>
     <row r="81" ht="26" spans="1:8">
       <c r="A81" s="34" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B81" s="34" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C81" s="34" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="D81" s="34" t="b">
         <v>0</v>
@@ -7742,7 +7745,7 @@
         <v>0</v>
       </c>
       <c r="F81" s="35" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="G81" s="34" t="s">
         <v>11</v>
@@ -7753,13 +7756,13 @@
     </row>
     <row r="82" ht="26" spans="1:8">
       <c r="A82" s="32" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B82" s="32" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="C82" s="32" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="D82" s="32" t="b">
         <v>0</v>
@@ -7768,7 +7771,7 @@
         <v>0</v>
       </c>
       <c r="F82" s="33" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="G82" s="32" t="s">
         <v>11</v>
@@ -7779,13 +7782,13 @@
     </row>
     <row r="83" spans="1:8">
       <c r="A83" s="34" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B83" s="34" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="C83" s="34" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="D83" s="34" t="b">
         <v>0</v>
@@ -7805,13 +7808,13 @@
     </row>
     <row r="84" spans="1:8">
       <c r="A84" s="32" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B84" s="32" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="C84" s="32" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="D84" s="32" t="b">
         <v>0</v>
@@ -7820,7 +7823,7 @@
         <v>0</v>
       </c>
       <c r="F84" s="33" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="G84" s="32" t="s">
         <v>11</v>
@@ -7857,13 +7860,13 @@
     </row>
     <row r="86" ht="65" spans="1:8">
       <c r="A86" s="32" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B86" s="32" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="C86" s="32" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="D86" s="32" t="b">
         <v>0</v>
@@ -7872,7 +7875,7 @@
         <v>0</v>
       </c>
       <c r="F86" s="33" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="G86" s="32" t="s">
         <v>11</v>
@@ -7883,13 +7886,13 @@
     </row>
     <row r="87" ht="44" customHeight="1" spans="1:8">
       <c r="A87" s="34" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B87" s="34" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="C87" s="34" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="D87" s="34" t="b">
         <v>1</v>
@@ -7898,7 +7901,7 @@
         <v>1</v>
       </c>
       <c r="F87" s="35" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="G87" s="34" t="s">
         <v>11</v>
@@ -7944,1255 +7947,1255 @@
         <v>5</v>
       </c>
       <c r="E1" s="12" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="F1" s="13" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="G1" s="13" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="14" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B2" s="15" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C2" s="16" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="D2" s="16" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="E2" s="16">
         <v>40</v>
       </c>
       <c r="F2" s="17" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="G2" s="17" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3" s="18" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B3" s="19" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="C3" s="20" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="D3" s="20" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="E3" s="20">
         <v>8</v>
       </c>
       <c r="F3" s="21" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="G3" s="21" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4" s="14" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B4" s="15" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="C4" s="16" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="D4" s="16" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="E4" s="16">
         <v>30</v>
       </c>
       <c r="F4" s="17" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="G4" s="17" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5" s="18" t="s">
-        <v>365</v>
-      </c>
-      <c r="B5" s="19" t="s">
-        <v>365</v>
+        <v>366</v>
+      </c>
+      <c r="B5" s="18" t="s">
+        <v>366</v>
       </c>
       <c r="C5" s="20" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="D5" s="20" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="E5" s="20">
         <v>10</v>
       </c>
       <c r="F5" s="21" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="G5" s="21" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6" s="14" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B6" s="15" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="C6" s="16" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="D6" s="16" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="E6" s="16">
         <v>25</v>
       </c>
       <c r="F6" s="17" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="G6" s="17" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7" s="18" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B7" s="19" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C7" s="20" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="D7" s="20" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="E7" s="20">
         <v>35</v>
       </c>
       <c r="F7" s="21" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="G7" s="21" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8" s="22" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="B8" s="23" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="C8" s="24" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="D8" s="24" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="E8" s="24">
         <v>50</v>
       </c>
       <c r="F8" s="25" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="G8" s="25" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9" s="26" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B9" s="27" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="C9" s="28" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="D9" s="28" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="E9" s="28">
         <v>55</v>
       </c>
       <c r="F9" s="29" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="G9" s="29" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="10" ht="17" spans="1:7">
       <c r="A10" s="22" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="B10" s="23" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="C10" s="24" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="D10" s="24" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="E10" s="24">
         <v>35</v>
       </c>
       <c r="F10" s="25" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="G10" s="25" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11" s="26" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="B11" s="27" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="C11" s="28" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="D11" s="28" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="E11" s="28">
         <v>30</v>
       </c>
       <c r="F11" s="29" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="G11" s="29" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12" s="22" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="B12" s="23" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="C12" s="24" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="D12" s="24" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="E12" s="24">
         <v>40</v>
       </c>
       <c r="F12" s="25" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="G12" s="25" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13" s="26" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B13" s="27" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="C13" s="28" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="D13" s="28" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="E13" s="28">
         <v>4</v>
       </c>
       <c r="F13" s="29" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="G13" s="29" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14" s="22" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="B14" s="23" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="C14" s="24" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="D14" s="24" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="E14" s="24">
         <v>30</v>
       </c>
       <c r="F14" s="25" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="G14" s="25" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15" s="26" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B15" s="27" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C15" s="28" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="D15" s="28" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="E15" s="28">
         <v>70</v>
       </c>
       <c r="F15" s="29" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="G15" s="29" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="16" spans="1:7">
       <c r="A16" s="22" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B16" s="23" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="C16" s="24" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="D16" s="24" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="E16" s="24">
         <v>60</v>
       </c>
       <c r="F16" s="25" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="G16" s="25" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="17" spans="1:7">
       <c r="A17" s="26" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="B17" s="27" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="C17" s="28" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="D17" s="28" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="E17" s="28">
         <v>30</v>
       </c>
       <c r="F17" s="29" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="G17" s="29" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="18" spans="1:7">
       <c r="A18" s="22" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="B18" s="23" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="C18" s="24" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="D18" s="24" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="E18" s="24">
         <v>30</v>
       </c>
       <c r="F18" s="25" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="G18" s="25" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="19" spans="1:7">
       <c r="A19" s="26" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B19" s="27" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="C19" s="28" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="D19" s="28" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="E19" s="28">
         <v>30</v>
       </c>
       <c r="F19" s="29" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="G19" s="29" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="20" ht="17" spans="1:7">
       <c r="A20" s="22" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="B20" s="23" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="C20" s="24" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="D20" s="24" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="E20" s="24">
         <v>20</v>
       </c>
       <c r="F20" s="25" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="G20" s="25" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="21" spans="1:7">
       <c r="A21" s="26" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="B21" s="27" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="C21" s="28" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="D21" s="28" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="E21" s="28">
         <v>100</v>
       </c>
       <c r="F21" s="29" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="G21" s="29" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="22" spans="1:7">
       <c r="A22" s="22" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="B22" s="23" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="C22" s="24" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="D22" s="24" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="E22" s="24">
         <v>10</v>
       </c>
       <c r="F22" s="25" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="G22" s="25" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="23" spans="1:7">
       <c r="A23" s="26" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="B23" s="27" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="C23" s="28" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="D23" s="28" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="E23" s="28">
         <v>20</v>
       </c>
       <c r="F23" s="29" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="G23" s="29" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="24" spans="1:7">
       <c r="A24" s="22" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="B24" s="23" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="C24" s="24" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="D24" s="24" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="E24" s="24">
         <v>20</v>
       </c>
       <c r="F24" s="25" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="G24" s="25" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="25" spans="1:7">
       <c r="A25" s="26" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="B25" s="27" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="C25" s="28" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="D25" s="28" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="E25" s="28">
         <v>35</v>
       </c>
       <c r="F25" s="29" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="G25" s="29" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="26" spans="1:7">
       <c r="A26" s="22" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B26" s="23" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="C26" s="24" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="D26" s="24" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="E26" s="24">
         <v>50</v>
       </c>
       <c r="F26" s="25" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="G26" s="25" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="27" spans="1:7">
       <c r="A27" s="26" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="B27" s="27" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="C27" s="28" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="D27" s="28" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="E27" s="28">
         <v>20</v>
       </c>
       <c r="F27" s="29" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="G27" s="29" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="28" spans="1:7">
       <c r="A28" s="22" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B28" s="23" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="C28" s="24" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="D28" s="24" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="E28" s="24">
         <v>5</v>
       </c>
       <c r="F28" s="25" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="G28" s="25" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="29" spans="1:7">
       <c r="A29" s="26" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="B29" s="27" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="C29" s="28" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="D29" s="28" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="E29" s="28">
         <v>20</v>
       </c>
       <c r="F29" s="29" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="G29" s="29" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="30" spans="1:7">
       <c r="A30" s="22" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="B30" s="23" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="C30" s="24" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="D30" s="24" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="E30" s="24">
         <v>15</v>
       </c>
       <c r="F30" s="25" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="G30" s="25" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="31" spans="1:7">
       <c r="A31" s="26" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="B31" s="27" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="C31" s="28" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="D31" s="28" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="E31" s="28">
         <v>15</v>
       </c>
       <c r="F31" s="29" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="G31" s="29" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="32" ht="17" spans="1:7">
       <c r="A32" s="22" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B32" s="23" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="C32" s="24" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="D32" s="24" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="E32" s="24">
         <v>15</v>
       </c>
       <c r="F32" s="25" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="G32" s="25" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="33" spans="1:7">
       <c r="A33" s="26" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="B33" s="27" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="C33" s="28" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="D33" s="28" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="E33" s="28">
         <v>5</v>
       </c>
       <c r="F33" s="29" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="G33" s="29" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="34" spans="1:7">
       <c r="A34" s="22" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B34" s="23" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="C34" s="24" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="D34" s="24" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="E34" s="24">
         <v>25</v>
       </c>
       <c r="F34" s="25" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="G34" s="25" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="35" spans="1:7">
       <c r="A35" s="26" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="B35" s="27" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="C35" s="28" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="D35" s="28" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="E35" s="28">
         <v>10</v>
       </c>
       <c r="F35" s="29" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="G35" s="29" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="36" spans="1:7">
       <c r="A36" s="22" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="B36" s="23" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="C36" s="24" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="D36" s="24" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="E36" s="24">
         <v>8</v>
       </c>
       <c r="F36" s="25" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="G36" s="25" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="37" spans="1:7">
       <c r="A37" s="26" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="B37" s="27" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="C37" s="28" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="D37" s="28" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="E37" s="28">
         <v>100</v>
       </c>
       <c r="F37" s="29" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="G37" s="29" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="38" spans="1:7">
       <c r="A38" s="22" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="B38" s="23" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="C38" s="24" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="D38" s="24" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="E38" s="24">
         <v>20</v>
       </c>
       <c r="F38" s="25" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="G38" s="25" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="39" ht="17" spans="1:7">
       <c r="A39" s="18" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="B39" s="19" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="C39" s="20" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="D39" s="20" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="E39" s="20">
         <v>10</v>
       </c>
       <c r="F39" s="21" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="G39" s="21" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="40" spans="1:7">
       <c r="A40" s="14" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="B40" s="15" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="C40" s="16" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="D40" s="16" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="E40" s="16">
         <v>10</v>
       </c>
       <c r="F40" s="17" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="G40" s="17" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="41" spans="1:7">
       <c r="A41" s="18" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="B41" s="19" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="C41" s="20" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="D41" s="20" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="E41" s="20">
         <v>12</v>
       </c>
       <c r="F41" s="21" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="G41" s="21" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="42" ht="17" spans="1:7">
       <c r="A42" s="14" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="B42" s="15" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="C42" s="16" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="D42" s="16" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="E42" s="16">
         <v>15</v>
       </c>
       <c r="F42" s="17" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="G42" s="17" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="43" spans="1:7">
       <c r="A43" s="18" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="B43" s="19" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="C43" s="20" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="D43" s="20" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="E43" s="20">
         <v>25</v>
       </c>
       <c r="F43" s="21" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="G43" s="21" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="44" spans="1:7">
       <c r="A44" s="14" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="B44" s="15" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="C44" s="16" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="D44" s="16" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="E44" s="16">
         <v>3</v>
       </c>
       <c r="F44" s="17" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="G44" s="17" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="45" spans="1:7">
       <c r="A45" s="18" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="B45" s="19" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="C45" s="20" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="D45" s="20" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="E45" s="20">
         <v>2</v>
       </c>
       <c r="F45" s="21" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="G45" s="21" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="46" spans="1:7">
       <c r="A46" s="14" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="B46" s="15" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="C46" s="16" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="D46" s="16" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="E46" s="16">
         <v>6</v>
       </c>
       <c r="F46" s="17" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="G46" s="17" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="47" spans="1:7">
       <c r="A47" s="18" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="B47" s="19" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="C47" s="20" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="D47" s="20" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="E47" s="20">
         <v>4</v>
       </c>
       <c r="F47" s="21" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="G47" s="21" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="48" spans="1:7">
       <c r="A48" s="14" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="B48" s="15" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="C48" s="16" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="D48" s="16" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="E48" s="16">
         <v>3</v>
       </c>
       <c r="F48" s="17" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="G48" s="17" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="49" spans="1:7">
       <c r="A49" s="18" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="B49" s="19" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="C49" s="20" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="D49" s="20" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="E49" s="20">
         <v>4</v>
       </c>
       <c r="F49" s="21" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="G49" s="21" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="50" spans="1:7">
       <c r="A50" s="14" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="B50" s="15" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="C50" s="16" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="D50" s="16" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="E50" s="16">
         <v>4</v>
       </c>
       <c r="F50" s="17" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="G50" s="17" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="51" spans="1:7">
       <c r="A51" s="18" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="B51" s="19" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="C51" s="20" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="D51" s="20" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="E51" s="20">
         <v>6</v>
       </c>
       <c r="F51" s="21" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="G51" s="21" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="52" spans="1:7">
       <c r="A52" s="14" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="B52" s="15" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="C52" s="16" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="D52" s="16" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="E52" s="16">
         <v>2</v>
       </c>
       <c r="F52" s="17" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="G52" s="17" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="53" spans="1:7">
       <c r="A53" s="18" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="B53" s="19" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="C53" s="20" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="D53" s="20" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="E53" s="20">
         <v>2</v>
       </c>
       <c r="F53" s="21" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="G53" s="21" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="54" spans="1:7">
       <c r="A54" s="14" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="B54" s="15" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="C54" s="16" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="D54" s="16" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="E54" s="16">
         <v>4</v>
       </c>
       <c r="F54" s="17" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="G54" s="17" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="55" spans="1:7">
       <c r="A55" s="18" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="B55" s="19" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="C55" s="20" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="D55" s="20" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="E55" s="20">
         <v>3</v>
       </c>
       <c r="F55" s="21" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="G55" s="21" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
   </sheetData>
@@ -9231,1424 +9234,1424 @@
         <v>5</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="2" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="D2" s="4"/>
       <c r="E2" s="5">
         <v>25</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="6" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="E3" s="5">
         <v>12</v>
       </c>
       <c r="F3" s="7" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="8" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="D4" s="4"/>
       <c r="E4" s="5">
         <v>20</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="6" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="D5" s="4"/>
       <c r="E5" s="5">
         <v>40</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="6" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="E6" s="5">
         <v>20</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="6" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="E7" s="5">
         <v>15</v>
       </c>
       <c r="F7" s="7" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="6" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="E8" s="5">
         <v>40</v>
       </c>
       <c r="F8" s="7" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="6" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="E9" s="5">
         <v>15</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="6" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="E10" s="5">
         <v>15</v>
       </c>
       <c r="F10" s="7" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="6" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="E11" s="5">
         <v>30</v>
       </c>
       <c r="F11" s="7" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="6" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="E12" s="5">
         <v>15</v>
       </c>
       <c r="F12" s="7" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="6" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="E13" s="5">
         <v>15</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="6" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="E14" s="5">
         <v>20</v>
       </c>
       <c r="F14" s="7" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="6" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="E15" s="5">
         <v>20</v>
       </c>
       <c r="F15" s="7" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="6" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="E16" s="5">
         <v>15</v>
       </c>
       <c r="F16" s="7" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
     </row>
     <row r="17" spans="1:6">
       <c r="A17" s="6" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="E17" s="5">
         <v>20</v>
       </c>
       <c r="F17" s="7" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
     </row>
     <row r="18" spans="1:6">
       <c r="A18" s="6" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="E18" s="5">
         <v>12</v>
       </c>
       <c r="F18" s="7" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
     </row>
     <row r="19" spans="1:6">
       <c r="A19" s="6" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="E19" s="5">
         <v>15</v>
       </c>
       <c r="F19" s="7" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
     </row>
     <row r="20" spans="1:6">
       <c r="A20" s="6" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="E20" s="5">
         <v>12</v>
       </c>
       <c r="F20" s="7" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
     </row>
     <row r="21" spans="1:6">
       <c r="A21" s="6" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="E21" s="5">
         <v>20</v>
       </c>
       <c r="F21" s="7" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
     </row>
     <row r="22" spans="1:6">
       <c r="A22" s="6" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="E22" s="5">
         <v>15</v>
       </c>
       <c r="F22" s="7" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
     </row>
     <row r="23" spans="1:6">
       <c r="A23" s="6" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="E23" s="5">
         <v>15</v>
       </c>
       <c r="F23" s="7" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
     </row>
     <row r="24" spans="1:6">
       <c r="A24" s="6" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="E24" s="5">
         <v>15</v>
       </c>
       <c r="F24" s="7" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
     </row>
     <row r="25" spans="1:6">
       <c r="A25" s="6" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="E25" s="5">
         <v>15</v>
       </c>
       <c r="F25" s="7" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
     </row>
     <row r="26" spans="1:6">
       <c r="A26" s="6" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="E26" s="5">
         <v>15</v>
       </c>
       <c r="F26" s="7" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
     </row>
     <row r="27" spans="1:6">
       <c r="A27" s="6" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="E27" s="5">
         <v>15</v>
       </c>
       <c r="F27" s="7" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
     </row>
     <row r="28" spans="1:6">
       <c r="A28" s="6" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="E28" s="5">
         <v>3</v>
       </c>
       <c r="F28" s="7" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
     </row>
     <row r="29" spans="1:6">
       <c r="A29" s="6" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="E29" s="5">
         <v>18</v>
       </c>
       <c r="F29" s="7" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
     </row>
     <row r="30" spans="1:6">
       <c r="A30" s="6" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="D30" s="5" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="E30" s="5">
         <v>15</v>
       </c>
       <c r="F30" s="7" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
     </row>
     <row r="31" spans="1:6">
       <c r="A31" s="6" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="E31" s="5">
         <v>15</v>
       </c>
       <c r="F31" s="7" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
     </row>
     <row r="32" spans="1:6">
       <c r="A32" s="6" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="E32" s="5">
         <v>15</v>
       </c>
       <c r="F32" s="7" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
     </row>
     <row r="33" spans="1:6">
       <c r="A33" s="6" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="E33" s="5">
         <v>18</v>
       </c>
       <c r="F33" s="7" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
     </row>
     <row r="34" spans="1:6">
       <c r="A34" s="6" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="E34" s="5">
         <v>20</v>
       </c>
       <c r="F34" s="7" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
     </row>
     <row r="35" spans="1:6">
       <c r="A35" s="6" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="D35" s="5" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="E35" s="5">
         <v>15</v>
       </c>
       <c r="F35" s="7" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
     </row>
     <row r="36" spans="1:6">
       <c r="A36" s="6" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="D36" s="5" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="E36" s="5">
         <v>18</v>
       </c>
       <c r="F36" s="7" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
     </row>
     <row r="37" spans="1:6">
       <c r="A37" s="6" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="B37" s="6" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="D37" s="5" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="E37" s="5">
         <v>15</v>
       </c>
       <c r="F37" s="7" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
     </row>
     <row r="38" spans="1:6">
       <c r="A38" s="6" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="D38" s="5" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="E38" s="5">
         <v>15</v>
       </c>
       <c r="F38" s="7" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
     </row>
     <row r="39" spans="1:6">
       <c r="A39" s="6" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="B39" s="6" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="D39" s="5" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="E39" s="5">
         <v>15</v>
       </c>
       <c r="F39" s="7" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
     </row>
     <row r="40" spans="1:6">
       <c r="A40" s="6" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="B40" s="6" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="D40" s="5" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="E40" s="5">
         <v>15</v>
       </c>
       <c r="F40" s="7" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
     </row>
     <row r="41" spans="1:6">
       <c r="A41" s="6" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="B41" s="6" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="D41" s="5" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="E41" s="5">
         <v>15</v>
       </c>
       <c r="F41" s="7" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
     </row>
     <row r="42" spans="1:6">
       <c r="A42" s="6" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="B42" s="6" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="D42" s="5" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="E42" s="5">
         <v>15</v>
       </c>
       <c r="F42" s="7" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
     </row>
     <row r="43" spans="1:6">
       <c r="A43" s="6" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="B43" s="6" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="D43" s="5" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="E43" s="5">
         <v>18</v>
       </c>
       <c r="F43" s="7" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
     </row>
     <row r="44" spans="1:6">
       <c r="A44" s="6" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="B44" s="6" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="D44" s="5" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="E44" s="5">
         <v>15</v>
       </c>
       <c r="F44" s="7" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
     </row>
     <row r="45" spans="1:6">
       <c r="A45" s="6" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="B45" s="6" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="D45" s="5" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="E45" s="5">
         <v>10000000</v>
       </c>
       <c r="F45" s="7" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
     </row>
     <row r="46" spans="1:6">
       <c r="A46" s="6" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="B46" s="6" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="D46" s="5" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="E46" s="5">
         <v>15</v>
       </c>
       <c r="F46" s="7" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
     </row>
     <row r="47" spans="1:6">
       <c r="A47" s="6" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="B47" s="6" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="D47" s="5" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="E47" s="5">
         <v>15</v>
       </c>
       <c r="F47" s="7" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
     </row>
     <row r="48" spans="1:6">
       <c r="A48" s="6" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="B48" s="6" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="D48" s="5" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="E48" s="5">
         <v>12</v>
       </c>
       <c r="F48" s="7" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
     </row>
     <row r="49" spans="1:6">
       <c r="A49" s="6" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="B49" s="6" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="D49" s="5" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="E49" s="5">
         <v>15</v>
       </c>
       <c r="F49" s="7" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
     </row>
     <row r="50" spans="1:6">
       <c r="A50" s="6" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="B50" s="6" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="D50" s="5" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="E50" s="5">
         <v>40</v>
       </c>
       <c r="F50" s="7" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
     </row>
     <row r="51" spans="1:6">
       <c r="A51" s="6" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="B51" s="6" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="D51" s="5" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="E51" s="5">
         <v>50</v>
       </c>
       <c r="F51" s="7" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
     </row>
     <row r="52" spans="1:6">
       <c r="A52" s="6" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="B52" s="6" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="C52" s="5" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="D52" s="5" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="E52" s="5">
         <v>18</v>
       </c>
       <c r="F52" s="7" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
     </row>
     <row r="53" spans="1:6">
       <c r="A53" s="6" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="B53" s="6" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="C53" s="5" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="D53" s="5" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="E53" s="5">
         <v>15</v>
       </c>
       <c r="F53" s="7" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
     </row>
     <row r="54" spans="1:6">
       <c r="A54" s="6" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="B54" s="6" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="C54" s="5" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="D54" s="5" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="E54" s="5">
         <v>20</v>
       </c>
       <c r="F54" s="7" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
     </row>
     <row r="55" spans="1:6">
       <c r="A55" s="6" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="B55" s="6" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="C55" s="5" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="D55" s="5" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="E55" s="5">
         <v>12</v>
       </c>
       <c r="F55" s="7" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
     </row>
     <row r="56" spans="1:6">
       <c r="A56" s="6" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="B56" s="6" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="C56" s="5" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="D56" s="5" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="E56" s="5">
         <v>20</v>
       </c>
       <c r="F56" s="7" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
     </row>
     <row r="57" spans="1:6">
       <c r="A57" s="6" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="B57" s="6" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="C57" s="5" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="D57" s="5" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="E57" s="5">
         <v>20</v>
       </c>
       <c r="F57" s="7" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
     </row>
     <row r="58" spans="1:6">
       <c r="A58" s="6" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="B58" s="6" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="C58" s="5" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="D58" s="5" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="E58" s="5">
         <v>15</v>
       </c>
       <c r="F58" s="7" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
     </row>
     <row r="59" spans="1:6">
       <c r="A59" s="6" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="B59" s="6" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="C59" s="5" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="D59" s="5" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="E59" s="5">
         <v>15</v>
       </c>
       <c r="F59" s="7" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
     </row>
     <row r="60" spans="1:6">
       <c r="A60" s="6" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="B60" s="6" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="C60" s="5" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="D60" s="5" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="E60" s="5">
         <v>40</v>
       </c>
       <c r="F60" s="7" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
     </row>
     <row r="61" spans="1:6">
       <c r="A61" s="6" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="B61" s="6" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="C61" s="5" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="D61" s="5" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="E61" s="5">
         <v>15</v>
       </c>
       <c r="F61" s="7" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
     </row>
     <row r="62" spans="1:6">
       <c r="A62" s="6" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="B62" s="6" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="C62" s="5" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="D62" s="5" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="E62" s="5">
         <v>20</v>
       </c>
       <c r="F62" s="7" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
     </row>
     <row r="63" spans="1:6">
       <c r="A63" s="6" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="B63" s="6" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="C63" s="5" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="D63" s="5" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="E63" s="5">
         <v>20</v>
       </c>
       <c r="F63" s="7" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
     </row>
     <row r="64" ht="26" spans="1:6">
       <c r="A64" s="6" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="B64" s="6" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="C64" s="5" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="D64" s="5" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="E64" s="5">
         <v>15</v>
       </c>
       <c r="F64" s="7" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
     </row>
     <row r="65" spans="1:6">
       <c r="A65" s="6" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="B65" s="6" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="C65" s="5" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="D65" s="5" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="E65" s="5">
         <v>20</v>
       </c>
       <c r="F65" s="7" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
     </row>
     <row r="66" spans="1:6">
       <c r="A66" s="6" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="B66" s="6" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="C66" s="5" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="D66" s="5" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="E66" s="5">
         <v>6</v>
       </c>
       <c r="F66" s="7" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
     </row>
     <row r="67" spans="1:6">
       <c r="A67" s="6" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="B67" s="6" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="C67" s="5" t="s">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="D67" s="5" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="E67" s="5">
         <v>20</v>
       </c>
       <c r="F67" s="7" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
     </row>
     <row r="68" spans="1:6">
       <c r="A68" s="6" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="B68" s="6" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="C68" s="5" t="s">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="D68" s="5" t="s">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="E68" s="5">
         <v>18</v>
       </c>
       <c r="F68" s="7" t="s">
-        <v>830</v>
+        <v>831</v>
       </c>
     </row>
     <row r="69" spans="1:6">
       <c r="A69" s="6" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="B69" s="6" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="C69" s="5" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="D69" s="5" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="E69" s="5">
         <v>12</v>
       </c>
       <c r="F69" s="7" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
     </row>
     <row r="70" spans="1:6">
       <c r="A70" s="6" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="B70" s="6" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="C70" s="5" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="D70" s="5" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="E70" s="5">
         <v>18</v>
       </c>
       <c r="F70" s="7" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
     </row>
     <row r="71" spans="1:6">
       <c r="A71" s="6" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="B71" s="6" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="C71" s="5" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="D71" s="5" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="E71" s="5">
         <v>6</v>
       </c>
       <c r="F71" s="7" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
     </row>
     <row r="72" spans="1:6">
       <c r="A72" s="6" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="B72" s="6" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="C72" s="5" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="D72" s="5" t="s">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="E72" s="5">
         <v>15</v>
       </c>
       <c r="F72" s="7" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
     </row>
     <row r="75" spans="1:6">

--- a/Src/Assets/StreamingAssets/Common/Tables/Tables/Hero&Enemy.xlsx
+++ b/Src/Assets/StreamingAssets/Common/Tables/Tables/Hero&Enemy.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1278" uniqueCount="848">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1273" uniqueCount="848">
   <si>
     <t>Key</t>
   </si>
@@ -1307,7 +1307,7 @@
     <t>毫毛术</t>
   </si>
   <si>
-    <t>第三回合起每隔6个回合，你分裂为3个分身，血量不变且每个单位分得1/3资源（向上取整），并失去【千钧棒】。该状态持续3回合，复原时六耳猕猴获得分身的所有资源与分身血量之和的1/3血量（向下取整）。</t>
+    <t>第三回合起每隔6个回合，你分裂为3个分身，血量不变且每个单位分得1/3资源（向上取整），并失去【千钧棒】。该状态持续3回合，复原时六耳猕猴获得分身的所有资源与分身血量之和的1/3血量（向下取整）。（先不装）</t>
   </si>
   <si>
     <t>Venom</t>
@@ -1410,7 +1410,7 @@
     <t>不可侵犯</t>
   </si>
   <si>
-    <t>若场上的图腾被破坏，立刻进入高攻击欲望状态。</t>
+    <t>若场上的图腾被破坏，立刻进入高攻击欲望状态。（先不装）</t>
   </si>
   <si>
     <t>Ominous Feather</t>
@@ -1428,7 +1428,7 @@
     <t>无休</t>
   </si>
   <si>
-    <t>高攻击欲望，你的攻击命中时，返回此次攻击消耗的资源。</t>
+    <t>高攻击欲望（先不装），你的攻击命中时，返回此次攻击消耗的资源。</t>
   </si>
   <si>
     <t>Sturdy Shield</t>
@@ -1437,7 +1437,7 @@
     <t>坚盾</t>
   </si>
   <si>
-    <t>低攻击欲望，你的防御行为生效于全体友方。</t>
+    <t>低攻击欲望（先不装），你的防御行为生效于全体友方。</t>
   </si>
   <si>
     <t>Overconfidence</t>
@@ -1461,7 +1461,7 @@
     <t>哺育</t>
   </si>
   <si>
-    <t>你入场的第三回合，成长为狼。</t>
+    <t>你入场的第三回合，成长为狼（暂时不装）</t>
   </si>
   <si>
     <t>Wolf Grudge</t>
@@ -1470,7 +1470,7 @@
     <t>狼怨</t>
   </si>
   <si>
-    <t>受伤叠加一层复仇，造成伤害失去一点复仇，幼狼死亡获得三点复仇，其他狼死亡获得两点复仇。你每有一层复仇，伤害+1，有复仇时为高攻击欲望。</t>
+    <t>受伤叠加一层复仇，造成伤害失去一点复仇，幼狼死亡获得三点复仇，其他狼死亡获得两点复仇。你每有一层复仇，伤害+1，有复仇时为高攻击欲望。（暂时没有实装后半段）</t>
   </si>
   <si>
     <t>Leader Catch</t>
@@ -3437,14 +3437,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <u/>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <i/>
       <sz val="11.25"/>
       <color rgb="FFFF0000"/>
@@ -3467,6 +3459,14 @@
     <font>
       <sz val="11.25"/>
       <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <u/>
+      <sz val="10"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -5636,7 +5636,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H87"/>
+  <dimension ref="A1:H86"/>
   <sheetFormatPr defaultColWidth="8.25" defaultRowHeight="14" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="1" width="28.3166666666667" style="10" customWidth="1"/>
@@ -7442,7 +7442,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:8">
+    <row r="70" ht="31" customHeight="1" spans="1:8">
       <c r="A70" s="32" t="s">
         <v>21</v>
       </c>
@@ -7557,10 +7557,10 @@
         <v>314</v>
       </c>
       <c r="D74" s="32" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E74" s="32">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F74" s="33" t="s">
         <v>315</v>
@@ -7647,7 +7647,7 @@
         <v>11</v>
       </c>
       <c r="H77" s="34">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="78" ht="26" spans="1:8">
@@ -7702,7 +7702,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" ht="26" spans="1:8">
+    <row r="80" ht="39" spans="1:8">
       <c r="A80" s="32" t="s">
         <v>329</v>
       </c>
@@ -7777,7 +7777,7 @@
         <v>11</v>
       </c>
       <c r="H82" s="32">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="83" spans="1:8">
@@ -7806,7 +7806,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:8">
+    <row r="84" ht="26" spans="1:8">
       <c r="A84" s="32" t="s">
         <v>340</v>
       </c>
@@ -7817,10 +7817,10 @@
         <v>341</v>
       </c>
       <c r="D84" s="32" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E84" s="32">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F84" s="33" t="s">
         <v>342</v>
@@ -7829,84 +7829,58 @@
         <v>11</v>
       </c>
       <c r="H84" s="32">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="85" ht="26" spans="1:8">
-      <c r="A85" s="34" t="s">
-        <v>300</v>
-      </c>
-      <c r="B85" s="34" t="s">
-        <v>300</v>
-      </c>
-      <c r="C85" s="34" t="s">
-        <v>301</v>
-      </c>
-      <c r="D85" s="34" t="b">
-        <v>0</v>
-      </c>
-      <c r="E85" s="34">
-        <v>0</v>
-      </c>
-      <c r="F85" s="35" t="s">
-        <v>302</v>
-      </c>
-      <c r="G85" s="34" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="85" ht="78" spans="1:8">
+      <c r="A85" s="32" t="s">
+        <v>343</v>
+      </c>
+      <c r="B85" s="32" t="s">
+        <v>343</v>
+      </c>
+      <c r="C85" s="32" t="s">
+        <v>344</v>
+      </c>
+      <c r="D85" s="32" t="b">
+        <v>0</v>
+      </c>
+      <c r="E85" s="32">
+        <v>0</v>
+      </c>
+      <c r="F85" s="33" t="s">
+        <v>345</v>
+      </c>
+      <c r="G85" s="32" t="s">
         <v>11</v>
       </c>
-      <c r="H85" s="34">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="86" ht="65" spans="1:8">
-      <c r="A86" s="32" t="s">
-        <v>343</v>
-      </c>
-      <c r="B86" s="32" t="s">
-        <v>343</v>
-      </c>
-      <c r="C86" s="32" t="s">
-        <v>344</v>
-      </c>
-      <c r="D86" s="32" t="b">
-        <v>0</v>
-      </c>
-      <c r="E86" s="32">
-        <v>0</v>
-      </c>
-      <c r="F86" s="33" t="s">
-        <v>345</v>
-      </c>
-      <c r="G86" s="32" t="s">
+      <c r="H85" s="32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" ht="44" customHeight="1" spans="1:8">
+      <c r="A86" s="34" t="s">
+        <v>346</v>
+      </c>
+      <c r="B86" s="34" t="s">
+        <v>346</v>
+      </c>
+      <c r="C86" s="34" t="s">
+        <v>347</v>
+      </c>
+      <c r="D86" s="34" t="b">
+        <v>1</v>
+      </c>
+      <c r="E86" s="34">
+        <v>1</v>
+      </c>
+      <c r="F86" s="35" t="s">
+        <v>348</v>
+      </c>
+      <c r="G86" s="34" t="s">
         <v>11</v>
       </c>
-      <c r="H86" s="32">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="87" ht="44" customHeight="1" spans="1:8">
-      <c r="A87" s="34" t="s">
-        <v>346</v>
-      </c>
-      <c r="B87" s="34" t="s">
-        <v>346</v>
-      </c>
-      <c r="C87" s="34" t="s">
-        <v>347</v>
-      </c>
-      <c r="D87" s="34" t="b">
-        <v>1</v>
-      </c>
-      <c r="E87" s="34">
-        <v>1</v>
-      </c>
-      <c r="F87" s="35" t="s">
-        <v>348</v>
-      </c>
-      <c r="G87" s="34" t="s">
-        <v>11</v>
-      </c>
-      <c r="H87" s="34">
+      <c r="H86" s="34">
         <v>0</v>
       </c>
     </row>

--- a/Src/Assets/StreamingAssets/Common/Tables/Tables/Hero&Enemy.xlsx
+++ b/Src/Assets/StreamingAssets/Common/Tables/Tables/Hero&Enemy.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1273" uniqueCount="848">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1273" uniqueCount="849">
   <si>
     <t>Key</t>
   </si>
@@ -1296,6 +1296,9 @@
   </si>
   <si>
     <t>你的攻击造成伤害时，你回复等量生命值。</t>
+  </si>
+  <si>
+    <t>Mountain Crusher_Enemy</t>
   </si>
   <si>
     <t>获得伤害*3算子</t>
@@ -7444,10 +7447,10 @@
     </row>
     <row r="70" ht="31" customHeight="1" spans="1:8">
       <c r="A70" s="32" t="s">
-        <v>21</v>
+        <v>303</v>
       </c>
       <c r="B70" s="32" t="s">
-        <v>21</v>
+        <v>303</v>
       </c>
       <c r="C70" s="32" t="s">
         <v>22</v>
@@ -7459,7 +7462,7 @@
         <v>1</v>
       </c>
       <c r="F70" s="33" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="G70" s="32" t="s">
         <v>11</v>
@@ -7470,13 +7473,13 @@
     </row>
     <row r="71" ht="91" spans="1:8">
       <c r="A71" s="34" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B71" s="34" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="C71" s="34" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="D71" s="34" t="b">
         <v>0</v>
@@ -7485,7 +7488,7 @@
         <v>0</v>
       </c>
       <c r="F71" s="35" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="G71" s="34" t="s">
         <v>11</v>
@@ -7496,13 +7499,13 @@
     </row>
     <row r="72" ht="39" spans="1:8">
       <c r="A72" s="32" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B72" s="32" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C72" s="32" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="D72" s="32" t="b">
         <v>0</v>
@@ -7511,7 +7514,7 @@
         <v>0</v>
       </c>
       <c r="F72" s="33" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="G72" s="32" t="s">
         <v>11</v>
@@ -7522,13 +7525,13 @@
     </row>
     <row r="73" spans="1:8">
       <c r="A73" s="34" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B73" s="34" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="C73" s="34" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="D73" s="34" t="b">
         <v>0</v>
@@ -7537,7 +7540,7 @@
         <v>0</v>
       </c>
       <c r="F73" s="35" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="G73" s="34" t="s">
         <v>11</v>
@@ -7548,13 +7551,13 @@
     </row>
     <row r="74" ht="17" spans="1:8">
       <c r="A74" s="32" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B74" s="32" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C74" s="32" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="D74" s="32" t="b">
         <v>1</v>
@@ -7563,7 +7566,7 @@
         <v>1</v>
       </c>
       <c r="F74" s="33" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="G74" s="32" t="s">
         <v>11</v>
@@ -7574,13 +7577,13 @@
     </row>
     <row r="75" spans="1:8">
       <c r="A75" s="34" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B75" s="34" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C75" s="34" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="D75" s="34" t="b">
         <v>0</v>
@@ -7589,7 +7592,7 @@
         <v>0</v>
       </c>
       <c r="F75" s="35" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="G75" s="34" t="s">
         <v>11</v>
@@ -7600,10 +7603,10 @@
     </row>
     <row r="76" spans="1:8">
       <c r="A76" s="32" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B76" s="32" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C76" s="32" t="s">
         <v>25</v>
@@ -7626,13 +7629,13 @@
     </row>
     <row r="77" ht="26" spans="1:8">
       <c r="A77" s="34" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B77" s="34" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="C77" s="34" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="D77" s="34" t="b">
         <v>0</v>
@@ -7641,7 +7644,7 @@
         <v>0</v>
       </c>
       <c r="F77" s="35" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="G77" s="34" t="s">
         <v>11</v>
@@ -7652,13 +7655,13 @@
     </row>
     <row r="78" ht="26" spans="1:8">
       <c r="A78" s="32" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B78" s="32" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="C78" s="32" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="D78" s="32" t="b">
         <v>0</v>
@@ -7667,7 +7670,7 @@
         <v>0</v>
       </c>
       <c r="F78" s="33" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="G78" s="32" t="s">
         <v>11</v>
@@ -7678,13 +7681,13 @@
     </row>
     <row r="79" ht="65" spans="1:8">
       <c r="A79" s="34" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B79" s="34" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C79" s="34" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="D79" s="34" t="b">
         <v>0</v>
@@ -7693,7 +7696,7 @@
         <v>0</v>
       </c>
       <c r="F79" s="35" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="G79" s="34" t="s">
         <v>11</v>
@@ -7704,13 +7707,13 @@
     </row>
     <row r="80" ht="39" spans="1:8">
       <c r="A80" s="32" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B80" s="32" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="C80" s="32" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="D80" s="32" t="b">
         <v>0</v>
@@ -7719,7 +7722,7 @@
         <v>0</v>
       </c>
       <c r="F80" s="33" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="G80" s="32" t="s">
         <v>11</v>
@@ -7730,13 +7733,13 @@
     </row>
     <row r="81" ht="26" spans="1:8">
       <c r="A81" s="34" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B81" s="34" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C81" s="34" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="D81" s="34" t="b">
         <v>0</v>
@@ -7745,7 +7748,7 @@
         <v>0</v>
       </c>
       <c r="F81" s="35" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="G81" s="34" t="s">
         <v>11</v>
@@ -7756,13 +7759,13 @@
     </row>
     <row r="82" ht="26" spans="1:8">
       <c r="A82" s="32" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B82" s="32" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="C82" s="32" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="D82" s="32" t="b">
         <v>0</v>
@@ -7771,7 +7774,7 @@
         <v>0</v>
       </c>
       <c r="F82" s="33" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="G82" s="32" t="s">
         <v>11</v>
@@ -7782,13 +7785,13 @@
     </row>
     <row r="83" spans="1:8">
       <c r="A83" s="34" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B83" s="34" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="C83" s="34" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="D83" s="34" t="b">
         <v>0</v>
@@ -7808,13 +7811,13 @@
     </row>
     <row r="84" ht="26" spans="1:8">
       <c r="A84" s="32" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B84" s="32" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="C84" s="32" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="D84" s="32" t="b">
         <v>1</v>
@@ -7823,7 +7826,7 @@
         <v>1</v>
       </c>
       <c r="F84" s="33" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="G84" s="32" t="s">
         <v>11</v>
@@ -7834,13 +7837,13 @@
     </row>
     <row r="85" ht="78" spans="1:8">
       <c r="A85" s="32" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B85" s="32" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="C85" s="32" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="D85" s="32" t="b">
         <v>0</v>
@@ -7849,7 +7852,7 @@
         <v>0</v>
       </c>
       <c r="F85" s="33" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="G85" s="32" t="s">
         <v>11</v>
@@ -7860,13 +7863,13 @@
     </row>
     <row r="86" ht="44" customHeight="1" spans="1:8">
       <c r="A86" s="34" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B86" s="34" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="C86" s="34" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="D86" s="34" t="b">
         <v>1</v>
@@ -7875,7 +7878,7 @@
         <v>1</v>
       </c>
       <c r="F86" s="35" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="G86" s="34" t="s">
         <v>11</v>
@@ -7921,1255 +7924,1255 @@
         <v>5</v>
       </c>
       <c r="E1" s="12" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="F1" s="13" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="G1" s="13" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="14" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B2" s="15" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="C2" s="16" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="D2" s="16" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="E2" s="16">
         <v>40</v>
       </c>
       <c r="F2" s="17" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="G2" s="17" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3" s="18" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B3" s="19" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C3" s="20" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="D3" s="20" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="E3" s="20">
         <v>8</v>
       </c>
       <c r="F3" s="21" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="G3" s="21" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4" s="14" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B4" s="15" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="C4" s="16" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="D4" s="16" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="E4" s="16">
         <v>30</v>
       </c>
       <c r="F4" s="17" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="G4" s="17" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5" s="18" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B5" s="18" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="C5" s="20" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="D5" s="20" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="E5" s="20">
         <v>10</v>
       </c>
       <c r="F5" s="21" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="G5" s="21" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6" s="14" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B6" s="15" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C6" s="16" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="D6" s="16" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="E6" s="16">
         <v>25</v>
       </c>
       <c r="F6" s="17" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="G6" s="17" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7" s="18" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B7" s="19" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="C7" s="20" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D7" s="20" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="E7" s="20">
         <v>35</v>
       </c>
       <c r="F7" s="21" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="G7" s="21" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8" s="22" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B8" s="23" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="C8" s="24" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="D8" s="24" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="E8" s="24">
         <v>50</v>
       </c>
       <c r="F8" s="25" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="G8" s="25" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9" s="26" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B9" s="27" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C9" s="28" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="D9" s="28" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="E9" s="28">
         <v>55</v>
       </c>
       <c r="F9" s="29" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="G9" s="29" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="10" ht="17" spans="1:7">
       <c r="A10" s="22" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B10" s="23" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="C10" s="24" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="D10" s="24" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="E10" s="24">
         <v>35</v>
       </c>
       <c r="F10" s="25" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="G10" s="25" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11" s="26" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B11" s="27" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="C11" s="28" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="D11" s="28" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="E11" s="28">
         <v>30</v>
       </c>
       <c r="F11" s="29" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="G11" s="29" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12" s="22" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="B12" s="23" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="C12" s="24" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="D12" s="24" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="E12" s="24">
         <v>40</v>
       </c>
       <c r="F12" s="25" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="G12" s="25" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13" s="26" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B13" s="27" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="C13" s="28" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="D13" s="28" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="E13" s="28">
         <v>4</v>
       </c>
       <c r="F13" s="29" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="G13" s="29" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14" s="22" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="B14" s="23" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="C14" s="24" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="D14" s="24" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="E14" s="24">
         <v>30</v>
       </c>
       <c r="F14" s="25" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="G14" s="25" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15" s="26" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B15" s="27" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="C15" s="28" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="D15" s="28" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="E15" s="28">
         <v>70</v>
       </c>
       <c r="F15" s="29" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="G15" s="29" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="16" spans="1:7">
       <c r="A16" s="22" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="B16" s="23" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="C16" s="24" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="D16" s="24" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="E16" s="24">
         <v>60</v>
       </c>
       <c r="F16" s="25" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="G16" s="25" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="17" spans="1:7">
       <c r="A17" s="26" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="B17" s="27" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="C17" s="28" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="D17" s="28" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="E17" s="28">
         <v>30</v>
       </c>
       <c r="F17" s="29" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="G17" s="29" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="18" spans="1:7">
       <c r="A18" s="22" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="B18" s="23" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="C18" s="24" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="D18" s="24" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="E18" s="24">
         <v>30</v>
       </c>
       <c r="F18" s="25" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="G18" s="25" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="19" spans="1:7">
       <c r="A19" s="26" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B19" s="27" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="C19" s="28" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="D19" s="28" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="E19" s="28">
         <v>30</v>
       </c>
       <c r="F19" s="29" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="G19" s="29" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="20" ht="17" spans="1:7">
       <c r="A20" s="22" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="B20" s="23" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="C20" s="24" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="D20" s="24" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="E20" s="24">
         <v>20</v>
       </c>
       <c r="F20" s="25" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="G20" s="25" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="21" spans="1:7">
       <c r="A21" s="26" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="B21" s="27" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="C21" s="28" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="D21" s="28" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="E21" s="28">
         <v>100</v>
       </c>
       <c r="F21" s="29" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="G21" s="29" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="22" spans="1:7">
       <c r="A22" s="22" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="B22" s="23" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="C22" s="24" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="D22" s="24" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="E22" s="24">
         <v>10</v>
       </c>
       <c r="F22" s="25" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="G22" s="25" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
     <row r="23" spans="1:7">
       <c r="A23" s="26" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="B23" s="27" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="C23" s="28" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="D23" s="28" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="E23" s="28">
         <v>20</v>
       </c>
       <c r="F23" s="29" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="G23" s="29" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
     </row>
     <row r="24" spans="1:7">
       <c r="A24" s="22" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="B24" s="23" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="C24" s="24" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="D24" s="24" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="E24" s="24">
         <v>20</v>
       </c>
       <c r="F24" s="25" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="G24" s="25" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
     </row>
     <row r="25" spans="1:7">
       <c r="A25" s="26" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="B25" s="27" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="C25" s="28" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="D25" s="28" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="E25" s="28">
         <v>35</v>
       </c>
       <c r="F25" s="29" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="G25" s="29" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
     </row>
     <row r="26" spans="1:7">
       <c r="A26" s="22" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="B26" s="23" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="C26" s="24" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="D26" s="24" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="E26" s="24">
         <v>50</v>
       </c>
       <c r="F26" s="25" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="G26" s="25" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
     </row>
     <row r="27" spans="1:7">
       <c r="A27" s="26" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="B27" s="27" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="C27" s="28" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="D27" s="28" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="E27" s="28">
         <v>20</v>
       </c>
       <c r="F27" s="29" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="G27" s="29" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
     </row>
     <row r="28" spans="1:7">
       <c r="A28" s="22" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="B28" s="23" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="C28" s="24" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="D28" s="24" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E28" s="24">
         <v>5</v>
       </c>
       <c r="F28" s="25" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="G28" s="25" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
     <row r="29" spans="1:7">
       <c r="A29" s="26" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="B29" s="27" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="C29" s="28" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="D29" s="28" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="E29" s="28">
         <v>20</v>
       </c>
       <c r="F29" s="29" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="G29" s="29" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
     </row>
     <row r="30" spans="1:7">
       <c r="A30" s="22" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="B30" s="23" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="C30" s="24" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="D30" s="24" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="E30" s="24">
         <v>15</v>
       </c>
       <c r="F30" s="25" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="G30" s="25" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
     </row>
     <row r="31" spans="1:7">
       <c r="A31" s="26" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="B31" s="27" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="C31" s="28" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="D31" s="28" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="E31" s="28">
         <v>15</v>
       </c>
       <c r="F31" s="29" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="G31" s="29" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
     </row>
     <row r="32" ht="17" spans="1:7">
       <c r="A32" s="22" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="B32" s="23" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="C32" s="24" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="D32" s="24" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="E32" s="24">
         <v>15</v>
       </c>
       <c r="F32" s="25" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="G32" s="25" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
     </row>
     <row r="33" spans="1:7">
       <c r="A33" s="26" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="B33" s="27" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="C33" s="28" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="D33" s="28" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="E33" s="28">
         <v>5</v>
       </c>
       <c r="F33" s="29" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="G33" s="29" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
     </row>
     <row r="34" spans="1:7">
       <c r="A34" s="22" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="B34" s="23" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="C34" s="24" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="D34" s="24" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="E34" s="24">
         <v>25</v>
       </c>
       <c r="F34" s="25" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="G34" s="25" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
     </row>
     <row r="35" spans="1:7">
       <c r="A35" s="26" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="B35" s="27" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="C35" s="28" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="D35" s="28" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="E35" s="28">
         <v>10</v>
       </c>
       <c r="F35" s="29" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="G35" s="29" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
     </row>
     <row r="36" spans="1:7">
       <c r="A36" s="22" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="B36" s="23" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="C36" s="24" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="D36" s="24" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="E36" s="24">
         <v>8</v>
       </c>
       <c r="F36" s="25" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="G36" s="25" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
     <row r="37" spans="1:7">
       <c r="A37" s="26" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="B37" s="27" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="C37" s="28" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="D37" s="28" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="E37" s="28">
         <v>100</v>
       </c>
       <c r="F37" s="29" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="G37" s="29" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
     </row>
     <row r="38" spans="1:7">
       <c r="A38" s="22" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="B38" s="23" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="C38" s="24" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="D38" s="24" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="E38" s="24">
         <v>20</v>
       </c>
       <c r="F38" s="25" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="G38" s="25" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
     </row>
     <row r="39" ht="17" spans="1:7">
       <c r="A39" s="18" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="B39" s="19" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="C39" s="20" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="D39" s="20" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="E39" s="20">
         <v>10</v>
       </c>
       <c r="F39" s="21" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="G39" s="21" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
     </row>
     <row r="40" spans="1:7">
       <c r="A40" s="14" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="B40" s="15" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="C40" s="16" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="D40" s="16" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="E40" s="16">
         <v>10</v>
       </c>
       <c r="F40" s="17" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="G40" s="17" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
     </row>
     <row r="41" spans="1:7">
       <c r="A41" s="18" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="B41" s="19" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="C41" s="20" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="D41" s="20" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="E41" s="20">
         <v>12</v>
       </c>
       <c r="F41" s="21" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="G41" s="21" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
     </row>
     <row r="42" ht="17" spans="1:7">
       <c r="A42" s="14" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="B42" s="15" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="C42" s="16" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="D42" s="16" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="E42" s="16">
         <v>15</v>
       </c>
       <c r="F42" s="17" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="G42" s="17" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
     </row>
     <row r="43" spans="1:7">
       <c r="A43" s="18" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="B43" s="19" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="C43" s="20" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="D43" s="20" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="E43" s="20">
         <v>25</v>
       </c>
       <c r="F43" s="21" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="G43" s="21" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
     </row>
     <row r="44" spans="1:7">
       <c r="A44" s="14" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="B44" s="15" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="C44" s="16" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="D44" s="16" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="E44" s="16">
         <v>3</v>
       </c>
       <c r="F44" s="17" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="G44" s="17" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
     <row r="45" spans="1:7">
       <c r="A45" s="18" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="B45" s="19" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="C45" s="20" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="D45" s="20" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="E45" s="20">
         <v>2</v>
       </c>
       <c r="F45" s="21" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="G45" s="21" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
     <row r="46" spans="1:7">
       <c r="A46" s="14" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="B46" s="15" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="C46" s="16" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="D46" s="16" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="E46" s="16">
         <v>6</v>
       </c>
       <c r="F46" s="17" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="G46" s="17" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
     <row r="47" spans="1:7">
       <c r="A47" s="18" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="B47" s="19" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="C47" s="20" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="D47" s="20" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="E47" s="20">
         <v>4</v>
       </c>
       <c r="F47" s="21" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="G47" s="21" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
     <row r="48" spans="1:7">
       <c r="A48" s="14" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="B48" s="15" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="C48" s="16" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="D48" s="16" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="E48" s="16">
         <v>3</v>
       </c>
       <c r="F48" s="17" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="G48" s="17" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
     <row r="49" spans="1:7">
       <c r="A49" s="18" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="B49" s="19" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="C49" s="20" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="D49" s="20" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="E49" s="20">
         <v>4</v>
       </c>
       <c r="F49" s="21" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="G49" s="21" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
     <row r="50" spans="1:7">
       <c r="A50" s="14" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="B50" s="15" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="C50" s="16" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="D50" s="16" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="E50" s="16">
         <v>4</v>
       </c>
       <c r="F50" s="17" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="G50" s="17" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
     <row r="51" spans="1:7">
       <c r="A51" s="18" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="B51" s="19" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="C51" s="20" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="D51" s="20" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="E51" s="20">
         <v>6</v>
       </c>
       <c r="F51" s="21" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="G51" s="21" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
     <row r="52" spans="1:7">
       <c r="A52" s="14" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="B52" s="15" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="C52" s="16" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="D52" s="16" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="E52" s="16">
         <v>2</v>
       </c>
       <c r="F52" s="17" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="G52" s="17" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
     <row r="53" spans="1:7">
       <c r="A53" s="18" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="B53" s="19" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="C53" s="20" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="D53" s="20" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="E53" s="20">
         <v>2</v>
       </c>
       <c r="F53" s="21" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="G53" s="21" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
     <row r="54" spans="1:7">
       <c r="A54" s="14" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="B54" s="15" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="C54" s="16" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="D54" s="16" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="E54" s="16">
         <v>4</v>
       </c>
       <c r="F54" s="17" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="G54" s="17" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
     <row r="55" spans="1:7">
       <c r="A55" s="18" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="B55" s="19" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="C55" s="20" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="D55" s="20" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="E55" s="20">
         <v>3</v>
       </c>
       <c r="F55" s="21" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="G55" s="21" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
   </sheetData>
@@ -9208,1424 +9211,1424 @@
         <v>5</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="2" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="D2" s="4"/>
       <c r="E2" s="5">
         <v>25</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="6" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="E3" s="5">
         <v>12</v>
       </c>
       <c r="F3" s="7" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="8" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="D4" s="4"/>
       <c r="E4" s="5">
         <v>20</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="6" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="D5" s="4"/>
       <c r="E5" s="5">
         <v>40</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="6" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="E6" s="5">
         <v>20</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="6" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="E7" s="5">
         <v>15</v>
       </c>
       <c r="F7" s="7" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="6" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="E8" s="5">
         <v>40</v>
       </c>
       <c r="F8" s="7" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="6" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="E9" s="5">
         <v>15</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="6" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="E10" s="5">
         <v>15</v>
       </c>
       <c r="F10" s="7" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="6" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="E11" s="5">
         <v>30</v>
       </c>
       <c r="F11" s="7" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="6" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="E12" s="5">
         <v>15</v>
       </c>
       <c r="F12" s="7" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="6" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="E13" s="5">
         <v>15</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="6" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="E14" s="5">
         <v>20</v>
       </c>
       <c r="F14" s="7" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="6" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="E15" s="5">
         <v>20</v>
       </c>
       <c r="F15" s="7" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="6" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="E16" s="5">
         <v>15</v>
       </c>
       <c r="F16" s="7" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
     </row>
     <row r="17" spans="1:6">
       <c r="A17" s="6" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="E17" s="5">
         <v>20</v>
       </c>
       <c r="F17" s="7" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
     </row>
     <row r="18" spans="1:6">
       <c r="A18" s="6" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="E18" s="5">
         <v>12</v>
       </c>
       <c r="F18" s="7" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
     </row>
     <row r="19" spans="1:6">
       <c r="A19" s="6" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="E19" s="5">
         <v>15</v>
       </c>
       <c r="F19" s="7" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
     </row>
     <row r="20" spans="1:6">
       <c r="A20" s="6" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="E20" s="5">
         <v>12</v>
       </c>
       <c r="F20" s="7" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
     </row>
     <row r="21" spans="1:6">
       <c r="A21" s="6" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="E21" s="5">
         <v>20</v>
       </c>
       <c r="F21" s="7" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
     </row>
     <row r="22" spans="1:6">
       <c r="A22" s="6" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="E22" s="5">
         <v>15</v>
       </c>
       <c r="F22" s="7" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
     </row>
     <row r="23" spans="1:6">
       <c r="A23" s="6" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="E23" s="5">
         <v>15</v>
       </c>
       <c r="F23" s="7" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
     </row>
     <row r="24" spans="1:6">
       <c r="A24" s="6" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="E24" s="5">
         <v>15</v>
       </c>
       <c r="F24" s="7" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
     </row>
     <row r="25" spans="1:6">
       <c r="A25" s="6" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="E25" s="5">
         <v>15</v>
       </c>
       <c r="F25" s="7" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
     </row>
     <row r="26" spans="1:6">
       <c r="A26" s="6" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="E26" s="5">
         <v>15</v>
       </c>
       <c r="F26" s="7" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
     </row>
     <row r="27" spans="1:6">
       <c r="A27" s="6" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="E27" s="5">
         <v>15</v>
       </c>
       <c r="F27" s="7" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
     </row>
     <row r="28" spans="1:6">
       <c r="A28" s="6" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="E28" s="5">
         <v>3</v>
       </c>
       <c r="F28" s="7" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
     </row>
     <row r="29" spans="1:6">
       <c r="A29" s="6" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="E29" s="5">
         <v>18</v>
       </c>
       <c r="F29" s="7" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
     </row>
     <row r="30" spans="1:6">
       <c r="A30" s="6" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="D30" s="5" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="E30" s="5">
         <v>15</v>
       </c>
       <c r="F30" s="7" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
     </row>
     <row r="31" spans="1:6">
       <c r="A31" s="6" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="E31" s="5">
         <v>15</v>
       </c>
       <c r="F31" s="7" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
     </row>
     <row r="32" spans="1:6">
       <c r="A32" s="6" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="E32" s="5">
         <v>15</v>
       </c>
       <c r="F32" s="7" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
     </row>
     <row r="33" spans="1:6">
       <c r="A33" s="6" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="E33" s="5">
         <v>18</v>
       </c>
       <c r="F33" s="7" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
     </row>
     <row r="34" spans="1:6">
       <c r="A34" s="6" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="E34" s="5">
         <v>20</v>
       </c>
       <c r="F34" s="7" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
     </row>
     <row r="35" spans="1:6">
       <c r="A35" s="6" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="D35" s="5" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="E35" s="5">
         <v>15</v>
       </c>
       <c r="F35" s="7" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
     </row>
     <row r="36" spans="1:6">
       <c r="A36" s="6" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="D36" s="5" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="E36" s="5">
         <v>18</v>
       </c>
       <c r="F36" s="7" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
     </row>
     <row r="37" spans="1:6">
       <c r="A37" s="6" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="B37" s="6" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="D37" s="5" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="E37" s="5">
         <v>15</v>
       </c>
       <c r="F37" s="7" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
     </row>
     <row r="38" spans="1:6">
       <c r="A38" s="6" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="D38" s="5" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="E38" s="5">
         <v>15</v>
       </c>
       <c r="F38" s="7" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
     </row>
     <row r="39" spans="1:6">
       <c r="A39" s="6" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="B39" s="6" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="D39" s="5" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="E39" s="5">
         <v>15</v>
       </c>
       <c r="F39" s="7" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
     </row>
     <row r="40" spans="1:6">
       <c r="A40" s="6" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="B40" s="6" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="D40" s="5" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="E40" s="5">
         <v>15</v>
       </c>
       <c r="F40" s="7" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
     </row>
     <row r="41" spans="1:6">
       <c r="A41" s="6" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="B41" s="6" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="D41" s="5" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="E41" s="5">
         <v>15</v>
       </c>
       <c r="F41" s="7" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
     </row>
     <row r="42" spans="1:6">
       <c r="A42" s="6" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="B42" s="6" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="D42" s="5" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="E42" s="5">
         <v>15</v>
       </c>
       <c r="F42" s="7" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
     </row>
     <row r="43" spans="1:6">
       <c r="A43" s="6" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="B43" s="6" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="D43" s="5" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="E43" s="5">
         <v>18</v>
       </c>
       <c r="F43" s="7" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
     </row>
     <row r="44" spans="1:6">
       <c r="A44" s="6" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="B44" s="6" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="D44" s="5" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="E44" s="5">
         <v>15</v>
       </c>
       <c r="F44" s="7" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
     </row>
     <row r="45" spans="1:6">
       <c r="A45" s="6" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="B45" s="6" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="D45" s="5" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="E45" s="5">
         <v>10000000</v>
       </c>
       <c r="F45" s="7" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
     </row>
     <row r="46" spans="1:6">
       <c r="A46" s="6" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="B46" s="6" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="D46" s="5" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="E46" s="5">
         <v>15</v>
       </c>
       <c r="F46" s="7" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
     </row>
     <row r="47" spans="1:6">
       <c r="A47" s="6" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="B47" s="6" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="D47" s="5" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="E47" s="5">
         <v>15</v>
       </c>
       <c r="F47" s="7" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
     </row>
     <row r="48" spans="1:6">
       <c r="A48" s="6" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="B48" s="6" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="D48" s="5" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="E48" s="5">
         <v>12</v>
       </c>
       <c r="F48" s="7" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
     </row>
     <row r="49" spans="1:6">
       <c r="A49" s="6" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="B49" s="6" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="D49" s="5" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="E49" s="5">
         <v>15</v>
       </c>
       <c r="F49" s="7" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
     </row>
     <row r="50" spans="1:6">
       <c r="A50" s="6" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="B50" s="6" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="D50" s="5" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="E50" s="5">
         <v>40</v>
       </c>
       <c r="F50" s="7" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
     </row>
     <row r="51" spans="1:6">
       <c r="A51" s="6" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="B51" s="6" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="D51" s="5" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="E51" s="5">
         <v>50</v>
       </c>
       <c r="F51" s="7" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
     </row>
     <row r="52" spans="1:6">
       <c r="A52" s="6" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="B52" s="6" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="C52" s="5" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="D52" s="5" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="E52" s="5">
         <v>18</v>
       </c>
       <c r="F52" s="7" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
     </row>
     <row r="53" spans="1:6">
       <c r="A53" s="6" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="B53" s="6" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="C53" s="5" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="D53" s="5" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="E53" s="5">
         <v>15</v>
       </c>
       <c r="F53" s="7" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
     </row>
     <row r="54" spans="1:6">
       <c r="A54" s="6" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="B54" s="6" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="C54" s="5" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="D54" s="5" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="E54" s="5">
         <v>20</v>
       </c>
       <c r="F54" s="7" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
     </row>
     <row r="55" spans="1:6">
       <c r="A55" s="6" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="B55" s="6" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="C55" s="5" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="D55" s="5" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="E55" s="5">
         <v>12</v>
       </c>
       <c r="F55" s="7" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
     </row>
     <row r="56" spans="1:6">
       <c r="A56" s="6" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="B56" s="6" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="C56" s="5" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="D56" s="5" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="E56" s="5">
         <v>20</v>
       </c>
       <c r="F56" s="7" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
     </row>
     <row r="57" spans="1:6">
       <c r="A57" s="6" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="B57" s="6" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="C57" s="5" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="D57" s="5" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="E57" s="5">
         <v>20</v>
       </c>
       <c r="F57" s="7" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
     </row>
     <row r="58" spans="1:6">
       <c r="A58" s="6" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="B58" s="6" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="C58" s="5" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="D58" s="5" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="E58" s="5">
         <v>15</v>
       </c>
       <c r="F58" s="7" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
     </row>
     <row r="59" spans="1:6">
       <c r="A59" s="6" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="B59" s="6" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="C59" s="5" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="D59" s="5" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="E59" s="5">
         <v>15</v>
       </c>
       <c r="F59" s="7" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
     </row>
     <row r="60" spans="1:6">
       <c r="A60" s="6" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="B60" s="6" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="C60" s="5" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="D60" s="5" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="E60" s="5">
         <v>40</v>
       </c>
       <c r="F60" s="7" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
     </row>
     <row r="61" spans="1:6">
       <c r="A61" s="6" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="B61" s="6" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="C61" s="5" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="D61" s="5" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="E61" s="5">
         <v>15</v>
       </c>
       <c r="F61" s="7" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
     </row>
     <row r="62" spans="1:6">
       <c r="A62" s="6" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="B62" s="6" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="C62" s="5" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="D62" s="5" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="E62" s="5">
         <v>20</v>
       </c>
       <c r="F62" s="7" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
     </row>
     <row r="63" spans="1:6">
       <c r="A63" s="6" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="B63" s="6" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="C63" s="5" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="D63" s="5" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="E63" s="5">
         <v>20</v>
       </c>
       <c r="F63" s="7" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
     </row>
     <row r="64" ht="26" spans="1:6">
       <c r="A64" s="6" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="B64" s="6" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="C64" s="5" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="D64" s="5" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="E64" s="5">
         <v>15</v>
       </c>
       <c r="F64" s="7" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
     </row>
     <row r="65" spans="1:6">
       <c r="A65" s="6" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="B65" s="6" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="C65" s="5" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="D65" s="5" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="E65" s="5">
         <v>20</v>
       </c>
       <c r="F65" s="7" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
     </row>
     <row r="66" spans="1:6">
       <c r="A66" s="6" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="B66" s="6" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="C66" s="5" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="D66" s="5" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="E66" s="5">
         <v>6</v>
       </c>
       <c r="F66" s="7" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
     </row>
     <row r="67" spans="1:6">
       <c r="A67" s="6" t="s">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="B67" s="6" t="s">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="C67" s="5" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="D67" s="5" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="E67" s="5">
         <v>20</v>
       </c>
       <c r="F67" s="7" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
     </row>
     <row r="68" spans="1:6">
       <c r="A68" s="6" t="s">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="B68" s="6" t="s">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="C68" s="5" t="s">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="D68" s="5" t="s">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="E68" s="5">
         <v>18</v>
       </c>
       <c r="F68" s="7" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
     </row>
     <row r="69" spans="1:6">
       <c r="A69" s="6" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="B69" s="6" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="C69" s="5" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="D69" s="5" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="E69" s="5">
         <v>12</v>
       </c>
       <c r="F69" s="7" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
     </row>
     <row r="70" spans="1:6">
       <c r="A70" s="6" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="B70" s="6" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="C70" s="5" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="D70" s="5" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="E70" s="5">
         <v>18</v>
       </c>
       <c r="F70" s="7" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
     </row>
     <row r="71" spans="1:6">
       <c r="A71" s="6" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="B71" s="6" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="C71" s="5" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="D71" s="5" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="E71" s="5">
         <v>6</v>
       </c>
       <c r="F71" s="7" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
     </row>
     <row r="72" spans="1:6">
       <c r="A72" s="6" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="B72" s="6" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="C72" s="5" t="s">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="D72" s="5" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="E72" s="5">
         <v>15</v>
       </c>
       <c r="F72" s="7" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
     </row>
     <row r="75" spans="1:6">

--- a/Src/Assets/StreamingAssets/Common/Tables/Tables/Hero&Enemy.xlsx
+++ b/Src/Assets/StreamingAssets/Common/Tables/Tables/Hero&Enemy.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="25600" windowHeight="12080" activeTab="2"/>
+    <workbookView windowWidth="25600" windowHeight="12080" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="HeroSkill" sheetId="4" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1273" uniqueCount="849">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1278" uniqueCount="852">
   <si>
     <t>Key</t>
   </si>
@@ -1570,6 +1570,15 @@
   </si>
   <si>
     <t>["FertileBlessing", "ReturnToEarth"]</t>
+  </si>
+  <si>
+    <t>LittleTree</t>
+  </si>
+  <si>
+    <t>小树灵</t>
+  </si>
+  <si>
+    <t>["DailyGrowing"]</t>
   </si>
   <si>
     <t>PlagueIncarnation</t>
@@ -3440,6 +3449,27 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <u/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11.25"/>
+      <color rgb="FFF9FAFB"/>
+      <name val="Segoe UI"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11.25"/>
+      <color rgb="FFF9FAFB"/>
+      <name val="Segoe UI"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <i/>
       <sz val="11.25"/>
       <color rgb="FFFF0000"/>
@@ -3463,27 +3493,6 @@
       <sz val="11.25"/>
       <color rgb="FFFF0000"/>
       <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <u/>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11.25"/>
-      <color rgb="FFF9FAFB"/>
-      <name val="Segoe UI"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11.25"/>
-      <color rgb="FFF9FAFB"/>
-      <name val="Segoe UI"/>
       <charset val="134"/>
     </font>
   </fonts>
@@ -3705,7 +3714,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="26">
+  <borders count="28">
     <border>
       <left/>
       <right/>
@@ -3747,6 +3756,30 @@
       </top>
       <bottom style="thin">
         <color theme="4" tint="0.399975585192419"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FF9DC3E6"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF9DC3E6"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF9DC3E6"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF9DC3E6"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF9DC3E6"/>
       </bottom>
       <diagonal/>
     </border>
@@ -4044,7 +4077,7 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="18" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -4056,34 +4089,34 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="19" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="21" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="19" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="21" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="20" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="22" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="7" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="23" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="22" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="8" borderId="24" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="8" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="8" borderId="23" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="9" borderId="23" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="9" borderId="25" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="24" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="26" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="25" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="27" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -4170,7 +4203,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="58">
+  <cellXfs count="61">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -4235,6 +4268,15 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="176" fontId="6" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="176" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -4259,74 +4301,65 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="4" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="6" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="5" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="7" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="6" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="8" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="7" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="9" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="6" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="8" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="7" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="9" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="50" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="8" xfId="50" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="9" xfId="50" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="2" borderId="10" xfId="50" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="10" xfId="50" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="11" xfId="50" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="11" xfId="50" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="12" xfId="50" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="12" xfId="50" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="12" xfId="50" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="5" borderId="13" xfId="50" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="13" xfId="50" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="50" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="14" xfId="50" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="50" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="15" xfId="50" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="15" xfId="50" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="50" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="50" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="14" xfId="50" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -4334,13 +4367,22 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="15" xfId="50" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="15" xfId="50" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="16" xfId="50" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="16" xfId="50" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="17" xfId="50" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="18" xfId="50" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="18" xfId="50" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="17" xfId="50" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="19" xfId="50" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -4723,720 +4765,720 @@
   </cols>
   <sheetData>
     <row r="1" ht="14.75" spans="1:8">
-      <c r="A1" s="30" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="30" t="s">
+      <c r="A1" s="33" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="33" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="30" t="s">
+      <c r="C1" s="33" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="30" t="s">
+      <c r="D1" s="33" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="30" t="s">
+      <c r="E1" s="33" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="31" t="s">
+      <c r="F1" s="34" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="30" t="s">
+      <c r="G1" s="33" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="30" t="s">
+      <c r="H1" s="33" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="2" ht="26" spans="1:8">
-      <c r="A2" s="38" t="s">
+      <c r="A2" s="41" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="38" t="s">
+      <c r="B2" s="41" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="38" t="s">
+      <c r="C2" s="41" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="38" t="b">
-        <v>0</v>
-      </c>
-      <c r="E2" s="38">
-        <v>0</v>
-      </c>
-      <c r="F2" s="39" t="s">
+      <c r="D2" s="41" t="b">
+        <v>0</v>
+      </c>
+      <c r="E2" s="41">
+        <v>0</v>
+      </c>
+      <c r="F2" s="42" t="s">
         <v>10</v>
       </c>
-      <c r="G2" s="38" t="s">
+      <c r="G2" s="41" t="s">
         <v>11</v>
       </c>
-      <c r="H2" s="38">
+      <c r="H2" s="41">
         <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:8">
-      <c r="A3" s="36" t="s">
+      <c r="A3" s="39" t="s">
         <v>12</v>
       </c>
-      <c r="B3" s="36" t="s">
+      <c r="B3" s="39" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="36" t="s">
+      <c r="C3" s="39" t="s">
         <v>13</v>
       </c>
-      <c r="D3" s="36" t="b">
-        <v>0</v>
-      </c>
-      <c r="E3" s="36">
-        <v>0</v>
-      </c>
-      <c r="F3" s="37" t="s">
+      <c r="D3" s="39" t="b">
+        <v>0</v>
+      </c>
+      <c r="E3" s="39">
+        <v>0</v>
+      </c>
+      <c r="F3" s="40" t="s">
         <v>14</v>
       </c>
-      <c r="G3" s="36" t="s">
+      <c r="G3" s="39" t="s">
         <v>11</v>
       </c>
-      <c r="H3" s="36">
+      <c r="H3" s="39">
         <v>0</v>
       </c>
     </row>
     <row r="4" ht="26" spans="1:8">
-      <c r="A4" s="38" t="s">
+      <c r="A4" s="41" t="s">
         <v>15</v>
       </c>
-      <c r="B4" s="38" t="s">
+      <c r="B4" s="41" t="s">
         <v>15</v>
       </c>
-      <c r="C4" s="38" t="s">
+      <c r="C4" s="41" t="s">
         <v>16</v>
       </c>
-      <c r="D4" s="38" t="b">
-        <v>0</v>
-      </c>
-      <c r="E4" s="38">
-        <v>0</v>
-      </c>
-      <c r="F4" s="39" t="s">
+      <c r="D4" s="41" t="b">
+        <v>0</v>
+      </c>
+      <c r="E4" s="41">
+        <v>0</v>
+      </c>
+      <c r="F4" s="42" t="s">
         <v>17</v>
       </c>
-      <c r="G4" s="38" t="s">
+      <c r="G4" s="41" t="s">
         <v>11</v>
       </c>
-      <c r="H4" s="38">
+      <c r="H4" s="41">
         <v>0</v>
       </c>
     </row>
     <row r="5" ht="26" spans="1:8">
-      <c r="A5" s="36" t="s">
+      <c r="A5" s="39" t="s">
         <v>18</v>
       </c>
-      <c r="B5" s="36" t="s">
+      <c r="B5" s="39" t="s">
         <v>18</v>
       </c>
-      <c r="C5" s="36" t="s">
+      <c r="C5" s="39" t="s">
         <v>19</v>
       </c>
-      <c r="D5" s="36" t="b">
-        <v>0</v>
-      </c>
-      <c r="E5" s="36">
-        <v>0</v>
-      </c>
-      <c r="F5" s="37" t="s">
+      <c r="D5" s="39" t="b">
+        <v>0</v>
+      </c>
+      <c r="E5" s="39">
+        <v>0</v>
+      </c>
+      <c r="F5" s="40" t="s">
         <v>20</v>
       </c>
-      <c r="G5" s="36" t="s">
+      <c r="G5" s="39" t="s">
         <v>11</v>
       </c>
-      <c r="H5" s="36">
+      <c r="H5" s="39">
         <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:8">
-      <c r="A6" s="38" t="s">
+      <c r="A6" s="41" t="s">
         <v>21</v>
       </c>
-      <c r="B6" s="38" t="s">
+      <c r="B6" s="41" t="s">
         <v>21</v>
       </c>
-      <c r="C6" s="38" t="s">
+      <c r="C6" s="41" t="s">
         <v>22</v>
       </c>
-      <c r="D6" s="38" t="b">
-        <v>0</v>
-      </c>
-      <c r="E6" s="38">
-        <v>0</v>
-      </c>
-      <c r="F6" s="39" t="s">
+      <c r="D6" s="41" t="b">
+        <v>0</v>
+      </c>
+      <c r="E6" s="41">
+        <v>0</v>
+      </c>
+      <c r="F6" s="42" t="s">
         <v>23</v>
       </c>
-      <c r="G6" s="38" t="s">
+      <c r="G6" s="41" t="s">
         <v>11</v>
       </c>
-      <c r="H6" s="38">
+      <c r="H6" s="41">
         <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:8">
-      <c r="A7" s="36" t="s">
+      <c r="A7" s="39" t="s">
         <v>24</v>
       </c>
-      <c r="B7" s="36" t="s">
+      <c r="B7" s="39" t="s">
         <v>24</v>
       </c>
-      <c r="C7" s="36" t="s">
+      <c r="C7" s="39" t="s">
         <v>25</v>
       </c>
-      <c r="D7" s="36" t="b">
-        <v>0</v>
-      </c>
-      <c r="E7" s="36">
-        <v>0</v>
-      </c>
-      <c r="F7" s="37" t="s">
+      <c r="D7" s="39" t="b">
+        <v>0</v>
+      </c>
+      <c r="E7" s="39">
+        <v>0</v>
+      </c>
+      <c r="F7" s="40" t="s">
         <v>26</v>
       </c>
-      <c r="G7" s="36" t="s">
+      <c r="G7" s="39" t="s">
         <v>11</v>
       </c>
-      <c r="H7" s="36">
+      <c r="H7" s="39">
         <v>0</v>
       </c>
     </row>
     <row r="8" ht="39" spans="1:8">
-      <c r="A8" s="38" t="s">
+      <c r="A8" s="41" t="s">
         <v>27</v>
       </c>
-      <c r="B8" s="38" t="s">
+      <c r="B8" s="41" t="s">
         <v>27</v>
       </c>
-      <c r="C8" s="38" t="s">
+      <c r="C8" s="41" t="s">
         <v>28</v>
       </c>
-      <c r="D8" s="38" t="b">
-        <v>0</v>
-      </c>
-      <c r="E8" s="38">
-        <v>0</v>
-      </c>
-      <c r="F8" s="39" t="s">
+      <c r="D8" s="41" t="b">
+        <v>0</v>
+      </c>
+      <c r="E8" s="41">
+        <v>0</v>
+      </c>
+      <c r="F8" s="42" t="s">
         <v>29</v>
       </c>
-      <c r="G8" s="38" t="s">
+      <c r="G8" s="41" t="s">
         <v>30</v>
       </c>
-      <c r="H8" s="38">
+      <c r="H8" s="41">
         <v>0</v>
       </c>
     </row>
     <row r="9" ht="26" spans="1:8">
-      <c r="A9" s="36" t="s">
+      <c r="A9" s="39" t="s">
         <v>31</v>
       </c>
-      <c r="B9" s="36" t="s">
+      <c r="B9" s="39" t="s">
         <v>31</v>
       </c>
-      <c r="C9" s="36" t="s">
+      <c r="C9" s="39" t="s">
         <v>32</v>
       </c>
-      <c r="D9" s="36" t="b">
-        <v>0</v>
-      </c>
-      <c r="E9" s="36">
-        <v>0</v>
-      </c>
-      <c r="F9" s="37" t="s">
+      <c r="D9" s="39" t="b">
+        <v>0</v>
+      </c>
+      <c r="E9" s="39">
+        <v>0</v>
+      </c>
+      <c r="F9" s="40" t="s">
         <v>33</v>
       </c>
-      <c r="G9" s="36" t="s">
+      <c r="G9" s="39" t="s">
         <v>11</v>
       </c>
-      <c r="H9" s="36">
+      <c r="H9" s="39">
         <v>0</v>
       </c>
     </row>
     <row r="10" ht="78" spans="1:8">
-      <c r="A10" s="38" t="s">
+      <c r="A10" s="41" t="s">
         <v>34</v>
       </c>
-      <c r="B10" s="38" t="s">
+      <c r="B10" s="41" t="s">
         <v>34</v>
       </c>
-      <c r="C10" s="38" t="s">
+      <c r="C10" s="41" t="s">
         <v>35</v>
       </c>
-      <c r="D10" s="38" t="b">
-        <v>0</v>
-      </c>
-      <c r="E10" s="38">
-        <v>0</v>
-      </c>
-      <c r="F10" s="39" t="s">
+      <c r="D10" s="41" t="b">
+        <v>0</v>
+      </c>
+      <c r="E10" s="41">
+        <v>0</v>
+      </c>
+      <c r="F10" s="42" t="s">
         <v>36</v>
       </c>
-      <c r="G10" s="38" t="s">
+      <c r="G10" s="41" t="s">
         <v>37</v>
       </c>
-      <c r="H10" s="38">
+      <c r="H10" s="41">
         <v>0</v>
       </c>
     </row>
     <row r="11" ht="91" spans="1:8">
-      <c r="A11" s="36" t="s">
+      <c r="A11" s="39" t="s">
         <v>38</v>
       </c>
-      <c r="B11" s="36" t="s">
+      <c r="B11" s="39" t="s">
         <v>38</v>
       </c>
-      <c r="C11" s="36" t="s">
+      <c r="C11" s="39" t="s">
         <v>39</v>
       </c>
-      <c r="D11" s="36" t="b">
-        <v>0</v>
-      </c>
-      <c r="E11" s="36">
-        <v>0</v>
-      </c>
-      <c r="F11" s="37" t="s">
+      <c r="D11" s="39" t="b">
+        <v>0</v>
+      </c>
+      <c r="E11" s="39">
+        <v>0</v>
+      </c>
+      <c r="F11" s="40" t="s">
         <v>40</v>
       </c>
-      <c r="G11" s="36" t="s">
+      <c r="G11" s="39" t="s">
         <v>11</v>
       </c>
-      <c r="H11" s="36">
+      <c r="H11" s="39">
         <v>0</v>
       </c>
     </row>
     <row r="12" ht="117" spans="1:8">
-      <c r="A12" s="38" t="s">
+      <c r="A12" s="41" t="s">
         <v>41</v>
       </c>
-      <c r="B12" s="38" t="s">
+      <c r="B12" s="41" t="s">
         <v>41</v>
       </c>
-      <c r="C12" s="38" t="s">
+      <c r="C12" s="41" t="s">
         <v>42</v>
       </c>
-      <c r="D12" s="38" t="b">
-        <v>0</v>
-      </c>
-      <c r="E12" s="38">
-        <v>0</v>
-      </c>
-      <c r="F12" s="39" t="s">
+      <c r="D12" s="41" t="b">
+        <v>0</v>
+      </c>
+      <c r="E12" s="41">
+        <v>0</v>
+      </c>
+      <c r="F12" s="42" t="s">
         <v>43</v>
       </c>
-      <c r="G12" s="38" t="s">
+      <c r="G12" s="41" t="s">
         <v>11</v>
       </c>
-      <c r="H12" s="38">
+      <c r="H12" s="41">
         <v>0</v>
       </c>
     </row>
     <row r="13" ht="52" spans="1:8">
-      <c r="A13" s="36" t="s">
+      <c r="A13" s="39" t="s">
         <v>44</v>
       </c>
-      <c r="B13" s="36" t="s">
+      <c r="B13" s="39" t="s">
         <v>44</v>
       </c>
-      <c r="C13" s="36" t="s">
+      <c r="C13" s="39" t="s">
         <v>45</v>
       </c>
-      <c r="D13" s="36" t="b">
-        <v>0</v>
-      </c>
-      <c r="E13" s="36">
-        <v>0</v>
-      </c>
-      <c r="F13" s="37" t="s">
+      <c r="D13" s="39" t="b">
+        <v>0</v>
+      </c>
+      <c r="E13" s="39">
+        <v>0</v>
+      </c>
+      <c r="F13" s="40" t="s">
         <v>46</v>
       </c>
-      <c r="G13" s="36" t="s">
+      <c r="G13" s="39" t="s">
         <v>11</v>
       </c>
-      <c r="H13" s="36">
+      <c r="H13" s="39">
         <v>0</v>
       </c>
     </row>
     <row r="14" ht="39" spans="1:8">
-      <c r="A14" s="38" t="s">
+      <c r="A14" s="41" t="s">
         <v>47</v>
       </c>
-      <c r="B14" s="38" t="s">
+      <c r="B14" s="41" t="s">
         <v>47</v>
       </c>
-      <c r="C14" s="38" t="s">
+      <c r="C14" s="41" t="s">
         <v>48</v>
       </c>
-      <c r="D14" s="38" t="b">
+      <c r="D14" s="41" t="b">
         <v>1</v>
       </c>
-      <c r="E14" s="38">
+      <c r="E14" s="41">
         <v>1</v>
       </c>
-      <c r="F14" s="39" t="s">
+      <c r="F14" s="42" t="s">
         <v>49</v>
       </c>
-      <c r="G14" s="38" t="s">
+      <c r="G14" s="41" t="s">
         <v>50</v>
       </c>
-      <c r="H14" s="38">
+      <c r="H14" s="41">
         <v>0</v>
       </c>
     </row>
     <row r="15" ht="39" spans="1:8">
-      <c r="A15" s="36" t="s">
+      <c r="A15" s="39" t="s">
         <v>51</v>
       </c>
-      <c r="B15" s="36" t="s">
+      <c r="B15" s="39" t="s">
         <v>51</v>
       </c>
-      <c r="C15" s="36" t="s">
+      <c r="C15" s="39" t="s">
         <v>52</v>
       </c>
-      <c r="D15" s="36" t="b">
-        <v>0</v>
-      </c>
-      <c r="E15" s="36">
-        <v>0</v>
-      </c>
-      <c r="F15" s="37" t="s">
+      <c r="D15" s="39" t="b">
+        <v>0</v>
+      </c>
+      <c r="E15" s="39">
+        <v>0</v>
+      </c>
+      <c r="F15" s="40" t="s">
         <v>53</v>
       </c>
-      <c r="G15" s="36" t="s">
+      <c r="G15" s="39" t="s">
         <v>11</v>
       </c>
-      <c r="H15" s="36">
+      <c r="H15" s="39">
         <v>0</v>
       </c>
     </row>
     <row r="16" ht="26" spans="1:8">
-      <c r="A16" s="38" t="s">
+      <c r="A16" s="41" t="s">
         <v>54</v>
       </c>
-      <c r="B16" s="38" t="s">
+      <c r="B16" s="41" t="s">
         <v>54</v>
       </c>
-      <c r="C16" s="38" t="s">
+      <c r="C16" s="41" t="s">
         <v>55</v>
       </c>
-      <c r="D16" s="38" t="b">
-        <v>0</v>
-      </c>
-      <c r="E16" s="38">
-        <v>0</v>
-      </c>
-      <c r="F16" s="39" t="s">
+      <c r="D16" s="41" t="b">
+        <v>0</v>
+      </c>
+      <c r="E16" s="41">
+        <v>0</v>
+      </c>
+      <c r="F16" s="42" t="s">
         <v>56</v>
       </c>
-      <c r="G16" s="38" t="s">
+      <c r="G16" s="41" t="s">
         <v>11</v>
       </c>
-      <c r="H16" s="38">
+      <c r="H16" s="41">
         <v>0</v>
       </c>
     </row>
     <row r="17" ht="52" spans="1:8">
-      <c r="A17" s="36" t="s">
+      <c r="A17" s="39" t="s">
         <v>57</v>
       </c>
-      <c r="B17" s="36" t="s">
+      <c r="B17" s="39" t="s">
         <v>57</v>
       </c>
-      <c r="C17" s="36" t="s">
+      <c r="C17" s="39" t="s">
         <v>58</v>
       </c>
-      <c r="D17" s="36" t="b">
-        <v>0</v>
-      </c>
-      <c r="E17" s="36">
-        <v>0</v>
-      </c>
-      <c r="F17" s="37" t="s">
+      <c r="D17" s="39" t="b">
+        <v>0</v>
+      </c>
+      <c r="E17" s="39">
+        <v>0</v>
+      </c>
+      <c r="F17" s="40" t="s">
         <v>59</v>
       </c>
-      <c r="G17" s="36" t="s">
+      <c r="G17" s="39" t="s">
         <v>11</v>
       </c>
-      <c r="H17" s="36">
+      <c r="H17" s="39">
         <v>0</v>
       </c>
     </row>
     <row r="18" ht="52" spans="1:8">
-      <c r="A18" s="38" t="s">
+      <c r="A18" s="41" t="s">
         <v>60</v>
       </c>
-      <c r="B18" s="38" t="s">
+      <c r="B18" s="41" t="s">
         <v>60</v>
       </c>
-      <c r="C18" s="38" t="s">
+      <c r="C18" s="41" t="s">
         <v>61</v>
       </c>
-      <c r="D18" s="38" t="b">
-        <v>0</v>
-      </c>
-      <c r="E18" s="38">
-        <v>0</v>
-      </c>
-      <c r="F18" s="39" t="s">
+      <c r="D18" s="41" t="b">
+        <v>0</v>
+      </c>
+      <c r="E18" s="41">
+        <v>0</v>
+      </c>
+      <c r="F18" s="42" t="s">
         <v>62</v>
       </c>
-      <c r="G18" s="38" t="s">
+      <c r="G18" s="41" t="s">
         <v>63</v>
       </c>
-      <c r="H18" s="38">
+      <c r="H18" s="41">
         <v>0</v>
       </c>
     </row>
     <row r="19" ht="26" spans="1:8">
-      <c r="A19" s="36" t="s">
+      <c r="A19" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="B19" s="36" t="s">
+      <c r="B19" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="C19" s="36" t="s">
+      <c r="C19" s="39" t="s">
         <v>65</v>
       </c>
-      <c r="D19" s="36" t="b">
-        <v>0</v>
-      </c>
-      <c r="E19" s="36">
-        <v>0</v>
-      </c>
-      <c r="F19" s="37" t="s">
+      <c r="D19" s="39" t="b">
+        <v>0</v>
+      </c>
+      <c r="E19" s="39">
+        <v>0</v>
+      </c>
+      <c r="F19" s="40" t="s">
         <v>66</v>
       </c>
-      <c r="G19" s="36" t="s">
+      <c r="G19" s="39" t="s">
         <v>11</v>
       </c>
-      <c r="H19" s="36">
+      <c r="H19" s="39">
         <v>0</v>
       </c>
     </row>
     <row r="20" ht="26" spans="1:8">
-      <c r="A20" s="38" t="s">
+      <c r="A20" s="41" t="s">
         <v>67</v>
       </c>
-      <c r="B20" s="38" t="s">
+      <c r="B20" s="41" t="s">
         <v>67</v>
       </c>
-      <c r="C20" s="38" t="s">
+      <c r="C20" s="41" t="s">
         <v>68</v>
       </c>
-      <c r="D20" s="38" t="b">
-        <v>0</v>
-      </c>
-      <c r="E20" s="38">
-        <v>0</v>
-      </c>
-      <c r="F20" s="39" t="s">
+      <c r="D20" s="41" t="b">
+        <v>0</v>
+      </c>
+      <c r="E20" s="41">
+        <v>0</v>
+      </c>
+      <c r="F20" s="42" t="s">
         <v>69</v>
       </c>
-      <c r="G20" s="38" t="s">
+      <c r="G20" s="41" t="s">
         <v>11</v>
       </c>
-      <c r="H20" s="38">
+      <c r="H20" s="41">
         <v>0</v>
       </c>
     </row>
     <row r="21" ht="182" spans="1:8">
-      <c r="A21" s="36" t="s">
+      <c r="A21" s="39" t="s">
         <v>70</v>
       </c>
-      <c r="B21" s="36" t="s">
+      <c r="B21" s="39" t="s">
         <v>70</v>
       </c>
-      <c r="C21" s="36" t="s">
+      <c r="C21" s="39" t="s">
         <v>71</v>
       </c>
-      <c r="D21" s="36" t="b">
-        <v>0</v>
-      </c>
-      <c r="E21" s="36">
-        <v>0</v>
-      </c>
-      <c r="F21" s="37" t="s">
+      <c r="D21" s="39" t="b">
+        <v>0</v>
+      </c>
+      <c r="E21" s="39">
+        <v>0</v>
+      </c>
+      <c r="F21" s="40" t="s">
         <v>72</v>
       </c>
-      <c r="G21" s="36" t="s">
+      <c r="G21" s="39" t="s">
         <v>11</v>
       </c>
-      <c r="H21" s="36">
+      <c r="H21" s="39">
         <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:8">
-      <c r="A22" s="38"/>
-      <c r="B22" s="38"/>
-      <c r="C22" s="38"/>
-      <c r="D22" s="38"/>
-      <c r="E22" s="38"/>
-      <c r="F22" s="39"/>
-      <c r="G22" s="38"/>
-      <c r="H22" s="38"/>
+      <c r="A22" s="41"/>
+      <c r="B22" s="41"/>
+      <c r="C22" s="41"/>
+      <c r="D22" s="41"/>
+      <c r="E22" s="41"/>
+      <c r="F22" s="42"/>
+      <c r="G22" s="41"/>
+      <c r="H22" s="41"/>
     </row>
     <row r="23" spans="1:8">
-      <c r="A23" s="36"/>
-      <c r="B23" s="36"/>
-      <c r="C23" s="36"/>
-      <c r="D23" s="36"/>
-      <c r="E23" s="36"/>
-      <c r="F23" s="37"/>
-      <c r="G23" s="36"/>
-      <c r="H23" s="36"/>
+      <c r="A23" s="39"/>
+      <c r="B23" s="39"/>
+      <c r="C23" s="39"/>
+      <c r="D23" s="39"/>
+      <c r="E23" s="39"/>
+      <c r="F23" s="40"/>
+      <c r="G23" s="39"/>
+      <c r="H23" s="39"/>
     </row>
     <row r="24" spans="1:8">
-      <c r="A24" s="38"/>
-      <c r="B24" s="38"/>
-      <c r="C24" s="38"/>
-      <c r="D24" s="38"/>
-      <c r="E24" s="38"/>
-      <c r="F24" s="39"/>
-      <c r="G24" s="38"/>
-      <c r="H24" s="38"/>
+      <c r="A24" s="41"/>
+      <c r="B24" s="41"/>
+      <c r="C24" s="41"/>
+      <c r="D24" s="41"/>
+      <c r="E24" s="41"/>
+      <c r="F24" s="42"/>
+      <c r="G24" s="41"/>
+      <c r="H24" s="41"/>
     </row>
     <row r="25" spans="1:8">
-      <c r="A25" s="36"/>
-      <c r="B25" s="36"/>
-      <c r="C25" s="36"/>
-      <c r="D25" s="36"/>
-      <c r="E25" s="36"/>
-      <c r="F25" s="37"/>
-      <c r="G25" s="36"/>
-      <c r="H25" s="36"/>
+      <c r="A25" s="39"/>
+      <c r="B25" s="39"/>
+      <c r="C25" s="39"/>
+      <c r="D25" s="39"/>
+      <c r="E25" s="39"/>
+      <c r="F25" s="40"/>
+      <c r="G25" s="39"/>
+      <c r="H25" s="39"/>
     </row>
     <row r="26" spans="1:8">
-      <c r="A26" s="38"/>
-      <c r="B26" s="38"/>
-      <c r="C26" s="38"/>
-      <c r="D26" s="38"/>
-      <c r="E26" s="38"/>
-      <c r="F26" s="39"/>
-      <c r="G26" s="38"/>
-      <c r="H26" s="38"/>
+      <c r="A26" s="41"/>
+      <c r="B26" s="41"/>
+      <c r="C26" s="41"/>
+      <c r="D26" s="41"/>
+      <c r="E26" s="41"/>
+      <c r="F26" s="42"/>
+      <c r="G26" s="41"/>
+      <c r="H26" s="41"/>
     </row>
     <row r="27" spans="1:8">
-      <c r="A27" s="36"/>
-      <c r="B27" s="36"/>
-      <c r="C27" s="36"/>
-      <c r="D27" s="36"/>
-      <c r="E27" s="36"/>
-      <c r="F27" s="37"/>
-      <c r="G27" s="36"/>
-      <c r="H27" s="36"/>
+      <c r="A27" s="39"/>
+      <c r="B27" s="39"/>
+      <c r="C27" s="39"/>
+      <c r="D27" s="39"/>
+      <c r="E27" s="39"/>
+      <c r="F27" s="40"/>
+      <c r="G27" s="39"/>
+      <c r="H27" s="39"/>
     </row>
     <row r="28" spans="1:8">
-      <c r="A28" s="38"/>
-      <c r="B28" s="38"/>
-      <c r="C28" s="38"/>
-      <c r="D28" s="38"/>
-      <c r="E28" s="38"/>
-      <c r="F28" s="39"/>
-      <c r="G28" s="38"/>
-      <c r="H28" s="38"/>
+      <c r="A28" s="41"/>
+      <c r="B28" s="41"/>
+      <c r="C28" s="41"/>
+      <c r="D28" s="41"/>
+      <c r="E28" s="41"/>
+      <c r="F28" s="42"/>
+      <c r="G28" s="41"/>
+      <c r="H28" s="41"/>
     </row>
     <row r="29" spans="1:8">
-      <c r="A29" s="36"/>
-      <c r="B29" s="36"/>
-      <c r="C29" s="36"/>
-      <c r="D29" s="36"/>
-      <c r="E29" s="36"/>
-      <c r="F29" s="37"/>
-      <c r="G29" s="36"/>
-      <c r="H29" s="36"/>
+      <c r="A29" s="39"/>
+      <c r="B29" s="39"/>
+      <c r="C29" s="39"/>
+      <c r="D29" s="39"/>
+      <c r="E29" s="39"/>
+      <c r="F29" s="40"/>
+      <c r="G29" s="39"/>
+      <c r="H29" s="39"/>
     </row>
     <row r="30" spans="1:8">
-      <c r="A30" s="38"/>
-      <c r="B30" s="38"/>
-      <c r="C30" s="38"/>
-      <c r="D30" s="38"/>
-      <c r="E30" s="38"/>
-      <c r="F30" s="39"/>
-      <c r="G30" s="38"/>
-      <c r="H30" s="38"/>
+      <c r="A30" s="41"/>
+      <c r="B30" s="41"/>
+      <c r="C30" s="41"/>
+      <c r="D30" s="41"/>
+      <c r="E30" s="41"/>
+      <c r="F30" s="42"/>
+      <c r="G30" s="41"/>
+      <c r="H30" s="41"/>
     </row>
     <row r="31" spans="1:8">
-      <c r="A31" s="36"/>
-      <c r="B31" s="36"/>
-      <c r="C31" s="36"/>
-      <c r="D31" s="36"/>
-      <c r="E31" s="36"/>
-      <c r="F31" s="37"/>
-      <c r="G31" s="36"/>
-      <c r="H31" s="36"/>
+      <c r="A31" s="39"/>
+      <c r="B31" s="39"/>
+      <c r="C31" s="39"/>
+      <c r="D31" s="39"/>
+      <c r="E31" s="39"/>
+      <c r="F31" s="40"/>
+      <c r="G31" s="39"/>
+      <c r="H31" s="39"/>
     </row>
     <row r="32" spans="1:8">
-      <c r="A32" s="38"/>
-      <c r="B32" s="38"/>
-      <c r="C32" s="38"/>
-      <c r="D32" s="38"/>
-      <c r="E32" s="38"/>
-      <c r="F32" s="39"/>
-      <c r="G32" s="38"/>
-      <c r="H32" s="38"/>
+      <c r="A32" s="41"/>
+      <c r="B32" s="41"/>
+      <c r="C32" s="41"/>
+      <c r="D32" s="41"/>
+      <c r="E32" s="41"/>
+      <c r="F32" s="42"/>
+      <c r="G32" s="41"/>
+      <c r="H32" s="41"/>
     </row>
     <row r="33" spans="1:8">
-      <c r="A33" s="36"/>
-      <c r="B33" s="36"/>
-      <c r="C33" s="36"/>
-      <c r="D33" s="36"/>
-      <c r="E33" s="36"/>
-      <c r="F33" s="37"/>
-      <c r="G33" s="36"/>
-      <c r="H33" s="36"/>
+      <c r="A33" s="39"/>
+      <c r="B33" s="39"/>
+      <c r="C33" s="39"/>
+      <c r="D33" s="39"/>
+      <c r="E33" s="39"/>
+      <c r="F33" s="40"/>
+      <c r="G33" s="39"/>
+      <c r="H33" s="39"/>
     </row>
     <row r="34" spans="1:8">
-      <c r="A34" s="38"/>
-      <c r="B34" s="38"/>
-      <c r="C34" s="38"/>
-      <c r="D34" s="38"/>
-      <c r="E34" s="38"/>
-      <c r="F34" s="39"/>
-      <c r="G34" s="38"/>
-      <c r="H34" s="38"/>
+      <c r="A34" s="41"/>
+      <c r="B34" s="41"/>
+      <c r="C34" s="41"/>
+      <c r="D34" s="41"/>
+      <c r="E34" s="41"/>
+      <c r="F34" s="42"/>
+      <c r="G34" s="41"/>
+      <c r="H34" s="41"/>
     </row>
     <row r="35" spans="1:8">
-      <c r="A35" s="36"/>
-      <c r="B35" s="36"/>
-      <c r="C35" s="36"/>
-      <c r="D35" s="36"/>
-      <c r="E35" s="36"/>
-      <c r="F35" s="37"/>
-      <c r="G35" s="36"/>
-      <c r="H35" s="36"/>
+      <c r="A35" s="39"/>
+      <c r="B35" s="39"/>
+      <c r="C35" s="39"/>
+      <c r="D35" s="39"/>
+      <c r="E35" s="39"/>
+      <c r="F35" s="40"/>
+      <c r="G35" s="39"/>
+      <c r="H35" s="39"/>
     </row>
     <row r="36" spans="1:8">
-      <c r="A36" s="38"/>
-      <c r="B36" s="38"/>
-      <c r="C36" s="38"/>
-      <c r="D36" s="38"/>
-      <c r="E36" s="38"/>
-      <c r="F36" s="39"/>
-      <c r="G36" s="38"/>
-      <c r="H36" s="38"/>
+      <c r="A36" s="41"/>
+      <c r="B36" s="41"/>
+      <c r="C36" s="41"/>
+      <c r="D36" s="41"/>
+      <c r="E36" s="41"/>
+      <c r="F36" s="42"/>
+      <c r="G36" s="41"/>
+      <c r="H36" s="41"/>
     </row>
     <row r="37" spans="1:8">
-      <c r="A37" s="36"/>
-      <c r="B37" s="36"/>
-      <c r="C37" s="36"/>
-      <c r="D37" s="36"/>
-      <c r="E37" s="36"/>
-      <c r="F37" s="37"/>
-      <c r="G37" s="36"/>
-      <c r="H37" s="36"/>
+      <c r="A37" s="39"/>
+      <c r="B37" s="39"/>
+      <c r="C37" s="39"/>
+      <c r="D37" s="39"/>
+      <c r="E37" s="39"/>
+      <c r="F37" s="40"/>
+      <c r="G37" s="39"/>
+      <c r="H37" s="39"/>
     </row>
     <row r="38" spans="1:8">
-      <c r="A38" s="38"/>
-      <c r="B38" s="38"/>
-      <c r="C38" s="38"/>
-      <c r="D38" s="38"/>
-      <c r="E38" s="38"/>
-      <c r="F38" s="39"/>
-      <c r="G38" s="38"/>
-      <c r="H38" s="38"/>
+      <c r="A38" s="41"/>
+      <c r="B38" s="41"/>
+      <c r="C38" s="41"/>
+      <c r="D38" s="41"/>
+      <c r="E38" s="41"/>
+      <c r="F38" s="42"/>
+      <c r="G38" s="41"/>
+      <c r="H38" s="41"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5458,147 +5500,147 @@
   </cols>
   <sheetData>
     <row r="1" ht="22.5" customHeight="1" spans="1:6">
-      <c r="A1" s="41" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="42" t="s">
+      <c r="A1" s="44" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="45" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="42" t="s">
+      <c r="C1" s="45" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="41" t="s">
+      <c r="D1" s="44" t="s">
         <v>73</v>
       </c>
-      <c r="E1" s="43" t="s">
+      <c r="E1" s="46" t="s">
         <v>74</v>
       </c>
-      <c r="F1" s="44" t="s">
+      <c r="F1" s="47" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="2" ht="25.5" customHeight="1" spans="1:6">
-      <c r="A2" s="45" t="s">
+      <c r="A2" s="48" t="s">
         <v>75</v>
       </c>
-      <c r="B2" s="46" t="s">
+      <c r="B2" s="49" t="s">
         <v>75</v>
       </c>
-      <c r="C2" s="46" t="s">
+      <c r="C2" s="49" t="s">
         <v>76</v>
       </c>
-      <c r="D2" s="45" t="s">
+      <c r="D2" s="48" t="s">
         <v>77</v>
       </c>
-      <c r="E2" s="47" t="s">
+      <c r="E2" s="50" t="s">
         <v>78</v>
       </c>
-      <c r="F2" s="48" t="s">
+      <c r="F2" s="51" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="3" ht="43" customHeight="1" spans="1:6">
-      <c r="A3" s="49" t="s">
+      <c r="A3" s="52" t="s">
         <v>80</v>
       </c>
-      <c r="B3" s="50" t="s">
+      <c r="B3" s="53" t="s">
         <v>80</v>
       </c>
-      <c r="C3" s="50" t="s">
+      <c r="C3" s="53" t="s">
         <v>81</v>
       </c>
-      <c r="D3" s="49" t="s">
+      <c r="D3" s="52" t="s">
         <v>77</v>
       </c>
-      <c r="E3" s="51" t="s">
+      <c r="E3" s="54" t="s">
         <v>78</v>
       </c>
-      <c r="F3" s="52" t="s">
+      <c r="F3" s="55" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="4" ht="23" customHeight="1" spans="1:6">
-      <c r="A4" s="53" t="s">
+      <c r="A4" s="56" t="s">
         <v>83</v>
       </c>
-      <c r="B4" s="54" t="s">
+      <c r="B4" s="57" t="s">
         <v>83</v>
       </c>
-      <c r="C4" s="54" t="s">
+      <c r="C4" s="57" t="s">
         <v>84</v>
       </c>
-      <c r="D4" s="53" t="s">
+      <c r="D4" s="56" t="s">
         <v>77</v>
       </c>
-      <c r="E4" s="55" t="s">
+      <c r="E4" s="58" t="s">
         <v>85</v>
       </c>
-      <c r="F4" s="56" t="s">
+      <c r="F4" s="59" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="5" s="40" customFormat="1" ht="52.75" spans="1:6">
-      <c r="A5" s="49" t="s">
+    <row r="5" s="43" customFormat="1" ht="52.75" spans="1:6">
+      <c r="A5" s="52" t="s">
         <v>87</v>
       </c>
-      <c r="B5" s="50" t="s">
+      <c r="B5" s="53" t="s">
         <v>87</v>
       </c>
-      <c r="C5" s="51" t="s">
+      <c r="C5" s="54" t="s">
         <v>88</v>
       </c>
-      <c r="D5" s="50" t="s">
+      <c r="D5" s="53" t="s">
         <v>89</v>
       </c>
-      <c r="E5" s="50" t="s">
+      <c r="E5" s="53" t="s">
         <v>90</v>
       </c>
-      <c r="F5" s="52" t="s">
+      <c r="F5" s="55" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="6" s="40" customFormat="1" ht="52" spans="1:6">
-      <c r="A6" s="49" t="s">
+    <row r="6" s="43" customFormat="1" ht="52" spans="1:6">
+      <c r="A6" s="52" t="s">
         <v>92</v>
       </c>
-      <c r="B6" s="50" t="s">
+      <c r="B6" s="53" t="s">
         <v>92</v>
       </c>
-      <c r="C6" s="51" t="s">
+      <c r="C6" s="54" t="s">
         <v>93</v>
       </c>
-      <c r="D6" s="50" t="s">
+      <c r="D6" s="53" t="s">
         <v>77</v>
       </c>
-      <c r="E6" s="50" t="s">
+      <c r="E6" s="53" t="s">
         <v>94</v>
       </c>
-      <c r="F6" s="52" t="s">
+      <c r="F6" s="55" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="45" t="s">
+      <c r="A7" s="48" t="s">
         <v>96</v>
       </c>
-      <c r="B7" s="46" t="s">
+      <c r="B7" s="49" t="s">
         <v>96</v>
       </c>
-      <c r="C7" s="47" t="s">
+      <c r="C7" s="50" t="s">
         <v>97</v>
       </c>
-      <c r="D7" s="46" t="s">
+      <c r="D7" s="49" t="s">
         <v>89</v>
       </c>
-      <c r="E7" s="46" t="s">
+      <c r="E7" s="49" t="s">
         <v>85</v>
       </c>
-      <c r="F7" s="48" t="s">
+      <c r="F7" s="51" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="57" t="s">
+      <c r="A8" s="60" t="s">
         <v>99</v>
       </c>
     </row>
@@ -5652,2238 +5694,2238 @@
   </cols>
   <sheetData>
     <row r="1" ht="14.75" spans="1:8">
-      <c r="A1" s="30" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="30" t="s">
+      <c r="A1" s="33" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="33" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="30" t="s">
+      <c r="C1" s="33" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="30" t="s">
+      <c r="D1" s="33" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="30" t="s">
+      <c r="E1" s="33" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="31" t="s">
+      <c r="F1" s="34" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="30" t="s">
+      <c r="G1" s="33" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="30" t="s">
+      <c r="H1" s="33" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="2" ht="52" spans="1:8">
-      <c r="A2" s="32" t="s">
+      <c r="A2" s="35" t="s">
         <v>100</v>
       </c>
-      <c r="B2" s="32" t="s">
+      <c r="B2" s="35" t="s">
         <v>100</v>
       </c>
-      <c r="C2" s="32" t="s">
+      <c r="C2" s="35" t="s">
         <v>101</v>
       </c>
-      <c r="D2" s="32" t="b">
+      <c r="D2" s="35" t="b">
         <v>1</v>
       </c>
-      <c r="E2" s="32">
+      <c r="E2" s="35">
         <v>1</v>
       </c>
-      <c r="F2" s="33" t="s">
+      <c r="F2" s="36" t="s">
         <v>102</v>
       </c>
-      <c r="G2" s="32" t="s">
+      <c r="G2" s="35" t="s">
         <v>11</v>
       </c>
-      <c r="H2" s="32">
+      <c r="H2" s="35">
         <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:8">
-      <c r="A3" s="34" t="s">
+      <c r="A3" s="37" t="s">
         <v>103</v>
       </c>
-      <c r="B3" s="34" t="s">
+      <c r="B3" s="37" t="s">
         <v>103</v>
       </c>
-      <c r="C3" s="34" t="s">
+      <c r="C3" s="37" t="s">
         <v>104</v>
       </c>
-      <c r="D3" s="34" t="b">
+      <c r="D3" s="37" t="b">
         <v>1</v>
       </c>
-      <c r="E3" s="34">
+      <c r="E3" s="37">
         <v>1</v>
       </c>
-      <c r="F3" s="35" t="s">
+      <c r="F3" s="38" t="s">
         <v>105</v>
       </c>
-      <c r="G3" s="34" t="s">
+      <c r="G3" s="37" t="s">
         <v>11</v>
       </c>
-      <c r="H3" s="34">
+      <c r="H3" s="37">
         <v>0</v>
       </c>
     </row>
     <row r="4" ht="26" spans="1:8">
-      <c r="A4" s="32" t="s">
+      <c r="A4" s="35" t="s">
         <v>106</v>
       </c>
-      <c r="B4" s="32" t="s">
+      <c r="B4" s="35" t="s">
         <v>106</v>
       </c>
-      <c r="C4" s="32" t="s">
+      <c r="C4" s="35" t="s">
         <v>107</v>
       </c>
-      <c r="D4" s="32" t="b">
-        <v>0</v>
-      </c>
-      <c r="E4" s="32">
-        <v>0</v>
-      </c>
-      <c r="F4" s="33" t="s">
+      <c r="D4" s="35" t="b">
+        <v>0</v>
+      </c>
+      <c r="E4" s="35">
+        <v>0</v>
+      </c>
+      <c r="F4" s="36" t="s">
         <v>108</v>
       </c>
-      <c r="G4" s="32" t="s">
+      <c r="G4" s="35" t="s">
         <v>11</v>
       </c>
-      <c r="H4" s="32">
+      <c r="H4" s="35">
         <v>3</v>
       </c>
     </row>
     <row r="5" ht="39" spans="1:8">
-      <c r="A5" s="34" t="s">
+      <c r="A5" s="37" t="s">
         <v>109</v>
       </c>
-      <c r="B5" s="34" t="s">
+      <c r="B5" s="37" t="s">
         <v>109</v>
       </c>
-      <c r="C5" s="34" t="s">
+      <c r="C5" s="37" t="s">
         <v>110</v>
       </c>
-      <c r="D5" s="34" t="b">
-        <v>0</v>
-      </c>
-      <c r="E5" s="34">
-        <v>0</v>
-      </c>
-      <c r="F5" s="35" t="s">
+      <c r="D5" s="37" t="b">
+        <v>0</v>
+      </c>
+      <c r="E5" s="37">
+        <v>0</v>
+      </c>
+      <c r="F5" s="38" t="s">
         <v>111</v>
       </c>
-      <c r="G5" s="34" t="s">
+      <c r="G5" s="37" t="s">
         <v>11</v>
       </c>
-      <c r="H5" s="34">
+      <c r="H5" s="37">
         <v>4</v>
       </c>
     </row>
     <row r="6" ht="26" spans="1:8">
-      <c r="A6" s="32" t="s">
+      <c r="A6" s="35" t="s">
         <v>112</v>
       </c>
-      <c r="B6" s="32" t="s">
+      <c r="B6" s="35" t="s">
         <v>112</v>
       </c>
-      <c r="C6" s="32" t="s">
+      <c r="C6" s="35" t="s">
         <v>113</v>
       </c>
-      <c r="D6" s="32" t="b">
-        <v>0</v>
-      </c>
-      <c r="E6" s="32">
-        <v>0</v>
-      </c>
-      <c r="F6" s="33" t="s">
+      <c r="D6" s="35" t="b">
+        <v>0</v>
+      </c>
+      <c r="E6" s="35">
+        <v>0</v>
+      </c>
+      <c r="F6" s="36" t="s">
         <v>114</v>
       </c>
-      <c r="G6" s="32" t="s">
+      <c r="G6" s="35" t="s">
         <v>11</v>
       </c>
-      <c r="H6" s="32">
+      <c r="H6" s="35">
         <v>0</v>
       </c>
     </row>
     <row r="7" ht="39" spans="1:8">
-      <c r="A7" s="34" t="s">
+      <c r="A7" s="37" t="s">
         <v>115</v>
       </c>
-      <c r="B7" s="34" t="s">
+      <c r="B7" s="37" t="s">
         <v>115</v>
       </c>
-      <c r="C7" s="34" t="s">
+      <c r="C7" s="37" t="s">
         <v>116</v>
       </c>
-      <c r="D7" s="34" t="b">
-        <v>0</v>
-      </c>
-      <c r="E7" s="34">
-        <v>0</v>
-      </c>
-      <c r="F7" s="35" t="s">
+      <c r="D7" s="37" t="b">
+        <v>0</v>
+      </c>
+      <c r="E7" s="37">
+        <v>0</v>
+      </c>
+      <c r="F7" s="38" t="s">
         <v>117</v>
       </c>
-      <c r="G7" s="34" t="s">
+      <c r="G7" s="37" t="s">
         <v>11</v>
       </c>
-      <c r="H7" s="34">
+      <c r="H7" s="37">
         <v>5</v>
       </c>
     </row>
     <row r="8" ht="65" spans="1:8">
-      <c r="A8" s="32" t="s">
+      <c r="A8" s="35" t="s">
         <v>118</v>
       </c>
-      <c r="B8" s="32" t="s">
+      <c r="B8" s="35" t="s">
         <v>118</v>
       </c>
-      <c r="C8" s="32" t="s">
+      <c r="C8" s="35" t="s">
         <v>119</v>
       </c>
-      <c r="D8" s="32" t="b">
-        <v>0</v>
-      </c>
-      <c r="E8" s="32">
-        <v>0</v>
-      </c>
-      <c r="F8" s="33" t="s">
+      <c r="D8" s="35" t="b">
+        <v>0</v>
+      </c>
+      <c r="E8" s="35">
+        <v>0</v>
+      </c>
+      <c r="F8" s="36" t="s">
         <v>120</v>
       </c>
-      <c r="G8" s="32" t="s">
+      <c r="G8" s="35" t="s">
         <v>11</v>
       </c>
-      <c r="H8" s="32">
+      <c r="H8" s="35">
         <v>0</v>
       </c>
     </row>
     <row r="9" ht="39" spans="1:8">
-      <c r="A9" s="34" t="s">
+      <c r="A9" s="37" t="s">
         <v>121</v>
       </c>
-      <c r="B9" s="34" t="s">
+      <c r="B9" s="37" t="s">
         <v>121</v>
       </c>
-      <c r="C9" s="34" t="s">
+      <c r="C9" s="37" t="s">
         <v>122</v>
       </c>
-      <c r="D9" s="34" t="b">
-        <v>0</v>
-      </c>
-      <c r="E9" s="34">
-        <v>0</v>
-      </c>
-      <c r="F9" s="35" t="s">
+      <c r="D9" s="37" t="b">
+        <v>0</v>
+      </c>
+      <c r="E9" s="37">
+        <v>0</v>
+      </c>
+      <c r="F9" s="38" t="s">
         <v>123</v>
       </c>
-      <c r="G9" s="34" t="s">
+      <c r="G9" s="37" t="s">
         <v>11</v>
       </c>
-      <c r="H9" s="34">
+      <c r="H9" s="37">
         <v>0</v>
       </c>
     </row>
     <row r="10" ht="39" spans="1:8">
-      <c r="A10" s="32" t="s">
+      <c r="A10" s="35" t="s">
         <v>124</v>
       </c>
-      <c r="B10" s="32" t="s">
+      <c r="B10" s="35" t="s">
         <v>124</v>
       </c>
-      <c r="C10" s="32" t="s">
+      <c r="C10" s="35" t="s">
         <v>125</v>
       </c>
-      <c r="D10" s="32" t="b">
-        <v>0</v>
-      </c>
-      <c r="E10" s="32">
-        <v>0</v>
-      </c>
-      <c r="F10" s="33" t="s">
+      <c r="D10" s="35" t="b">
+        <v>0</v>
+      </c>
+      <c r="E10" s="35">
+        <v>0</v>
+      </c>
+      <c r="F10" s="36" t="s">
         <v>126</v>
       </c>
-      <c r="G10" s="32" t="s">
+      <c r="G10" s="35" t="s">
         <v>11</v>
       </c>
-      <c r="H10" s="32">
+      <c r="H10" s="35">
         <v>0</v>
       </c>
     </row>
     <row r="11" ht="117" spans="1:8">
-      <c r="A11" s="36" t="s">
+      <c r="A11" s="39" t="s">
         <v>127</v>
       </c>
-      <c r="B11" s="36" t="s">
+      <c r="B11" s="39" t="s">
         <v>127</v>
       </c>
-      <c r="C11" s="36" t="s">
+      <c r="C11" s="39" t="s">
         <v>128</v>
       </c>
-      <c r="D11" s="36" t="b">
-        <v>0</v>
-      </c>
-      <c r="E11" s="36">
-        <v>0</v>
-      </c>
-      <c r="F11" s="37" t="s">
+      <c r="D11" s="39" t="b">
+        <v>0</v>
+      </c>
+      <c r="E11" s="39">
+        <v>0</v>
+      </c>
+      <c r="F11" s="40" t="s">
         <v>129</v>
       </c>
-      <c r="G11" s="36" t="s">
+      <c r="G11" s="39" t="s">
         <v>11</v>
       </c>
-      <c r="H11" s="36">
+      <c r="H11" s="39">
         <v>0</v>
       </c>
     </row>
     <row r="12" ht="39" spans="1:8">
-      <c r="A12" s="38" t="s">
+      <c r="A12" s="41" t="s">
         <v>130</v>
       </c>
-      <c r="B12" s="38" t="s">
+      <c r="B12" s="41" t="s">
         <v>130</v>
       </c>
-      <c r="C12" s="38" t="s">
+      <c r="C12" s="41" t="s">
         <v>131</v>
       </c>
-      <c r="D12" s="38" t="b">
-        <v>0</v>
-      </c>
-      <c r="E12" s="38">
-        <v>0</v>
-      </c>
-      <c r="F12" s="39" t="s">
+      <c r="D12" s="41" t="b">
+        <v>0</v>
+      </c>
+      <c r="E12" s="41">
+        <v>0</v>
+      </c>
+      <c r="F12" s="42" t="s">
         <v>132</v>
       </c>
-      <c r="G12" s="38" t="s">
+      <c r="G12" s="41" t="s">
         <v>11</v>
       </c>
-      <c r="H12" s="38">
+      <c r="H12" s="41">
         <v>0</v>
       </c>
     </row>
     <row r="13" ht="26" spans="1:8">
-      <c r="A13" s="36" t="s">
+      <c r="A13" s="39" t="s">
         <v>133</v>
       </c>
-      <c r="B13" s="36" t="s">
+      <c r="B13" s="39" t="s">
         <v>133</v>
       </c>
-      <c r="C13" s="36" t="s">
+      <c r="C13" s="39" t="s">
         <v>134</v>
       </c>
-      <c r="D13" s="36" t="b">
-        <v>0</v>
-      </c>
-      <c r="E13" s="36">
-        <v>0</v>
-      </c>
-      <c r="F13" s="37" t="s">
+      <c r="D13" s="39" t="b">
+        <v>0</v>
+      </c>
+      <c r="E13" s="39">
+        <v>0</v>
+      </c>
+      <c r="F13" s="40" t="s">
         <v>135</v>
       </c>
-      <c r="G13" s="36" t="s">
+      <c r="G13" s="39" t="s">
         <v>11</v>
       </c>
-      <c r="H13" s="36">
+      <c r="H13" s="39">
         <v>0</v>
       </c>
     </row>
     <row r="14" ht="26" spans="1:8">
-      <c r="A14" s="38" t="s">
+      <c r="A14" s="41" t="s">
         <v>136</v>
       </c>
-      <c r="B14" s="38" t="s">
+      <c r="B14" s="41" t="s">
         <v>136</v>
       </c>
-      <c r="C14" s="38" t="s">
+      <c r="C14" s="41" t="s">
         <v>137</v>
       </c>
-      <c r="D14" s="38" t="b">
-        <v>0</v>
-      </c>
-      <c r="E14" s="38">
-        <v>0</v>
-      </c>
-      <c r="F14" s="39" t="s">
+      <c r="D14" s="41" t="b">
+        <v>0</v>
+      </c>
+      <c r="E14" s="41">
+        <v>0</v>
+      </c>
+      <c r="F14" s="42" t="s">
         <v>138</v>
       </c>
-      <c r="G14" s="38" t="s">
+      <c r="G14" s="41" t="s">
         <v>11</v>
       </c>
-      <c r="H14" s="38">
+      <c r="H14" s="41">
         <v>0</v>
       </c>
     </row>
     <row r="15" ht="17" spans="1:8">
-      <c r="A15" s="36" t="s">
+      <c r="A15" s="39" t="s">
         <v>139</v>
       </c>
-      <c r="B15" s="36" t="s">
+      <c r="B15" s="39" t="s">
         <v>139</v>
       </c>
-      <c r="C15" s="36" t="s">
+      <c r="C15" s="39" t="s">
         <v>140</v>
       </c>
-      <c r="D15" s="36" t="b">
-        <v>0</v>
-      </c>
-      <c r="E15" s="36">
-        <v>0</v>
-      </c>
-      <c r="F15" s="37" t="s">
+      <c r="D15" s="39" t="b">
+        <v>0</v>
+      </c>
+      <c r="E15" s="39">
+        <v>0</v>
+      </c>
+      <c r="F15" s="40" t="s">
         <v>141</v>
       </c>
-      <c r="G15" s="36" t="s">
+      <c r="G15" s="39" t="s">
         <v>11</v>
       </c>
-      <c r="H15" s="36">
+      <c r="H15" s="39">
         <v>0</v>
       </c>
     </row>
     <row r="16" ht="39" spans="1:8">
-      <c r="A16" s="38" t="s">
+      <c r="A16" s="41" t="s">
         <v>142</v>
       </c>
-      <c r="B16" s="38" t="s">
+      <c r="B16" s="41" t="s">
         <v>142</v>
       </c>
-      <c r="C16" s="38" t="s">
+      <c r="C16" s="41" t="s">
         <v>143</v>
       </c>
-      <c r="D16" s="38" t="b">
-        <v>0</v>
-      </c>
-      <c r="E16" s="38">
-        <v>0</v>
-      </c>
-      <c r="F16" s="39" t="s">
+      <c r="D16" s="41" t="b">
+        <v>0</v>
+      </c>
+      <c r="E16" s="41">
+        <v>0</v>
+      </c>
+      <c r="F16" s="42" t="s">
         <v>144</v>
       </c>
-      <c r="G16" s="38" t="s">
+      <c r="G16" s="41" t="s">
         <v>11</v>
       </c>
-      <c r="H16" s="38">
+      <c r="H16" s="41">
         <v>0</v>
       </c>
     </row>
     <row r="17" ht="26" spans="1:8">
-      <c r="A17" s="36" t="s">
+      <c r="A17" s="39" t="s">
         <v>145</v>
       </c>
-      <c r="B17" s="36" t="s">
+      <c r="B17" s="39" t="s">
         <v>145</v>
       </c>
-      <c r="C17" s="36" t="s">
+      <c r="C17" s="39" t="s">
         <v>146</v>
       </c>
-      <c r="D17" s="36" t="b">
-        <v>0</v>
-      </c>
-      <c r="E17" s="36">
-        <v>0</v>
-      </c>
-      <c r="F17" s="37" t="s">
+      <c r="D17" s="39" t="b">
+        <v>0</v>
+      </c>
+      <c r="E17" s="39">
+        <v>0</v>
+      </c>
+      <c r="F17" s="40" t="s">
         <v>147</v>
       </c>
-      <c r="G17" s="36" t="s">
+      <c r="G17" s="39" t="s">
         <v>11</v>
       </c>
-      <c r="H17" s="36">
+      <c r="H17" s="39">
         <v>0</v>
       </c>
     </row>
     <row r="18" ht="26" spans="1:8">
-      <c r="A18" s="38" t="s">
+      <c r="A18" s="41" t="s">
         <v>148</v>
       </c>
-      <c r="B18" s="38" t="s">
+      <c r="B18" s="41" t="s">
         <v>148</v>
       </c>
-      <c r="C18" s="38" t="s">
+      <c r="C18" s="41" t="s">
         <v>149</v>
       </c>
-      <c r="D18" s="38" t="b">
-        <v>0</v>
-      </c>
-      <c r="E18" s="38">
-        <v>0</v>
-      </c>
-      <c r="F18" s="39" t="s">
+      <c r="D18" s="41" t="b">
+        <v>0</v>
+      </c>
+      <c r="E18" s="41">
+        <v>0</v>
+      </c>
+      <c r="F18" s="42" t="s">
         <v>150</v>
       </c>
-      <c r="G18" s="38" t="s">
+      <c r="G18" s="41" t="s">
         <v>11</v>
       </c>
-      <c r="H18" s="38">
+      <c r="H18" s="41">
         <v>0</v>
       </c>
     </row>
     <row r="19" ht="78" spans="1:8">
-      <c r="A19" s="36" t="s">
+      <c r="A19" s="39" t="s">
         <v>151</v>
       </c>
-      <c r="B19" s="36" t="s">
+      <c r="B19" s="39" t="s">
         <v>151</v>
       </c>
-      <c r="C19" s="36" t="s">
+      <c r="C19" s="39" t="s">
         <v>152</v>
       </c>
-      <c r="D19" s="36" t="b">
-        <v>0</v>
-      </c>
-      <c r="E19" s="36">
-        <v>0</v>
-      </c>
-      <c r="F19" s="37" t="s">
+      <c r="D19" s="39" t="b">
+        <v>0</v>
+      </c>
+      <c r="E19" s="39">
+        <v>0</v>
+      </c>
+      <c r="F19" s="40" t="s">
         <v>153</v>
       </c>
-      <c r="G19" s="36" t="s">
+      <c r="G19" s="39" t="s">
         <v>11</v>
       </c>
-      <c r="H19" s="36">
+      <c r="H19" s="39">
         <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:8">
-      <c r="A20" s="38" t="s">
+      <c r="A20" s="41" t="s">
         <v>154</v>
       </c>
-      <c r="B20" s="38" t="s">
+      <c r="B20" s="41" t="s">
         <v>154</v>
       </c>
-      <c r="C20" s="38" t="s">
+      <c r="C20" s="41" t="s">
         <v>155</v>
       </c>
-      <c r="D20" s="38" t="b">
-        <v>0</v>
-      </c>
-      <c r="E20" s="38">
-        <v>0</v>
-      </c>
-      <c r="F20" s="39" t="s">
+      <c r="D20" s="41" t="b">
+        <v>0</v>
+      </c>
+      <c r="E20" s="41">
+        <v>0</v>
+      </c>
+      <c r="F20" s="42" t="s">
         <v>156</v>
       </c>
-      <c r="G20" s="38" t="s">
+      <c r="G20" s="41" t="s">
         <v>11</v>
       </c>
-      <c r="H20" s="38">
+      <c r="H20" s="41">
         <v>0</v>
       </c>
     </row>
     <row r="21" ht="26" spans="1:8">
-      <c r="A21" s="36" t="s">
+      <c r="A21" s="39" t="s">
         <v>157</v>
       </c>
-      <c r="B21" s="36" t="s">
+      <c r="B21" s="39" t="s">
         <v>157</v>
       </c>
-      <c r="C21" s="36" t="s">
+      <c r="C21" s="39" t="s">
         <v>158</v>
       </c>
-      <c r="D21" s="36" t="b">
-        <v>0</v>
-      </c>
-      <c r="E21" s="36">
-        <v>0</v>
-      </c>
-      <c r="F21" s="37" t="s">
+      <c r="D21" s="39" t="b">
+        <v>0</v>
+      </c>
+      <c r="E21" s="39">
+        <v>0</v>
+      </c>
+      <c r="F21" s="40" t="s">
         <v>159</v>
       </c>
-      <c r="G21" s="36" t="s">
+      <c r="G21" s="39" t="s">
         <v>11</v>
       </c>
-      <c r="H21" s="36">
+      <c r="H21" s="39">
         <v>0</v>
       </c>
     </row>
     <row r="22" ht="26" spans="1:8">
-      <c r="A22" s="38" t="s">
+      <c r="A22" s="41" t="s">
         <v>160</v>
       </c>
-      <c r="B22" s="38" t="s">
+      <c r="B22" s="41" t="s">
         <v>160</v>
       </c>
-      <c r="C22" s="38" t="s">
+      <c r="C22" s="41" t="s">
         <v>161</v>
       </c>
-      <c r="D22" s="38" t="b">
+      <c r="D22" s="41" t="b">
         <v>1</v>
       </c>
-      <c r="E22" s="38">
+      <c r="E22" s="41">
         <v>1</v>
       </c>
-      <c r="F22" s="39" t="s">
+      <c r="F22" s="42" t="s">
         <v>162</v>
       </c>
-      <c r="G22" s="38" t="s">
+      <c r="G22" s="41" t="s">
         <v>11</v>
       </c>
-      <c r="H22" s="38">
+      <c r="H22" s="41">
         <v>0</v>
       </c>
     </row>
     <row r="23" ht="65" spans="1:8">
-      <c r="A23" s="36" t="s">
+      <c r="A23" s="39" t="s">
         <v>163</v>
       </c>
-      <c r="B23" s="36" t="s">
+      <c r="B23" s="39" t="s">
         <v>163</v>
       </c>
-      <c r="C23" s="36" t="s">
+      <c r="C23" s="39" t="s">
         <v>88</v>
       </c>
-      <c r="D23" s="36" t="b">
-        <v>0</v>
-      </c>
-      <c r="E23" s="36">
-        <v>0</v>
-      </c>
-      <c r="F23" s="37" t="s">
+      <c r="D23" s="39" t="b">
+        <v>0</v>
+      </c>
+      <c r="E23" s="39">
+        <v>0</v>
+      </c>
+      <c r="F23" s="40" t="s">
         <v>164</v>
       </c>
-      <c r="G23" s="36" t="s">
+      <c r="G23" s="39" t="s">
         <v>11</v>
       </c>
-      <c r="H23" s="36">
+      <c r="H23" s="39">
         <v>0</v>
       </c>
     </row>
     <row r="24" ht="65" spans="1:8">
-      <c r="A24" s="38" t="s">
+      <c r="A24" s="41" t="s">
         <v>165</v>
       </c>
-      <c r="B24" s="38" t="s">
+      <c r="B24" s="41" t="s">
         <v>165</v>
       </c>
-      <c r="C24" s="38" t="s">
+      <c r="C24" s="41" t="s">
         <v>166</v>
       </c>
-      <c r="D24" s="38" t="b">
-        <v>0</v>
-      </c>
-      <c r="E24" s="38">
-        <v>0</v>
-      </c>
-      <c r="F24" s="39" t="s">
+      <c r="D24" s="41" t="b">
+        <v>0</v>
+      </c>
+      <c r="E24" s="41">
+        <v>0</v>
+      </c>
+      <c r="F24" s="42" t="s">
         <v>167</v>
       </c>
-      <c r="G24" s="38" t="s">
+      <c r="G24" s="41" t="s">
         <v>11</v>
       </c>
-      <c r="H24" s="38">
+      <c r="H24" s="41">
         <v>0</v>
       </c>
     </row>
     <row r="25" ht="26" spans="1:8">
-      <c r="A25" s="36" t="s">
+      <c r="A25" s="39" t="s">
         <v>168</v>
       </c>
-      <c r="B25" s="36" t="s">
+      <c r="B25" s="39" t="s">
         <v>168</v>
       </c>
-      <c r="C25" s="36" t="s">
+      <c r="C25" s="39" t="s">
         <v>169</v>
       </c>
-      <c r="D25" s="36" t="b">
-        <v>0</v>
-      </c>
-      <c r="E25" s="36">
-        <v>0</v>
-      </c>
-      <c r="F25" s="37" t="s">
+      <c r="D25" s="39" t="b">
+        <v>0</v>
+      </c>
+      <c r="E25" s="39">
+        <v>0</v>
+      </c>
+      <c r="F25" s="40" t="s">
         <v>170</v>
       </c>
-      <c r="G25" s="36" t="s">
+      <c r="G25" s="39" t="s">
         <v>11</v>
       </c>
-      <c r="H25" s="36">
+      <c r="H25" s="39">
         <v>0</v>
       </c>
     </row>
     <row r="26" ht="78" spans="1:8">
-      <c r="A26" s="38" t="s">
+      <c r="A26" s="41" t="s">
         <v>171</v>
       </c>
-      <c r="B26" s="38" t="s">
+      <c r="B26" s="41" t="s">
         <v>171</v>
       </c>
-      <c r="C26" s="38" t="s">
+      <c r="C26" s="41" t="s">
         <v>172</v>
       </c>
-      <c r="D26" s="38" t="b">
+      <c r="D26" s="41" t="b">
         <v>1</v>
       </c>
-      <c r="E26" s="38">
+      <c r="E26" s="41">
         <v>1</v>
       </c>
-      <c r="F26" s="39" t="s">
+      <c r="F26" s="42" t="s">
         <v>173</v>
       </c>
-      <c r="G26" s="38" t="s">
+      <c r="G26" s="41" t="s">
         <v>11</v>
       </c>
-      <c r="H26" s="38">
+      <c r="H26" s="41">
         <v>0</v>
       </c>
     </row>
     <row r="27" ht="52" spans="1:8">
-      <c r="A27" s="36" t="s">
+      <c r="A27" s="39" t="s">
         <v>174</v>
       </c>
-      <c r="B27" s="36" t="s">
+      <c r="B27" s="39" t="s">
         <v>174</v>
       </c>
-      <c r="C27" s="36" t="s">
+      <c r="C27" s="39" t="s">
         <v>175</v>
       </c>
-      <c r="D27" s="36" t="b">
-        <v>0</v>
-      </c>
-      <c r="E27" s="36">
-        <v>0</v>
-      </c>
-      <c r="F27" s="37" t="s">
+      <c r="D27" s="39" t="b">
+        <v>0</v>
+      </c>
+      <c r="E27" s="39">
+        <v>0</v>
+      </c>
+      <c r="F27" s="40" t="s">
         <v>176</v>
       </c>
-      <c r="G27" s="36" t="s">
+      <c r="G27" s="39" t="s">
         <v>11</v>
       </c>
-      <c r="H27" s="36">
+      <c r="H27" s="39">
         <v>0</v>
       </c>
     </row>
     <row r="28" ht="65" spans="1:8">
-      <c r="A28" s="38" t="s">
+      <c r="A28" s="41" t="s">
         <v>177</v>
       </c>
-      <c r="B28" s="38" t="s">
+      <c r="B28" s="41" t="s">
         <v>177</v>
       </c>
-      <c r="C28" s="38" t="s">
+      <c r="C28" s="41" t="s">
         <v>178</v>
       </c>
-      <c r="D28" s="38" t="b">
-        <v>0</v>
-      </c>
-      <c r="E28" s="38">
-        <v>0</v>
-      </c>
-      <c r="F28" s="39" t="s">
+      <c r="D28" s="41" t="b">
+        <v>0</v>
+      </c>
+      <c r="E28" s="41">
+        <v>0</v>
+      </c>
+      <c r="F28" s="42" t="s">
         <v>179</v>
       </c>
-      <c r="G28" s="38" t="s">
+      <c r="G28" s="41" t="s">
         <v>11</v>
       </c>
-      <c r="H28" s="38">
+      <c r="H28" s="41">
         <v>0</v>
       </c>
     </row>
     <row r="29" ht="26" spans="1:8">
-      <c r="A29" s="36" t="s">
+      <c r="A29" s="39" t="s">
         <v>180</v>
       </c>
-      <c r="B29" s="36" t="s">
+      <c r="B29" s="39" t="s">
         <v>180</v>
       </c>
-      <c r="C29" s="36" t="s">
+      <c r="C29" s="39" t="s">
         <v>181</v>
       </c>
-      <c r="D29" s="36" t="b">
-        <v>0</v>
-      </c>
-      <c r="E29" s="36">
-        <v>0</v>
-      </c>
-      <c r="F29" s="37" t="s">
+      <c r="D29" s="39" t="b">
+        <v>0</v>
+      </c>
+      <c r="E29" s="39">
+        <v>0</v>
+      </c>
+      <c r="F29" s="40" t="s">
         <v>182</v>
       </c>
-      <c r="G29" s="36" t="s">
+      <c r="G29" s="39" t="s">
         <v>11</v>
       </c>
-      <c r="H29" s="36">
+      <c r="H29" s="39">
         <v>0</v>
       </c>
     </row>
     <row r="30" ht="39" spans="1:8">
-      <c r="A30" s="38" t="s">
+      <c r="A30" s="41" t="s">
         <v>183</v>
       </c>
-      <c r="B30" s="38" t="s">
+      <c r="B30" s="41" t="s">
         <v>183</v>
       </c>
-      <c r="C30" s="38" t="s">
+      <c r="C30" s="41" t="s">
         <v>184</v>
       </c>
-      <c r="D30" s="38" t="b">
-        <v>0</v>
-      </c>
-      <c r="E30" s="38">
-        <v>0</v>
-      </c>
-      <c r="F30" s="39" t="s">
+      <c r="D30" s="41" t="b">
+        <v>0</v>
+      </c>
+      <c r="E30" s="41">
+        <v>0</v>
+      </c>
+      <c r="F30" s="42" t="s">
         <v>185</v>
       </c>
-      <c r="G30" s="38" t="s">
+      <c r="G30" s="41" t="s">
         <v>11</v>
       </c>
-      <c r="H30" s="38">
+      <c r="H30" s="41">
         <v>0</v>
       </c>
     </row>
     <row r="31" ht="26" spans="1:8">
-      <c r="A31" s="36" t="s">
+      <c r="A31" s="39" t="s">
         <v>186</v>
       </c>
-      <c r="B31" s="36" t="s">
+      <c r="B31" s="39" t="s">
         <v>186</v>
       </c>
-      <c r="C31" s="36" t="s">
+      <c r="C31" s="39" t="s">
         <v>187</v>
       </c>
-      <c r="D31" s="36" t="b">
-        <v>0</v>
-      </c>
-      <c r="E31" s="36">
-        <v>0</v>
-      </c>
-      <c r="F31" s="37" t="s">
+      <c r="D31" s="39" t="b">
+        <v>0</v>
+      </c>
+      <c r="E31" s="39">
+        <v>0</v>
+      </c>
+      <c r="F31" s="40" t="s">
         <v>188</v>
       </c>
-      <c r="G31" s="36" t="s">
+      <c r="G31" s="39" t="s">
         <v>11</v>
       </c>
-      <c r="H31" s="36">
+      <c r="H31" s="39">
         <v>0</v>
       </c>
     </row>
     <row r="32" ht="26" spans="1:8">
-      <c r="A32" s="38" t="s">
+      <c r="A32" s="41" t="s">
         <v>189</v>
       </c>
-      <c r="B32" s="38" t="s">
+      <c r="B32" s="41" t="s">
         <v>189</v>
       </c>
-      <c r="C32" s="38" t="s">
+      <c r="C32" s="41" t="s">
         <v>190</v>
       </c>
-      <c r="D32" s="38" t="b">
-        <v>0</v>
-      </c>
-      <c r="E32" s="38">
-        <v>0</v>
-      </c>
-      <c r="F32" s="39" t="s">
+      <c r="D32" s="41" t="b">
+        <v>0</v>
+      </c>
+      <c r="E32" s="41">
+        <v>0</v>
+      </c>
+      <c r="F32" s="42" t="s">
         <v>191</v>
       </c>
-      <c r="G32" s="38" t="s">
+      <c r="G32" s="41" t="s">
         <v>11</v>
       </c>
-      <c r="H32" s="38">
+      <c r="H32" s="41">
         <v>0</v>
       </c>
     </row>
     <row r="33" ht="39" spans="1:8">
-      <c r="A33" s="36" t="s">
+      <c r="A33" s="39" t="s">
         <v>192</v>
       </c>
-      <c r="B33" s="36" t="s">
+      <c r="B33" s="39" t="s">
         <v>192</v>
       </c>
-      <c r="C33" s="36" t="s">
+      <c r="C33" s="39" t="s">
         <v>193</v>
       </c>
-      <c r="D33" s="36" t="b">
-        <v>0</v>
-      </c>
-      <c r="E33" s="36">
-        <v>0</v>
-      </c>
-      <c r="F33" s="37" t="s">
+      <c r="D33" s="39" t="b">
+        <v>0</v>
+      </c>
+      <c r="E33" s="39">
+        <v>0</v>
+      </c>
+      <c r="F33" s="40" t="s">
         <v>194</v>
       </c>
-      <c r="G33" s="36" t="s">
+      <c r="G33" s="39" t="s">
         <v>11</v>
       </c>
-      <c r="H33" s="36">
+      <c r="H33" s="39">
         <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:8">
-      <c r="A34" s="38" t="s">
+      <c r="A34" s="41" t="s">
         <v>195</v>
       </c>
-      <c r="B34" s="38" t="s">
+      <c r="B34" s="41" t="s">
         <v>195</v>
       </c>
-      <c r="C34" s="38" t="s">
+      <c r="C34" s="41" t="s">
         <v>196</v>
       </c>
-      <c r="D34" s="38" t="b">
-        <v>0</v>
-      </c>
-      <c r="E34" s="38">
-        <v>0</v>
-      </c>
-      <c r="F34" s="39" t="s">
+      <c r="D34" s="41" t="b">
+        <v>0</v>
+      </c>
+      <c r="E34" s="41">
+        <v>0</v>
+      </c>
+      <c r="F34" s="42" t="s">
         <v>197</v>
       </c>
-      <c r="G34" s="38" t="s">
+      <c r="G34" s="41" t="s">
         <v>11</v>
       </c>
-      <c r="H34" s="38">
+      <c r="H34" s="41">
         <v>0</v>
       </c>
     </row>
     <row r="35" ht="130" spans="1:8">
-      <c r="A35" s="36" t="s">
+      <c r="A35" s="39" t="s">
         <v>198</v>
       </c>
-      <c r="B35" s="36" t="s">
+      <c r="B35" s="39" t="s">
         <v>198</v>
       </c>
-      <c r="C35" s="36" t="s">
+      <c r="C35" s="39" t="s">
         <v>199</v>
       </c>
-      <c r="D35" s="36" t="b">
-        <v>0</v>
-      </c>
-      <c r="E35" s="36">
-        <v>0</v>
-      </c>
-      <c r="F35" s="37" t="s">
+      <c r="D35" s="39" t="b">
+        <v>0</v>
+      </c>
+      <c r="E35" s="39">
+        <v>0</v>
+      </c>
+      <c r="F35" s="40" t="s">
         <v>200</v>
       </c>
-      <c r="G35" s="36" t="s">
+      <c r="G35" s="39" t="s">
         <v>11</v>
       </c>
-      <c r="H35" s="36">
+      <c r="H35" s="39">
         <v>0</v>
       </c>
     </row>
     <row r="36" spans="1:8">
-      <c r="A36" s="38" t="s">
+      <c r="A36" s="41" t="s">
         <v>201</v>
       </c>
-      <c r="B36" s="38" t="s">
+      <c r="B36" s="41" t="s">
         <v>201</v>
       </c>
-      <c r="C36" s="38" t="s">
+      <c r="C36" s="41" t="s">
         <v>202</v>
       </c>
-      <c r="D36" s="38" t="b">
-        <v>0</v>
-      </c>
-      <c r="E36" s="38">
-        <v>0</v>
-      </c>
-      <c r="F36" s="39" t="s">
+      <c r="D36" s="41" t="b">
+        <v>0</v>
+      </c>
+      <c r="E36" s="41">
+        <v>0</v>
+      </c>
+      <c r="F36" s="42" t="s">
         <v>203</v>
       </c>
-      <c r="G36" s="38" t="s">
+      <c r="G36" s="41" t="s">
         <v>11</v>
       </c>
-      <c r="H36" s="38">
+      <c r="H36" s="41">
         <v>0</v>
       </c>
     </row>
     <row r="37" spans="1:8">
-      <c r="A37" s="36" t="s">
+      <c r="A37" s="39" t="s">
         <v>204</v>
       </c>
-      <c r="B37" s="36" t="s">
+      <c r="B37" s="39" t="s">
         <v>204</v>
       </c>
-      <c r="C37" s="36" t="s">
+      <c r="C37" s="39" t="s">
         <v>205</v>
       </c>
-      <c r="D37" s="36" t="b">
-        <v>0</v>
-      </c>
-      <c r="E37" s="36">
-        <v>0</v>
-      </c>
-      <c r="F37" s="37" t="s">
+      <c r="D37" s="39" t="b">
+        <v>0</v>
+      </c>
+      <c r="E37" s="39">
+        <v>0</v>
+      </c>
+      <c r="F37" s="40" t="s">
         <v>206</v>
       </c>
-      <c r="G37" s="36" t="s">
+      <c r="G37" s="39" t="s">
         <v>11</v>
       </c>
-      <c r="H37" s="36">
+      <c r="H37" s="39">
         <v>0</v>
       </c>
     </row>
     <row r="38" ht="39" spans="1:8">
-      <c r="A38" s="38" t="s">
+      <c r="A38" s="41" t="s">
         <v>207</v>
       </c>
-      <c r="B38" s="38" t="s">
+      <c r="B38" s="41" t="s">
         <v>207</v>
       </c>
-      <c r="C38" s="38" t="s">
+      <c r="C38" s="41" t="s">
         <v>208</v>
       </c>
-      <c r="D38" s="38" t="b">
-        <v>0</v>
-      </c>
-      <c r="E38" s="38">
-        <v>0</v>
-      </c>
-      <c r="F38" s="39" t="s">
+      <c r="D38" s="41" t="b">
+        <v>0</v>
+      </c>
+      <c r="E38" s="41">
+        <v>0</v>
+      </c>
+      <c r="F38" s="42" t="s">
         <v>209</v>
       </c>
-      <c r="G38" s="38" t="s">
+      <c r="G38" s="41" t="s">
         <v>11</v>
       </c>
-      <c r="H38" s="38">
+      <c r="H38" s="41">
         <v>0</v>
       </c>
     </row>
     <row r="39" ht="26" spans="1:8">
-      <c r="A39" s="36" t="s">
+      <c r="A39" s="39" t="s">
         <v>210</v>
       </c>
-      <c r="B39" s="36" t="s">
+      <c r="B39" s="39" t="s">
         <v>210</v>
       </c>
-      <c r="C39" s="36" t="s">
+      <c r="C39" s="39" t="s">
         <v>211</v>
       </c>
-      <c r="D39" s="36" t="b">
-        <v>0</v>
-      </c>
-      <c r="E39" s="36">
-        <v>0</v>
-      </c>
-      <c r="F39" s="37" t="s">
+      <c r="D39" s="39" t="b">
+        <v>0</v>
+      </c>
+      <c r="E39" s="39">
+        <v>0</v>
+      </c>
+      <c r="F39" s="40" t="s">
         <v>212</v>
       </c>
-      <c r="G39" s="36" t="s">
+      <c r="G39" s="39" t="s">
         <v>11</v>
       </c>
-      <c r="H39" s="36">
+      <c r="H39" s="39">
         <v>0</v>
       </c>
     </row>
     <row r="40" spans="1:8">
-      <c r="A40" s="38" t="s">
+      <c r="A40" s="41" t="s">
         <v>213</v>
       </c>
-      <c r="B40" s="38" t="s">
+      <c r="B40" s="41" t="s">
         <v>213</v>
       </c>
-      <c r="C40" s="38" t="s">
+      <c r="C40" s="41" t="s">
         <v>214</v>
       </c>
-      <c r="D40" s="38" t="b">
-        <v>0</v>
-      </c>
-      <c r="E40" s="38">
-        <v>0</v>
-      </c>
-      <c r="F40" s="39" t="s">
+      <c r="D40" s="41" t="b">
+        <v>0</v>
+      </c>
+      <c r="E40" s="41">
+        <v>0</v>
+      </c>
+      <c r="F40" s="42" t="s">
         <v>215</v>
       </c>
-      <c r="G40" s="38" t="s">
+      <c r="G40" s="41" t="s">
         <v>11</v>
       </c>
-      <c r="H40" s="38">
+      <c r="H40" s="41">
         <v>0</v>
       </c>
     </row>
     <row r="41" ht="26" spans="1:8">
-      <c r="A41" s="36" t="s">
+      <c r="A41" s="39" t="s">
         <v>216</v>
       </c>
-      <c r="B41" s="36" t="s">
+      <c r="B41" s="39" t="s">
         <v>216</v>
       </c>
-      <c r="C41" s="36" t="s">
+      <c r="C41" s="39" t="s">
         <v>217</v>
       </c>
-      <c r="D41" s="36" t="b">
-        <v>0</v>
-      </c>
-      <c r="E41" s="36">
-        <v>0</v>
-      </c>
-      <c r="F41" s="37" t="s">
+      <c r="D41" s="39" t="b">
+        <v>0</v>
+      </c>
+      <c r="E41" s="39">
+        <v>0</v>
+      </c>
+      <c r="F41" s="40" t="s">
         <v>218</v>
       </c>
-      <c r="G41" s="36" t="s">
+      <c r="G41" s="39" t="s">
         <v>11</v>
       </c>
-      <c r="H41" s="36">
+      <c r="H41" s="39">
         <v>0</v>
       </c>
     </row>
     <row r="42" ht="26" spans="1:8">
-      <c r="A42" s="38" t="s">
+      <c r="A42" s="41" t="s">
         <v>219</v>
       </c>
-      <c r="B42" s="38" t="s">
+      <c r="B42" s="41" t="s">
         <v>219</v>
       </c>
-      <c r="C42" s="38" t="s">
+      <c r="C42" s="41" t="s">
         <v>220</v>
       </c>
-      <c r="D42" s="38" t="b">
-        <v>0</v>
-      </c>
-      <c r="E42" s="38">
-        <v>0</v>
-      </c>
-      <c r="F42" s="39" t="s">
+      <c r="D42" s="41" t="b">
+        <v>0</v>
+      </c>
+      <c r="E42" s="41">
+        <v>0</v>
+      </c>
+      <c r="F42" s="42" t="s">
         <v>221</v>
       </c>
-      <c r="G42" s="38" t="s">
+      <c r="G42" s="41" t="s">
         <v>11</v>
       </c>
-      <c r="H42" s="38">
+      <c r="H42" s="41">
         <v>0</v>
       </c>
     </row>
     <row r="43" ht="26" spans="1:8">
-      <c r="A43" s="36" t="s">
+      <c r="A43" s="39" t="s">
         <v>222</v>
       </c>
-      <c r="B43" s="36" t="s">
+      <c r="B43" s="39" t="s">
         <v>222</v>
       </c>
-      <c r="C43" s="36" t="s">
+      <c r="C43" s="39" t="s">
         <v>223</v>
       </c>
-      <c r="D43" s="36" t="b">
-        <v>0</v>
-      </c>
-      <c r="E43" s="36">
-        <v>0</v>
-      </c>
-      <c r="F43" s="37" t="s">
+      <c r="D43" s="39" t="b">
+        <v>0</v>
+      </c>
+      <c r="E43" s="39">
+        <v>0</v>
+      </c>
+      <c r="F43" s="40" t="s">
         <v>224</v>
       </c>
-      <c r="G43" s="36" t="s">
+      <c r="G43" s="39" t="s">
         <v>11</v>
       </c>
-      <c r="H43" s="36">
+      <c r="H43" s="39">
         <v>0</v>
       </c>
     </row>
     <row r="44" ht="39" spans="1:8">
-      <c r="A44" s="38" t="s">
+      <c r="A44" s="41" t="s">
         <v>225</v>
       </c>
-      <c r="B44" s="38" t="s">
+      <c r="B44" s="41" t="s">
         <v>225</v>
       </c>
-      <c r="C44" s="38" t="s">
+      <c r="C44" s="41" t="s">
         <v>226</v>
       </c>
-      <c r="D44" s="38" t="b">
-        <v>0</v>
-      </c>
-      <c r="E44" s="38">
-        <v>0</v>
-      </c>
-      <c r="F44" s="39" t="s">
+      <c r="D44" s="41" t="b">
+        <v>0</v>
+      </c>
+      <c r="E44" s="41">
+        <v>0</v>
+      </c>
+      <c r="F44" s="42" t="s">
         <v>227</v>
       </c>
-      <c r="G44" s="38" t="s">
+      <c r="G44" s="41" t="s">
         <v>11</v>
       </c>
-      <c r="H44" s="38">
+      <c r="H44" s="41">
         <v>0</v>
       </c>
     </row>
     <row r="45" ht="26" spans="1:8">
-      <c r="A45" s="36" t="s">
+      <c r="A45" s="39" t="s">
         <v>228</v>
       </c>
-      <c r="B45" s="36" t="s">
+      <c r="B45" s="39" t="s">
         <v>228</v>
       </c>
-      <c r="C45" s="36" t="s">
+      <c r="C45" s="39" t="s">
         <v>229</v>
       </c>
-      <c r="D45" s="36" t="b">
-        <v>0</v>
-      </c>
-      <c r="E45" s="36">
-        <v>0</v>
-      </c>
-      <c r="F45" s="37" t="s">
+      <c r="D45" s="39" t="b">
+        <v>0</v>
+      </c>
+      <c r="E45" s="39">
+        <v>0</v>
+      </c>
+      <c r="F45" s="40" t="s">
         <v>230</v>
       </c>
-      <c r="G45" s="36" t="s">
+      <c r="G45" s="39" t="s">
         <v>11</v>
       </c>
-      <c r="H45" s="36">
+      <c r="H45" s="39">
         <v>0</v>
       </c>
     </row>
     <row r="46" ht="26" spans="1:8">
-      <c r="A46" s="38" t="s">
+      <c r="A46" s="41" t="s">
         <v>231</v>
       </c>
-      <c r="B46" s="38" t="s">
+      <c r="B46" s="41" t="s">
         <v>231</v>
       </c>
-      <c r="C46" s="38" t="s">
+      <c r="C46" s="41" t="s">
         <v>232</v>
       </c>
-      <c r="D46" s="38" t="b">
-        <v>0</v>
-      </c>
-      <c r="E46" s="38">
-        <v>0</v>
-      </c>
-      <c r="F46" s="39" t="s">
+      <c r="D46" s="41" t="b">
+        <v>0</v>
+      </c>
+      <c r="E46" s="41">
+        <v>0</v>
+      </c>
+      <c r="F46" s="42" t="s">
         <v>233</v>
       </c>
-      <c r="G46" s="38" t="s">
+      <c r="G46" s="41" t="s">
         <v>11</v>
       </c>
-      <c r="H46" s="38">
+      <c r="H46" s="41">
         <v>0</v>
       </c>
     </row>
     <row r="47" ht="52" spans="1:8">
-      <c r="A47" s="36" t="s">
+      <c r="A47" s="39" t="s">
         <v>234</v>
       </c>
-      <c r="B47" s="36" t="s">
+      <c r="B47" s="39" t="s">
         <v>234</v>
       </c>
-      <c r="C47" s="36" t="s">
+      <c r="C47" s="39" t="s">
         <v>235</v>
       </c>
-      <c r="D47" s="36" t="b">
-        <v>0</v>
-      </c>
-      <c r="E47" s="36">
-        <v>0</v>
-      </c>
-      <c r="F47" s="37" t="s">
+      <c r="D47" s="39" t="b">
+        <v>0</v>
+      </c>
+      <c r="E47" s="39">
+        <v>0</v>
+      </c>
+      <c r="F47" s="40" t="s">
         <v>236</v>
       </c>
-      <c r="G47" s="36" t="s">
+      <c r="G47" s="39" t="s">
         <v>11</v>
       </c>
-      <c r="H47" s="36">
+      <c r="H47" s="39">
         <v>0</v>
       </c>
     </row>
     <row r="48" ht="65" spans="1:8">
-      <c r="A48" s="38" t="s">
+      <c r="A48" s="41" t="s">
         <v>237</v>
       </c>
-      <c r="B48" s="38" t="s">
+      <c r="B48" s="41" t="s">
         <v>237</v>
       </c>
-      <c r="C48" s="38" t="s">
+      <c r="C48" s="41" t="s">
         <v>238</v>
       </c>
-      <c r="D48" s="38" t="b">
-        <v>0</v>
-      </c>
-      <c r="E48" s="38">
-        <v>0</v>
-      </c>
-      <c r="F48" s="39" t="s">
+      <c r="D48" s="41" t="b">
+        <v>0</v>
+      </c>
+      <c r="E48" s="41">
+        <v>0</v>
+      </c>
+      <c r="F48" s="42" t="s">
         <v>239</v>
       </c>
-      <c r="G48" s="38" t="s">
+      <c r="G48" s="41" t="s">
         <v>11</v>
       </c>
-      <c r="H48" s="38">
+      <c r="H48" s="41">
         <v>0</v>
       </c>
     </row>
     <row r="49" spans="1:8">
-      <c r="A49" s="36" t="s">
+      <c r="A49" s="39" t="s">
         <v>240</v>
       </c>
-      <c r="B49" s="36" t="s">
+      <c r="B49" s="39" t="s">
         <v>240</v>
       </c>
-      <c r="C49" s="36" t="s">
+      <c r="C49" s="39" t="s">
         <v>241</v>
       </c>
-      <c r="D49" s="36" t="b">
-        <v>0</v>
-      </c>
-      <c r="E49" s="36">
-        <v>0</v>
-      </c>
-      <c r="F49" s="37" t="s">
+      <c r="D49" s="39" t="b">
+        <v>0</v>
+      </c>
+      <c r="E49" s="39">
+        <v>0</v>
+      </c>
+      <c r="F49" s="40" t="s">
         <v>242</v>
       </c>
-      <c r="G49" s="36" t="s">
+      <c r="G49" s="39" t="s">
         <v>11</v>
       </c>
-      <c r="H49" s="36">
+      <c r="H49" s="39">
         <v>0</v>
       </c>
     </row>
     <row r="50" ht="39" spans="1:8">
-      <c r="A50" s="38" t="s">
+      <c r="A50" s="41" t="s">
         <v>243</v>
       </c>
-      <c r="B50" s="38" t="s">
+      <c r="B50" s="41" t="s">
         <v>243</v>
       </c>
-      <c r="C50" s="38" t="s">
+      <c r="C50" s="41" t="s">
         <v>244</v>
       </c>
-      <c r="D50" s="38" t="b">
-        <v>0</v>
-      </c>
-      <c r="E50" s="38">
-        <v>0</v>
-      </c>
-      <c r="F50" s="39" t="s">
+      <c r="D50" s="41" t="b">
+        <v>0</v>
+      </c>
+      <c r="E50" s="41">
+        <v>0</v>
+      </c>
+      <c r="F50" s="42" t="s">
         <v>245</v>
       </c>
-      <c r="G50" s="38" t="s">
+      <c r="G50" s="41" t="s">
         <v>11</v>
       </c>
-      <c r="H50" s="38">
+      <c r="H50" s="41">
         <v>0</v>
       </c>
     </row>
     <row r="51" spans="1:8">
-      <c r="A51" s="36" t="s">
+      <c r="A51" s="39" t="s">
         <v>246</v>
       </c>
-      <c r="B51" s="36" t="s">
+      <c r="B51" s="39" t="s">
         <v>246</v>
       </c>
-      <c r="C51" s="36" t="s">
+      <c r="C51" s="39" t="s">
         <v>247</v>
       </c>
-      <c r="D51" s="36" t="b">
-        <v>0</v>
-      </c>
-      <c r="E51" s="36">
-        <v>0</v>
-      </c>
-      <c r="F51" s="37" t="s">
+      <c r="D51" s="39" t="b">
+        <v>0</v>
+      </c>
+      <c r="E51" s="39">
+        <v>0</v>
+      </c>
+      <c r="F51" s="40" t="s">
         <v>248</v>
       </c>
-      <c r="G51" s="36" t="s">
+      <c r="G51" s="39" t="s">
         <v>11</v>
       </c>
-      <c r="H51" s="36">
+      <c r="H51" s="39">
         <v>0</v>
       </c>
     </row>
     <row r="52" ht="26" spans="1:8">
-      <c r="A52" s="38" t="s">
+      <c r="A52" s="41" t="s">
         <v>249</v>
       </c>
-      <c r="B52" s="38" t="s">
+      <c r="B52" s="41" t="s">
         <v>249</v>
       </c>
-      <c r="C52" s="38" t="s">
+      <c r="C52" s="41" t="s">
         <v>250</v>
       </c>
-      <c r="D52" s="38" t="b">
-        <v>0</v>
-      </c>
-      <c r="E52" s="38">
-        <v>0</v>
-      </c>
-      <c r="F52" s="39" t="s">
+      <c r="D52" s="41" t="b">
+        <v>0</v>
+      </c>
+      <c r="E52" s="41">
+        <v>0</v>
+      </c>
+      <c r="F52" s="42" t="s">
         <v>251</v>
       </c>
-      <c r="G52" s="38" t="s">
+      <c r="G52" s="41" t="s">
         <v>11</v>
       </c>
-      <c r="H52" s="38">
+      <c r="H52" s="41">
         <v>0</v>
       </c>
     </row>
     <row r="53" ht="26" spans="1:8">
-      <c r="A53" s="36" t="s">
+      <c r="A53" s="39" t="s">
         <v>252</v>
       </c>
-      <c r="B53" s="36" t="s">
+      <c r="B53" s="39" t="s">
         <v>252</v>
       </c>
-      <c r="C53" s="36" t="s">
+      <c r="C53" s="39" t="s">
         <v>253</v>
       </c>
-      <c r="D53" s="36" t="b">
-        <v>0</v>
-      </c>
-      <c r="E53" s="36">
-        <v>0</v>
-      </c>
-      <c r="F53" s="37" t="s">
+      <c r="D53" s="39" t="b">
+        <v>0</v>
+      </c>
+      <c r="E53" s="39">
+        <v>0</v>
+      </c>
+      <c r="F53" s="40" t="s">
         <v>254</v>
       </c>
-      <c r="G53" s="36" t="s">
+      <c r="G53" s="39" t="s">
         <v>11</v>
       </c>
-      <c r="H53" s="36">
+      <c r="H53" s="39">
         <v>0</v>
       </c>
     </row>
     <row r="54" ht="26" spans="1:8">
-      <c r="A54" s="38" t="s">
+      <c r="A54" s="41" t="s">
         <v>255</v>
       </c>
-      <c r="B54" s="38" t="s">
+      <c r="B54" s="41" t="s">
         <v>255</v>
       </c>
-      <c r="C54" s="38" t="s">
+      <c r="C54" s="41" t="s">
         <v>256</v>
       </c>
-      <c r="D54" s="38" t="b">
-        <v>0</v>
-      </c>
-      <c r="E54" s="38">
-        <v>0</v>
-      </c>
-      <c r="F54" s="39" t="s">
+      <c r="D54" s="41" t="b">
+        <v>0</v>
+      </c>
+      <c r="E54" s="41">
+        <v>0</v>
+      </c>
+      <c r="F54" s="42" t="s">
         <v>257</v>
       </c>
-      <c r="G54" s="38" t="s">
+      <c r="G54" s="41" t="s">
         <v>11</v>
       </c>
-      <c r="H54" s="38">
+      <c r="H54" s="41">
         <v>0</v>
       </c>
     </row>
     <row r="55" ht="39" spans="1:8">
-      <c r="A55" s="36" t="s">
+      <c r="A55" s="39" t="s">
         <v>258</v>
       </c>
-      <c r="B55" s="36" t="s">
+      <c r="B55" s="39" t="s">
         <v>258</v>
       </c>
-      <c r="C55" s="36" t="s">
+      <c r="C55" s="39" t="s">
         <v>259</v>
       </c>
-      <c r="D55" s="36" t="b">
-        <v>0</v>
-      </c>
-      <c r="E55" s="36">
-        <v>0</v>
-      </c>
-      <c r="F55" s="37" t="s">
+      <c r="D55" s="39" t="b">
+        <v>0</v>
+      </c>
+      <c r="E55" s="39">
+        <v>0</v>
+      </c>
+      <c r="F55" s="40" t="s">
         <v>260</v>
       </c>
-      <c r="G55" s="36" t="s">
+      <c r="G55" s="39" t="s">
         <v>11</v>
       </c>
-      <c r="H55" s="36">
+      <c r="H55" s="39">
         <v>0</v>
       </c>
     </row>
     <row r="56" ht="26" spans="1:8">
-      <c r="A56" s="38" t="s">
+      <c r="A56" s="41" t="s">
         <v>261</v>
       </c>
-      <c r="B56" s="38" t="s">
+      <c r="B56" s="41" t="s">
         <v>261</v>
       </c>
-      <c r="C56" s="38" t="s">
+      <c r="C56" s="41" t="s">
         <v>262</v>
       </c>
-      <c r="D56" s="38" t="b">
-        <v>0</v>
-      </c>
-      <c r="E56" s="38">
-        <v>0</v>
-      </c>
-      <c r="F56" s="39" t="s">
+      <c r="D56" s="41" t="b">
+        <v>0</v>
+      </c>
+      <c r="E56" s="41">
+        <v>0</v>
+      </c>
+      <c r="F56" s="42" t="s">
         <v>263</v>
       </c>
-      <c r="G56" s="38" t="s">
+      <c r="G56" s="41" t="s">
         <v>11</v>
       </c>
-      <c r="H56" s="38">
+      <c r="H56" s="41">
         <v>0</v>
       </c>
     </row>
     <row r="57" ht="26" spans="1:8">
-      <c r="A57" s="36" t="s">
+      <c r="A57" s="39" t="s">
         <v>264</v>
       </c>
-      <c r="B57" s="36" t="s">
+      <c r="B57" s="39" t="s">
         <v>264</v>
       </c>
-      <c r="C57" s="36" t="s">
+      <c r="C57" s="39" t="s">
         <v>265</v>
       </c>
-      <c r="D57" s="36" t="b">
-        <v>0</v>
-      </c>
-      <c r="E57" s="36">
-        <v>0</v>
-      </c>
-      <c r="F57" s="37" t="s">
+      <c r="D57" s="39" t="b">
+        <v>0</v>
+      </c>
+      <c r="E57" s="39">
+        <v>0</v>
+      </c>
+      <c r="F57" s="40" t="s">
         <v>266</v>
       </c>
-      <c r="G57" s="36" t="s">
+      <c r="G57" s="39" t="s">
         <v>11</v>
       </c>
-      <c r="H57" s="36">
+      <c r="H57" s="39">
         <v>0</v>
       </c>
     </row>
     <row r="58" ht="26" spans="1:8">
-      <c r="A58" s="38" t="s">
+      <c r="A58" s="41" t="s">
         <v>267</v>
       </c>
-      <c r="B58" s="38" t="s">
+      <c r="B58" s="41" t="s">
         <v>267</v>
       </c>
-      <c r="C58" s="38" t="s">
+      <c r="C58" s="41" t="s">
         <v>268</v>
       </c>
-      <c r="D58" s="38" t="b">
-        <v>0</v>
-      </c>
-      <c r="E58" s="38">
-        <v>0</v>
-      </c>
-      <c r="F58" s="39" t="s">
+      <c r="D58" s="41" t="b">
+        <v>0</v>
+      </c>
+      <c r="E58" s="41">
+        <v>0</v>
+      </c>
+      <c r="F58" s="42" t="s">
         <v>269</v>
       </c>
-      <c r="G58" s="38" t="s">
+      <c r="G58" s="41" t="s">
         <v>11</v>
       </c>
-      <c r="H58" s="38">
+      <c r="H58" s="41">
         <v>0</v>
       </c>
     </row>
     <row r="59" ht="30" spans="1:8">
-      <c r="A59" s="36" t="s">
+      <c r="A59" s="39" t="s">
         <v>270</v>
       </c>
-      <c r="B59" s="36" t="s">
+      <c r="B59" s="39" t="s">
         <v>270</v>
       </c>
-      <c r="C59" s="36" t="s">
+      <c r="C59" s="39" t="s">
         <v>271</v>
       </c>
-      <c r="D59" s="36" t="b">
-        <v>0</v>
-      </c>
-      <c r="E59" s="36">
-        <v>0</v>
-      </c>
-      <c r="F59" s="37" t="s">
+      <c r="D59" s="39" t="b">
+        <v>0</v>
+      </c>
+      <c r="E59" s="39">
+        <v>0</v>
+      </c>
+      <c r="F59" s="40" t="s">
         <v>272</v>
       </c>
-      <c r="G59" s="36" t="s">
+      <c r="G59" s="39" t="s">
         <v>11</v>
       </c>
-      <c r="H59" s="36">
+      <c r="H59" s="39">
         <v>0</v>
       </c>
     </row>
     <row r="60" spans="1:8">
-      <c r="A60" s="38" t="s">
+      <c r="A60" s="41" t="s">
         <v>273</v>
       </c>
-      <c r="B60" s="38" t="s">
+      <c r="B60" s="41" t="s">
         <v>273</v>
       </c>
-      <c r="C60" s="38" t="s">
+      <c r="C60" s="41" t="s">
         <v>274</v>
       </c>
-      <c r="D60" s="38" t="b">
-        <v>0</v>
-      </c>
-      <c r="E60" s="38">
-        <v>0</v>
-      </c>
-      <c r="F60" s="39" t="s">
+      <c r="D60" s="41" t="b">
+        <v>0</v>
+      </c>
+      <c r="E60" s="41">
+        <v>0</v>
+      </c>
+      <c r="F60" s="42" t="s">
         <v>275</v>
       </c>
-      <c r="G60" s="38" t="s">
+      <c r="G60" s="41" t="s">
         <v>11</v>
       </c>
-      <c r="H60" s="38">
+      <c r="H60" s="41">
         <v>0</v>
       </c>
     </row>
     <row r="61" ht="52" spans="1:8">
-      <c r="A61" s="36" t="s">
+      <c r="A61" s="39" t="s">
         <v>276</v>
       </c>
-      <c r="B61" s="36" t="s">
+      <c r="B61" s="39" t="s">
         <v>276</v>
       </c>
-      <c r="C61" s="36" t="s">
+      <c r="C61" s="39" t="s">
         <v>277</v>
       </c>
-      <c r="D61" s="36" t="b">
-        <v>0</v>
-      </c>
-      <c r="E61" s="36">
-        <v>0</v>
-      </c>
-      <c r="F61" s="37" t="s">
+      <c r="D61" s="39" t="b">
+        <v>0</v>
+      </c>
+      <c r="E61" s="39">
+        <v>0</v>
+      </c>
+      <c r="F61" s="40" t="s">
         <v>278</v>
       </c>
-      <c r="G61" s="36" t="s">
+      <c r="G61" s="39" t="s">
         <v>11</v>
       </c>
-      <c r="H61" s="36">
+      <c r="H61" s="39">
         <v>0</v>
       </c>
     </row>
     <row r="62" ht="26" spans="1:8">
-      <c r="A62" s="38" t="s">
+      <c r="A62" s="41" t="s">
         <v>279</v>
       </c>
-      <c r="B62" s="38" t="s">
+      <c r="B62" s="41" t="s">
         <v>279</v>
       </c>
-      <c r="C62" s="38" t="s">
+      <c r="C62" s="41" t="s">
         <v>280</v>
       </c>
-      <c r="D62" s="38" t="b">
-        <v>0</v>
-      </c>
-      <c r="E62" s="38">
-        <v>0</v>
-      </c>
-      <c r="F62" s="39" t="s">
+      <c r="D62" s="41" t="b">
+        <v>0</v>
+      </c>
+      <c r="E62" s="41">
+        <v>0</v>
+      </c>
+      <c r="F62" s="42" t="s">
         <v>281</v>
       </c>
-      <c r="G62" s="38" t="s">
+      <c r="G62" s="41" t="s">
         <v>11</v>
       </c>
-      <c r="H62" s="38">
+      <c r="H62" s="41">
         <v>0</v>
       </c>
     </row>
     <row r="63" ht="39" spans="1:8">
-      <c r="A63" s="36" t="s">
+      <c r="A63" s="39" t="s">
         <v>282</v>
       </c>
-      <c r="B63" s="36" t="s">
+      <c r="B63" s="39" t="s">
         <v>282</v>
       </c>
-      <c r="C63" s="36" t="s">
+      <c r="C63" s="39" t="s">
         <v>283</v>
       </c>
-      <c r="D63" s="36" t="b">
-        <v>0</v>
-      </c>
-      <c r="E63" s="36">
-        <v>0</v>
-      </c>
-      <c r="F63" s="37" t="s">
+      <c r="D63" s="39" t="b">
+        <v>0</v>
+      </c>
+      <c r="E63" s="39">
+        <v>0</v>
+      </c>
+      <c r="F63" s="40" t="s">
         <v>284</v>
       </c>
-      <c r="G63" s="36" t="s">
+      <c r="G63" s="39" t="s">
         <v>11</v>
       </c>
-      <c r="H63" s="36">
+      <c r="H63" s="39">
         <v>0</v>
       </c>
     </row>
     <row r="64" spans="1:8">
-      <c r="A64" s="38" t="s">
+      <c r="A64" s="41" t="s">
         <v>285</v>
       </c>
-      <c r="B64" s="38" t="s">
+      <c r="B64" s="41" t="s">
         <v>285</v>
       </c>
-      <c r="C64" s="38" t="s">
+      <c r="C64" s="41" t="s">
         <v>286</v>
       </c>
-      <c r="D64" s="38" t="b">
-        <v>0</v>
-      </c>
-      <c r="E64" s="38">
-        <v>0</v>
-      </c>
-      <c r="F64" s="39" t="s">
+      <c r="D64" s="41" t="b">
+        <v>0</v>
+      </c>
+      <c r="E64" s="41">
+        <v>0</v>
+      </c>
+      <c r="F64" s="42" t="s">
         <v>287</v>
       </c>
-      <c r="G64" s="38" t="s">
+      <c r="G64" s="41" t="s">
         <v>11</v>
       </c>
-      <c r="H64" s="38">
+      <c r="H64" s="41">
         <v>0</v>
       </c>
     </row>
     <row r="65" ht="26" spans="1:8">
-      <c r="A65" s="36" t="s">
+      <c r="A65" s="39" t="s">
         <v>288</v>
       </c>
-      <c r="B65" s="36" t="s">
+      <c r="B65" s="39" t="s">
         <v>288</v>
       </c>
-      <c r="C65" s="36" t="s">
+      <c r="C65" s="39" t="s">
         <v>289</v>
       </c>
-      <c r="D65" s="36" t="b">
-        <v>0</v>
-      </c>
-      <c r="E65" s="36">
-        <v>0</v>
-      </c>
-      <c r="F65" s="37" t="s">
+      <c r="D65" s="39" t="b">
+        <v>0</v>
+      </c>
+      <c r="E65" s="39">
+        <v>0</v>
+      </c>
+      <c r="F65" s="40" t="s">
         <v>290</v>
       </c>
-      <c r="G65" s="36" t="s">
+      <c r="G65" s="39" t="s">
         <v>11</v>
       </c>
-      <c r="H65" s="36">
+      <c r="H65" s="39">
         <v>0</v>
       </c>
     </row>
     <row r="66" ht="39" spans="1:8">
-      <c r="A66" s="38" t="s">
+      <c r="A66" s="41" t="s">
         <v>291</v>
       </c>
-      <c r="B66" s="38" t="s">
+      <c r="B66" s="41" t="s">
         <v>291</v>
       </c>
-      <c r="C66" s="38" t="s">
+      <c r="C66" s="41" t="s">
         <v>292</v>
       </c>
-      <c r="D66" s="38" t="b">
-        <v>0</v>
-      </c>
-      <c r="E66" s="38">
-        <v>0</v>
-      </c>
-      <c r="F66" s="39" t="s">
+      <c r="D66" s="41" t="b">
+        <v>0</v>
+      </c>
+      <c r="E66" s="41">
+        <v>0</v>
+      </c>
+      <c r="F66" s="42" t="s">
         <v>293</v>
       </c>
-      <c r="G66" s="38" t="s">
+      <c r="G66" s="41" t="s">
         <v>11</v>
       </c>
-      <c r="H66" s="38">
+      <c r="H66" s="41">
         <v>0</v>
       </c>
     </row>
     <row r="67" ht="52" spans="1:8">
-      <c r="A67" s="36" t="s">
+      <c r="A67" s="39" t="s">
         <v>294</v>
       </c>
-      <c r="B67" s="36" t="s">
+      <c r="B67" s="39" t="s">
         <v>294</v>
       </c>
-      <c r="C67" s="36" t="s">
+      <c r="C67" s="39" t="s">
         <v>295</v>
       </c>
-      <c r="D67" s="36" t="b">
-        <v>0</v>
-      </c>
-      <c r="E67" s="36">
-        <v>0</v>
-      </c>
-      <c r="F67" s="37" t="s">
+      <c r="D67" s="39" t="b">
+        <v>0</v>
+      </c>
+      <c r="E67" s="39">
+        <v>0</v>
+      </c>
+      <c r="F67" s="40" t="s">
         <v>296</v>
       </c>
-      <c r="G67" s="36" t="s">
+      <c r="G67" s="39" t="s">
         <v>11</v>
       </c>
-      <c r="H67" s="36">
+      <c r="H67" s="39">
         <v>0</v>
       </c>
     </row>
     <row r="68" ht="47" spans="1:8">
-      <c r="A68" s="32" t="s">
+      <c r="A68" s="35" t="s">
         <v>297</v>
       </c>
-      <c r="B68" s="32" t="s">
+      <c r="B68" s="35" t="s">
         <v>297</v>
       </c>
-      <c r="C68" s="32" t="s">
+      <c r="C68" s="35" t="s">
         <v>298</v>
       </c>
-      <c r="D68" s="32" t="b">
+      <c r="D68" s="35" t="b">
         <v>1</v>
       </c>
-      <c r="E68" s="32">
+      <c r="E68" s="35">
         <v>2</v>
       </c>
-      <c r="F68" s="33" t="s">
+      <c r="F68" s="36" t="s">
         <v>299</v>
       </c>
-      <c r="G68" s="32" t="s">
+      <c r="G68" s="35" t="s">
         <v>11</v>
       </c>
-      <c r="H68" s="32">
+      <c r="H68" s="35">
         <v>0</v>
       </c>
     </row>
     <row r="69" ht="26" spans="1:8">
-      <c r="A69" s="34" t="s">
+      <c r="A69" s="37" t="s">
         <v>300</v>
       </c>
-      <c r="B69" s="34" t="s">
+      <c r="B69" s="37" t="s">
         <v>300</v>
       </c>
-      <c r="C69" s="34" t="s">
+      <c r="C69" s="37" t="s">
         <v>301</v>
       </c>
-      <c r="D69" s="34" t="b">
-        <v>0</v>
-      </c>
-      <c r="E69" s="34">
-        <v>0</v>
-      </c>
-      <c r="F69" s="35" t="s">
+      <c r="D69" s="37" t="b">
+        <v>0</v>
+      </c>
+      <c r="E69" s="37">
+        <v>0</v>
+      </c>
+      <c r="F69" s="38" t="s">
         <v>302</v>
       </c>
-      <c r="G69" s="34" t="s">
+      <c r="G69" s="37" t="s">
         <v>11</v>
       </c>
-      <c r="H69" s="34">
+      <c r="H69" s="37">
         <v>0</v>
       </c>
     </row>
     <row r="70" ht="31" customHeight="1" spans="1:8">
-      <c r="A70" s="32" t="s">
+      <c r="A70" s="35" t="s">
         <v>303</v>
       </c>
-      <c r="B70" s="32" t="s">
+      <c r="B70" s="35" t="s">
         <v>303</v>
       </c>
-      <c r="C70" s="32" t="s">
+      <c r="C70" s="35" t="s">
         <v>22</v>
       </c>
-      <c r="D70" s="32" t="b">
+      <c r="D70" s="35" t="b">
         <v>1</v>
       </c>
-      <c r="E70" s="32">
+      <c r="E70" s="35">
         <v>1</v>
       </c>
-      <c r="F70" s="33" t="s">
+      <c r="F70" s="36" t="s">
         <v>304</v>
       </c>
-      <c r="G70" s="32" t="s">
+      <c r="G70" s="35" t="s">
         <v>11</v>
       </c>
-      <c r="H70" s="32">
+      <c r="H70" s="35">
         <v>0</v>
       </c>
     </row>
     <row r="71" ht="91" spans="1:8">
-      <c r="A71" s="34" t="s">
+      <c r="A71" s="37" t="s">
         <v>305</v>
       </c>
-      <c r="B71" s="34" t="s">
+      <c r="B71" s="37" t="s">
         <v>305</v>
       </c>
-      <c r="C71" s="34" t="s">
+      <c r="C71" s="37" t="s">
         <v>306</v>
       </c>
-      <c r="D71" s="34" t="b">
-        <v>0</v>
-      </c>
-      <c r="E71" s="34">
-        <v>0</v>
-      </c>
-      <c r="F71" s="35" t="s">
+      <c r="D71" s="37" t="b">
+        <v>0</v>
+      </c>
+      <c r="E71" s="37">
+        <v>0</v>
+      </c>
+      <c r="F71" s="38" t="s">
         <v>307</v>
       </c>
-      <c r="G71" s="34" t="s">
+      <c r="G71" s="37" t="s">
         <v>11</v>
       </c>
-      <c r="H71" s="34">
+      <c r="H71" s="37">
         <v>0</v>
       </c>
     </row>
     <row r="72" ht="39" spans="1:8">
-      <c r="A72" s="32" t="s">
+      <c r="A72" s="35" t="s">
         <v>308</v>
       </c>
-      <c r="B72" s="32" t="s">
+      <c r="B72" s="35" t="s">
         <v>308</v>
       </c>
-      <c r="C72" s="32" t="s">
+      <c r="C72" s="35" t="s">
         <v>309</v>
       </c>
-      <c r="D72" s="32" t="b">
-        <v>0</v>
-      </c>
-      <c r="E72" s="32">
-        <v>0</v>
-      </c>
-      <c r="F72" s="33" t="s">
+      <c r="D72" s="35" t="b">
+        <v>0</v>
+      </c>
+      <c r="E72" s="35">
+        <v>0</v>
+      </c>
+      <c r="F72" s="36" t="s">
         <v>310</v>
       </c>
-      <c r="G72" s="32" t="s">
+      <c r="G72" s="35" t="s">
         <v>11</v>
       </c>
-      <c r="H72" s="32">
+      <c r="H72" s="35">
         <v>0</v>
       </c>
     </row>
     <row r="73" spans="1:8">
-      <c r="A73" s="34" t="s">
+      <c r="A73" s="37" t="s">
         <v>311</v>
       </c>
-      <c r="B73" s="34" t="s">
+      <c r="B73" s="37" t="s">
         <v>311</v>
       </c>
-      <c r="C73" s="34" t="s">
+      <c r="C73" s="37" t="s">
         <v>312</v>
       </c>
-      <c r="D73" s="34" t="b">
-        <v>0</v>
-      </c>
-      <c r="E73" s="34">
-        <v>0</v>
-      </c>
-      <c r="F73" s="35" t="s">
+      <c r="D73" s="37" t="b">
+        <v>0</v>
+      </c>
+      <c r="E73" s="37">
+        <v>0</v>
+      </c>
+      <c r="F73" s="38" t="s">
         <v>313</v>
       </c>
-      <c r="G73" s="34" t="s">
+      <c r="G73" s="37" t="s">
         <v>11</v>
       </c>
-      <c r="H73" s="34">
+      <c r="H73" s="37">
         <v>0</v>
       </c>
     </row>
     <row r="74" ht="17" spans="1:8">
-      <c r="A74" s="32" t="s">
+      <c r="A74" s="35" t="s">
         <v>314</v>
       </c>
-      <c r="B74" s="32" t="s">
+      <c r="B74" s="35" t="s">
         <v>314</v>
       </c>
-      <c r="C74" s="32" t="s">
+      <c r="C74" s="35" t="s">
         <v>315</v>
       </c>
-      <c r="D74" s="32" t="b">
+      <c r="D74" s="35" t="b">
         <v>1</v>
       </c>
-      <c r="E74" s="32">
+      <c r="E74" s="35">
         <v>1</v>
       </c>
-      <c r="F74" s="33" t="s">
+      <c r="F74" s="36" t="s">
         <v>316</v>
       </c>
-      <c r="G74" s="32" t="s">
+      <c r="G74" s="35" t="s">
         <v>11</v>
       </c>
-      <c r="H74" s="32">
+      <c r="H74" s="35">
         <v>0</v>
       </c>
     </row>
     <row r="75" spans="1:8">
-      <c r="A75" s="34" t="s">
+      <c r="A75" s="37" t="s">
         <v>317</v>
       </c>
-      <c r="B75" s="34" t="s">
+      <c r="B75" s="37" t="s">
         <v>317</v>
       </c>
-      <c r="C75" s="34" t="s">
+      <c r="C75" s="37" t="s">
         <v>318</v>
       </c>
-      <c r="D75" s="34" t="b">
-        <v>0</v>
-      </c>
-      <c r="E75" s="34">
-        <v>0</v>
-      </c>
-      <c r="F75" s="35" t="s">
+      <c r="D75" s="37" t="b">
+        <v>0</v>
+      </c>
+      <c r="E75" s="37">
+        <v>0</v>
+      </c>
+      <c r="F75" s="38" t="s">
         <v>319</v>
       </c>
-      <c r="G75" s="34" t="s">
+      <c r="G75" s="37" t="s">
         <v>11</v>
       </c>
-      <c r="H75" s="34">
+      <c r="H75" s="37">
         <v>0</v>
       </c>
     </row>
     <row r="76" spans="1:8">
-      <c r="A76" s="32" t="s">
+      <c r="A76" s="35" t="s">
         <v>320</v>
       </c>
-      <c r="B76" s="32" t="s">
+      <c r="B76" s="35" t="s">
         <v>320</v>
       </c>
-      <c r="C76" s="32" t="s">
+      <c r="C76" s="35" t="s">
         <v>25</v>
       </c>
-      <c r="D76" s="32" t="b">
-        <v>0</v>
-      </c>
-      <c r="E76" s="32">
-        <v>0</v>
-      </c>
-      <c r="F76" s="33" t="s">
+      <c r="D76" s="35" t="b">
+        <v>0</v>
+      </c>
+      <c r="E76" s="35">
+        <v>0</v>
+      </c>
+      <c r="F76" s="36" t="s">
         <v>26</v>
       </c>
-      <c r="G76" s="32" t="s">
+      <c r="G76" s="35" t="s">
         <v>11</v>
       </c>
-      <c r="H76" s="32">
+      <c r="H76" s="35">
         <v>0</v>
       </c>
     </row>
     <row r="77" ht="26" spans="1:8">
-      <c r="A77" s="34" t="s">
+      <c r="A77" s="37" t="s">
         <v>321</v>
       </c>
-      <c r="B77" s="34" t="s">
+      <c r="B77" s="37" t="s">
         <v>321</v>
       </c>
-      <c r="C77" s="34" t="s">
+      <c r="C77" s="37" t="s">
         <v>322</v>
       </c>
-      <c r="D77" s="34" t="b">
-        <v>0</v>
-      </c>
-      <c r="E77" s="34">
-        <v>0</v>
-      </c>
-      <c r="F77" s="35" t="s">
+      <c r="D77" s="37" t="b">
+        <v>0</v>
+      </c>
+      <c r="E77" s="37">
+        <v>0</v>
+      </c>
+      <c r="F77" s="38" t="s">
         <v>323</v>
       </c>
-      <c r="G77" s="34" t="s">
+      <c r="G77" s="37" t="s">
         <v>11</v>
       </c>
-      <c r="H77" s="34">
+      <c r="H77" s="37">
         <v>1</v>
       </c>
     </row>
     <row r="78" ht="26" spans="1:8">
-      <c r="A78" s="32" t="s">
+      <c r="A78" s="35" t="s">
         <v>324</v>
       </c>
-      <c r="B78" s="32" t="s">
+      <c r="B78" s="35" t="s">
         <v>324</v>
       </c>
-      <c r="C78" s="32" t="s">
+      <c r="C78" s="35" t="s">
         <v>325</v>
       </c>
-      <c r="D78" s="32" t="b">
-        <v>0</v>
-      </c>
-      <c r="E78" s="32">
-        <v>0</v>
-      </c>
-      <c r="F78" s="33" t="s">
+      <c r="D78" s="35" t="b">
+        <v>0</v>
+      </c>
+      <c r="E78" s="35">
+        <v>0</v>
+      </c>
+      <c r="F78" s="36" t="s">
         <v>326</v>
       </c>
-      <c r="G78" s="32" t="s">
+      <c r="G78" s="35" t="s">
         <v>11</v>
       </c>
-      <c r="H78" s="32">
+      <c r="H78" s="35">
         <v>0</v>
       </c>
     </row>
     <row r="79" ht="65" spans="1:8">
-      <c r="A79" s="34" t="s">
+      <c r="A79" s="37" t="s">
         <v>327</v>
       </c>
-      <c r="B79" s="34" t="s">
+      <c r="B79" s="37" t="s">
         <v>327</v>
       </c>
-      <c r="C79" s="34" t="s">
+      <c r="C79" s="37" t="s">
         <v>328</v>
       </c>
-      <c r="D79" s="34" t="b">
-        <v>0</v>
-      </c>
-      <c r="E79" s="34">
-        <v>0</v>
-      </c>
-      <c r="F79" s="35" t="s">
+      <c r="D79" s="37" t="b">
+        <v>0</v>
+      </c>
+      <c r="E79" s="37">
+        <v>0</v>
+      </c>
+      <c r="F79" s="38" t="s">
         <v>329</v>
       </c>
-      <c r="G79" s="34" t="s">
+      <c r="G79" s="37" t="s">
         <v>11</v>
       </c>
-      <c r="H79" s="34">
+      <c r="H79" s="37">
         <v>0</v>
       </c>
     </row>
     <row r="80" ht="39" spans="1:8">
-      <c r="A80" s="32" t="s">
+      <c r="A80" s="35" t="s">
         <v>330</v>
       </c>
-      <c r="B80" s="32" t="s">
+      <c r="B80" s="35" t="s">
         <v>330</v>
       </c>
-      <c r="C80" s="32" t="s">
+      <c r="C80" s="35" t="s">
         <v>331</v>
       </c>
-      <c r="D80" s="32" t="b">
-        <v>0</v>
-      </c>
-      <c r="E80" s="32">
-        <v>0</v>
-      </c>
-      <c r="F80" s="33" t="s">
+      <c r="D80" s="35" t="b">
+        <v>0</v>
+      </c>
+      <c r="E80" s="35">
+        <v>0</v>
+      </c>
+      <c r="F80" s="36" t="s">
         <v>332</v>
       </c>
-      <c r="G80" s="32" t="s">
+      <c r="G80" s="35" t="s">
         <v>11</v>
       </c>
-      <c r="H80" s="32">
+      <c r="H80" s="35">
         <v>0</v>
       </c>
     </row>
     <row r="81" ht="26" spans="1:8">
-      <c r="A81" s="34" t="s">
+      <c r="A81" s="37" t="s">
         <v>333</v>
       </c>
-      <c r="B81" s="34" t="s">
+      <c r="B81" s="37" t="s">
         <v>333</v>
       </c>
-      <c r="C81" s="34" t="s">
+      <c r="C81" s="37" t="s">
         <v>334</v>
       </c>
-      <c r="D81" s="34" t="b">
-        <v>0</v>
-      </c>
-      <c r="E81" s="34">
-        <v>0</v>
-      </c>
-      <c r="F81" s="35" t="s">
+      <c r="D81" s="37" t="b">
+        <v>0</v>
+      </c>
+      <c r="E81" s="37">
+        <v>0</v>
+      </c>
+      <c r="F81" s="38" t="s">
         <v>335</v>
       </c>
-      <c r="G81" s="34" t="s">
+      <c r="G81" s="37" t="s">
         <v>11</v>
       </c>
-      <c r="H81" s="34">
+      <c r="H81" s="37">
         <v>0</v>
       </c>
     </row>
     <row r="82" ht="26" spans="1:8">
-      <c r="A82" s="32" t="s">
+      <c r="A82" s="35" t="s">
         <v>336</v>
       </c>
-      <c r="B82" s="32" t="s">
+      <c r="B82" s="35" t="s">
         <v>336</v>
       </c>
-      <c r="C82" s="32" t="s">
+      <c r="C82" s="35" t="s">
         <v>337</v>
       </c>
-      <c r="D82" s="32" t="b">
-        <v>0</v>
-      </c>
-      <c r="E82" s="32">
-        <v>0</v>
-      </c>
-      <c r="F82" s="33" t="s">
+      <c r="D82" s="35" t="b">
+        <v>0</v>
+      </c>
+      <c r="E82" s="35">
+        <v>0</v>
+      </c>
+      <c r="F82" s="36" t="s">
         <v>338</v>
       </c>
-      <c r="G82" s="32" t="s">
+      <c r="G82" s="35" t="s">
         <v>11</v>
       </c>
-      <c r="H82" s="32">
+      <c r="H82" s="35">
         <v>1</v>
       </c>
     </row>
     <row r="83" spans="1:8">
-      <c r="A83" s="34" t="s">
+      <c r="A83" s="37" t="s">
         <v>339</v>
       </c>
-      <c r="B83" s="34" t="s">
+      <c r="B83" s="37" t="s">
         <v>339</v>
       </c>
-      <c r="C83" s="34" t="s">
+      <c r="C83" s="37" t="s">
         <v>340</v>
       </c>
-      <c r="D83" s="34" t="b">
-        <v>0</v>
-      </c>
-      <c r="E83" s="34">
-        <v>0</v>
-      </c>
-      <c r="F83" s="35" t="s">
+      <c r="D83" s="37" t="b">
+        <v>0</v>
+      </c>
+      <c r="E83" s="37">
+        <v>0</v>
+      </c>
+      <c r="F83" s="38" t="s">
         <v>287</v>
       </c>
-      <c r="G83" s="34" t="s">
+      <c r="G83" s="37" t="s">
         <v>11</v>
       </c>
-      <c r="H83" s="34">
+      <c r="H83" s="37">
         <v>0</v>
       </c>
     </row>
     <row r="84" ht="26" spans="1:8">
-      <c r="A84" s="32" t="s">
+      <c r="A84" s="35" t="s">
         <v>341</v>
       </c>
-      <c r="B84" s="32" t="s">
+      <c r="B84" s="35" t="s">
         <v>341</v>
       </c>
-      <c r="C84" s="32" t="s">
+      <c r="C84" s="35" t="s">
         <v>342</v>
       </c>
-      <c r="D84" s="32" t="b">
+      <c r="D84" s="35" t="b">
         <v>1</v>
       </c>
-      <c r="E84" s="32">
+      <c r="E84" s="35">
         <v>1</v>
       </c>
-      <c r="F84" s="33" t="s">
+      <c r="F84" s="36" t="s">
         <v>343</v>
       </c>
-      <c r="G84" s="32" t="s">
+      <c r="G84" s="35" t="s">
         <v>11</v>
       </c>
-      <c r="H84" s="32">
+      <c r="H84" s="35">
         <v>3</v>
       </c>
     </row>
     <row r="85" ht="78" spans="1:8">
-      <c r="A85" s="32" t="s">
+      <c r="A85" s="35" t="s">
         <v>344</v>
       </c>
-      <c r="B85" s="32" t="s">
+      <c r="B85" s="35" t="s">
         <v>344</v>
       </c>
-      <c r="C85" s="32" t="s">
+      <c r="C85" s="35" t="s">
         <v>345</v>
       </c>
-      <c r="D85" s="32" t="b">
-        <v>0</v>
-      </c>
-      <c r="E85" s="32">
-        <v>0</v>
-      </c>
-      <c r="F85" s="33" t="s">
+      <c r="D85" s="35" t="b">
+        <v>0</v>
+      </c>
+      <c r="E85" s="35">
+        <v>0</v>
+      </c>
+      <c r="F85" s="36" t="s">
         <v>346</v>
       </c>
-      <c r="G85" s="32" t="s">
+      <c r="G85" s="35" t="s">
         <v>11</v>
       </c>
-      <c r="H85" s="32">
+      <c r="H85" s="35">
         <v>0</v>
       </c>
     </row>
     <row r="86" ht="44" customHeight="1" spans="1:8">
-      <c r="A86" s="34" t="s">
+      <c r="A86" s="37" t="s">
         <v>347</v>
       </c>
-      <c r="B86" s="34" t="s">
+      <c r="B86" s="37" t="s">
         <v>347</v>
       </c>
-      <c r="C86" s="34" t="s">
+      <c r="C86" s="37" t="s">
         <v>348</v>
       </c>
-      <c r="D86" s="34" t="b">
+      <c r="D86" s="37" t="b">
         <v>1</v>
       </c>
-      <c r="E86" s="34">
+      <c r="E86" s="37">
         <v>1</v>
       </c>
-      <c r="F86" s="35" t="s">
+      <c r="F86" s="38" t="s">
         <v>349</v>
       </c>
-      <c r="G86" s="34" t="s">
+      <c r="G86" s="37" t="s">
         <v>11</v>
       </c>
-      <c r="H86" s="34">
+      <c r="H86" s="37">
         <v>0</v>
       </c>
     </row>
@@ -7897,7 +7939,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G55"/>
+  <dimension ref="A1:G56"/>
   <sheetFormatPr defaultColWidth="8.25" defaultRowHeight="14" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="20.75" style="10" customWidth="1"/>
@@ -8075,1103 +8117,1124 @@
       <c r="A8" s="22" t="s">
         <v>379</v>
       </c>
-      <c r="B8" s="23" t="s">
+      <c r="B8" s="22" t="s">
         <v>379</v>
       </c>
-      <c r="C8" s="24" t="s">
+      <c r="C8" s="23" t="s">
         <v>380</v>
       </c>
-      <c r="D8" s="24" t="s">
+      <c r="D8" s="23"/>
+      <c r="E8" s="23">
+        <v>3</v>
+      </c>
+      <c r="F8" s="24" t="s">
         <v>381</v>
       </c>
-      <c r="E8" s="24">
+      <c r="G8" s="24" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9" s="25" t="s">
+        <v>382</v>
+      </c>
+      <c r="B9" s="26" t="s">
+        <v>382</v>
+      </c>
+      <c r="C9" s="27" t="s">
+        <v>383</v>
+      </c>
+      <c r="D9" s="27" t="s">
+        <v>384</v>
+      </c>
+      <c r="E9" s="27">
         <v>50</v>
       </c>
-      <c r="F8" s="25" t="s">
-        <v>382</v>
-      </c>
-      <c r="G8" s="25" t="s">
+      <c r="F9" s="28" t="s">
+        <v>385</v>
+      </c>
+      <c r="G9" s="28" t="s">
         <v>357</v>
       </c>
     </row>
-    <row r="9" spans="1:7">
-      <c r="A9" s="26" t="s">
-        <v>383</v>
-      </c>
-      <c r="B9" s="27" t="s">
-        <v>383</v>
-      </c>
-      <c r="C9" s="28" t="s">
-        <v>384</v>
-      </c>
-      <c r="D9" s="28" t="s">
-        <v>385</v>
-      </c>
-      <c r="E9" s="28">
+    <row r="10" spans="1:7">
+      <c r="A10" s="29" t="s">
+        <v>386</v>
+      </c>
+      <c r="B10" s="30" t="s">
+        <v>386</v>
+      </c>
+      <c r="C10" s="31" t="s">
+        <v>387</v>
+      </c>
+      <c r="D10" s="31" t="s">
+        <v>388</v>
+      </c>
+      <c r="E10" s="31">
         <v>55</v>
       </c>
-      <c r="F9" s="29" t="s">
-        <v>386</v>
-      </c>
-      <c r="G9" s="29" t="s">
+      <c r="F10" s="32" t="s">
+        <v>389</v>
+      </c>
+      <c r="G10" s="32" t="s">
         <v>357</v>
       </c>
     </row>
-    <row r="10" ht="17" spans="1:7">
-      <c r="A10" s="22" t="s">
-        <v>387</v>
-      </c>
-      <c r="B10" s="23" t="s">
-        <v>387</v>
-      </c>
-      <c r="C10" s="24" t="s">
-        <v>388</v>
-      </c>
-      <c r="D10" s="24" t="s">
-        <v>389</v>
-      </c>
-      <c r="E10" s="24">
+    <row r="11" ht="17" spans="1:7">
+      <c r="A11" s="25" t="s">
+        <v>390</v>
+      </c>
+      <c r="B11" s="26" t="s">
+        <v>390</v>
+      </c>
+      <c r="C11" s="27" t="s">
+        <v>391</v>
+      </c>
+      <c r="D11" s="27" t="s">
+        <v>392</v>
+      </c>
+      <c r="E11" s="27">
         <v>35</v>
       </c>
-      <c r="F10" s="25" t="s">
-        <v>390</v>
-      </c>
-      <c r="G10" s="25" t="s">
+      <c r="F11" s="28" t="s">
+        <v>393</v>
+      </c>
+      <c r="G11" s="28" t="s">
         <v>357</v>
       </c>
     </row>
-    <row r="11" spans="1:7">
-      <c r="A11" s="26" t="s">
-        <v>391</v>
-      </c>
-      <c r="B11" s="27" t="s">
-        <v>391</v>
-      </c>
-      <c r="C11" s="28" t="s">
-        <v>392</v>
-      </c>
-      <c r="D11" s="28" t="s">
-        <v>393</v>
-      </c>
-      <c r="E11" s="28">
+    <row r="12" spans="1:7">
+      <c r="A12" s="29" t="s">
+        <v>394</v>
+      </c>
+      <c r="B12" s="30" t="s">
+        <v>394</v>
+      </c>
+      <c r="C12" s="31" t="s">
+        <v>395</v>
+      </c>
+      <c r="D12" s="31" t="s">
+        <v>396</v>
+      </c>
+      <c r="E12" s="31">
         <v>30</v>
       </c>
-      <c r="F11" s="29" t="s">
-        <v>394</v>
-      </c>
-      <c r="G11" s="29" t="s">
+      <c r="F12" s="32" t="s">
+        <v>397</v>
+      </c>
+      <c r="G12" s="32" t="s">
         <v>357</v>
       </c>
     </row>
-    <row r="12" spans="1:7">
-      <c r="A12" s="22" t="s">
-        <v>395</v>
-      </c>
-      <c r="B12" s="23" t="s">
-        <v>395</v>
-      </c>
-      <c r="C12" s="24" t="s">
-        <v>396</v>
-      </c>
-      <c r="D12" s="24" t="s">
-        <v>397</v>
-      </c>
-      <c r="E12" s="24">
+    <row r="13" spans="1:7">
+      <c r="A13" s="25" t="s">
+        <v>398</v>
+      </c>
+      <c r="B13" s="26" t="s">
+        <v>398</v>
+      </c>
+      <c r="C13" s="27" t="s">
+        <v>399</v>
+      </c>
+      <c r="D13" s="27" t="s">
+        <v>400</v>
+      </c>
+      <c r="E13" s="27">
         <v>40</v>
       </c>
-      <c r="F12" s="25" t="s">
-        <v>398</v>
-      </c>
-      <c r="G12" s="25" t="s">
+      <c r="F13" s="28" t="s">
+        <v>401</v>
+      </c>
+      <c r="G13" s="28" t="s">
         <v>357</v>
       </c>
     </row>
-    <row r="13" spans="1:7">
-      <c r="A13" s="26" t="s">
-        <v>399</v>
-      </c>
-      <c r="B13" s="27" t="s">
-        <v>399</v>
-      </c>
-      <c r="C13" s="28" t="s">
-        <v>400</v>
-      </c>
-      <c r="D13" s="28" t="s">
-        <v>401</v>
-      </c>
-      <c r="E13" s="28">
+    <row r="14" spans="1:7">
+      <c r="A14" s="29" t="s">
+        <v>402</v>
+      </c>
+      <c r="B14" s="30" t="s">
+        <v>402</v>
+      </c>
+      <c r="C14" s="31" t="s">
+        <v>403</v>
+      </c>
+      <c r="D14" s="31" t="s">
+        <v>404</v>
+      </c>
+      <c r="E14" s="31">
         <v>4</v>
       </c>
-      <c r="F13" s="29" t="s">
-        <v>402</v>
-      </c>
-      <c r="G13" s="29" t="s">
+      <c r="F14" s="32" t="s">
+        <v>405</v>
+      </c>
+      <c r="G14" s="32" t="s">
         <v>362</v>
       </c>
     </row>
-    <row r="14" spans="1:7">
-      <c r="A14" s="22" t="s">
-        <v>403</v>
-      </c>
-      <c r="B14" s="23" t="s">
-        <v>403</v>
-      </c>
-      <c r="C14" s="24" t="s">
+    <row r="15" spans="1:7">
+      <c r="A15" s="25" t="s">
+        <v>406</v>
+      </c>
+      <c r="B15" s="26" t="s">
+        <v>406</v>
+      </c>
+      <c r="C15" s="27" t="s">
+        <v>407</v>
+      </c>
+      <c r="D15" s="27" t="s">
+        <v>408</v>
+      </c>
+      <c r="E15" s="27">
+        <v>30</v>
+      </c>
+      <c r="F15" s="28" t="s">
+        <v>409</v>
+      </c>
+      <c r="G15" s="28" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16" s="29" t="s">
+        <v>410</v>
+      </c>
+      <c r="B16" s="30" t="s">
+        <v>410</v>
+      </c>
+      <c r="C16" s="31" t="s">
+        <v>411</v>
+      </c>
+      <c r="D16" s="31" t="s">
+        <v>412</v>
+      </c>
+      <c r="E16" s="31">
+        <v>70</v>
+      </c>
+      <c r="F16" s="32" t="s">
+        <v>413</v>
+      </c>
+      <c r="G16" s="32" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17" s="25" t="s">
+        <v>414</v>
+      </c>
+      <c r="B17" s="26" t="s">
+        <v>414</v>
+      </c>
+      <c r="C17" s="27" t="s">
+        <v>415</v>
+      </c>
+      <c r="D17" s="27" t="s">
+        <v>416</v>
+      </c>
+      <c r="E17" s="27">
+        <v>60</v>
+      </c>
+      <c r="F17" s="28" t="s">
+        <v>417</v>
+      </c>
+      <c r="G17" s="28" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18" s="29" t="s">
+        <v>418</v>
+      </c>
+      <c r="B18" s="30" t="s">
+        <v>418</v>
+      </c>
+      <c r="C18" s="31" t="s">
+        <v>419</v>
+      </c>
+      <c r="D18" s="31" t="s">
+        <v>420</v>
+      </c>
+      <c r="E18" s="31">
+        <v>30</v>
+      </c>
+      <c r="F18" s="32" t="s">
+        <v>421</v>
+      </c>
+      <c r="G18" s="32" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19" s="25" t="s">
+        <v>422</v>
+      </c>
+      <c r="B19" s="26" t="s">
+        <v>422</v>
+      </c>
+      <c r="C19" s="27" t="s">
+        <v>423</v>
+      </c>
+      <c r="D19" s="27" t="s">
+        <v>424</v>
+      </c>
+      <c r="E19" s="27">
+        <v>30</v>
+      </c>
+      <c r="F19" s="28" t="s">
+        <v>425</v>
+      </c>
+      <c r="G19" s="28" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20" s="29" t="s">
+        <v>426</v>
+      </c>
+      <c r="B20" s="30" t="s">
+        <v>426</v>
+      </c>
+      <c r="C20" s="31" t="s">
+        <v>427</v>
+      </c>
+      <c r="D20" s="31" t="s">
+        <v>428</v>
+      </c>
+      <c r="E20" s="31">
+        <v>30</v>
+      </c>
+      <c r="F20" s="32" t="s">
+        <v>429</v>
+      </c>
+      <c r="G20" s="32" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="21" ht="17" spans="1:7">
+      <c r="A21" s="25" t="s">
+        <v>430</v>
+      </c>
+      <c r="B21" s="26" t="s">
+        <v>430</v>
+      </c>
+      <c r="C21" s="27" t="s">
+        <v>431</v>
+      </c>
+      <c r="D21" s="27" t="s">
+        <v>432</v>
+      </c>
+      <c r="E21" s="27">
+        <v>20</v>
+      </c>
+      <c r="F21" s="28" t="s">
+        <v>433</v>
+      </c>
+      <c r="G21" s="28" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
+      <c r="A22" s="29" t="s">
+        <v>434</v>
+      </c>
+      <c r="B22" s="30" t="s">
+        <v>434</v>
+      </c>
+      <c r="C22" s="31" t="s">
+        <v>435</v>
+      </c>
+      <c r="D22" s="31" t="s">
+        <v>436</v>
+      </c>
+      <c r="E22" s="31">
+        <v>100</v>
+      </c>
+      <c r="F22" s="32" t="s">
+        <v>437</v>
+      </c>
+      <c r="G22" s="32" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7">
+      <c r="A23" s="25" t="s">
+        <v>438</v>
+      </c>
+      <c r="B23" s="26" t="s">
+        <v>438</v>
+      </c>
+      <c r="C23" s="27" t="s">
+        <v>439</v>
+      </c>
+      <c r="D23" s="27" t="s">
+        <v>440</v>
+      </c>
+      <c r="E23" s="27">
+        <v>10</v>
+      </c>
+      <c r="F23" s="28" t="s">
+        <v>441</v>
+      </c>
+      <c r="G23" s="28" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7">
+      <c r="A24" s="29" t="s">
+        <v>442</v>
+      </c>
+      <c r="B24" s="30" t="s">
+        <v>442</v>
+      </c>
+      <c r="C24" s="31" t="s">
+        <v>443</v>
+      </c>
+      <c r="D24" s="31" t="s">
+        <v>444</v>
+      </c>
+      <c r="E24" s="31">
+        <v>20</v>
+      </c>
+      <c r="F24" s="32" t="s">
+        <v>445</v>
+      </c>
+      <c r="G24" s="32" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7">
+      <c r="A25" s="25" t="s">
+        <v>447</v>
+      </c>
+      <c r="B25" s="26" t="s">
+        <v>447</v>
+      </c>
+      <c r="C25" s="27" t="s">
+        <v>448</v>
+      </c>
+      <c r="D25" s="27" t="s">
+        <v>449</v>
+      </c>
+      <c r="E25" s="27">
+        <v>20</v>
+      </c>
+      <c r="F25" s="28" t="s">
+        <v>450</v>
+      </c>
+      <c r="G25" s="28" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7">
+      <c r="A26" s="29" t="s">
+        <v>451</v>
+      </c>
+      <c r="B26" s="30" t="s">
+        <v>451</v>
+      </c>
+      <c r="C26" s="31" t="s">
+        <v>452</v>
+      </c>
+      <c r="D26" s="31" t="s">
+        <v>453</v>
+      </c>
+      <c r="E26" s="31">
+        <v>35</v>
+      </c>
+      <c r="F26" s="32" t="s">
+        <v>454</v>
+      </c>
+      <c r="G26" s="32" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7">
+      <c r="A27" s="25" t="s">
+        <v>455</v>
+      </c>
+      <c r="B27" s="26" t="s">
+        <v>455</v>
+      </c>
+      <c r="C27" s="27" t="s">
+        <v>456</v>
+      </c>
+      <c r="D27" s="27" t="s">
+        <v>457</v>
+      </c>
+      <c r="E27" s="27">
+        <v>50</v>
+      </c>
+      <c r="F27" s="28" t="s">
+        <v>458</v>
+      </c>
+      <c r="G27" s="28" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7">
+      <c r="A28" s="29" t="s">
+        <v>459</v>
+      </c>
+      <c r="B28" s="30" t="s">
+        <v>459</v>
+      </c>
+      <c r="C28" s="31" t="s">
+        <v>460</v>
+      </c>
+      <c r="D28" s="31" t="s">
+        <v>461</v>
+      </c>
+      <c r="E28" s="31">
+        <v>20</v>
+      </c>
+      <c r="F28" s="32" t="s">
+        <v>462</v>
+      </c>
+      <c r="G28" s="32" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7">
+      <c r="A29" s="25" t="s">
+        <v>463</v>
+      </c>
+      <c r="B29" s="26" t="s">
+        <v>463</v>
+      </c>
+      <c r="C29" s="27" t="s">
+        <v>464</v>
+      </c>
+      <c r="D29" s="27" t="s">
+        <v>465</v>
+      </c>
+      <c r="E29" s="27">
+        <v>5</v>
+      </c>
+      <c r="F29" s="28" t="s">
+        <v>466</v>
+      </c>
+      <c r="G29" s="28" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7">
+      <c r="A30" s="29" t="s">
+        <v>467</v>
+      </c>
+      <c r="B30" s="30" t="s">
+        <v>467</v>
+      </c>
+      <c r="C30" s="31" t="s">
+        <v>468</v>
+      </c>
+      <c r="D30" s="31" t="s">
+        <v>469</v>
+      </c>
+      <c r="E30" s="31">
+        <v>20</v>
+      </c>
+      <c r="F30" s="32" t="s">
+        <v>470</v>
+      </c>
+      <c r="G30" s="32" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7">
+      <c r="A31" s="25" t="s">
+        <v>471</v>
+      </c>
+      <c r="B31" s="26" t="s">
+        <v>471</v>
+      </c>
+      <c r="C31" s="27" t="s">
+        <v>472</v>
+      </c>
+      <c r="D31" s="27" t="s">
+        <v>473</v>
+      </c>
+      <c r="E31" s="27">
+        <v>15</v>
+      </c>
+      <c r="F31" s="28" t="s">
+        <v>474</v>
+      </c>
+      <c r="G31" s="28" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7">
+      <c r="A32" s="29" t="s">
+        <v>475</v>
+      </c>
+      <c r="B32" s="30" t="s">
+        <v>475</v>
+      </c>
+      <c r="C32" s="31" t="s">
+        <v>476</v>
+      </c>
+      <c r="D32" s="31" t="s">
+        <v>477</v>
+      </c>
+      <c r="E32" s="31">
+        <v>15</v>
+      </c>
+      <c r="F32" s="32" t="s">
+        <v>478</v>
+      </c>
+      <c r="G32" s="32" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="33" ht="17" spans="1:7">
+      <c r="A33" s="25" t="s">
+        <v>479</v>
+      </c>
+      <c r="B33" s="26" t="s">
+        <v>479</v>
+      </c>
+      <c r="C33" s="27" t="s">
+        <v>480</v>
+      </c>
+      <c r="D33" s="27" t="s">
+        <v>481</v>
+      </c>
+      <c r="E33" s="27">
+        <v>15</v>
+      </c>
+      <c r="F33" s="28" t="s">
+        <v>482</v>
+      </c>
+      <c r="G33" s="28" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7">
+      <c r="A34" s="29" t="s">
+        <v>483</v>
+      </c>
+      <c r="B34" s="30" t="s">
+        <v>483</v>
+      </c>
+      <c r="C34" s="31" t="s">
+        <v>484</v>
+      </c>
+      <c r="D34" s="31" t="s">
+        <v>485</v>
+      </c>
+      <c r="E34" s="31">
+        <v>5</v>
+      </c>
+      <c r="F34" s="32" t="s">
+        <v>486</v>
+      </c>
+      <c r="G34" s="32" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7">
+      <c r="A35" s="25" t="s">
+        <v>487</v>
+      </c>
+      <c r="B35" s="26" t="s">
+        <v>487</v>
+      </c>
+      <c r="C35" s="27" t="s">
+        <v>488</v>
+      </c>
+      <c r="D35" s="27" t="s">
+        <v>489</v>
+      </c>
+      <c r="E35" s="27">
+        <v>25</v>
+      </c>
+      <c r="F35" s="28" t="s">
+        <v>490</v>
+      </c>
+      <c r="G35" s="28" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7">
+      <c r="A36" s="29" t="s">
+        <v>491</v>
+      </c>
+      <c r="B36" s="30" t="s">
+        <v>491</v>
+      </c>
+      <c r="C36" s="31" t="s">
+        <v>492</v>
+      </c>
+      <c r="D36" s="31" t="s">
+        <v>493</v>
+      </c>
+      <c r="E36" s="31">
+        <v>10</v>
+      </c>
+      <c r="F36" s="32" t="s">
+        <v>494</v>
+      </c>
+      <c r="G36" s="32" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7">
+      <c r="A37" s="25" t="s">
+        <v>495</v>
+      </c>
+      <c r="B37" s="26" t="s">
+        <v>495</v>
+      </c>
+      <c r="C37" s="27" t="s">
+        <v>496</v>
+      </c>
+      <c r="D37" s="27" t="s">
+        <v>497</v>
+      </c>
+      <c r="E37" s="27">
+        <v>8</v>
+      </c>
+      <c r="F37" s="28" t="s">
+        <v>498</v>
+      </c>
+      <c r="G37" s="28" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7">
+      <c r="A38" s="29" t="s">
+        <v>499</v>
+      </c>
+      <c r="B38" s="30" t="s">
+        <v>499</v>
+      </c>
+      <c r="C38" s="31" t="s">
+        <v>500</v>
+      </c>
+      <c r="D38" s="31" t="s">
+        <v>501</v>
+      </c>
+      <c r="E38" s="31">
+        <v>100</v>
+      </c>
+      <c r="F38" s="32" t="s">
+        <v>502</v>
+      </c>
+      <c r="G38" s="32" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7">
+      <c r="A39" s="25" t="s">
+        <v>503</v>
+      </c>
+      <c r="B39" s="26" t="s">
+        <v>503</v>
+      </c>
+      <c r="C39" s="27" t="s">
+        <v>504</v>
+      </c>
+      <c r="D39" s="27" t="s">
+        <v>505</v>
+      </c>
+      <c r="E39" s="27">
+        <v>20</v>
+      </c>
+      <c r="F39" s="28" t="s">
+        <v>506</v>
+      </c>
+      <c r="G39" s="28" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="40" ht="17" spans="1:7">
+      <c r="A40" s="18" t="s">
+        <v>507</v>
+      </c>
+      <c r="B40" s="19" t="s">
+        <v>507</v>
+      </c>
+      <c r="C40" s="20" t="s">
+        <v>508</v>
+      </c>
+      <c r="D40" s="20" t="s">
+        <v>509</v>
+      </c>
+      <c r="E40" s="20">
+        <v>10</v>
+      </c>
+      <c r="F40" s="21" t="s">
+        <v>510</v>
+      </c>
+      <c r="G40" s="21" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7">
+      <c r="A41" s="14" t="s">
+        <v>511</v>
+      </c>
+      <c r="B41" s="15" t="s">
+        <v>511</v>
+      </c>
+      <c r="C41" s="16" t="s">
+        <v>512</v>
+      </c>
+      <c r="D41" s="16" t="s">
+        <v>513</v>
+      </c>
+      <c r="E41" s="16">
+        <v>10</v>
+      </c>
+      <c r="F41" s="17" t="s">
+        <v>514</v>
+      </c>
+      <c r="G41" s="17" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7">
+      <c r="A42" s="18" t="s">
+        <v>515</v>
+      </c>
+      <c r="B42" s="19" t="s">
+        <v>515</v>
+      </c>
+      <c r="C42" s="20" t="s">
+        <v>516</v>
+      </c>
+      <c r="D42" s="20" t="s">
+        <v>517</v>
+      </c>
+      <c r="E42" s="20">
+        <v>12</v>
+      </c>
+      <c r="F42" s="21" t="s">
+        <v>518</v>
+      </c>
+      <c r="G42" s="21" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="43" ht="17" spans="1:7">
+      <c r="A43" s="14" t="s">
+        <v>519</v>
+      </c>
+      <c r="B43" s="15" t="s">
+        <v>519</v>
+      </c>
+      <c r="C43" s="16" t="s">
+        <v>520</v>
+      </c>
+      <c r="D43" s="16" t="s">
+        <v>521</v>
+      </c>
+      <c r="E43" s="16">
+        <v>15</v>
+      </c>
+      <c r="F43" s="17" t="s">
+        <v>522</v>
+      </c>
+      <c r="G43" s="17" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7">
+      <c r="A44" s="18" t="s">
+        <v>523</v>
+      </c>
+      <c r="B44" s="19" t="s">
+        <v>523</v>
+      </c>
+      <c r="C44" s="20" t="s">
+        <v>524</v>
+      </c>
+      <c r="D44" s="20" t="s">
         <v>404</v>
       </c>
-      <c r="D14" s="24" t="s">
-        <v>405</v>
-      </c>
-      <c r="E14" s="24">
-        <v>30</v>
-      </c>
-      <c r="F14" s="25" t="s">
-        <v>406</v>
-      </c>
-      <c r="G14" s="25" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15" s="26" t="s">
-        <v>407</v>
-      </c>
-      <c r="B15" s="27" t="s">
-        <v>407</v>
-      </c>
-      <c r="C15" s="28" t="s">
-        <v>408</v>
-      </c>
-      <c r="D15" s="28" t="s">
-        <v>409</v>
-      </c>
-      <c r="E15" s="28">
-        <v>70</v>
-      </c>
-      <c r="F15" s="29" t="s">
-        <v>410</v>
-      </c>
-      <c r="G15" s="29" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16" s="22" t="s">
-        <v>411</v>
-      </c>
-      <c r="B16" s="23" t="s">
-        <v>411</v>
-      </c>
-      <c r="C16" s="24" t="s">
-        <v>412</v>
-      </c>
-      <c r="D16" s="24" t="s">
-        <v>413</v>
-      </c>
-      <c r="E16" s="24">
-        <v>60</v>
-      </c>
-      <c r="F16" s="25" t="s">
-        <v>414</v>
-      </c>
-      <c r="G16" s="25" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17" s="26" t="s">
-        <v>415</v>
-      </c>
-      <c r="B17" s="27" t="s">
-        <v>415</v>
-      </c>
-      <c r="C17" s="28" t="s">
-        <v>416</v>
-      </c>
-      <c r="D17" s="28" t="s">
-        <v>417</v>
-      </c>
-      <c r="E17" s="28">
-        <v>30</v>
-      </c>
-      <c r="F17" s="29" t="s">
-        <v>418</v>
-      </c>
-      <c r="G17" s="29" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18" s="22" t="s">
-        <v>419</v>
-      </c>
-      <c r="B18" s="23" t="s">
-        <v>419</v>
-      </c>
-      <c r="C18" s="24" t="s">
-        <v>420</v>
-      </c>
-      <c r="D18" s="24" t="s">
-        <v>421</v>
-      </c>
-      <c r="E18" s="24">
-        <v>30</v>
-      </c>
-      <c r="F18" s="25" t="s">
-        <v>422</v>
-      </c>
-      <c r="G18" s="25" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19" s="26" t="s">
-        <v>423</v>
-      </c>
-      <c r="B19" s="27" t="s">
-        <v>423</v>
-      </c>
-      <c r="C19" s="28" t="s">
-        <v>424</v>
-      </c>
-      <c r="D19" s="28" t="s">
-        <v>425</v>
-      </c>
-      <c r="E19" s="28">
-        <v>30</v>
-      </c>
-      <c r="F19" s="29" t="s">
-        <v>426</v>
-      </c>
-      <c r="G19" s="29" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="20" ht="17" spans="1:7">
-      <c r="A20" s="22" t="s">
-        <v>427</v>
-      </c>
-      <c r="B20" s="23" t="s">
-        <v>427</v>
-      </c>
-      <c r="C20" s="24" t="s">
-        <v>428</v>
-      </c>
-      <c r="D20" s="24" t="s">
-        <v>429</v>
-      </c>
-      <c r="E20" s="24">
-        <v>20</v>
-      </c>
-      <c r="F20" s="25" t="s">
-        <v>430</v>
-      </c>
-      <c r="G20" s="25" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7">
-      <c r="A21" s="26" t="s">
-        <v>431</v>
-      </c>
-      <c r="B21" s="27" t="s">
-        <v>431</v>
-      </c>
-      <c r="C21" s="28" t="s">
-        <v>432</v>
-      </c>
-      <c r="D21" s="28" t="s">
-        <v>433</v>
-      </c>
-      <c r="E21" s="28">
-        <v>100</v>
-      </c>
-      <c r="F21" s="29" t="s">
-        <v>434</v>
-      </c>
-      <c r="G21" s="29" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7">
-      <c r="A22" s="22" t="s">
-        <v>435</v>
-      </c>
-      <c r="B22" s="23" t="s">
-        <v>435</v>
-      </c>
-      <c r="C22" s="24" t="s">
-        <v>436</v>
-      </c>
-      <c r="D22" s="24" t="s">
-        <v>437</v>
-      </c>
-      <c r="E22" s="24">
-        <v>10</v>
-      </c>
-      <c r="F22" s="25" t="s">
-        <v>438</v>
-      </c>
-      <c r="G22" s="25" t="s">
+      <c r="E44" s="20">
+        <v>25</v>
+      </c>
+      <c r="F44" s="21" t="s">
+        <v>361</v>
+      </c>
+      <c r="G44" s="21" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7">
+      <c r="A45" s="14" t="s">
+        <v>525</v>
+      </c>
+      <c r="B45" s="15" t="s">
+        <v>525</v>
+      </c>
+      <c r="C45" s="16" t="s">
+        <v>526</v>
+      </c>
+      <c r="D45" s="16" t="s">
+        <v>527</v>
+      </c>
+      <c r="E45" s="16">
+        <v>3</v>
+      </c>
+      <c r="F45" s="17" t="s">
+        <v>528</v>
+      </c>
+      <c r="G45" s="17" t="s">
         <v>362</v>
       </c>
     </row>
-    <row r="23" spans="1:7">
-      <c r="A23" s="26" t="s">
-        <v>439</v>
-      </c>
-      <c r="B23" s="27" t="s">
-        <v>439</v>
-      </c>
-      <c r="C23" s="28" t="s">
-        <v>440</v>
-      </c>
-      <c r="D23" s="28" t="s">
-        <v>441</v>
-      </c>
-      <c r="E23" s="28">
-        <v>20</v>
-      </c>
-      <c r="F23" s="29" t="s">
-        <v>442</v>
-      </c>
-      <c r="G23" s="29" t="s">
-        <v>443</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7">
-      <c r="A24" s="22" t="s">
-        <v>444</v>
-      </c>
-      <c r="B24" s="23" t="s">
-        <v>444</v>
-      </c>
-      <c r="C24" s="24" t="s">
-        <v>445</v>
-      </c>
-      <c r="D24" s="24" t="s">
-        <v>446</v>
-      </c>
-      <c r="E24" s="24">
-        <v>20</v>
-      </c>
-      <c r="F24" s="25" t="s">
-        <v>447</v>
-      </c>
-      <c r="G24" s="25" t="s">
-        <v>443</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7">
-      <c r="A25" s="26" t="s">
-        <v>448</v>
-      </c>
-      <c r="B25" s="27" t="s">
-        <v>448</v>
-      </c>
-      <c r="C25" s="28" t="s">
-        <v>449</v>
-      </c>
-      <c r="D25" s="28" t="s">
-        <v>450</v>
-      </c>
-      <c r="E25" s="28">
-        <v>35</v>
-      </c>
-      <c r="F25" s="29" t="s">
-        <v>451</v>
-      </c>
-      <c r="G25" s="29" t="s">
-        <v>443</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7">
-      <c r="A26" s="22" t="s">
-        <v>452</v>
-      </c>
-      <c r="B26" s="23" t="s">
-        <v>452</v>
-      </c>
-      <c r="C26" s="24" t="s">
-        <v>453</v>
-      </c>
-      <c r="D26" s="24" t="s">
-        <v>454</v>
-      </c>
-      <c r="E26" s="24">
-        <v>50</v>
-      </c>
-      <c r="F26" s="25" t="s">
-        <v>455</v>
-      </c>
-      <c r="G26" s="25" t="s">
-        <v>443</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7">
-      <c r="A27" s="26" t="s">
-        <v>456</v>
-      </c>
-      <c r="B27" s="27" t="s">
-        <v>456</v>
-      </c>
-      <c r="C27" s="28" t="s">
-        <v>457</v>
-      </c>
-      <c r="D27" s="28" t="s">
-        <v>458</v>
-      </c>
-      <c r="E27" s="28">
-        <v>20</v>
-      </c>
-      <c r="F27" s="29" t="s">
-        <v>459</v>
-      </c>
-      <c r="G27" s="29" t="s">
-        <v>443</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7">
-      <c r="A28" s="22" t="s">
-        <v>460</v>
-      </c>
-      <c r="B28" s="23" t="s">
-        <v>460</v>
-      </c>
-      <c r="C28" s="24" t="s">
-        <v>461</v>
-      </c>
-      <c r="D28" s="24" t="s">
-        <v>462</v>
-      </c>
-      <c r="E28" s="24">
-        <v>5</v>
-      </c>
-      <c r="F28" s="25" t="s">
-        <v>463</v>
-      </c>
-      <c r="G28" s="25" t="s">
+    <row r="46" spans="1:7">
+      <c r="A46" s="18" t="s">
+        <v>529</v>
+      </c>
+      <c r="B46" s="19" t="s">
+        <v>529</v>
+      </c>
+      <c r="C46" s="20" t="s">
+        <v>530</v>
+      </c>
+      <c r="D46" s="20" t="s">
+        <v>531</v>
+      </c>
+      <c r="E46" s="20">
+        <v>2</v>
+      </c>
+      <c r="F46" s="21" t="s">
+        <v>532</v>
+      </c>
+      <c r="G46" s="21" t="s">
         <v>362</v>
       </c>
     </row>
-    <row r="29" spans="1:7">
-      <c r="A29" s="26" t="s">
-        <v>464</v>
-      </c>
-      <c r="B29" s="27" t="s">
-        <v>464</v>
-      </c>
-      <c r="C29" s="28" t="s">
-        <v>465</v>
-      </c>
-      <c r="D29" s="28" t="s">
-        <v>466</v>
-      </c>
-      <c r="E29" s="28">
-        <v>20</v>
-      </c>
-      <c r="F29" s="29" t="s">
-        <v>467</v>
-      </c>
-      <c r="G29" s="29" t="s">
-        <v>443</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7">
-      <c r="A30" s="22" t="s">
-        <v>468</v>
-      </c>
-      <c r="B30" s="23" t="s">
-        <v>468</v>
-      </c>
-      <c r="C30" s="24" t="s">
-        <v>469</v>
-      </c>
-      <c r="D30" s="24" t="s">
-        <v>470</v>
-      </c>
-      <c r="E30" s="24">
-        <v>15</v>
-      </c>
-      <c r="F30" s="25" t="s">
-        <v>471</v>
-      </c>
-      <c r="G30" s="25" t="s">
-        <v>443</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7">
-      <c r="A31" s="26" t="s">
-        <v>472</v>
-      </c>
-      <c r="B31" s="27" t="s">
-        <v>472</v>
-      </c>
-      <c r="C31" s="28" t="s">
-        <v>473</v>
-      </c>
-      <c r="D31" s="28" t="s">
-        <v>474</v>
-      </c>
-      <c r="E31" s="28">
-        <v>15</v>
-      </c>
-      <c r="F31" s="29" t="s">
-        <v>475</v>
-      </c>
-      <c r="G31" s="29" t="s">
-        <v>443</v>
-      </c>
-    </row>
-    <row r="32" ht="17" spans="1:7">
-      <c r="A32" s="22" t="s">
-        <v>476</v>
-      </c>
-      <c r="B32" s="23" t="s">
-        <v>476</v>
-      </c>
-      <c r="C32" s="24" t="s">
-        <v>477</v>
-      </c>
-      <c r="D32" s="24" t="s">
-        <v>478</v>
-      </c>
-      <c r="E32" s="24">
-        <v>15</v>
-      </c>
-      <c r="F32" s="25" t="s">
-        <v>479</v>
-      </c>
-      <c r="G32" s="25" t="s">
-        <v>443</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7">
-      <c r="A33" s="26" t="s">
-        <v>480</v>
-      </c>
-      <c r="B33" s="27" t="s">
-        <v>480</v>
-      </c>
-      <c r="C33" s="28" t="s">
-        <v>481</v>
-      </c>
-      <c r="D33" s="28" t="s">
-        <v>482</v>
-      </c>
-      <c r="E33" s="28">
-        <v>5</v>
-      </c>
-      <c r="F33" s="29" t="s">
-        <v>483</v>
-      </c>
-      <c r="G33" s="29" t="s">
-        <v>443</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7">
-      <c r="A34" s="22" t="s">
-        <v>484</v>
-      </c>
-      <c r="B34" s="23" t="s">
-        <v>484</v>
-      </c>
-      <c r="C34" s="24" t="s">
-        <v>485</v>
-      </c>
-      <c r="D34" s="24" t="s">
-        <v>486</v>
-      </c>
-      <c r="E34" s="24">
-        <v>25</v>
-      </c>
-      <c r="F34" s="25" t="s">
-        <v>487</v>
-      </c>
-      <c r="G34" s="25" t="s">
-        <v>443</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7">
-      <c r="A35" s="26" t="s">
-        <v>488</v>
-      </c>
-      <c r="B35" s="27" t="s">
-        <v>488</v>
-      </c>
-      <c r="C35" s="28" t="s">
-        <v>489</v>
-      </c>
-      <c r="D35" s="28" t="s">
-        <v>490</v>
-      </c>
-      <c r="E35" s="28">
-        <v>10</v>
-      </c>
-      <c r="F35" s="29" t="s">
-        <v>491</v>
-      </c>
-      <c r="G35" s="29" t="s">
-        <v>443</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7">
-      <c r="A36" s="22" t="s">
-        <v>492</v>
-      </c>
-      <c r="B36" s="23" t="s">
-        <v>492</v>
-      </c>
-      <c r="C36" s="24" t="s">
-        <v>493</v>
-      </c>
-      <c r="D36" s="24" t="s">
-        <v>494</v>
-      </c>
-      <c r="E36" s="24">
-        <v>8</v>
-      </c>
-      <c r="F36" s="25" t="s">
-        <v>495</v>
-      </c>
-      <c r="G36" s="25" t="s">
+    <row r="47" spans="1:7">
+      <c r="A47" s="14" t="s">
+        <v>533</v>
+      </c>
+      <c r="B47" s="15" t="s">
+        <v>533</v>
+      </c>
+      <c r="C47" s="16" t="s">
+        <v>534</v>
+      </c>
+      <c r="D47" s="16" t="s">
+        <v>535</v>
+      </c>
+      <c r="E47" s="16">
+        <v>6</v>
+      </c>
+      <c r="F47" s="17" t="s">
+        <v>536</v>
+      </c>
+      <c r="G47" s="17" t="s">
         <v>362</v>
       </c>
     </row>
-    <row r="37" spans="1:7">
-      <c r="A37" s="26" t="s">
-        <v>496</v>
-      </c>
-      <c r="B37" s="27" t="s">
-        <v>496</v>
-      </c>
-      <c r="C37" s="28" t="s">
-        <v>497</v>
-      </c>
-      <c r="D37" s="28" t="s">
-        <v>498</v>
-      </c>
-      <c r="E37" s="28">
-        <v>100</v>
-      </c>
-      <c r="F37" s="29" t="s">
-        <v>499</v>
-      </c>
-      <c r="G37" s="29" t="s">
-        <v>443</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7">
-      <c r="A38" s="22" t="s">
-        <v>500</v>
-      </c>
-      <c r="B38" s="23" t="s">
-        <v>500</v>
-      </c>
-      <c r="C38" s="24" t="s">
-        <v>501</v>
-      </c>
-      <c r="D38" s="24" t="s">
-        <v>502</v>
-      </c>
-      <c r="E38" s="24">
-        <v>20</v>
-      </c>
-      <c r="F38" s="25" t="s">
-        <v>503</v>
-      </c>
-      <c r="G38" s="25" t="s">
-        <v>443</v>
-      </c>
-    </row>
-    <row r="39" ht="17" spans="1:7">
-      <c r="A39" s="18" t="s">
-        <v>504</v>
-      </c>
-      <c r="B39" s="19" t="s">
-        <v>504</v>
-      </c>
-      <c r="C39" s="20" t="s">
-        <v>505</v>
-      </c>
-      <c r="D39" s="20" t="s">
-        <v>506</v>
-      </c>
-      <c r="E39" s="20">
-        <v>10</v>
-      </c>
-      <c r="F39" s="21" t="s">
-        <v>507</v>
-      </c>
-      <c r="G39" s="21" t="s">
-        <v>443</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7">
-      <c r="A40" s="14" t="s">
-        <v>508</v>
-      </c>
-      <c r="B40" s="15" t="s">
-        <v>508</v>
-      </c>
-      <c r="C40" s="16" t="s">
-        <v>509</v>
-      </c>
-      <c r="D40" s="16" t="s">
-        <v>510</v>
-      </c>
-      <c r="E40" s="16">
-        <v>10</v>
-      </c>
-      <c r="F40" s="17" t="s">
-        <v>511</v>
-      </c>
-      <c r="G40" s="17" t="s">
-        <v>443</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7">
-      <c r="A41" s="18" t="s">
-        <v>512</v>
-      </c>
-      <c r="B41" s="19" t="s">
-        <v>512</v>
-      </c>
-      <c r="C41" s="20" t="s">
-        <v>513</v>
-      </c>
-      <c r="D41" s="20" t="s">
-        <v>514</v>
-      </c>
-      <c r="E41" s="20">
-        <v>12</v>
-      </c>
-      <c r="F41" s="21" t="s">
-        <v>515</v>
-      </c>
-      <c r="G41" s="21" t="s">
-        <v>443</v>
-      </c>
-    </row>
-    <row r="42" ht="17" spans="1:7">
-      <c r="A42" s="14" t="s">
-        <v>516</v>
-      </c>
-      <c r="B42" s="15" t="s">
-        <v>516</v>
-      </c>
-      <c r="C42" s="16" t="s">
-        <v>517</v>
-      </c>
-      <c r="D42" s="16" t="s">
-        <v>518</v>
-      </c>
-      <c r="E42" s="16">
-        <v>15</v>
-      </c>
-      <c r="F42" s="17" t="s">
-        <v>519</v>
-      </c>
-      <c r="G42" s="17" t="s">
-        <v>443</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7">
-      <c r="A43" s="18" t="s">
-        <v>520</v>
-      </c>
-      <c r="B43" s="19" t="s">
-        <v>520</v>
-      </c>
-      <c r="C43" s="20" t="s">
-        <v>521</v>
-      </c>
-      <c r="D43" s="20" t="s">
-        <v>401</v>
-      </c>
-      <c r="E43" s="20">
-        <v>25</v>
-      </c>
-      <c r="F43" s="21" t="s">
+    <row r="48" spans="1:7">
+      <c r="A48" s="18" t="s">
+        <v>537</v>
+      </c>
+      <c r="B48" s="19" t="s">
+        <v>537</v>
+      </c>
+      <c r="C48" s="20" t="s">
+        <v>538</v>
+      </c>
+      <c r="D48" s="20" t="s">
+        <v>539</v>
+      </c>
+      <c r="E48" s="20">
+        <v>4</v>
+      </c>
+      <c r="F48" s="21" t="s">
+        <v>540</v>
+      </c>
+      <c r="G48" s="21" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7">
+      <c r="A49" s="14" t="s">
+        <v>541</v>
+      </c>
+      <c r="B49" s="15" t="s">
+        <v>541</v>
+      </c>
+      <c r="C49" s="16" t="s">
+        <v>542</v>
+      </c>
+      <c r="D49" s="16" t="s">
+        <v>404</v>
+      </c>
+      <c r="E49" s="16">
+        <v>3</v>
+      </c>
+      <c r="F49" s="17" t="s">
         <v>361</v>
       </c>
-      <c r="G43" s="21" t="s">
-        <v>443</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7">
-      <c r="A44" s="14" t="s">
-        <v>522</v>
-      </c>
-      <c r="B44" s="15" t="s">
-        <v>522</v>
-      </c>
-      <c r="C44" s="16" t="s">
-        <v>523</v>
-      </c>
-      <c r="D44" s="16" t="s">
-        <v>524</v>
-      </c>
-      <c r="E44" s="16">
+      <c r="G49" s="17" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7">
+      <c r="A50" s="18" t="s">
+        <v>543</v>
+      </c>
+      <c r="B50" s="19" t="s">
+        <v>543</v>
+      </c>
+      <c r="C50" s="20" t="s">
+        <v>544</v>
+      </c>
+      <c r="D50" s="20" t="s">
+        <v>545</v>
+      </c>
+      <c r="E50" s="20">
+        <v>4</v>
+      </c>
+      <c r="F50" s="21" t="s">
+        <v>546</v>
+      </c>
+      <c r="G50" s="21" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7">
+      <c r="A51" s="14" t="s">
+        <v>547</v>
+      </c>
+      <c r="B51" s="15" t="s">
+        <v>547</v>
+      </c>
+      <c r="C51" s="16" t="s">
+        <v>548</v>
+      </c>
+      <c r="D51" s="16" t="s">
+        <v>549</v>
+      </c>
+      <c r="E51" s="16">
+        <v>4</v>
+      </c>
+      <c r="F51" s="17" t="s">
+        <v>550</v>
+      </c>
+      <c r="G51" s="17" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7">
+      <c r="A52" s="18" t="s">
+        <v>551</v>
+      </c>
+      <c r="B52" s="19" t="s">
+        <v>551</v>
+      </c>
+      <c r="C52" s="20" t="s">
+        <v>552</v>
+      </c>
+      <c r="D52" s="20" t="s">
+        <v>553</v>
+      </c>
+      <c r="E52" s="20">
+        <v>6</v>
+      </c>
+      <c r="F52" s="21" t="s">
+        <v>554</v>
+      </c>
+      <c r="G52" s="21" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7">
+      <c r="A53" s="14" t="s">
+        <v>555</v>
+      </c>
+      <c r="B53" s="15" t="s">
+        <v>555</v>
+      </c>
+      <c r="C53" s="16" t="s">
+        <v>556</v>
+      </c>
+      <c r="D53" s="16" t="s">
+        <v>557</v>
+      </c>
+      <c r="E53" s="16">
+        <v>2</v>
+      </c>
+      <c r="F53" s="17" t="s">
+        <v>558</v>
+      </c>
+      <c r="G53" s="17" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7">
+      <c r="A54" s="18" t="s">
+        <v>559</v>
+      </c>
+      <c r="B54" s="19" t="s">
+        <v>559</v>
+      </c>
+      <c r="C54" s="20" t="s">
+        <v>560</v>
+      </c>
+      <c r="D54" s="20" t="s">
+        <v>561</v>
+      </c>
+      <c r="E54" s="20">
+        <v>2</v>
+      </c>
+      <c r="F54" s="21" t="s">
+        <v>562</v>
+      </c>
+      <c r="G54" s="21" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7">
+      <c r="A55" s="14" t="s">
+        <v>563</v>
+      </c>
+      <c r="B55" s="15" t="s">
+        <v>563</v>
+      </c>
+      <c r="C55" s="16" t="s">
+        <v>564</v>
+      </c>
+      <c r="D55" s="16" t="s">
+        <v>565</v>
+      </c>
+      <c r="E55" s="16">
+        <v>4</v>
+      </c>
+      <c r="F55" s="17" t="s">
+        <v>566</v>
+      </c>
+      <c r="G55" s="17" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7">
+      <c r="A56" s="18" t="s">
+        <v>567</v>
+      </c>
+      <c r="B56" s="19" t="s">
+        <v>567</v>
+      </c>
+      <c r="C56" s="20" t="s">
+        <v>568</v>
+      </c>
+      <c r="D56" s="20" t="s">
+        <v>569</v>
+      </c>
+      <c r="E56" s="20">
         <v>3</v>
       </c>
-      <c r="F44" s="17" t="s">
-        <v>525</v>
-      </c>
-      <c r="G44" s="17" t="s">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7">
-      <c r="A45" s="18" t="s">
-        <v>526</v>
-      </c>
-      <c r="B45" s="19" t="s">
-        <v>526</v>
-      </c>
-      <c r="C45" s="20" t="s">
-        <v>527</v>
-      </c>
-      <c r="D45" s="20" t="s">
-        <v>528</v>
-      </c>
-      <c r="E45" s="20">
-        <v>2</v>
-      </c>
-      <c r="F45" s="21" t="s">
-        <v>529</v>
-      </c>
-      <c r="G45" s="21" t="s">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7">
-      <c r="A46" s="14" t="s">
-        <v>530</v>
-      </c>
-      <c r="B46" s="15" t="s">
-        <v>530</v>
-      </c>
-      <c r="C46" s="16" t="s">
-        <v>531</v>
-      </c>
-      <c r="D46" s="16" t="s">
-        <v>532</v>
-      </c>
-      <c r="E46" s="16">
-        <v>6</v>
-      </c>
-      <c r="F46" s="17" t="s">
-        <v>533</v>
-      </c>
-      <c r="G46" s="17" t="s">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7">
-      <c r="A47" s="18" t="s">
-        <v>534</v>
-      </c>
-      <c r="B47" s="19" t="s">
-        <v>534</v>
-      </c>
-      <c r="C47" s="20" t="s">
-        <v>535</v>
-      </c>
-      <c r="D47" s="20" t="s">
-        <v>536</v>
-      </c>
-      <c r="E47" s="20">
-        <v>4</v>
-      </c>
-      <c r="F47" s="21" t="s">
-        <v>537</v>
-      </c>
-      <c r="G47" s="21" t="s">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7">
-      <c r="A48" s="14" t="s">
-        <v>538</v>
-      </c>
-      <c r="B48" s="15" t="s">
-        <v>538</v>
-      </c>
-      <c r="C48" s="16" t="s">
-        <v>539</v>
-      </c>
-      <c r="D48" s="16" t="s">
-        <v>401</v>
-      </c>
-      <c r="E48" s="16">
-        <v>3</v>
-      </c>
-      <c r="F48" s="17" t="s">
-        <v>361</v>
-      </c>
-      <c r="G48" s="17" t="s">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="49" spans="1:7">
-      <c r="A49" s="18" t="s">
-        <v>540</v>
-      </c>
-      <c r="B49" s="19" t="s">
-        <v>540</v>
-      </c>
-      <c r="C49" s="20" t="s">
-        <v>541</v>
-      </c>
-      <c r="D49" s="20" t="s">
-        <v>542</v>
-      </c>
-      <c r="E49" s="20">
-        <v>4</v>
-      </c>
-      <c r="F49" s="21" t="s">
-        <v>543</v>
-      </c>
-      <c r="G49" s="21" t="s">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="50" spans="1:7">
-      <c r="A50" s="14" t="s">
-        <v>544</v>
-      </c>
-      <c r="B50" s="15" t="s">
-        <v>544</v>
-      </c>
-      <c r="C50" s="16" t="s">
-        <v>545</v>
-      </c>
-      <c r="D50" s="16" t="s">
-        <v>546</v>
-      </c>
-      <c r="E50" s="16">
-        <v>4</v>
-      </c>
-      <c r="F50" s="17" t="s">
-        <v>547</v>
-      </c>
-      <c r="G50" s="17" t="s">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="51" spans="1:7">
-      <c r="A51" s="18" t="s">
-        <v>548</v>
-      </c>
-      <c r="B51" s="19" t="s">
-        <v>548</v>
-      </c>
-      <c r="C51" s="20" t="s">
-        <v>549</v>
-      </c>
-      <c r="D51" s="20" t="s">
-        <v>550</v>
-      </c>
-      <c r="E51" s="20">
-        <v>6</v>
-      </c>
-      <c r="F51" s="21" t="s">
-        <v>551</v>
-      </c>
-      <c r="G51" s="21" t="s">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="52" spans="1:7">
-      <c r="A52" s="14" t="s">
-        <v>552</v>
-      </c>
-      <c r="B52" s="15" t="s">
-        <v>552</v>
-      </c>
-      <c r="C52" s="16" t="s">
-        <v>553</v>
-      </c>
-      <c r="D52" s="16" t="s">
-        <v>554</v>
-      </c>
-      <c r="E52" s="16">
-        <v>2</v>
-      </c>
-      <c r="F52" s="17" t="s">
-        <v>555</v>
-      </c>
-      <c r="G52" s="17" t="s">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="53" spans="1:7">
-      <c r="A53" s="18" t="s">
-        <v>556</v>
-      </c>
-      <c r="B53" s="19" t="s">
-        <v>556</v>
-      </c>
-      <c r="C53" s="20" t="s">
-        <v>557</v>
-      </c>
-      <c r="D53" s="20" t="s">
-        <v>558</v>
-      </c>
-      <c r="E53" s="20">
-        <v>2</v>
-      </c>
-      <c r="F53" s="21" t="s">
-        <v>559</v>
-      </c>
-      <c r="G53" s="21" t="s">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="54" spans="1:7">
-      <c r="A54" s="14" t="s">
-        <v>560</v>
-      </c>
-      <c r="B54" s="15" t="s">
-        <v>560</v>
-      </c>
-      <c r="C54" s="16" t="s">
-        <v>561</v>
-      </c>
-      <c r="D54" s="16" t="s">
-        <v>562</v>
-      </c>
-      <c r="E54" s="16">
-        <v>4</v>
-      </c>
-      <c r="F54" s="17" t="s">
-        <v>563</v>
-      </c>
-      <c r="G54" s="17" t="s">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="55" spans="1:7">
-      <c r="A55" s="18" t="s">
-        <v>564</v>
-      </c>
-      <c r="B55" s="19" t="s">
-        <v>564</v>
-      </c>
-      <c r="C55" s="20" t="s">
-        <v>565</v>
-      </c>
-      <c r="D55" s="20" t="s">
-        <v>566</v>
-      </c>
-      <c r="E55" s="20">
-        <v>3</v>
-      </c>
-      <c r="F55" s="21" t="s">
-        <v>567</v>
-      </c>
-      <c r="G55" s="21" t="s">
+      <c r="F56" s="21" t="s">
+        <v>570</v>
+      </c>
+      <c r="G56" s="21" t="s">
         <v>362</v>
       </c>
     </row>
@@ -9219,1416 +9282,1416 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="2" t="s">
-        <v>568</v>
+        <v>571</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>569</v>
+        <v>572</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>570</v>
+        <v>573</v>
       </c>
       <c r="D2" s="4"/>
       <c r="E2" s="5">
         <v>25</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>571</v>
+        <v>574</v>
       </c>
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="6" t="s">
-        <v>572</v>
+        <v>575</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>572</v>
+        <v>575</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>573</v>
+        <v>576</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>574</v>
+        <v>577</v>
       </c>
       <c r="E3" s="5">
         <v>12</v>
       </c>
       <c r="F3" s="7" t="s">
-        <v>575</v>
+        <v>578</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="8" t="s">
-        <v>576</v>
+        <v>579</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>576</v>
+        <v>579</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>577</v>
+        <v>580</v>
       </c>
       <c r="D4" s="4"/>
       <c r="E4" s="5">
         <v>20</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>578</v>
+        <v>581</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="6" t="s">
-        <v>579</v>
+        <v>582</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>579</v>
+        <v>582</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>580</v>
+        <v>583</v>
       </c>
       <c r="D5" s="4"/>
       <c r="E5" s="5">
         <v>40</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>581</v>
+        <v>584</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="6" t="s">
-        <v>582</v>
+        <v>585</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>582</v>
+        <v>585</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>583</v>
+        <v>586</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>584</v>
+        <v>587</v>
       </c>
       <c r="E6" s="5">
         <v>20</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>585</v>
+        <v>588</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="6" t="s">
-        <v>586</v>
+        <v>589</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>586</v>
+        <v>589</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>587</v>
+        <v>590</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>588</v>
+        <v>591</v>
       </c>
       <c r="E7" s="5">
         <v>15</v>
       </c>
       <c r="F7" s="7" t="s">
-        <v>589</v>
+        <v>592</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="6" t="s">
-        <v>590</v>
+        <v>593</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>590</v>
+        <v>593</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>591</v>
+        <v>594</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>592</v>
+        <v>595</v>
       </c>
       <c r="E8" s="5">
         <v>40</v>
       </c>
       <c r="F8" s="7" t="s">
-        <v>593</v>
+        <v>596</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="6" t="s">
-        <v>594</v>
+        <v>597</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>594</v>
+        <v>597</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>595</v>
+        <v>598</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>596</v>
+        <v>599</v>
       </c>
       <c r="E9" s="5">
         <v>15</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>597</v>
+        <v>600</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="6" t="s">
-        <v>598</v>
+        <v>601</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>598</v>
+        <v>601</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>599</v>
+        <v>602</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>600</v>
+        <v>603</v>
       </c>
       <c r="E10" s="5">
         <v>15</v>
       </c>
       <c r="F10" s="7" t="s">
-        <v>601</v>
+        <v>604</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="6" t="s">
-        <v>602</v>
+        <v>605</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>602</v>
+        <v>605</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>603</v>
+        <v>606</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>604</v>
+        <v>607</v>
       </c>
       <c r="E11" s="5">
         <v>30</v>
       </c>
       <c r="F11" s="7" t="s">
-        <v>605</v>
+        <v>608</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="6" t="s">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>607</v>
+        <v>610</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>608</v>
+        <v>611</v>
       </c>
       <c r="E12" s="5">
         <v>15</v>
       </c>
       <c r="F12" s="7" t="s">
-        <v>609</v>
+        <v>612</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="6" t="s">
-        <v>610</v>
+        <v>613</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>610</v>
+        <v>613</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>611</v>
+        <v>614</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>612</v>
+        <v>615</v>
       </c>
       <c r="E13" s="5">
         <v>15</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>613</v>
+        <v>616</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="6" t="s">
-        <v>614</v>
+        <v>617</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>614</v>
+        <v>617</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>615</v>
+        <v>618</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>616</v>
+        <v>619</v>
       </c>
       <c r="E14" s="5">
         <v>20</v>
       </c>
       <c r="F14" s="7" t="s">
-        <v>617</v>
+        <v>620</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="6" t="s">
-        <v>618</v>
+        <v>621</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>618</v>
+        <v>621</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>619</v>
+        <v>622</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>620</v>
+        <v>623</v>
       </c>
       <c r="E15" s="5">
         <v>20</v>
       </c>
       <c r="F15" s="7" t="s">
-        <v>621</v>
+        <v>624</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="6" t="s">
-        <v>622</v>
+        <v>625</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>622</v>
+        <v>625</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>623</v>
+        <v>626</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>624</v>
+        <v>627</v>
       </c>
       <c r="E16" s="5">
         <v>15</v>
       </c>
       <c r="F16" s="7" t="s">
-        <v>625</v>
+        <v>628</v>
       </c>
     </row>
     <row r="17" spans="1:6">
       <c r="A17" s="6" t="s">
-        <v>626</v>
+        <v>629</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>626</v>
+        <v>629</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>627</v>
+        <v>630</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>628</v>
+        <v>631</v>
       </c>
       <c r="E17" s="5">
         <v>20</v>
       </c>
       <c r="F17" s="7" t="s">
-        <v>629</v>
+        <v>632</v>
       </c>
     </row>
     <row r="18" spans="1:6">
       <c r="A18" s="6" t="s">
-        <v>630</v>
+        <v>633</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>630</v>
+        <v>633</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>631</v>
+        <v>634</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>632</v>
+        <v>635</v>
       </c>
       <c r="E18" s="5">
         <v>12</v>
       </c>
       <c r="F18" s="7" t="s">
-        <v>633</v>
+        <v>636</v>
       </c>
     </row>
     <row r="19" spans="1:6">
       <c r="A19" s="6" t="s">
-        <v>634</v>
+        <v>637</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>634</v>
+        <v>637</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>635</v>
+        <v>638</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>636</v>
+        <v>639</v>
       </c>
       <c r="E19" s="5">
         <v>15</v>
       </c>
       <c r="F19" s="7" t="s">
-        <v>637</v>
+        <v>640</v>
       </c>
     </row>
     <row r="20" spans="1:6">
       <c r="A20" s="6" t="s">
-        <v>638</v>
+        <v>641</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>638</v>
+        <v>641</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>639</v>
+        <v>642</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>640</v>
+        <v>643</v>
       </c>
       <c r="E20" s="5">
         <v>12</v>
       </c>
       <c r="F20" s="7" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
     </row>
     <row r="21" spans="1:6">
       <c r="A21" s="6" t="s">
-        <v>642</v>
+        <v>645</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>642</v>
+        <v>645</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>643</v>
+        <v>646</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>644</v>
+        <v>647</v>
       </c>
       <c r="E21" s="5">
         <v>20</v>
       </c>
       <c r="F21" s="7" t="s">
-        <v>645</v>
+        <v>648</v>
       </c>
     </row>
     <row r="22" spans="1:6">
       <c r="A22" s="6" t="s">
-        <v>646</v>
+        <v>649</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>646</v>
+        <v>649</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>647</v>
+        <v>650</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>648</v>
+        <v>651</v>
       </c>
       <c r="E22" s="5">
         <v>15</v>
       </c>
       <c r="F22" s="7" t="s">
-        <v>649</v>
+        <v>652</v>
       </c>
     </row>
     <row r="23" spans="1:6">
       <c r="A23" s="6" t="s">
-        <v>650</v>
+        <v>653</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>650</v>
+        <v>653</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>651</v>
+        <v>654</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>652</v>
+        <v>655</v>
       </c>
       <c r="E23" s="5">
         <v>15</v>
       </c>
       <c r="F23" s="7" t="s">
-        <v>653</v>
+        <v>656</v>
       </c>
     </row>
     <row r="24" spans="1:6">
       <c r="A24" s="6" t="s">
-        <v>654</v>
+        <v>657</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>654</v>
+        <v>657</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>655</v>
+        <v>658</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>656</v>
+        <v>659</v>
       </c>
       <c r="E24" s="5">
         <v>15</v>
       </c>
       <c r="F24" s="7" t="s">
-        <v>657</v>
+        <v>660</v>
       </c>
     </row>
     <row r="25" spans="1:6">
       <c r="A25" s="6" t="s">
-        <v>658</v>
+        <v>661</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>658</v>
+        <v>661</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>659</v>
+        <v>662</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>660</v>
+        <v>663</v>
       </c>
       <c r="E25" s="5">
         <v>15</v>
       </c>
       <c r="F25" s="7" t="s">
-        <v>661</v>
+        <v>664</v>
       </c>
     </row>
     <row r="26" spans="1:6">
       <c r="A26" s="6" t="s">
-        <v>662</v>
+        <v>665</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>662</v>
+        <v>665</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>663</v>
+        <v>666</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>664</v>
+        <v>667</v>
       </c>
       <c r="E26" s="5">
         <v>15</v>
       </c>
       <c r="F26" s="7" t="s">
-        <v>665</v>
+        <v>668</v>
       </c>
     </row>
     <row r="27" spans="1:6">
       <c r="A27" s="6" t="s">
-        <v>666</v>
+        <v>669</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>666</v>
+        <v>669</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>667</v>
+        <v>670</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>668</v>
+        <v>671</v>
       </c>
       <c r="E27" s="5">
         <v>15</v>
       </c>
       <c r="F27" s="7" t="s">
-        <v>669</v>
+        <v>672</v>
       </c>
     </row>
     <row r="28" spans="1:6">
       <c r="A28" s="6" t="s">
-        <v>670</v>
+        <v>673</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>670</v>
+        <v>673</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>671</v>
+        <v>674</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>672</v>
+        <v>675</v>
       </c>
       <c r="E28" s="5">
         <v>3</v>
       </c>
       <c r="F28" s="7" t="s">
-        <v>483</v>
+        <v>486</v>
       </c>
     </row>
     <row r="29" spans="1:6">
       <c r="A29" s="6" t="s">
-        <v>673</v>
+        <v>676</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>673</v>
+        <v>676</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>674</v>
+        <v>677</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>675</v>
+        <v>678</v>
       </c>
       <c r="E29" s="5">
         <v>18</v>
       </c>
       <c r="F29" s="7" t="s">
-        <v>676</v>
+        <v>679</v>
       </c>
     </row>
     <row r="30" spans="1:6">
       <c r="A30" s="6" t="s">
-        <v>677</v>
+        <v>680</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>677</v>
+        <v>680</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>678</v>
+        <v>681</v>
       </c>
       <c r="D30" s="5" t="s">
-        <v>679</v>
+        <v>682</v>
       </c>
       <c r="E30" s="5">
         <v>15</v>
       </c>
       <c r="F30" s="7" t="s">
-        <v>680</v>
+        <v>683</v>
       </c>
     </row>
     <row r="31" spans="1:6">
       <c r="A31" s="6" t="s">
-        <v>681</v>
+        <v>684</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>681</v>
+        <v>684</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>682</v>
+        <v>685</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>683</v>
+        <v>686</v>
       </c>
       <c r="E31" s="5">
         <v>15</v>
       </c>
       <c r="F31" s="7" t="s">
-        <v>684</v>
+        <v>687</v>
       </c>
     </row>
     <row r="32" spans="1:6">
       <c r="A32" s="6" t="s">
-        <v>685</v>
+        <v>688</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>685</v>
+        <v>688</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>686</v>
+        <v>689</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>687</v>
+        <v>690</v>
       </c>
       <c r="E32" s="5">
         <v>15</v>
       </c>
       <c r="F32" s="7" t="s">
-        <v>688</v>
+        <v>691</v>
       </c>
     </row>
     <row r="33" spans="1:6">
       <c r="A33" s="6" t="s">
-        <v>689</v>
+        <v>692</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>689</v>
+        <v>692</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>690</v>
+        <v>693</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>691</v>
+        <v>694</v>
       </c>
       <c r="E33" s="5">
         <v>18</v>
       </c>
       <c r="F33" s="7" t="s">
-        <v>692</v>
+        <v>695</v>
       </c>
     </row>
     <row r="34" spans="1:6">
       <c r="A34" s="6" t="s">
-        <v>693</v>
+        <v>696</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>693</v>
+        <v>696</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>694</v>
+        <v>697</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>695</v>
+        <v>698</v>
       </c>
       <c r="E34" s="5">
         <v>20</v>
       </c>
       <c r="F34" s="7" t="s">
-        <v>696</v>
+        <v>699</v>
       </c>
     </row>
     <row r="35" spans="1:6">
       <c r="A35" s="6" t="s">
-        <v>697</v>
+        <v>700</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>697</v>
+        <v>700</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>698</v>
+        <v>701</v>
       </c>
       <c r="D35" s="5" t="s">
-        <v>699</v>
+        <v>702</v>
       </c>
       <c r="E35" s="5">
         <v>15</v>
       </c>
       <c r="F35" s="7" t="s">
-        <v>700</v>
+        <v>703</v>
       </c>
     </row>
     <row r="36" spans="1:6">
       <c r="A36" s="6" t="s">
-        <v>701</v>
+        <v>704</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>701</v>
+        <v>704</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>702</v>
+        <v>705</v>
       </c>
       <c r="D36" s="5" t="s">
-        <v>703</v>
+        <v>706</v>
       </c>
       <c r="E36" s="5">
         <v>18</v>
       </c>
       <c r="F36" s="7" t="s">
-        <v>704</v>
+        <v>707</v>
       </c>
     </row>
     <row r="37" spans="1:6">
       <c r="A37" s="6" t="s">
-        <v>705</v>
+        <v>708</v>
       </c>
       <c r="B37" s="6" t="s">
-        <v>705</v>
+        <v>708</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>706</v>
+        <v>709</v>
       </c>
       <c r="D37" s="5" t="s">
-        <v>707</v>
+        <v>710</v>
       </c>
       <c r="E37" s="5">
         <v>15</v>
       </c>
       <c r="F37" s="7" t="s">
-        <v>708</v>
+        <v>711</v>
       </c>
     </row>
     <row r="38" spans="1:6">
       <c r="A38" s="6" t="s">
-        <v>709</v>
+        <v>712</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>709</v>
+        <v>712</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>710</v>
+        <v>713</v>
       </c>
       <c r="D38" s="5" t="s">
-        <v>711</v>
+        <v>714</v>
       </c>
       <c r="E38" s="5">
         <v>15</v>
       </c>
       <c r="F38" s="7" t="s">
-        <v>712</v>
+        <v>715</v>
       </c>
     </row>
     <row r="39" spans="1:6">
       <c r="A39" s="6" t="s">
-        <v>713</v>
+        <v>716</v>
       </c>
       <c r="B39" s="6" t="s">
-        <v>713</v>
+        <v>716</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>714</v>
+        <v>717</v>
       </c>
       <c r="D39" s="5" t="s">
-        <v>715</v>
+        <v>718</v>
       </c>
       <c r="E39" s="5">
         <v>15</v>
       </c>
       <c r="F39" s="7" t="s">
-        <v>716</v>
+        <v>719</v>
       </c>
     </row>
     <row r="40" spans="1:6">
       <c r="A40" s="6" t="s">
-        <v>717</v>
+        <v>720</v>
       </c>
       <c r="B40" s="6" t="s">
-        <v>717</v>
+        <v>720</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>718</v>
+        <v>721</v>
       </c>
       <c r="D40" s="5" t="s">
-        <v>719</v>
+        <v>722</v>
       </c>
       <c r="E40" s="5">
         <v>15</v>
       </c>
       <c r="F40" s="7" t="s">
-        <v>720</v>
+        <v>723</v>
       </c>
     </row>
     <row r="41" spans="1:6">
       <c r="A41" s="6" t="s">
-        <v>721</v>
+        <v>724</v>
       </c>
       <c r="B41" s="6" t="s">
-        <v>721</v>
+        <v>724</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>722</v>
+        <v>725</v>
       </c>
       <c r="D41" s="5" t="s">
-        <v>723</v>
+        <v>726</v>
       </c>
       <c r="E41" s="5">
         <v>15</v>
       </c>
       <c r="F41" s="7" t="s">
-        <v>724</v>
+        <v>727</v>
       </c>
     </row>
     <row r="42" spans="1:6">
       <c r="A42" s="6" t="s">
-        <v>725</v>
+        <v>728</v>
       </c>
       <c r="B42" s="6" t="s">
-        <v>725</v>
+        <v>728</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>726</v>
+        <v>729</v>
       </c>
       <c r="D42" s="5" t="s">
-        <v>727</v>
+        <v>730</v>
       </c>
       <c r="E42" s="5">
         <v>15</v>
       </c>
       <c r="F42" s="7" t="s">
-        <v>728</v>
+        <v>731</v>
       </c>
     </row>
     <row r="43" spans="1:6">
       <c r="A43" s="6" t="s">
-        <v>729</v>
+        <v>732</v>
       </c>
       <c r="B43" s="6" t="s">
-        <v>729</v>
+        <v>732</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>730</v>
+        <v>733</v>
       </c>
       <c r="D43" s="5" t="s">
-        <v>731</v>
+        <v>734</v>
       </c>
       <c r="E43" s="5">
         <v>18</v>
       </c>
       <c r="F43" s="7" t="s">
-        <v>732</v>
+        <v>735</v>
       </c>
     </row>
     <row r="44" spans="1:6">
       <c r="A44" s="6" t="s">
-        <v>733</v>
+        <v>736</v>
       </c>
       <c r="B44" s="6" t="s">
-        <v>733</v>
+        <v>736</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>734</v>
+        <v>737</v>
       </c>
       <c r="D44" s="5" t="s">
-        <v>735</v>
+        <v>738</v>
       </c>
       <c r="E44" s="5">
         <v>15</v>
       </c>
       <c r="F44" s="7" t="s">
-        <v>736</v>
+        <v>739</v>
       </c>
     </row>
     <row r="45" spans="1:6">
       <c r="A45" s="6" t="s">
-        <v>737</v>
+        <v>740</v>
       </c>
       <c r="B45" s="6" t="s">
-        <v>737</v>
+        <v>740</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>738</v>
+        <v>741</v>
       </c>
       <c r="D45" s="5" t="s">
-        <v>739</v>
+        <v>742</v>
       </c>
       <c r="E45" s="5">
         <v>10000000</v>
       </c>
       <c r="F45" s="7" t="s">
-        <v>740</v>
+        <v>743</v>
       </c>
     </row>
     <row r="46" spans="1:6">
       <c r="A46" s="6" t="s">
-        <v>741</v>
+        <v>744</v>
       </c>
       <c r="B46" s="6" t="s">
-        <v>741</v>
+        <v>744</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>742</v>
+        <v>745</v>
       </c>
       <c r="D46" s="5" t="s">
-        <v>743</v>
+        <v>746</v>
       </c>
       <c r="E46" s="5">
         <v>15</v>
       </c>
       <c r="F46" s="7" t="s">
-        <v>744</v>
+        <v>747</v>
       </c>
     </row>
     <row r="47" spans="1:6">
       <c r="A47" s="6" t="s">
-        <v>745</v>
+        <v>748</v>
       </c>
       <c r="B47" s="6" t="s">
-        <v>745</v>
+        <v>748</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>746</v>
+        <v>749</v>
       </c>
       <c r="D47" s="5" t="s">
-        <v>747</v>
+        <v>750</v>
       </c>
       <c r="E47" s="5">
         <v>15</v>
       </c>
       <c r="F47" s="7" t="s">
-        <v>748</v>
+        <v>751</v>
       </c>
     </row>
     <row r="48" spans="1:6">
       <c r="A48" s="6" t="s">
-        <v>749</v>
+        <v>752</v>
       </c>
       <c r="B48" s="6" t="s">
-        <v>749</v>
+        <v>752</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>750</v>
+        <v>753</v>
       </c>
       <c r="D48" s="5" t="s">
-        <v>751</v>
+        <v>754</v>
       </c>
       <c r="E48" s="5">
         <v>12</v>
       </c>
       <c r="F48" s="7" t="s">
-        <v>752</v>
+        <v>755</v>
       </c>
     </row>
     <row r="49" spans="1:6">
       <c r="A49" s="6" t="s">
-        <v>753</v>
+        <v>756</v>
       </c>
       <c r="B49" s="6" t="s">
-        <v>753</v>
+        <v>756</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>754</v>
+        <v>757</v>
       </c>
       <c r="D49" s="5" t="s">
-        <v>755</v>
+        <v>758</v>
       </c>
       <c r="E49" s="5">
         <v>15</v>
       </c>
       <c r="F49" s="7" t="s">
-        <v>756</v>
+        <v>759</v>
       </c>
     </row>
     <row r="50" spans="1:6">
       <c r="A50" s="6" t="s">
-        <v>757</v>
+        <v>760</v>
       </c>
       <c r="B50" s="6" t="s">
-        <v>757</v>
+        <v>760</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>758</v>
+        <v>761</v>
       </c>
       <c r="D50" s="5" t="s">
-        <v>759</v>
+        <v>762</v>
       </c>
       <c r="E50" s="5">
         <v>40</v>
       </c>
       <c r="F50" s="7" t="s">
-        <v>760</v>
+        <v>763</v>
       </c>
     </row>
     <row r="51" spans="1:6">
       <c r="A51" s="6" t="s">
-        <v>761</v>
+        <v>764</v>
       </c>
       <c r="B51" s="6" t="s">
-        <v>761</v>
+        <v>764</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>762</v>
+        <v>765</v>
       </c>
       <c r="D51" s="5" t="s">
-        <v>763</v>
+        <v>766</v>
       </c>
       <c r="E51" s="5">
         <v>50</v>
       </c>
       <c r="F51" s="7" t="s">
-        <v>764</v>
+        <v>767</v>
       </c>
     </row>
     <row r="52" spans="1:6">
       <c r="A52" s="6" t="s">
-        <v>765</v>
+        <v>768</v>
       </c>
       <c r="B52" s="6" t="s">
-        <v>765</v>
+        <v>768</v>
       </c>
       <c r="C52" s="5" t="s">
-        <v>766</v>
+        <v>769</v>
       </c>
       <c r="D52" s="5" t="s">
-        <v>767</v>
+        <v>770</v>
       </c>
       <c r="E52" s="5">
         <v>18</v>
       </c>
       <c r="F52" s="7" t="s">
-        <v>768</v>
+        <v>771</v>
       </c>
     </row>
     <row r="53" spans="1:6">
       <c r="A53" s="6" t="s">
-        <v>769</v>
+        <v>772</v>
       </c>
       <c r="B53" s="6" t="s">
-        <v>769</v>
+        <v>772</v>
       </c>
       <c r="C53" s="5" t="s">
-        <v>770</v>
+        <v>773</v>
       </c>
       <c r="D53" s="5" t="s">
-        <v>771</v>
+        <v>774</v>
       </c>
       <c r="E53" s="5">
         <v>15</v>
       </c>
       <c r="F53" s="7" t="s">
-        <v>772</v>
+        <v>775</v>
       </c>
     </row>
     <row r="54" spans="1:6">
       <c r="A54" s="6" t="s">
-        <v>773</v>
+        <v>776</v>
       </c>
       <c r="B54" s="6" t="s">
-        <v>773</v>
+        <v>776</v>
       </c>
       <c r="C54" s="5" t="s">
-        <v>774</v>
+        <v>777</v>
       </c>
       <c r="D54" s="5" t="s">
-        <v>775</v>
+        <v>778</v>
       </c>
       <c r="E54" s="5">
         <v>20</v>
       </c>
       <c r="F54" s="7" t="s">
-        <v>776</v>
+        <v>779</v>
       </c>
     </row>
     <row r="55" spans="1:6">
       <c r="A55" s="6" t="s">
-        <v>777</v>
+        <v>780</v>
       </c>
       <c r="B55" s="6" t="s">
-        <v>777</v>
+        <v>780</v>
       </c>
       <c r="C55" s="5" t="s">
-        <v>778</v>
+        <v>781</v>
       </c>
       <c r="D55" s="5" t="s">
-        <v>779</v>
+        <v>782</v>
       </c>
       <c r="E55" s="5">
         <v>12</v>
       </c>
       <c r="F55" s="7" t="s">
-        <v>780</v>
+        <v>783</v>
       </c>
     </row>
     <row r="56" spans="1:6">
       <c r="A56" s="6" t="s">
-        <v>781</v>
+        <v>784</v>
       </c>
       <c r="B56" s="6" t="s">
-        <v>781</v>
+        <v>784</v>
       </c>
       <c r="C56" s="5" t="s">
-        <v>782</v>
+        <v>785</v>
       </c>
       <c r="D56" s="5" t="s">
-        <v>783</v>
+        <v>786</v>
       </c>
       <c r="E56" s="5">
         <v>20</v>
       </c>
       <c r="F56" s="7" t="s">
-        <v>784</v>
+        <v>787</v>
       </c>
     </row>
     <row r="57" spans="1:6">
       <c r="A57" s="6" t="s">
-        <v>785</v>
+        <v>788</v>
       </c>
       <c r="B57" s="6" t="s">
-        <v>785</v>
+        <v>788</v>
       </c>
       <c r="C57" s="5" t="s">
-        <v>786</v>
+        <v>789</v>
       </c>
       <c r="D57" s="5" t="s">
-        <v>787</v>
+        <v>790</v>
       </c>
       <c r="E57" s="5">
         <v>20</v>
       </c>
       <c r="F57" s="7" t="s">
-        <v>788</v>
+        <v>791</v>
       </c>
     </row>
     <row r="58" spans="1:6">
       <c r="A58" s="6" t="s">
-        <v>789</v>
+        <v>792</v>
       </c>
       <c r="B58" s="6" t="s">
-        <v>789</v>
+        <v>792</v>
       </c>
       <c r="C58" s="5" t="s">
-        <v>790</v>
+        <v>793</v>
       </c>
       <c r="D58" s="5" t="s">
-        <v>791</v>
+        <v>794</v>
       </c>
       <c r="E58" s="5">
         <v>15</v>
       </c>
       <c r="F58" s="7" t="s">
-        <v>792</v>
+        <v>795</v>
       </c>
     </row>
     <row r="59" spans="1:6">
       <c r="A59" s="6" t="s">
-        <v>793</v>
+        <v>796</v>
       </c>
       <c r="B59" s="6" t="s">
-        <v>793</v>
+        <v>796</v>
       </c>
       <c r="C59" s="5" t="s">
-        <v>794</v>
+        <v>797</v>
       </c>
       <c r="D59" s="5" t="s">
-        <v>795</v>
+        <v>798</v>
       </c>
       <c r="E59" s="5">
         <v>15</v>
       </c>
       <c r="F59" s="7" t="s">
-        <v>796</v>
+        <v>799</v>
       </c>
     </row>
     <row r="60" spans="1:6">
       <c r="A60" s="6" t="s">
-        <v>797</v>
+        <v>800</v>
       </c>
       <c r="B60" s="6" t="s">
-        <v>797</v>
+        <v>800</v>
       </c>
       <c r="C60" s="5" t="s">
-        <v>798</v>
+        <v>801</v>
       </c>
       <c r="D60" s="5" t="s">
-        <v>799</v>
+        <v>802</v>
       </c>
       <c r="E60" s="5">
         <v>40</v>
       </c>
       <c r="F60" s="7" t="s">
-        <v>800</v>
+        <v>803</v>
       </c>
     </row>
     <row r="61" spans="1:6">
       <c r="A61" s="6" t="s">
-        <v>801</v>
+        <v>804</v>
       </c>
       <c r="B61" s="6" t="s">
-        <v>801</v>
+        <v>804</v>
       </c>
       <c r="C61" s="5" t="s">
-        <v>802</v>
+        <v>805</v>
       </c>
       <c r="D61" s="5" t="s">
-        <v>803</v>
+        <v>806</v>
       </c>
       <c r="E61" s="5">
         <v>15</v>
       </c>
       <c r="F61" s="7" t="s">
-        <v>804</v>
+        <v>807</v>
       </c>
     </row>
     <row r="62" spans="1:6">
       <c r="A62" s="6" t="s">
-        <v>805</v>
+        <v>808</v>
       </c>
       <c r="B62" s="6" t="s">
-        <v>805</v>
+        <v>808</v>
       </c>
       <c r="C62" s="5" t="s">
-        <v>806</v>
+        <v>809</v>
       </c>
       <c r="D62" s="5" t="s">
-        <v>807</v>
+        <v>810</v>
       </c>
       <c r="E62" s="5">
         <v>20</v>
       </c>
       <c r="F62" s="7" t="s">
-        <v>808</v>
+        <v>811</v>
       </c>
     </row>
     <row r="63" spans="1:6">
       <c r="A63" s="6" t="s">
-        <v>809</v>
+        <v>812</v>
       </c>
       <c r="B63" s="6" t="s">
-        <v>809</v>
+        <v>812</v>
       </c>
       <c r="C63" s="5" t="s">
-        <v>810</v>
+        <v>813</v>
       </c>
       <c r="D63" s="5" t="s">
-        <v>811</v>
+        <v>814</v>
       </c>
       <c r="E63" s="5">
         <v>20</v>
       </c>
       <c r="F63" s="7" t="s">
-        <v>812</v>
+        <v>815</v>
       </c>
     </row>
     <row r="64" ht="26" spans="1:6">
       <c r="A64" s="6" t="s">
-        <v>813</v>
+        <v>816</v>
       </c>
       <c r="B64" s="6" t="s">
-        <v>813</v>
+        <v>816</v>
       </c>
       <c r="C64" s="5" t="s">
-        <v>814</v>
+        <v>817</v>
       </c>
       <c r="D64" s="5" t="s">
-        <v>815</v>
+        <v>818</v>
       </c>
       <c r="E64" s="5">
         <v>15</v>
       </c>
       <c r="F64" s="7" t="s">
-        <v>816</v>
+        <v>819</v>
       </c>
     </row>
     <row r="65" spans="1:6">
       <c r="A65" s="6" t="s">
-        <v>817</v>
+        <v>820</v>
       </c>
       <c r="B65" s="6" t="s">
-        <v>817</v>
+        <v>820</v>
       </c>
       <c r="C65" s="5" t="s">
-        <v>818</v>
+        <v>821</v>
       </c>
       <c r="D65" s="5" t="s">
-        <v>819</v>
+        <v>822</v>
       </c>
       <c r="E65" s="5">
         <v>20</v>
       </c>
       <c r="F65" s="7" t="s">
-        <v>820</v>
+        <v>823</v>
       </c>
     </row>
     <row r="66" spans="1:6">
       <c r="A66" s="6" t="s">
-        <v>821</v>
+        <v>824</v>
       </c>
       <c r="B66" s="6" t="s">
-        <v>821</v>
+        <v>824</v>
       </c>
       <c r="C66" s="5" t="s">
-        <v>822</v>
+        <v>825</v>
       </c>
       <c r="D66" s="5" t="s">
-        <v>823</v>
+        <v>826</v>
       </c>
       <c r="E66" s="5">
         <v>6</v>
       </c>
       <c r="F66" s="7" t="s">
-        <v>824</v>
+        <v>827</v>
       </c>
     </row>
     <row r="67" spans="1:6">
       <c r="A67" s="6" t="s">
-        <v>825</v>
+        <v>828</v>
       </c>
       <c r="B67" s="6" t="s">
-        <v>825</v>
+        <v>828</v>
       </c>
       <c r="C67" s="5" t="s">
-        <v>826</v>
+        <v>829</v>
       </c>
       <c r="D67" s="5" t="s">
-        <v>827</v>
+        <v>830</v>
       </c>
       <c r="E67" s="5">
         <v>20</v>
       </c>
       <c r="F67" s="7" t="s">
-        <v>828</v>
+        <v>831</v>
       </c>
     </row>
     <row r="68" spans="1:6">
       <c r="A68" s="6" t="s">
-        <v>829</v>
+        <v>832</v>
       </c>
       <c r="B68" s="6" t="s">
-        <v>829</v>
+        <v>832</v>
       </c>
       <c r="C68" s="5" t="s">
-        <v>830</v>
+        <v>833</v>
       </c>
       <c r="D68" s="5" t="s">
-        <v>831</v>
+        <v>834</v>
       </c>
       <c r="E68" s="5">
         <v>18</v>
       </c>
       <c r="F68" s="7" t="s">
-        <v>832</v>
+        <v>835</v>
       </c>
     </row>
     <row r="69" spans="1:6">
       <c r="A69" s="6" t="s">
-        <v>833</v>
+        <v>836</v>
       </c>
       <c r="B69" s="6" t="s">
-        <v>833</v>
+        <v>836</v>
       </c>
       <c r="C69" s="5" t="s">
-        <v>834</v>
+        <v>837</v>
       </c>
       <c r="D69" s="5" t="s">
-        <v>835</v>
+        <v>838</v>
       </c>
       <c r="E69" s="5">
         <v>12</v>
       </c>
       <c r="F69" s="7" t="s">
-        <v>836</v>
+        <v>839</v>
       </c>
     </row>
     <row r="70" spans="1:6">
       <c r="A70" s="6" t="s">
-        <v>837</v>
+        <v>840</v>
       </c>
       <c r="B70" s="6" t="s">
-        <v>837</v>
+        <v>840</v>
       </c>
       <c r="C70" s="5" t="s">
-        <v>838</v>
+        <v>841</v>
       </c>
       <c r="D70" s="5" t="s">
-        <v>839</v>
+        <v>842</v>
       </c>
       <c r="E70" s="5">
         <v>18</v>
       </c>
       <c r="F70" s="7" t="s">
-        <v>840</v>
+        <v>843</v>
       </c>
     </row>
     <row r="71" spans="1:6">
       <c r="A71" s="6" t="s">
-        <v>841</v>
+        <v>844</v>
       </c>
       <c r="B71" s="6" t="s">
-        <v>841</v>
+        <v>844</v>
       </c>
       <c r="C71" s="5" t="s">
-        <v>842</v>
+        <v>845</v>
       </c>
       <c r="D71" s="5" t="s">
-        <v>843</v>
+        <v>846</v>
       </c>
       <c r="E71" s="5">
         <v>6</v>
       </c>
       <c r="F71" s="7" t="s">
-        <v>844</v>
+        <v>847</v>
       </c>
     </row>
     <row r="72" spans="1:6">
       <c r="A72" s="6" t="s">
-        <v>845</v>
+        <v>848</v>
       </c>
       <c r="B72" s="6" t="s">
-        <v>845</v>
+        <v>848</v>
       </c>
       <c r="C72" s="5" t="s">
-        <v>846</v>
+        <v>849</v>
       </c>
       <c r="D72" s="5" t="s">
-        <v>847</v>
+        <v>850</v>
       </c>
       <c r="E72" s="5">
         <v>15</v>
       </c>
       <c r="F72" s="7" t="s">
-        <v>848</v>
+        <v>851</v>
       </c>
     </row>
     <row r="75" spans="1:6">

--- a/Src/Assets/StreamingAssets/Common/Tables/Tables/Hero&Enemy.xlsx
+++ b/Src/Assets/StreamingAssets/Common/Tables/Tables/Hero&Enemy.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="25600" windowHeight="12080" activeTab="3"/>
+    <workbookView windowWidth="21600" windowHeight="9555" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="HeroSkill" sheetId="4" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1278" uniqueCount="852">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1288" uniqueCount="852">
   <si>
     <t>Key</t>
   </si>
@@ -1298,19 +1298,13 @@
     <t>你的攻击造成伤害时，你回复等量生命值。</t>
   </si>
   <si>
-    <t>Mountain Crusher_Enemy</t>
-  </si>
-  <si>
-    <t>获得伤害*3算子</t>
-  </si>
-  <si>
     <t>Clone Technique</t>
   </si>
   <si>
     <t>毫毛术</t>
   </si>
   <si>
-    <t>第三回合起每隔6个回合，你分裂为3个分身，血量不变且每个单位分得1/3资源（向上取整），并失去【千钧棒】。该状态持续3回合，复原时六耳猕猴获得分身的所有资源与分身血量之和的1/3血量（向下取整）。（先不装）</t>
+    <t>第三回合起每隔6个回合，你分裂为3个分身，血量不变且每个单位分得1/3资源（向上取整），并失去【千钧棒】。该状态持续3回合，复原时六耳猕猴获得分身的所有资源与分身血量之和的1/3血量（向下取整）。</t>
   </si>
   <si>
     <t>Venom</t>
@@ -1413,7 +1407,7 @@
     <t>不可侵犯</t>
   </si>
   <si>
-    <t>若场上的图腾被破坏，立刻进入高攻击欲望状态。（先不装）</t>
+    <t>若场上的图腾被破坏，立刻进入高攻击欲望状态。</t>
   </si>
   <si>
     <t>Ominous Feather</t>
@@ -1431,7 +1425,7 @@
     <t>无休</t>
   </si>
   <si>
-    <t>高攻击欲望（先不装），你的攻击命中时，返回此次攻击消耗的资源。</t>
+    <t>高攻击欲望，你的攻击命中时，返回此次攻击消耗的资源。</t>
   </si>
   <si>
     <t>Sturdy Shield</t>
@@ -1440,7 +1434,7 @@
     <t>坚盾</t>
   </si>
   <si>
-    <t>低攻击欲望（先不装），你的防御行为生效于全体友方。</t>
+    <t>低攻击欲望，你的防御行为生效于全体友方。</t>
   </si>
   <si>
     <t>Overconfidence</t>
@@ -1464,7 +1458,7 @@
     <t>哺育</t>
   </si>
   <si>
-    <t>你入场的第三回合，成长为狼（暂时不装）</t>
+    <t>你入场的第三回合，成长为狼。</t>
   </si>
   <si>
     <t>Wolf Grudge</t>
@@ -1473,7 +1467,7 @@
     <t>狼怨</t>
   </si>
   <si>
-    <t>受伤叠加一层复仇，造成伤害失去一点复仇，幼狼死亡获得三点复仇，其他狼死亡获得两点复仇。你每有一层复仇，伤害+1，有复仇时为高攻击欲望。（暂时没有实装后半段）</t>
+    <t>受伤叠加一层复仇，造成伤害失去一点复仇，幼狼死亡获得三点复仇，其他狼死亡获得两点复仇。你每有一层复仇，伤害+1，有复仇时为高攻击欲望。</t>
   </si>
   <si>
     <t>Leader Catch</t>
@@ -1485,6 +1479,12 @@
     <t>当场上所有类型为Boss和Elite的单位全部死亡时，玩家赢得此局游戏。</t>
   </si>
   <si>
+    <t>Daily Growing</t>
+  </si>
+  <si>
+    <t>每回合结束时，你造成的伤害+1（可叠加）。</t>
+  </si>
+  <si>
     <t>MaxHP</t>
   </si>
   <si>
@@ -1494,7 +1494,7 @@
     <t>EnemyType</t>
   </si>
   <si>
-    <t>BronzeGuardian</t>
+    <t>Bronze Guardian</t>
   </si>
   <si>
     <t>青铜镇守者</t>
@@ -1503,13 +1503,13 @@
     <t>【熔铸】第9回合，你击杀场上所有存活的青铜小鬼，并获得它们的资源，你每击杀一个青铜小鬼，你的伤害*2，攻击力+0.5。</t>
   </si>
   <si>
-    <t>["MoltenCast", "Leader Catch"]</t>
+    <t>["Molten Cast", "Leader Catch"]</t>
   </si>
   <si>
     <t>Boss</t>
   </si>
   <si>
-    <t>BronzeImp</t>
+    <t>Bronze Imp</t>
   </si>
   <si>
     <t>青铜小鬼</t>
@@ -1524,7 +1524,7 @@
     <t>Minion</t>
   </si>
   <si>
-    <t>AncientTree</t>
+    <t>Ancient Tree</t>
   </si>
   <si>
     <t>古老树木</t>
@@ -1533,10 +1533,19 @@
     <t>【播种】从第2回合起每隔3回合，你失去3点血量，召唤两个小树领。【枝繁叶茂】若你连续4回合未受到伤害，你回复5点血量，然后重置此技能计数。</t>
   </si>
   <si>
-    <t>["Sow", "LushGrowth", "Leader Catch"]</t>
-  </si>
-  <si>
-    <t>IntangibleWater</t>
+    <t>["Sow", "Lush Growth", "Leader Catch"]</t>
+  </si>
+  <si>
+    <t>Little Tree</t>
+  </si>
+  <si>
+    <t>小树灵</t>
+  </si>
+  <si>
+    <t>["Daily Growing"]</t>
+  </si>
+  <si>
+    <t>Formless Water</t>
   </si>
   <si>
     <t>无形之水</t>
@@ -1548,7 +1557,7 @@
     <t>["Tsunami"]</t>
   </si>
   <si>
-    <t>BurningAvenger</t>
+    <t>Burning Avenger</t>
   </si>
   <si>
     <t>焚烧复仇者</t>
@@ -1557,10 +1566,10 @@
     <t>【焚烧殆尽】你第一次补给时获得10个'焚'标记，每回合结束时你失去一个'焚'标记，当你击杀一名角色时你获得3个'焚'标记。每拥有一个'焚'标记，你的伤害+1。</t>
   </si>
   <si>
-    <t>["ScorchedOblivion"]</t>
-  </si>
-  <si>
-    <t>EarthBurier</t>
+    <t>["Scorched Oblivion"]</t>
+  </si>
+  <si>
+    <t>Earth Burier</t>
   </si>
   <si>
     <t>大地送葬者</t>
@@ -1569,19 +1578,10 @@
     <t>【丰壤祝福】当你造成一次伤害后，你可以获得一个伤害护盾（抵消一次伤害），该护盾可叠加。【回归大地】当你对一名角色造成伤害时，若其血量小于自身血量上限的1/3，你直接将其击杀。</t>
   </si>
   <si>
-    <t>["FertileBlessing", "ReturnToEarth"]</t>
-  </si>
-  <si>
-    <t>LittleTree</t>
-  </si>
-  <si>
-    <t>小树灵</t>
-  </si>
-  <si>
-    <t>["DailyGrowing"]</t>
-  </si>
-  <si>
-    <t>PlagueIncarnation</t>
+    <t>["Fertile Blessing", "Return to Earth"]</t>
+  </si>
+  <si>
+    <t>Plague Incarnation</t>
   </si>
   <si>
     <t>瘟疫化身</t>
@@ -1590,10 +1590,10 @@
     <t>【瘴气】第3回合，你对全体敌方成员施加一层'尸毒'标记。当你对其他角色造成伤害时令其获得一层'尸毒'标记，当拥有'尸毒'标记的角色攻击你且未对你造成伤害时你可令其获得一个标记，当拥有标记的角色对你造成伤害时其失去所有标记。回合结束时，你对拥有n个标记的角色造成n点伤害。【焚城】第3回合起的每一个回合中，没有消耗资源的其他角色均受到来源于你的1点伤害。</t>
   </si>
   <si>
-    <t>["Miasma", "CityBurn"]</t>
-  </si>
-  <si>
-    <t>WarKing</t>
+    <t>["Miasma", "City Burn"]</t>
+  </si>
+  <si>
+    <t>War King</t>
   </si>
   <si>
     <t>战争之王</t>
@@ -1605,39 +1605,13 @@
     <t>["Conqueror", "Invader"]</t>
   </si>
   <si>
-    <t>FamineReaper</t>
+    <t>Famine Reaper</t>
   </si>
   <si>
     <t>饥民收割者</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>【巨贾】你开局拥有子弹</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11.25"/>
-        <color rgb="FFF9FAFB"/>
-        <rFont val="Segoe UI"/>
-        <charset val="134"/>
-      </rPr>
-      <t>20，剑</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11.25"/>
-        <color rgb="FFF9FAFB"/>
-        <rFont val="Segoe UI"/>
-        <charset val="134"/>
-      </rPr>
-      <t>10。【斩杀者】当你对敌方角色造成伤害时，若其剩余血量不大于n/3，你将其斩杀。（n为你们的资源数之差）</t>
-    </r>
+    <t>【巨贾】你开局拥有子弹20，剑10。【斩杀者】当你对敌方角色造成伤害时，若其剩余血量不大于n/3，你将其斩杀。（n为你们的资源数之差）</t>
   </si>
   <si>
     <t>["Magnate", "Slayer"]</t>
@@ -1652,7 +1626,7 @@
     <t>【赤地千里】当你攻击时，场上所有其他角色的补给无效。【虚像】当你使用'过来'时，最多受到5点伤害。</t>
   </si>
   <si>
-    <t>["ScorchedEarth", "Mirage"]</t>
+    <t>["Scorched Earth", "Mirage"]</t>
   </si>
   <si>
     <t>Death</t>
@@ -1664,7 +1638,7 @@
     <t>【死亡化身】第4回合起，你每隔4回合进入一次'生命收割'状态。'生命收割'状态下你不受到任何伤害，且伤害*4。该状态持续3回合。若你在一次'生命收割'状态下未能击杀任何目标，你下回合眩晕。</t>
   </si>
   <si>
-    <t>["DeathIncarnate", "Leader Catch"]</t>
+    <t>["Death Incarnate", "Leader Catch"]</t>
   </si>
   <si>
     <t>Imp</t>
@@ -1676,7 +1650,7 @@
     <t>无技能。</t>
   </si>
   <si>
-    <t>["DeathBound"]</t>
+    <t>["Deathbound"]</t>
   </si>
   <si>
     <t>Prophet</t>
@@ -1688,10 +1662,10 @@
     <t>【明镜】你的防御拥有反弹效果。【重演】你造成的伤害+n（n为你上次受到的伤害值）。【死亡感应】限定技，若正常判定下你将要死亡，你可以使用一次'逆转决策'。</t>
   </si>
   <si>
-    <t>["ClearMirror", "Encore", "DeathSense"]</t>
-  </si>
-  <si>
-    <t>NamelessSwordsaint</t>
+    <t>["Clear Mirror", "Encore", "Death Sense"]</t>
+  </si>
+  <si>
+    <t>Nameless Swordsaint</t>
   </si>
   <si>
     <t>无名剑圣</t>
@@ -1700,10 +1674,10 @@
     <t>【会心】当你的刀剑攻击命中时发动，你的下次攻击基础攻击力为10且无视一切防御和反弹效果，若此次攻击发动时目标使用了'挑衅'，则其不受到任何伤害。【剑势】你每造成一次伤害，都可获得一层'剑势'，每层'剑势'使你的攻击力+1，且刀剑攻击可以额外执行一次。当你受到伤害时，你的剑势清零。【求不得】若你最近的3次攻击都未对敌方单位造成伤害，你眩晕。【断舍离】限定技，当你的血量值降低到10以下，你的下次攻击消耗你的所有子弹和（m-6）把剑，且此次攻击的攻击力和伤害均+n。（m为你当前的刀剑数，n为你此次攻击消耗的资源。）</t>
   </si>
   <si>
-    <t>["CriticalStrike", "SwordMomentum", "Unattainable", "LettingGo"]</t>
-  </si>
-  <si>
-    <t>MagicBulletShooter</t>
+    <t>["Critical Strike", "Sword Momentum", "Unattainable", "Letting Go"]</t>
+  </si>
+  <si>
+    <t>Magic Bullet Shooter</t>
   </si>
   <si>
     <t>魔弹射手</t>
@@ -1712,7 +1686,7 @@
     <t>【魔弹】你开局拥有6颗'魔弹'，你的每次子弹攻击会消耗一颗'魔弹'。若你一次消耗了魔弹的攻击成功命中了敌方目标，则你直接将其击杀。【恶魔祭礼】你的第7n次子弹攻击拥有'恶魔祭品'效果，若此次攻击命中敌方目标，则你获得6颗'魔弹'；若此次攻击被反弹，则反弹伤害为你当前血量的一半（向上取整）。</t>
   </si>
   <si>
-    <t>["MagicBullet", "DemonicRite"]</t>
+    <t>["Magic Bullet", "Demonic Rite"]</t>
   </si>
   <si>
     <t>GanJiang</t>
@@ -1724,7 +1698,7 @@
     <t>【神锋】你的刀剑攻击造成的伤害*n（n为该攻击消耗的刀剑数）。【同命】莫邪受到伤害时，你令此伤害减半（向下取整），同时你受到等量伤害。</t>
   </si>
   <si>
-    <t>["DivineBlade", "SharedFate"]</t>
+    <t>["Divine Blade", "Shared Fate"]</t>
   </si>
   <si>
     <t>MoYe</t>
@@ -1736,7 +1710,7 @@
     <t>【淬刃】你的刀剑攻击可以指定全体敌方单位为目标，且攻击力+1。【同命】干将受到伤害时，你令此伤害减半（向下取整），同时你受到等量伤害。</t>
   </si>
   <si>
-    <t>["TemperedEdge", "SharedFate"]</t>
+    <t>["Tempered Edge", "Shared Fate"]</t>
   </si>
   <si>
     <t>MeiJianChi</t>
@@ -1748,7 +1722,7 @@
     <t>【庇佑】当干将与莫邪造成伤害时，你回复等量的血量。【复仇】当干将与莫邪都死亡时，你失去【庇佑】，获得【神锋】和【淬刃】。</t>
   </si>
   <si>
-    <t>["Benediction", "Vengeance", "DivineBlade", "TemperedEdge"]</t>
+    <t>["Benediction", "Vengeance", "Divine Blade", "Tempered Edge"]</t>
   </si>
   <si>
     <t>Faust</t>
@@ -1757,36 +1731,10 @@
     <t>浮士德</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>【梅菲斯特的契约】你每回合最多受到1点伤害。【堕落的进取者】若本回合场上进行补给的角色为多数，你下回合拥有【寻欢】。若场上进行攻击的角色为多数，你下回合拥有技能【好斗】。若场上防御的角色为多数，你下回合拥有技能【安逸】。若场上进行特殊行动的角色为多数，你下回合拥有技能【求爱】。若场上进行每类行动的角色数相同，你下回合拥有技能【求知】。其中【寻欢】你因补给获得的资源</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11.25"/>
-        <color rgb="FFF9FAFB"/>
-        <rFont val="Segoe UI"/>
-        <charset val="134"/>
-      </rPr>
-      <t>3；【好斗】你造成的伤害</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11.25"/>
-        <color rgb="FFF9FAFB"/>
-        <rFont val="Segoe UI"/>
-        <charset val="134"/>
-      </rPr>
-      <t>3，攻击力+1.5；【安逸】你可以使用2种防御，且若你如此做，视为你额外使用了一次'过来'；【求爱】当你造成伤害时，你可以获取对方3个资源（子弹优先）；【求知】你其他技能中的基础数值+1。</t>
-    </r>
-  </si>
-  <si>
-    <t>["MephistosPact", "FallenStriver", "PleasureSeeking", "Combativeness", "Ease", "Courtship", "KnowledgeSeeking"]</t>
+    <t>【梅菲斯特的契约】你每回合最多受到1点伤害。【堕落的进取者】若本回合场上进行补给的角色为多数，你下回合拥有【寻欢】。若场上进行攻击的角色为多数，你下回合拥有技能【好斗】。若场上防御的角色为多数，你下回合拥有技能【安逸】。若场上进行特殊行动的角色为多数，你下回合拥有技能【求爱】。若场上进行每类行动的角色数相同，你下回合拥有技能【求知】。其中【寻欢】你因补给获得的资源3；【好斗】你造成的伤害3，攻击力+1.5；【安逸】你可以使用2种防御，且若你如此做，视为你额外使用了一次'过来'；【求爱】当你造成伤害时，你可以获取对方3个资源（子弹优先）；【求知】你其他技能中的基础数值+1。</t>
+  </si>
+  <si>
+    <t>["Mephisto's Pact", "Fallen Striver", "Pleasure Seeking", "Combativeness", "Ease", "Courtship", "Knowledge Seeking"]</t>
   </si>
   <si>
     <t>Lucifer</t>
@@ -1798,10 +1746,10 @@
     <t>【崩坏】当你是场上血量最多的角色时，你每回合失去2点血量。【地狱集结】每隔5回合，你召唤3个堕落天使。场上最多同时存在7个堕落天使。【奋不顾身】当你的血量小于20时，你失去【地狱集结】，获得【你死我活】。</t>
   </si>
   <si>
-    <t>["Collapse", "HellGather", "DesperateStruggle", "LifeOrDeath", "Leader Catch"]</t>
-  </si>
-  <si>
-    <t>FallenAngel</t>
+    <t>["Collapse", "Hell Gather", "Desperate Struggle", "Life or Death", "Leader Catch"]</t>
+  </si>
+  <si>
+    <t>Fallen Angel</t>
   </si>
   <si>
     <t>堕落天使</t>
@@ -1810,10 +1758,10 @@
     <t>【你死我活】当你造成伤害时，你失去一半的血量（向下取整），对目标额外造成2n点伤害（n为你失去的血量）。</t>
   </si>
   <si>
-    <t>["LifeOrDeath"]</t>
-  </si>
-  <si>
-    <t>CunningJester</t>
+    <t>["Life or Death"]</t>
+  </si>
+  <si>
+    <t>Cunning Jester</t>
   </si>
   <si>
     <t>狡诈小丑</t>
@@ -1822,13 +1770,13 @@
     <t>【诡异戏法】敌方英雄每进行一次攻击，你的伤害+1。</t>
   </si>
   <si>
-    <t>["DeceptiveTrick"]</t>
+    <t>["Deceptive Trick"]</t>
   </si>
   <si>
     <t>Elite</t>
   </si>
   <si>
-    <t>RagingGiant</t>
+    <t>Raging Giant</t>
   </si>
   <si>
     <t>狂怒巨人</t>
@@ -1837,10 +1785,10 @@
     <t>【冲撞践踏】敌方英雄每进行一次防御，你的伤害+1。</t>
   </si>
   <si>
-    <t>["RampageStomp"]</t>
-  </si>
-  <si>
-    <t>FallingBlossomGeneral</t>
+    <t>["Rampage Stomp"]</t>
+  </si>
+  <si>
+    <t>Falling Blossom General</t>
   </si>
   <si>
     <t>落英飞将</t>
@@ -1849,10 +1797,10 @@
     <t>【飞花剑】你每造成一次伤害，获得一个"飞花"标记，在场上召唤一名"剑冢"（最多8个）。每个"飞花"标记使你的攻击力+0.5。【花辞树】你的血量不大于7时，你摧毁场上的所有"剑冢"，失去所有"飞花"标记，每个被摧毁的剑冢使你的伤害+1，受伤-1，且此回合起你每回合失去1点体力。</t>
   </si>
   <si>
-    <t>["FlyingFlower", "FlowerFarewell"]</t>
-  </si>
-  <si>
-    <t>SwordTomb</t>
+    <t>["Flying Flower", "Flower Farewell"]</t>
+  </si>
+  <si>
+    <t>Sword Tomb</t>
   </si>
   <si>
     <t>剑冢</t>
@@ -1864,7 +1812,7 @@
     <t>["Silence"]</t>
   </si>
   <si>
-    <t>CultLeader</t>
+    <t>Cult Leader</t>
   </si>
   <si>
     <t>密教领袖</t>
@@ -1873,7 +1821,7 @@
     <t>【图腾召唤】每三回合随机召唤一个图腾，场上有空余格子时为低攻击欲望，场上没有空余格子时为高攻击欲望。</t>
   </si>
   <si>
-    <t>["TotemCall", "Leader Catch"]</t>
+    <t>["Totem Call", "Leader Catch"]</t>
   </si>
   <si>
     <t>Follower</t>
@@ -1888,7 +1836,7 @@
     <t>["Devotion"]</t>
   </si>
   <si>
-    <t>BlackPhoenix</t>
+    <t>Black Phoenix</t>
   </si>
   <si>
     <t>黑炎凤凰</t>
@@ -1900,7 +1848,7 @@
     <t>["Rebirth", "Emberize"]</t>
   </si>
   <si>
-    <t>CorruptedTailor</t>
+    <t>Corrupted Tailor</t>
   </si>
   <si>
     <t>堕落裁缝</t>
@@ -1909,10 +1857,10 @@
     <t>【罗织】你开局获得n层伤害护盾（n为玩家拥有的装备总数）。【铸甲】你每3回合给除你以外的所有友方单位增加n点护甲。</t>
   </si>
   <si>
-    <t>["Fabrication", "ArmorForging"]</t>
-  </si>
-  <si>
-    <t>CorruptedBlacksmith</t>
+    <t>["Fabrication", "Armor Forging"]</t>
+  </si>
+  <si>
+    <t>Corrupted Blacksmith</t>
   </si>
   <si>
     <t>堕落铁匠</t>
@@ -1921,48 +1869,22 @@
     <t>【百炼】你的伤害+n。（n为玩家拥有的升级卡牌总数）。【铸刃】你每3回合令除你以外的所有友方单位下次攻击伤害+1。</t>
   </si>
   <si>
-    <t>["Tempering", "BladeForging"]</t>
-  </si>
-  <si>
-    <t>CorruptedAlchemist</t>
+    <t>["Tempering", "Blade Forging"]</t>
+  </si>
+  <si>
+    <t>Corrupted Alchemist</t>
   </si>
   <si>
     <t>堕落炼金师</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>【药品囤积】你开局拥有n发子弹，n把剑（n为玩家拥有的一次性道具总数）。【药品配给】你每3回合令除你以外的所有友方单位获得剑</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11.25"/>
-        <color rgb="FFF9FAFB"/>
-        <rFont val="Segoe UI"/>
-        <charset val="134"/>
-      </rPr>
-      <t>1，子弹</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11.25"/>
-        <color rgb="FFF9FAFB"/>
-        <rFont val="Segoe UI"/>
-        <charset val="134"/>
-      </rPr>
-      <t>1。</t>
-    </r>
-  </si>
-  <si>
-    <t>["PotionStockpiling", "PotionRationing"]</t>
-  </si>
-  <si>
-    <t>KingPhantom</t>
+    <t>【药品囤积】你开局拥有n发子弹，n把剑（n为玩家拥有的一次性道具总数）。【药品配给】你每3回合令除你以外的所有友方单位获得剑1，子弹1。</t>
+  </si>
+  <si>
+    <t>["Potion Stockpiling", "Potion Rationing"]</t>
+  </si>
+  <si>
+    <t>King Phantom</t>
   </si>
   <si>
     <t>王者虚像</t>
@@ -1974,7 +1896,7 @@
     <t>["Golden Vault", "Divine Pride"]</t>
   </si>
   <si>
-    <t>DisasterMaster</t>
+    <t>Disaster Master</t>
   </si>
   <si>
     <t>灾祸掌管者</t>
@@ -1983,10 +1905,10 @@
     <t>【天罚】每20回合，你对敌方场上的所有单位造成20点伤害。</t>
   </si>
   <si>
-    <t>["HeavenlyPunishment"]</t>
-  </si>
-  <si>
-    <t>PuppetMaster</t>
+    <t>["Heavenly Punishment"]</t>
+  </si>
+  <si>
+    <t>Puppet Master</t>
   </si>
   <si>
     <t>傀儡之王</t>
@@ -1995,10 +1917,10 @@
     <t>【金蝉脱壳】你死亡时，你在当前拥有资源最多的士兵雕像身上重生，血量不变，眩晕一回合。【凶暴】你造成的伤害*2。</t>
   </si>
   <si>
-    <t>["CicadaShell", "Ferocity"]</t>
-  </si>
-  <si>
-    <t>SoldierStatue</t>
+    <t>["Cicada Shell", "Ferocity"]</t>
+  </si>
+  <si>
+    <t>Soldier Statue</t>
   </si>
   <si>
     <t>士兵雕像</t>
@@ -2010,7 +1932,7 @@
     <t>["Revival"]</t>
   </si>
   <si>
-    <t>SagePhantom</t>
+    <t>Sage Phantom</t>
   </si>
   <si>
     <t>圣人虚像</t>
@@ -2022,7 +1944,7 @@
     <t>["Redemption"]</t>
   </si>
   <si>
-    <t>DarkCrow</t>
+    <t>Dark Crow</t>
   </si>
   <si>
     <t>暗鸦</t>
@@ -2031,86 +1953,22 @@
     <t>【默杀】你第n次造成伤害时可以给目标叠加n个"凶"标记。拥有"凶"标记的角色每回合失去n点资源和一个"凶"标记。</t>
   </si>
   <si>
-    <t>["SilentKill"]</t>
-  </si>
-  <si>
-    <t>WhiteWolfKing</t>
+    <t>["Silent Kill"]</t>
+  </si>
+  <si>
+    <t>White Wolf King</t>
   </si>
   <si>
     <t>白狼王</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>【狼嚎】你在开局和生命值首次降低到5以下时会召唤幼狼</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11.25"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Segoe UI"/>
-        <charset val="134"/>
-      </rPr>
-      <t>1</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11.25"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>，狼母</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11.25"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Segoe UI"/>
-        <charset val="134"/>
-      </rPr>
-      <t>1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11.25"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>，狼</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11.25"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Segoe UI"/>
-        <charset val="134"/>
-      </rPr>
-      <t>*2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11.25"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>。【嗜血】你的攻击造成伤害时回复等量生命值。</t>
-    </r>
-  </si>
-  <si>
-    <t>["WolfHowl", "Bloodlust", "Leader Catch"]</t>
-  </si>
-  <si>
-    <t>SixEarMacaque</t>
+    <t>【狼嚎】你在开局和生命值首次降低到5以下时会召唤幼狼1，狼母1，狼*2。【嗜血】你的攻击造成伤害时回复等量生命值。</t>
+  </si>
+  <si>
+    <t>["Wolf Howl", "Bloodlust", "Leader Catch"]</t>
+  </si>
+  <si>
+    <t>Six Ear Macaque</t>
   </si>
   <si>
     <t>六耳猕猴</t>
@@ -2119,10 +1977,10 @@
     <t>【千钧棒】你造成的伤害*3。【毫毛术】第三回合起每隔6个回合，你分裂为3个分身，血量不变且每个单位分得1/3资源（向上取整），并失去【千钧棒】。该状态持续3回合，复原时六耳猕猴获得分身的所有资源与分身血量之和的1/3血量（向下取整）。</t>
   </si>
   <si>
-    <t>["MightyStrike", "CloneTechnique"]</t>
-  </si>
-  <si>
-    <t>TwoHeadedSnake</t>
+    <t>["Mountain Crusher", "Clone Technique"]</t>
+  </si>
+  <si>
+    <t>Two Headed Snake</t>
   </si>
   <si>
     <t>两头蛇</t>
@@ -2131,65 +1989,19 @@
     <t>【毒液】你的攻击造成伤害时，对目标施加一层"中毒"标记。中毒：每回合失去一点生命值，每回合-1层。【双头】你的每次攻击进行两次结算。</t>
   </si>
   <si>
-    <t>["Venom", "TwoHeads"]</t>
-  </si>
-  <si>
-    <t>BanditLeader</t>
+    <t>["Venom", "Two Heads"]</t>
+  </si>
+  <si>
+    <t>Bandit Leader</t>
   </si>
   <si>
     <t>强盗首领</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>【装备精良】你开局拥有子弹</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11.25"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Segoe UI"/>
-        <charset val="134"/>
-      </rPr>
-      <t>5</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11.25"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>，剑</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11.25"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Segoe UI"/>
-        <charset val="134"/>
-      </rPr>
-      <t>5</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11.25"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>。</t>
-    </r>
-  </si>
-  <si>
-    <t>["WellEquipped", "Leader Catch"]</t>
+    <t>【装备精良】你开局拥有子弹5，剑5。</t>
+  </si>
+  <si>
+    <t>["Well Equipped", "Leader Catch"]</t>
   </si>
   <si>
     <t>Troll</t>
@@ -2198,7 +2010,7 @@
     <t>巨魔</t>
   </si>
   <si>
-    <t>ClumsyGunner</t>
+    <t>Clumsy Gunner</t>
   </si>
   <si>
     <t>拙劣枪手</t>
@@ -2207,10 +2019,10 @@
     <t>【近战苦手】你不能拔剑。</t>
   </si>
   <si>
-    <t>["MeleeDisability"]</t>
-  </si>
-  <si>
-    <t>MountainBanditCluster</t>
+    <t>["Melee Disability"]</t>
+  </si>
+  <si>
+    <t>Mountain Bandit Cluster</t>
   </si>
   <si>
     <t>山匪</t>
@@ -2219,7 +2031,7 @@
     <t>【圣剑】你不能补子弹。</t>
   </si>
   <si>
-    <t>["Royal Knight"]</t>
+    <t>["Holy Sword"]</t>
   </si>
   <si>
     <t>Cultist</t>
@@ -2243,16 +2055,16 @@
     <t>【不吉之羽】你造成一次伤害时，对目标附加一个"凶"标记，拥有"凶"标记的角色每回合失去n点资源和一个"凶"标记，（n为该角色拥有的"凶"标记数）。</t>
   </si>
   <si>
-    <t>["OminousFeather"]</t>
-  </si>
-  <si>
-    <t>MercenarySoldier</t>
+    <t>["Ominous Feather"]</t>
+  </si>
+  <si>
+    <t>Mercenary Soldier</t>
   </si>
   <si>
     <t>佣兵士兵</t>
   </si>
   <si>
-    <t>MercenaryWarrior</t>
+    <t>Mercenary Warrior</t>
   </si>
   <si>
     <t>佣兵战士</t>
@@ -2264,7 +2076,7 @@
     <t>["Relentless"]</t>
   </si>
   <si>
-    <t>MercenaryShieldGuard</t>
+    <t>Mercenary Shield Guard</t>
   </si>
   <si>
     <t>佣兵盾卫</t>
@@ -2273,10 +2085,10 @@
     <t>【坚盾】低攻击欲望，你的防御行为生效于全体友方。</t>
   </si>
   <si>
-    <t>["SturdyShield"]</t>
-  </si>
-  <si>
-    <t>MercenaryEmployer</t>
+    <t>["Sturdy Shield"]</t>
+  </si>
+  <si>
+    <t>Mercenary Employer</t>
   </si>
   <si>
     <t>佣兵雇主</t>
@@ -2288,7 +2100,7 @@
     <t>["Overconfidence"]</t>
   </si>
   <si>
-    <t>LittleMonkey</t>
+    <t>Little Monkey</t>
   </si>
   <si>
     <t>小猴</t>
@@ -2297,10 +2109,10 @@
     <t>【灵猿】你造成的伤害*2。</t>
   </si>
   <si>
-    <t>["AgileApe"]</t>
-  </si>
-  <si>
-    <t>WolfCub</t>
+    <t>["Agile Ape"]</t>
+  </si>
+  <si>
+    <t>Wolf Cub</t>
   </si>
   <si>
     <t>幼狼</t>
@@ -2324,7 +2136,7 @@
     <t>["Bloodlust"]</t>
   </si>
   <si>
-    <t>WolfMother</t>
+    <t>Wolf Mother</t>
   </si>
   <si>
     <t>狼母</t>
@@ -2333,7 +2145,7 @@
     <t>【狼怨】受伤叠加一层复仇，造成伤害失去一点复仇，幼狼死亡获得三点复仇，其他狼死亡获得两点复仇。你每有一层复仇，伤害+1，有复仇时为高攻击欲望。</t>
   </si>
   <si>
-    <t>["WolfGrudge"]</t>
+    <t>["Wolf Grudge"]</t>
   </si>
   <si>
     <t>Blank</t>
@@ -3449,27 +3261,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <u/>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11.25"/>
-      <color rgb="FFF9FAFB"/>
-      <name val="Segoe UI"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11.25"/>
-      <color rgb="FFF9FAFB"/>
-      <name val="Segoe UI"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <i/>
       <sz val="11.25"/>
       <color rgb="FFFF0000"/>
@@ -3493,6 +3284,27 @@
       <sz val="11.25"/>
       <color rgb="FFFF0000"/>
       <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <u/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11.25"/>
+      <color rgb="FFF9FAFB"/>
+      <name val="Segoe UI"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11.25"/>
+      <color rgb="FFF9FAFB"/>
+      <name val="Segoe UI"/>
       <charset val="134"/>
     </font>
   </fonts>
@@ -3714,7 +3526,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="28">
+  <borders count="26">
     <border>
       <left/>
       <right/>
@@ -3756,30 +3568,6 @@
       </top>
       <bottom style="thin">
         <color theme="4" tint="0.399975585192419"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color rgb="FF9DC3E6"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF9DC3E6"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FF9DC3E6"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF9DC3E6"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF9DC3E6"/>
       </bottom>
       <diagonal/>
     </border>
@@ -4077,7 +3865,7 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="18" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -4089,34 +3877,34 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="21" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="19" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="21" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="19" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="22" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="20" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="7" borderId="23" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="24" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="8" borderId="22" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="8" borderId="23" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="8" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="9" borderId="25" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="9" borderId="23" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="26" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="24" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="27" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="25" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -4203,7 +3991,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="61">
+  <cellXfs count="58">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -4268,15 +4056,6 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="6" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="176" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -4301,65 +4080,74 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="6" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="4" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="7" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="5" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="8" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="6" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="9" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="7" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="8" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="6" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="9" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="7" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="50" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="8" xfId="50" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="9" xfId="50" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="2" borderId="10" xfId="50" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="11" xfId="50" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="10" xfId="50" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="11" xfId="50" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="12" xfId="50" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="12" xfId="50" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="12" xfId="50" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="5" borderId="13" xfId="50" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="14" xfId="50" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="13" xfId="50" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="50" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="15" xfId="50" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="50" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="15" xfId="50" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="50" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="50" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="14" xfId="50" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -4367,22 +4155,13 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="15" xfId="50" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="15" xfId="50" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="16" xfId="50" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="17" xfId="50" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="18" xfId="50" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="18" xfId="50" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="16" xfId="50" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="19" xfId="50" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="17" xfId="50" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -4752,733 +4531,733 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:H38"/>
-  <sheetFormatPr defaultColWidth="8.25" defaultRowHeight="14" outlineLevelCol="7"/>
+  <sheetFormatPr defaultColWidth="8.24778761061947" defaultRowHeight="13.85" outlineLevelCol="7"/>
   <cols>
-    <col min="1" max="1" width="22.8166666666667" style="10" customWidth="1"/>
-    <col min="2" max="2" width="21.4916666666667" style="10" customWidth="1"/>
-    <col min="3" max="3" width="8.25" style="10"/>
-    <col min="4" max="4" width="15.2083333333333" style="10" customWidth="1"/>
+    <col min="1" max="1" width="22.8141592920354" style="10" customWidth="1"/>
+    <col min="2" max="2" width="21.5044247787611" style="10" customWidth="1"/>
+    <col min="3" max="3" width="8.24778761061947" style="10"/>
+    <col min="4" max="4" width="15.212389380531" style="10" customWidth="1"/>
     <col min="5" max="5" width="14" style="10" customWidth="1"/>
-    <col min="6" max="6" width="23.675" style="10" customWidth="1"/>
-    <col min="7" max="7" width="8.70833333333333" style="10" customWidth="1"/>
-    <col min="8" max="16382" width="8.25" style="10"/>
+    <col min="6" max="6" width="23.6725663716814" style="10" customWidth="1"/>
+    <col min="7" max="7" width="8.70796460176991" style="10" customWidth="1"/>
+    <col min="8" max="16382" width="8.24778761061947" style="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="14.75" spans="1:8">
-      <c r="A1" s="33" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="33" t="s">
+    <row r="1" ht="14.6" spans="1:8">
+      <c r="A1" s="30" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="30" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="33" t="s">
+      <c r="C1" s="30" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="33" t="s">
+      <c r="D1" s="30" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="33" t="s">
+      <c r="E1" s="30" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="34" t="s">
+      <c r="F1" s="31" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="33" t="s">
+      <c r="G1" s="30" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="33" t="s">
+      <c r="H1" s="30" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" ht="26" spans="1:8">
-      <c r="A2" s="41" t="s">
+    <row r="2" ht="25.5" spans="1:8">
+      <c r="A2" s="38" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="41" t="s">
+      <c r="B2" s="38" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="41" t="s">
+      <c r="C2" s="38" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="41" t="b">
-        <v>0</v>
-      </c>
-      <c r="E2" s="41">
-        <v>0</v>
-      </c>
-      <c r="F2" s="42" t="s">
+      <c r="D2" s="38" t="b">
+        <v>0</v>
+      </c>
+      <c r="E2" s="38">
+        <v>0</v>
+      </c>
+      <c r="F2" s="39" t="s">
         <v>10</v>
       </c>
-      <c r="G2" s="41" t="s">
+      <c r="G2" s="38" t="s">
         <v>11</v>
       </c>
-      <c r="H2" s="41">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8">
-      <c r="A3" s="39" t="s">
+      <c r="H2" s="38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" ht="25.5" spans="1:8">
+      <c r="A3" s="36" t="s">
         <v>12</v>
       </c>
-      <c r="B3" s="39" t="s">
+      <c r="B3" s="36" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="39" t="s">
+      <c r="C3" s="36" t="s">
         <v>13</v>
       </c>
-      <c r="D3" s="39" t="b">
-        <v>0</v>
-      </c>
-      <c r="E3" s="39">
-        <v>0</v>
-      </c>
-      <c r="F3" s="40" t="s">
+      <c r="D3" s="36" t="b">
+        <v>0</v>
+      </c>
+      <c r="E3" s="36">
+        <v>0</v>
+      </c>
+      <c r="F3" s="37" t="s">
         <v>14</v>
       </c>
-      <c r="G3" s="39" t="s">
+      <c r="G3" s="36" t="s">
         <v>11</v>
       </c>
-      <c r="H3" s="39">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" ht="26" spans="1:8">
-      <c r="A4" s="41" t="s">
+      <c r="H3" s="36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" ht="25.5" spans="1:8">
+      <c r="A4" s="38" t="s">
         <v>15</v>
       </c>
-      <c r="B4" s="41" t="s">
+      <c r="B4" s="38" t="s">
         <v>15</v>
       </c>
-      <c r="C4" s="41" t="s">
+      <c r="C4" s="38" t="s">
         <v>16</v>
       </c>
-      <c r="D4" s="41" t="b">
-        <v>0</v>
-      </c>
-      <c r="E4" s="41">
-        <v>0</v>
-      </c>
-      <c r="F4" s="42" t="s">
+      <c r="D4" s="38" t="b">
+        <v>0</v>
+      </c>
+      <c r="E4" s="38">
+        <v>0</v>
+      </c>
+      <c r="F4" s="39" t="s">
         <v>17</v>
       </c>
-      <c r="G4" s="41" t="s">
+      <c r="G4" s="38" t="s">
         <v>11</v>
       </c>
-      <c r="H4" s="41">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" ht="26" spans="1:8">
-      <c r="A5" s="39" t="s">
+      <c r="H4" s="38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" ht="25.5" spans="1:8">
+      <c r="A5" s="36" t="s">
         <v>18</v>
       </c>
-      <c r="B5" s="39" t="s">
+      <c r="B5" s="36" t="s">
         <v>18</v>
       </c>
-      <c r="C5" s="39" t="s">
+      <c r="C5" s="36" t="s">
         <v>19</v>
       </c>
-      <c r="D5" s="39" t="b">
-        <v>0</v>
-      </c>
-      <c r="E5" s="39">
-        <v>0</v>
-      </c>
-      <c r="F5" s="40" t="s">
+      <c r="D5" s="36" t="b">
+        <v>0</v>
+      </c>
+      <c r="E5" s="36">
+        <v>0</v>
+      </c>
+      <c r="F5" s="37" t="s">
         <v>20</v>
       </c>
-      <c r="G5" s="39" t="s">
+      <c r="G5" s="36" t="s">
         <v>11</v>
       </c>
-      <c r="H5" s="39">
+      <c r="H5" s="36">
         <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:8">
-      <c r="A6" s="41" t="s">
+      <c r="A6" s="38" t="s">
         <v>21</v>
       </c>
-      <c r="B6" s="41" t="s">
+      <c r="B6" s="38" t="s">
         <v>21</v>
       </c>
-      <c r="C6" s="41" t="s">
+      <c r="C6" s="38" t="s">
         <v>22</v>
       </c>
-      <c r="D6" s="41" t="b">
-        <v>0</v>
-      </c>
-      <c r="E6" s="41">
-        <v>0</v>
-      </c>
-      <c r="F6" s="42" t="s">
+      <c r="D6" s="38" t="b">
+        <v>0</v>
+      </c>
+      <c r="E6" s="38">
+        <v>0</v>
+      </c>
+      <c r="F6" s="39" t="s">
         <v>23</v>
       </c>
-      <c r="G6" s="41" t="s">
+      <c r="G6" s="38" t="s">
         <v>11</v>
       </c>
-      <c r="H6" s="41">
+      <c r="H6" s="38">
         <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:8">
-      <c r="A7" s="39" t="s">
+      <c r="A7" s="36" t="s">
         <v>24</v>
       </c>
-      <c r="B7" s="39" t="s">
+      <c r="B7" s="36" t="s">
         <v>24</v>
       </c>
-      <c r="C7" s="39" t="s">
+      <c r="C7" s="36" t="s">
         <v>25</v>
       </c>
-      <c r="D7" s="39" t="b">
-        <v>0</v>
-      </c>
-      <c r="E7" s="39">
-        <v>0</v>
-      </c>
-      <c r="F7" s="40" t="s">
+      <c r="D7" s="36" t="b">
+        <v>0</v>
+      </c>
+      <c r="E7" s="36">
+        <v>0</v>
+      </c>
+      <c r="F7" s="37" t="s">
         <v>26</v>
       </c>
-      <c r="G7" s="39" t="s">
+      <c r="G7" s="36" t="s">
         <v>11</v>
       </c>
-      <c r="H7" s="39">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" ht="39" spans="1:8">
-      <c r="A8" s="41" t="s">
+      <c r="H7" s="36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" ht="38.25" spans="1:8">
+      <c r="A8" s="38" t="s">
         <v>27</v>
       </c>
-      <c r="B8" s="41" t="s">
+      <c r="B8" s="38" t="s">
         <v>27</v>
       </c>
-      <c r="C8" s="41" t="s">
+      <c r="C8" s="38" t="s">
         <v>28</v>
       </c>
-      <c r="D8" s="41" t="b">
-        <v>0</v>
-      </c>
-      <c r="E8" s="41">
-        <v>0</v>
-      </c>
-      <c r="F8" s="42" t="s">
+      <c r="D8" s="38" t="b">
+        <v>0</v>
+      </c>
+      <c r="E8" s="38">
+        <v>0</v>
+      </c>
+      <c r="F8" s="39" t="s">
         <v>29</v>
       </c>
-      <c r="G8" s="41" t="s">
+      <c r="G8" s="38" t="s">
         <v>30</v>
       </c>
-      <c r="H8" s="41">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" ht="26" spans="1:8">
-      <c r="A9" s="39" t="s">
+      <c r="H8" s="38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" ht="25.5" spans="1:8">
+      <c r="A9" s="36" t="s">
         <v>31</v>
       </c>
-      <c r="B9" s="39" t="s">
+      <c r="B9" s="36" t="s">
         <v>31</v>
       </c>
-      <c r="C9" s="39" t="s">
+      <c r="C9" s="36" t="s">
         <v>32</v>
       </c>
-      <c r="D9" s="39" t="b">
-        <v>0</v>
-      </c>
-      <c r="E9" s="39">
-        <v>0</v>
-      </c>
-      <c r="F9" s="40" t="s">
+      <c r="D9" s="36" t="b">
+        <v>0</v>
+      </c>
+      <c r="E9" s="36">
+        <v>0</v>
+      </c>
+      <c r="F9" s="37" t="s">
         <v>33</v>
       </c>
-      <c r="G9" s="39" t="s">
+      <c r="G9" s="36" t="s">
         <v>11</v>
       </c>
-      <c r="H9" s="39">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" ht="78" spans="1:8">
-      <c r="A10" s="41" t="s">
+      <c r="H9" s="36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" ht="89.25" spans="1:8">
+      <c r="A10" s="38" t="s">
         <v>34</v>
       </c>
-      <c r="B10" s="41" t="s">
+      <c r="B10" s="38" t="s">
         <v>34</v>
       </c>
-      <c r="C10" s="41" t="s">
+      <c r="C10" s="38" t="s">
         <v>35</v>
       </c>
-      <c r="D10" s="41" t="b">
-        <v>0</v>
-      </c>
-      <c r="E10" s="41">
-        <v>0</v>
-      </c>
-      <c r="F10" s="42" t="s">
+      <c r="D10" s="38" t="b">
+        <v>0</v>
+      </c>
+      <c r="E10" s="38">
+        <v>0</v>
+      </c>
+      <c r="F10" s="39" t="s">
         <v>36</v>
       </c>
-      <c r="G10" s="41" t="s">
+      <c r="G10" s="38" t="s">
         <v>37</v>
       </c>
-      <c r="H10" s="41">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" ht="91" spans="1:8">
-      <c r="A11" s="39" t="s">
+      <c r="H10" s="38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" ht="89.25" spans="1:8">
+      <c r="A11" s="36" t="s">
         <v>38</v>
       </c>
-      <c r="B11" s="39" t="s">
+      <c r="B11" s="36" t="s">
         <v>38</v>
       </c>
-      <c r="C11" s="39" t="s">
+      <c r="C11" s="36" t="s">
         <v>39</v>
       </c>
-      <c r="D11" s="39" t="b">
-        <v>0</v>
-      </c>
-      <c r="E11" s="39">
-        <v>0</v>
-      </c>
-      <c r="F11" s="40" t="s">
+      <c r="D11" s="36" t="b">
+        <v>0</v>
+      </c>
+      <c r="E11" s="36">
+        <v>0</v>
+      </c>
+      <c r="F11" s="37" t="s">
         <v>40</v>
       </c>
-      <c r="G11" s="39" t="s">
+      <c r="G11" s="36" t="s">
         <v>11</v>
       </c>
-      <c r="H11" s="39">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" ht="117" spans="1:8">
-      <c r="A12" s="41" t="s">
+      <c r="H11" s="36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" ht="127.5" spans="1:8">
+      <c r="A12" s="38" t="s">
         <v>41</v>
       </c>
-      <c r="B12" s="41" t="s">
+      <c r="B12" s="38" t="s">
         <v>41</v>
       </c>
-      <c r="C12" s="41" t="s">
+      <c r="C12" s="38" t="s">
         <v>42</v>
       </c>
-      <c r="D12" s="41" t="b">
-        <v>0</v>
-      </c>
-      <c r="E12" s="41">
-        <v>0</v>
-      </c>
-      <c r="F12" s="42" t="s">
+      <c r="D12" s="38" t="b">
+        <v>0</v>
+      </c>
+      <c r="E12" s="38">
+        <v>0</v>
+      </c>
+      <c r="F12" s="39" t="s">
         <v>43</v>
       </c>
-      <c r="G12" s="41" t="s">
+      <c r="G12" s="38" t="s">
         <v>11</v>
       </c>
-      <c r="H12" s="41">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" ht="52" spans="1:8">
-      <c r="A13" s="39" t="s">
+      <c r="H12" s="38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" ht="51" spans="1:8">
+      <c r="A13" s="36" t="s">
         <v>44</v>
       </c>
-      <c r="B13" s="39" t="s">
+      <c r="B13" s="36" t="s">
         <v>44</v>
       </c>
-      <c r="C13" s="39" t="s">
+      <c r="C13" s="36" t="s">
         <v>45</v>
       </c>
-      <c r="D13" s="39" t="b">
-        <v>0</v>
-      </c>
-      <c r="E13" s="39">
-        <v>0</v>
-      </c>
-      <c r="F13" s="40" t="s">
+      <c r="D13" s="36" t="b">
+        <v>0</v>
+      </c>
+      <c r="E13" s="36">
+        <v>0</v>
+      </c>
+      <c r="F13" s="37" t="s">
         <v>46</v>
       </c>
-      <c r="G13" s="39" t="s">
+      <c r="G13" s="36" t="s">
         <v>11</v>
       </c>
-      <c r="H13" s="39">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" ht="39" spans="1:8">
-      <c r="A14" s="41" t="s">
+      <c r="H13" s="36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" ht="38.25" spans="1:8">
+      <c r="A14" s="38" t="s">
         <v>47</v>
       </c>
-      <c r="B14" s="41" t="s">
+      <c r="B14" s="38" t="s">
         <v>47</v>
       </c>
-      <c r="C14" s="41" t="s">
+      <c r="C14" s="38" t="s">
         <v>48</v>
       </c>
-      <c r="D14" s="41" t="b">
+      <c r="D14" s="38" t="b">
         <v>1</v>
       </c>
-      <c r="E14" s="41">
+      <c r="E14" s="38">
         <v>1</v>
       </c>
-      <c r="F14" s="42" t="s">
+      <c r="F14" s="39" t="s">
         <v>49</v>
       </c>
-      <c r="G14" s="41" t="s">
+      <c r="G14" s="38" t="s">
         <v>50</v>
       </c>
-      <c r="H14" s="41">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" ht="39" spans="1:8">
-      <c r="A15" s="39" t="s">
+      <c r="H14" s="38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" ht="38.25" spans="1:8">
+      <c r="A15" s="36" t="s">
         <v>51</v>
       </c>
-      <c r="B15" s="39" t="s">
+      <c r="B15" s="36" t="s">
         <v>51</v>
       </c>
-      <c r="C15" s="39" t="s">
+      <c r="C15" s="36" t="s">
         <v>52</v>
       </c>
-      <c r="D15" s="39" t="b">
-        <v>0</v>
-      </c>
-      <c r="E15" s="39">
-        <v>0</v>
-      </c>
-      <c r="F15" s="40" t="s">
+      <c r="D15" s="36" t="b">
+        <v>0</v>
+      </c>
+      <c r="E15" s="36">
+        <v>0</v>
+      </c>
+      <c r="F15" s="37" t="s">
         <v>53</v>
       </c>
-      <c r="G15" s="39" t="s">
+      <c r="G15" s="36" t="s">
         <v>11</v>
       </c>
-      <c r="H15" s="39">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" ht="26" spans="1:8">
-      <c r="A16" s="41" t="s">
+      <c r="H15" s="36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" ht="25.5" spans="1:8">
+      <c r="A16" s="38" t="s">
         <v>54</v>
       </c>
-      <c r="B16" s="41" t="s">
+      <c r="B16" s="38" t="s">
         <v>54</v>
       </c>
-      <c r="C16" s="41" t="s">
+      <c r="C16" s="38" t="s">
         <v>55</v>
       </c>
-      <c r="D16" s="41" t="b">
-        <v>0</v>
-      </c>
-      <c r="E16" s="41">
-        <v>0</v>
-      </c>
-      <c r="F16" s="42" t="s">
+      <c r="D16" s="38" t="b">
+        <v>0</v>
+      </c>
+      <c r="E16" s="38">
+        <v>0</v>
+      </c>
+      <c r="F16" s="39" t="s">
         <v>56</v>
       </c>
-      <c r="G16" s="41" t="s">
+      <c r="G16" s="38" t="s">
         <v>11</v>
       </c>
-      <c r="H16" s="41">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" ht="52" spans="1:8">
-      <c r="A17" s="39" t="s">
+      <c r="H16" s="38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" ht="63.75" spans="1:8">
+      <c r="A17" s="36" t="s">
         <v>57</v>
       </c>
-      <c r="B17" s="39" t="s">
+      <c r="B17" s="36" t="s">
         <v>57</v>
       </c>
-      <c r="C17" s="39" t="s">
+      <c r="C17" s="36" t="s">
         <v>58</v>
       </c>
-      <c r="D17" s="39" t="b">
-        <v>0</v>
-      </c>
-      <c r="E17" s="39">
-        <v>0</v>
-      </c>
-      <c r="F17" s="40" t="s">
+      <c r="D17" s="36" t="b">
+        <v>0</v>
+      </c>
+      <c r="E17" s="36">
+        <v>0</v>
+      </c>
+      <c r="F17" s="37" t="s">
         <v>59</v>
       </c>
-      <c r="G17" s="39" t="s">
+      <c r="G17" s="36" t="s">
         <v>11</v>
       </c>
-      <c r="H17" s="39">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" ht="52" spans="1:8">
-      <c r="A18" s="41" t="s">
+      <c r="H17" s="36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" ht="51" spans="1:8">
+      <c r="A18" s="38" t="s">
         <v>60</v>
       </c>
-      <c r="B18" s="41" t="s">
+      <c r="B18" s="38" t="s">
         <v>60</v>
       </c>
-      <c r="C18" s="41" t="s">
+      <c r="C18" s="38" t="s">
         <v>61</v>
       </c>
-      <c r="D18" s="41" t="b">
-        <v>0</v>
-      </c>
-      <c r="E18" s="41">
-        <v>0</v>
-      </c>
-      <c r="F18" s="42" t="s">
+      <c r="D18" s="38" t="b">
+        <v>0</v>
+      </c>
+      <c r="E18" s="38">
+        <v>0</v>
+      </c>
+      <c r="F18" s="39" t="s">
         <v>62</v>
       </c>
-      <c r="G18" s="41" t="s">
+      <c r="G18" s="38" t="s">
         <v>63</v>
       </c>
-      <c r="H18" s="41">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" ht="26" spans="1:8">
-      <c r="A19" s="39" t="s">
+      <c r="H18" s="38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" ht="25.5" spans="1:8">
+      <c r="A19" s="36" t="s">
         <v>64</v>
       </c>
-      <c r="B19" s="39" t="s">
+      <c r="B19" s="36" t="s">
         <v>64</v>
       </c>
-      <c r="C19" s="39" t="s">
+      <c r="C19" s="36" t="s">
         <v>65</v>
       </c>
-      <c r="D19" s="39" t="b">
-        <v>0</v>
-      </c>
-      <c r="E19" s="39">
-        <v>0</v>
-      </c>
-      <c r="F19" s="40" t="s">
+      <c r="D19" s="36" t="b">
+        <v>0</v>
+      </c>
+      <c r="E19" s="36">
+        <v>0</v>
+      </c>
+      <c r="F19" s="37" t="s">
         <v>66</v>
       </c>
-      <c r="G19" s="39" t="s">
+      <c r="G19" s="36" t="s">
         <v>11</v>
       </c>
-      <c r="H19" s="39">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" ht="26" spans="1:8">
-      <c r="A20" s="41" t="s">
+      <c r="H19" s="36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" ht="25.5" spans="1:8">
+      <c r="A20" s="38" t="s">
         <v>67</v>
       </c>
-      <c r="B20" s="41" t="s">
+      <c r="B20" s="38" t="s">
         <v>67</v>
       </c>
-      <c r="C20" s="41" t="s">
+      <c r="C20" s="38" t="s">
         <v>68</v>
       </c>
-      <c r="D20" s="41" t="b">
-        <v>0</v>
-      </c>
-      <c r="E20" s="41">
-        <v>0</v>
-      </c>
-      <c r="F20" s="42" t="s">
+      <c r="D20" s="38" t="b">
+        <v>0</v>
+      </c>
+      <c r="E20" s="38">
+        <v>0</v>
+      </c>
+      <c r="F20" s="39" t="s">
         <v>69</v>
       </c>
-      <c r="G20" s="41" t="s">
+      <c r="G20" s="38" t="s">
         <v>11</v>
       </c>
-      <c r="H20" s="41">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" ht="182" spans="1:8">
-      <c r="A21" s="39" t="s">
+      <c r="H20" s="38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" ht="191.25" spans="1:8">
+      <c r="A21" s="36" t="s">
         <v>70</v>
       </c>
-      <c r="B21" s="39" t="s">
+      <c r="B21" s="36" t="s">
         <v>70</v>
       </c>
-      <c r="C21" s="39" t="s">
+      <c r="C21" s="36" t="s">
         <v>71</v>
       </c>
-      <c r="D21" s="39" t="b">
-        <v>0</v>
-      </c>
-      <c r="E21" s="39">
-        <v>0</v>
-      </c>
-      <c r="F21" s="40" t="s">
+      <c r="D21" s="36" t="b">
+        <v>0</v>
+      </c>
+      <c r="E21" s="36">
+        <v>0</v>
+      </c>
+      <c r="F21" s="37" t="s">
         <v>72</v>
       </c>
-      <c r="G21" s="39" t="s">
+      <c r="G21" s="36" t="s">
         <v>11</v>
       </c>
-      <c r="H21" s="39">
+      <c r="H21" s="36">
         <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:8">
-      <c r="A22" s="41"/>
-      <c r="B22" s="41"/>
-      <c r="C22" s="41"/>
-      <c r="D22" s="41"/>
-      <c r="E22" s="41"/>
-      <c r="F22" s="42"/>
-      <c r="G22" s="41"/>
-      <c r="H22" s="41"/>
+      <c r="A22" s="38"/>
+      <c r="B22" s="38"/>
+      <c r="C22" s="38"/>
+      <c r="D22" s="38"/>
+      <c r="E22" s="38"/>
+      <c r="F22" s="39"/>
+      <c r="G22" s="38"/>
+      <c r="H22" s="38"/>
     </row>
     <row r="23" spans="1:8">
-      <c r="A23" s="39"/>
-      <c r="B23" s="39"/>
-      <c r="C23" s="39"/>
-      <c r="D23" s="39"/>
-      <c r="E23" s="39"/>
-      <c r="F23" s="40"/>
-      <c r="G23" s="39"/>
-      <c r="H23" s="39"/>
+      <c r="A23" s="36"/>
+      <c r="B23" s="36"/>
+      <c r="C23" s="36"/>
+      <c r="D23" s="36"/>
+      <c r="E23" s="36"/>
+      <c r="F23" s="37"/>
+      <c r="G23" s="36"/>
+      <c r="H23" s="36"/>
     </row>
     <row r="24" spans="1:8">
-      <c r="A24" s="41"/>
-      <c r="B24" s="41"/>
-      <c r="C24" s="41"/>
-      <c r="D24" s="41"/>
-      <c r="E24" s="41"/>
-      <c r="F24" s="42"/>
-      <c r="G24" s="41"/>
-      <c r="H24" s="41"/>
+      <c r="A24" s="38"/>
+      <c r="B24" s="38"/>
+      <c r="C24" s="38"/>
+      <c r="D24" s="38"/>
+      <c r="E24" s="38"/>
+      <c r="F24" s="39"/>
+      <c r="G24" s="38"/>
+      <c r="H24" s="38"/>
     </row>
     <row r="25" spans="1:8">
-      <c r="A25" s="39"/>
-      <c r="B25" s="39"/>
-      <c r="C25" s="39"/>
-      <c r="D25" s="39"/>
-      <c r="E25" s="39"/>
-      <c r="F25" s="40"/>
-      <c r="G25" s="39"/>
-      <c r="H25" s="39"/>
+      <c r="A25" s="36"/>
+      <c r="B25" s="36"/>
+      <c r="C25" s="36"/>
+      <c r="D25" s="36"/>
+      <c r="E25" s="36"/>
+      <c r="F25" s="37"/>
+      <c r="G25" s="36"/>
+      <c r="H25" s="36"/>
     </row>
     <row r="26" spans="1:8">
-      <c r="A26" s="41"/>
-      <c r="B26" s="41"/>
-      <c r="C26" s="41"/>
-      <c r="D26" s="41"/>
-      <c r="E26" s="41"/>
-      <c r="F26" s="42"/>
-      <c r="G26" s="41"/>
-      <c r="H26" s="41"/>
+      <c r="A26" s="38"/>
+      <c r="B26" s="38"/>
+      <c r="C26" s="38"/>
+      <c r="D26" s="38"/>
+      <c r="E26" s="38"/>
+      <c r="F26" s="39"/>
+      <c r="G26" s="38"/>
+      <c r="H26" s="38"/>
     </row>
     <row r="27" spans="1:8">
-      <c r="A27" s="39"/>
-      <c r="B27" s="39"/>
-      <c r="C27" s="39"/>
-      <c r="D27" s="39"/>
-      <c r="E27" s="39"/>
-      <c r="F27" s="40"/>
-      <c r="G27" s="39"/>
-      <c r="H27" s="39"/>
+      <c r="A27" s="36"/>
+      <c r="B27" s="36"/>
+      <c r="C27" s="36"/>
+      <c r="D27" s="36"/>
+      <c r="E27" s="36"/>
+      <c r="F27" s="37"/>
+      <c r="G27" s="36"/>
+      <c r="H27" s="36"/>
     </row>
     <row r="28" spans="1:8">
-      <c r="A28" s="41"/>
-      <c r="B28" s="41"/>
-      <c r="C28" s="41"/>
-      <c r="D28" s="41"/>
-      <c r="E28" s="41"/>
-      <c r="F28" s="42"/>
-      <c r="G28" s="41"/>
-      <c r="H28" s="41"/>
+      <c r="A28" s="38"/>
+      <c r="B28" s="38"/>
+      <c r="C28" s="38"/>
+      <c r="D28" s="38"/>
+      <c r="E28" s="38"/>
+      <c r="F28" s="39"/>
+      <c r="G28" s="38"/>
+      <c r="H28" s="38"/>
     </row>
     <row r="29" spans="1:8">
-      <c r="A29" s="39"/>
-      <c r="B29" s="39"/>
-      <c r="C29" s="39"/>
-      <c r="D29" s="39"/>
-      <c r="E29" s="39"/>
-      <c r="F29" s="40"/>
-      <c r="G29" s="39"/>
-      <c r="H29" s="39"/>
+      <c r="A29" s="36"/>
+      <c r="B29" s="36"/>
+      <c r="C29" s="36"/>
+      <c r="D29" s="36"/>
+      <c r="E29" s="36"/>
+      <c r="F29" s="37"/>
+      <c r="G29" s="36"/>
+      <c r="H29" s="36"/>
     </row>
     <row r="30" spans="1:8">
-      <c r="A30" s="41"/>
-      <c r="B30" s="41"/>
-      <c r="C30" s="41"/>
-      <c r="D30" s="41"/>
-      <c r="E30" s="41"/>
-      <c r="F30" s="42"/>
-      <c r="G30" s="41"/>
-      <c r="H30" s="41"/>
+      <c r="A30" s="38"/>
+      <c r="B30" s="38"/>
+      <c r="C30" s="38"/>
+      <c r="D30" s="38"/>
+      <c r="E30" s="38"/>
+      <c r="F30" s="39"/>
+      <c r="G30" s="38"/>
+      <c r="H30" s="38"/>
     </row>
     <row r="31" spans="1:8">
-      <c r="A31" s="39"/>
-      <c r="B31" s="39"/>
-      <c r="C31" s="39"/>
-      <c r="D31" s="39"/>
-      <c r="E31" s="39"/>
-      <c r="F31" s="40"/>
-      <c r="G31" s="39"/>
-      <c r="H31" s="39"/>
+      <c r="A31" s="36"/>
+      <c r="B31" s="36"/>
+      <c r="C31" s="36"/>
+      <c r="D31" s="36"/>
+      <c r="E31" s="36"/>
+      <c r="F31" s="37"/>
+      <c r="G31" s="36"/>
+      <c r="H31" s="36"/>
     </row>
     <row r="32" spans="1:8">
-      <c r="A32" s="41"/>
-      <c r="B32" s="41"/>
-      <c r="C32" s="41"/>
-      <c r="D32" s="41"/>
-      <c r="E32" s="41"/>
-      <c r="F32" s="42"/>
-      <c r="G32" s="41"/>
-      <c r="H32" s="41"/>
+      <c r="A32" s="38"/>
+      <c r="B32" s="38"/>
+      <c r="C32" s="38"/>
+      <c r="D32" s="38"/>
+      <c r="E32" s="38"/>
+      <c r="F32" s="39"/>
+      <c r="G32" s="38"/>
+      <c r="H32" s="38"/>
     </row>
     <row r="33" spans="1:8">
-      <c r="A33" s="39"/>
-      <c r="B33" s="39"/>
-      <c r="C33" s="39"/>
-      <c r="D33" s="39"/>
-      <c r="E33" s="39"/>
-      <c r="F33" s="40"/>
-      <c r="G33" s="39"/>
-      <c r="H33" s="39"/>
+      <c r="A33" s="36"/>
+      <c r="B33" s="36"/>
+      <c r="C33" s="36"/>
+      <c r="D33" s="36"/>
+      <c r="E33" s="36"/>
+      <c r="F33" s="37"/>
+      <c r="G33" s="36"/>
+      <c r="H33" s="36"/>
     </row>
     <row r="34" spans="1:8">
-      <c r="A34" s="41"/>
-      <c r="B34" s="41"/>
-      <c r="C34" s="41"/>
-      <c r="D34" s="41"/>
-      <c r="E34" s="41"/>
-      <c r="F34" s="42"/>
-      <c r="G34" s="41"/>
-      <c r="H34" s="41"/>
+      <c r="A34" s="38"/>
+      <c r="B34" s="38"/>
+      <c r="C34" s="38"/>
+      <c r="D34" s="38"/>
+      <c r="E34" s="38"/>
+      <c r="F34" s="39"/>
+      <c r="G34" s="38"/>
+      <c r="H34" s="38"/>
     </row>
     <row r="35" spans="1:8">
-      <c r="A35" s="39"/>
-      <c r="B35" s="39"/>
-      <c r="C35" s="39"/>
-      <c r="D35" s="39"/>
-      <c r="E35" s="39"/>
-      <c r="F35" s="40"/>
-      <c r="G35" s="39"/>
-      <c r="H35" s="39"/>
+      <c r="A35" s="36"/>
+      <c r="B35" s="36"/>
+      <c r="C35" s="36"/>
+      <c r="D35" s="36"/>
+      <c r="E35" s="36"/>
+      <c r="F35" s="37"/>
+      <c r="G35" s="36"/>
+      <c r="H35" s="36"/>
     </row>
     <row r="36" spans="1:8">
-      <c r="A36" s="41"/>
-      <c r="B36" s="41"/>
-      <c r="C36" s="41"/>
-      <c r="D36" s="41"/>
-      <c r="E36" s="41"/>
-      <c r="F36" s="42"/>
-      <c r="G36" s="41"/>
-      <c r="H36" s="41"/>
+      <c r="A36" s="38"/>
+      <c r="B36" s="38"/>
+      <c r="C36" s="38"/>
+      <c r="D36" s="38"/>
+      <c r="E36" s="38"/>
+      <c r="F36" s="39"/>
+      <c r="G36" s="38"/>
+      <c r="H36" s="38"/>
     </row>
     <row r="37" spans="1:8">
-      <c r="A37" s="39"/>
-      <c r="B37" s="39"/>
-      <c r="C37" s="39"/>
-      <c r="D37" s="39"/>
-      <c r="E37" s="39"/>
-      <c r="F37" s="40"/>
-      <c r="G37" s="39"/>
-      <c r="H37" s="39"/>
+      <c r="A37" s="36"/>
+      <c r="B37" s="36"/>
+      <c r="C37" s="36"/>
+      <c r="D37" s="36"/>
+      <c r="E37" s="36"/>
+      <c r="F37" s="37"/>
+      <c r="G37" s="36"/>
+      <c r="H37" s="36"/>
     </row>
     <row r="38" spans="1:8">
-      <c r="A38" s="41"/>
-      <c r="B38" s="41"/>
-      <c r="C38" s="41"/>
-      <c r="D38" s="41"/>
-      <c r="E38" s="41"/>
-      <c r="F38" s="42"/>
-      <c r="G38" s="41"/>
-      <c r="H38" s="41"/>
+      <c r="A38" s="38"/>
+      <c r="B38" s="38"/>
+      <c r="C38" s="38"/>
+      <c r="D38" s="38"/>
+      <c r="E38" s="38"/>
+      <c r="F38" s="39"/>
+      <c r="G38" s="38"/>
+      <c r="H38" s="38"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5491,156 +5270,156 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F8"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="7" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.85" outlineLevelRow="7" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="17.2666666666667" customWidth="1"/>
-    <col min="2" max="2" width="16.1833333333333" customWidth="1"/>
-    <col min="5" max="5" width="12.45" customWidth="1"/>
-    <col min="6" max="6" width="39.1833333333333" customWidth="1"/>
+    <col min="1" max="1" width="17.2654867256637" customWidth="1"/>
+    <col min="2" max="2" width="16.1858407079646" customWidth="1"/>
+    <col min="5" max="5" width="12.4513274336283" customWidth="1"/>
+    <col min="6" max="6" width="39.1858407079646" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="22.5" customHeight="1" spans="1:6">
-      <c r="A1" s="44" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="45" t="s">
+      <c r="A1" s="41" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="42" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="45" t="s">
+      <c r="C1" s="42" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="44" t="s">
+      <c r="D1" s="41" t="s">
         <v>73</v>
       </c>
-      <c r="E1" s="46" t="s">
+      <c r="E1" s="43" t="s">
         <v>74</v>
       </c>
-      <c r="F1" s="47" t="s">
+      <c r="F1" s="44" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="2" ht="25.5" customHeight="1" spans="1:6">
-      <c r="A2" s="48" t="s">
+      <c r="A2" s="45" t="s">
         <v>75</v>
       </c>
-      <c r="B2" s="49" t="s">
+      <c r="B2" s="46" t="s">
         <v>75</v>
       </c>
-      <c r="C2" s="49" t="s">
+      <c r="C2" s="46" t="s">
         <v>76</v>
       </c>
-      <c r="D2" s="48" t="s">
+      <c r="D2" s="45" t="s">
         <v>77</v>
       </c>
-      <c r="E2" s="50" t="s">
+      <c r="E2" s="47" t="s">
         <v>78</v>
       </c>
-      <c r="F2" s="51" t="s">
+      <c r="F2" s="48" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="3" ht="43" customHeight="1" spans="1:6">
-      <c r="A3" s="52" t="s">
+      <c r="A3" s="49" t="s">
         <v>80</v>
       </c>
-      <c r="B3" s="53" t="s">
+      <c r="B3" s="50" t="s">
         <v>80</v>
       </c>
-      <c r="C3" s="53" t="s">
+      <c r="C3" s="50" t="s">
         <v>81</v>
       </c>
-      <c r="D3" s="52" t="s">
+      <c r="D3" s="49" t="s">
         <v>77</v>
       </c>
-      <c r="E3" s="54" t="s">
+      <c r="E3" s="51" t="s">
         <v>78</v>
       </c>
-      <c r="F3" s="55" t="s">
+      <c r="F3" s="52" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="4" ht="23" customHeight="1" spans="1:6">
-      <c r="A4" s="56" t="s">
+      <c r="A4" s="53" t="s">
         <v>83</v>
       </c>
-      <c r="B4" s="57" t="s">
+      <c r="B4" s="54" t="s">
         <v>83</v>
       </c>
-      <c r="C4" s="57" t="s">
+      <c r="C4" s="54" t="s">
         <v>84</v>
       </c>
-      <c r="D4" s="56" t="s">
+      <c r="D4" s="53" t="s">
         <v>77</v>
       </c>
-      <c r="E4" s="58" t="s">
+      <c r="E4" s="55" t="s">
         <v>85</v>
       </c>
-      <c r="F4" s="59" t="s">
+      <c r="F4" s="56" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="5" s="43" customFormat="1" ht="52.75" spans="1:6">
-      <c r="A5" s="52" t="s">
+    <row r="5" s="40" customFormat="1" ht="51.75" spans="1:6">
+      <c r="A5" s="49" t="s">
         <v>87</v>
       </c>
-      <c r="B5" s="53" t="s">
+      <c r="B5" s="50" t="s">
         <v>87</v>
       </c>
-      <c r="C5" s="54" t="s">
+      <c r="C5" s="51" t="s">
         <v>88</v>
       </c>
-      <c r="D5" s="53" t="s">
+      <c r="D5" s="50" t="s">
         <v>89</v>
       </c>
-      <c r="E5" s="53" t="s">
+      <c r="E5" s="50" t="s">
         <v>90</v>
       </c>
-      <c r="F5" s="55" t="s">
+      <c r="F5" s="52" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="6" s="43" customFormat="1" ht="52" spans="1:6">
-      <c r="A6" s="52" t="s">
+    <row r="6" s="40" customFormat="1" ht="51" spans="1:6">
+      <c r="A6" s="49" t="s">
         <v>92</v>
       </c>
-      <c r="B6" s="53" t="s">
+      <c r="B6" s="50" t="s">
         <v>92</v>
       </c>
-      <c r="C6" s="54" t="s">
+      <c r="C6" s="51" t="s">
         <v>93</v>
       </c>
-      <c r="D6" s="53" t="s">
+      <c r="D6" s="50" t="s">
         <v>77</v>
       </c>
-      <c r="E6" s="53" t="s">
+      <c r="E6" s="50" t="s">
         <v>94</v>
       </c>
-      <c r="F6" s="55" t="s">
+      <c r="F6" s="52" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="48" t="s">
+      <c r="A7" s="45" t="s">
         <v>96</v>
       </c>
-      <c r="B7" s="49" t="s">
+      <c r="B7" s="46" t="s">
         <v>96</v>
       </c>
-      <c r="C7" s="50" t="s">
+      <c r="C7" s="47" t="s">
         <v>97</v>
       </c>
-      <c r="D7" s="49" t="s">
+      <c r="D7" s="46" t="s">
         <v>89</v>
       </c>
-      <c r="E7" s="49" t="s">
+      <c r="E7" s="46" t="s">
         <v>85</v>
       </c>
-      <c r="F7" s="51" t="s">
+      <c r="F7" s="48" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="60" t="s">
+      <c r="A8" s="57" t="s">
         <v>99</v>
       </c>
     </row>
@@ -5681,2251 +5460,2303 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H86"/>
-  <sheetFormatPr defaultColWidth="8.25" defaultRowHeight="14" outlineLevelCol="7"/>
+  <dimension ref="A1:H88"/>
+  <sheetFormatPr defaultColWidth="8.24778761061947" defaultRowHeight="13.85" outlineLevelCol="7"/>
   <cols>
-    <col min="1" max="1" width="28.3166666666667" style="10" customWidth="1"/>
-    <col min="2" max="2" width="23.9333333333333" style="10" customWidth="1"/>
-    <col min="3" max="3" width="16.9083333333333" style="10" customWidth="1"/>
-    <col min="4" max="4" width="15.7916666666667" style="10" customWidth="1"/>
-    <col min="5" max="5" width="13.2416666666667" style="10" customWidth="1"/>
-    <col min="6" max="6" width="25.975" style="10" customWidth="1"/>
-    <col min="7" max="16382" width="8.25" style="10"/>
+    <col min="1" max="1" width="28.3185840707965" style="10" customWidth="1"/>
+    <col min="2" max="2" width="23.929203539823" style="10" customWidth="1"/>
+    <col min="3" max="3" width="16.9115044247788" style="10" customWidth="1"/>
+    <col min="4" max="4" width="15.787610619469" style="10" customWidth="1"/>
+    <col min="5" max="5" width="13.2389380530973" style="10" customWidth="1"/>
+    <col min="6" max="6" width="25.9734513274336" style="10" customWidth="1"/>
+    <col min="7" max="16382" width="8.24778761061947" style="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="14.75" spans="1:8">
-      <c r="A1" s="33" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="33" t="s">
+    <row r="1" ht="14.6" spans="1:8">
+      <c r="A1" s="30" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="30" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="33" t="s">
+      <c r="C1" s="30" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="33" t="s">
+      <c r="D1" s="30" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="33" t="s">
+      <c r="E1" s="30" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="34" t="s">
+      <c r="F1" s="31" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="33" t="s">
+      <c r="G1" s="30" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="33" t="s">
+      <c r="H1" s="30" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" ht="52" spans="1:8">
-      <c r="A2" s="35" t="s">
+    <row r="2" ht="51" spans="1:8">
+      <c r="A2" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="B2" s="35" t="s">
+      <c r="B2" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="C2" s="35" t="s">
+      <c r="C2" s="32" t="s">
         <v>101</v>
       </c>
-      <c r="D2" s="35" t="b">
+      <c r="D2" s="32" t="b">
         <v>1</v>
       </c>
-      <c r="E2" s="35">
+      <c r="E2" s="32">
         <v>1</v>
       </c>
-      <c r="F2" s="36" t="s">
+      <c r="F2" s="33" t="s">
         <v>102</v>
       </c>
-      <c r="G2" s="35" t="s">
+      <c r="G2" s="32" t="s">
         <v>11</v>
       </c>
-      <c r="H2" s="35">
+      <c r="H2" s="32">
         <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:8">
-      <c r="A3" s="37" t="s">
+      <c r="A3" s="34" t="s">
         <v>103</v>
       </c>
-      <c r="B3" s="37" t="s">
+      <c r="B3" s="34" t="s">
         <v>103</v>
       </c>
-      <c r="C3" s="37" t="s">
+      <c r="C3" s="34" t="s">
         <v>104</v>
       </c>
-      <c r="D3" s="37" t="b">
+      <c r="D3" s="34" t="b">
         <v>1</v>
       </c>
-      <c r="E3" s="37">
+      <c r="E3" s="34">
         <v>1</v>
       </c>
-      <c r="F3" s="38" t="s">
+      <c r="F3" s="35" t="s">
         <v>105</v>
       </c>
-      <c r="G3" s="37" t="s">
+      <c r="G3" s="34" t="s">
         <v>11</v>
       </c>
-      <c r="H3" s="37">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" ht="26" spans="1:8">
-      <c r="A4" s="35" t="s">
+      <c r="H3" s="34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" ht="25.5" spans="1:8">
+      <c r="A4" s="32" t="s">
         <v>106</v>
       </c>
-      <c r="B4" s="35" t="s">
+      <c r="B4" s="32" t="s">
         <v>106</v>
       </c>
-      <c r="C4" s="35" t="s">
+      <c r="C4" s="32" t="s">
         <v>107</v>
       </c>
-      <c r="D4" s="35" t="b">
-        <v>0</v>
-      </c>
-      <c r="E4" s="35">
-        <v>0</v>
-      </c>
-      <c r="F4" s="36" t="s">
+      <c r="D4" s="32" t="b">
+        <v>0</v>
+      </c>
+      <c r="E4" s="32">
+        <v>0</v>
+      </c>
+      <c r="F4" s="33" t="s">
         <v>108</v>
       </c>
-      <c r="G4" s="35" t="s">
+      <c r="G4" s="32" t="s">
         <v>11</v>
       </c>
-      <c r="H4" s="35">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5" ht="39" spans="1:8">
-      <c r="A5" s="37" t="s">
+      <c r="H4" s="32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" ht="38.25" spans="1:8">
+      <c r="A5" s="34" t="s">
         <v>109</v>
       </c>
-      <c r="B5" s="37" t="s">
+      <c r="B5" s="34" t="s">
         <v>109</v>
       </c>
-      <c r="C5" s="37" t="s">
+      <c r="C5" s="34" t="s">
         <v>110</v>
       </c>
-      <c r="D5" s="37" t="b">
-        <v>0</v>
-      </c>
-      <c r="E5" s="37">
-        <v>0</v>
-      </c>
-      <c r="F5" s="38" t="s">
+      <c r="D5" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="E5" s="34">
+        <v>0</v>
+      </c>
+      <c r="F5" s="35" t="s">
         <v>111</v>
       </c>
-      <c r="G5" s="37" t="s">
+      <c r="G5" s="34" t="s">
         <v>11</v>
       </c>
-      <c r="H5" s="37">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="6" ht="26" spans="1:8">
-      <c r="A6" s="35" t="s">
+      <c r="H5" s="34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" ht="25.5" spans="1:8">
+      <c r="A6" s="32" t="s">
         <v>112</v>
       </c>
-      <c r="B6" s="35" t="s">
+      <c r="B6" s="32" t="s">
         <v>112</v>
       </c>
-      <c r="C6" s="35" t="s">
+      <c r="C6" s="32" t="s">
         <v>113</v>
       </c>
-      <c r="D6" s="35" t="b">
-        <v>0</v>
-      </c>
-      <c r="E6" s="35">
-        <v>0</v>
-      </c>
-      <c r="F6" s="36" t="s">
+      <c r="D6" s="32" t="b">
+        <v>0</v>
+      </c>
+      <c r="E6" s="32">
+        <v>0</v>
+      </c>
+      <c r="F6" s="33" t="s">
         <v>114</v>
       </c>
-      <c r="G6" s="35" t="s">
+      <c r="G6" s="32" t="s">
         <v>11</v>
       </c>
-      <c r="H6" s="35">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" ht="39" spans="1:8">
-      <c r="A7" s="37" t="s">
+      <c r="H6" s="32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" ht="38.25" spans="1:8">
+      <c r="A7" s="34" t="s">
         <v>115</v>
       </c>
-      <c r="B7" s="37" t="s">
+      <c r="B7" s="34" t="s">
         <v>115</v>
       </c>
-      <c r="C7" s="37" t="s">
+      <c r="C7" s="34" t="s">
         <v>116</v>
       </c>
-      <c r="D7" s="37" t="b">
-        <v>0</v>
-      </c>
-      <c r="E7" s="37">
-        <v>0</v>
-      </c>
-      <c r="F7" s="38" t="s">
+      <c r="D7" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="E7" s="34">
+        <v>0</v>
+      </c>
+      <c r="F7" s="35" t="s">
         <v>117</v>
       </c>
-      <c r="G7" s="37" t="s">
+      <c r="G7" s="34" t="s">
         <v>11</v>
       </c>
-      <c r="H7" s="37">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" ht="65" spans="1:8">
-      <c r="A8" s="35" t="s">
+      <c r="H7" s="34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" ht="63.75" spans="1:8">
+      <c r="A8" s="32" t="s">
         <v>118</v>
       </c>
-      <c r="B8" s="35" t="s">
+      <c r="B8" s="32" t="s">
         <v>118</v>
       </c>
-      <c r="C8" s="35" t="s">
+      <c r="C8" s="32" t="s">
         <v>119</v>
       </c>
-      <c r="D8" s="35" t="b">
-        <v>0</v>
-      </c>
-      <c r="E8" s="35">
-        <v>0</v>
-      </c>
-      <c r="F8" s="36" t="s">
+      <c r="D8" s="32" t="b">
+        <v>0</v>
+      </c>
+      <c r="E8" s="32">
+        <v>0</v>
+      </c>
+      <c r="F8" s="33" t="s">
         <v>120</v>
       </c>
-      <c r="G8" s="35" t="s">
+      <c r="G8" s="32" t="s">
         <v>11</v>
       </c>
-      <c r="H8" s="35">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" ht="39" spans="1:8">
-      <c r="A9" s="37" t="s">
+      <c r="H8" s="32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" ht="38.25" spans="1:8">
+      <c r="A9" s="34" t="s">
         <v>121</v>
       </c>
-      <c r="B9" s="37" t="s">
+      <c r="B9" s="34" t="s">
         <v>121</v>
       </c>
-      <c r="C9" s="37" t="s">
+      <c r="C9" s="34" t="s">
         <v>122</v>
       </c>
-      <c r="D9" s="37" t="b">
-        <v>0</v>
-      </c>
-      <c r="E9" s="37">
-        <v>0</v>
-      </c>
-      <c r="F9" s="38" t="s">
+      <c r="D9" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="E9" s="34">
+        <v>0</v>
+      </c>
+      <c r="F9" s="35" t="s">
         <v>123</v>
       </c>
-      <c r="G9" s="37" t="s">
+      <c r="G9" s="34" t="s">
         <v>11</v>
       </c>
-      <c r="H9" s="37">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" ht="39" spans="1:8">
-      <c r="A10" s="35" t="s">
+      <c r="H9" s="34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" ht="38.25" spans="1:8">
+      <c r="A10" s="32" t="s">
         <v>124</v>
       </c>
-      <c r="B10" s="35" t="s">
+      <c r="B10" s="32" t="s">
         <v>124</v>
       </c>
-      <c r="C10" s="35" t="s">
+      <c r="C10" s="32" t="s">
         <v>125</v>
       </c>
-      <c r="D10" s="35" t="b">
-        <v>0</v>
-      </c>
-      <c r="E10" s="35">
-        <v>0</v>
-      </c>
-      <c r="F10" s="36" t="s">
+      <c r="D10" s="32" t="b">
+        <v>0</v>
+      </c>
+      <c r="E10" s="32">
+        <v>0</v>
+      </c>
+      <c r="F10" s="33" t="s">
         <v>126</v>
       </c>
-      <c r="G10" s="35" t="s">
+      <c r="G10" s="32" t="s">
         <v>11</v>
       </c>
-      <c r="H10" s="35">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" ht="117" spans="1:8">
-      <c r="A11" s="39" t="s">
+      <c r="H10" s="32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" ht="127.5" spans="1:8">
+      <c r="A11" s="36" t="s">
         <v>127</v>
       </c>
-      <c r="B11" s="39" t="s">
+      <c r="B11" s="36" t="s">
         <v>127</v>
       </c>
-      <c r="C11" s="39" t="s">
+      <c r="C11" s="36" t="s">
         <v>128</v>
       </c>
-      <c r="D11" s="39" t="b">
-        <v>0</v>
-      </c>
-      <c r="E11" s="39">
-        <v>0</v>
-      </c>
-      <c r="F11" s="40" t="s">
+      <c r="D11" s="36" t="b">
+        <v>0</v>
+      </c>
+      <c r="E11" s="36">
+        <v>0</v>
+      </c>
+      <c r="F11" s="37" t="s">
         <v>129</v>
       </c>
-      <c r="G11" s="39" t="s">
+      <c r="G11" s="36" t="s">
         <v>11</v>
       </c>
-      <c r="H11" s="39">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" ht="39" spans="1:8">
-      <c r="A12" s="41" t="s">
+      <c r="H11" s="36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" ht="38.25" spans="1:8">
+      <c r="A12" s="38" t="s">
         <v>130</v>
       </c>
-      <c r="B12" s="41" t="s">
+      <c r="B12" s="38" t="s">
         <v>130</v>
       </c>
-      <c r="C12" s="41" t="s">
+      <c r="C12" s="38" t="s">
         <v>131</v>
       </c>
-      <c r="D12" s="41" t="b">
-        <v>0</v>
-      </c>
-      <c r="E12" s="41">
-        <v>0</v>
-      </c>
-      <c r="F12" s="42" t="s">
+      <c r="D12" s="38" t="b">
+        <v>0</v>
+      </c>
+      <c r="E12" s="38">
+        <v>0</v>
+      </c>
+      <c r="F12" s="39" t="s">
         <v>132</v>
       </c>
-      <c r="G12" s="41" t="s">
+      <c r="G12" s="38" t="s">
         <v>11</v>
       </c>
-      <c r="H12" s="41">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" ht="26" spans="1:8">
-      <c r="A13" s="39" t="s">
+      <c r="H12" s="38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" ht="25.5" spans="1:8">
+      <c r="A13" s="36" t="s">
         <v>133</v>
       </c>
-      <c r="B13" s="39" t="s">
+      <c r="B13" s="36" t="s">
         <v>133</v>
       </c>
-      <c r="C13" s="39" t="s">
+      <c r="C13" s="36" t="s">
         <v>134</v>
       </c>
-      <c r="D13" s="39" t="b">
-        <v>0</v>
-      </c>
-      <c r="E13" s="39">
-        <v>0</v>
-      </c>
-      <c r="F13" s="40" t="s">
+      <c r="D13" s="36" t="b">
+        <v>0</v>
+      </c>
+      <c r="E13" s="36">
+        <v>0</v>
+      </c>
+      <c r="F13" s="37" t="s">
         <v>135</v>
       </c>
-      <c r="G13" s="39" t="s">
+      <c r="G13" s="36" t="s">
         <v>11</v>
       </c>
-      <c r="H13" s="39">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" ht="26" spans="1:8">
-      <c r="A14" s="41" t="s">
+      <c r="H13" s="36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" ht="25.5" spans="1:8">
+      <c r="A14" s="38" t="s">
         <v>136</v>
       </c>
-      <c r="B14" s="41" t="s">
+      <c r="B14" s="38" t="s">
         <v>136</v>
       </c>
-      <c r="C14" s="41" t="s">
+      <c r="C14" s="38" t="s">
         <v>137</v>
       </c>
-      <c r="D14" s="41" t="b">
-        <v>0</v>
-      </c>
-      <c r="E14" s="41">
-        <v>0</v>
-      </c>
-      <c r="F14" s="42" t="s">
+      <c r="D14" s="38" t="b">
+        <v>0</v>
+      </c>
+      <c r="E14" s="38">
+        <v>0</v>
+      </c>
+      <c r="F14" s="39" t="s">
         <v>138</v>
       </c>
-      <c r="G14" s="41" t="s">
+      <c r="G14" s="38" t="s">
         <v>11</v>
       </c>
-      <c r="H14" s="41">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" ht="17" spans="1:8">
-      <c r="A15" s="39" t="s">
+      <c r="H14" s="38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" ht="16.9" spans="1:8">
+      <c r="A15" s="36" t="s">
         <v>139</v>
       </c>
-      <c r="B15" s="39" t="s">
+      <c r="B15" s="36" t="s">
         <v>139</v>
       </c>
-      <c r="C15" s="39" t="s">
+      <c r="C15" s="36" t="s">
         <v>140</v>
       </c>
-      <c r="D15" s="39" t="b">
-        <v>0</v>
-      </c>
-      <c r="E15" s="39">
-        <v>0</v>
-      </c>
-      <c r="F15" s="40" t="s">
+      <c r="D15" s="36" t="b">
+        <v>0</v>
+      </c>
+      <c r="E15" s="36">
+        <v>0</v>
+      </c>
+      <c r="F15" s="37" t="s">
         <v>141</v>
       </c>
-      <c r="G15" s="39" t="s">
+      <c r="G15" s="36" t="s">
         <v>11</v>
       </c>
-      <c r="H15" s="39">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" ht="39" spans="1:8">
-      <c r="A16" s="41" t="s">
+      <c r="H15" s="36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" ht="51" spans="1:8">
+      <c r="A16" s="38" t="s">
         <v>142</v>
       </c>
-      <c r="B16" s="41" t="s">
+      <c r="B16" s="38" t="s">
         <v>142</v>
       </c>
-      <c r="C16" s="41" t="s">
+      <c r="C16" s="38" t="s">
         <v>143</v>
       </c>
-      <c r="D16" s="41" t="b">
-        <v>0</v>
-      </c>
-      <c r="E16" s="41">
-        <v>0</v>
-      </c>
-      <c r="F16" s="42" t="s">
+      <c r="D16" s="38" t="b">
+        <v>0</v>
+      </c>
+      <c r="E16" s="38">
+        <v>0</v>
+      </c>
+      <c r="F16" s="39" t="s">
         <v>144</v>
       </c>
-      <c r="G16" s="41" t="s">
+      <c r="G16" s="38" t="s">
         <v>11</v>
       </c>
-      <c r="H16" s="41">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" ht="26" spans="1:8">
-      <c r="A17" s="39" t="s">
+      <c r="H16" s="38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" ht="25.5" spans="1:8">
+      <c r="A17" s="36" t="s">
         <v>145</v>
       </c>
-      <c r="B17" s="39" t="s">
+      <c r="B17" s="36" t="s">
         <v>145</v>
       </c>
-      <c r="C17" s="39" t="s">
+      <c r="C17" s="36" t="s">
         <v>146</v>
       </c>
-      <c r="D17" s="39" t="b">
-        <v>0</v>
-      </c>
-      <c r="E17" s="39">
-        <v>0</v>
-      </c>
-      <c r="F17" s="40" t="s">
+      <c r="D17" s="36" t="b">
+        <v>0</v>
+      </c>
+      <c r="E17" s="36">
+        <v>0</v>
+      </c>
+      <c r="F17" s="37" t="s">
         <v>147</v>
       </c>
-      <c r="G17" s="39" t="s">
+      <c r="G17" s="36" t="s">
         <v>11</v>
       </c>
-      <c r="H17" s="39">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" ht="26" spans="1:8">
-      <c r="A18" s="41" t="s">
+      <c r="H17" s="36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" ht="25.5" spans="1:8">
+      <c r="A18" s="38" t="s">
         <v>148</v>
       </c>
-      <c r="B18" s="41" t="s">
+      <c r="B18" s="38" t="s">
         <v>148</v>
       </c>
-      <c r="C18" s="41" t="s">
+      <c r="C18" s="38" t="s">
         <v>149</v>
       </c>
-      <c r="D18" s="41" t="b">
-        <v>0</v>
-      </c>
-      <c r="E18" s="41">
-        <v>0</v>
-      </c>
-      <c r="F18" s="42" t="s">
+      <c r="D18" s="38" t="b">
+        <v>0</v>
+      </c>
+      <c r="E18" s="38">
+        <v>0</v>
+      </c>
+      <c r="F18" s="39" t="s">
         <v>150</v>
       </c>
-      <c r="G18" s="41" t="s">
+      <c r="G18" s="38" t="s">
         <v>11</v>
       </c>
-      <c r="H18" s="41">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" ht="78" spans="1:8">
-      <c r="A19" s="39" t="s">
+      <c r="H18" s="38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" ht="76.5" spans="1:8">
+      <c r="A19" s="36" t="s">
         <v>151</v>
       </c>
-      <c r="B19" s="39" t="s">
+      <c r="B19" s="36" t="s">
         <v>151</v>
       </c>
-      <c r="C19" s="39" t="s">
+      <c r="C19" s="36" t="s">
         <v>152</v>
       </c>
-      <c r="D19" s="39" t="b">
-        <v>0</v>
-      </c>
-      <c r="E19" s="39">
-        <v>0</v>
-      </c>
-      <c r="F19" s="40" t="s">
+      <c r="D19" s="36" t="b">
+        <v>0</v>
+      </c>
+      <c r="E19" s="36">
+        <v>0</v>
+      </c>
+      <c r="F19" s="37" t="s">
         <v>153</v>
       </c>
-      <c r="G19" s="39" t="s">
+      <c r="G19" s="36" t="s">
         <v>11</v>
       </c>
-      <c r="H19" s="39">
+      <c r="H19" s="36">
         <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:8">
-      <c r="A20" s="41" t="s">
+      <c r="A20" s="38" t="s">
         <v>154</v>
       </c>
-      <c r="B20" s="41" t="s">
+      <c r="B20" s="38" t="s">
         <v>154</v>
       </c>
-      <c r="C20" s="41" t="s">
+      <c r="C20" s="38" t="s">
         <v>155</v>
       </c>
-      <c r="D20" s="41" t="b">
-        <v>0</v>
-      </c>
-      <c r="E20" s="41">
-        <v>0</v>
-      </c>
-      <c r="F20" s="42" t="s">
+      <c r="D20" s="38" t="b">
+        <v>0</v>
+      </c>
+      <c r="E20" s="38">
+        <v>0</v>
+      </c>
+      <c r="F20" s="39" t="s">
         <v>156</v>
       </c>
-      <c r="G20" s="41" t="s">
+      <c r="G20" s="38" t="s">
         <v>11</v>
       </c>
-      <c r="H20" s="41">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" ht="26" spans="1:8">
-      <c r="A21" s="39" t="s">
+      <c r="H20" s="38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" ht="25.5" spans="1:8">
+      <c r="A21" s="36" t="s">
         <v>157</v>
       </c>
-      <c r="B21" s="39" t="s">
+      <c r="B21" s="36" t="s">
         <v>157</v>
       </c>
-      <c r="C21" s="39" t="s">
+      <c r="C21" s="36" t="s">
         <v>158</v>
       </c>
-      <c r="D21" s="39" t="b">
-        <v>0</v>
-      </c>
-      <c r="E21" s="39">
-        <v>0</v>
-      </c>
-      <c r="F21" s="40" t="s">
+      <c r="D21" s="36" t="b">
+        <v>0</v>
+      </c>
+      <c r="E21" s="36">
+        <v>0</v>
+      </c>
+      <c r="F21" s="37" t="s">
         <v>159</v>
       </c>
-      <c r="G21" s="39" t="s">
+      <c r="G21" s="36" t="s">
         <v>11</v>
       </c>
-      <c r="H21" s="39">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" ht="26" spans="1:8">
-      <c r="A22" s="41" t="s">
+      <c r="H21" s="36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" ht="38.25" spans="1:8">
+      <c r="A22" s="38" t="s">
         <v>160</v>
       </c>
-      <c r="B22" s="41" t="s">
+      <c r="B22" s="38" t="s">
         <v>160</v>
       </c>
-      <c r="C22" s="41" t="s">
+      <c r="C22" s="38" t="s">
         <v>161</v>
       </c>
-      <c r="D22" s="41" t="b">
+      <c r="D22" s="38" t="b">
         <v>1</v>
       </c>
-      <c r="E22" s="41">
+      <c r="E22" s="38">
         <v>1</v>
       </c>
-      <c r="F22" s="42" t="s">
+      <c r="F22" s="39" t="s">
         <v>162</v>
       </c>
-      <c r="G22" s="41" t="s">
+      <c r="G22" s="38" t="s">
         <v>11</v>
       </c>
-      <c r="H22" s="41">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" ht="65" spans="1:8">
-      <c r="A23" s="39" t="s">
+      <c r="H22" s="38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" ht="63.75" spans="1:8">
+      <c r="A23" s="36" t="s">
         <v>163</v>
       </c>
-      <c r="B23" s="39" t="s">
+      <c r="B23" s="36" t="s">
         <v>163</v>
       </c>
-      <c r="C23" s="39" t="s">
+      <c r="C23" s="36" t="s">
         <v>88</v>
       </c>
-      <c r="D23" s="39" t="b">
-        <v>0</v>
-      </c>
-      <c r="E23" s="39">
-        <v>0</v>
-      </c>
-      <c r="F23" s="40" t="s">
+      <c r="D23" s="36" t="b">
+        <v>0</v>
+      </c>
+      <c r="E23" s="36">
+        <v>0</v>
+      </c>
+      <c r="F23" s="37" t="s">
         <v>164</v>
       </c>
-      <c r="G23" s="39" t="s">
+      <c r="G23" s="36" t="s">
         <v>11</v>
       </c>
-      <c r="H23" s="39">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" ht="65" spans="1:8">
-      <c r="A24" s="41" t="s">
+      <c r="H23" s="36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" ht="63.75" spans="1:8">
+      <c r="A24" s="38" t="s">
         <v>165</v>
       </c>
-      <c r="B24" s="41" t="s">
+      <c r="B24" s="38" t="s">
         <v>165</v>
       </c>
-      <c r="C24" s="41" t="s">
+      <c r="C24" s="38" t="s">
         <v>166</v>
       </c>
-      <c r="D24" s="41" t="b">
-        <v>0</v>
-      </c>
-      <c r="E24" s="41">
-        <v>0</v>
-      </c>
-      <c r="F24" s="42" t="s">
+      <c r="D24" s="38" t="b">
+        <v>0</v>
+      </c>
+      <c r="E24" s="38">
+        <v>0</v>
+      </c>
+      <c r="F24" s="39" t="s">
         <v>167</v>
       </c>
-      <c r="G24" s="41" t="s">
+      <c r="G24" s="38" t="s">
         <v>11</v>
       </c>
-      <c r="H24" s="41">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" ht="26" spans="1:8">
-      <c r="A25" s="39" t="s">
+      <c r="H24" s="38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" ht="25.5" spans="1:8">
+      <c r="A25" s="36" t="s">
         <v>168</v>
       </c>
-      <c r="B25" s="39" t="s">
+      <c r="B25" s="36" t="s">
         <v>168</v>
       </c>
-      <c r="C25" s="39" t="s">
+      <c r="C25" s="36" t="s">
         <v>169</v>
       </c>
-      <c r="D25" s="39" t="b">
-        <v>0</v>
-      </c>
-      <c r="E25" s="39">
-        <v>0</v>
-      </c>
-      <c r="F25" s="40" t="s">
+      <c r="D25" s="36" t="b">
+        <v>0</v>
+      </c>
+      <c r="E25" s="36">
+        <v>0</v>
+      </c>
+      <c r="F25" s="37" t="s">
         <v>170</v>
       </c>
-      <c r="G25" s="39" t="s">
+      <c r="G25" s="36" t="s">
         <v>11</v>
       </c>
-      <c r="H25" s="39">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" ht="78" spans="1:8">
-      <c r="A26" s="41" t="s">
+      <c r="H25" s="36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" ht="76.5" spans="1:8">
+      <c r="A26" s="38" t="s">
         <v>171</v>
       </c>
-      <c r="B26" s="41" t="s">
+      <c r="B26" s="38" t="s">
         <v>171</v>
       </c>
-      <c r="C26" s="41" t="s">
+      <c r="C26" s="38" t="s">
         <v>172</v>
       </c>
-      <c r="D26" s="41" t="b">
+      <c r="D26" s="38" t="b">
         <v>1</v>
       </c>
-      <c r="E26" s="41">
+      <c r="E26" s="38">
         <v>1</v>
       </c>
-      <c r="F26" s="42" t="s">
+      <c r="F26" s="39" t="s">
         <v>173</v>
       </c>
-      <c r="G26" s="41" t="s">
+      <c r="G26" s="38" t="s">
         <v>11</v>
       </c>
-      <c r="H26" s="41">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" ht="52" spans="1:8">
-      <c r="A27" s="39" t="s">
+      <c r="H26" s="38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" ht="63.75" spans="1:8">
+      <c r="A27" s="36" t="s">
         <v>174</v>
       </c>
-      <c r="B27" s="39" t="s">
+      <c r="B27" s="36" t="s">
         <v>174</v>
       </c>
-      <c r="C27" s="39" t="s">
+      <c r="C27" s="36" t="s">
         <v>175</v>
       </c>
-      <c r="D27" s="39" t="b">
-        <v>0</v>
-      </c>
-      <c r="E27" s="39">
-        <v>0</v>
-      </c>
-      <c r="F27" s="40" t="s">
+      <c r="D27" s="36" t="b">
+        <v>0</v>
+      </c>
+      <c r="E27" s="36">
+        <v>0</v>
+      </c>
+      <c r="F27" s="37" t="s">
         <v>176</v>
       </c>
-      <c r="G27" s="39" t="s">
+      <c r="G27" s="36" t="s">
         <v>11</v>
       </c>
-      <c r="H27" s="39">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" ht="65" spans="1:8">
-      <c r="A28" s="41" t="s">
+      <c r="H27" s="36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" ht="76.5" spans="1:8">
+      <c r="A28" s="38" t="s">
         <v>177</v>
       </c>
-      <c r="B28" s="41" t="s">
+      <c r="B28" s="38" t="s">
         <v>177</v>
       </c>
-      <c r="C28" s="41" t="s">
+      <c r="C28" s="38" t="s">
         <v>178</v>
       </c>
-      <c r="D28" s="41" t="b">
-        <v>0</v>
-      </c>
-      <c r="E28" s="41">
-        <v>0</v>
-      </c>
-      <c r="F28" s="42" t="s">
+      <c r="D28" s="38" t="b">
+        <v>0</v>
+      </c>
+      <c r="E28" s="38">
+        <v>0</v>
+      </c>
+      <c r="F28" s="39" t="s">
         <v>179</v>
       </c>
-      <c r="G28" s="41" t="s">
+      <c r="G28" s="38" t="s">
         <v>11</v>
       </c>
-      <c r="H28" s="41">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" ht="26" spans="1:8">
-      <c r="A29" s="39" t="s">
+      <c r="H28" s="38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" ht="25.5" spans="1:8">
+      <c r="A29" s="36" t="s">
         <v>180</v>
       </c>
-      <c r="B29" s="39" t="s">
+      <c r="B29" s="36" t="s">
         <v>180</v>
       </c>
-      <c r="C29" s="39" t="s">
+      <c r="C29" s="36" t="s">
         <v>181</v>
       </c>
-      <c r="D29" s="39" t="b">
-        <v>0</v>
-      </c>
-      <c r="E29" s="39">
-        <v>0</v>
-      </c>
-      <c r="F29" s="40" t="s">
+      <c r="D29" s="36" t="b">
+        <v>0</v>
+      </c>
+      <c r="E29" s="36">
+        <v>0</v>
+      </c>
+      <c r="F29" s="37" t="s">
         <v>182</v>
       </c>
-      <c r="G29" s="39" t="s">
+      <c r="G29" s="36" t="s">
         <v>11</v>
       </c>
-      <c r="H29" s="39">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" ht="39" spans="1:8">
-      <c r="A30" s="41" t="s">
+      <c r="H29" s="36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" ht="38.25" spans="1:8">
+      <c r="A30" s="38" t="s">
         <v>183</v>
       </c>
-      <c r="B30" s="41" t="s">
+      <c r="B30" s="38" t="s">
         <v>183</v>
       </c>
-      <c r="C30" s="41" t="s">
+      <c r="C30" s="38" t="s">
         <v>184</v>
       </c>
-      <c r="D30" s="41" t="b">
-        <v>0</v>
-      </c>
-      <c r="E30" s="41">
-        <v>0</v>
-      </c>
-      <c r="F30" s="42" t="s">
+      <c r="D30" s="38" t="b">
+        <v>0</v>
+      </c>
+      <c r="E30" s="38">
+        <v>0</v>
+      </c>
+      <c r="F30" s="39" t="s">
         <v>185</v>
       </c>
-      <c r="G30" s="41" t="s">
+      <c r="G30" s="38" t="s">
         <v>11</v>
       </c>
-      <c r="H30" s="41">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" ht="26" spans="1:8">
-      <c r="A31" s="39" t="s">
+      <c r="H30" s="38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" ht="25.5" spans="1:8">
+      <c r="A31" s="36" t="s">
         <v>186</v>
       </c>
-      <c r="B31" s="39" t="s">
+      <c r="B31" s="36" t="s">
         <v>186</v>
       </c>
-      <c r="C31" s="39" t="s">
+      <c r="C31" s="36" t="s">
         <v>187</v>
       </c>
-      <c r="D31" s="39" t="b">
-        <v>0</v>
-      </c>
-      <c r="E31" s="39">
-        <v>0</v>
-      </c>
-      <c r="F31" s="40" t="s">
+      <c r="D31" s="36" t="b">
+        <v>0</v>
+      </c>
+      <c r="E31" s="36">
+        <v>0</v>
+      </c>
+      <c r="F31" s="37" t="s">
         <v>188</v>
       </c>
-      <c r="G31" s="39" t="s">
+      <c r="G31" s="36" t="s">
         <v>11</v>
       </c>
-      <c r="H31" s="39">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" ht="26" spans="1:8">
-      <c r="A32" s="41" t="s">
+      <c r="H31" s="36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" ht="25.5" spans="1:8">
+      <c r="A32" s="38" t="s">
         <v>189</v>
       </c>
-      <c r="B32" s="41" t="s">
+      <c r="B32" s="38" t="s">
         <v>189</v>
       </c>
-      <c r="C32" s="41" t="s">
+      <c r="C32" s="38" t="s">
         <v>190</v>
       </c>
-      <c r="D32" s="41" t="b">
-        <v>0</v>
-      </c>
-      <c r="E32" s="41">
-        <v>0</v>
-      </c>
-      <c r="F32" s="42" t="s">
+      <c r="D32" s="38" t="b">
+        <v>0</v>
+      </c>
+      <c r="E32" s="38">
+        <v>0</v>
+      </c>
+      <c r="F32" s="39" t="s">
         <v>191</v>
       </c>
-      <c r="G32" s="41" t="s">
+      <c r="G32" s="38" t="s">
         <v>11</v>
       </c>
-      <c r="H32" s="41">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" ht="39" spans="1:8">
-      <c r="A33" s="39" t="s">
+      <c r="H32" s="38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" ht="38.25" spans="1:8">
+      <c r="A33" s="36" t="s">
         <v>192</v>
       </c>
-      <c r="B33" s="39" t="s">
+      <c r="B33" s="36" t="s">
         <v>192</v>
       </c>
-      <c r="C33" s="39" t="s">
+      <c r="C33" s="36" t="s">
         <v>193</v>
       </c>
-      <c r="D33" s="39" t="b">
-        <v>0</v>
-      </c>
-      <c r="E33" s="39">
-        <v>0</v>
-      </c>
-      <c r="F33" s="40" t="s">
+      <c r="D33" s="36" t="b">
+        <v>0</v>
+      </c>
+      <c r="E33" s="36">
+        <v>0</v>
+      </c>
+      <c r="F33" s="37" t="s">
         <v>194</v>
       </c>
-      <c r="G33" s="39" t="s">
+      <c r="G33" s="36" t="s">
         <v>11</v>
       </c>
-      <c r="H33" s="39">
+      <c r="H33" s="36">
         <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:8">
-      <c r="A34" s="41" t="s">
+      <c r="A34" s="38" t="s">
         <v>195</v>
       </c>
-      <c r="B34" s="41" t="s">
+      <c r="B34" s="38" t="s">
         <v>195</v>
       </c>
-      <c r="C34" s="41" t="s">
+      <c r="C34" s="38" t="s">
         <v>196</v>
       </c>
-      <c r="D34" s="41" t="b">
-        <v>0</v>
-      </c>
-      <c r="E34" s="41">
-        <v>0</v>
-      </c>
-      <c r="F34" s="42" t="s">
+      <c r="D34" s="38" t="b">
+        <v>0</v>
+      </c>
+      <c r="E34" s="38">
+        <v>0</v>
+      </c>
+      <c r="F34" s="39" t="s">
         <v>197</v>
       </c>
-      <c r="G34" s="41" t="s">
+      <c r="G34" s="38" t="s">
         <v>11</v>
       </c>
-      <c r="H34" s="41">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" ht="130" spans="1:8">
-      <c r="A35" s="39" t="s">
+      <c r="H34" s="38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" ht="127.5" spans="1:8">
+      <c r="A35" s="36" t="s">
         <v>198</v>
       </c>
-      <c r="B35" s="39" t="s">
+      <c r="B35" s="36" t="s">
         <v>198</v>
       </c>
-      <c r="C35" s="39" t="s">
+      <c r="C35" s="36" t="s">
         <v>199</v>
       </c>
-      <c r="D35" s="39" t="b">
-        <v>0</v>
-      </c>
-      <c r="E35" s="39">
-        <v>0</v>
-      </c>
-      <c r="F35" s="40" t="s">
+      <c r="D35" s="36" t="b">
+        <v>0</v>
+      </c>
+      <c r="E35" s="36">
+        <v>0</v>
+      </c>
+      <c r="F35" s="37" t="s">
         <v>200</v>
       </c>
-      <c r="G35" s="39" t="s">
+      <c r="G35" s="36" t="s">
         <v>11</v>
       </c>
-      <c r="H35" s="39">
+      <c r="H35" s="36">
         <v>0</v>
       </c>
     </row>
     <row r="36" spans="1:8">
-      <c r="A36" s="41" t="s">
+      <c r="A36" s="38" t="s">
         <v>201</v>
       </c>
-      <c r="B36" s="41" t="s">
+      <c r="B36" s="38" t="s">
         <v>201</v>
       </c>
-      <c r="C36" s="41" t="s">
+      <c r="C36" s="38" t="s">
         <v>202</v>
       </c>
-      <c r="D36" s="41" t="b">
-        <v>0</v>
-      </c>
-      <c r="E36" s="41">
-        <v>0</v>
-      </c>
-      <c r="F36" s="42" t="s">
+      <c r="D36" s="38" t="b">
+        <v>0</v>
+      </c>
+      <c r="E36" s="38">
+        <v>0</v>
+      </c>
+      <c r="F36" s="39" t="s">
         <v>203</v>
       </c>
-      <c r="G36" s="41" t="s">
+      <c r="G36" s="38" t="s">
         <v>11</v>
       </c>
-      <c r="H36" s="41">
+      <c r="H36" s="38">
         <v>0</v>
       </c>
     </row>
     <row r="37" spans="1:8">
-      <c r="A37" s="39" t="s">
+      <c r="A37" s="36" t="s">
         <v>204</v>
       </c>
-      <c r="B37" s="39" t="s">
+      <c r="B37" s="36" t="s">
         <v>204</v>
       </c>
-      <c r="C37" s="39" t="s">
+      <c r="C37" s="36" t="s">
         <v>205</v>
       </c>
-      <c r="D37" s="39" t="b">
-        <v>0</v>
-      </c>
-      <c r="E37" s="39">
-        <v>0</v>
-      </c>
-      <c r="F37" s="40" t="s">
+      <c r="D37" s="36" t="b">
+        <v>0</v>
+      </c>
+      <c r="E37" s="36">
+        <v>0</v>
+      </c>
+      <c r="F37" s="37" t="s">
         <v>206</v>
       </c>
-      <c r="G37" s="39" t="s">
+      <c r="G37" s="36" t="s">
         <v>11</v>
       </c>
-      <c r="H37" s="39">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38" ht="39" spans="1:8">
-      <c r="A38" s="41" t="s">
+      <c r="H37" s="36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" ht="38.25" spans="1:8">
+      <c r="A38" s="38" t="s">
         <v>207</v>
       </c>
-      <c r="B38" s="41" t="s">
+      <c r="B38" s="38" t="s">
         <v>207</v>
       </c>
-      <c r="C38" s="41" t="s">
+      <c r="C38" s="38" t="s">
         <v>208</v>
       </c>
-      <c r="D38" s="41" t="b">
-        <v>0</v>
-      </c>
-      <c r="E38" s="41">
-        <v>0</v>
-      </c>
-      <c r="F38" s="42" t="s">
+      <c r="D38" s="38" t="b">
+        <v>0</v>
+      </c>
+      <c r="E38" s="38">
+        <v>0</v>
+      </c>
+      <c r="F38" s="39" t="s">
         <v>209</v>
       </c>
-      <c r="G38" s="41" t="s">
+      <c r="G38" s="38" t="s">
         <v>11</v>
       </c>
-      <c r="H38" s="41">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" ht="26" spans="1:8">
-      <c r="A39" s="39" t="s">
+      <c r="H38" s="38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" ht="25.5" spans="1:8">
+      <c r="A39" s="36" t="s">
         <v>210</v>
       </c>
-      <c r="B39" s="39" t="s">
+      <c r="B39" s="36" t="s">
         <v>210</v>
       </c>
-      <c r="C39" s="39" t="s">
+      <c r="C39" s="36" t="s">
         <v>211</v>
       </c>
-      <c r="D39" s="39" t="b">
-        <v>0</v>
-      </c>
-      <c r="E39" s="39">
-        <v>0</v>
-      </c>
-      <c r="F39" s="40" t="s">
+      <c r="D39" s="36" t="b">
+        <v>0</v>
+      </c>
+      <c r="E39" s="36">
+        <v>0</v>
+      </c>
+      <c r="F39" s="37" t="s">
         <v>212</v>
       </c>
-      <c r="G39" s="39" t="s">
+      <c r="G39" s="36" t="s">
         <v>11</v>
       </c>
-      <c r="H39" s="39">
+      <c r="H39" s="36">
         <v>0</v>
       </c>
     </row>
     <row r="40" spans="1:8">
-      <c r="A40" s="41" t="s">
+      <c r="A40" s="38" t="s">
         <v>213</v>
       </c>
-      <c r="B40" s="41" t="s">
+      <c r="B40" s="38" t="s">
         <v>213</v>
       </c>
-      <c r="C40" s="41" t="s">
+      <c r="C40" s="38" t="s">
         <v>214</v>
       </c>
-      <c r="D40" s="41" t="b">
-        <v>0</v>
-      </c>
-      <c r="E40" s="41">
-        <v>0</v>
-      </c>
-      <c r="F40" s="42" t="s">
+      <c r="D40" s="38" t="b">
+        <v>0</v>
+      </c>
+      <c r="E40" s="38">
+        <v>0</v>
+      </c>
+      <c r="F40" s="39" t="s">
         <v>215</v>
       </c>
-      <c r="G40" s="41" t="s">
+      <c r="G40" s="38" t="s">
         <v>11</v>
       </c>
-      <c r="H40" s="41">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41" ht="26" spans="1:8">
-      <c r="A41" s="39" t="s">
+      <c r="H40" s="38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" ht="25.5" spans="1:8">
+      <c r="A41" s="36" t="s">
         <v>216</v>
       </c>
-      <c r="B41" s="39" t="s">
+      <c r="B41" s="36" t="s">
         <v>216</v>
       </c>
-      <c r="C41" s="39" t="s">
+      <c r="C41" s="36" t="s">
         <v>217</v>
       </c>
-      <c r="D41" s="39" t="b">
-        <v>0</v>
-      </c>
-      <c r="E41" s="39">
-        <v>0</v>
-      </c>
-      <c r="F41" s="40" t="s">
+      <c r="D41" s="36" t="b">
+        <v>0</v>
+      </c>
+      <c r="E41" s="36">
+        <v>0</v>
+      </c>
+      <c r="F41" s="37" t="s">
         <v>218</v>
       </c>
-      <c r="G41" s="39" t="s">
+      <c r="G41" s="36" t="s">
         <v>11</v>
       </c>
-      <c r="H41" s="39">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42" ht="26" spans="1:8">
-      <c r="A42" s="41" t="s">
+      <c r="H41" s="36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" ht="38.25" spans="1:8">
+      <c r="A42" s="38" t="s">
         <v>219</v>
       </c>
-      <c r="B42" s="41" t="s">
+      <c r="B42" s="38" t="s">
         <v>219</v>
       </c>
-      <c r="C42" s="41" t="s">
+      <c r="C42" s="38" t="s">
         <v>220</v>
       </c>
-      <c r="D42" s="41" t="b">
-        <v>0</v>
-      </c>
-      <c r="E42" s="41">
-        <v>0</v>
-      </c>
-      <c r="F42" s="42" t="s">
+      <c r="D42" s="38" t="b">
+        <v>0</v>
+      </c>
+      <c r="E42" s="38">
+        <v>0</v>
+      </c>
+      <c r="F42" s="39" t="s">
         <v>221</v>
       </c>
-      <c r="G42" s="41" t="s">
+      <c r="G42" s="38" t="s">
         <v>11</v>
       </c>
-      <c r="H42" s="41">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43" ht="26" spans="1:8">
-      <c r="A43" s="39" t="s">
+      <c r="H42" s="38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" ht="38.25" spans="1:8">
+      <c r="A43" s="36" t="s">
         <v>222</v>
       </c>
-      <c r="B43" s="39" t="s">
+      <c r="B43" s="36" t="s">
         <v>222</v>
       </c>
-      <c r="C43" s="39" t="s">
+      <c r="C43" s="36" t="s">
         <v>223</v>
       </c>
-      <c r="D43" s="39" t="b">
-        <v>0</v>
-      </c>
-      <c r="E43" s="39">
-        <v>0</v>
-      </c>
-      <c r="F43" s="40" t="s">
+      <c r="D43" s="36" t="b">
+        <v>0</v>
+      </c>
+      <c r="E43" s="36">
+        <v>0</v>
+      </c>
+      <c r="F43" s="37" t="s">
         <v>224</v>
       </c>
-      <c r="G43" s="39" t="s">
+      <c r="G43" s="36" t="s">
         <v>11</v>
       </c>
-      <c r="H43" s="39">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44" ht="39" spans="1:8">
-      <c r="A44" s="41" t="s">
+      <c r="H43" s="36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" ht="51" spans="1:8">
+      <c r="A44" s="38" t="s">
         <v>225</v>
       </c>
-      <c r="B44" s="41" t="s">
+      <c r="B44" s="38" t="s">
         <v>225</v>
       </c>
-      <c r="C44" s="41" t="s">
+      <c r="C44" s="38" t="s">
         <v>226</v>
       </c>
-      <c r="D44" s="41" t="b">
-        <v>0</v>
-      </c>
-      <c r="E44" s="41">
-        <v>0</v>
-      </c>
-      <c r="F44" s="42" t="s">
+      <c r="D44" s="38" t="b">
+        <v>0</v>
+      </c>
+      <c r="E44" s="38">
+        <v>0</v>
+      </c>
+      <c r="F44" s="39" t="s">
         <v>227</v>
       </c>
-      <c r="G44" s="41" t="s">
+      <c r="G44" s="38" t="s">
         <v>11</v>
       </c>
-      <c r="H44" s="41">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45" ht="26" spans="1:8">
-      <c r="A45" s="39" t="s">
+      <c r="H44" s="38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" ht="25.5" spans="1:8">
+      <c r="A45" s="36" t="s">
         <v>228</v>
       </c>
-      <c r="B45" s="39" t="s">
+      <c r="B45" s="36" t="s">
         <v>228</v>
       </c>
-      <c r="C45" s="39" t="s">
+      <c r="C45" s="36" t="s">
         <v>229</v>
       </c>
-      <c r="D45" s="39" t="b">
-        <v>0</v>
-      </c>
-      <c r="E45" s="39">
-        <v>0</v>
-      </c>
-      <c r="F45" s="40" t="s">
+      <c r="D45" s="36" t="b">
+        <v>0</v>
+      </c>
+      <c r="E45" s="36">
+        <v>0</v>
+      </c>
+      <c r="F45" s="37" t="s">
         <v>230</v>
       </c>
-      <c r="G45" s="39" t="s">
+      <c r="G45" s="36" t="s">
         <v>11</v>
       </c>
-      <c r="H45" s="39">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46" ht="26" spans="1:8">
-      <c r="A46" s="41" t="s">
+      <c r="H45" s="36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" ht="25.5" spans="1:8">
+      <c r="A46" s="38" t="s">
         <v>231</v>
       </c>
-      <c r="B46" s="41" t="s">
+      <c r="B46" s="38" t="s">
         <v>231</v>
       </c>
-      <c r="C46" s="41" t="s">
+      <c r="C46" s="38" t="s">
         <v>232</v>
       </c>
-      <c r="D46" s="41" t="b">
-        <v>0</v>
-      </c>
-      <c r="E46" s="41">
-        <v>0</v>
-      </c>
-      <c r="F46" s="42" t="s">
+      <c r="D46" s="38" t="b">
+        <v>0</v>
+      </c>
+      <c r="E46" s="38">
+        <v>0</v>
+      </c>
+      <c r="F46" s="39" t="s">
         <v>233</v>
       </c>
-      <c r="G46" s="41" t="s">
+      <c r="G46" s="38" t="s">
         <v>11</v>
       </c>
-      <c r="H46" s="41">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="47" ht="52" spans="1:8">
-      <c r="A47" s="39" t="s">
+      <c r="H46" s="38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" ht="51" spans="1:8">
+      <c r="A47" s="36" t="s">
         <v>234</v>
       </c>
-      <c r="B47" s="39" t="s">
+      <c r="B47" s="36" t="s">
         <v>234</v>
       </c>
-      <c r="C47" s="39" t="s">
+      <c r="C47" s="36" t="s">
         <v>235</v>
       </c>
-      <c r="D47" s="39" t="b">
-        <v>0</v>
-      </c>
-      <c r="E47" s="39">
-        <v>0</v>
-      </c>
-      <c r="F47" s="40" t="s">
+      <c r="D47" s="36" t="b">
+        <v>0</v>
+      </c>
+      <c r="E47" s="36">
+        <v>0</v>
+      </c>
+      <c r="F47" s="37" t="s">
         <v>236</v>
       </c>
-      <c r="G47" s="39" t="s">
+      <c r="G47" s="36" t="s">
         <v>11</v>
       </c>
-      <c r="H47" s="39">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48" ht="65" spans="1:8">
-      <c r="A48" s="41" t="s">
+      <c r="H47" s="36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" ht="63.75" spans="1:8">
+      <c r="A48" s="38" t="s">
         <v>237</v>
       </c>
-      <c r="B48" s="41" t="s">
+      <c r="B48" s="38" t="s">
         <v>237</v>
       </c>
-      <c r="C48" s="41" t="s">
+      <c r="C48" s="38" t="s">
         <v>238</v>
       </c>
-      <c r="D48" s="41" t="b">
-        <v>0</v>
-      </c>
-      <c r="E48" s="41">
-        <v>0</v>
-      </c>
-      <c r="F48" s="42" t="s">
+      <c r="D48" s="38" t="b">
+        <v>0</v>
+      </c>
+      <c r="E48" s="38">
+        <v>0</v>
+      </c>
+      <c r="F48" s="39" t="s">
         <v>239</v>
       </c>
-      <c r="G48" s="41" t="s">
+      <c r="G48" s="38" t="s">
         <v>11</v>
       </c>
-      <c r="H48" s="41">
+      <c r="H48" s="38">
         <v>0</v>
       </c>
     </row>
     <row r="49" spans="1:8">
-      <c r="A49" s="39" t="s">
+      <c r="A49" s="36" t="s">
         <v>240</v>
       </c>
-      <c r="B49" s="39" t="s">
+      <c r="B49" s="36" t="s">
         <v>240</v>
       </c>
-      <c r="C49" s="39" t="s">
+      <c r="C49" s="36" t="s">
         <v>241</v>
       </c>
-      <c r="D49" s="39" t="b">
-        <v>0</v>
-      </c>
-      <c r="E49" s="39">
-        <v>0</v>
-      </c>
-      <c r="F49" s="40" t="s">
+      <c r="D49" s="36" t="b">
+        <v>0</v>
+      </c>
+      <c r="E49" s="36">
+        <v>0</v>
+      </c>
+      <c r="F49" s="37" t="s">
         <v>242</v>
       </c>
-      <c r="G49" s="39" t="s">
+      <c r="G49" s="36" t="s">
         <v>11</v>
       </c>
-      <c r="H49" s="39">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="50" ht="39" spans="1:8">
-      <c r="A50" s="41" t="s">
+      <c r="H49" s="36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" ht="51" spans="1:8">
+      <c r="A50" s="38" t="s">
         <v>243</v>
       </c>
-      <c r="B50" s="41" t="s">
+      <c r="B50" s="38" t="s">
         <v>243</v>
       </c>
-      <c r="C50" s="41" t="s">
+      <c r="C50" s="38" t="s">
         <v>244</v>
       </c>
-      <c r="D50" s="41" t="b">
-        <v>0</v>
-      </c>
-      <c r="E50" s="41">
-        <v>0</v>
-      </c>
-      <c r="F50" s="42" t="s">
+      <c r="D50" s="38" t="b">
+        <v>0</v>
+      </c>
+      <c r="E50" s="38">
+        <v>0</v>
+      </c>
+      <c r="F50" s="39" t="s">
         <v>245</v>
       </c>
-      <c r="G50" s="41" t="s">
+      <c r="G50" s="38" t="s">
         <v>11</v>
       </c>
-      <c r="H50" s="41">
+      <c r="H50" s="38">
         <v>0</v>
       </c>
     </row>
     <row r="51" spans="1:8">
-      <c r="A51" s="39" t="s">
+      <c r="A51" s="36" t="s">
         <v>246</v>
       </c>
-      <c r="B51" s="39" t="s">
+      <c r="B51" s="36" t="s">
         <v>246</v>
       </c>
-      <c r="C51" s="39" t="s">
+      <c r="C51" s="36" t="s">
         <v>247</v>
       </c>
-      <c r="D51" s="39" t="b">
-        <v>0</v>
-      </c>
-      <c r="E51" s="39">
-        <v>0</v>
-      </c>
-      <c r="F51" s="40" t="s">
+      <c r="D51" s="36" t="b">
+        <v>0</v>
+      </c>
+      <c r="E51" s="36">
+        <v>0</v>
+      </c>
+      <c r="F51" s="37" t="s">
         <v>248</v>
       </c>
-      <c r="G51" s="39" t="s">
+      <c r="G51" s="36" t="s">
         <v>11</v>
       </c>
-      <c r="H51" s="39">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="52" ht="26" spans="1:8">
-      <c r="A52" s="41" t="s">
+      <c r="H51" s="36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" ht="38.25" spans="1:8">
+      <c r="A52" s="38" t="s">
         <v>249</v>
       </c>
-      <c r="B52" s="41" t="s">
+      <c r="B52" s="38" t="s">
         <v>249</v>
       </c>
-      <c r="C52" s="41" t="s">
+      <c r="C52" s="38" t="s">
         <v>250</v>
       </c>
-      <c r="D52" s="41" t="b">
-        <v>0</v>
-      </c>
-      <c r="E52" s="41">
-        <v>0</v>
-      </c>
-      <c r="F52" s="42" t="s">
+      <c r="D52" s="38" t="b">
+        <v>0</v>
+      </c>
+      <c r="E52" s="38">
+        <v>0</v>
+      </c>
+      <c r="F52" s="39" t="s">
         <v>251</v>
       </c>
-      <c r="G52" s="41" t="s">
+      <c r="G52" s="38" t="s">
         <v>11</v>
       </c>
-      <c r="H52" s="41">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="53" ht="26" spans="1:8">
-      <c r="A53" s="39" t="s">
+      <c r="H52" s="38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" ht="25.5" spans="1:8">
+      <c r="A53" s="36" t="s">
         <v>252</v>
       </c>
-      <c r="B53" s="39" t="s">
+      <c r="B53" s="36" t="s">
         <v>252</v>
       </c>
-      <c r="C53" s="39" t="s">
+      <c r="C53" s="36" t="s">
         <v>253</v>
       </c>
-      <c r="D53" s="39" t="b">
-        <v>0</v>
-      </c>
-      <c r="E53" s="39">
-        <v>0</v>
-      </c>
-      <c r="F53" s="40" t="s">
+      <c r="D53" s="36" t="b">
+        <v>0</v>
+      </c>
+      <c r="E53" s="36">
+        <v>0</v>
+      </c>
+      <c r="F53" s="37" t="s">
         <v>254</v>
       </c>
-      <c r="G53" s="39" t="s">
+      <c r="G53" s="36" t="s">
         <v>11</v>
       </c>
-      <c r="H53" s="39">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="54" ht="26" spans="1:8">
-      <c r="A54" s="41" t="s">
+      <c r="H53" s="36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" ht="25.5" spans="1:8">
+      <c r="A54" s="38" t="s">
         <v>255</v>
       </c>
-      <c r="B54" s="41" t="s">
+      <c r="B54" s="38" t="s">
         <v>255</v>
       </c>
-      <c r="C54" s="41" t="s">
+      <c r="C54" s="38" t="s">
         <v>256</v>
       </c>
-      <c r="D54" s="41" t="b">
-        <v>0</v>
-      </c>
-      <c r="E54" s="41">
-        <v>0</v>
-      </c>
-      <c r="F54" s="42" t="s">
+      <c r="D54" s="38" t="b">
+        <v>0</v>
+      </c>
+      <c r="E54" s="38">
+        <v>0</v>
+      </c>
+      <c r="F54" s="39" t="s">
         <v>257</v>
       </c>
-      <c r="G54" s="41" t="s">
+      <c r="G54" s="38" t="s">
         <v>11</v>
       </c>
-      <c r="H54" s="41">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="55" ht="39" spans="1:8">
-      <c r="A55" s="39" t="s">
+      <c r="H54" s="38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" ht="38.25" spans="1:8">
+      <c r="A55" s="36" t="s">
         <v>258</v>
       </c>
-      <c r="B55" s="39" t="s">
+      <c r="B55" s="36" t="s">
         <v>258</v>
       </c>
-      <c r="C55" s="39" t="s">
+      <c r="C55" s="36" t="s">
         <v>259</v>
       </c>
-      <c r="D55" s="39" t="b">
-        <v>0</v>
-      </c>
-      <c r="E55" s="39">
-        <v>0</v>
-      </c>
-      <c r="F55" s="40" t="s">
+      <c r="D55" s="36" t="b">
+        <v>0</v>
+      </c>
+      <c r="E55" s="36">
+        <v>0</v>
+      </c>
+      <c r="F55" s="37" t="s">
         <v>260</v>
       </c>
-      <c r="G55" s="39" t="s">
+      <c r="G55" s="36" t="s">
         <v>11</v>
       </c>
-      <c r="H55" s="39">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="56" ht="26" spans="1:8">
-      <c r="A56" s="41" t="s">
+      <c r="H55" s="36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" ht="25.5" spans="1:8">
+      <c r="A56" s="38" t="s">
         <v>261</v>
       </c>
-      <c r="B56" s="41" t="s">
+      <c r="B56" s="38" t="s">
         <v>261</v>
       </c>
-      <c r="C56" s="41" t="s">
+      <c r="C56" s="38" t="s">
         <v>262</v>
       </c>
-      <c r="D56" s="41" t="b">
-        <v>0</v>
-      </c>
-      <c r="E56" s="41">
-        <v>0</v>
-      </c>
-      <c r="F56" s="42" t="s">
+      <c r="D56" s="38" t="b">
+        <v>0</v>
+      </c>
+      <c r="E56" s="38">
+        <v>0</v>
+      </c>
+      <c r="F56" s="39" t="s">
         <v>263</v>
       </c>
-      <c r="G56" s="41" t="s">
+      <c r="G56" s="38" t="s">
         <v>11</v>
       </c>
-      <c r="H56" s="41">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="57" ht="26" spans="1:8">
-      <c r="A57" s="39" t="s">
+      <c r="H56" s="38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" ht="25.5" spans="1:8">
+      <c r="A57" s="36" t="s">
         <v>264</v>
       </c>
-      <c r="B57" s="39" t="s">
+      <c r="B57" s="36" t="s">
         <v>264</v>
       </c>
-      <c r="C57" s="39" t="s">
+      <c r="C57" s="36" t="s">
         <v>265</v>
       </c>
-      <c r="D57" s="39" t="b">
-        <v>0</v>
-      </c>
-      <c r="E57" s="39">
-        <v>0</v>
-      </c>
-      <c r="F57" s="40" t="s">
+      <c r="D57" s="36" t="b">
+        <v>0</v>
+      </c>
+      <c r="E57" s="36">
+        <v>0</v>
+      </c>
+      <c r="F57" s="37" t="s">
         <v>266</v>
       </c>
-      <c r="G57" s="39" t="s">
+      <c r="G57" s="36" t="s">
         <v>11</v>
       </c>
-      <c r="H57" s="39">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="58" ht="26" spans="1:8">
-      <c r="A58" s="41" t="s">
+      <c r="H57" s="36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" ht="38.25" spans="1:8">
+      <c r="A58" s="38" t="s">
         <v>267</v>
       </c>
-      <c r="B58" s="41" t="s">
+      <c r="B58" s="38" t="s">
         <v>267</v>
       </c>
-      <c r="C58" s="41" t="s">
+      <c r="C58" s="38" t="s">
         <v>268</v>
       </c>
-      <c r="D58" s="41" t="b">
-        <v>0</v>
-      </c>
-      <c r="E58" s="41">
-        <v>0</v>
-      </c>
-      <c r="F58" s="42" t="s">
+      <c r="D58" s="38" t="b">
+        <v>0</v>
+      </c>
+      <c r="E58" s="38">
+        <v>0</v>
+      </c>
+      <c r="F58" s="39" t="s">
         <v>269</v>
       </c>
-      <c r="G58" s="41" t="s">
+      <c r="G58" s="38" t="s">
         <v>11</v>
       </c>
-      <c r="H58" s="41">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="59" ht="30" spans="1:8">
-      <c r="A59" s="39" t="s">
+      <c r="H58" s="38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" ht="29.65" spans="1:8">
+      <c r="A59" s="36" t="s">
         <v>270</v>
       </c>
-      <c r="B59" s="39" t="s">
+      <c r="B59" s="36" t="s">
         <v>270</v>
       </c>
-      <c r="C59" s="39" t="s">
+      <c r="C59" s="36" t="s">
         <v>271</v>
       </c>
-      <c r="D59" s="39" t="b">
-        <v>0</v>
-      </c>
-      <c r="E59" s="39">
-        <v>0</v>
-      </c>
-      <c r="F59" s="40" t="s">
+      <c r="D59" s="36" t="b">
+        <v>0</v>
+      </c>
+      <c r="E59" s="36">
+        <v>0</v>
+      </c>
+      <c r="F59" s="37" t="s">
         <v>272</v>
       </c>
-      <c r="G59" s="39" t="s">
+      <c r="G59" s="36" t="s">
         <v>11</v>
       </c>
-      <c r="H59" s="39">
+      <c r="H59" s="36">
         <v>0</v>
       </c>
     </row>
     <row r="60" spans="1:8">
-      <c r="A60" s="41" t="s">
+      <c r="A60" s="38" t="s">
         <v>273</v>
       </c>
-      <c r="B60" s="41" t="s">
+      <c r="B60" s="38" t="s">
         <v>273</v>
       </c>
-      <c r="C60" s="41" t="s">
+      <c r="C60" s="38" t="s">
         <v>274</v>
       </c>
-      <c r="D60" s="41" t="b">
-        <v>0</v>
-      </c>
-      <c r="E60" s="41">
-        <v>0</v>
-      </c>
-      <c r="F60" s="42" t="s">
+      <c r="D60" s="38" t="b">
+        <v>0</v>
+      </c>
+      <c r="E60" s="38">
+        <v>0</v>
+      </c>
+      <c r="F60" s="39" t="s">
         <v>275</v>
       </c>
-      <c r="G60" s="41" t="s">
+      <c r="G60" s="38" t="s">
         <v>11</v>
       </c>
-      <c r="H60" s="41">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="61" ht="52" spans="1:8">
-      <c r="A61" s="39" t="s">
+      <c r="H60" s="38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" ht="51" spans="1:8">
+      <c r="A61" s="36" t="s">
         <v>276</v>
       </c>
-      <c r="B61" s="39" t="s">
+      <c r="B61" s="36" t="s">
         <v>276</v>
       </c>
-      <c r="C61" s="39" t="s">
+      <c r="C61" s="36" t="s">
         <v>277</v>
       </c>
-      <c r="D61" s="39" t="b">
-        <v>0</v>
-      </c>
-      <c r="E61" s="39">
-        <v>0</v>
-      </c>
-      <c r="F61" s="40" t="s">
+      <c r="D61" s="36" t="b">
+        <v>0</v>
+      </c>
+      <c r="E61" s="36">
+        <v>0</v>
+      </c>
+      <c r="F61" s="37" t="s">
         <v>278</v>
       </c>
-      <c r="G61" s="39" t="s">
+      <c r="G61" s="36" t="s">
         <v>11</v>
       </c>
-      <c r="H61" s="39">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62" ht="26" spans="1:8">
-      <c r="A62" s="41" t="s">
+      <c r="H61" s="36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" ht="25.5" spans="1:8">
+      <c r="A62" s="38" t="s">
         <v>279</v>
       </c>
-      <c r="B62" s="41" t="s">
+      <c r="B62" s="38" t="s">
         <v>279</v>
       </c>
-      <c r="C62" s="41" t="s">
+      <c r="C62" s="38" t="s">
         <v>280</v>
       </c>
-      <c r="D62" s="41" t="b">
-        <v>0</v>
-      </c>
-      <c r="E62" s="41">
-        <v>0</v>
-      </c>
-      <c r="F62" s="42" t="s">
+      <c r="D62" s="38" t="b">
+        <v>0</v>
+      </c>
+      <c r="E62" s="38">
+        <v>0</v>
+      </c>
+      <c r="F62" s="39" t="s">
         <v>281</v>
       </c>
-      <c r="G62" s="41" t="s">
+      <c r="G62" s="38" t="s">
         <v>11</v>
       </c>
-      <c r="H62" s="41">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="63" ht="39" spans="1:8">
-      <c r="A63" s="39" t="s">
+      <c r="H62" s="38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" ht="38.25" spans="1:8">
+      <c r="A63" s="36" t="s">
         <v>282</v>
       </c>
-      <c r="B63" s="39" t="s">
+      <c r="B63" s="36" t="s">
         <v>282</v>
       </c>
-      <c r="C63" s="39" t="s">
+      <c r="C63" s="36" t="s">
         <v>283</v>
       </c>
-      <c r="D63" s="39" t="b">
-        <v>0</v>
-      </c>
-      <c r="E63" s="39">
-        <v>0</v>
-      </c>
-      <c r="F63" s="40" t="s">
+      <c r="D63" s="36" t="b">
+        <v>0</v>
+      </c>
+      <c r="E63" s="36">
+        <v>0</v>
+      </c>
+      <c r="F63" s="37" t="s">
         <v>284</v>
       </c>
-      <c r="G63" s="39" t="s">
+      <c r="G63" s="36" t="s">
         <v>11</v>
       </c>
-      <c r="H63" s="39">
+      <c r="H63" s="36">
         <v>0</v>
       </c>
     </row>
     <row r="64" spans="1:8">
-      <c r="A64" s="41" t="s">
+      <c r="A64" s="38" t="s">
         <v>285</v>
       </c>
-      <c r="B64" s="41" t="s">
+      <c r="B64" s="38" t="s">
         <v>285</v>
       </c>
-      <c r="C64" s="41" t="s">
+      <c r="C64" s="38" t="s">
         <v>286</v>
       </c>
-      <c r="D64" s="41" t="b">
-        <v>0</v>
-      </c>
-      <c r="E64" s="41">
-        <v>0</v>
-      </c>
-      <c r="F64" s="42" t="s">
+      <c r="D64" s="38" t="b">
+        <v>0</v>
+      </c>
+      <c r="E64" s="38">
+        <v>0</v>
+      </c>
+      <c r="F64" s="39" t="s">
         <v>287</v>
       </c>
-      <c r="G64" s="41" t="s">
+      <c r="G64" s="38" t="s">
         <v>11</v>
       </c>
-      <c r="H64" s="41">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="65" ht="26" spans="1:8">
-      <c r="A65" s="39" t="s">
+      <c r="H64" s="38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" ht="25.5" spans="1:8">
+      <c r="A65" s="36" t="s">
         <v>288</v>
       </c>
-      <c r="B65" s="39" t="s">
+      <c r="B65" s="36" t="s">
         <v>288</v>
       </c>
-      <c r="C65" s="39" t="s">
+      <c r="C65" s="36" t="s">
         <v>289</v>
       </c>
-      <c r="D65" s="39" t="b">
-        <v>0</v>
-      </c>
-      <c r="E65" s="39">
-        <v>0</v>
-      </c>
-      <c r="F65" s="40" t="s">
+      <c r="D65" s="36" t="b">
+        <v>0</v>
+      </c>
+      <c r="E65" s="36">
+        <v>0</v>
+      </c>
+      <c r="F65" s="37" t="s">
         <v>290</v>
       </c>
-      <c r="G65" s="39" t="s">
+      <c r="G65" s="36" t="s">
         <v>11</v>
       </c>
-      <c r="H65" s="39">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="66" ht="39" spans="1:8">
-      <c r="A66" s="41" t="s">
+      <c r="H65" s="36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" ht="38.25" spans="1:8">
+      <c r="A66" s="38" t="s">
         <v>291</v>
       </c>
-      <c r="B66" s="41" t="s">
+      <c r="B66" s="38" t="s">
         <v>291</v>
       </c>
-      <c r="C66" s="41" t="s">
+      <c r="C66" s="38" t="s">
         <v>292</v>
       </c>
-      <c r="D66" s="41" t="b">
-        <v>0</v>
-      </c>
-      <c r="E66" s="41">
-        <v>0</v>
-      </c>
-      <c r="F66" s="42" t="s">
+      <c r="D66" s="38" t="b">
+        <v>0</v>
+      </c>
+      <c r="E66" s="38">
+        <v>0</v>
+      </c>
+      <c r="F66" s="39" t="s">
         <v>293</v>
       </c>
-      <c r="G66" s="41" t="s">
+      <c r="G66" s="38" t="s">
         <v>11</v>
       </c>
-      <c r="H66" s="41">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="67" ht="52" spans="1:8">
-      <c r="A67" s="39" t="s">
+      <c r="H66" s="38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" ht="51" spans="1:8">
+      <c r="A67" s="36" t="s">
         <v>294</v>
       </c>
-      <c r="B67" s="39" t="s">
+      <c r="B67" s="36" t="s">
         <v>294</v>
       </c>
-      <c r="C67" s="39" t="s">
+      <c r="C67" s="36" t="s">
         <v>295</v>
       </c>
-      <c r="D67" s="39" t="b">
-        <v>0</v>
-      </c>
-      <c r="E67" s="39">
-        <v>0</v>
-      </c>
-      <c r="F67" s="40" t="s">
+      <c r="D67" s="36" t="b">
+        <v>0</v>
+      </c>
+      <c r="E67" s="36">
+        <v>0</v>
+      </c>
+      <c r="F67" s="37" t="s">
         <v>296</v>
       </c>
-      <c r="G67" s="39" t="s">
+      <c r="G67" s="36" t="s">
         <v>11</v>
       </c>
-      <c r="H67" s="39">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="68" ht="47" spans="1:8">
-      <c r="A68" s="35" t="s">
+      <c r="H67" s="36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" ht="46.5" spans="1:8">
+      <c r="A68" s="32" t="s">
         <v>297</v>
       </c>
-      <c r="B68" s="35" t="s">
+      <c r="B68" s="32" t="s">
         <v>297</v>
       </c>
-      <c r="C68" s="35" t="s">
+      <c r="C68" s="32" t="s">
         <v>298</v>
       </c>
-      <c r="D68" s="35" t="b">
+      <c r="D68" s="32" t="b">
         <v>1</v>
       </c>
-      <c r="E68" s="35">
+      <c r="E68" s="32">
         <v>2</v>
       </c>
-      <c r="F68" s="36" t="s">
+      <c r="F68" s="33" t="s">
         <v>299</v>
       </c>
-      <c r="G68" s="35" t="s">
+      <c r="G68" s="32" t="s">
         <v>11</v>
       </c>
-      <c r="H68" s="35">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="69" ht="26" spans="1:8">
-      <c r="A69" s="37" t="s">
+      <c r="H68" s="32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" ht="25.5" spans="1:8">
+      <c r="A69" s="34" t="s">
         <v>300</v>
       </c>
-      <c r="B69" s="37" t="s">
+      <c r="B69" s="34" t="s">
         <v>300</v>
       </c>
-      <c r="C69" s="37" t="s">
+      <c r="C69" s="34" t="s">
         <v>301</v>
       </c>
-      <c r="D69" s="37" t="b">
-        <v>0</v>
-      </c>
-      <c r="E69" s="37">
-        <v>0</v>
-      </c>
-      <c r="F69" s="38" t="s">
+      <c r="D69" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="E69" s="34">
+        <v>0</v>
+      </c>
+      <c r="F69" s="35" t="s">
         <v>302</v>
       </c>
-      <c r="G69" s="37" t="s">
+      <c r="G69" s="34" t="s">
         <v>11</v>
       </c>
-      <c r="H69" s="37">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="70" ht="31" customHeight="1" spans="1:8">
-      <c r="A70" s="35" t="s">
+      <c r="H69" s="34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8">
+      <c r="A70" s="32" t="s">
+        <v>21</v>
+      </c>
+      <c r="B70" s="32" t="s">
+        <v>21</v>
+      </c>
+      <c r="C70" s="32" t="s">
+        <v>22</v>
+      </c>
+      <c r="D70" s="32" t="b">
+        <v>0</v>
+      </c>
+      <c r="E70" s="32">
+        <v>0</v>
+      </c>
+      <c r="F70" s="33" t="s">
+        <v>23</v>
+      </c>
+      <c r="G70" s="32" t="s">
+        <v>11</v>
+      </c>
+      <c r="H70" s="32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" ht="89.25" spans="1:8">
+      <c r="A71" s="34" t="s">
         <v>303</v>
       </c>
-      <c r="B70" s="35" t="s">
+      <c r="B71" s="34" t="s">
         <v>303</v>
       </c>
-      <c r="C70" s="35" t="s">
-        <v>22</v>
-      </c>
-      <c r="D70" s="35" t="b">
+      <c r="C71" s="34" t="s">
+        <v>304</v>
+      </c>
+      <c r="D71" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="E71" s="34">
+        <v>0</v>
+      </c>
+      <c r="F71" s="35" t="s">
+        <v>305</v>
+      </c>
+      <c r="G71" s="34" t="s">
+        <v>11</v>
+      </c>
+      <c r="H71" s="34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" ht="51" spans="1:8">
+      <c r="A72" s="32" t="s">
+        <v>306</v>
+      </c>
+      <c r="B72" s="32" t="s">
+        <v>306</v>
+      </c>
+      <c r="C72" s="32" t="s">
+        <v>307</v>
+      </c>
+      <c r="D72" s="32" t="b">
+        <v>0</v>
+      </c>
+      <c r="E72" s="32">
+        <v>0</v>
+      </c>
+      <c r="F72" s="33" t="s">
+        <v>308</v>
+      </c>
+      <c r="G72" s="32" t="s">
+        <v>11</v>
+      </c>
+      <c r="H72" s="32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8">
+      <c r="A73" s="34" t="s">
+        <v>309</v>
+      </c>
+      <c r="B73" s="34" t="s">
+        <v>309</v>
+      </c>
+      <c r="C73" s="34" t="s">
+        <v>310</v>
+      </c>
+      <c r="D73" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="E73" s="34">
+        <v>0</v>
+      </c>
+      <c r="F73" s="35" t="s">
+        <v>311</v>
+      </c>
+      <c r="G73" s="34" t="s">
+        <v>11</v>
+      </c>
+      <c r="H73" s="34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" ht="16.9" spans="1:8">
+      <c r="A74" s="32" t="s">
+        <v>312</v>
+      </c>
+      <c r="B74" s="32" t="s">
+        <v>312</v>
+      </c>
+      <c r="C74" s="32" t="s">
+        <v>313</v>
+      </c>
+      <c r="D74" s="32" t="b">
+        <v>0</v>
+      </c>
+      <c r="E74" s="32">
+        <v>0</v>
+      </c>
+      <c r="F74" s="33" t="s">
+        <v>314</v>
+      </c>
+      <c r="G74" s="32" t="s">
+        <v>11</v>
+      </c>
+      <c r="H74" s="32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8">
+      <c r="A75" s="34" t="s">
+        <v>315</v>
+      </c>
+      <c r="B75" s="34" t="s">
+        <v>315</v>
+      </c>
+      <c r="C75" s="34" t="s">
+        <v>316</v>
+      </c>
+      <c r="D75" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="E75" s="34">
+        <v>0</v>
+      </c>
+      <c r="F75" s="35" t="s">
+        <v>317</v>
+      </c>
+      <c r="G75" s="34" t="s">
+        <v>11</v>
+      </c>
+      <c r="H75" s="34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8">
+      <c r="A76" s="32" t="s">
+        <v>318</v>
+      </c>
+      <c r="B76" s="32" t="s">
+        <v>318</v>
+      </c>
+      <c r="C76" s="32" t="s">
+        <v>25</v>
+      </c>
+      <c r="D76" s="32" t="b">
+        <v>0</v>
+      </c>
+      <c r="E76" s="32">
+        <v>0</v>
+      </c>
+      <c r="F76" s="33" t="s">
+        <v>26</v>
+      </c>
+      <c r="G76" s="32" t="s">
+        <v>11</v>
+      </c>
+      <c r="H76" s="32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" ht="25.5" spans="1:8">
+      <c r="A77" s="34" t="s">
+        <v>319</v>
+      </c>
+      <c r="B77" s="34" t="s">
+        <v>319</v>
+      </c>
+      <c r="C77" s="34" t="s">
+        <v>320</v>
+      </c>
+      <c r="D77" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="E77" s="34">
+        <v>0</v>
+      </c>
+      <c r="F77" s="35" t="s">
+        <v>321</v>
+      </c>
+      <c r="G77" s="34" t="s">
+        <v>11</v>
+      </c>
+      <c r="H77" s="34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" ht="25.5" spans="1:8">
+      <c r="A78" s="32" t="s">
+        <v>322</v>
+      </c>
+      <c r="B78" s="32" t="s">
+        <v>322</v>
+      </c>
+      <c r="C78" s="32" t="s">
+        <v>323</v>
+      </c>
+      <c r="D78" s="32" t="b">
+        <v>0</v>
+      </c>
+      <c r="E78" s="32">
+        <v>0</v>
+      </c>
+      <c r="F78" s="33" t="s">
+        <v>324</v>
+      </c>
+      <c r="G78" s="32" t="s">
+        <v>11</v>
+      </c>
+      <c r="H78" s="32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" ht="63.75" spans="1:8">
+      <c r="A79" s="34" t="s">
+        <v>325</v>
+      </c>
+      <c r="B79" s="34" t="s">
+        <v>325</v>
+      </c>
+      <c r="C79" s="34" t="s">
+        <v>326</v>
+      </c>
+      <c r="D79" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="E79" s="34">
+        <v>0</v>
+      </c>
+      <c r="F79" s="35" t="s">
+        <v>327</v>
+      </c>
+      <c r="G79" s="34" t="s">
+        <v>11</v>
+      </c>
+      <c r="H79" s="34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" ht="25.5" spans="1:8">
+      <c r="A80" s="32" t="s">
+        <v>328</v>
+      </c>
+      <c r="B80" s="32" t="s">
+        <v>328</v>
+      </c>
+      <c r="C80" s="32" t="s">
+        <v>329</v>
+      </c>
+      <c r="D80" s="32" t="b">
+        <v>0</v>
+      </c>
+      <c r="E80" s="32">
+        <v>0</v>
+      </c>
+      <c r="F80" s="33" t="s">
+        <v>330</v>
+      </c>
+      <c r="G80" s="32" t="s">
+        <v>11</v>
+      </c>
+      <c r="H80" s="32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81" ht="25.5" spans="1:8">
+      <c r="A81" s="34" t="s">
+        <v>331</v>
+      </c>
+      <c r="B81" s="34" t="s">
+        <v>331</v>
+      </c>
+      <c r="C81" s="34" t="s">
+        <v>332</v>
+      </c>
+      <c r="D81" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="E81" s="34">
+        <v>0</v>
+      </c>
+      <c r="F81" s="35" t="s">
+        <v>333</v>
+      </c>
+      <c r="G81" s="34" t="s">
+        <v>11</v>
+      </c>
+      <c r="H81" s="34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" ht="25.5" spans="1:8">
+      <c r="A82" s="32" t="s">
+        <v>334</v>
+      </c>
+      <c r="B82" s="32" t="s">
+        <v>334</v>
+      </c>
+      <c r="C82" s="32" t="s">
+        <v>335</v>
+      </c>
+      <c r="D82" s="32" t="b">
+        <v>0</v>
+      </c>
+      <c r="E82" s="32">
+        <v>0</v>
+      </c>
+      <c r="F82" s="33" t="s">
+        <v>336</v>
+      </c>
+      <c r="G82" s="32" t="s">
+        <v>11</v>
+      </c>
+      <c r="H82" s="32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8">
+      <c r="A83" s="34" t="s">
+        <v>337</v>
+      </c>
+      <c r="B83" s="34" t="s">
+        <v>337</v>
+      </c>
+      <c r="C83" s="34" t="s">
+        <v>338</v>
+      </c>
+      <c r="D83" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="E83" s="34">
+        <v>0</v>
+      </c>
+      <c r="F83" s="35" t="s">
+        <v>287</v>
+      </c>
+      <c r="G83" s="34" t="s">
+        <v>11</v>
+      </c>
+      <c r="H83" s="34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8">
+      <c r="A84" s="32" t="s">
+        <v>339</v>
+      </c>
+      <c r="B84" s="32" t="s">
+        <v>339</v>
+      </c>
+      <c r="C84" s="32" t="s">
+        <v>340</v>
+      </c>
+      <c r="D84" s="32" t="b">
+        <v>0</v>
+      </c>
+      <c r="E84" s="32">
+        <v>0</v>
+      </c>
+      <c r="F84" s="33" t="s">
+        <v>341</v>
+      </c>
+      <c r="G84" s="32" t="s">
+        <v>11</v>
+      </c>
+      <c r="H84" s="32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" ht="25.5" spans="1:8">
+      <c r="A85" s="34" t="s">
+        <v>300</v>
+      </c>
+      <c r="B85" s="34" t="s">
+        <v>300</v>
+      </c>
+      <c r="C85" s="34" t="s">
+        <v>301</v>
+      </c>
+      <c r="D85" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="E85" s="34">
+        <v>0</v>
+      </c>
+      <c r="F85" s="35" t="s">
+        <v>302</v>
+      </c>
+      <c r="G85" s="34" t="s">
+        <v>11</v>
+      </c>
+      <c r="H85" s="34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" ht="63.75" spans="1:8">
+      <c r="A86" s="32" t="s">
+        <v>342</v>
+      </c>
+      <c r="B86" s="32" t="s">
+        <v>342</v>
+      </c>
+      <c r="C86" s="32" t="s">
+        <v>343</v>
+      </c>
+      <c r="D86" s="32" t="b">
+        <v>0</v>
+      </c>
+      <c r="E86" s="32">
+        <v>0</v>
+      </c>
+      <c r="F86" s="33" t="s">
+        <v>344</v>
+      </c>
+      <c r="G86" s="32" t="s">
+        <v>11</v>
+      </c>
+      <c r="H86" s="32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" ht="44" customHeight="1" spans="1:8">
+      <c r="A87" s="34" t="s">
+        <v>345</v>
+      </c>
+      <c r="B87" s="34" t="s">
+        <v>345</v>
+      </c>
+      <c r="C87" s="34" t="s">
+        <v>346</v>
+      </c>
+      <c r="D87" s="34" t="b">
         <v>1</v>
       </c>
-      <c r="E70" s="35">
+      <c r="E87" s="34">
         <v>1</v>
       </c>
-      <c r="F70" s="36" t="s">
-        <v>304</v>
-      </c>
-      <c r="G70" s="35" t="s">
+      <c r="F87" s="35" t="s">
+        <v>347</v>
+      </c>
+      <c r="G87" s="34" t="s">
         <v>11</v>
       </c>
-      <c r="H70" s="35">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="71" ht="91" spans="1:8">
-      <c r="A71" s="37" t="s">
-        <v>305</v>
-      </c>
-      <c r="B71" s="37" t="s">
-        <v>305</v>
-      </c>
-      <c r="C71" s="37" t="s">
-        <v>306</v>
-      </c>
-      <c r="D71" s="37" t="b">
-        <v>0</v>
-      </c>
-      <c r="E71" s="37">
-        <v>0</v>
-      </c>
-      <c r="F71" s="38" t="s">
-        <v>307</v>
-      </c>
-      <c r="G71" s="37" t="s">
+      <c r="H87" s="34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" ht="40" customHeight="1" spans="1:8">
+      <c r="A88" s="32" t="s">
+        <v>348</v>
+      </c>
+      <c r="B88" s="32" t="s">
+        <v>348</v>
+      </c>
+      <c r="C88" s="32" t="s">
+        <v>113</v>
+      </c>
+      <c r="D88" s="32" t="b">
+        <v>0</v>
+      </c>
+      <c r="E88" s="32">
+        <v>0</v>
+      </c>
+      <c r="F88" s="33" t="s">
+        <v>349</v>
+      </c>
+      <c r="G88" s="32" t="s">
         <v>11</v>
       </c>
-      <c r="H71" s="37">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="72" ht="39" spans="1:8">
-      <c r="A72" s="35" t="s">
-        <v>308</v>
-      </c>
-      <c r="B72" s="35" t="s">
-        <v>308</v>
-      </c>
-      <c r="C72" s="35" t="s">
-        <v>309</v>
-      </c>
-      <c r="D72" s="35" t="b">
-        <v>0</v>
-      </c>
-      <c r="E72" s="35">
-        <v>0</v>
-      </c>
-      <c r="F72" s="36" t="s">
-        <v>310</v>
-      </c>
-      <c r="G72" s="35" t="s">
-        <v>11</v>
-      </c>
-      <c r="H72" s="35">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="73" spans="1:8">
-      <c r="A73" s="37" t="s">
-        <v>311</v>
-      </c>
-      <c r="B73" s="37" t="s">
-        <v>311</v>
-      </c>
-      <c r="C73" s="37" t="s">
-        <v>312</v>
-      </c>
-      <c r="D73" s="37" t="b">
-        <v>0</v>
-      </c>
-      <c r="E73" s="37">
-        <v>0</v>
-      </c>
-      <c r="F73" s="38" t="s">
-        <v>313</v>
-      </c>
-      <c r="G73" s="37" t="s">
-        <v>11</v>
-      </c>
-      <c r="H73" s="37">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="74" ht="17" spans="1:8">
-      <c r="A74" s="35" t="s">
-        <v>314</v>
-      </c>
-      <c r="B74" s="35" t="s">
-        <v>314</v>
-      </c>
-      <c r="C74" s="35" t="s">
-        <v>315</v>
-      </c>
-      <c r="D74" s="35" t="b">
-        <v>1</v>
-      </c>
-      <c r="E74" s="35">
-        <v>1</v>
-      </c>
-      <c r="F74" s="36" t="s">
-        <v>316</v>
-      </c>
-      <c r="G74" s="35" t="s">
-        <v>11</v>
-      </c>
-      <c r="H74" s="35">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="75" spans="1:8">
-      <c r="A75" s="37" t="s">
-        <v>317</v>
-      </c>
-      <c r="B75" s="37" t="s">
-        <v>317</v>
-      </c>
-      <c r="C75" s="37" t="s">
-        <v>318</v>
-      </c>
-      <c r="D75" s="37" t="b">
-        <v>0</v>
-      </c>
-      <c r="E75" s="37">
-        <v>0</v>
-      </c>
-      <c r="F75" s="38" t="s">
-        <v>319</v>
-      </c>
-      <c r="G75" s="37" t="s">
-        <v>11</v>
-      </c>
-      <c r="H75" s="37">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="76" spans="1:8">
-      <c r="A76" s="35" t="s">
-        <v>320</v>
-      </c>
-      <c r="B76" s="35" t="s">
-        <v>320</v>
-      </c>
-      <c r="C76" s="35" t="s">
-        <v>25</v>
-      </c>
-      <c r="D76" s="35" t="b">
-        <v>0</v>
-      </c>
-      <c r="E76" s="35">
-        <v>0</v>
-      </c>
-      <c r="F76" s="36" t="s">
-        <v>26</v>
-      </c>
-      <c r="G76" s="35" t="s">
-        <v>11</v>
-      </c>
-      <c r="H76" s="35">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="77" ht="26" spans="1:8">
-      <c r="A77" s="37" t="s">
-        <v>321</v>
-      </c>
-      <c r="B77" s="37" t="s">
-        <v>321</v>
-      </c>
-      <c r="C77" s="37" t="s">
-        <v>322</v>
-      </c>
-      <c r="D77" s="37" t="b">
-        <v>0</v>
-      </c>
-      <c r="E77" s="37">
-        <v>0</v>
-      </c>
-      <c r="F77" s="38" t="s">
-        <v>323</v>
-      </c>
-      <c r="G77" s="37" t="s">
-        <v>11</v>
-      </c>
-      <c r="H77" s="37">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="78" ht="26" spans="1:8">
-      <c r="A78" s="35" t="s">
-        <v>324</v>
-      </c>
-      <c r="B78" s="35" t="s">
-        <v>324</v>
-      </c>
-      <c r="C78" s="35" t="s">
-        <v>325</v>
-      </c>
-      <c r="D78" s="35" t="b">
-        <v>0</v>
-      </c>
-      <c r="E78" s="35">
-        <v>0</v>
-      </c>
-      <c r="F78" s="36" t="s">
-        <v>326</v>
-      </c>
-      <c r="G78" s="35" t="s">
-        <v>11</v>
-      </c>
-      <c r="H78" s="35">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="79" ht="65" spans="1:8">
-      <c r="A79" s="37" t="s">
-        <v>327</v>
-      </c>
-      <c r="B79" s="37" t="s">
-        <v>327</v>
-      </c>
-      <c r="C79" s="37" t="s">
-        <v>328</v>
-      </c>
-      <c r="D79" s="37" t="b">
-        <v>0</v>
-      </c>
-      <c r="E79" s="37">
-        <v>0</v>
-      </c>
-      <c r="F79" s="38" t="s">
-        <v>329</v>
-      </c>
-      <c r="G79" s="37" t="s">
-        <v>11</v>
-      </c>
-      <c r="H79" s="37">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="80" ht="39" spans="1:8">
-      <c r="A80" s="35" t="s">
-        <v>330</v>
-      </c>
-      <c r="B80" s="35" t="s">
-        <v>330</v>
-      </c>
-      <c r="C80" s="35" t="s">
-        <v>331</v>
-      </c>
-      <c r="D80" s="35" t="b">
-        <v>0</v>
-      </c>
-      <c r="E80" s="35">
-        <v>0</v>
-      </c>
-      <c r="F80" s="36" t="s">
-        <v>332</v>
-      </c>
-      <c r="G80" s="35" t="s">
-        <v>11</v>
-      </c>
-      <c r="H80" s="35">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="81" ht="26" spans="1:8">
-      <c r="A81" s="37" t="s">
-        <v>333</v>
-      </c>
-      <c r="B81" s="37" t="s">
-        <v>333</v>
-      </c>
-      <c r="C81" s="37" t="s">
-        <v>334</v>
-      </c>
-      <c r="D81" s="37" t="b">
-        <v>0</v>
-      </c>
-      <c r="E81" s="37">
-        <v>0</v>
-      </c>
-      <c r="F81" s="38" t="s">
-        <v>335</v>
-      </c>
-      <c r="G81" s="37" t="s">
-        <v>11</v>
-      </c>
-      <c r="H81" s="37">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="82" ht="26" spans="1:8">
-      <c r="A82" s="35" t="s">
-        <v>336</v>
-      </c>
-      <c r="B82" s="35" t="s">
-        <v>336</v>
-      </c>
-      <c r="C82" s="35" t="s">
-        <v>337</v>
-      </c>
-      <c r="D82" s="35" t="b">
-        <v>0</v>
-      </c>
-      <c r="E82" s="35">
-        <v>0</v>
-      </c>
-      <c r="F82" s="36" t="s">
-        <v>338</v>
-      </c>
-      <c r="G82" s="35" t="s">
-        <v>11</v>
-      </c>
-      <c r="H82" s="35">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="83" spans="1:8">
-      <c r="A83" s="37" t="s">
-        <v>339</v>
-      </c>
-      <c r="B83" s="37" t="s">
-        <v>339</v>
-      </c>
-      <c r="C83" s="37" t="s">
-        <v>340</v>
-      </c>
-      <c r="D83" s="37" t="b">
-        <v>0</v>
-      </c>
-      <c r="E83" s="37">
-        <v>0</v>
-      </c>
-      <c r="F83" s="38" t="s">
-        <v>287</v>
-      </c>
-      <c r="G83" s="37" t="s">
-        <v>11</v>
-      </c>
-      <c r="H83" s="37">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="84" ht="26" spans="1:8">
-      <c r="A84" s="35" t="s">
-        <v>341</v>
-      </c>
-      <c r="B84" s="35" t="s">
-        <v>341</v>
-      </c>
-      <c r="C84" s="35" t="s">
-        <v>342</v>
-      </c>
-      <c r="D84" s="35" t="b">
-        <v>1</v>
-      </c>
-      <c r="E84" s="35">
-        <v>1</v>
-      </c>
-      <c r="F84" s="36" t="s">
-        <v>343</v>
-      </c>
-      <c r="G84" s="35" t="s">
-        <v>11</v>
-      </c>
-      <c r="H84" s="35">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="85" ht="78" spans="1:8">
-      <c r="A85" s="35" t="s">
-        <v>344</v>
-      </c>
-      <c r="B85" s="35" t="s">
-        <v>344</v>
-      </c>
-      <c r="C85" s="35" t="s">
-        <v>345</v>
-      </c>
-      <c r="D85" s="35" t="b">
-        <v>0</v>
-      </c>
-      <c r="E85" s="35">
-        <v>0</v>
-      </c>
-      <c r="F85" s="36" t="s">
-        <v>346</v>
-      </c>
-      <c r="G85" s="35" t="s">
-        <v>11</v>
-      </c>
-      <c r="H85" s="35">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="86" ht="44" customHeight="1" spans="1:8">
-      <c r="A86" s="37" t="s">
-        <v>347</v>
-      </c>
-      <c r="B86" s="37" t="s">
-        <v>347</v>
-      </c>
-      <c r="C86" s="37" t="s">
-        <v>348</v>
-      </c>
-      <c r="D86" s="37" t="b">
-        <v>1</v>
-      </c>
-      <c r="E86" s="37">
-        <v>1</v>
-      </c>
-      <c r="F86" s="38" t="s">
-        <v>349</v>
-      </c>
-      <c r="G86" s="37" t="s">
-        <v>11</v>
-      </c>
-      <c r="H86" s="37">
+      <c r="H88" s="32">
         <v>0</v>
       </c>
     </row>
@@ -7940,16 +7771,16 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:G56"/>
-  <sheetFormatPr defaultColWidth="8.25" defaultRowHeight="14" outlineLevelCol="6"/>
+  <sheetFormatPr defaultColWidth="8.24778761061947" defaultRowHeight="13.85" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="20.75" style="10" customWidth="1"/>
-    <col min="2" max="2" width="18.1416666666667" style="10" customWidth="1"/>
-    <col min="3" max="3" width="14.3666666666667" style="10" customWidth="1"/>
-    <col min="4" max="4" width="47.4666666666667" style="10" hidden="1" customWidth="1"/>
-    <col min="5" max="5" width="8.25" style="10"/>
-    <col min="6" max="6" width="104.891666666667" style="10" customWidth="1"/>
-    <col min="7" max="7" width="26.6583333333333" style="10" customWidth="1"/>
-    <col min="8" max="16384" width="8.25" style="10"/>
+    <col min="1" max="1" width="20.7522123893805" style="10" customWidth="1"/>
+    <col min="2" max="2" width="18.141592920354" style="10" customWidth="1"/>
+    <col min="3" max="3" width="14.3628318584071" style="10" customWidth="1"/>
+    <col min="4" max="4" width="47.4690265486726" style="10" hidden="1" customWidth="1"/>
+    <col min="5" max="5" width="8.24778761061947" style="10"/>
+    <col min="6" max="6" width="104.893805309735" style="10" customWidth="1"/>
+    <col min="7" max="7" width="26.6548672566372" style="10" customWidth="1"/>
+    <col min="8" max="16384" width="8.24778761061947" style="10"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
@@ -8048,806 +7879,806 @@
       <c r="A5" s="18" t="s">
         <v>367</v>
       </c>
-      <c r="B5" s="18" t="s">
+      <c r="B5" s="19" t="s">
         <v>367</v>
       </c>
       <c r="C5" s="20" t="s">
         <v>368</v>
       </c>
-      <c r="D5" s="20" t="s">
+      <c r="D5" s="20"/>
+      <c r="E5" s="20">
+        <v>3</v>
+      </c>
+      <c r="F5" s="21" t="s">
         <v>369</v>
       </c>
-      <c r="E5" s="20">
+      <c r="G5" s="21" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6" s="18" t="s">
+        <v>370</v>
+      </c>
+      <c r="B6" s="19" t="s">
+        <v>370</v>
+      </c>
+      <c r="C6" s="20" t="s">
+        <v>371</v>
+      </c>
+      <c r="D6" s="20" t="s">
+        <v>372</v>
+      </c>
+      <c r="E6" s="20">
         <v>10</v>
       </c>
-      <c r="F5" s="21" t="s">
-        <v>370</v>
-      </c>
-      <c r="G5" s="21" t="s">
+      <c r="F6" s="21" t="s">
+        <v>373</v>
+      </c>
+      <c r="G6" s="21" t="s">
         <v>357</v>
       </c>
     </row>
-    <row r="6" spans="1:7">
-      <c r="A6" s="14" t="s">
-        <v>371</v>
-      </c>
-      <c r="B6" s="15" t="s">
-        <v>371</v>
-      </c>
-      <c r="C6" s="16" t="s">
-        <v>372</v>
-      </c>
-      <c r="D6" s="16" t="s">
-        <v>373</v>
-      </c>
-      <c r="E6" s="16">
+    <row r="7" spans="1:7">
+      <c r="A7" s="14" t="s">
+        <v>374</v>
+      </c>
+      <c r="B7" s="15" t="s">
+        <v>374</v>
+      </c>
+      <c r="C7" s="16" t="s">
+        <v>375</v>
+      </c>
+      <c r="D7" s="16" t="s">
+        <v>376</v>
+      </c>
+      <c r="E7" s="16">
         <v>25</v>
       </c>
-      <c r="F6" s="17" t="s">
-        <v>374</v>
-      </c>
-      <c r="G6" s="17" t="s">
+      <c r="F7" s="17" t="s">
+        <v>377</v>
+      </c>
+      <c r="G7" s="17" t="s">
         <v>357</v>
       </c>
     </row>
-    <row r="7" spans="1:7">
-      <c r="A7" s="18" t="s">
-        <v>375</v>
-      </c>
-      <c r="B7" s="19" t="s">
-        <v>375</v>
-      </c>
-      <c r="C7" s="20" t="s">
-        <v>376</v>
-      </c>
-      <c r="D7" s="20" t="s">
-        <v>377</v>
-      </c>
-      <c r="E7" s="20">
+    <row r="8" spans="1:7">
+      <c r="A8" s="18" t="s">
+        <v>378</v>
+      </c>
+      <c r="B8" s="19" t="s">
+        <v>378</v>
+      </c>
+      <c r="C8" s="20" t="s">
+        <v>379</v>
+      </c>
+      <c r="D8" s="20" t="s">
+        <v>380</v>
+      </c>
+      <c r="E8" s="20">
         <v>35</v>
       </c>
-      <c r="F7" s="21" t="s">
-        <v>378</v>
-      </c>
-      <c r="G7" s="21" t="s">
+      <c r="F8" s="21" t="s">
+        <v>381</v>
+      </c>
+      <c r="G8" s="21" t="s">
         <v>357</v>
       </c>
     </row>
-    <row r="8" spans="1:7">
-      <c r="A8" s="22" t="s">
-        <v>379</v>
-      </c>
-      <c r="B8" s="22" t="s">
-        <v>379</v>
-      </c>
-      <c r="C8" s="23" t="s">
-        <v>380</v>
-      </c>
-      <c r="D8" s="23"/>
-      <c r="E8" s="23">
-        <v>3</v>
-      </c>
-      <c r="F8" s="24" t="s">
-        <v>381</v>
-      </c>
-      <c r="G8" s="24" t="s">
+    <row r="9" spans="1:7">
+      <c r="A9" s="22" t="s">
+        <v>382</v>
+      </c>
+      <c r="B9" s="23" t="s">
+        <v>382</v>
+      </c>
+      <c r="C9" s="24" t="s">
+        <v>383</v>
+      </c>
+      <c r="D9" s="24" t="s">
+        <v>384</v>
+      </c>
+      <c r="E9" s="24">
+        <v>50</v>
+      </c>
+      <c r="F9" s="25" t="s">
+        <v>385</v>
+      </c>
+      <c r="G9" s="25" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10" s="26" t="s">
+        <v>386</v>
+      </c>
+      <c r="B10" s="27" t="s">
+        <v>386</v>
+      </c>
+      <c r="C10" s="28" t="s">
+        <v>387</v>
+      </c>
+      <c r="D10" s="28" t="s">
+        <v>388</v>
+      </c>
+      <c r="E10" s="28">
+        <v>55</v>
+      </c>
+      <c r="F10" s="29" t="s">
+        <v>389</v>
+      </c>
+      <c r="G10" s="29" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11" s="22" t="s">
+        <v>390</v>
+      </c>
+      <c r="B11" s="23" t="s">
+        <v>390</v>
+      </c>
+      <c r="C11" s="24" t="s">
+        <v>391</v>
+      </c>
+      <c r="D11" s="24" t="s">
+        <v>392</v>
+      </c>
+      <c r="E11" s="24">
+        <v>35</v>
+      </c>
+      <c r="F11" s="25" t="s">
+        <v>393</v>
+      </c>
+      <c r="G11" s="25" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12" s="26" t="s">
+        <v>394</v>
+      </c>
+      <c r="B12" s="27" t="s">
+        <v>394</v>
+      </c>
+      <c r="C12" s="28" t="s">
+        <v>395</v>
+      </c>
+      <c r="D12" s="28" t="s">
+        <v>396</v>
+      </c>
+      <c r="E12" s="28">
+        <v>30</v>
+      </c>
+      <c r="F12" s="29" t="s">
+        <v>397</v>
+      </c>
+      <c r="G12" s="29" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13" s="22" t="s">
+        <v>398</v>
+      </c>
+      <c r="B13" s="23" t="s">
+        <v>398</v>
+      </c>
+      <c r="C13" s="24" t="s">
+        <v>399</v>
+      </c>
+      <c r="D13" s="24" t="s">
+        <v>400</v>
+      </c>
+      <c r="E13" s="24">
+        <v>40</v>
+      </c>
+      <c r="F13" s="25" t="s">
+        <v>401</v>
+      </c>
+      <c r="G13" s="25" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14" s="26" t="s">
+        <v>402</v>
+      </c>
+      <c r="B14" s="27" t="s">
+        <v>402</v>
+      </c>
+      <c r="C14" s="28" t="s">
+        <v>403</v>
+      </c>
+      <c r="D14" s="28" t="s">
+        <v>404</v>
+      </c>
+      <c r="E14" s="28">
+        <v>4</v>
+      </c>
+      <c r="F14" s="29" t="s">
+        <v>405</v>
+      </c>
+      <c r="G14" s="29" t="s">
         <v>362</v>
       </c>
     </row>
-    <row r="9" spans="1:7">
-      <c r="A9" s="25" t="s">
-        <v>382</v>
-      </c>
-      <c r="B9" s="26" t="s">
-        <v>382</v>
-      </c>
-      <c r="C9" s="27" t="s">
-        <v>383</v>
-      </c>
-      <c r="D9" s="27" t="s">
-        <v>384</v>
-      </c>
-      <c r="E9" s="27">
+    <row r="15" spans="1:7">
+      <c r="A15" s="22" t="s">
+        <v>406</v>
+      </c>
+      <c r="B15" s="23" t="s">
+        <v>406</v>
+      </c>
+      <c r="C15" s="24" t="s">
+        <v>407</v>
+      </c>
+      <c r="D15" s="24" t="s">
+        <v>408</v>
+      </c>
+      <c r="E15" s="24">
+        <v>30</v>
+      </c>
+      <c r="F15" s="25" t="s">
+        <v>409</v>
+      </c>
+      <c r="G15" s="25" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16" s="26" t="s">
+        <v>410</v>
+      </c>
+      <c r="B16" s="27" t="s">
+        <v>410</v>
+      </c>
+      <c r="C16" s="28" t="s">
+        <v>411</v>
+      </c>
+      <c r="D16" s="28" t="s">
+        <v>412</v>
+      </c>
+      <c r="E16" s="28">
+        <v>70</v>
+      </c>
+      <c r="F16" s="29" t="s">
+        <v>413</v>
+      </c>
+      <c r="G16" s="29" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17" s="22" t="s">
+        <v>414</v>
+      </c>
+      <c r="B17" s="23" t="s">
+        <v>414</v>
+      </c>
+      <c r="C17" s="24" t="s">
+        <v>415</v>
+      </c>
+      <c r="D17" s="24" t="s">
+        <v>416</v>
+      </c>
+      <c r="E17" s="24">
+        <v>60</v>
+      </c>
+      <c r="F17" s="25" t="s">
+        <v>417</v>
+      </c>
+      <c r="G17" s="25" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18" s="26" t="s">
+        <v>418</v>
+      </c>
+      <c r="B18" s="27" t="s">
+        <v>418</v>
+      </c>
+      <c r="C18" s="28" t="s">
+        <v>419</v>
+      </c>
+      <c r="D18" s="28" t="s">
+        <v>420</v>
+      </c>
+      <c r="E18" s="28">
+        <v>30</v>
+      </c>
+      <c r="F18" s="29" t="s">
+        <v>421</v>
+      </c>
+      <c r="G18" s="29" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19" s="22" t="s">
+        <v>422</v>
+      </c>
+      <c r="B19" s="23" t="s">
+        <v>422</v>
+      </c>
+      <c r="C19" s="24" t="s">
+        <v>423</v>
+      </c>
+      <c r="D19" s="24" t="s">
+        <v>424</v>
+      </c>
+      <c r="E19" s="24">
+        <v>30</v>
+      </c>
+      <c r="F19" s="25" t="s">
+        <v>425</v>
+      </c>
+      <c r="G19" s="25" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20" s="26" t="s">
+        <v>426</v>
+      </c>
+      <c r="B20" s="27" t="s">
+        <v>426</v>
+      </c>
+      <c r="C20" s="28" t="s">
+        <v>427</v>
+      </c>
+      <c r="D20" s="28" t="s">
+        <v>428</v>
+      </c>
+      <c r="E20" s="28">
+        <v>30</v>
+      </c>
+      <c r="F20" s="29" t="s">
+        <v>429</v>
+      </c>
+      <c r="G20" s="29" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
+      <c r="A21" s="22" t="s">
+        <v>430</v>
+      </c>
+      <c r="B21" s="23" t="s">
+        <v>430</v>
+      </c>
+      <c r="C21" s="24" t="s">
+        <v>431</v>
+      </c>
+      <c r="D21" s="24" t="s">
+        <v>432</v>
+      </c>
+      <c r="E21" s="24">
+        <v>20</v>
+      </c>
+      <c r="F21" s="25" t="s">
+        <v>433</v>
+      </c>
+      <c r="G21" s="25" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
+      <c r="A22" s="26" t="s">
+        <v>434</v>
+      </c>
+      <c r="B22" s="27" t="s">
+        <v>434</v>
+      </c>
+      <c r="C22" s="28" t="s">
+        <v>435</v>
+      </c>
+      <c r="D22" s="28" t="s">
+        <v>436</v>
+      </c>
+      <c r="E22" s="28">
+        <v>100</v>
+      </c>
+      <c r="F22" s="29" t="s">
+        <v>437</v>
+      </c>
+      <c r="G22" s="29" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7">
+      <c r="A23" s="22" t="s">
+        <v>438</v>
+      </c>
+      <c r="B23" s="23" t="s">
+        <v>438</v>
+      </c>
+      <c r="C23" s="24" t="s">
+        <v>439</v>
+      </c>
+      <c r="D23" s="24" t="s">
+        <v>440</v>
+      </c>
+      <c r="E23" s="24">
+        <v>10</v>
+      </c>
+      <c r="F23" s="25" t="s">
+        <v>441</v>
+      </c>
+      <c r="G23" s="25" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7">
+      <c r="A24" s="26" t="s">
+        <v>442</v>
+      </c>
+      <c r="B24" s="27" t="s">
+        <v>442</v>
+      </c>
+      <c r="C24" s="28" t="s">
+        <v>443</v>
+      </c>
+      <c r="D24" s="28" t="s">
+        <v>444</v>
+      </c>
+      <c r="E24" s="28">
+        <v>20</v>
+      </c>
+      <c r="F24" s="29" t="s">
+        <v>445</v>
+      </c>
+      <c r="G24" s="29" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7">
+      <c r="A25" s="22" t="s">
+        <v>447</v>
+      </c>
+      <c r="B25" s="23" t="s">
+        <v>447</v>
+      </c>
+      <c r="C25" s="24" t="s">
+        <v>448</v>
+      </c>
+      <c r="D25" s="24" t="s">
+        <v>449</v>
+      </c>
+      <c r="E25" s="24">
+        <v>20</v>
+      </c>
+      <c r="F25" s="25" t="s">
+        <v>450</v>
+      </c>
+      <c r="G25" s="25" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="26" ht="24.75" spans="1:7">
+      <c r="A26" s="26" t="s">
+        <v>451</v>
+      </c>
+      <c r="B26" s="27" t="s">
+        <v>451</v>
+      </c>
+      <c r="C26" s="28" t="s">
+        <v>452</v>
+      </c>
+      <c r="D26" s="28" t="s">
+        <v>453</v>
+      </c>
+      <c r="E26" s="28">
+        <v>35</v>
+      </c>
+      <c r="F26" s="29" t="s">
+        <v>454</v>
+      </c>
+      <c r="G26" s="29" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7">
+      <c r="A27" s="22" t="s">
+        <v>455</v>
+      </c>
+      <c r="B27" s="23" t="s">
+        <v>455</v>
+      </c>
+      <c r="C27" s="24" t="s">
+        <v>456</v>
+      </c>
+      <c r="D27" s="24" t="s">
+        <v>457</v>
+      </c>
+      <c r="E27" s="24">
         <v>50</v>
       </c>
-      <c r="F9" s="28" t="s">
-        <v>385</v>
-      </c>
-      <c r="G9" s="28" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10" s="29" t="s">
-        <v>386</v>
-      </c>
-      <c r="B10" s="30" t="s">
-        <v>386</v>
-      </c>
-      <c r="C10" s="31" t="s">
-        <v>387</v>
-      </c>
-      <c r="D10" s="31" t="s">
-        <v>388</v>
-      </c>
-      <c r="E10" s="31">
-        <v>55</v>
-      </c>
-      <c r="F10" s="32" t="s">
-        <v>389</v>
-      </c>
-      <c r="G10" s="32" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="11" ht="17" spans="1:7">
-      <c r="A11" s="25" t="s">
-        <v>390</v>
-      </c>
-      <c r="B11" s="26" t="s">
-        <v>390</v>
-      </c>
-      <c r="C11" s="27" t="s">
-        <v>391</v>
-      </c>
-      <c r="D11" s="27" t="s">
-        <v>392</v>
-      </c>
-      <c r="E11" s="27">
-        <v>35</v>
-      </c>
-      <c r="F11" s="28" t="s">
-        <v>393</v>
-      </c>
-      <c r="G11" s="28" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12" s="29" t="s">
-        <v>394</v>
-      </c>
-      <c r="B12" s="30" t="s">
-        <v>394</v>
-      </c>
-      <c r="C12" s="31" t="s">
-        <v>395</v>
-      </c>
-      <c r="D12" s="31" t="s">
-        <v>396</v>
-      </c>
-      <c r="E12" s="31">
-        <v>30</v>
-      </c>
-      <c r="F12" s="32" t="s">
-        <v>397</v>
-      </c>
-      <c r="G12" s="32" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13" s="25" t="s">
-        <v>398</v>
-      </c>
-      <c r="B13" s="26" t="s">
-        <v>398</v>
-      </c>
-      <c r="C13" s="27" t="s">
-        <v>399</v>
-      </c>
-      <c r="D13" s="27" t="s">
-        <v>400</v>
-      </c>
-      <c r="E13" s="27">
-        <v>40</v>
-      </c>
-      <c r="F13" s="28" t="s">
-        <v>401</v>
-      </c>
-      <c r="G13" s="28" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14" s="29" t="s">
-        <v>402</v>
-      </c>
-      <c r="B14" s="30" t="s">
-        <v>402</v>
-      </c>
-      <c r="C14" s="31" t="s">
-        <v>403</v>
-      </c>
-      <c r="D14" s="31" t="s">
-        <v>404</v>
-      </c>
-      <c r="E14" s="31">
-        <v>4</v>
-      </c>
-      <c r="F14" s="32" t="s">
-        <v>405</v>
-      </c>
-      <c r="G14" s="32" t="s">
+      <c r="F27" s="25" t="s">
+        <v>458</v>
+      </c>
+      <c r="G27" s="25" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7">
+      <c r="A28" s="26" t="s">
+        <v>459</v>
+      </c>
+      <c r="B28" s="27" t="s">
+        <v>459</v>
+      </c>
+      <c r="C28" s="28" t="s">
+        <v>460</v>
+      </c>
+      <c r="D28" s="28" t="s">
+        <v>461</v>
+      </c>
+      <c r="E28" s="28">
+        <v>20</v>
+      </c>
+      <c r="F28" s="29" t="s">
+        <v>462</v>
+      </c>
+      <c r="G28" s="29" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7">
+      <c r="A29" s="22" t="s">
+        <v>463</v>
+      </c>
+      <c r="B29" s="23" t="s">
+        <v>463</v>
+      </c>
+      <c r="C29" s="24" t="s">
+        <v>464</v>
+      </c>
+      <c r="D29" s="24" t="s">
+        <v>465</v>
+      </c>
+      <c r="E29" s="24">
+        <v>5</v>
+      </c>
+      <c r="F29" s="25" t="s">
+        <v>466</v>
+      </c>
+      <c r="G29" s="25" t="s">
         <v>362</v>
       </c>
     </row>
-    <row r="15" spans="1:7">
-      <c r="A15" s="25" t="s">
-        <v>406</v>
-      </c>
-      <c r="B15" s="26" t="s">
-        <v>406</v>
-      </c>
-      <c r="C15" s="27" t="s">
-        <v>407</v>
-      </c>
-      <c r="D15" s="27" t="s">
-        <v>408</v>
-      </c>
-      <c r="E15" s="27">
-        <v>30</v>
-      </c>
-      <c r="F15" s="28" t="s">
-        <v>409</v>
-      </c>
-      <c r="G15" s="28" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16" s="29" t="s">
-        <v>410</v>
-      </c>
-      <c r="B16" s="30" t="s">
-        <v>410</v>
-      </c>
-      <c r="C16" s="31" t="s">
-        <v>411</v>
-      </c>
-      <c r="D16" s="31" t="s">
-        <v>412</v>
-      </c>
-      <c r="E16" s="31">
-        <v>70</v>
-      </c>
-      <c r="F16" s="32" t="s">
-        <v>413</v>
-      </c>
-      <c r="G16" s="32" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17" s="25" t="s">
-        <v>414</v>
-      </c>
-      <c r="B17" s="26" t="s">
-        <v>414</v>
-      </c>
-      <c r="C17" s="27" t="s">
-        <v>415</v>
-      </c>
-      <c r="D17" s="27" t="s">
-        <v>416</v>
-      </c>
-      <c r="E17" s="27">
-        <v>60</v>
-      </c>
-      <c r="F17" s="28" t="s">
-        <v>417</v>
-      </c>
-      <c r="G17" s="28" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18" s="29" t="s">
-        <v>418</v>
-      </c>
-      <c r="B18" s="30" t="s">
-        <v>418</v>
-      </c>
-      <c r="C18" s="31" t="s">
-        <v>419</v>
-      </c>
-      <c r="D18" s="31" t="s">
-        <v>420</v>
-      </c>
-      <c r="E18" s="31">
-        <v>30</v>
-      </c>
-      <c r="F18" s="32" t="s">
-        <v>421</v>
-      </c>
-      <c r="G18" s="32" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19" s="25" t="s">
-        <v>422</v>
-      </c>
-      <c r="B19" s="26" t="s">
-        <v>422</v>
-      </c>
-      <c r="C19" s="27" t="s">
-        <v>423</v>
-      </c>
-      <c r="D19" s="27" t="s">
-        <v>424</v>
-      </c>
-      <c r="E19" s="27">
-        <v>30</v>
-      </c>
-      <c r="F19" s="28" t="s">
-        <v>425</v>
-      </c>
-      <c r="G19" s="28" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
-      <c r="A20" s="29" t="s">
-        <v>426</v>
-      </c>
-      <c r="B20" s="30" t="s">
-        <v>426</v>
-      </c>
-      <c r="C20" s="31" t="s">
-        <v>427</v>
-      </c>
-      <c r="D20" s="31" t="s">
-        <v>428</v>
-      </c>
-      <c r="E20" s="31">
-        <v>30</v>
-      </c>
-      <c r="F20" s="32" t="s">
-        <v>429</v>
-      </c>
-      <c r="G20" s="32" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="21" ht="17" spans="1:7">
-      <c r="A21" s="25" t="s">
-        <v>430</v>
-      </c>
-      <c r="B21" s="26" t="s">
-        <v>430</v>
-      </c>
-      <c r="C21" s="27" t="s">
-        <v>431</v>
-      </c>
-      <c r="D21" s="27" t="s">
-        <v>432</v>
-      </c>
-      <c r="E21" s="27">
+    <row r="30" spans="1:7">
+      <c r="A30" s="26" t="s">
+        <v>467</v>
+      </c>
+      <c r="B30" s="27" t="s">
+        <v>467</v>
+      </c>
+      <c r="C30" s="28" t="s">
+        <v>468</v>
+      </c>
+      <c r="D30" s="28" t="s">
+        <v>469</v>
+      </c>
+      <c r="E30" s="28">
         <v>20</v>
       </c>
-      <c r="F21" s="28" t="s">
-        <v>433</v>
-      </c>
-      <c r="G21" s="28" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7">
-      <c r="A22" s="29" t="s">
-        <v>434</v>
-      </c>
-      <c r="B22" s="30" t="s">
-        <v>434</v>
-      </c>
-      <c r="C22" s="31" t="s">
-        <v>435</v>
-      </c>
-      <c r="D22" s="31" t="s">
-        <v>436</v>
-      </c>
-      <c r="E22" s="31">
+      <c r="F30" s="29" t="s">
+        <v>470</v>
+      </c>
+      <c r="G30" s="29" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7">
+      <c r="A31" s="22" t="s">
+        <v>471</v>
+      </c>
+      <c r="B31" s="23" t="s">
+        <v>471</v>
+      </c>
+      <c r="C31" s="24" t="s">
+        <v>472</v>
+      </c>
+      <c r="D31" s="24" t="s">
+        <v>473</v>
+      </c>
+      <c r="E31" s="24">
+        <v>15</v>
+      </c>
+      <c r="F31" s="25" t="s">
+        <v>474</v>
+      </c>
+      <c r="G31" s="25" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7">
+      <c r="A32" s="26" t="s">
+        <v>475</v>
+      </c>
+      <c r="B32" s="27" t="s">
+        <v>475</v>
+      </c>
+      <c r="C32" s="28" t="s">
+        <v>476</v>
+      </c>
+      <c r="D32" s="28" t="s">
+        <v>477</v>
+      </c>
+      <c r="E32" s="28">
+        <v>15</v>
+      </c>
+      <c r="F32" s="29" t="s">
+        <v>478</v>
+      </c>
+      <c r="G32" s="29" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7">
+      <c r="A33" s="22" t="s">
+        <v>479</v>
+      </c>
+      <c r="B33" s="23" t="s">
+        <v>479</v>
+      </c>
+      <c r="C33" s="24" t="s">
+        <v>480</v>
+      </c>
+      <c r="D33" s="24" t="s">
+        <v>481</v>
+      </c>
+      <c r="E33" s="24">
+        <v>15</v>
+      </c>
+      <c r="F33" s="25" t="s">
+        <v>482</v>
+      </c>
+      <c r="G33" s="25" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7">
+      <c r="A34" s="26" t="s">
+        <v>483</v>
+      </c>
+      <c r="B34" s="27" t="s">
+        <v>483</v>
+      </c>
+      <c r="C34" s="28" t="s">
+        <v>484</v>
+      </c>
+      <c r="D34" s="28" t="s">
+        <v>485</v>
+      </c>
+      <c r="E34" s="28">
+        <v>5</v>
+      </c>
+      <c r="F34" s="29" t="s">
+        <v>486</v>
+      </c>
+      <c r="G34" s="29" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7">
+      <c r="A35" s="22" t="s">
+        <v>487</v>
+      </c>
+      <c r="B35" s="23" t="s">
+        <v>487</v>
+      </c>
+      <c r="C35" s="24" t="s">
+        <v>488</v>
+      </c>
+      <c r="D35" s="24" t="s">
+        <v>489</v>
+      </c>
+      <c r="E35" s="24">
+        <v>25</v>
+      </c>
+      <c r="F35" s="25" t="s">
+        <v>490</v>
+      </c>
+      <c r="G35" s="25" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7">
+      <c r="A36" s="26" t="s">
+        <v>491</v>
+      </c>
+      <c r="B36" s="27" t="s">
+        <v>491</v>
+      </c>
+      <c r="C36" s="28" t="s">
+        <v>492</v>
+      </c>
+      <c r="D36" s="28" t="s">
+        <v>493</v>
+      </c>
+      <c r="E36" s="28">
+        <v>10</v>
+      </c>
+      <c r="F36" s="29" t="s">
+        <v>494</v>
+      </c>
+      <c r="G36" s="29" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7">
+      <c r="A37" s="22" t="s">
+        <v>495</v>
+      </c>
+      <c r="B37" s="23" t="s">
+        <v>495</v>
+      </c>
+      <c r="C37" s="24" t="s">
+        <v>496</v>
+      </c>
+      <c r="D37" s="24" t="s">
+        <v>497</v>
+      </c>
+      <c r="E37" s="24">
+        <v>8</v>
+      </c>
+      <c r="F37" s="25" t="s">
+        <v>498</v>
+      </c>
+      <c r="G37" s="25" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7">
+      <c r="A38" s="26" t="s">
+        <v>499</v>
+      </c>
+      <c r="B38" s="27" t="s">
+        <v>499</v>
+      </c>
+      <c r="C38" s="28" t="s">
+        <v>500</v>
+      </c>
+      <c r="D38" s="28" t="s">
+        <v>501</v>
+      </c>
+      <c r="E38" s="28">
         <v>100</v>
       </c>
-      <c r="F22" s="32" t="s">
-        <v>437</v>
-      </c>
-      <c r="G22" s="32" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7">
-      <c r="A23" s="25" t="s">
-        <v>438</v>
-      </c>
-      <c r="B23" s="26" t="s">
-        <v>438</v>
-      </c>
-      <c r="C23" s="27" t="s">
-        <v>439</v>
-      </c>
-      <c r="D23" s="27" t="s">
-        <v>440</v>
-      </c>
-      <c r="E23" s="27">
-        <v>10</v>
-      </c>
-      <c r="F23" s="28" t="s">
-        <v>441</v>
-      </c>
-      <c r="G23" s="28" t="s">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7">
-      <c r="A24" s="29" t="s">
-        <v>442</v>
-      </c>
-      <c r="B24" s="30" t="s">
-        <v>442</v>
-      </c>
-      <c r="C24" s="31" t="s">
-        <v>443</v>
-      </c>
-      <c r="D24" s="31" t="s">
-        <v>444</v>
-      </c>
-      <c r="E24" s="31">
+      <c r="F38" s="29" t="s">
+        <v>502</v>
+      </c>
+      <c r="G38" s="29" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7">
+      <c r="A39" s="22" t="s">
+        <v>503</v>
+      </c>
+      <c r="B39" s="23" t="s">
+        <v>503</v>
+      </c>
+      <c r="C39" s="24" t="s">
+        <v>504</v>
+      </c>
+      <c r="D39" s="24" t="s">
+        <v>505</v>
+      </c>
+      <c r="E39" s="24">
         <v>20</v>
       </c>
-      <c r="F24" s="32" t="s">
-        <v>445</v>
-      </c>
-      <c r="G24" s="32" t="s">
+      <c r="F39" s="25" t="s">
+        <v>506</v>
+      </c>
+      <c r="G39" s="25" t="s">
         <v>446</v>
       </c>
     </row>
-    <row r="25" spans="1:7">
-      <c r="A25" s="25" t="s">
-        <v>447</v>
-      </c>
-      <c r="B25" s="26" t="s">
-        <v>447</v>
-      </c>
-      <c r="C25" s="27" t="s">
-        <v>448</v>
-      </c>
-      <c r="D25" s="27" t="s">
-        <v>449</v>
-      </c>
-      <c r="E25" s="27">
-        <v>20</v>
-      </c>
-      <c r="F25" s="28" t="s">
-        <v>450</v>
-      </c>
-      <c r="G25" s="28" t="s">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7">
-      <c r="A26" s="29" t="s">
-        <v>451</v>
-      </c>
-      <c r="B26" s="30" t="s">
-        <v>451</v>
-      </c>
-      <c r="C26" s="31" t="s">
-        <v>452</v>
-      </c>
-      <c r="D26" s="31" t="s">
-        <v>453</v>
-      </c>
-      <c r="E26" s="31">
-        <v>35</v>
-      </c>
-      <c r="F26" s="32" t="s">
-        <v>454</v>
-      </c>
-      <c r="G26" s="32" t="s">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7">
-      <c r="A27" s="25" t="s">
-        <v>455</v>
-      </c>
-      <c r="B27" s="26" t="s">
-        <v>455</v>
-      </c>
-      <c r="C27" s="27" t="s">
-        <v>456</v>
-      </c>
-      <c r="D27" s="27" t="s">
-        <v>457</v>
-      </c>
-      <c r="E27" s="27">
-        <v>50</v>
-      </c>
-      <c r="F27" s="28" t="s">
-        <v>458</v>
-      </c>
-      <c r="G27" s="28" t="s">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7">
-      <c r="A28" s="29" t="s">
-        <v>459</v>
-      </c>
-      <c r="B28" s="30" t="s">
-        <v>459</v>
-      </c>
-      <c r="C28" s="31" t="s">
-        <v>460</v>
-      </c>
-      <c r="D28" s="31" t="s">
-        <v>461</v>
-      </c>
-      <c r="E28" s="31">
-        <v>20</v>
-      </c>
-      <c r="F28" s="32" t="s">
-        <v>462</v>
-      </c>
-      <c r="G28" s="32" t="s">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7">
-      <c r="A29" s="25" t="s">
-        <v>463</v>
-      </c>
-      <c r="B29" s="26" t="s">
-        <v>463</v>
-      </c>
-      <c r="C29" s="27" t="s">
-        <v>464</v>
-      </c>
-      <c r="D29" s="27" t="s">
-        <v>465</v>
-      </c>
-      <c r="E29" s="27">
-        <v>5</v>
-      </c>
-      <c r="F29" s="28" t="s">
-        <v>466</v>
-      </c>
-      <c r="G29" s="28" t="s">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7">
-      <c r="A30" s="29" t="s">
-        <v>467</v>
-      </c>
-      <c r="B30" s="30" t="s">
-        <v>467</v>
-      </c>
-      <c r="C30" s="31" t="s">
-        <v>468</v>
-      </c>
-      <c r="D30" s="31" t="s">
-        <v>469</v>
-      </c>
-      <c r="E30" s="31">
-        <v>20</v>
-      </c>
-      <c r="F30" s="32" t="s">
-        <v>470</v>
-      </c>
-      <c r="G30" s="32" t="s">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7">
-      <c r="A31" s="25" t="s">
-        <v>471</v>
-      </c>
-      <c r="B31" s="26" t="s">
-        <v>471</v>
-      </c>
-      <c r="C31" s="27" t="s">
-        <v>472</v>
-      </c>
-      <c r="D31" s="27" t="s">
-        <v>473</v>
-      </c>
-      <c r="E31" s="27">
-        <v>15</v>
-      </c>
-      <c r="F31" s="28" t="s">
-        <v>474</v>
-      </c>
-      <c r="G31" s="28" t="s">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7">
-      <c r="A32" s="29" t="s">
-        <v>475</v>
-      </c>
-      <c r="B32" s="30" t="s">
-        <v>475</v>
-      </c>
-      <c r="C32" s="31" t="s">
-        <v>476</v>
-      </c>
-      <c r="D32" s="31" t="s">
-        <v>477</v>
-      </c>
-      <c r="E32" s="31">
-        <v>15</v>
-      </c>
-      <c r="F32" s="32" t="s">
-        <v>478</v>
-      </c>
-      <c r="G32" s="32" t="s">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="33" ht="17" spans="1:7">
-      <c r="A33" s="25" t="s">
-        <v>479</v>
-      </c>
-      <c r="B33" s="26" t="s">
-        <v>479</v>
-      </c>
-      <c r="C33" s="27" t="s">
-        <v>480</v>
-      </c>
-      <c r="D33" s="27" t="s">
-        <v>481</v>
-      </c>
-      <c r="E33" s="27">
-        <v>15</v>
-      </c>
-      <c r="F33" s="28" t="s">
-        <v>482</v>
-      </c>
-      <c r="G33" s="28" t="s">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7">
-      <c r="A34" s="29" t="s">
-        <v>483</v>
-      </c>
-      <c r="B34" s="30" t="s">
-        <v>483</v>
-      </c>
-      <c r="C34" s="31" t="s">
-        <v>484</v>
-      </c>
-      <c r="D34" s="31" t="s">
-        <v>485</v>
-      </c>
-      <c r="E34" s="31">
-        <v>5</v>
-      </c>
-      <c r="F34" s="32" t="s">
-        <v>486</v>
-      </c>
-      <c r="G34" s="32" t="s">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7">
-      <c r="A35" s="25" t="s">
-        <v>487</v>
-      </c>
-      <c r="B35" s="26" t="s">
-        <v>487</v>
-      </c>
-      <c r="C35" s="27" t="s">
-        <v>488</v>
-      </c>
-      <c r="D35" s="27" t="s">
-        <v>489</v>
-      </c>
-      <c r="E35" s="27">
-        <v>25</v>
-      </c>
-      <c r="F35" s="28" t="s">
-        <v>490</v>
-      </c>
-      <c r="G35" s="28" t="s">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7">
-      <c r="A36" s="29" t="s">
-        <v>491</v>
-      </c>
-      <c r="B36" s="30" t="s">
-        <v>491</v>
-      </c>
-      <c r="C36" s="31" t="s">
-        <v>492</v>
-      </c>
-      <c r="D36" s="31" t="s">
-        <v>493</v>
-      </c>
-      <c r="E36" s="31">
-        <v>10</v>
-      </c>
-      <c r="F36" s="32" t="s">
-        <v>494</v>
-      </c>
-      <c r="G36" s="32" t="s">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7">
-      <c r="A37" s="25" t="s">
-        <v>495</v>
-      </c>
-      <c r="B37" s="26" t="s">
-        <v>495</v>
-      </c>
-      <c r="C37" s="27" t="s">
-        <v>496</v>
-      </c>
-      <c r="D37" s="27" t="s">
-        <v>497</v>
-      </c>
-      <c r="E37" s="27">
-        <v>8</v>
-      </c>
-      <c r="F37" s="28" t="s">
-        <v>498</v>
-      </c>
-      <c r="G37" s="28" t="s">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7">
-      <c r="A38" s="29" t="s">
-        <v>499</v>
-      </c>
-      <c r="B38" s="30" t="s">
-        <v>499</v>
-      </c>
-      <c r="C38" s="31" t="s">
-        <v>500</v>
-      </c>
-      <c r="D38" s="31" t="s">
-        <v>501</v>
-      </c>
-      <c r="E38" s="31">
-        <v>100</v>
-      </c>
-      <c r="F38" s="32" t="s">
-        <v>502</v>
-      </c>
-      <c r="G38" s="32" t="s">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7">
-      <c r="A39" s="25" t="s">
-        <v>503</v>
-      </c>
-      <c r="B39" s="26" t="s">
-        <v>503</v>
-      </c>
-      <c r="C39" s="27" t="s">
-        <v>504</v>
-      </c>
-      <c r="D39" s="27" t="s">
-        <v>505</v>
-      </c>
-      <c r="E39" s="27">
-        <v>20</v>
-      </c>
-      <c r="F39" s="28" t="s">
-        <v>506</v>
-      </c>
-      <c r="G39" s="28" t="s">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="40" ht="17" spans="1:7">
+    <row r="40" spans="1:7">
       <c r="A40" s="18" t="s">
         <v>507</v>
       </c>
@@ -8916,7 +8747,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="43" ht="17" spans="1:7">
+    <row r="43" spans="1:7">
       <c r="A43" s="14" t="s">
         <v>519</v>
       </c>
@@ -8985,7 +8816,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="46" spans="1:7">
+    <row r="46" ht="24.75" spans="1:7">
       <c r="A46" s="18" t="s">
         <v>529</v>
       </c>
@@ -9100,7 +8931,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="51" spans="1:7">
+    <row r="51" ht="24.75" spans="1:7">
       <c r="A51" s="14" t="s">
         <v>547</v>
       </c>
@@ -9249,15 +9080,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F99"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.85" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="17.775" customWidth="1"/>
-    <col min="2" max="2" width="25.4416666666667" customWidth="1"/>
-    <col min="3" max="3" width="20.3333333333333" customWidth="1"/>
-    <col min="4" max="4" width="24.4416666666667" hidden="1" customWidth="1"/>
-    <col min="5" max="5" width="17.1083333333333" customWidth="1"/>
-    <col min="6" max="6" width="119.333333333333" customWidth="1"/>
-    <col min="7" max="7" width="12.775" customWidth="1"/>
+    <col min="1" max="1" width="17.7787610619469" customWidth="1"/>
+    <col min="2" max="2" width="25.4424778761062" customWidth="1"/>
+    <col min="3" max="3" width="20.3362831858407" customWidth="1"/>
+    <col min="4" max="4" width="24.4424778761062" hidden="1" customWidth="1"/>
+    <col min="5" max="5" width="17.1061946902655" customWidth="1"/>
+    <col min="6" max="6" width="119.336283185841" customWidth="1"/>
+    <col min="7" max="7" width="12.7787610619469" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
@@ -9514,7 +9345,7 @@
         <v>616</v>
       </c>
     </row>
-    <row r="14" spans="1:6">
+    <row r="14" ht="24.75" spans="1:6">
       <c r="A14" s="6" t="s">
         <v>617</v>
       </c>
@@ -10514,7 +10345,7 @@
         <v>815</v>
       </c>
     </row>
-    <row r="64" ht="26" spans="1:6">
+    <row r="64" ht="24.75" spans="1:6">
       <c r="A64" s="6" t="s">
         <v>816</v>
       </c>
@@ -10614,7 +10445,7 @@
         <v>835</v>
       </c>
     </row>
-    <row r="69" spans="1:6">
+    <row r="69" ht="24.75" spans="1:6">
       <c r="A69" s="6" t="s">
         <v>836</v>
       </c>

--- a/Src/Assets/StreamingAssets/Common/Tables/Tables/Hero&Enemy.xlsx
+++ b/Src/Assets/StreamingAssets/Common/Tables/Tables/Hero&Enemy.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="21600" windowHeight="9555" activeTab="4"/>
+    <workbookView windowWidth="25600" windowHeight="12080" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="HeroSkill" sheetId="4" r:id="rId1"/>
@@ -3261,6 +3261,27 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <u/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11.25"/>
+      <color rgb="FFF9FAFB"/>
+      <name val="Segoe UI"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11.25"/>
+      <color rgb="FFF9FAFB"/>
+      <name val="Segoe UI"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <i/>
       <sz val="11.25"/>
       <color rgb="FFFF0000"/>
@@ -3284,27 +3305,6 @@
       <sz val="11.25"/>
       <color rgb="FFFF0000"/>
       <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <u/>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11.25"/>
-      <color rgb="FFF9FAFB"/>
-      <name val="Segoe UI"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11.25"/>
-      <color rgb="FFF9FAFB"/>
-      <name val="Segoe UI"/>
       <charset val="134"/>
     </font>
   </fonts>
@@ -4531,19 +4531,19 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:H38"/>
-  <sheetFormatPr defaultColWidth="8.24778761061947" defaultRowHeight="13.85" outlineLevelCol="7"/>
+  <sheetFormatPr defaultColWidth="8.25" defaultRowHeight="14" outlineLevelCol="7"/>
   <cols>
-    <col min="1" max="1" width="22.8141592920354" style="10" customWidth="1"/>
-    <col min="2" max="2" width="21.5044247787611" style="10" customWidth="1"/>
-    <col min="3" max="3" width="8.24778761061947" style="10"/>
-    <col min="4" max="4" width="15.212389380531" style="10" customWidth="1"/>
+    <col min="1" max="1" width="22.8166666666667" style="10" customWidth="1"/>
+    <col min="2" max="2" width="21.5083333333333" style="10" customWidth="1"/>
+    <col min="3" max="3" width="8.25" style="10"/>
+    <col min="4" max="4" width="15.2083333333333" style="10" customWidth="1"/>
     <col min="5" max="5" width="14" style="10" customWidth="1"/>
-    <col min="6" max="6" width="23.6725663716814" style="10" customWidth="1"/>
-    <col min="7" max="7" width="8.70796460176991" style="10" customWidth="1"/>
-    <col min="8" max="16382" width="8.24778761061947" style="10"/>
+    <col min="6" max="6" width="23.675" style="10" customWidth="1"/>
+    <col min="7" max="7" width="8.70833333333333" style="10" customWidth="1"/>
+    <col min="8" max="16382" width="8.25" style="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="14.6" spans="1:8">
+    <row r="1" ht="14.75" spans="1:8">
       <c r="A1" s="30" t="s">
         <v>0</v>
       </c>
@@ -4569,7 +4569,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" ht="25.5" spans="1:8">
+    <row r="2" ht="26" spans="1:8">
       <c r="A2" s="38" t="s">
         <v>8</v>
       </c>
@@ -4595,7 +4595,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" ht="25.5" spans="1:8">
+    <row r="3" spans="1:8">
       <c r="A3" s="36" t="s">
         <v>12</v>
       </c>
@@ -4621,7 +4621,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" ht="25.5" spans="1:8">
+    <row r="4" ht="26" spans="1:8">
       <c r="A4" s="38" t="s">
         <v>15</v>
       </c>
@@ -4647,7 +4647,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" ht="25.5" spans="1:8">
+    <row r="5" ht="26" spans="1:8">
       <c r="A5" s="36" t="s">
         <v>18</v>
       </c>
@@ -4725,7 +4725,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" ht="38.25" spans="1:8">
+    <row r="8" ht="39" spans="1:8">
       <c r="A8" s="38" t="s">
         <v>27</v>
       </c>
@@ -4751,7 +4751,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" ht="25.5" spans="1:8">
+    <row r="9" ht="26" spans="1:8">
       <c r="A9" s="36" t="s">
         <v>31</v>
       </c>
@@ -4777,7 +4777,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" ht="89.25" spans="1:8">
+    <row r="10" ht="78" spans="1:8">
       <c r="A10" s="38" t="s">
         <v>34</v>
       </c>
@@ -4803,7 +4803,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" ht="89.25" spans="1:8">
+    <row r="11" ht="91" spans="1:8">
       <c r="A11" s="36" t="s">
         <v>38</v>
       </c>
@@ -4829,7 +4829,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" ht="127.5" spans="1:8">
+    <row r="12" ht="117" spans="1:8">
       <c r="A12" s="38" t="s">
         <v>41</v>
       </c>
@@ -4855,7 +4855,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" ht="51" spans="1:8">
+    <row r="13" ht="52" spans="1:8">
       <c r="A13" s="36" t="s">
         <v>44</v>
       </c>
@@ -4881,7 +4881,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" ht="38.25" spans="1:8">
+    <row r="14" ht="39" spans="1:8">
       <c r="A14" s="38" t="s">
         <v>47</v>
       </c>
@@ -4907,7 +4907,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" ht="38.25" spans="1:8">
+    <row r="15" ht="39" spans="1:8">
       <c r="A15" s="36" t="s">
         <v>51</v>
       </c>
@@ -4933,7 +4933,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" ht="25.5" spans="1:8">
+    <row r="16" ht="26" spans="1:8">
       <c r="A16" s="38" t="s">
         <v>54</v>
       </c>
@@ -4959,7 +4959,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" ht="63.75" spans="1:8">
+    <row r="17" ht="52" spans="1:8">
       <c r="A17" s="36" t="s">
         <v>57</v>
       </c>
@@ -4985,7 +4985,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" ht="51" spans="1:8">
+    <row r="18" ht="52" spans="1:8">
       <c r="A18" s="38" t="s">
         <v>60</v>
       </c>
@@ -5011,7 +5011,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" ht="25.5" spans="1:8">
+    <row r="19" ht="26" spans="1:8">
       <c r="A19" s="36" t="s">
         <v>64</v>
       </c>
@@ -5037,7 +5037,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" ht="25.5" spans="1:8">
+    <row r="20" ht="26" spans="1:8">
       <c r="A20" s="38" t="s">
         <v>67</v>
       </c>
@@ -5063,7 +5063,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" ht="191.25" spans="1:8">
+    <row r="21" ht="182" spans="1:8">
       <c r="A21" s="36" t="s">
         <v>70</v>
       </c>
@@ -5270,12 +5270,12 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F8"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.85" outlineLevelRow="7" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="7" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="17.2654867256637" customWidth="1"/>
-    <col min="2" max="2" width="16.1858407079646" customWidth="1"/>
-    <col min="5" max="5" width="12.4513274336283" customWidth="1"/>
-    <col min="6" max="6" width="39.1858407079646" customWidth="1"/>
+    <col min="1" max="1" width="17.2666666666667" customWidth="1"/>
+    <col min="2" max="2" width="16.1833333333333" customWidth="1"/>
+    <col min="5" max="5" width="12.45" customWidth="1"/>
+    <col min="6" max="6" width="39.1833333333333" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="22.5" customHeight="1" spans="1:6">
@@ -5358,7 +5358,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="5" s="40" customFormat="1" ht="51.75" spans="1:6">
+    <row r="5" s="40" customFormat="1" ht="52.75" spans="1:6">
       <c r="A5" s="49" t="s">
         <v>87</v>
       </c>
@@ -5378,7 +5378,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="6" s="40" customFormat="1" ht="51" spans="1:6">
+    <row r="6" s="40" customFormat="1" ht="52" spans="1:6">
       <c r="A6" s="49" t="s">
         <v>92</v>
       </c>
@@ -5461,18 +5461,18 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:H88"/>
-  <sheetFormatPr defaultColWidth="8.24778761061947" defaultRowHeight="13.85" outlineLevelCol="7"/>
+  <sheetFormatPr defaultColWidth="8.25" defaultRowHeight="14" outlineLevelCol="7"/>
   <cols>
-    <col min="1" max="1" width="28.3185840707965" style="10" customWidth="1"/>
-    <col min="2" max="2" width="23.929203539823" style="10" customWidth="1"/>
-    <col min="3" max="3" width="16.9115044247788" style="10" customWidth="1"/>
-    <col min="4" max="4" width="15.787610619469" style="10" customWidth="1"/>
-    <col min="5" max="5" width="13.2389380530973" style="10" customWidth="1"/>
-    <col min="6" max="6" width="25.9734513274336" style="10" customWidth="1"/>
-    <col min="7" max="16382" width="8.24778761061947" style="10"/>
+    <col min="1" max="1" width="28.3166666666667" style="10" customWidth="1"/>
+    <col min="2" max="2" width="23.9333333333333" style="10" customWidth="1"/>
+    <col min="3" max="3" width="16.9083333333333" style="10" customWidth="1"/>
+    <col min="4" max="4" width="15.7916666666667" style="10" customWidth="1"/>
+    <col min="5" max="5" width="13.2416666666667" style="10" customWidth="1"/>
+    <col min="6" max="6" width="25.975" style="10" customWidth="1"/>
+    <col min="7" max="16382" width="8.25" style="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="14.6" spans="1:8">
+    <row r="1" ht="14.75" spans="1:8">
       <c r="A1" s="30" t="s">
         <v>0</v>
       </c>
@@ -5498,7 +5498,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" ht="51" spans="1:8">
+    <row r="2" ht="52" spans="1:8">
       <c r="A2" s="32" t="s">
         <v>100</v>
       </c>
@@ -5550,7 +5550,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" ht="25.5" spans="1:8">
+    <row r="4" ht="26" spans="1:8">
       <c r="A4" s="32" t="s">
         <v>106</v>
       </c>
@@ -5576,7 +5576,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" ht="38.25" spans="1:8">
+    <row r="5" ht="39" spans="1:8">
       <c r="A5" s="34" t="s">
         <v>109</v>
       </c>
@@ -5602,7 +5602,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" ht="25.5" spans="1:8">
+    <row r="6" ht="26" spans="1:8">
       <c r="A6" s="32" t="s">
         <v>112</v>
       </c>
@@ -5628,7 +5628,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" ht="38.25" spans="1:8">
+    <row r="7" ht="39" spans="1:8">
       <c r="A7" s="34" t="s">
         <v>115</v>
       </c>
@@ -5654,7 +5654,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" ht="63.75" spans="1:8">
+    <row r="8" ht="65" spans="1:8">
       <c r="A8" s="32" t="s">
         <v>118</v>
       </c>
@@ -5680,7 +5680,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" ht="38.25" spans="1:8">
+    <row r="9" ht="39" spans="1:8">
       <c r="A9" s="34" t="s">
         <v>121</v>
       </c>
@@ -5706,7 +5706,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" ht="38.25" spans="1:8">
+    <row r="10" ht="39" spans="1:8">
       <c r="A10" s="32" t="s">
         <v>124</v>
       </c>
@@ -5732,7 +5732,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" ht="127.5" spans="1:8">
+    <row r="11" ht="117" spans="1:8">
       <c r="A11" s="36" t="s">
         <v>127</v>
       </c>
@@ -5758,7 +5758,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" ht="38.25" spans="1:8">
+    <row r="12" ht="39" spans="1:8">
       <c r="A12" s="38" t="s">
         <v>130</v>
       </c>
@@ -5784,7 +5784,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" ht="25.5" spans="1:8">
+    <row r="13" ht="26" spans="1:8">
       <c r="A13" s="36" t="s">
         <v>133</v>
       </c>
@@ -5810,7 +5810,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" ht="25.5" spans="1:8">
+    <row r="14" ht="26" spans="1:8">
       <c r="A14" s="38" t="s">
         <v>136</v>
       </c>
@@ -5836,7 +5836,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" ht="16.9" spans="1:8">
+    <row r="15" ht="17" spans="1:8">
       <c r="A15" s="36" t="s">
         <v>139</v>
       </c>
@@ -5862,7 +5862,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" ht="51" spans="1:8">
+    <row r="16" ht="39" spans="1:8">
       <c r="A16" s="38" t="s">
         <v>142</v>
       </c>
@@ -5888,7 +5888,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" ht="25.5" spans="1:8">
+    <row r="17" ht="26" spans="1:8">
       <c r="A17" s="36" t="s">
         <v>145</v>
       </c>
@@ -5914,7 +5914,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" ht="25.5" spans="1:8">
+    <row r="18" ht="26" spans="1:8">
       <c r="A18" s="38" t="s">
         <v>148</v>
       </c>
@@ -5940,7 +5940,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" ht="76.5" spans="1:8">
+    <row r="19" ht="78" spans="1:8">
       <c r="A19" s="36" t="s">
         <v>151</v>
       </c>
@@ -5992,7 +5992,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" ht="25.5" spans="1:8">
+    <row r="21" ht="26" spans="1:8">
       <c r="A21" s="36" t="s">
         <v>157</v>
       </c>
@@ -6018,7 +6018,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" ht="38.25" spans="1:8">
+    <row r="22" ht="26" spans="1:8">
       <c r="A22" s="38" t="s">
         <v>160</v>
       </c>
@@ -6044,7 +6044,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" ht="63.75" spans="1:8">
+    <row r="23" ht="65" spans="1:8">
       <c r="A23" s="36" t="s">
         <v>163</v>
       </c>
@@ -6070,7 +6070,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" ht="63.75" spans="1:8">
+    <row r="24" ht="65" spans="1:8">
       <c r="A24" s="38" t="s">
         <v>165</v>
       </c>
@@ -6096,7 +6096,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" ht="25.5" spans="1:8">
+    <row r="25" ht="26" spans="1:8">
       <c r="A25" s="36" t="s">
         <v>168</v>
       </c>
@@ -6122,7 +6122,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" ht="76.5" spans="1:8">
+    <row r="26" ht="78" spans="1:8">
       <c r="A26" s="38" t="s">
         <v>171</v>
       </c>
@@ -6148,7 +6148,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" ht="63.75" spans="1:8">
+    <row r="27" ht="52" spans="1:8">
       <c r="A27" s="36" t="s">
         <v>174</v>
       </c>
@@ -6174,7 +6174,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" ht="76.5" spans="1:8">
+    <row r="28" ht="65" spans="1:8">
       <c r="A28" s="38" t="s">
         <v>177</v>
       </c>
@@ -6200,7 +6200,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" ht="25.5" spans="1:8">
+    <row r="29" ht="26" spans="1:8">
       <c r="A29" s="36" t="s">
         <v>180</v>
       </c>
@@ -6226,7 +6226,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" ht="38.25" spans="1:8">
+    <row r="30" ht="39" spans="1:8">
       <c r="A30" s="38" t="s">
         <v>183</v>
       </c>
@@ -6252,7 +6252,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" ht="25.5" spans="1:8">
+    <row r="31" ht="26" spans="1:8">
       <c r="A31" s="36" t="s">
         <v>186</v>
       </c>
@@ -6278,7 +6278,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" ht="25.5" spans="1:8">
+    <row r="32" ht="26" spans="1:8">
       <c r="A32" s="38" t="s">
         <v>189</v>
       </c>
@@ -6304,7 +6304,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" ht="38.25" spans="1:8">
+    <row r="33" ht="39" spans="1:8">
       <c r="A33" s="36" t="s">
         <v>192</v>
       </c>
@@ -6356,7 +6356,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" ht="127.5" spans="1:8">
+    <row r="35" ht="130" spans="1:8">
       <c r="A35" s="36" t="s">
         <v>198</v>
       </c>
@@ -6434,7 +6434,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" ht="38.25" spans="1:8">
+    <row r="38" ht="39" spans="1:8">
       <c r="A38" s="38" t="s">
         <v>207</v>
       </c>
@@ -6460,7 +6460,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" ht="25.5" spans="1:8">
+    <row r="39" ht="26" spans="1:8">
       <c r="A39" s="36" t="s">
         <v>210</v>
       </c>
@@ -6512,7 +6512,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" ht="25.5" spans="1:8">
+    <row r="41" ht="26" spans="1:8">
       <c r="A41" s="36" t="s">
         <v>216</v>
       </c>
@@ -6538,7 +6538,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" ht="38.25" spans="1:8">
+    <row r="42" ht="26" spans="1:8">
       <c r="A42" s="38" t="s">
         <v>219</v>
       </c>
@@ -6564,7 +6564,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" ht="38.25" spans="1:8">
+    <row r="43" ht="26" spans="1:8">
       <c r="A43" s="36" t="s">
         <v>222</v>
       </c>
@@ -6590,7 +6590,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" ht="51" spans="1:8">
+    <row r="44" ht="39" spans="1:8">
       <c r="A44" s="38" t="s">
         <v>225</v>
       </c>
@@ -6616,7 +6616,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" ht="25.5" spans="1:8">
+    <row r="45" ht="26" spans="1:8">
       <c r="A45" s="36" t="s">
         <v>228</v>
       </c>
@@ -6642,7 +6642,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" ht="25.5" spans="1:8">
+    <row r="46" ht="26" spans="1:8">
       <c r="A46" s="38" t="s">
         <v>231</v>
       </c>
@@ -6668,7 +6668,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" ht="51" spans="1:8">
+    <row r="47" ht="52" spans="1:8">
       <c r="A47" s="36" t="s">
         <v>234</v>
       </c>
@@ -6694,7 +6694,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" ht="63.75" spans="1:8">
+    <row r="48" ht="65" spans="1:8">
       <c r="A48" s="38" t="s">
         <v>237</v>
       </c>
@@ -6746,7 +6746,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" ht="51" spans="1:8">
+    <row r="50" ht="39" spans="1:8">
       <c r="A50" s="38" t="s">
         <v>243</v>
       </c>
@@ -6798,7 +6798,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" ht="38.25" spans="1:8">
+    <row r="52" ht="26" spans="1:8">
       <c r="A52" s="38" t="s">
         <v>249</v>
       </c>
@@ -6824,7 +6824,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" ht="25.5" spans="1:8">
+    <row r="53" ht="26" spans="1:8">
       <c r="A53" s="36" t="s">
         <v>252</v>
       </c>
@@ -6850,7 +6850,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" ht="25.5" spans="1:8">
+    <row r="54" ht="26" spans="1:8">
       <c r="A54" s="38" t="s">
         <v>255</v>
       </c>
@@ -6876,7 +6876,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" ht="38.25" spans="1:8">
+    <row r="55" ht="39" spans="1:8">
       <c r="A55" s="36" t="s">
         <v>258</v>
       </c>
@@ -6902,7 +6902,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" ht="25.5" spans="1:8">
+    <row r="56" ht="26" spans="1:8">
       <c r="A56" s="38" t="s">
         <v>261</v>
       </c>
@@ -6928,7 +6928,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" ht="25.5" spans="1:8">
+    <row r="57" ht="26" spans="1:8">
       <c r="A57" s="36" t="s">
         <v>264</v>
       </c>
@@ -6954,7 +6954,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" ht="38.25" spans="1:8">
+    <row r="58" ht="26" spans="1:8">
       <c r="A58" s="38" t="s">
         <v>267</v>
       </c>
@@ -6980,7 +6980,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" ht="29.65" spans="1:8">
+    <row r="59" ht="30" spans="1:8">
       <c r="A59" s="36" t="s">
         <v>270</v>
       </c>
@@ -7032,7 +7032,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" ht="51" spans="1:8">
+    <row r="61" ht="52" spans="1:8">
       <c r="A61" s="36" t="s">
         <v>276</v>
       </c>
@@ -7058,7 +7058,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" ht="25.5" spans="1:8">
+    <row r="62" ht="26" spans="1:8">
       <c r="A62" s="38" t="s">
         <v>279</v>
       </c>
@@ -7084,7 +7084,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" ht="38.25" spans="1:8">
+    <row r="63" ht="39" spans="1:8">
       <c r="A63" s="36" t="s">
         <v>282</v>
       </c>
@@ -7136,7 +7136,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" ht="25.5" spans="1:8">
+    <row r="65" ht="26" spans="1:8">
       <c r="A65" s="36" t="s">
         <v>288</v>
       </c>
@@ -7162,7 +7162,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" ht="38.25" spans="1:8">
+    <row r="66" ht="39" spans="1:8">
       <c r="A66" s="38" t="s">
         <v>291</v>
       </c>
@@ -7188,7 +7188,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" ht="51" spans="1:8">
+    <row r="67" ht="52" spans="1:8">
       <c r="A67" s="36" t="s">
         <v>294</v>
       </c>
@@ -7214,7 +7214,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" ht="46.5" spans="1:8">
+    <row r="68" ht="47" spans="1:8">
       <c r="A68" s="32" t="s">
         <v>297</v>
       </c>
@@ -7240,7 +7240,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" ht="25.5" spans="1:8">
+    <row r="69" ht="26" spans="1:8">
       <c r="A69" s="34" t="s">
         <v>300</v>
       </c>
@@ -7292,7 +7292,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" ht="89.25" spans="1:8">
+    <row r="71" ht="91" spans="1:8">
       <c r="A71" s="34" t="s">
         <v>303</v>
       </c>
@@ -7318,7 +7318,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" ht="51" spans="1:8">
+    <row r="72" ht="39" spans="1:8">
       <c r="A72" s="32" t="s">
         <v>306</v>
       </c>
@@ -7370,7 +7370,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" ht="16.9" spans="1:8">
+    <row r="74" ht="17" spans="1:8">
       <c r="A74" s="32" t="s">
         <v>312</v>
       </c>
@@ -7448,7 +7448,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" ht="25.5" spans="1:8">
+    <row r="77" ht="26" spans="1:8">
       <c r="A77" s="34" t="s">
         <v>319</v>
       </c>
@@ -7474,7 +7474,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" ht="25.5" spans="1:8">
+    <row r="78" ht="26" spans="1:8">
       <c r="A78" s="32" t="s">
         <v>322</v>
       </c>
@@ -7500,7 +7500,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" ht="63.75" spans="1:8">
+    <row r="79" ht="65" spans="1:8">
       <c r="A79" s="34" t="s">
         <v>325</v>
       </c>
@@ -7526,7 +7526,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" ht="25.5" spans="1:8">
+    <row r="80" ht="26" spans="1:8">
       <c r="A80" s="32" t="s">
         <v>328</v>
       </c>
@@ -7552,7 +7552,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" ht="25.5" spans="1:8">
+    <row r="81" ht="26" spans="1:8">
       <c r="A81" s="34" t="s">
         <v>331</v>
       </c>
@@ -7578,7 +7578,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" ht="25.5" spans="1:8">
+    <row r="82" ht="26" spans="1:8">
       <c r="A82" s="32" t="s">
         <v>334</v>
       </c>
@@ -7656,7 +7656,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" ht="25.5" spans="1:8">
+    <row r="85" ht="26" spans="1:8">
       <c r="A85" s="34" t="s">
         <v>300</v>
       </c>
@@ -7682,7 +7682,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" ht="63.75" spans="1:8">
+    <row r="86" ht="65" spans="1:8">
       <c r="A86" s="32" t="s">
         <v>342</v>
       </c>
@@ -7771,16 +7771,16 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:G56"/>
-  <sheetFormatPr defaultColWidth="8.24778761061947" defaultRowHeight="13.85" outlineLevelCol="6"/>
+  <sheetFormatPr defaultColWidth="8.25" defaultRowHeight="14" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="20.7522123893805" style="10" customWidth="1"/>
-    <col min="2" max="2" width="18.141592920354" style="10" customWidth="1"/>
-    <col min="3" max="3" width="14.3628318584071" style="10" customWidth="1"/>
-    <col min="4" max="4" width="47.4690265486726" style="10" hidden="1" customWidth="1"/>
-    <col min="5" max="5" width="8.24778761061947" style="10"/>
-    <col min="6" max="6" width="104.893805309735" style="10" customWidth="1"/>
-    <col min="7" max="7" width="26.6548672566372" style="10" customWidth="1"/>
-    <col min="8" max="16384" width="8.24778761061947" style="10"/>
+    <col min="1" max="1" width="20.75" style="10" customWidth="1"/>
+    <col min="2" max="2" width="18.1416666666667" style="10" customWidth="1"/>
+    <col min="3" max="3" width="14.3666666666667" style="10" customWidth="1"/>
+    <col min="4" max="4" width="47.4666666666667" style="10" hidden="1" customWidth="1"/>
+    <col min="5" max="5" width="8.25" style="10"/>
+    <col min="6" max="6" width="104.891666666667" style="10" customWidth="1"/>
+    <col min="7" max="7" width="26.6583333333333" style="10" customWidth="1"/>
+    <col min="8" max="16384" width="8.25" style="10"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
@@ -8356,7 +8356,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="26" ht="24.75" spans="1:7">
+    <row r="26" spans="1:7">
       <c r="A26" s="26" t="s">
         <v>451</v>
       </c>
@@ -8816,7 +8816,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="46" ht="24.75" spans="1:7">
+    <row r="46" spans="1:7">
       <c r="A46" s="18" t="s">
         <v>529</v>
       </c>
@@ -8931,7 +8931,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="51" ht="24.75" spans="1:7">
+    <row r="51" spans="1:7">
       <c r="A51" s="14" t="s">
         <v>547</v>
       </c>
@@ -9080,15 +9080,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F99"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.85" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="17.7787610619469" customWidth="1"/>
-    <col min="2" max="2" width="25.4424778761062" customWidth="1"/>
-    <col min="3" max="3" width="20.3362831858407" customWidth="1"/>
-    <col min="4" max="4" width="24.4424778761062" hidden="1" customWidth="1"/>
-    <col min="5" max="5" width="17.1061946902655" customWidth="1"/>
-    <col min="6" max="6" width="119.336283185841" customWidth="1"/>
-    <col min="7" max="7" width="12.7787610619469" customWidth="1"/>
+    <col min="1" max="1" width="17.775" customWidth="1"/>
+    <col min="2" max="2" width="25.4416666666667" customWidth="1"/>
+    <col min="3" max="3" width="20.3333333333333" customWidth="1"/>
+    <col min="4" max="4" width="24.4416666666667" hidden="1" customWidth="1"/>
+    <col min="5" max="5" width="17.1083333333333" customWidth="1"/>
+    <col min="6" max="6" width="119.333333333333" customWidth="1"/>
+    <col min="7" max="7" width="12.775" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
@@ -9345,7 +9345,7 @@
         <v>616</v>
       </c>
     </row>
-    <row r="14" ht="24.75" spans="1:6">
+    <row r="14" spans="1:6">
       <c r="A14" s="6" t="s">
         <v>617</v>
       </c>
@@ -10345,7 +10345,7 @@
         <v>815</v>
       </c>
     </row>
-    <row r="64" ht="24.75" spans="1:6">
+    <row r="64" ht="26" spans="1:6">
       <c r="A64" s="6" t="s">
         <v>816</v>
       </c>
@@ -10445,7 +10445,7 @@
         <v>835</v>
       </c>
     </row>
-    <row r="69" ht="24.75" spans="1:6">
+    <row r="69" spans="1:6">
       <c r="A69" s="6" t="s">
         <v>836</v>
       </c>

--- a/Src/Assets/StreamingAssets/Common/Tables/Tables/Hero&Enemy.xlsx
+++ b/Src/Assets/StreamingAssets/Common/Tables/Tables/Hero&Enemy.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="25600" windowHeight="12080" activeTab="3"/>
+    <workbookView windowWidth="25600" windowHeight="12080" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="HeroSkill" sheetId="4" r:id="rId1"/>

--- a/Src/Assets/StreamingAssets/Common/Tables/Tables/Hero&Enemy.xlsx
+++ b/Src/Assets/StreamingAssets/Common/Tables/Tables/Hero&Enemy.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="25600" windowHeight="12080" activeTab="2"/>
+    <workbookView windowWidth="25600" windowHeight="12080"/>
   </bookViews>
   <sheets>
     <sheet name="HeroSkill" sheetId="4" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1288" uniqueCount="852">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1289" uniqueCount="853">
   <si>
     <t>Key</t>
   </si>
@@ -100,6 +100,9 @@
   </si>
   <si>
     <t>千钧棒</t>
+  </si>
+  <si>
+    <t>TURE</t>
   </si>
   <si>
     <t>你造成的伤害*3。</t>
@@ -4683,14 +4686,14 @@
       <c r="C6" s="38" t="s">
         <v>22</v>
       </c>
-      <c r="D6" s="38" t="b">
-        <v>0</v>
+      <c r="D6" s="38" t="s">
+        <v>23</v>
       </c>
       <c r="E6" s="38">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F6" s="39" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G6" s="38" t="s">
         <v>11</v>
@@ -4701,13 +4704,13 @@
     </row>
     <row r="7" spans="1:8">
       <c r="A7" s="36" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B7" s="36" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C7" s="36" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D7" s="36" t="b">
         <v>0</v>
@@ -4716,7 +4719,7 @@
         <v>0</v>
       </c>
       <c r="F7" s="37" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G7" s="36" t="s">
         <v>11</v>
@@ -4727,13 +4730,13 @@
     </row>
     <row r="8" ht="39" spans="1:8">
       <c r="A8" s="38" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B8" s="38" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C8" s="38" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D8" s="38" t="b">
         <v>0</v>
@@ -4742,10 +4745,10 @@
         <v>0</v>
       </c>
       <c r="F8" s="39" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G8" s="38" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H8" s="38">
         <v>0</v>
@@ -4753,13 +4756,13 @@
     </row>
     <row r="9" ht="26" spans="1:8">
       <c r="A9" s="36" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B9" s="36" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C9" s="36" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D9" s="36" t="b">
         <v>0</v>
@@ -4768,7 +4771,7 @@
         <v>0</v>
       </c>
       <c r="F9" s="37" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G9" s="36" t="s">
         <v>11</v>
@@ -4779,13 +4782,13 @@
     </row>
     <row r="10" ht="78" spans="1:8">
       <c r="A10" s="38" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B10" s="38" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C10" s="38" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D10" s="38" t="b">
         <v>0</v>
@@ -4794,10 +4797,10 @@
         <v>0</v>
       </c>
       <c r="F10" s="39" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G10" s="38" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H10" s="38">
         <v>0</v>
@@ -4805,13 +4808,13 @@
     </row>
     <row r="11" ht="91" spans="1:8">
       <c r="A11" s="36" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B11" s="36" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C11" s="36" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D11" s="36" t="b">
         <v>0</v>
@@ -4820,7 +4823,7 @@
         <v>0</v>
       </c>
       <c r="F11" s="37" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G11" s="36" t="s">
         <v>11</v>
@@ -4831,13 +4834,13 @@
     </row>
     <row r="12" ht="117" spans="1:8">
       <c r="A12" s="38" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B12" s="38" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C12" s="38" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D12" s="38" t="b">
         <v>0</v>
@@ -4846,7 +4849,7 @@
         <v>0</v>
       </c>
       <c r="F12" s="39" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G12" s="38" t="s">
         <v>11</v>
@@ -4857,13 +4860,13 @@
     </row>
     <row r="13" ht="52" spans="1:8">
       <c r="A13" s="36" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B13" s="36" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C13" s="36" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D13" s="36" t="b">
         <v>0</v>
@@ -4872,7 +4875,7 @@
         <v>0</v>
       </c>
       <c r="F13" s="37" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G13" s="36" t="s">
         <v>11</v>
@@ -4883,13 +4886,13 @@
     </row>
     <row r="14" ht="39" spans="1:8">
       <c r="A14" s="38" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B14" s="38" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C14" s="38" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D14" s="38" t="b">
         <v>1</v>
@@ -4898,10 +4901,10 @@
         <v>1</v>
       </c>
       <c r="F14" s="39" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G14" s="38" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H14" s="38">
         <v>0</v>
@@ -4909,13 +4912,13 @@
     </row>
     <row r="15" ht="39" spans="1:8">
       <c r="A15" s="36" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B15" s="36" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C15" s="36" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D15" s="36" t="b">
         <v>0</v>
@@ -4924,7 +4927,7 @@
         <v>0</v>
       </c>
       <c r="F15" s="37" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G15" s="36" t="s">
         <v>11</v>
@@ -4935,13 +4938,13 @@
     </row>
     <row r="16" ht="26" spans="1:8">
       <c r="A16" s="38" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B16" s="38" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C16" s="38" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D16" s="38" t="b">
         <v>0</v>
@@ -4950,7 +4953,7 @@
         <v>0</v>
       </c>
       <c r="F16" s="39" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G16" s="38" t="s">
         <v>11</v>
@@ -4961,13 +4964,13 @@
     </row>
     <row r="17" ht="52" spans="1:8">
       <c r="A17" s="36" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B17" s="36" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C17" s="36" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D17" s="36" t="b">
         <v>0</v>
@@ -4976,7 +4979,7 @@
         <v>0</v>
       </c>
       <c r="F17" s="37" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G17" s="36" t="s">
         <v>11</v>
@@ -4987,13 +4990,13 @@
     </row>
     <row r="18" ht="52" spans="1:8">
       <c r="A18" s="38" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B18" s="38" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C18" s="38" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D18" s="38" t="b">
         <v>0</v>
@@ -5002,10 +5005,10 @@
         <v>0</v>
       </c>
       <c r="F18" s="39" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G18" s="38" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H18" s="38">
         <v>0</v>
@@ -5013,13 +5016,13 @@
     </row>
     <row r="19" ht="26" spans="1:8">
       <c r="A19" s="36" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B19" s="36" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C19" s="36" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D19" s="36" t="b">
         <v>0</v>
@@ -5028,7 +5031,7 @@
         <v>0</v>
       </c>
       <c r="F19" s="37" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G19" s="36" t="s">
         <v>11</v>
@@ -5039,13 +5042,13 @@
     </row>
     <row r="20" ht="26" spans="1:8">
       <c r="A20" s="38" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B20" s="38" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C20" s="38" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D20" s="38" t="b">
         <v>0</v>
@@ -5054,7 +5057,7 @@
         <v>0</v>
       </c>
       <c r="F20" s="39" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G20" s="38" t="s">
         <v>11</v>
@@ -5065,13 +5068,13 @@
     </row>
     <row r="21" ht="182" spans="1:8">
       <c r="A21" s="36" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B21" s="36" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C21" s="36" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D21" s="36" t="b">
         <v>0</v>
@@ -5080,7 +5083,7 @@
         <v>0</v>
       </c>
       <c r="F21" s="37" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G21" s="36" t="s">
         <v>11</v>
@@ -5289,10 +5292,10 @@
         <v>2</v>
       </c>
       <c r="D1" s="41" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E1" s="43" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F1" s="44" t="s">
         <v>5</v>
@@ -5300,127 +5303,127 @@
     </row>
     <row r="2" ht="25.5" customHeight="1" spans="1:6">
       <c r="A2" s="45" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B2" s="46" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C2" s="46" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D2" s="45" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E2" s="47" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F2" s="48" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="3" ht="43" customHeight="1" spans="1:6">
       <c r="A3" s="49" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B3" s="50" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C3" s="50" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D3" s="49" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E3" s="51" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F3" s="52" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="4" ht="23" customHeight="1" spans="1:6">
       <c r="A4" s="53" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B4" s="54" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C4" s="54" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D4" s="53" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E4" s="55" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F4" s="56" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="5" s="40" customFormat="1" ht="52.75" spans="1:6">
       <c r="A5" s="49" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B5" s="50" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C5" s="51" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D5" s="50" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E5" s="50" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F5" s="52" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="6" s="40" customFormat="1" ht="52" spans="1:6">
       <c r="A6" s="49" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B6" s="50" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C6" s="51" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D6" s="50" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E6" s="50" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F6" s="52" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="45" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B7" s="46" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C7" s="47" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D7" s="46" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E7" s="46" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F7" s="48" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="57" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
   </sheetData>
@@ -5500,13 +5503,13 @@
     </row>
     <row r="2" ht="52" spans="1:8">
       <c r="A2" s="32" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B2" s="32" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C2" s="32" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D2" s="32" t="b">
         <v>1</v>
@@ -5515,7 +5518,7 @@
         <v>1</v>
       </c>
       <c r="F2" s="33" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="G2" s="32" t="s">
         <v>11</v>
@@ -5526,13 +5529,13 @@
     </row>
     <row r="3" spans="1:8">
       <c r="A3" s="34" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B3" s="34" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C3" s="34" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D3" s="34" t="b">
         <v>1</v>
@@ -5541,7 +5544,7 @@
         <v>1</v>
       </c>
       <c r="F3" s="35" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="G3" s="34" t="s">
         <v>11</v>
@@ -5552,13 +5555,13 @@
     </row>
     <row r="4" ht="26" spans="1:8">
       <c r="A4" s="32" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B4" s="32" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C4" s="32" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D4" s="32" t="b">
         <v>0</v>
@@ -5567,7 +5570,7 @@
         <v>0</v>
       </c>
       <c r="F4" s="33" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="G4" s="32" t="s">
         <v>11</v>
@@ -5578,13 +5581,13 @@
     </row>
     <row r="5" ht="39" spans="1:8">
       <c r="A5" s="34" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B5" s="34" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C5" s="34" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D5" s="34" t="b">
         <v>0</v>
@@ -5593,7 +5596,7 @@
         <v>0</v>
       </c>
       <c r="F5" s="35" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="G5" s="34" t="s">
         <v>11</v>
@@ -5604,13 +5607,13 @@
     </row>
     <row r="6" ht="26" spans="1:8">
       <c r="A6" s="32" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B6" s="32" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C6" s="32" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D6" s="32" t="b">
         <v>0</v>
@@ -5619,7 +5622,7 @@
         <v>0</v>
       </c>
       <c r="F6" s="33" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="G6" s="32" t="s">
         <v>11</v>
@@ -5630,13 +5633,13 @@
     </row>
     <row r="7" ht="39" spans="1:8">
       <c r="A7" s="34" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B7" s="34" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C7" s="34" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D7" s="34" t="b">
         <v>0</v>
@@ -5645,7 +5648,7 @@
         <v>0</v>
       </c>
       <c r="F7" s="35" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="G7" s="34" t="s">
         <v>11</v>
@@ -5656,13 +5659,13 @@
     </row>
     <row r="8" ht="65" spans="1:8">
       <c r="A8" s="32" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B8" s="32" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C8" s="32" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D8" s="32" t="b">
         <v>0</v>
@@ -5671,7 +5674,7 @@
         <v>0</v>
       </c>
       <c r="F8" s="33" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="G8" s="32" t="s">
         <v>11</v>
@@ -5682,13 +5685,13 @@
     </row>
     <row r="9" ht="39" spans="1:8">
       <c r="A9" s="34" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B9" s="34" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C9" s="34" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D9" s="34" t="b">
         <v>0</v>
@@ -5697,7 +5700,7 @@
         <v>0</v>
       </c>
       <c r="F9" s="35" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="G9" s="34" t="s">
         <v>11</v>
@@ -5708,13 +5711,13 @@
     </row>
     <row r="10" ht="39" spans="1:8">
       <c r="A10" s="32" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B10" s="32" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C10" s="32" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="D10" s="32" t="b">
         <v>0</v>
@@ -5723,7 +5726,7 @@
         <v>0</v>
       </c>
       <c r="F10" s="33" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="G10" s="32" t="s">
         <v>11</v>
@@ -5734,13 +5737,13 @@
     </row>
     <row r="11" ht="117" spans="1:8">
       <c r="A11" s="36" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B11" s="36" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C11" s="36" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D11" s="36" t="b">
         <v>0</v>
@@ -5749,7 +5752,7 @@
         <v>0</v>
       </c>
       <c r="F11" s="37" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="G11" s="36" t="s">
         <v>11</v>
@@ -5760,13 +5763,13 @@
     </row>
     <row r="12" ht="39" spans="1:8">
       <c r="A12" s="38" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B12" s="38" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C12" s="38" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D12" s="38" t="b">
         <v>0</v>
@@ -5775,7 +5778,7 @@
         <v>0</v>
       </c>
       <c r="F12" s="39" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="G12" s="38" t="s">
         <v>11</v>
@@ -5786,13 +5789,13 @@
     </row>
     <row r="13" ht="26" spans="1:8">
       <c r="A13" s="36" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B13" s="36" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C13" s="36" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D13" s="36" t="b">
         <v>0</v>
@@ -5801,7 +5804,7 @@
         <v>0</v>
       </c>
       <c r="F13" s="37" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="G13" s="36" t="s">
         <v>11</v>
@@ -5812,13 +5815,13 @@
     </row>
     <row r="14" ht="26" spans="1:8">
       <c r="A14" s="38" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B14" s="38" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C14" s="38" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D14" s="38" t="b">
         <v>0</v>
@@ -5827,7 +5830,7 @@
         <v>0</v>
       </c>
       <c r="F14" s="39" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="G14" s="38" t="s">
         <v>11</v>
@@ -5838,13 +5841,13 @@
     </row>
     <row r="15" ht="17" spans="1:8">
       <c r="A15" s="36" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B15" s="36" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C15" s="36" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D15" s="36" t="b">
         <v>0</v>
@@ -5853,7 +5856,7 @@
         <v>0</v>
       </c>
       <c r="F15" s="37" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="G15" s="36" t="s">
         <v>11</v>
@@ -5864,13 +5867,13 @@
     </row>
     <row r="16" ht="39" spans="1:8">
       <c r="A16" s="38" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B16" s="38" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C16" s="38" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D16" s="38" t="b">
         <v>0</v>
@@ -5879,7 +5882,7 @@
         <v>0</v>
       </c>
       <c r="F16" s="39" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="G16" s="38" t="s">
         <v>11</v>
@@ -5890,13 +5893,13 @@
     </row>
     <row r="17" ht="26" spans="1:8">
       <c r="A17" s="36" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B17" s="36" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C17" s="36" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D17" s="36" t="b">
         <v>0</v>
@@ -5905,7 +5908,7 @@
         <v>0</v>
       </c>
       <c r="F17" s="37" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="G17" s="36" t="s">
         <v>11</v>
@@ -5916,13 +5919,13 @@
     </row>
     <row r="18" ht="26" spans="1:8">
       <c r="A18" s="38" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B18" s="38" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C18" s="38" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D18" s="38" t="b">
         <v>0</v>
@@ -5931,7 +5934,7 @@
         <v>0</v>
       </c>
       <c r="F18" s="39" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="G18" s="38" t="s">
         <v>11</v>
@@ -5942,13 +5945,13 @@
     </row>
     <row r="19" ht="78" spans="1:8">
       <c r="A19" s="36" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B19" s="36" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C19" s="36" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="D19" s="36" t="b">
         <v>0</v>
@@ -5957,7 +5960,7 @@
         <v>0</v>
       </c>
       <c r="F19" s="37" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="G19" s="36" t="s">
         <v>11</v>
@@ -5968,13 +5971,13 @@
     </row>
     <row r="20" spans="1:8">
       <c r="A20" s="38" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B20" s="38" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C20" s="38" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D20" s="38" t="b">
         <v>0</v>
@@ -5983,7 +5986,7 @@
         <v>0</v>
       </c>
       <c r="F20" s="39" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="G20" s="38" t="s">
         <v>11</v>
@@ -5994,13 +5997,13 @@
     </row>
     <row r="21" ht="26" spans="1:8">
       <c r="A21" s="36" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B21" s="36" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C21" s="36" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D21" s="36" t="b">
         <v>0</v>
@@ -6009,7 +6012,7 @@
         <v>0</v>
       </c>
       <c r="F21" s="37" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="G21" s="36" t="s">
         <v>11</v>
@@ -6020,13 +6023,13 @@
     </row>
     <row r="22" ht="26" spans="1:8">
       <c r="A22" s="38" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B22" s="38" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C22" s="38" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="D22" s="38" t="b">
         <v>1</v>
@@ -6035,7 +6038,7 @@
         <v>1</v>
       </c>
       <c r="F22" s="39" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="G22" s="38" t="s">
         <v>11</v>
@@ -6046,13 +6049,13 @@
     </row>
     <row r="23" ht="65" spans="1:8">
       <c r="A23" s="36" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B23" s="36" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C23" s="36" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D23" s="36" t="b">
         <v>0</v>
@@ -6061,7 +6064,7 @@
         <v>0</v>
       </c>
       <c r="F23" s="37" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="G23" s="36" t="s">
         <v>11</v>
@@ -6072,13 +6075,13 @@
     </row>
     <row r="24" ht="65" spans="1:8">
       <c r="A24" s="38" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B24" s="38" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C24" s="38" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D24" s="38" t="b">
         <v>0</v>
@@ -6087,7 +6090,7 @@
         <v>0</v>
       </c>
       <c r="F24" s="39" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="G24" s="38" t="s">
         <v>11</v>
@@ -6098,13 +6101,13 @@
     </row>
     <row r="25" ht="26" spans="1:8">
       <c r="A25" s="36" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B25" s="36" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C25" s="36" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="D25" s="36" t="b">
         <v>0</v>
@@ -6113,7 +6116,7 @@
         <v>0</v>
       </c>
       <c r="F25" s="37" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="G25" s="36" t="s">
         <v>11</v>
@@ -6124,13 +6127,13 @@
     </row>
     <row r="26" ht="78" spans="1:8">
       <c r="A26" s="38" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B26" s="38" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C26" s="38" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D26" s="38" t="b">
         <v>1</v>
@@ -6139,7 +6142,7 @@
         <v>1</v>
       </c>
       <c r="F26" s="39" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="G26" s="38" t="s">
         <v>11</v>
@@ -6150,13 +6153,13 @@
     </row>
     <row r="27" ht="52" spans="1:8">
       <c r="A27" s="36" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B27" s="36" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C27" s="36" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="D27" s="36" t="b">
         <v>0</v>
@@ -6165,7 +6168,7 @@
         <v>0</v>
       </c>
       <c r="F27" s="37" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="G27" s="36" t="s">
         <v>11</v>
@@ -6176,13 +6179,13 @@
     </row>
     <row r="28" ht="65" spans="1:8">
       <c r="A28" s="38" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B28" s="38" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C28" s="38" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="D28" s="38" t="b">
         <v>0</v>
@@ -6191,7 +6194,7 @@
         <v>0</v>
       </c>
       <c r="F28" s="39" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="G28" s="38" t="s">
         <v>11</v>
@@ -6202,13 +6205,13 @@
     </row>
     <row r="29" ht="26" spans="1:8">
       <c r="A29" s="36" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B29" s="36" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C29" s="36" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="D29" s="36" t="b">
         <v>0</v>
@@ -6217,7 +6220,7 @@
         <v>0</v>
       </c>
       <c r="F29" s="37" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="G29" s="36" t="s">
         <v>11</v>
@@ -6228,13 +6231,13 @@
     </row>
     <row r="30" ht="39" spans="1:8">
       <c r="A30" s="38" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B30" s="38" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C30" s="38" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="D30" s="38" t="b">
         <v>0</v>
@@ -6243,7 +6246,7 @@
         <v>0</v>
       </c>
       <c r="F30" s="39" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="G30" s="38" t="s">
         <v>11</v>
@@ -6254,13 +6257,13 @@
     </row>
     <row r="31" ht="26" spans="1:8">
       <c r="A31" s="36" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B31" s="36" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C31" s="36" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D31" s="36" t="b">
         <v>0</v>
@@ -6269,7 +6272,7 @@
         <v>0</v>
       </c>
       <c r="F31" s="37" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="G31" s="36" t="s">
         <v>11</v>
@@ -6280,13 +6283,13 @@
     </row>
     <row r="32" ht="26" spans="1:8">
       <c r="A32" s="38" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B32" s="38" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C32" s="38" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="D32" s="38" t="b">
         <v>0</v>
@@ -6295,7 +6298,7 @@
         <v>0</v>
       </c>
       <c r="F32" s="39" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="G32" s="38" t="s">
         <v>11</v>
@@ -6306,13 +6309,13 @@
     </row>
     <row r="33" ht="39" spans="1:8">
       <c r="A33" s="36" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B33" s="36" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C33" s="36" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="D33" s="36" t="b">
         <v>0</v>
@@ -6321,7 +6324,7 @@
         <v>0</v>
       </c>
       <c r="F33" s="37" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="G33" s="36" t="s">
         <v>11</v>
@@ -6332,13 +6335,13 @@
     </row>
     <row r="34" spans="1:8">
       <c r="A34" s="38" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B34" s="38" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C34" s="38" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="D34" s="38" t="b">
         <v>0</v>
@@ -6347,7 +6350,7 @@
         <v>0</v>
       </c>
       <c r="F34" s="39" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="G34" s="38" t="s">
         <v>11</v>
@@ -6358,13 +6361,13 @@
     </row>
     <row r="35" ht="130" spans="1:8">
       <c r="A35" s="36" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B35" s="36" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C35" s="36" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="D35" s="36" t="b">
         <v>0</v>
@@ -6373,7 +6376,7 @@
         <v>0</v>
       </c>
       <c r="F35" s="37" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="G35" s="36" t="s">
         <v>11</v>
@@ -6384,13 +6387,13 @@
     </row>
     <row r="36" spans="1:8">
       <c r="A36" s="38" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B36" s="38" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C36" s="38" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="D36" s="38" t="b">
         <v>0</v>
@@ -6399,7 +6402,7 @@
         <v>0</v>
       </c>
       <c r="F36" s="39" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="G36" s="38" t="s">
         <v>11</v>
@@ -6410,13 +6413,13 @@
     </row>
     <row r="37" spans="1:8">
       <c r="A37" s="36" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B37" s="36" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C37" s="36" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="D37" s="36" t="b">
         <v>0</v>
@@ -6425,7 +6428,7 @@
         <v>0</v>
       </c>
       <c r="F37" s="37" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="G37" s="36" t="s">
         <v>11</v>
@@ -6436,13 +6439,13 @@
     </row>
     <row r="38" ht="39" spans="1:8">
       <c r="A38" s="38" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B38" s="38" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C38" s="38" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D38" s="38" t="b">
         <v>0</v>
@@ -6451,7 +6454,7 @@
         <v>0</v>
       </c>
       <c r="F38" s="39" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="G38" s="38" t="s">
         <v>11</v>
@@ -6462,13 +6465,13 @@
     </row>
     <row r="39" ht="26" spans="1:8">
       <c r="A39" s="36" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B39" s="36" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C39" s="36" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="D39" s="36" t="b">
         <v>0</v>
@@ -6477,7 +6480,7 @@
         <v>0</v>
       </c>
       <c r="F39" s="37" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="G39" s="36" t="s">
         <v>11</v>
@@ -6488,13 +6491,13 @@
     </row>
     <row r="40" spans="1:8">
       <c r="A40" s="38" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B40" s="38" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C40" s="38" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="D40" s="38" t="b">
         <v>0</v>
@@ -6503,7 +6506,7 @@
         <v>0</v>
       </c>
       <c r="F40" s="39" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="G40" s="38" t="s">
         <v>11</v>
@@ -6514,13 +6517,13 @@
     </row>
     <row r="41" ht="26" spans="1:8">
       <c r="A41" s="36" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B41" s="36" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C41" s="36" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="D41" s="36" t="b">
         <v>0</v>
@@ -6529,7 +6532,7 @@
         <v>0</v>
       </c>
       <c r="F41" s="37" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G41" s="36" t="s">
         <v>11</v>
@@ -6540,13 +6543,13 @@
     </row>
     <row r="42" ht="26" spans="1:8">
       <c r="A42" s="38" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B42" s="38" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C42" s="38" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="D42" s="38" t="b">
         <v>0</v>
@@ -6555,7 +6558,7 @@
         <v>0</v>
       </c>
       <c r="F42" s="39" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="G42" s="38" t="s">
         <v>11</v>
@@ -6566,13 +6569,13 @@
     </row>
     <row r="43" ht="26" spans="1:8">
       <c r="A43" s="36" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B43" s="36" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C43" s="36" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="D43" s="36" t="b">
         <v>0</v>
@@ -6581,7 +6584,7 @@
         <v>0</v>
       </c>
       <c r="F43" s="37" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="G43" s="36" t="s">
         <v>11</v>
@@ -6592,13 +6595,13 @@
     </row>
     <row r="44" ht="39" spans="1:8">
       <c r="A44" s="38" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B44" s="38" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C44" s="38" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="D44" s="38" t="b">
         <v>0</v>
@@ -6607,7 +6610,7 @@
         <v>0</v>
       </c>
       <c r="F44" s="39" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="G44" s="38" t="s">
         <v>11</v>
@@ -6618,13 +6621,13 @@
     </row>
     <row r="45" ht="26" spans="1:8">
       <c r="A45" s="36" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B45" s="36" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C45" s="36" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="D45" s="36" t="b">
         <v>0</v>
@@ -6633,7 +6636,7 @@
         <v>0</v>
       </c>
       <c r="F45" s="37" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="G45" s="36" t="s">
         <v>11</v>
@@ -6644,13 +6647,13 @@
     </row>
     <row r="46" ht="26" spans="1:8">
       <c r="A46" s="38" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B46" s="38" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C46" s="38" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="D46" s="38" t="b">
         <v>0</v>
@@ -6659,7 +6662,7 @@
         <v>0</v>
       </c>
       <c r="F46" s="39" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="G46" s="38" t="s">
         <v>11</v>
@@ -6670,13 +6673,13 @@
     </row>
     <row r="47" ht="52" spans="1:8">
       <c r="A47" s="36" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B47" s="36" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C47" s="36" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="D47" s="36" t="b">
         <v>0</v>
@@ -6685,7 +6688,7 @@
         <v>0</v>
       </c>
       <c r="F47" s="37" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="G47" s="36" t="s">
         <v>11</v>
@@ -6696,13 +6699,13 @@
     </row>
     <row r="48" ht="65" spans="1:8">
       <c r="A48" s="38" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B48" s="38" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C48" s="38" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="D48" s="38" t="b">
         <v>0</v>
@@ -6711,7 +6714,7 @@
         <v>0</v>
       </c>
       <c r="F48" s="39" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="G48" s="38" t="s">
         <v>11</v>
@@ -6722,13 +6725,13 @@
     </row>
     <row r="49" spans="1:8">
       <c r="A49" s="36" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B49" s="36" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C49" s="36" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="D49" s="36" t="b">
         <v>0</v>
@@ -6737,7 +6740,7 @@
         <v>0</v>
       </c>
       <c r="F49" s="37" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G49" s="36" t="s">
         <v>11</v>
@@ -6748,13 +6751,13 @@
     </row>
     <row r="50" ht="39" spans="1:8">
       <c r="A50" s="38" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B50" s="38" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C50" s="38" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="D50" s="38" t="b">
         <v>0</v>
@@ -6763,7 +6766,7 @@
         <v>0</v>
       </c>
       <c r="F50" s="39" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="G50" s="38" t="s">
         <v>11</v>
@@ -6774,13 +6777,13 @@
     </row>
     <row r="51" spans="1:8">
       <c r="A51" s="36" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B51" s="36" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C51" s="36" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D51" s="36" t="b">
         <v>0</v>
@@ -6789,7 +6792,7 @@
         <v>0</v>
       </c>
       <c r="F51" s="37" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="G51" s="36" t="s">
         <v>11</v>
@@ -6800,13 +6803,13 @@
     </row>
     <row r="52" ht="26" spans="1:8">
       <c r="A52" s="38" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B52" s="38" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="C52" s="38" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D52" s="38" t="b">
         <v>0</v>
@@ -6815,7 +6818,7 @@
         <v>0</v>
       </c>
       <c r="F52" s="39" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="G52" s="38" t="s">
         <v>11</v>
@@ -6826,13 +6829,13 @@
     </row>
     <row r="53" ht="26" spans="1:8">
       <c r="A53" s="36" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B53" s="36" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C53" s="36" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D53" s="36" t="b">
         <v>0</v>
@@ -6841,7 +6844,7 @@
         <v>0</v>
       </c>
       <c r="F53" s="37" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="G53" s="36" t="s">
         <v>11</v>
@@ -6852,13 +6855,13 @@
     </row>
     <row r="54" ht="26" spans="1:8">
       <c r="A54" s="38" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B54" s="38" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C54" s="38" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D54" s="38" t="b">
         <v>0</v>
@@ -6867,7 +6870,7 @@
         <v>0</v>
       </c>
       <c r="F54" s="39" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="G54" s="38" t="s">
         <v>11</v>
@@ -6878,13 +6881,13 @@
     </row>
     <row r="55" ht="39" spans="1:8">
       <c r="A55" s="36" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B55" s="36" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="C55" s="36" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D55" s="36" t="b">
         <v>0</v>
@@ -6893,7 +6896,7 @@
         <v>0</v>
       </c>
       <c r="F55" s="37" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="G55" s="36" t="s">
         <v>11</v>
@@ -6904,13 +6907,13 @@
     </row>
     <row r="56" ht="26" spans="1:8">
       <c r="A56" s="38" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B56" s="38" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C56" s="38" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D56" s="38" t="b">
         <v>0</v>
@@ -6919,7 +6922,7 @@
         <v>0</v>
       </c>
       <c r="F56" s="39" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="G56" s="38" t="s">
         <v>11</v>
@@ -6930,13 +6933,13 @@
     </row>
     <row r="57" ht="26" spans="1:8">
       <c r="A57" s="36" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B57" s="36" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C57" s="36" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D57" s="36" t="b">
         <v>0</v>
@@ -6945,7 +6948,7 @@
         <v>0</v>
       </c>
       <c r="F57" s="37" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="G57" s="36" t="s">
         <v>11</v>
@@ -6956,13 +6959,13 @@
     </row>
     <row r="58" ht="26" spans="1:8">
       <c r="A58" s="38" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B58" s="38" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="C58" s="38" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D58" s="38" t="b">
         <v>0</v>
@@ -6971,7 +6974,7 @@
         <v>0</v>
       </c>
       <c r="F58" s="39" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="G58" s="38" t="s">
         <v>11</v>
@@ -6982,13 +6985,13 @@
     </row>
     <row r="59" ht="30" spans="1:8">
       <c r="A59" s="36" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B59" s="36" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C59" s="36" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="D59" s="36" t="b">
         <v>0</v>
@@ -6997,7 +7000,7 @@
         <v>0</v>
       </c>
       <c r="F59" s="37" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="G59" s="36" t="s">
         <v>11</v>
@@ -7008,13 +7011,13 @@
     </row>
     <row r="60" spans="1:8">
       <c r="A60" s="38" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B60" s="38" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="C60" s="38" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="D60" s="38" t="b">
         <v>0</v>
@@ -7023,7 +7026,7 @@
         <v>0</v>
       </c>
       <c r="F60" s="39" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="G60" s="38" t="s">
         <v>11</v>
@@ -7034,13 +7037,13 @@
     </row>
     <row r="61" ht="52" spans="1:8">
       <c r="A61" s="36" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B61" s="36" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C61" s="36" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="D61" s="36" t="b">
         <v>0</v>
@@ -7049,7 +7052,7 @@
         <v>0</v>
       </c>
       <c r="F61" s="37" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="G61" s="36" t="s">
         <v>11</v>
@@ -7060,13 +7063,13 @@
     </row>
     <row r="62" ht="26" spans="1:8">
       <c r="A62" s="38" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B62" s="38" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C62" s="38" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="D62" s="38" t="b">
         <v>0</v>
@@ -7075,7 +7078,7 @@
         <v>0</v>
       </c>
       <c r="F62" s="39" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="G62" s="38" t="s">
         <v>11</v>
@@ -7086,13 +7089,13 @@
     </row>
     <row r="63" ht="39" spans="1:8">
       <c r="A63" s="36" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B63" s="36" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C63" s="36" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="D63" s="36" t="b">
         <v>0</v>
@@ -7101,7 +7104,7 @@
         <v>0</v>
       </c>
       <c r="F63" s="37" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="G63" s="36" t="s">
         <v>11</v>
@@ -7112,13 +7115,13 @@
     </row>
     <row r="64" spans="1:8">
       <c r="A64" s="38" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B64" s="38" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="C64" s="38" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="D64" s="38" t="b">
         <v>0</v>
@@ -7127,7 +7130,7 @@
         <v>0</v>
       </c>
       <c r="F64" s="39" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="G64" s="38" t="s">
         <v>11</v>
@@ -7138,13 +7141,13 @@
     </row>
     <row r="65" ht="26" spans="1:8">
       <c r="A65" s="36" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B65" s="36" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C65" s="36" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D65" s="36" t="b">
         <v>0</v>
@@ -7153,7 +7156,7 @@
         <v>0</v>
       </c>
       <c r="F65" s="37" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="G65" s="36" t="s">
         <v>11</v>
@@ -7164,13 +7167,13 @@
     </row>
     <row r="66" ht="39" spans="1:8">
       <c r="A66" s="38" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B66" s="38" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C66" s="38" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="D66" s="38" t="b">
         <v>0</v>
@@ -7179,7 +7182,7 @@
         <v>0</v>
       </c>
       <c r="F66" s="39" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="G66" s="38" t="s">
         <v>11</v>
@@ -7190,13 +7193,13 @@
     </row>
     <row r="67" ht="52" spans="1:8">
       <c r="A67" s="36" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B67" s="36" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="C67" s="36" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="D67" s="36" t="b">
         <v>0</v>
@@ -7205,7 +7208,7 @@
         <v>0</v>
       </c>
       <c r="F67" s="37" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="G67" s="36" t="s">
         <v>11</v>
@@ -7216,13 +7219,13 @@
     </row>
     <row r="68" ht="47" spans="1:8">
       <c r="A68" s="32" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B68" s="32" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="C68" s="32" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="D68" s="32" t="b">
         <v>1</v>
@@ -7231,7 +7234,7 @@
         <v>2</v>
       </c>
       <c r="F68" s="33" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="G68" s="32" t="s">
         <v>11</v>
@@ -7242,13 +7245,13 @@
     </row>
     <row r="69" ht="26" spans="1:8">
       <c r="A69" s="34" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B69" s="34" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C69" s="34" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="D69" s="34" t="b">
         <v>0</v>
@@ -7257,7 +7260,7 @@
         <v>0</v>
       </c>
       <c r="F69" s="35" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="G69" s="34" t="s">
         <v>11</v>
@@ -7283,7 +7286,7 @@
         <v>0</v>
       </c>
       <c r="F70" s="33" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G70" s="32" t="s">
         <v>11</v>
@@ -7294,13 +7297,13 @@
     </row>
     <row r="71" ht="91" spans="1:8">
       <c r="A71" s="34" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B71" s="34" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C71" s="34" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="D71" s="34" t="b">
         <v>0</v>
@@ -7309,7 +7312,7 @@
         <v>0</v>
       </c>
       <c r="F71" s="35" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="G71" s="34" t="s">
         <v>11</v>
@@ -7320,13 +7323,13 @@
     </row>
     <row r="72" ht="39" spans="1:8">
       <c r="A72" s="32" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B72" s="32" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="C72" s="32" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="D72" s="32" t="b">
         <v>0</v>
@@ -7335,7 +7338,7 @@
         <v>0</v>
       </c>
       <c r="F72" s="33" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="G72" s="32" t="s">
         <v>11</v>
@@ -7346,13 +7349,13 @@
     </row>
     <row r="73" spans="1:8">
       <c r="A73" s="34" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B73" s="34" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C73" s="34" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="D73" s="34" t="b">
         <v>0</v>
@@ -7361,7 +7364,7 @@
         <v>0</v>
       </c>
       <c r="F73" s="35" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="G73" s="34" t="s">
         <v>11</v>
@@ -7372,13 +7375,13 @@
     </row>
     <row r="74" ht="17" spans="1:8">
       <c r="A74" s="32" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B74" s="32" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C74" s="32" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="D74" s="32" t="b">
         <v>0</v>
@@ -7387,7 +7390,7 @@
         <v>0</v>
       </c>
       <c r="F74" s="33" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="G74" s="32" t="s">
         <v>11</v>
@@ -7398,13 +7401,13 @@
     </row>
     <row r="75" spans="1:8">
       <c r="A75" s="34" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B75" s="34" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C75" s="34" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="D75" s="34" t="b">
         <v>0</v>
@@ -7413,7 +7416,7 @@
         <v>0</v>
       </c>
       <c r="F75" s="35" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="G75" s="34" t="s">
         <v>11</v>
@@ -7424,13 +7427,13 @@
     </row>
     <row r="76" spans="1:8">
       <c r="A76" s="32" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B76" s="32" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="C76" s="32" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D76" s="32" t="b">
         <v>0</v>
@@ -7439,7 +7442,7 @@
         <v>0</v>
       </c>
       <c r="F76" s="33" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G76" s="32" t="s">
         <v>11</v>
@@ -7450,13 +7453,13 @@
     </row>
     <row r="77" ht="26" spans="1:8">
       <c r="A77" s="34" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B77" s="34" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C77" s="34" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="D77" s="34" t="b">
         <v>0</v>
@@ -7465,7 +7468,7 @@
         <v>0</v>
       </c>
       <c r="F77" s="35" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="G77" s="34" t="s">
         <v>11</v>
@@ -7476,13 +7479,13 @@
     </row>
     <row r="78" ht="26" spans="1:8">
       <c r="A78" s="32" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B78" s="32" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="C78" s="32" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="D78" s="32" t="b">
         <v>0</v>
@@ -7491,7 +7494,7 @@
         <v>0</v>
       </c>
       <c r="F78" s="33" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="G78" s="32" t="s">
         <v>11</v>
@@ -7502,13 +7505,13 @@
     </row>
     <row r="79" ht="65" spans="1:8">
       <c r="A79" s="34" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B79" s="34" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C79" s="34" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="D79" s="34" t="b">
         <v>0</v>
@@ -7517,7 +7520,7 @@
         <v>0</v>
       </c>
       <c r="F79" s="35" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="G79" s="34" t="s">
         <v>11</v>
@@ -7528,13 +7531,13 @@
     </row>
     <row r="80" ht="26" spans="1:8">
       <c r="A80" s="32" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B80" s="32" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C80" s="32" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="D80" s="32" t="b">
         <v>0</v>
@@ -7543,7 +7546,7 @@
         <v>0</v>
       </c>
       <c r="F80" s="33" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="G80" s="32" t="s">
         <v>11</v>
@@ -7554,13 +7557,13 @@
     </row>
     <row r="81" ht="26" spans="1:8">
       <c r="A81" s="34" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B81" s="34" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C81" s="34" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="D81" s="34" t="b">
         <v>0</v>
@@ -7569,7 +7572,7 @@
         <v>0</v>
       </c>
       <c r="F81" s="35" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="G81" s="34" t="s">
         <v>11</v>
@@ -7580,13 +7583,13 @@
     </row>
     <row r="82" ht="26" spans="1:8">
       <c r="A82" s="32" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B82" s="32" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="C82" s="32" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="D82" s="32" t="b">
         <v>0</v>
@@ -7595,7 +7598,7 @@
         <v>0</v>
       </c>
       <c r="F82" s="33" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="G82" s="32" t="s">
         <v>11</v>
@@ -7606,13 +7609,13 @@
     </row>
     <row r="83" spans="1:8">
       <c r="A83" s="34" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B83" s="34" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="C83" s="34" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="D83" s="34" t="b">
         <v>0</v>
@@ -7621,7 +7624,7 @@
         <v>0</v>
       </c>
       <c r="F83" s="35" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="G83" s="34" t="s">
         <v>11</v>
@@ -7632,13 +7635,13 @@
     </row>
     <row r="84" spans="1:8">
       <c r="A84" s="32" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B84" s="32" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="C84" s="32" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="D84" s="32" t="b">
         <v>0</v>
@@ -7647,7 +7650,7 @@
         <v>0</v>
       </c>
       <c r="F84" s="33" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="G84" s="32" t="s">
         <v>11</v>
@@ -7658,13 +7661,13 @@
     </row>
     <row r="85" ht="26" spans="1:8">
       <c r="A85" s="34" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B85" s="34" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C85" s="34" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="D85" s="34" t="b">
         <v>0</v>
@@ -7673,7 +7676,7 @@
         <v>0</v>
       </c>
       <c r="F85" s="35" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="G85" s="34" t="s">
         <v>11</v>
@@ -7684,13 +7687,13 @@
     </row>
     <row r="86" ht="65" spans="1:8">
       <c r="A86" s="32" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B86" s="32" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="C86" s="32" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="D86" s="32" t="b">
         <v>0</v>
@@ -7699,7 +7702,7 @@
         <v>0</v>
       </c>
       <c r="F86" s="33" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="G86" s="32" t="s">
         <v>11</v>
@@ -7710,13 +7713,13 @@
     </row>
     <row r="87" ht="44" customHeight="1" spans="1:8">
       <c r="A87" s="34" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B87" s="34" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="C87" s="34" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="D87" s="34" t="b">
         <v>1</v>
@@ -7725,7 +7728,7 @@
         <v>1</v>
       </c>
       <c r="F87" s="35" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="G87" s="34" t="s">
         <v>11</v>
@@ -7736,13 +7739,13 @@
     </row>
     <row r="88" ht="40" customHeight="1" spans="1:8">
       <c r="A88" s="32" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B88" s="32" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="C88" s="32" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D88" s="32" t="b">
         <v>0</v>
@@ -7751,7 +7754,7 @@
         <v>0</v>
       </c>
       <c r="F88" s="33" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="G88" s="32" t="s">
         <v>11</v>
@@ -7797,1276 +7800,1276 @@
         <v>5</v>
       </c>
       <c r="E1" s="12" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="F1" s="13" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="G1" s="13" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="14" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B2" s="15" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="C2" s="16" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="D2" s="16" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="E2" s="16">
         <v>40</v>
       </c>
       <c r="F2" s="17" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="G2" s="17" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3" s="18" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B3" s="19" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="C3" s="20" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="D3" s="20" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="E3" s="20">
         <v>8</v>
       </c>
       <c r="F3" s="21" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="G3" s="21" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4" s="14" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B4" s="15" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C4" s="16" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="D4" s="16" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="E4" s="16">
         <v>30</v>
       </c>
       <c r="F4" s="17" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="G4" s="17" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5" s="18" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B5" s="19" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="C5" s="20" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="D5" s="20"/>
       <c r="E5" s="20">
         <v>3</v>
       </c>
       <c r="F5" s="21" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="G5" s="21" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6" s="18" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B6" s="19" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C6" s="20" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="D6" s="20" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="E6" s="20">
         <v>10</v>
       </c>
       <c r="F6" s="21" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="G6" s="21" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7" s="14" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B7" s="15" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="C7" s="16" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D7" s="16" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="E7" s="16">
         <v>25</v>
       </c>
       <c r="F7" s="17" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="G7" s="17" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8" s="18" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B8" s="19" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="C8" s="20" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="D8" s="20" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="E8" s="20">
         <v>35</v>
       </c>
       <c r="F8" s="21" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="G8" s="21" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9" s="22" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B9" s="23" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C9" s="24" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="D9" s="24" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="E9" s="24">
         <v>50</v>
       </c>
       <c r="F9" s="25" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="G9" s="25" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10" s="26" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B10" s="27" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="C10" s="28" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="D10" s="28" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="E10" s="28">
         <v>55</v>
       </c>
       <c r="F10" s="29" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="G10" s="29" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11" s="22" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B11" s="23" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="C11" s="24" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="D11" s="24" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="E11" s="24">
         <v>35</v>
       </c>
       <c r="F11" s="25" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="G11" s="25" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12" s="26" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="B12" s="27" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="C12" s="28" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="D12" s="28" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="E12" s="28">
         <v>30</v>
       </c>
       <c r="F12" s="29" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="G12" s="29" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13" s="22" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B13" s="23" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="C13" s="24" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="D13" s="24" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="E13" s="24">
         <v>40</v>
       </c>
       <c r="F13" s="25" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="G13" s="25" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14" s="26" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="B14" s="27" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="C14" s="28" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="D14" s="28" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="E14" s="28">
         <v>4</v>
       </c>
       <c r="F14" s="29" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="G14" s="29" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15" s="22" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B15" s="23" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="C15" s="24" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="D15" s="24" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="E15" s="24">
         <v>30</v>
       </c>
       <c r="F15" s="25" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="G15" s="25" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="16" spans="1:7">
       <c r="A16" s="26" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="B16" s="27" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="C16" s="28" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="D16" s="28" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="E16" s="28">
         <v>70</v>
       </c>
       <c r="F16" s="29" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="G16" s="29" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="17" spans="1:7">
       <c r="A17" s="22" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="B17" s="23" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="C17" s="24" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="D17" s="24" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="E17" s="24">
         <v>60</v>
       </c>
       <c r="F17" s="25" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="G17" s="25" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="18" spans="1:7">
       <c r="A18" s="26" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="B18" s="27" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="C18" s="28" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="D18" s="28" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="E18" s="28">
         <v>30</v>
       </c>
       <c r="F18" s="29" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="G18" s="29" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="19" spans="1:7">
       <c r="A19" s="22" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B19" s="23" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="C19" s="24" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="D19" s="24" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="E19" s="24">
         <v>30</v>
       </c>
       <c r="F19" s="25" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="G19" s="25" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="20" spans="1:7">
       <c r="A20" s="26" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="B20" s="27" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="C20" s="28" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="D20" s="28" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="E20" s="28">
         <v>30</v>
       </c>
       <c r="F20" s="29" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="G20" s="29" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="21" spans="1:7">
       <c r="A21" s="22" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="B21" s="23" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="C21" s="24" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="D21" s="24" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="E21" s="24">
         <v>20</v>
       </c>
       <c r="F21" s="25" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="G21" s="25" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="22" spans="1:7">
       <c r="A22" s="26" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="B22" s="27" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="C22" s="28" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="D22" s="28" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="E22" s="28">
         <v>100</v>
       </c>
       <c r="F22" s="29" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="G22" s="29" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="23" spans="1:7">
       <c r="A23" s="22" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="B23" s="23" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="C23" s="24" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="D23" s="24" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="E23" s="24">
         <v>10</v>
       </c>
       <c r="F23" s="25" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="G23" s="25" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="24" spans="1:7">
       <c r="A24" s="26" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="B24" s="27" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="C24" s="28" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="D24" s="28" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="E24" s="28">
         <v>20</v>
       </c>
       <c r="F24" s="29" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="G24" s="29" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
     <row r="25" spans="1:7">
       <c r="A25" s="22" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="B25" s="23" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="C25" s="24" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="D25" s="24" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="E25" s="24">
         <v>20</v>
       </c>
       <c r="F25" s="25" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="G25" s="25" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
     <row r="26" spans="1:7">
       <c r="A26" s="26" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="B26" s="27" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="C26" s="28" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="D26" s="28" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="E26" s="28">
         <v>35</v>
       </c>
       <c r="F26" s="29" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="G26" s="29" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
     <row r="27" spans="1:7">
       <c r="A27" s="22" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="B27" s="23" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="C27" s="24" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="D27" s="24" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="E27" s="24">
         <v>50</v>
       </c>
       <c r="F27" s="25" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="G27" s="25" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
     <row r="28" spans="1:7">
       <c r="A28" s="26" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="B28" s="27" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="C28" s="28" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="D28" s="28" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E28" s="28">
         <v>20</v>
       </c>
       <c r="F28" s="29" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="G28" s="29" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
     <row r="29" spans="1:7">
       <c r="A29" s="22" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="B29" s="23" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="C29" s="24" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="D29" s="24" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="E29" s="24">
         <v>5</v>
       </c>
       <c r="F29" s="25" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="G29" s="25" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="30" spans="1:7">
       <c r="A30" s="26" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="B30" s="27" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="C30" s="28" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="D30" s="28" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="E30" s="28">
         <v>20</v>
       </c>
       <c r="F30" s="29" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="G30" s="29" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
     <row r="31" spans="1:7">
       <c r="A31" s="22" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="B31" s="23" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="C31" s="24" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="D31" s="24" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="E31" s="24">
         <v>15</v>
       </c>
       <c r="F31" s="25" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="G31" s="25" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
     <row r="32" spans="1:7">
       <c r="A32" s="26" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="B32" s="27" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="C32" s="28" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="D32" s="28" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="E32" s="28">
         <v>15</v>
       </c>
       <c r="F32" s="29" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="G32" s="29" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
     <row r="33" spans="1:7">
       <c r="A33" s="22" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="B33" s="23" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="C33" s="24" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="D33" s="24" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="E33" s="24">
         <v>15</v>
       </c>
       <c r="F33" s="25" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="G33" s="25" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
     <row r="34" spans="1:7">
       <c r="A34" s="26" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="B34" s="27" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="C34" s="28" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="D34" s="28" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="E34" s="28">
         <v>5</v>
       </c>
       <c r="F34" s="29" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="G34" s="29" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
     <row r="35" spans="1:7">
       <c r="A35" s="22" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="B35" s="23" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="C35" s="24" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="D35" s="24" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="E35" s="24">
         <v>25</v>
       </c>
       <c r="F35" s="25" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="G35" s="25" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
     <row r="36" spans="1:7">
       <c r="A36" s="26" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="B36" s="27" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="C36" s="28" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="D36" s="28" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="E36" s="28">
         <v>10</v>
       </c>
       <c r="F36" s="29" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="G36" s="29" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
     <row r="37" spans="1:7">
       <c r="A37" s="22" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="B37" s="23" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="C37" s="24" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="D37" s="24" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="E37" s="24">
         <v>8</v>
       </c>
       <c r="F37" s="25" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="G37" s="25" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="38" spans="1:7">
       <c r="A38" s="26" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="B38" s="27" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="C38" s="28" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="D38" s="28" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="E38" s="28">
         <v>100</v>
       </c>
       <c r="F38" s="29" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="G38" s="29" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
     <row r="39" spans="1:7">
       <c r="A39" s="22" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="B39" s="23" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="C39" s="24" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="D39" s="24" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="E39" s="24">
         <v>20</v>
       </c>
       <c r="F39" s="25" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="G39" s="25" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
     <row r="40" spans="1:7">
       <c r="A40" s="18" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="B40" s="19" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="C40" s="20" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="D40" s="20" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="E40" s="20">
         <v>10</v>
       </c>
       <c r="F40" s="21" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="G40" s="21" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
     <row r="41" spans="1:7">
       <c r="A41" s="14" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="B41" s="15" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="C41" s="16" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="D41" s="16" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="E41" s="16">
         <v>10</v>
       </c>
       <c r="F41" s="17" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="G41" s="17" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
     <row r="42" spans="1:7">
       <c r="A42" s="18" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="B42" s="19" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="C42" s="20" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="D42" s="20" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="E42" s="20">
         <v>12</v>
       </c>
       <c r="F42" s="21" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="G42" s="21" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
     <row r="43" spans="1:7">
       <c r="A43" s="14" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="B43" s="15" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="C43" s="16" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="D43" s="16" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="E43" s="16">
         <v>15</v>
       </c>
       <c r="F43" s="17" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="G43" s="17" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
     <row r="44" spans="1:7">
       <c r="A44" s="18" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="B44" s="19" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="C44" s="20" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="D44" s="20" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="E44" s="20">
         <v>25</v>
       </c>
       <c r="F44" s="21" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="G44" s="21" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
     <row r="45" spans="1:7">
       <c r="A45" s="14" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="B45" s="15" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="C45" s="16" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="D45" s="16" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="E45" s="16">
         <v>3</v>
       </c>
       <c r="F45" s="17" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="G45" s="17" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="46" spans="1:7">
       <c r="A46" s="18" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="B46" s="19" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="C46" s="20" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="D46" s="20" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="E46" s="20">
         <v>2</v>
       </c>
       <c r="F46" s="21" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="G46" s="21" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="47" spans="1:7">
       <c r="A47" s="14" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="B47" s="15" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="C47" s="16" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="D47" s="16" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="E47" s="16">
         <v>6</v>
       </c>
       <c r="F47" s="17" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="G47" s="17" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="48" spans="1:7">
       <c r="A48" s="18" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="B48" s="19" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="C48" s="20" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="D48" s="20" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="E48" s="20">
         <v>4</v>
       </c>
       <c r="F48" s="21" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="G48" s="21" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="49" spans="1:7">
       <c r="A49" s="14" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="B49" s="15" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="C49" s="16" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="D49" s="16" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="E49" s="16">
         <v>3</v>
       </c>
       <c r="F49" s="17" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="G49" s="17" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="50" spans="1:7">
       <c r="A50" s="18" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="B50" s="19" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="C50" s="20" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="D50" s="20" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="E50" s="20">
         <v>4</v>
       </c>
       <c r="F50" s="21" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="G50" s="21" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="51" spans="1:7">
       <c r="A51" s="14" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="B51" s="15" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="C51" s="16" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="D51" s="16" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="E51" s="16">
         <v>4</v>
       </c>
       <c r="F51" s="17" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="G51" s="17" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="52" spans="1:7">
       <c r="A52" s="18" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="B52" s="19" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="C52" s="20" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="D52" s="20" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="E52" s="20">
         <v>6</v>
       </c>
       <c r="F52" s="21" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="G52" s="21" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="53" spans="1:7">
       <c r="A53" s="14" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="B53" s="15" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="C53" s="16" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="D53" s="16" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="E53" s="16">
         <v>2</v>
       </c>
       <c r="F53" s="17" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="G53" s="17" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="54" spans="1:7">
       <c r="A54" s="18" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="B54" s="19" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="C54" s="20" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="D54" s="20" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="E54" s="20">
         <v>2</v>
       </c>
       <c r="F54" s="21" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="G54" s="21" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="55" spans="1:7">
       <c r="A55" s="14" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="B55" s="15" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="C55" s="16" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="D55" s="16" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="E55" s="16">
         <v>4</v>
       </c>
       <c r="F55" s="17" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="G55" s="17" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="56" spans="1:7">
       <c r="A56" s="18" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="B56" s="19" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="C56" s="20" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="D56" s="20" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="E56" s="20">
         <v>3</v>
       </c>
       <c r="F56" s="21" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="G56" s="21" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
   </sheetData>
@@ -9105,1424 +9108,1424 @@
         <v>5</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="2" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="D2" s="4"/>
       <c r="E2" s="5">
         <v>25</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="6" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="E3" s="5">
         <v>12</v>
       </c>
       <c r="F3" s="7" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="8" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="D4" s="4"/>
       <c r="E4" s="5">
         <v>20</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="6" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="D5" s="4"/>
       <c r="E5" s="5">
         <v>40</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="6" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="E6" s="5">
         <v>20</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="6" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="E7" s="5">
         <v>15</v>
       </c>
       <c r="F7" s="7" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="6" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="E8" s="5">
         <v>40</v>
       </c>
       <c r="F8" s="7" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="6" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="E9" s="5">
         <v>15</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="6" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="E10" s="5">
         <v>15</v>
       </c>
       <c r="F10" s="7" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="6" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="E11" s="5">
         <v>30</v>
       </c>
       <c r="F11" s="7" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="6" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="E12" s="5">
         <v>15</v>
       </c>
       <c r="F12" s="7" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="6" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="E13" s="5">
         <v>15</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="6" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="E14" s="5">
         <v>20</v>
       </c>
       <c r="F14" s="7" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="6" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="E15" s="5">
         <v>20</v>
       </c>
       <c r="F15" s="7" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="6" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="E16" s="5">
         <v>15</v>
       </c>
       <c r="F16" s="7" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
     </row>
     <row r="17" spans="1:6">
       <c r="A17" s="6" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="E17" s="5">
         <v>20</v>
       </c>
       <c r="F17" s="7" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
     </row>
     <row r="18" spans="1:6">
       <c r="A18" s="6" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="E18" s="5">
         <v>12</v>
       </c>
       <c r="F18" s="7" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
     </row>
     <row r="19" spans="1:6">
       <c r="A19" s="6" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="E19" s="5">
         <v>15</v>
       </c>
       <c r="F19" s="7" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
     </row>
     <row r="20" spans="1:6">
       <c r="A20" s="6" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="E20" s="5">
         <v>12</v>
       </c>
       <c r="F20" s="7" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
     </row>
     <row r="21" spans="1:6">
       <c r="A21" s="6" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="E21" s="5">
         <v>20</v>
       </c>
       <c r="F21" s="7" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
     </row>
     <row r="22" spans="1:6">
       <c r="A22" s="6" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="E22" s="5">
         <v>15</v>
       </c>
       <c r="F22" s="7" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
     </row>
     <row r="23" spans="1:6">
       <c r="A23" s="6" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="E23" s="5">
         <v>15</v>
       </c>
       <c r="F23" s="7" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
     </row>
     <row r="24" spans="1:6">
       <c r="A24" s="6" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="E24" s="5">
         <v>15</v>
       </c>
       <c r="F24" s="7" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
     </row>
     <row r="25" spans="1:6">
       <c r="A25" s="6" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="E25" s="5">
         <v>15</v>
       </c>
       <c r="F25" s="7" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
     </row>
     <row r="26" spans="1:6">
       <c r="A26" s="6" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="E26" s="5">
         <v>15</v>
       </c>
       <c r="F26" s="7" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
     </row>
     <row r="27" spans="1:6">
       <c r="A27" s="6" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="E27" s="5">
         <v>15</v>
       </c>
       <c r="F27" s="7" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
     </row>
     <row r="28" spans="1:6">
       <c r="A28" s="6" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="E28" s="5">
         <v>3</v>
       </c>
       <c r="F28" s="7" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
     </row>
     <row r="29" spans="1:6">
       <c r="A29" s="6" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="E29" s="5">
         <v>18</v>
       </c>
       <c r="F29" s="7" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
     </row>
     <row r="30" spans="1:6">
       <c r="A30" s="6" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="D30" s="5" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="E30" s="5">
         <v>15</v>
       </c>
       <c r="F30" s="7" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
     </row>
     <row r="31" spans="1:6">
       <c r="A31" s="6" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="E31" s="5">
         <v>15</v>
       </c>
       <c r="F31" s="7" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
     </row>
     <row r="32" spans="1:6">
       <c r="A32" s="6" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="E32" s="5">
         <v>15</v>
       </c>
       <c r="F32" s="7" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
     </row>
     <row r="33" spans="1:6">
       <c r="A33" s="6" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="E33" s="5">
         <v>18</v>
       </c>
       <c r="F33" s="7" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
     </row>
     <row r="34" spans="1:6">
       <c r="A34" s="6" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="E34" s="5">
         <v>20</v>
       </c>
       <c r="F34" s="7" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
     </row>
     <row r="35" spans="1:6">
       <c r="A35" s="6" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="D35" s="5" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="E35" s="5">
         <v>15</v>
       </c>
       <c r="F35" s="7" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
     </row>
     <row r="36" spans="1:6">
       <c r="A36" s="6" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="D36" s="5" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="E36" s="5">
         <v>18</v>
       </c>
       <c r="F36" s="7" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
     </row>
     <row r="37" spans="1:6">
       <c r="A37" s="6" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="B37" s="6" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="D37" s="5" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="E37" s="5">
         <v>15</v>
       </c>
       <c r="F37" s="7" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
     </row>
     <row r="38" spans="1:6">
       <c r="A38" s="6" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="D38" s="5" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="E38" s="5">
         <v>15</v>
       </c>
       <c r="F38" s="7" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
     </row>
     <row r="39" spans="1:6">
       <c r="A39" s="6" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="B39" s="6" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="D39" s="5" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="E39" s="5">
         <v>15</v>
       </c>
       <c r="F39" s="7" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
     </row>
     <row r="40" spans="1:6">
       <c r="A40" s="6" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="B40" s="6" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="D40" s="5" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="E40" s="5">
         <v>15</v>
       </c>
       <c r="F40" s="7" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
     </row>
     <row r="41" spans="1:6">
       <c r="A41" s="6" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="B41" s="6" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="D41" s="5" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="E41" s="5">
         <v>15</v>
       </c>
       <c r="F41" s="7" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
     </row>
     <row r="42" spans="1:6">
       <c r="A42" s="6" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="B42" s="6" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="D42" s="5" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="E42" s="5">
         <v>15</v>
       </c>
       <c r="F42" s="7" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
     </row>
     <row r="43" spans="1:6">
       <c r="A43" s="6" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="B43" s="6" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="D43" s="5" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="E43" s="5">
         <v>18</v>
       </c>
       <c r="F43" s="7" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
     </row>
     <row r="44" spans="1:6">
       <c r="A44" s="6" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="B44" s="6" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="D44" s="5" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="E44" s="5">
         <v>15</v>
       </c>
       <c r="F44" s="7" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
     </row>
     <row r="45" spans="1:6">
       <c r="A45" s="6" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="B45" s="6" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="D45" s="5" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="E45" s="5">
         <v>10000000</v>
       </c>
       <c r="F45" s="7" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
     </row>
     <row r="46" spans="1:6">
       <c r="A46" s="6" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="B46" s="6" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="D46" s="5" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="E46" s="5">
         <v>15</v>
       </c>
       <c r="F46" s="7" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
     </row>
     <row r="47" spans="1:6">
       <c r="A47" s="6" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="B47" s="6" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="D47" s="5" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="E47" s="5">
         <v>15</v>
       </c>
       <c r="F47" s="7" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
     </row>
     <row r="48" spans="1:6">
       <c r="A48" s="6" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="B48" s="6" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="D48" s="5" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="E48" s="5">
         <v>12</v>
       </c>
       <c r="F48" s="7" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
     </row>
     <row r="49" spans="1:6">
       <c r="A49" s="6" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="B49" s="6" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="D49" s="5" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="E49" s="5">
         <v>15</v>
       </c>
       <c r="F49" s="7" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
     </row>
     <row r="50" spans="1:6">
       <c r="A50" s="6" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="B50" s="6" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="D50" s="5" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="E50" s="5">
         <v>40</v>
       </c>
       <c r="F50" s="7" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
     </row>
     <row r="51" spans="1:6">
       <c r="A51" s="6" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="B51" s="6" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="D51" s="5" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="E51" s="5">
         <v>50</v>
       </c>
       <c r="F51" s="7" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
     </row>
     <row r="52" spans="1:6">
       <c r="A52" s="6" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="B52" s="6" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="C52" s="5" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="D52" s="5" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="E52" s="5">
         <v>18</v>
       </c>
       <c r="F52" s="7" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
     </row>
     <row r="53" spans="1:6">
       <c r="A53" s="6" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="B53" s="6" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="C53" s="5" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="D53" s="5" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="E53" s="5">
         <v>15</v>
       </c>
       <c r="F53" s="7" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
     </row>
     <row r="54" spans="1:6">
       <c r="A54" s="6" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="B54" s="6" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="C54" s="5" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="D54" s="5" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="E54" s="5">
         <v>20</v>
       </c>
       <c r="F54" s="7" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
     </row>
     <row r="55" spans="1:6">
       <c r="A55" s="6" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="B55" s="6" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="C55" s="5" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="D55" s="5" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="E55" s="5">
         <v>12</v>
       </c>
       <c r="F55" s="7" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
     </row>
     <row r="56" spans="1:6">
       <c r="A56" s="6" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="B56" s="6" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="C56" s="5" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="D56" s="5" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="E56" s="5">
         <v>20</v>
       </c>
       <c r="F56" s="7" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
     </row>
     <row r="57" spans="1:6">
       <c r="A57" s="6" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="B57" s="6" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="C57" s="5" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="D57" s="5" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="E57" s="5">
         <v>20</v>
       </c>
       <c r="F57" s="7" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
     </row>
     <row r="58" spans="1:6">
       <c r="A58" s="6" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="B58" s="6" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="C58" s="5" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="D58" s="5" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="E58" s="5">
         <v>15</v>
       </c>
       <c r="F58" s="7" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
     </row>
     <row r="59" spans="1:6">
       <c r="A59" s="6" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="B59" s="6" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="C59" s="5" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="D59" s="5" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="E59" s="5">
         <v>15</v>
       </c>
       <c r="F59" s="7" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
     </row>
     <row r="60" spans="1:6">
       <c r="A60" s="6" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="B60" s="6" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="C60" s="5" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="D60" s="5" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="E60" s="5">
         <v>40</v>
       </c>
       <c r="F60" s="7" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
     </row>
     <row r="61" spans="1:6">
       <c r="A61" s="6" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="B61" s="6" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="C61" s="5" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="D61" s="5" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="E61" s="5">
         <v>15</v>
       </c>
       <c r="F61" s="7" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
     </row>
     <row r="62" spans="1:6">
       <c r="A62" s="6" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="B62" s="6" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="C62" s="5" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="D62" s="5" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="E62" s="5">
         <v>20</v>
       </c>
       <c r="F62" s="7" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
     </row>
     <row r="63" spans="1:6">
       <c r="A63" s="6" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="B63" s="6" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="C63" s="5" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="D63" s="5" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="E63" s="5">
         <v>20</v>
       </c>
       <c r="F63" s="7" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
     </row>
     <row r="64" ht="26" spans="1:6">
       <c r="A64" s="6" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="B64" s="6" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="C64" s="5" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="D64" s="5" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="E64" s="5">
         <v>15</v>
       </c>
       <c r="F64" s="7" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
     </row>
     <row r="65" spans="1:6">
       <c r="A65" s="6" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="B65" s="6" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="C65" s="5" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="D65" s="5" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="E65" s="5">
         <v>20</v>
       </c>
       <c r="F65" s="7" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
     </row>
     <row r="66" spans="1:6">
       <c r="A66" s="6" t="s">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="B66" s="6" t="s">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="C66" s="5" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="D66" s="5" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="E66" s="5">
         <v>6</v>
       </c>
       <c r="F66" s="7" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
     </row>
     <row r="67" spans="1:6">
       <c r="A67" s="6" t="s">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="B67" s="6" t="s">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="C67" s="5" t="s">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="D67" s="5" t="s">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="E67" s="5">
         <v>20</v>
       </c>
       <c r="F67" s="7" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
     </row>
     <row r="68" spans="1:6">
       <c r="A68" s="6" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="B68" s="6" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="C68" s="5" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="D68" s="5" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="E68" s="5">
         <v>18</v>
       </c>
       <c r="F68" s="7" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
     </row>
     <row r="69" spans="1:6">
       <c r="A69" s="6" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="B69" s="6" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="C69" s="5" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="D69" s="5" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="E69" s="5">
         <v>12</v>
       </c>
       <c r="F69" s="7" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
     </row>
     <row r="70" spans="1:6">
       <c r="A70" s="6" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="B70" s="6" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="C70" s="5" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="D70" s="5" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="E70" s="5">
         <v>18</v>
       </c>
       <c r="F70" s="7" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
     </row>
     <row r="71" spans="1:6">
       <c r="A71" s="6" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="B71" s="6" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="C71" s="5" t="s">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="D71" s="5" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="E71" s="5">
         <v>6</v>
       </c>
       <c r="F71" s="7" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
     </row>
     <row r="72" spans="1:6">
       <c r="A72" s="6" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="B72" s="6" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="C72" s="5" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="D72" s="5" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="E72" s="5">
         <v>15</v>
       </c>
       <c r="F72" s="7" t="s">
-        <v>851</v>
+        <v>852</v>
       </c>
     </row>
     <row r="75" spans="1:6">

--- a/Src/Assets/StreamingAssets/Common/Tables/Tables/Hero&Enemy.xlsx
+++ b/Src/Assets/StreamingAssets/Common/Tables/Tables/Hero&Enemy.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1289" uniqueCount="853">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1288" uniqueCount="852">
   <si>
     <t>Key</t>
   </si>
@@ -100,9 +100,6 @@
   </si>
   <si>
     <t>千钧棒</t>
-  </si>
-  <si>
-    <t>TURE</t>
   </si>
   <si>
     <t>你造成的伤害*3。</t>
@@ -4686,14 +4683,14 @@
       <c r="C6" s="38" t="s">
         <v>22</v>
       </c>
-      <c r="D6" s="38" t="s">
+      <c r="D6" s="38" t="b">
+        <v>0</v>
+      </c>
+      <c r="E6" s="38">
+        <v>0</v>
+      </c>
+      <c r="F6" s="39" t="s">
         <v>23</v>
-      </c>
-      <c r="E6" s="38">
-        <v>1</v>
-      </c>
-      <c r="F6" s="39" t="s">
-        <v>24</v>
       </c>
       <c r="G6" s="38" t="s">
         <v>11</v>
@@ -4704,22 +4701,22 @@
     </row>
     <row r="7" spans="1:8">
       <c r="A7" s="36" t="s">
+        <v>24</v>
+      </c>
+      <c r="B7" s="36" t="s">
+        <v>24</v>
+      </c>
+      <c r="C7" s="36" t="s">
         <v>25</v>
       </c>
-      <c r="B7" s="36" t="s">
-        <v>25</v>
-      </c>
-      <c r="C7" s="36" t="s">
+      <c r="D7" s="36" t="b">
+        <v>0</v>
+      </c>
+      <c r="E7" s="36">
+        <v>0</v>
+      </c>
+      <c r="F7" s="37" t="s">
         <v>26</v>
-      </c>
-      <c r="D7" s="36" t="b">
-        <v>0</v>
-      </c>
-      <c r="E7" s="36">
-        <v>0</v>
-      </c>
-      <c r="F7" s="37" t="s">
-        <v>27</v>
       </c>
       <c r="G7" s="36" t="s">
         <v>11</v>
@@ -4730,25 +4727,25 @@
     </row>
     <row r="8" ht="39" spans="1:8">
       <c r="A8" s="38" t="s">
+        <v>27</v>
+      </c>
+      <c r="B8" s="38" t="s">
+        <v>27</v>
+      </c>
+      <c r="C8" s="38" t="s">
         <v>28</v>
       </c>
-      <c r="B8" s="38" t="s">
-        <v>28</v>
-      </c>
-      <c r="C8" s="38" t="s">
+      <c r="D8" s="38" t="b">
+        <v>0</v>
+      </c>
+      <c r="E8" s="38">
+        <v>0</v>
+      </c>
+      <c r="F8" s="39" t="s">
         <v>29</v>
       </c>
-      <c r="D8" s="38" t="b">
-        <v>0</v>
-      </c>
-      <c r="E8" s="38">
-        <v>0</v>
-      </c>
-      <c r="F8" s="39" t="s">
+      <c r="G8" s="38" t="s">
         <v>30</v>
-      </c>
-      <c r="G8" s="38" t="s">
-        <v>31</v>
       </c>
       <c r="H8" s="38">
         <v>0</v>
@@ -4756,22 +4753,22 @@
     </row>
     <row r="9" ht="26" spans="1:8">
       <c r="A9" s="36" t="s">
+        <v>31</v>
+      </c>
+      <c r="B9" s="36" t="s">
+        <v>31</v>
+      </c>
+      <c r="C9" s="36" t="s">
         <v>32</v>
       </c>
-      <c r="B9" s="36" t="s">
-        <v>32</v>
-      </c>
-      <c r="C9" s="36" t="s">
+      <c r="D9" s="36" t="b">
+        <v>0</v>
+      </c>
+      <c r="E9" s="36">
+        <v>0</v>
+      </c>
+      <c r="F9" s="37" t="s">
         <v>33</v>
-      </c>
-      <c r="D9" s="36" t="b">
-        <v>0</v>
-      </c>
-      <c r="E9" s="36">
-        <v>0</v>
-      </c>
-      <c r="F9" s="37" t="s">
-        <v>34</v>
       </c>
       <c r="G9" s="36" t="s">
         <v>11</v>
@@ -4782,25 +4779,25 @@
     </row>
     <row r="10" ht="78" spans="1:8">
       <c r="A10" s="38" t="s">
+        <v>34</v>
+      </c>
+      <c r="B10" s="38" t="s">
+        <v>34</v>
+      </c>
+      <c r="C10" s="38" t="s">
         <v>35</v>
       </c>
-      <c r="B10" s="38" t="s">
-        <v>35</v>
-      </c>
-      <c r="C10" s="38" t="s">
+      <c r="D10" s="38" t="b">
+        <v>0</v>
+      </c>
+      <c r="E10" s="38">
+        <v>0</v>
+      </c>
+      <c r="F10" s="39" t="s">
         <v>36</v>
       </c>
-      <c r="D10" s="38" t="b">
-        <v>0</v>
-      </c>
-      <c r="E10" s="38">
-        <v>0</v>
-      </c>
-      <c r="F10" s="39" t="s">
+      <c r="G10" s="38" t="s">
         <v>37</v>
-      </c>
-      <c r="G10" s="38" t="s">
-        <v>38</v>
       </c>
       <c r="H10" s="38">
         <v>0</v>
@@ -4808,22 +4805,22 @@
     </row>
     <row r="11" ht="91" spans="1:8">
       <c r="A11" s="36" t="s">
+        <v>38</v>
+      </c>
+      <c r="B11" s="36" t="s">
+        <v>38</v>
+      </c>
+      <c r="C11" s="36" t="s">
         <v>39</v>
       </c>
-      <c r="B11" s="36" t="s">
-        <v>39</v>
-      </c>
-      <c r="C11" s="36" t="s">
+      <c r="D11" s="36" t="b">
+        <v>0</v>
+      </c>
+      <c r="E11" s="36">
+        <v>0</v>
+      </c>
+      <c r="F11" s="37" t="s">
         <v>40</v>
-      </c>
-      <c r="D11" s="36" t="b">
-        <v>0</v>
-      </c>
-      <c r="E11" s="36">
-        <v>0</v>
-      </c>
-      <c r="F11" s="37" t="s">
-        <v>41</v>
       </c>
       <c r="G11" s="36" t="s">
         <v>11</v>
@@ -4834,22 +4831,22 @@
     </row>
     <row r="12" ht="117" spans="1:8">
       <c r="A12" s="38" t="s">
+        <v>41</v>
+      </c>
+      <c r="B12" s="38" t="s">
+        <v>41</v>
+      </c>
+      <c r="C12" s="38" t="s">
         <v>42</v>
       </c>
-      <c r="B12" s="38" t="s">
-        <v>42</v>
-      </c>
-      <c r="C12" s="38" t="s">
+      <c r="D12" s="38" t="b">
+        <v>0</v>
+      </c>
+      <c r="E12" s="38">
+        <v>0</v>
+      </c>
+      <c r="F12" s="39" t="s">
         <v>43</v>
-      </c>
-      <c r="D12" s="38" t="b">
-        <v>0</v>
-      </c>
-      <c r="E12" s="38">
-        <v>0</v>
-      </c>
-      <c r="F12" s="39" t="s">
-        <v>44</v>
       </c>
       <c r="G12" s="38" t="s">
         <v>11</v>
@@ -4860,22 +4857,22 @@
     </row>
     <row r="13" ht="52" spans="1:8">
       <c r="A13" s="36" t="s">
+        <v>44</v>
+      </c>
+      <c r="B13" s="36" t="s">
+        <v>44</v>
+      </c>
+      <c r="C13" s="36" t="s">
         <v>45</v>
       </c>
-      <c r="B13" s="36" t="s">
-        <v>45</v>
-      </c>
-      <c r="C13" s="36" t="s">
+      <c r="D13" s="36" t="b">
+        <v>0</v>
+      </c>
+      <c r="E13" s="36">
+        <v>0</v>
+      </c>
+      <c r="F13" s="37" t="s">
         <v>46</v>
-      </c>
-      <c r="D13" s="36" t="b">
-        <v>0</v>
-      </c>
-      <c r="E13" s="36">
-        <v>0</v>
-      </c>
-      <c r="F13" s="37" t="s">
-        <v>47</v>
       </c>
       <c r="G13" s="36" t="s">
         <v>11</v>
@@ -4886,13 +4883,13 @@
     </row>
     <row r="14" ht="39" spans="1:8">
       <c r="A14" s="38" t="s">
+        <v>47</v>
+      </c>
+      <c r="B14" s="38" t="s">
+        <v>47</v>
+      </c>
+      <c r="C14" s="38" t="s">
         <v>48</v>
-      </c>
-      <c r="B14" s="38" t="s">
-        <v>48</v>
-      </c>
-      <c r="C14" s="38" t="s">
-        <v>49</v>
       </c>
       <c r="D14" s="38" t="b">
         <v>1</v>
@@ -4901,10 +4898,10 @@
         <v>1</v>
       </c>
       <c r="F14" s="39" t="s">
+        <v>49</v>
+      </c>
+      <c r="G14" s="38" t="s">
         <v>50</v>
-      </c>
-      <c r="G14" s="38" t="s">
-        <v>51</v>
       </c>
       <c r="H14" s="38">
         <v>0</v>
@@ -4912,22 +4909,22 @@
     </row>
     <row r="15" ht="39" spans="1:8">
       <c r="A15" s="36" t="s">
+        <v>51</v>
+      </c>
+      <c r="B15" s="36" t="s">
+        <v>51</v>
+      </c>
+      <c r="C15" s="36" t="s">
         <v>52</v>
       </c>
-      <c r="B15" s="36" t="s">
-        <v>52</v>
-      </c>
-      <c r="C15" s="36" t="s">
+      <c r="D15" s="36" t="b">
+        <v>0</v>
+      </c>
+      <c r="E15" s="36">
+        <v>0</v>
+      </c>
+      <c r="F15" s="37" t="s">
         <v>53</v>
-      </c>
-      <c r="D15" s="36" t="b">
-        <v>0</v>
-      </c>
-      <c r="E15" s="36">
-        <v>0</v>
-      </c>
-      <c r="F15" s="37" t="s">
-        <v>54</v>
       </c>
       <c r="G15" s="36" t="s">
         <v>11</v>
@@ -4938,22 +4935,22 @@
     </row>
     <row r="16" ht="26" spans="1:8">
       <c r="A16" s="38" t="s">
+        <v>54</v>
+      </c>
+      <c r="B16" s="38" t="s">
+        <v>54</v>
+      </c>
+      <c r="C16" s="38" t="s">
         <v>55</v>
       </c>
-      <c r="B16" s="38" t="s">
-        <v>55</v>
-      </c>
-      <c r="C16" s="38" t="s">
+      <c r="D16" s="38" t="b">
+        <v>0</v>
+      </c>
+      <c r="E16" s="38">
+        <v>0</v>
+      </c>
+      <c r="F16" s="39" t="s">
         <v>56</v>
-      </c>
-      <c r="D16" s="38" t="b">
-        <v>0</v>
-      </c>
-      <c r="E16" s="38">
-        <v>0</v>
-      </c>
-      <c r="F16" s="39" t="s">
-        <v>57</v>
       </c>
       <c r="G16" s="38" t="s">
         <v>11</v>
@@ -4964,22 +4961,22 @@
     </row>
     <row r="17" ht="52" spans="1:8">
       <c r="A17" s="36" t="s">
+        <v>57</v>
+      </c>
+      <c r="B17" s="36" t="s">
+        <v>57</v>
+      </c>
+      <c r="C17" s="36" t="s">
         <v>58</v>
       </c>
-      <c r="B17" s="36" t="s">
-        <v>58</v>
-      </c>
-      <c r="C17" s="36" t="s">
+      <c r="D17" s="36" t="b">
+        <v>0</v>
+      </c>
+      <c r="E17" s="36">
+        <v>0</v>
+      </c>
+      <c r="F17" s="37" t="s">
         <v>59</v>
-      </c>
-      <c r="D17" s="36" t="b">
-        <v>0</v>
-      </c>
-      <c r="E17" s="36">
-        <v>0</v>
-      </c>
-      <c r="F17" s="37" t="s">
-        <v>60</v>
       </c>
       <c r="G17" s="36" t="s">
         <v>11</v>
@@ -4990,25 +4987,25 @@
     </row>
     <row r="18" ht="52" spans="1:8">
       <c r="A18" s="38" t="s">
+        <v>60</v>
+      </c>
+      <c r="B18" s="38" t="s">
+        <v>60</v>
+      </c>
+      <c r="C18" s="38" t="s">
         <v>61</v>
       </c>
-      <c r="B18" s="38" t="s">
-        <v>61</v>
-      </c>
-      <c r="C18" s="38" t="s">
+      <c r="D18" s="38" t="b">
+        <v>0</v>
+      </c>
+      <c r="E18" s="38">
+        <v>0</v>
+      </c>
+      <c r="F18" s="39" t="s">
         <v>62</v>
       </c>
-      <c r="D18" s="38" t="b">
-        <v>0</v>
-      </c>
-      <c r="E18" s="38">
-        <v>0</v>
-      </c>
-      <c r="F18" s="39" t="s">
+      <c r="G18" s="38" t="s">
         <v>63</v>
-      </c>
-      <c r="G18" s="38" t="s">
-        <v>64</v>
       </c>
       <c r="H18" s="38">
         <v>0</v>
@@ -5016,22 +5013,22 @@
     </row>
     <row r="19" ht="26" spans="1:8">
       <c r="A19" s="36" t="s">
+        <v>64</v>
+      </c>
+      <c r="B19" s="36" t="s">
+        <v>64</v>
+      </c>
+      <c r="C19" s="36" t="s">
         <v>65</v>
       </c>
-      <c r="B19" s="36" t="s">
-        <v>65</v>
-      </c>
-      <c r="C19" s="36" t="s">
+      <c r="D19" s="36" t="b">
+        <v>0</v>
+      </c>
+      <c r="E19" s="36">
+        <v>0</v>
+      </c>
+      <c r="F19" s="37" t="s">
         <v>66</v>
-      </c>
-      <c r="D19" s="36" t="b">
-        <v>0</v>
-      </c>
-      <c r="E19" s="36">
-        <v>0</v>
-      </c>
-      <c r="F19" s="37" t="s">
-        <v>67</v>
       </c>
       <c r="G19" s="36" t="s">
         <v>11</v>
@@ -5042,22 +5039,22 @@
     </row>
     <row r="20" ht="26" spans="1:8">
       <c r="A20" s="38" t="s">
+        <v>67</v>
+      </c>
+      <c r="B20" s="38" t="s">
+        <v>67</v>
+      </c>
+      <c r="C20" s="38" t="s">
         <v>68</v>
       </c>
-      <c r="B20" s="38" t="s">
-        <v>68</v>
-      </c>
-      <c r="C20" s="38" t="s">
+      <c r="D20" s="38" t="b">
+        <v>0</v>
+      </c>
+      <c r="E20" s="38">
+        <v>0</v>
+      </c>
+      <c r="F20" s="39" t="s">
         <v>69</v>
-      </c>
-      <c r="D20" s="38" t="b">
-        <v>0</v>
-      </c>
-      <c r="E20" s="38">
-        <v>0</v>
-      </c>
-      <c r="F20" s="39" t="s">
-        <v>70</v>
       </c>
       <c r="G20" s="38" t="s">
         <v>11</v>
@@ -5068,22 +5065,22 @@
     </row>
     <row r="21" ht="182" spans="1:8">
       <c r="A21" s="36" t="s">
+        <v>70</v>
+      </c>
+      <c r="B21" s="36" t="s">
+        <v>70</v>
+      </c>
+      <c r="C21" s="36" t="s">
         <v>71</v>
       </c>
-      <c r="B21" s="36" t="s">
-        <v>71</v>
-      </c>
-      <c r="C21" s="36" t="s">
+      <c r="D21" s="36" t="b">
+        <v>0</v>
+      </c>
+      <c r="E21" s="36">
+        <v>0</v>
+      </c>
+      <c r="F21" s="37" t="s">
         <v>72</v>
-      </c>
-      <c r="D21" s="36" t="b">
-        <v>0</v>
-      </c>
-      <c r="E21" s="36">
-        <v>0</v>
-      </c>
-      <c r="F21" s="37" t="s">
-        <v>73</v>
       </c>
       <c r="G21" s="36" t="s">
         <v>11</v>
@@ -5292,10 +5289,10 @@
         <v>2</v>
       </c>
       <c r="D1" s="41" t="s">
+        <v>73</v>
+      </c>
+      <c r="E1" s="43" t="s">
         <v>74</v>
-      </c>
-      <c r="E1" s="43" t="s">
-        <v>75</v>
       </c>
       <c r="F1" s="44" t="s">
         <v>5</v>
@@ -5303,127 +5300,127 @@
     </row>
     <row r="2" ht="25.5" customHeight="1" spans="1:6">
       <c r="A2" s="45" t="s">
+        <v>75</v>
+      </c>
+      <c r="B2" s="46" t="s">
+        <v>75</v>
+      </c>
+      <c r="C2" s="46" t="s">
         <v>76</v>
       </c>
-      <c r="B2" s="46" t="s">
-        <v>76</v>
-      </c>
-      <c r="C2" s="46" t="s">
+      <c r="D2" s="45" t="s">
         <v>77</v>
       </c>
-      <c r="D2" s="45" t="s">
+      <c r="E2" s="47" t="s">
         <v>78</v>
       </c>
-      <c r="E2" s="47" t="s">
+      <c r="F2" s="48" t="s">
         <v>79</v>
-      </c>
-      <c r="F2" s="48" t="s">
-        <v>80</v>
       </c>
     </row>
     <row r="3" ht="43" customHeight="1" spans="1:6">
       <c r="A3" s="49" t="s">
+        <v>80</v>
+      </c>
+      <c r="B3" s="50" t="s">
+        <v>80</v>
+      </c>
+      <c r="C3" s="50" t="s">
         <v>81</v>
       </c>
-      <c r="B3" s="50" t="s">
-        <v>81</v>
-      </c>
-      <c r="C3" s="50" t="s">
+      <c r="D3" s="49" t="s">
+        <v>77</v>
+      </c>
+      <c r="E3" s="51" t="s">
+        <v>78</v>
+      </c>
+      <c r="F3" s="52" t="s">
         <v>82</v>
-      </c>
-      <c r="D3" s="49" t="s">
-        <v>78</v>
-      </c>
-      <c r="E3" s="51" t="s">
-        <v>79</v>
-      </c>
-      <c r="F3" s="52" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="4" ht="23" customHeight="1" spans="1:6">
       <c r="A4" s="53" t="s">
+        <v>83</v>
+      </c>
+      <c r="B4" s="54" t="s">
+        <v>83</v>
+      </c>
+      <c r="C4" s="54" t="s">
         <v>84</v>
       </c>
-      <c r="B4" s="54" t="s">
-        <v>84</v>
-      </c>
-      <c r="C4" s="54" t="s">
+      <c r="D4" s="53" t="s">
+        <v>77</v>
+      </c>
+      <c r="E4" s="55" t="s">
         <v>85</v>
       </c>
-      <c r="D4" s="53" t="s">
-        <v>78</v>
-      </c>
-      <c r="E4" s="55" t="s">
+      <c r="F4" s="56" t="s">
         <v>86</v>
-      </c>
-      <c r="F4" s="56" t="s">
-        <v>87</v>
       </c>
     </row>
     <row r="5" s="40" customFormat="1" ht="52.75" spans="1:6">
       <c r="A5" s="49" t="s">
+        <v>87</v>
+      </c>
+      <c r="B5" s="50" t="s">
+        <v>87</v>
+      </c>
+      <c r="C5" s="51" t="s">
         <v>88</v>
       </c>
-      <c r="B5" s="50" t="s">
-        <v>88</v>
-      </c>
-      <c r="C5" s="51" t="s">
+      <c r="D5" s="50" t="s">
         <v>89</v>
       </c>
-      <c r="D5" s="50" t="s">
+      <c r="E5" s="50" t="s">
         <v>90</v>
       </c>
-      <c r="E5" s="50" t="s">
+      <c r="F5" s="52" t="s">
         <v>91</v>
-      </c>
-      <c r="F5" s="52" t="s">
-        <v>92</v>
       </c>
     </row>
     <row r="6" s="40" customFormat="1" ht="52" spans="1:6">
       <c r="A6" s="49" t="s">
+        <v>92</v>
+      </c>
+      <c r="B6" s="50" t="s">
+        <v>92</v>
+      </c>
+      <c r="C6" s="51" t="s">
         <v>93</v>
       </c>
-      <c r="B6" s="50" t="s">
-        <v>93</v>
-      </c>
-      <c r="C6" s="51" t="s">
+      <c r="D6" s="50" t="s">
+        <v>77</v>
+      </c>
+      <c r="E6" s="50" t="s">
         <v>94</v>
       </c>
-      <c r="D6" s="50" t="s">
-        <v>78</v>
-      </c>
-      <c r="E6" s="50" t="s">
+      <c r="F6" s="52" t="s">
         <v>95</v>
-      </c>
-      <c r="F6" s="52" t="s">
-        <v>96</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="45" t="s">
+        <v>96</v>
+      </c>
+      <c r="B7" s="46" t="s">
+        <v>96</v>
+      </c>
+      <c r="C7" s="47" t="s">
         <v>97</v>
       </c>
-      <c r="B7" s="46" t="s">
-        <v>97</v>
-      </c>
-      <c r="C7" s="47" t="s">
+      <c r="D7" s="46" t="s">
+        <v>89</v>
+      </c>
+      <c r="E7" s="46" t="s">
+        <v>85</v>
+      </c>
+      <c r="F7" s="48" t="s">
         <v>98</v>
-      </c>
-      <c r="D7" s="46" t="s">
-        <v>90</v>
-      </c>
-      <c r="E7" s="46" t="s">
-        <v>86</v>
-      </c>
-      <c r="F7" s="48" t="s">
-        <v>99</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="57" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
   </sheetData>
@@ -5503,13 +5500,13 @@
     </row>
     <row r="2" ht="52" spans="1:8">
       <c r="A2" s="32" t="s">
+        <v>100</v>
+      </c>
+      <c r="B2" s="32" t="s">
+        <v>100</v>
+      </c>
+      <c r="C2" s="32" t="s">
         <v>101</v>
-      </c>
-      <c r="B2" s="32" t="s">
-        <v>101</v>
-      </c>
-      <c r="C2" s="32" t="s">
-        <v>102</v>
       </c>
       <c r="D2" s="32" t="b">
         <v>1</v>
@@ -5518,7 +5515,7 @@
         <v>1</v>
       </c>
       <c r="F2" s="33" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="G2" s="32" t="s">
         <v>11</v>
@@ -5529,13 +5526,13 @@
     </row>
     <row r="3" spans="1:8">
       <c r="A3" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="B3" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="C3" s="34" t="s">
         <v>104</v>
-      </c>
-      <c r="B3" s="34" t="s">
-        <v>104</v>
-      </c>
-      <c r="C3" s="34" t="s">
-        <v>105</v>
       </c>
       <c r="D3" s="34" t="b">
         <v>1</v>
@@ -5544,7 +5541,7 @@
         <v>1</v>
       </c>
       <c r="F3" s="35" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="G3" s="34" t="s">
         <v>11</v>
@@ -5555,22 +5552,22 @@
     </row>
     <row r="4" ht="26" spans="1:8">
       <c r="A4" s="32" t="s">
+        <v>106</v>
+      </c>
+      <c r="B4" s="32" t="s">
+        <v>106</v>
+      </c>
+      <c r="C4" s="32" t="s">
         <v>107</v>
       </c>
-      <c r="B4" s="32" t="s">
-        <v>107</v>
-      </c>
-      <c r="C4" s="32" t="s">
+      <c r="D4" s="32" t="b">
+        <v>0</v>
+      </c>
+      <c r="E4" s="32">
+        <v>0</v>
+      </c>
+      <c r="F4" s="33" t="s">
         <v>108</v>
-      </c>
-      <c r="D4" s="32" t="b">
-        <v>0</v>
-      </c>
-      <c r="E4" s="32">
-        <v>0</v>
-      </c>
-      <c r="F4" s="33" t="s">
-        <v>109</v>
       </c>
       <c r="G4" s="32" t="s">
         <v>11</v>
@@ -5581,22 +5578,22 @@
     </row>
     <row r="5" ht="39" spans="1:8">
       <c r="A5" s="34" t="s">
+        <v>109</v>
+      </c>
+      <c r="B5" s="34" t="s">
+        <v>109</v>
+      </c>
+      <c r="C5" s="34" t="s">
         <v>110</v>
       </c>
-      <c r="B5" s="34" t="s">
-        <v>110</v>
-      </c>
-      <c r="C5" s="34" t="s">
+      <c r="D5" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="E5" s="34">
+        <v>0</v>
+      </c>
+      <c r="F5" s="35" t="s">
         <v>111</v>
-      </c>
-      <c r="D5" s="34" t="b">
-        <v>0</v>
-      </c>
-      <c r="E5" s="34">
-        <v>0</v>
-      </c>
-      <c r="F5" s="35" t="s">
-        <v>112</v>
       </c>
       <c r="G5" s="34" t="s">
         <v>11</v>
@@ -5607,22 +5604,22 @@
     </row>
     <row r="6" ht="26" spans="1:8">
       <c r="A6" s="32" t="s">
+        <v>112</v>
+      </c>
+      <c r="B6" s="32" t="s">
+        <v>112</v>
+      </c>
+      <c r="C6" s="32" t="s">
         <v>113</v>
       </c>
-      <c r="B6" s="32" t="s">
-        <v>113</v>
-      </c>
-      <c r="C6" s="32" t="s">
+      <c r="D6" s="32" t="b">
+        <v>0</v>
+      </c>
+      <c r="E6" s="32">
+        <v>0</v>
+      </c>
+      <c r="F6" s="33" t="s">
         <v>114</v>
-      </c>
-      <c r="D6" s="32" t="b">
-        <v>0</v>
-      </c>
-      <c r="E6" s="32">
-        <v>0</v>
-      </c>
-      <c r="F6" s="33" t="s">
-        <v>115</v>
       </c>
       <c r="G6" s="32" t="s">
         <v>11</v>
@@ -5633,22 +5630,22 @@
     </row>
     <row r="7" ht="39" spans="1:8">
       <c r="A7" s="34" t="s">
+        <v>115</v>
+      </c>
+      <c r="B7" s="34" t="s">
+        <v>115</v>
+      </c>
+      <c r="C7" s="34" t="s">
         <v>116</v>
       </c>
-      <c r="B7" s="34" t="s">
-        <v>116</v>
-      </c>
-      <c r="C7" s="34" t="s">
+      <c r="D7" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="E7" s="34">
+        <v>0</v>
+      </c>
+      <c r="F7" s="35" t="s">
         <v>117</v>
-      </c>
-      <c r="D7" s="34" t="b">
-        <v>0</v>
-      </c>
-      <c r="E7" s="34">
-        <v>0</v>
-      </c>
-      <c r="F7" s="35" t="s">
-        <v>118</v>
       </c>
       <c r="G7" s="34" t="s">
         <v>11</v>
@@ -5659,22 +5656,22 @@
     </row>
     <row r="8" ht="65" spans="1:8">
       <c r="A8" s="32" t="s">
+        <v>118</v>
+      </c>
+      <c r="B8" s="32" t="s">
+        <v>118</v>
+      </c>
+      <c r="C8" s="32" t="s">
         <v>119</v>
       </c>
-      <c r="B8" s="32" t="s">
-        <v>119</v>
-      </c>
-      <c r="C8" s="32" t="s">
+      <c r="D8" s="32" t="b">
+        <v>0</v>
+      </c>
+      <c r="E8" s="32">
+        <v>0</v>
+      </c>
+      <c r="F8" s="33" t="s">
         <v>120</v>
-      </c>
-      <c r="D8" s="32" t="b">
-        <v>0</v>
-      </c>
-      <c r="E8" s="32">
-        <v>0</v>
-      </c>
-      <c r="F8" s="33" t="s">
-        <v>121</v>
       </c>
       <c r="G8" s="32" t="s">
         <v>11</v>
@@ -5685,22 +5682,22 @@
     </row>
     <row r="9" ht="39" spans="1:8">
       <c r="A9" s="34" t="s">
+        <v>121</v>
+      </c>
+      <c r="B9" s="34" t="s">
+        <v>121</v>
+      </c>
+      <c r="C9" s="34" t="s">
         <v>122</v>
       </c>
-      <c r="B9" s="34" t="s">
-        <v>122</v>
-      </c>
-      <c r="C9" s="34" t="s">
+      <c r="D9" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="E9" s="34">
+        <v>0</v>
+      </c>
+      <c r="F9" s="35" t="s">
         <v>123</v>
-      </c>
-      <c r="D9" s="34" t="b">
-        <v>0</v>
-      </c>
-      <c r="E9" s="34">
-        <v>0</v>
-      </c>
-      <c r="F9" s="35" t="s">
-        <v>124</v>
       </c>
       <c r="G9" s="34" t="s">
         <v>11</v>
@@ -5711,22 +5708,22 @@
     </row>
     <row r="10" ht="39" spans="1:8">
       <c r="A10" s="32" t="s">
+        <v>124</v>
+      </c>
+      <c r="B10" s="32" t="s">
+        <v>124</v>
+      </c>
+      <c r="C10" s="32" t="s">
         <v>125</v>
       </c>
-      <c r="B10" s="32" t="s">
-        <v>125</v>
-      </c>
-      <c r="C10" s="32" t="s">
+      <c r="D10" s="32" t="b">
+        <v>0</v>
+      </c>
+      <c r="E10" s="32">
+        <v>0</v>
+      </c>
+      <c r="F10" s="33" t="s">
         <v>126</v>
-      </c>
-      <c r="D10" s="32" t="b">
-        <v>0</v>
-      </c>
-      <c r="E10" s="32">
-        <v>0</v>
-      </c>
-      <c r="F10" s="33" t="s">
-        <v>127</v>
       </c>
       <c r="G10" s="32" t="s">
         <v>11</v>
@@ -5737,22 +5734,22 @@
     </row>
     <row r="11" ht="117" spans="1:8">
       <c r="A11" s="36" t="s">
+        <v>127</v>
+      </c>
+      <c r="B11" s="36" t="s">
+        <v>127</v>
+      </c>
+      <c r="C11" s="36" t="s">
         <v>128</v>
       </c>
-      <c r="B11" s="36" t="s">
-        <v>128</v>
-      </c>
-      <c r="C11" s="36" t="s">
+      <c r="D11" s="36" t="b">
+        <v>0</v>
+      </c>
+      <c r="E11" s="36">
+        <v>0</v>
+      </c>
+      <c r="F11" s="37" t="s">
         <v>129</v>
-      </c>
-      <c r="D11" s="36" t="b">
-        <v>0</v>
-      </c>
-      <c r="E11" s="36">
-        <v>0</v>
-      </c>
-      <c r="F11" s="37" t="s">
-        <v>130</v>
       </c>
       <c r="G11" s="36" t="s">
         <v>11</v>
@@ -5763,22 +5760,22 @@
     </row>
     <row r="12" ht="39" spans="1:8">
       <c r="A12" s="38" t="s">
+        <v>130</v>
+      </c>
+      <c r="B12" s="38" t="s">
+        <v>130</v>
+      </c>
+      <c r="C12" s="38" t="s">
         <v>131</v>
       </c>
-      <c r="B12" s="38" t="s">
-        <v>131</v>
-      </c>
-      <c r="C12" s="38" t="s">
+      <c r="D12" s="38" t="b">
+        <v>0</v>
+      </c>
+      <c r="E12" s="38">
+        <v>0</v>
+      </c>
+      <c r="F12" s="39" t="s">
         <v>132</v>
-      </c>
-      <c r="D12" s="38" t="b">
-        <v>0</v>
-      </c>
-      <c r="E12" s="38">
-        <v>0</v>
-      </c>
-      <c r="F12" s="39" t="s">
-        <v>133</v>
       </c>
       <c r="G12" s="38" t="s">
         <v>11</v>
@@ -5789,22 +5786,22 @@
     </row>
     <row r="13" ht="26" spans="1:8">
       <c r="A13" s="36" t="s">
+        <v>133</v>
+      </c>
+      <c r="B13" s="36" t="s">
+        <v>133</v>
+      </c>
+      <c r="C13" s="36" t="s">
         <v>134</v>
       </c>
-      <c r="B13" s="36" t="s">
-        <v>134</v>
-      </c>
-      <c r="C13" s="36" t="s">
+      <c r="D13" s="36" t="b">
+        <v>0</v>
+      </c>
+      <c r="E13" s="36">
+        <v>0</v>
+      </c>
+      <c r="F13" s="37" t="s">
         <v>135</v>
-      </c>
-      <c r="D13" s="36" t="b">
-        <v>0</v>
-      </c>
-      <c r="E13" s="36">
-        <v>0</v>
-      </c>
-      <c r="F13" s="37" t="s">
-        <v>136</v>
       </c>
       <c r="G13" s="36" t="s">
         <v>11</v>
@@ -5815,22 +5812,22 @@
     </row>
     <row r="14" ht="26" spans="1:8">
       <c r="A14" s="38" t="s">
+        <v>136</v>
+      </c>
+      <c r="B14" s="38" t="s">
+        <v>136</v>
+      </c>
+      <c r="C14" s="38" t="s">
         <v>137</v>
       </c>
-      <c r="B14" s="38" t="s">
-        <v>137</v>
-      </c>
-      <c r="C14" s="38" t="s">
+      <c r="D14" s="38" t="b">
+        <v>0</v>
+      </c>
+      <c r="E14" s="38">
+        <v>0</v>
+      </c>
+      <c r="F14" s="39" t="s">
         <v>138</v>
-      </c>
-      <c r="D14" s="38" t="b">
-        <v>0</v>
-      </c>
-      <c r="E14" s="38">
-        <v>0</v>
-      </c>
-      <c r="F14" s="39" t="s">
-        <v>139</v>
       </c>
       <c r="G14" s="38" t="s">
         <v>11</v>
@@ -5841,22 +5838,22 @@
     </row>
     <row r="15" ht="17" spans="1:8">
       <c r="A15" s="36" t="s">
+        <v>139</v>
+      </c>
+      <c r="B15" s="36" t="s">
+        <v>139</v>
+      </c>
+      <c r="C15" s="36" t="s">
         <v>140</v>
       </c>
-      <c r="B15" s="36" t="s">
-        <v>140</v>
-      </c>
-      <c r="C15" s="36" t="s">
+      <c r="D15" s="36" t="b">
+        <v>0</v>
+      </c>
+      <c r="E15" s="36">
+        <v>0</v>
+      </c>
+      <c r="F15" s="37" t="s">
         <v>141</v>
-      </c>
-      <c r="D15" s="36" t="b">
-        <v>0</v>
-      </c>
-      <c r="E15" s="36">
-        <v>0</v>
-      </c>
-      <c r="F15" s="37" t="s">
-        <v>142</v>
       </c>
       <c r="G15" s="36" t="s">
         <v>11</v>
@@ -5867,22 +5864,22 @@
     </row>
     <row r="16" ht="39" spans="1:8">
       <c r="A16" s="38" t="s">
+        <v>142</v>
+      </c>
+      <c r="B16" s="38" t="s">
+        <v>142</v>
+      </c>
+      <c r="C16" s="38" t="s">
         <v>143</v>
       </c>
-      <c r="B16" s="38" t="s">
-        <v>143</v>
-      </c>
-      <c r="C16" s="38" t="s">
+      <c r="D16" s="38" t="b">
+        <v>0</v>
+      </c>
+      <c r="E16" s="38">
+        <v>0</v>
+      </c>
+      <c r="F16" s="39" t="s">
         <v>144</v>
-      </c>
-      <c r="D16" s="38" t="b">
-        <v>0</v>
-      </c>
-      <c r="E16" s="38">
-        <v>0</v>
-      </c>
-      <c r="F16" s="39" t="s">
-        <v>145</v>
       </c>
       <c r="G16" s="38" t="s">
         <v>11</v>
@@ -5893,22 +5890,22 @@
     </row>
     <row r="17" ht="26" spans="1:8">
       <c r="A17" s="36" t="s">
+        <v>145</v>
+      </c>
+      <c r="B17" s="36" t="s">
+        <v>145</v>
+      </c>
+      <c r="C17" s="36" t="s">
         <v>146</v>
       </c>
-      <c r="B17" s="36" t="s">
-        <v>146</v>
-      </c>
-      <c r="C17" s="36" t="s">
+      <c r="D17" s="36" t="b">
+        <v>0</v>
+      </c>
+      <c r="E17" s="36">
+        <v>0</v>
+      </c>
+      <c r="F17" s="37" t="s">
         <v>147</v>
-      </c>
-      <c r="D17" s="36" t="b">
-        <v>0</v>
-      </c>
-      <c r="E17" s="36">
-        <v>0</v>
-      </c>
-      <c r="F17" s="37" t="s">
-        <v>148</v>
       </c>
       <c r="G17" s="36" t="s">
         <v>11</v>
@@ -5919,22 +5916,22 @@
     </row>
     <row r="18" ht="26" spans="1:8">
       <c r="A18" s="38" t="s">
+        <v>148</v>
+      </c>
+      <c r="B18" s="38" t="s">
+        <v>148</v>
+      </c>
+      <c r="C18" s="38" t="s">
         <v>149</v>
       </c>
-      <c r="B18" s="38" t="s">
-        <v>149</v>
-      </c>
-      <c r="C18" s="38" t="s">
+      <c r="D18" s="38" t="b">
+        <v>0</v>
+      </c>
+      <c r="E18" s="38">
+        <v>0</v>
+      </c>
+      <c r="F18" s="39" t="s">
         <v>150</v>
-      </c>
-      <c r="D18" s="38" t="b">
-        <v>0</v>
-      </c>
-      <c r="E18" s="38">
-        <v>0</v>
-      </c>
-      <c r="F18" s="39" t="s">
-        <v>151</v>
       </c>
       <c r="G18" s="38" t="s">
         <v>11</v>
@@ -5945,22 +5942,22 @@
     </row>
     <row r="19" ht="78" spans="1:8">
       <c r="A19" s="36" t="s">
+        <v>151</v>
+      </c>
+      <c r="B19" s="36" t="s">
+        <v>151</v>
+      </c>
+      <c r="C19" s="36" t="s">
         <v>152</v>
       </c>
-      <c r="B19" s="36" t="s">
-        <v>152</v>
-      </c>
-      <c r="C19" s="36" t="s">
+      <c r="D19" s="36" t="b">
+        <v>0</v>
+      </c>
+      <c r="E19" s="36">
+        <v>0</v>
+      </c>
+      <c r="F19" s="37" t="s">
         <v>153</v>
-      </c>
-      <c r="D19" s="36" t="b">
-        <v>0</v>
-      </c>
-      <c r="E19" s="36">
-        <v>0</v>
-      </c>
-      <c r="F19" s="37" t="s">
-        <v>154</v>
       </c>
       <c r="G19" s="36" t="s">
         <v>11</v>
@@ -5971,22 +5968,22 @@
     </row>
     <row r="20" spans="1:8">
       <c r="A20" s="38" t="s">
+        <v>154</v>
+      </c>
+      <c r="B20" s="38" t="s">
+        <v>154</v>
+      </c>
+      <c r="C20" s="38" t="s">
         <v>155</v>
       </c>
-      <c r="B20" s="38" t="s">
-        <v>155</v>
-      </c>
-      <c r="C20" s="38" t="s">
+      <c r="D20" s="38" t="b">
+        <v>0</v>
+      </c>
+      <c r="E20" s="38">
+        <v>0</v>
+      </c>
+      <c r="F20" s="39" t="s">
         <v>156</v>
-      </c>
-      <c r="D20" s="38" t="b">
-        <v>0</v>
-      </c>
-      <c r="E20" s="38">
-        <v>0</v>
-      </c>
-      <c r="F20" s="39" t="s">
-        <v>157</v>
       </c>
       <c r="G20" s="38" t="s">
         <v>11</v>
@@ -5997,22 +5994,22 @@
     </row>
     <row r="21" ht="26" spans="1:8">
       <c r="A21" s="36" t="s">
+        <v>157</v>
+      </c>
+      <c r="B21" s="36" t="s">
+        <v>157</v>
+      </c>
+      <c r="C21" s="36" t="s">
         <v>158</v>
       </c>
-      <c r="B21" s="36" t="s">
-        <v>158</v>
-      </c>
-      <c r="C21" s="36" t="s">
+      <c r="D21" s="36" t="b">
+        <v>0</v>
+      </c>
+      <c r="E21" s="36">
+        <v>0</v>
+      </c>
+      <c r="F21" s="37" t="s">
         <v>159</v>
-      </c>
-      <c r="D21" s="36" t="b">
-        <v>0</v>
-      </c>
-      <c r="E21" s="36">
-        <v>0</v>
-      </c>
-      <c r="F21" s="37" t="s">
-        <v>160</v>
       </c>
       <c r="G21" s="36" t="s">
         <v>11</v>
@@ -6023,13 +6020,13 @@
     </row>
     <row r="22" ht="26" spans="1:8">
       <c r="A22" s="38" t="s">
+        <v>160</v>
+      </c>
+      <c r="B22" s="38" t="s">
+        <v>160</v>
+      </c>
+      <c r="C22" s="38" t="s">
         <v>161</v>
-      </c>
-      <c r="B22" s="38" t="s">
-        <v>161</v>
-      </c>
-      <c r="C22" s="38" t="s">
-        <v>162</v>
       </c>
       <c r="D22" s="38" t="b">
         <v>1</v>
@@ -6038,7 +6035,7 @@
         <v>1</v>
       </c>
       <c r="F22" s="39" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="G22" s="38" t="s">
         <v>11</v>
@@ -6049,22 +6046,22 @@
     </row>
     <row r="23" ht="65" spans="1:8">
       <c r="A23" s="36" t="s">
+        <v>163</v>
+      </c>
+      <c r="B23" s="36" t="s">
+        <v>163</v>
+      </c>
+      <c r="C23" s="36" t="s">
+        <v>88</v>
+      </c>
+      <c r="D23" s="36" t="b">
+        <v>0</v>
+      </c>
+      <c r="E23" s="36">
+        <v>0</v>
+      </c>
+      <c r="F23" s="37" t="s">
         <v>164</v>
-      </c>
-      <c r="B23" s="36" t="s">
-        <v>164</v>
-      </c>
-      <c r="C23" s="36" t="s">
-        <v>89</v>
-      </c>
-      <c r="D23" s="36" t="b">
-        <v>0</v>
-      </c>
-      <c r="E23" s="36">
-        <v>0</v>
-      </c>
-      <c r="F23" s="37" t="s">
-        <v>165</v>
       </c>
       <c r="G23" s="36" t="s">
         <v>11</v>
@@ -6075,22 +6072,22 @@
     </row>
     <row r="24" ht="65" spans="1:8">
       <c r="A24" s="38" t="s">
+        <v>165</v>
+      </c>
+      <c r="B24" s="38" t="s">
+        <v>165</v>
+      </c>
+      <c r="C24" s="38" t="s">
         <v>166</v>
       </c>
-      <c r="B24" s="38" t="s">
-        <v>166</v>
-      </c>
-      <c r="C24" s="38" t="s">
+      <c r="D24" s="38" t="b">
+        <v>0</v>
+      </c>
+      <c r="E24" s="38">
+        <v>0</v>
+      </c>
+      <c r="F24" s="39" t="s">
         <v>167</v>
-      </c>
-      <c r="D24" s="38" t="b">
-        <v>0</v>
-      </c>
-      <c r="E24" s="38">
-        <v>0</v>
-      </c>
-      <c r="F24" s="39" t="s">
-        <v>168</v>
       </c>
       <c r="G24" s="38" t="s">
         <v>11</v>
@@ -6101,22 +6098,22 @@
     </row>
     <row r="25" ht="26" spans="1:8">
       <c r="A25" s="36" t="s">
+        <v>168</v>
+      </c>
+      <c r="B25" s="36" t="s">
+        <v>168</v>
+      </c>
+      <c r="C25" s="36" t="s">
         <v>169</v>
       </c>
-      <c r="B25" s="36" t="s">
-        <v>169</v>
-      </c>
-      <c r="C25" s="36" t="s">
+      <c r="D25" s="36" t="b">
+        <v>0</v>
+      </c>
+      <c r="E25" s="36">
+        <v>0</v>
+      </c>
+      <c r="F25" s="37" t="s">
         <v>170</v>
-      </c>
-      <c r="D25" s="36" t="b">
-        <v>0</v>
-      </c>
-      <c r="E25" s="36">
-        <v>0</v>
-      </c>
-      <c r="F25" s="37" t="s">
-        <v>171</v>
       </c>
       <c r="G25" s="36" t="s">
         <v>11</v>
@@ -6127,13 +6124,13 @@
     </row>
     <row r="26" ht="78" spans="1:8">
       <c r="A26" s="38" t="s">
+        <v>171</v>
+      </c>
+      <c r="B26" s="38" t="s">
+        <v>171</v>
+      </c>
+      <c r="C26" s="38" t="s">
         <v>172</v>
-      </c>
-      <c r="B26" s="38" t="s">
-        <v>172</v>
-      </c>
-      <c r="C26" s="38" t="s">
-        <v>173</v>
       </c>
       <c r="D26" s="38" t="b">
         <v>1</v>
@@ -6142,7 +6139,7 @@
         <v>1</v>
       </c>
       <c r="F26" s="39" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="G26" s="38" t="s">
         <v>11</v>
@@ -6153,22 +6150,22 @@
     </row>
     <row r="27" ht="52" spans="1:8">
       <c r="A27" s="36" t="s">
+        <v>174</v>
+      </c>
+      <c r="B27" s="36" t="s">
+        <v>174</v>
+      </c>
+      <c r="C27" s="36" t="s">
         <v>175</v>
       </c>
-      <c r="B27" s="36" t="s">
-        <v>175</v>
-      </c>
-      <c r="C27" s="36" t="s">
+      <c r="D27" s="36" t="b">
+        <v>0</v>
+      </c>
+      <c r="E27" s="36">
+        <v>0</v>
+      </c>
+      <c r="F27" s="37" t="s">
         <v>176</v>
-      </c>
-      <c r="D27" s="36" t="b">
-        <v>0</v>
-      </c>
-      <c r="E27" s="36">
-        <v>0</v>
-      </c>
-      <c r="F27" s="37" t="s">
-        <v>177</v>
       </c>
       <c r="G27" s="36" t="s">
         <v>11</v>
@@ -6179,22 +6176,22 @@
     </row>
     <row r="28" ht="65" spans="1:8">
       <c r="A28" s="38" t="s">
+        <v>177</v>
+      </c>
+      <c r="B28" s="38" t="s">
+        <v>177</v>
+      </c>
+      <c r="C28" s="38" t="s">
         <v>178</v>
       </c>
-      <c r="B28" s="38" t="s">
-        <v>178</v>
-      </c>
-      <c r="C28" s="38" t="s">
+      <c r="D28" s="38" t="b">
+        <v>0</v>
+      </c>
+      <c r="E28" s="38">
+        <v>0</v>
+      </c>
+      <c r="F28" s="39" t="s">
         <v>179</v>
-      </c>
-      <c r="D28" s="38" t="b">
-        <v>0</v>
-      </c>
-      <c r="E28" s="38">
-        <v>0</v>
-      </c>
-      <c r="F28" s="39" t="s">
-        <v>180</v>
       </c>
       <c r="G28" s="38" t="s">
         <v>11</v>
@@ -6205,22 +6202,22 @@
     </row>
     <row r="29" ht="26" spans="1:8">
       <c r="A29" s="36" t="s">
+        <v>180</v>
+      </c>
+      <c r="B29" s="36" t="s">
+        <v>180</v>
+      </c>
+      <c r="C29" s="36" t="s">
         <v>181</v>
       </c>
-      <c r="B29" s="36" t="s">
-        <v>181</v>
-      </c>
-      <c r="C29" s="36" t="s">
+      <c r="D29" s="36" t="b">
+        <v>0</v>
+      </c>
+      <c r="E29" s="36">
+        <v>0</v>
+      </c>
+      <c r="F29" s="37" t="s">
         <v>182</v>
-      </c>
-      <c r="D29" s="36" t="b">
-        <v>0</v>
-      </c>
-      <c r="E29" s="36">
-        <v>0</v>
-      </c>
-      <c r="F29" s="37" t="s">
-        <v>183</v>
       </c>
       <c r="G29" s="36" t="s">
         <v>11</v>
@@ -6231,22 +6228,22 @@
     </row>
     <row r="30" ht="39" spans="1:8">
       <c r="A30" s="38" t="s">
+        <v>183</v>
+      </c>
+      <c r="B30" s="38" t="s">
+        <v>183</v>
+      </c>
+      <c r="C30" s="38" t="s">
         <v>184</v>
       </c>
-      <c r="B30" s="38" t="s">
-        <v>184</v>
-      </c>
-      <c r="C30" s="38" t="s">
+      <c r="D30" s="38" t="b">
+        <v>0</v>
+      </c>
+      <c r="E30" s="38">
+        <v>0</v>
+      </c>
+      <c r="F30" s="39" t="s">
         <v>185</v>
-      </c>
-      <c r="D30" s="38" t="b">
-        <v>0</v>
-      </c>
-      <c r="E30" s="38">
-        <v>0</v>
-      </c>
-      <c r="F30" s="39" t="s">
-        <v>186</v>
       </c>
       <c r="G30" s="38" t="s">
         <v>11</v>
@@ -6257,22 +6254,22 @@
     </row>
     <row r="31" ht="26" spans="1:8">
       <c r="A31" s="36" t="s">
+        <v>186</v>
+      </c>
+      <c r="B31" s="36" t="s">
+        <v>186</v>
+      </c>
+      <c r="C31" s="36" t="s">
         <v>187</v>
       </c>
-      <c r="B31" s="36" t="s">
-        <v>187</v>
-      </c>
-      <c r="C31" s="36" t="s">
+      <c r="D31" s="36" t="b">
+        <v>0</v>
+      </c>
+      <c r="E31" s="36">
+        <v>0</v>
+      </c>
+      <c r="F31" s="37" t="s">
         <v>188</v>
-      </c>
-      <c r="D31" s="36" t="b">
-        <v>0</v>
-      </c>
-      <c r="E31" s="36">
-        <v>0</v>
-      </c>
-      <c r="F31" s="37" t="s">
-        <v>189</v>
       </c>
       <c r="G31" s="36" t="s">
         <v>11</v>
@@ -6283,22 +6280,22 @@
     </row>
     <row r="32" ht="26" spans="1:8">
       <c r="A32" s="38" t="s">
+        <v>189</v>
+      </c>
+      <c r="B32" s="38" t="s">
+        <v>189</v>
+      </c>
+      <c r="C32" s="38" t="s">
         <v>190</v>
       </c>
-      <c r="B32" s="38" t="s">
-        <v>190</v>
-      </c>
-      <c r="C32" s="38" t="s">
+      <c r="D32" s="38" t="b">
+        <v>0</v>
+      </c>
+      <c r="E32" s="38">
+        <v>0</v>
+      </c>
+      <c r="F32" s="39" t="s">
         <v>191</v>
-      </c>
-      <c r="D32" s="38" t="b">
-        <v>0</v>
-      </c>
-      <c r="E32" s="38">
-        <v>0</v>
-      </c>
-      <c r="F32" s="39" t="s">
-        <v>192</v>
       </c>
       <c r="G32" s="38" t="s">
         <v>11</v>
@@ -6309,22 +6306,22 @@
     </row>
     <row r="33" ht="39" spans="1:8">
       <c r="A33" s="36" t="s">
+        <v>192</v>
+      </c>
+      <c r="B33" s="36" t="s">
+        <v>192</v>
+      </c>
+      <c r="C33" s="36" t="s">
         <v>193</v>
       </c>
-      <c r="B33" s="36" t="s">
-        <v>193</v>
-      </c>
-      <c r="C33" s="36" t="s">
+      <c r="D33" s="36" t="b">
+        <v>0</v>
+      </c>
+      <c r="E33" s="36">
+        <v>0</v>
+      </c>
+      <c r="F33" s="37" t="s">
         <v>194</v>
-      </c>
-      <c r="D33" s="36" t="b">
-        <v>0</v>
-      </c>
-      <c r="E33" s="36">
-        <v>0</v>
-      </c>
-      <c r="F33" s="37" t="s">
-        <v>195</v>
       </c>
       <c r="G33" s="36" t="s">
         <v>11</v>
@@ -6335,22 +6332,22 @@
     </row>
     <row r="34" spans="1:8">
       <c r="A34" s="38" t="s">
+        <v>195</v>
+      </c>
+      <c r="B34" s="38" t="s">
+        <v>195</v>
+      </c>
+      <c r="C34" s="38" t="s">
         <v>196</v>
       </c>
-      <c r="B34" s="38" t="s">
-        <v>196</v>
-      </c>
-      <c r="C34" s="38" t="s">
+      <c r="D34" s="38" t="b">
+        <v>0</v>
+      </c>
+      <c r="E34" s="38">
+        <v>0</v>
+      </c>
+      <c r="F34" s="39" t="s">
         <v>197</v>
-      </c>
-      <c r="D34" s="38" t="b">
-        <v>0</v>
-      </c>
-      <c r="E34" s="38">
-        <v>0</v>
-      </c>
-      <c r="F34" s="39" t="s">
-        <v>198</v>
       </c>
       <c r="G34" s="38" t="s">
         <v>11</v>
@@ -6361,22 +6358,22 @@
     </row>
     <row r="35" ht="130" spans="1:8">
       <c r="A35" s="36" t="s">
+        <v>198</v>
+      </c>
+      <c r="B35" s="36" t="s">
+        <v>198</v>
+      </c>
+      <c r="C35" s="36" t="s">
         <v>199</v>
       </c>
-      <c r="B35" s="36" t="s">
-        <v>199</v>
-      </c>
-      <c r="C35" s="36" t="s">
+      <c r="D35" s="36" t="b">
+        <v>0</v>
+      </c>
+      <c r="E35" s="36">
+        <v>0</v>
+      </c>
+      <c r="F35" s="37" t="s">
         <v>200</v>
-      </c>
-      <c r="D35" s="36" t="b">
-        <v>0</v>
-      </c>
-      <c r="E35" s="36">
-        <v>0</v>
-      </c>
-      <c r="F35" s="37" t="s">
-        <v>201</v>
       </c>
       <c r="G35" s="36" t="s">
         <v>11</v>
@@ -6387,22 +6384,22 @@
     </row>
     <row r="36" spans="1:8">
       <c r="A36" s="38" t="s">
+        <v>201</v>
+      </c>
+      <c r="B36" s="38" t="s">
+        <v>201</v>
+      </c>
+      <c r="C36" s="38" t="s">
         <v>202</v>
       </c>
-      <c r="B36" s="38" t="s">
-        <v>202</v>
-      </c>
-      <c r="C36" s="38" t="s">
+      <c r="D36" s="38" t="b">
+        <v>0</v>
+      </c>
+      <c r="E36" s="38">
+        <v>0</v>
+      </c>
+      <c r="F36" s="39" t="s">
         <v>203</v>
-      </c>
-      <c r="D36" s="38" t="b">
-        <v>0</v>
-      </c>
-      <c r="E36" s="38">
-        <v>0</v>
-      </c>
-      <c r="F36" s="39" t="s">
-        <v>204</v>
       </c>
       <c r="G36" s="38" t="s">
         <v>11</v>
@@ -6413,22 +6410,22 @@
     </row>
     <row r="37" spans="1:8">
       <c r="A37" s="36" t="s">
+        <v>204</v>
+      </c>
+      <c r="B37" s="36" t="s">
+        <v>204</v>
+      </c>
+      <c r="C37" s="36" t="s">
         <v>205</v>
       </c>
-      <c r="B37" s="36" t="s">
-        <v>205</v>
-      </c>
-      <c r="C37" s="36" t="s">
+      <c r="D37" s="36" t="b">
+        <v>0</v>
+      </c>
+      <c r="E37" s="36">
+        <v>0</v>
+      </c>
+      <c r="F37" s="37" t="s">
         <v>206</v>
-      </c>
-      <c r="D37" s="36" t="b">
-        <v>0</v>
-      </c>
-      <c r="E37" s="36">
-        <v>0</v>
-      </c>
-      <c r="F37" s="37" t="s">
-        <v>207</v>
       </c>
       <c r="G37" s="36" t="s">
         <v>11</v>
@@ -6439,22 +6436,22 @@
     </row>
     <row r="38" ht="39" spans="1:8">
       <c r="A38" s="38" t="s">
+        <v>207</v>
+      </c>
+      <c r="B38" s="38" t="s">
+        <v>207</v>
+      </c>
+      <c r="C38" s="38" t="s">
         <v>208</v>
       </c>
-      <c r="B38" s="38" t="s">
-        <v>208</v>
-      </c>
-      <c r="C38" s="38" t="s">
+      <c r="D38" s="38" t="b">
+        <v>0</v>
+      </c>
+      <c r="E38" s="38">
+        <v>0</v>
+      </c>
+      <c r="F38" s="39" t="s">
         <v>209</v>
-      </c>
-      <c r="D38" s="38" t="b">
-        <v>0</v>
-      </c>
-      <c r="E38" s="38">
-        <v>0</v>
-      </c>
-      <c r="F38" s="39" t="s">
-        <v>210</v>
       </c>
       <c r="G38" s="38" t="s">
         <v>11</v>
@@ -6465,22 +6462,22 @@
     </row>
     <row r="39" ht="26" spans="1:8">
       <c r="A39" s="36" t="s">
+        <v>210</v>
+      </c>
+      <c r="B39" s="36" t="s">
+        <v>210</v>
+      </c>
+      <c r="C39" s="36" t="s">
         <v>211</v>
       </c>
-      <c r="B39" s="36" t="s">
-        <v>211</v>
-      </c>
-      <c r="C39" s="36" t="s">
+      <c r="D39" s="36" t="b">
+        <v>0</v>
+      </c>
+      <c r="E39" s="36">
+        <v>0</v>
+      </c>
+      <c r="F39" s="37" t="s">
         <v>212</v>
-      </c>
-      <c r="D39" s="36" t="b">
-        <v>0</v>
-      </c>
-      <c r="E39" s="36">
-        <v>0</v>
-      </c>
-      <c r="F39" s="37" t="s">
-        <v>213</v>
       </c>
       <c r="G39" s="36" t="s">
         <v>11</v>
@@ -6491,22 +6488,22 @@
     </row>
     <row r="40" spans="1:8">
       <c r="A40" s="38" t="s">
+        <v>213</v>
+      </c>
+      <c r="B40" s="38" t="s">
+        <v>213</v>
+      </c>
+      <c r="C40" s="38" t="s">
         <v>214</v>
       </c>
-      <c r="B40" s="38" t="s">
-        <v>214</v>
-      </c>
-      <c r="C40" s="38" t="s">
+      <c r="D40" s="38" t="b">
+        <v>0</v>
+      </c>
+      <c r="E40" s="38">
+        <v>0</v>
+      </c>
+      <c r="F40" s="39" t="s">
         <v>215</v>
-      </c>
-      <c r="D40" s="38" t="b">
-        <v>0</v>
-      </c>
-      <c r="E40" s="38">
-        <v>0</v>
-      </c>
-      <c r="F40" s="39" t="s">
-        <v>216</v>
       </c>
       <c r="G40" s="38" t="s">
         <v>11</v>
@@ -6517,22 +6514,22 @@
     </row>
     <row r="41" ht="26" spans="1:8">
       <c r="A41" s="36" t="s">
+        <v>216</v>
+      </c>
+      <c r="B41" s="36" t="s">
+        <v>216</v>
+      </c>
+      <c r="C41" s="36" t="s">
         <v>217</v>
       </c>
-      <c r="B41" s="36" t="s">
-        <v>217</v>
-      </c>
-      <c r="C41" s="36" t="s">
+      <c r="D41" s="36" t="b">
+        <v>0</v>
+      </c>
+      <c r="E41" s="36">
+        <v>0</v>
+      </c>
+      <c r="F41" s="37" t="s">
         <v>218</v>
-      </c>
-      <c r="D41" s="36" t="b">
-        <v>0</v>
-      </c>
-      <c r="E41" s="36">
-        <v>0</v>
-      </c>
-      <c r="F41" s="37" t="s">
-        <v>219</v>
       </c>
       <c r="G41" s="36" t="s">
         <v>11</v>
@@ -6543,22 +6540,22 @@
     </row>
     <row r="42" ht="26" spans="1:8">
       <c r="A42" s="38" t="s">
+        <v>219</v>
+      </c>
+      <c r="B42" s="38" t="s">
+        <v>219</v>
+      </c>
+      <c r="C42" s="38" t="s">
         <v>220</v>
       </c>
-      <c r="B42" s="38" t="s">
-        <v>220</v>
-      </c>
-      <c r="C42" s="38" t="s">
+      <c r="D42" s="38" t="b">
+        <v>0</v>
+      </c>
+      <c r="E42" s="38">
+        <v>0</v>
+      </c>
+      <c r="F42" s="39" t="s">
         <v>221</v>
-      </c>
-      <c r="D42" s="38" t="b">
-        <v>0</v>
-      </c>
-      <c r="E42" s="38">
-        <v>0</v>
-      </c>
-      <c r="F42" s="39" t="s">
-        <v>222</v>
       </c>
       <c r="G42" s="38" t="s">
         <v>11</v>
@@ -6569,22 +6566,22 @@
     </row>
     <row r="43" ht="26" spans="1:8">
       <c r="A43" s="36" t="s">
+        <v>222</v>
+      </c>
+      <c r="B43" s="36" t="s">
+        <v>222</v>
+      </c>
+      <c r="C43" s="36" t="s">
         <v>223</v>
       </c>
-      <c r="B43" s="36" t="s">
-        <v>223</v>
-      </c>
-      <c r="C43" s="36" t="s">
+      <c r="D43" s="36" t="b">
+        <v>0</v>
+      </c>
+      <c r="E43" s="36">
+        <v>0</v>
+      </c>
+      <c r="F43" s="37" t="s">
         <v>224</v>
-      </c>
-      <c r="D43" s="36" t="b">
-        <v>0</v>
-      </c>
-      <c r="E43" s="36">
-        <v>0</v>
-      </c>
-      <c r="F43" s="37" t="s">
-        <v>225</v>
       </c>
       <c r="G43" s="36" t="s">
         <v>11</v>
@@ -6595,22 +6592,22 @@
     </row>
     <row r="44" ht="39" spans="1:8">
       <c r="A44" s="38" t="s">
+        <v>225</v>
+      </c>
+      <c r="B44" s="38" t="s">
+        <v>225</v>
+      </c>
+      <c r="C44" s="38" t="s">
         <v>226</v>
       </c>
-      <c r="B44" s="38" t="s">
-        <v>226</v>
-      </c>
-      <c r="C44" s="38" t="s">
+      <c r="D44" s="38" t="b">
+        <v>0</v>
+      </c>
+      <c r="E44" s="38">
+        <v>0</v>
+      </c>
+      <c r="F44" s="39" t="s">
         <v>227</v>
-      </c>
-      <c r="D44" s="38" t="b">
-        <v>0</v>
-      </c>
-      <c r="E44" s="38">
-        <v>0</v>
-      </c>
-      <c r="F44" s="39" t="s">
-        <v>228</v>
       </c>
       <c r="G44" s="38" t="s">
         <v>11</v>
@@ -6621,22 +6618,22 @@
     </row>
     <row r="45" ht="26" spans="1:8">
       <c r="A45" s="36" t="s">
+        <v>228</v>
+      </c>
+      <c r="B45" s="36" t="s">
+        <v>228</v>
+      </c>
+      <c r="C45" s="36" t="s">
         <v>229</v>
       </c>
-      <c r="B45" s="36" t="s">
-        <v>229</v>
-      </c>
-      <c r="C45" s="36" t="s">
+      <c r="D45" s="36" t="b">
+        <v>0</v>
+      </c>
+      <c r="E45" s="36">
+        <v>0</v>
+      </c>
+      <c r="F45" s="37" t="s">
         <v>230</v>
-      </c>
-      <c r="D45" s="36" t="b">
-        <v>0</v>
-      </c>
-      <c r="E45" s="36">
-        <v>0</v>
-      </c>
-      <c r="F45" s="37" t="s">
-        <v>231</v>
       </c>
       <c r="G45" s="36" t="s">
         <v>11</v>
@@ -6647,22 +6644,22 @@
     </row>
     <row r="46" ht="26" spans="1:8">
       <c r="A46" s="38" t="s">
+        <v>231</v>
+      </c>
+      <c r="B46" s="38" t="s">
+        <v>231</v>
+      </c>
+      <c r="C46" s="38" t="s">
         <v>232</v>
       </c>
-      <c r="B46" s="38" t="s">
-        <v>232</v>
-      </c>
-      <c r="C46" s="38" t="s">
+      <c r="D46" s="38" t="b">
+        <v>0</v>
+      </c>
+      <c r="E46" s="38">
+        <v>0</v>
+      </c>
+      <c r="F46" s="39" t="s">
         <v>233</v>
-      </c>
-      <c r="D46" s="38" t="b">
-        <v>0</v>
-      </c>
-      <c r="E46" s="38">
-        <v>0</v>
-      </c>
-      <c r="F46" s="39" t="s">
-        <v>234</v>
       </c>
       <c r="G46" s="38" t="s">
         <v>11</v>
@@ -6673,22 +6670,22 @@
     </row>
     <row r="47" ht="52" spans="1:8">
       <c r="A47" s="36" t="s">
+        <v>234</v>
+      </c>
+      <c r="B47" s="36" t="s">
+        <v>234</v>
+      </c>
+      <c r="C47" s="36" t="s">
         <v>235</v>
       </c>
-      <c r="B47" s="36" t="s">
-        <v>235</v>
-      </c>
-      <c r="C47" s="36" t="s">
+      <c r="D47" s="36" t="b">
+        <v>0</v>
+      </c>
+      <c r="E47" s="36">
+        <v>0</v>
+      </c>
+      <c r="F47" s="37" t="s">
         <v>236</v>
-      </c>
-      <c r="D47" s="36" t="b">
-        <v>0</v>
-      </c>
-      <c r="E47" s="36">
-        <v>0</v>
-      </c>
-      <c r="F47" s="37" t="s">
-        <v>237</v>
       </c>
       <c r="G47" s="36" t="s">
         <v>11</v>
@@ -6699,22 +6696,22 @@
     </row>
     <row r="48" ht="65" spans="1:8">
       <c r="A48" s="38" t="s">
+        <v>237</v>
+      </c>
+      <c r="B48" s="38" t="s">
+        <v>237</v>
+      </c>
+      <c r="C48" s="38" t="s">
         <v>238</v>
       </c>
-      <c r="B48" s="38" t="s">
-        <v>238</v>
-      </c>
-      <c r="C48" s="38" t="s">
+      <c r="D48" s="38" t="b">
+        <v>0</v>
+      </c>
+      <c r="E48" s="38">
+        <v>0</v>
+      </c>
+      <c r="F48" s="39" t="s">
         <v>239</v>
-      </c>
-      <c r="D48" s="38" t="b">
-        <v>0</v>
-      </c>
-      <c r="E48" s="38">
-        <v>0</v>
-      </c>
-      <c r="F48" s="39" t="s">
-        <v>240</v>
       </c>
       <c r="G48" s="38" t="s">
         <v>11</v>
@@ -6725,22 +6722,22 @@
     </row>
     <row r="49" spans="1:8">
       <c r="A49" s="36" t="s">
+        <v>240</v>
+      </c>
+      <c r="B49" s="36" t="s">
+        <v>240</v>
+      </c>
+      <c r="C49" s="36" t="s">
         <v>241</v>
       </c>
-      <c r="B49" s="36" t="s">
-        <v>241</v>
-      </c>
-      <c r="C49" s="36" t="s">
+      <c r="D49" s="36" t="b">
+        <v>0</v>
+      </c>
+      <c r="E49" s="36">
+        <v>0</v>
+      </c>
+      <c r="F49" s="37" t="s">
         <v>242</v>
-      </c>
-      <c r="D49" s="36" t="b">
-        <v>0</v>
-      </c>
-      <c r="E49" s="36">
-        <v>0</v>
-      </c>
-      <c r="F49" s="37" t="s">
-        <v>243</v>
       </c>
       <c r="G49" s="36" t="s">
         <v>11</v>
@@ -6751,22 +6748,22 @@
     </row>
     <row r="50" ht="39" spans="1:8">
       <c r="A50" s="38" t="s">
+        <v>243</v>
+      </c>
+      <c r="B50" s="38" t="s">
+        <v>243</v>
+      </c>
+      <c r="C50" s="38" t="s">
         <v>244</v>
       </c>
-      <c r="B50" s="38" t="s">
-        <v>244</v>
-      </c>
-      <c r="C50" s="38" t="s">
+      <c r="D50" s="38" t="b">
+        <v>0</v>
+      </c>
+      <c r="E50" s="38">
+        <v>0</v>
+      </c>
+      <c r="F50" s="39" t="s">
         <v>245</v>
-      </c>
-      <c r="D50" s="38" t="b">
-        <v>0</v>
-      </c>
-      <c r="E50" s="38">
-        <v>0</v>
-      </c>
-      <c r="F50" s="39" t="s">
-        <v>246</v>
       </c>
       <c r="G50" s="38" t="s">
         <v>11</v>
@@ -6777,22 +6774,22 @@
     </row>
     <row r="51" spans="1:8">
       <c r="A51" s="36" t="s">
+        <v>246</v>
+      </c>
+      <c r="B51" s="36" t="s">
+        <v>246</v>
+      </c>
+      <c r="C51" s="36" t="s">
         <v>247</v>
       </c>
-      <c r="B51" s="36" t="s">
-        <v>247</v>
-      </c>
-      <c r="C51" s="36" t="s">
+      <c r="D51" s="36" t="b">
+        <v>0</v>
+      </c>
+      <c r="E51" s="36">
+        <v>0</v>
+      </c>
+      <c r="F51" s="37" t="s">
         <v>248</v>
-      </c>
-      <c r="D51" s="36" t="b">
-        <v>0</v>
-      </c>
-      <c r="E51" s="36">
-        <v>0</v>
-      </c>
-      <c r="F51" s="37" t="s">
-        <v>249</v>
       </c>
       <c r="G51" s="36" t="s">
         <v>11</v>
@@ -6803,22 +6800,22 @@
     </row>
     <row r="52" ht="26" spans="1:8">
       <c r="A52" s="38" t="s">
+        <v>249</v>
+      </c>
+      <c r="B52" s="38" t="s">
+        <v>249</v>
+      </c>
+      <c r="C52" s="38" t="s">
         <v>250</v>
       </c>
-      <c r="B52" s="38" t="s">
-        <v>250</v>
-      </c>
-      <c r="C52" s="38" t="s">
+      <c r="D52" s="38" t="b">
+        <v>0</v>
+      </c>
+      <c r="E52" s="38">
+        <v>0</v>
+      </c>
+      <c r="F52" s="39" t="s">
         <v>251</v>
-      </c>
-      <c r="D52" s="38" t="b">
-        <v>0</v>
-      </c>
-      <c r="E52" s="38">
-        <v>0</v>
-      </c>
-      <c r="F52" s="39" t="s">
-        <v>252</v>
       </c>
       <c r="G52" s="38" t="s">
         <v>11</v>
@@ -6829,22 +6826,22 @@
     </row>
     <row r="53" ht="26" spans="1:8">
       <c r="A53" s="36" t="s">
+        <v>252</v>
+      </c>
+      <c r="B53" s="36" t="s">
+        <v>252</v>
+      </c>
+      <c r="C53" s="36" t="s">
         <v>253</v>
       </c>
-      <c r="B53" s="36" t="s">
-        <v>253</v>
-      </c>
-      <c r="C53" s="36" t="s">
+      <c r="D53" s="36" t="b">
+        <v>0</v>
+      </c>
+      <c r="E53" s="36">
+        <v>0</v>
+      </c>
+      <c r="F53" s="37" t="s">
         <v>254</v>
-      </c>
-      <c r="D53" s="36" t="b">
-        <v>0</v>
-      </c>
-      <c r="E53" s="36">
-        <v>0</v>
-      </c>
-      <c r="F53" s="37" t="s">
-        <v>255</v>
       </c>
       <c r="G53" s="36" t="s">
         <v>11</v>
@@ -6855,22 +6852,22 @@
     </row>
     <row r="54" ht="26" spans="1:8">
       <c r="A54" s="38" t="s">
+        <v>255</v>
+      </c>
+      <c r="B54" s="38" t="s">
+        <v>255</v>
+      </c>
+      <c r="C54" s="38" t="s">
         <v>256</v>
       </c>
-      <c r="B54" s="38" t="s">
-        <v>256</v>
-      </c>
-      <c r="C54" s="38" t="s">
+      <c r="D54" s="38" t="b">
+        <v>0</v>
+      </c>
+      <c r="E54" s="38">
+        <v>0</v>
+      </c>
+      <c r="F54" s="39" t="s">
         <v>257</v>
-      </c>
-      <c r="D54" s="38" t="b">
-        <v>0</v>
-      </c>
-      <c r="E54" s="38">
-        <v>0</v>
-      </c>
-      <c r="F54" s="39" t="s">
-        <v>258</v>
       </c>
       <c r="G54" s="38" t="s">
         <v>11</v>
@@ -6881,22 +6878,22 @@
     </row>
     <row r="55" ht="39" spans="1:8">
       <c r="A55" s="36" t="s">
+        <v>258</v>
+      </c>
+      <c r="B55" s="36" t="s">
+        <v>258</v>
+      </c>
+      <c r="C55" s="36" t="s">
         <v>259</v>
       </c>
-      <c r="B55" s="36" t="s">
-        <v>259</v>
-      </c>
-      <c r="C55" s="36" t="s">
+      <c r="D55" s="36" t="b">
+        <v>0</v>
+      </c>
+      <c r="E55" s="36">
+        <v>0</v>
+      </c>
+      <c r="F55" s="37" t="s">
         <v>260</v>
-      </c>
-      <c r="D55" s="36" t="b">
-        <v>0</v>
-      </c>
-      <c r="E55" s="36">
-        <v>0</v>
-      </c>
-      <c r="F55" s="37" t="s">
-        <v>261</v>
       </c>
       <c r="G55" s="36" t="s">
         <v>11</v>
@@ -6907,22 +6904,22 @@
     </row>
     <row r="56" ht="26" spans="1:8">
       <c r="A56" s="38" t="s">
+        <v>261</v>
+      </c>
+      <c r="B56" s="38" t="s">
+        <v>261</v>
+      </c>
+      <c r="C56" s="38" t="s">
         <v>262</v>
       </c>
-      <c r="B56" s="38" t="s">
-        <v>262</v>
-      </c>
-      <c r="C56" s="38" t="s">
+      <c r="D56" s="38" t="b">
+        <v>0</v>
+      </c>
+      <c r="E56" s="38">
+        <v>0</v>
+      </c>
+      <c r="F56" s="39" t="s">
         <v>263</v>
-      </c>
-      <c r="D56" s="38" t="b">
-        <v>0</v>
-      </c>
-      <c r="E56" s="38">
-        <v>0</v>
-      </c>
-      <c r="F56" s="39" t="s">
-        <v>264</v>
       </c>
       <c r="G56" s="38" t="s">
         <v>11</v>
@@ -6933,22 +6930,22 @@
     </row>
     <row r="57" ht="26" spans="1:8">
       <c r="A57" s="36" t="s">
+        <v>264</v>
+      </c>
+      <c r="B57" s="36" t="s">
+        <v>264</v>
+      </c>
+      <c r="C57" s="36" t="s">
         <v>265</v>
       </c>
-      <c r="B57" s="36" t="s">
-        <v>265</v>
-      </c>
-      <c r="C57" s="36" t="s">
+      <c r="D57" s="36" t="b">
+        <v>0</v>
+      </c>
+      <c r="E57" s="36">
+        <v>0</v>
+      </c>
+      <c r="F57" s="37" t="s">
         <v>266</v>
-      </c>
-      <c r="D57" s="36" t="b">
-        <v>0</v>
-      </c>
-      <c r="E57" s="36">
-        <v>0</v>
-      </c>
-      <c r="F57" s="37" t="s">
-        <v>267</v>
       </c>
       <c r="G57" s="36" t="s">
         <v>11</v>
@@ -6959,22 +6956,22 @@
     </row>
     <row r="58" ht="26" spans="1:8">
       <c r="A58" s="38" t="s">
+        <v>267</v>
+      </c>
+      <c r="B58" s="38" t="s">
+        <v>267</v>
+      </c>
+      <c r="C58" s="38" t="s">
         <v>268</v>
       </c>
-      <c r="B58" s="38" t="s">
-        <v>268</v>
-      </c>
-      <c r="C58" s="38" t="s">
+      <c r="D58" s="38" t="b">
+        <v>0</v>
+      </c>
+      <c r="E58" s="38">
+        <v>0</v>
+      </c>
+      <c r="F58" s="39" t="s">
         <v>269</v>
-      </c>
-      <c r="D58" s="38" t="b">
-        <v>0</v>
-      </c>
-      <c r="E58" s="38">
-        <v>0</v>
-      </c>
-      <c r="F58" s="39" t="s">
-        <v>270</v>
       </c>
       <c r="G58" s="38" t="s">
         <v>11</v>
@@ -6985,22 +6982,22 @@
     </row>
     <row r="59" ht="30" spans="1:8">
       <c r="A59" s="36" t="s">
+        <v>270</v>
+      </c>
+      <c r="B59" s="36" t="s">
+        <v>270</v>
+      </c>
+      <c r="C59" s="36" t="s">
         <v>271</v>
       </c>
-      <c r="B59" s="36" t="s">
-        <v>271</v>
-      </c>
-      <c r="C59" s="36" t="s">
+      <c r="D59" s="36" t="b">
+        <v>0</v>
+      </c>
+      <c r="E59" s="36">
+        <v>0</v>
+      </c>
+      <c r="F59" s="37" t="s">
         <v>272</v>
-      </c>
-      <c r="D59" s="36" t="b">
-        <v>0</v>
-      </c>
-      <c r="E59" s="36">
-        <v>0</v>
-      </c>
-      <c r="F59" s="37" t="s">
-        <v>273</v>
       </c>
       <c r="G59" s="36" t="s">
         <v>11</v>
@@ -7011,22 +7008,22 @@
     </row>
     <row r="60" spans="1:8">
       <c r="A60" s="38" t="s">
+        <v>273</v>
+      </c>
+      <c r="B60" s="38" t="s">
+        <v>273</v>
+      </c>
+      <c r="C60" s="38" t="s">
         <v>274</v>
       </c>
-      <c r="B60" s="38" t="s">
-        <v>274</v>
-      </c>
-      <c r="C60" s="38" t="s">
+      <c r="D60" s="38" t="b">
+        <v>0</v>
+      </c>
+      <c r="E60" s="38">
+        <v>0</v>
+      </c>
+      <c r="F60" s="39" t="s">
         <v>275</v>
-      </c>
-      <c r="D60" s="38" t="b">
-        <v>0</v>
-      </c>
-      <c r="E60" s="38">
-        <v>0</v>
-      </c>
-      <c r="F60" s="39" t="s">
-        <v>276</v>
       </c>
       <c r="G60" s="38" t="s">
         <v>11</v>
@@ -7037,22 +7034,22 @@
     </row>
     <row r="61" ht="52" spans="1:8">
       <c r="A61" s="36" t="s">
+        <v>276</v>
+      </c>
+      <c r="B61" s="36" t="s">
+        <v>276</v>
+      </c>
+      <c r="C61" s="36" t="s">
         <v>277</v>
       </c>
-      <c r="B61" s="36" t="s">
-        <v>277</v>
-      </c>
-      <c r="C61" s="36" t="s">
+      <c r="D61" s="36" t="b">
+        <v>0</v>
+      </c>
+      <c r="E61" s="36">
+        <v>0</v>
+      </c>
+      <c r="F61" s="37" t="s">
         <v>278</v>
-      </c>
-      <c r="D61" s="36" t="b">
-        <v>0</v>
-      </c>
-      <c r="E61" s="36">
-        <v>0</v>
-      </c>
-      <c r="F61" s="37" t="s">
-        <v>279</v>
       </c>
       <c r="G61" s="36" t="s">
         <v>11</v>
@@ -7063,22 +7060,22 @@
     </row>
     <row r="62" ht="26" spans="1:8">
       <c r="A62" s="38" t="s">
+        <v>279</v>
+      </c>
+      <c r="B62" s="38" t="s">
+        <v>279</v>
+      </c>
+      <c r="C62" s="38" t="s">
         <v>280</v>
       </c>
-      <c r="B62" s="38" t="s">
-        <v>280</v>
-      </c>
-      <c r="C62" s="38" t="s">
+      <c r="D62" s="38" t="b">
+        <v>0</v>
+      </c>
+      <c r="E62" s="38">
+        <v>0</v>
+      </c>
+      <c r="F62" s="39" t="s">
         <v>281</v>
-      </c>
-      <c r="D62" s="38" t="b">
-        <v>0</v>
-      </c>
-      <c r="E62" s="38">
-        <v>0</v>
-      </c>
-      <c r="F62" s="39" t="s">
-        <v>282</v>
       </c>
       <c r="G62" s="38" t="s">
         <v>11</v>
@@ -7089,22 +7086,22 @@
     </row>
     <row r="63" ht="39" spans="1:8">
       <c r="A63" s="36" t="s">
+        <v>282</v>
+      </c>
+      <c r="B63" s="36" t="s">
+        <v>282</v>
+      </c>
+      <c r="C63" s="36" t="s">
         <v>283</v>
       </c>
-      <c r="B63" s="36" t="s">
-        <v>283</v>
-      </c>
-      <c r="C63" s="36" t="s">
+      <c r="D63" s="36" t="b">
+        <v>0</v>
+      </c>
+      <c r="E63" s="36">
+        <v>0</v>
+      </c>
+      <c r="F63" s="37" t="s">
         <v>284</v>
-      </c>
-      <c r="D63" s="36" t="b">
-        <v>0</v>
-      </c>
-      <c r="E63" s="36">
-        <v>0</v>
-      </c>
-      <c r="F63" s="37" t="s">
-        <v>285</v>
       </c>
       <c r="G63" s="36" t="s">
         <v>11</v>
@@ -7115,22 +7112,22 @@
     </row>
     <row r="64" spans="1:8">
       <c r="A64" s="38" t="s">
+        <v>285</v>
+      </c>
+      <c r="B64" s="38" t="s">
+        <v>285</v>
+      </c>
+      <c r="C64" s="38" t="s">
         <v>286</v>
       </c>
-      <c r="B64" s="38" t="s">
-        <v>286</v>
-      </c>
-      <c r="C64" s="38" t="s">
+      <c r="D64" s="38" t="b">
+        <v>0</v>
+      </c>
+      <c r="E64" s="38">
+        <v>0</v>
+      </c>
+      <c r="F64" s="39" t="s">
         <v>287</v>
-      </c>
-      <c r="D64" s="38" t="b">
-        <v>0</v>
-      </c>
-      <c r="E64" s="38">
-        <v>0</v>
-      </c>
-      <c r="F64" s="39" t="s">
-        <v>288</v>
       </c>
       <c r="G64" s="38" t="s">
         <v>11</v>
@@ -7141,22 +7138,22 @@
     </row>
     <row r="65" ht="26" spans="1:8">
       <c r="A65" s="36" t="s">
+        <v>288</v>
+      </c>
+      <c r="B65" s="36" t="s">
+        <v>288</v>
+      </c>
+      <c r="C65" s="36" t="s">
         <v>289</v>
       </c>
-      <c r="B65" s="36" t="s">
-        <v>289</v>
-      </c>
-      <c r="C65" s="36" t="s">
+      <c r="D65" s="36" t="b">
+        <v>0</v>
+      </c>
+      <c r="E65" s="36">
+        <v>0</v>
+      </c>
+      <c r="F65" s="37" t="s">
         <v>290</v>
-      </c>
-      <c r="D65" s="36" t="b">
-        <v>0</v>
-      </c>
-      <c r="E65" s="36">
-        <v>0</v>
-      </c>
-      <c r="F65" s="37" t="s">
-        <v>291</v>
       </c>
       <c r="G65" s="36" t="s">
         <v>11</v>
@@ -7167,22 +7164,22 @@
     </row>
     <row r="66" ht="39" spans="1:8">
       <c r="A66" s="38" t="s">
+        <v>291</v>
+      </c>
+      <c r="B66" s="38" t="s">
+        <v>291</v>
+      </c>
+      <c r="C66" s="38" t="s">
         <v>292</v>
       </c>
-      <c r="B66" s="38" t="s">
-        <v>292</v>
-      </c>
-      <c r="C66" s="38" t="s">
+      <c r="D66" s="38" t="b">
+        <v>0</v>
+      </c>
+      <c r="E66" s="38">
+        <v>0</v>
+      </c>
+      <c r="F66" s="39" t="s">
         <v>293</v>
-      </c>
-      <c r="D66" s="38" t="b">
-        <v>0</v>
-      </c>
-      <c r="E66" s="38">
-        <v>0</v>
-      </c>
-      <c r="F66" s="39" t="s">
-        <v>294</v>
       </c>
       <c r="G66" s="38" t="s">
         <v>11</v>
@@ -7193,22 +7190,22 @@
     </row>
     <row r="67" ht="52" spans="1:8">
       <c r="A67" s="36" t="s">
+        <v>294</v>
+      </c>
+      <c r="B67" s="36" t="s">
+        <v>294</v>
+      </c>
+      <c r="C67" s="36" t="s">
         <v>295</v>
       </c>
-      <c r="B67" s="36" t="s">
-        <v>295</v>
-      </c>
-      <c r="C67" s="36" t="s">
+      <c r="D67" s="36" t="b">
+        <v>0</v>
+      </c>
+      <c r="E67" s="36">
+        <v>0</v>
+      </c>
+      <c r="F67" s="37" t="s">
         <v>296</v>
-      </c>
-      <c r="D67" s="36" t="b">
-        <v>0</v>
-      </c>
-      <c r="E67" s="36">
-        <v>0</v>
-      </c>
-      <c r="F67" s="37" t="s">
-        <v>297</v>
       </c>
       <c r="G67" s="36" t="s">
         <v>11</v>
@@ -7219,13 +7216,13 @@
     </row>
     <row r="68" ht="47" spans="1:8">
       <c r="A68" s="32" t="s">
+        <v>297</v>
+      </c>
+      <c r="B68" s="32" t="s">
+        <v>297</v>
+      </c>
+      <c r="C68" s="32" t="s">
         <v>298</v>
-      </c>
-      <c r="B68" s="32" t="s">
-        <v>298</v>
-      </c>
-      <c r="C68" s="32" t="s">
-        <v>299</v>
       </c>
       <c r="D68" s="32" t="b">
         <v>1</v>
@@ -7234,7 +7231,7 @@
         <v>2</v>
       </c>
       <c r="F68" s="33" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="G68" s="32" t="s">
         <v>11</v>
@@ -7245,22 +7242,22 @@
     </row>
     <row r="69" ht="26" spans="1:8">
       <c r="A69" s="34" t="s">
+        <v>300</v>
+      </c>
+      <c r="B69" s="34" t="s">
+        <v>300</v>
+      </c>
+      <c r="C69" s="34" t="s">
         <v>301</v>
       </c>
-      <c r="B69" s="34" t="s">
-        <v>301</v>
-      </c>
-      <c r="C69" s="34" t="s">
+      <c r="D69" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="E69" s="34">
+        <v>0</v>
+      </c>
+      <c r="F69" s="35" t="s">
         <v>302</v>
-      </c>
-      <c r="D69" s="34" t="b">
-        <v>0</v>
-      </c>
-      <c r="E69" s="34">
-        <v>0</v>
-      </c>
-      <c r="F69" s="35" t="s">
-        <v>303</v>
       </c>
       <c r="G69" s="34" t="s">
         <v>11</v>
@@ -7286,7 +7283,7 @@
         <v>0</v>
       </c>
       <c r="F70" s="33" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G70" s="32" t="s">
         <v>11</v>
@@ -7297,22 +7294,22 @@
     </row>
     <row r="71" ht="91" spans="1:8">
       <c r="A71" s="34" t="s">
+        <v>303</v>
+      </c>
+      <c r="B71" s="34" t="s">
+        <v>303</v>
+      </c>
+      <c r="C71" s="34" t="s">
         <v>304</v>
       </c>
-      <c r="B71" s="34" t="s">
-        <v>304</v>
-      </c>
-      <c r="C71" s="34" t="s">
+      <c r="D71" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="E71" s="34">
+        <v>0</v>
+      </c>
+      <c r="F71" s="35" t="s">
         <v>305</v>
-      </c>
-      <c r="D71" s="34" t="b">
-        <v>0</v>
-      </c>
-      <c r="E71" s="34">
-        <v>0</v>
-      </c>
-      <c r="F71" s="35" t="s">
-        <v>306</v>
       </c>
       <c r="G71" s="34" t="s">
         <v>11</v>
@@ -7323,22 +7320,22 @@
     </row>
     <row r="72" ht="39" spans="1:8">
       <c r="A72" s="32" t="s">
+        <v>306</v>
+      </c>
+      <c r="B72" s="32" t="s">
+        <v>306</v>
+      </c>
+      <c r="C72" s="32" t="s">
         <v>307</v>
       </c>
-      <c r="B72" s="32" t="s">
-        <v>307</v>
-      </c>
-      <c r="C72" s="32" t="s">
+      <c r="D72" s="32" t="b">
+        <v>0</v>
+      </c>
+      <c r="E72" s="32">
+        <v>0</v>
+      </c>
+      <c r="F72" s="33" t="s">
         <v>308</v>
-      </c>
-      <c r="D72" s="32" t="b">
-        <v>0</v>
-      </c>
-      <c r="E72" s="32">
-        <v>0</v>
-      </c>
-      <c r="F72" s="33" t="s">
-        <v>309</v>
       </c>
       <c r="G72" s="32" t="s">
         <v>11</v>
@@ -7349,22 +7346,22 @@
     </row>
     <row r="73" spans="1:8">
       <c r="A73" s="34" t="s">
+        <v>309</v>
+      </c>
+      <c r="B73" s="34" t="s">
+        <v>309</v>
+      </c>
+      <c r="C73" s="34" t="s">
         <v>310</v>
       </c>
-      <c r="B73" s="34" t="s">
-        <v>310</v>
-      </c>
-      <c r="C73" s="34" t="s">
+      <c r="D73" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="E73" s="34">
+        <v>0</v>
+      </c>
+      <c r="F73" s="35" t="s">
         <v>311</v>
-      </c>
-      <c r="D73" s="34" t="b">
-        <v>0</v>
-      </c>
-      <c r="E73" s="34">
-        <v>0</v>
-      </c>
-      <c r="F73" s="35" t="s">
-        <v>312</v>
       </c>
       <c r="G73" s="34" t="s">
         <v>11</v>
@@ -7375,22 +7372,22 @@
     </row>
     <row r="74" ht="17" spans="1:8">
       <c r="A74" s="32" t="s">
+        <v>312</v>
+      </c>
+      <c r="B74" s="32" t="s">
+        <v>312</v>
+      </c>
+      <c r="C74" s="32" t="s">
         <v>313</v>
       </c>
-      <c r="B74" s="32" t="s">
-        <v>313</v>
-      </c>
-      <c r="C74" s="32" t="s">
+      <c r="D74" s="32" t="b">
+        <v>0</v>
+      </c>
+      <c r="E74" s="32">
+        <v>0</v>
+      </c>
+      <c r="F74" s="33" t="s">
         <v>314</v>
-      </c>
-      <c r="D74" s="32" t="b">
-        <v>0</v>
-      </c>
-      <c r="E74" s="32">
-        <v>0</v>
-      </c>
-      <c r="F74" s="33" t="s">
-        <v>315</v>
       </c>
       <c r="G74" s="32" t="s">
         <v>11</v>
@@ -7401,22 +7398,22 @@
     </row>
     <row r="75" spans="1:8">
       <c r="A75" s="34" t="s">
+        <v>315</v>
+      </c>
+      <c r="B75" s="34" t="s">
+        <v>315</v>
+      </c>
+      <c r="C75" s="34" t="s">
         <v>316</v>
       </c>
-      <c r="B75" s="34" t="s">
-        <v>316</v>
-      </c>
-      <c r="C75" s="34" t="s">
+      <c r="D75" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="E75" s="34">
+        <v>0</v>
+      </c>
+      <c r="F75" s="35" t="s">
         <v>317</v>
-      </c>
-      <c r="D75" s="34" t="b">
-        <v>0</v>
-      </c>
-      <c r="E75" s="34">
-        <v>0</v>
-      </c>
-      <c r="F75" s="35" t="s">
-        <v>318</v>
       </c>
       <c r="G75" s="34" t="s">
         <v>11</v>
@@ -7427,22 +7424,22 @@
     </row>
     <row r="76" spans="1:8">
       <c r="A76" s="32" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B76" s="32" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C76" s="32" t="s">
+        <v>25</v>
+      </c>
+      <c r="D76" s="32" t="b">
+        <v>0</v>
+      </c>
+      <c r="E76" s="32">
+        <v>0</v>
+      </c>
+      <c r="F76" s="33" t="s">
         <v>26</v>
-      </c>
-      <c r="D76" s="32" t="b">
-        <v>0</v>
-      </c>
-      <c r="E76" s="32">
-        <v>0</v>
-      </c>
-      <c r="F76" s="33" t="s">
-        <v>27</v>
       </c>
       <c r="G76" s="32" t="s">
         <v>11</v>
@@ -7453,22 +7450,22 @@
     </row>
     <row r="77" ht="26" spans="1:8">
       <c r="A77" s="34" t="s">
+        <v>319</v>
+      </c>
+      <c r="B77" s="34" t="s">
+        <v>319</v>
+      </c>
+      <c r="C77" s="34" t="s">
         <v>320</v>
       </c>
-      <c r="B77" s="34" t="s">
-        <v>320</v>
-      </c>
-      <c r="C77" s="34" t="s">
+      <c r="D77" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="E77" s="34">
+        <v>0</v>
+      </c>
+      <c r="F77" s="35" t="s">
         <v>321</v>
-      </c>
-      <c r="D77" s="34" t="b">
-        <v>0</v>
-      </c>
-      <c r="E77" s="34">
-        <v>0</v>
-      </c>
-      <c r="F77" s="35" t="s">
-        <v>322</v>
       </c>
       <c r="G77" s="34" t="s">
         <v>11</v>
@@ -7479,22 +7476,22 @@
     </row>
     <row r="78" ht="26" spans="1:8">
       <c r="A78" s="32" t="s">
+        <v>322</v>
+      </c>
+      <c r="B78" s="32" t="s">
+        <v>322</v>
+      </c>
+      <c r="C78" s="32" t="s">
         <v>323</v>
       </c>
-      <c r="B78" s="32" t="s">
-        <v>323</v>
-      </c>
-      <c r="C78" s="32" t="s">
+      <c r="D78" s="32" t="b">
+        <v>0</v>
+      </c>
+      <c r="E78" s="32">
+        <v>0</v>
+      </c>
+      <c r="F78" s="33" t="s">
         <v>324</v>
-      </c>
-      <c r="D78" s="32" t="b">
-        <v>0</v>
-      </c>
-      <c r="E78" s="32">
-        <v>0</v>
-      </c>
-      <c r="F78" s="33" t="s">
-        <v>325</v>
       </c>
       <c r="G78" s="32" t="s">
         <v>11</v>
@@ -7505,22 +7502,22 @@
     </row>
     <row r="79" ht="65" spans="1:8">
       <c r="A79" s="34" t="s">
+        <v>325</v>
+      </c>
+      <c r="B79" s="34" t="s">
+        <v>325</v>
+      </c>
+      <c r="C79" s="34" t="s">
         <v>326</v>
       </c>
-      <c r="B79" s="34" t="s">
-        <v>326</v>
-      </c>
-      <c r="C79" s="34" t="s">
+      <c r="D79" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="E79" s="34">
+        <v>0</v>
+      </c>
+      <c r="F79" s="35" t="s">
         <v>327</v>
-      </c>
-      <c r="D79" s="34" t="b">
-        <v>0</v>
-      </c>
-      <c r="E79" s="34">
-        <v>0</v>
-      </c>
-      <c r="F79" s="35" t="s">
-        <v>328</v>
       </c>
       <c r="G79" s="34" t="s">
         <v>11</v>
@@ -7531,22 +7528,22 @@
     </row>
     <row r="80" ht="26" spans="1:8">
       <c r="A80" s="32" t="s">
+        <v>328</v>
+      </c>
+      <c r="B80" s="32" t="s">
+        <v>328</v>
+      </c>
+      <c r="C80" s="32" t="s">
         <v>329</v>
       </c>
-      <c r="B80" s="32" t="s">
-        <v>329</v>
-      </c>
-      <c r="C80" s="32" t="s">
+      <c r="D80" s="32" t="b">
+        <v>0</v>
+      </c>
+      <c r="E80" s="32">
+        <v>0</v>
+      </c>
+      <c r="F80" s="33" t="s">
         <v>330</v>
-      </c>
-      <c r="D80" s="32" t="b">
-        <v>0</v>
-      </c>
-      <c r="E80" s="32">
-        <v>0</v>
-      </c>
-      <c r="F80" s="33" t="s">
-        <v>331</v>
       </c>
       <c r="G80" s="32" t="s">
         <v>11</v>
@@ -7557,22 +7554,22 @@
     </row>
     <row r="81" ht="26" spans="1:8">
       <c r="A81" s="34" t="s">
+        <v>331</v>
+      </c>
+      <c r="B81" s="34" t="s">
+        <v>331</v>
+      </c>
+      <c r="C81" s="34" t="s">
         <v>332</v>
       </c>
-      <c r="B81" s="34" t="s">
-        <v>332</v>
-      </c>
-      <c r="C81" s="34" t="s">
+      <c r="D81" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="E81" s="34">
+        <v>0</v>
+      </c>
+      <c r="F81" s="35" t="s">
         <v>333</v>
-      </c>
-      <c r="D81" s="34" t="b">
-        <v>0</v>
-      </c>
-      <c r="E81" s="34">
-        <v>0</v>
-      </c>
-      <c r="F81" s="35" t="s">
-        <v>334</v>
       </c>
       <c r="G81" s="34" t="s">
         <v>11</v>
@@ -7583,22 +7580,22 @@
     </row>
     <row r="82" ht="26" spans="1:8">
       <c r="A82" s="32" t="s">
+        <v>334</v>
+      </c>
+      <c r="B82" s="32" t="s">
+        <v>334</v>
+      </c>
+      <c r="C82" s="32" t="s">
         <v>335</v>
       </c>
-      <c r="B82" s="32" t="s">
-        <v>335</v>
-      </c>
-      <c r="C82" s="32" t="s">
+      <c r="D82" s="32" t="b">
+        <v>0</v>
+      </c>
+      <c r="E82" s="32">
+        <v>0</v>
+      </c>
+      <c r="F82" s="33" t="s">
         <v>336</v>
-      </c>
-      <c r="D82" s="32" t="b">
-        <v>0</v>
-      </c>
-      <c r="E82" s="32">
-        <v>0</v>
-      </c>
-      <c r="F82" s="33" t="s">
-        <v>337</v>
       </c>
       <c r="G82" s="32" t="s">
         <v>11</v>
@@ -7609,14 +7606,14 @@
     </row>
     <row r="83" spans="1:8">
       <c r="A83" s="34" t="s">
+        <v>337</v>
+      </c>
+      <c r="B83" s="34" t="s">
+        <v>337</v>
+      </c>
+      <c r="C83" s="34" t="s">
         <v>338</v>
       </c>
-      <c r="B83" s="34" t="s">
-        <v>338</v>
-      </c>
-      <c r="C83" s="34" t="s">
-        <v>339</v>
-      </c>
       <c r="D83" s="34" t="b">
         <v>0</v>
       </c>
@@ -7624,7 +7621,7 @@
         <v>0</v>
       </c>
       <c r="F83" s="35" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="G83" s="34" t="s">
         <v>11</v>
@@ -7635,22 +7632,22 @@
     </row>
     <row r="84" spans="1:8">
       <c r="A84" s="32" t="s">
+        <v>339</v>
+      </c>
+      <c r="B84" s="32" t="s">
+        <v>339</v>
+      </c>
+      <c r="C84" s="32" t="s">
         <v>340</v>
       </c>
-      <c r="B84" s="32" t="s">
-        <v>340</v>
-      </c>
-      <c r="C84" s="32" t="s">
+      <c r="D84" s="32" t="b">
+        <v>0</v>
+      </c>
+      <c r="E84" s="32">
+        <v>0</v>
+      </c>
+      <c r="F84" s="33" t="s">
         <v>341</v>
-      </c>
-      <c r="D84" s="32" t="b">
-        <v>0</v>
-      </c>
-      <c r="E84" s="32">
-        <v>0</v>
-      </c>
-      <c r="F84" s="33" t="s">
-        <v>342</v>
       </c>
       <c r="G84" s="32" t="s">
         <v>11</v>
@@ -7661,22 +7658,22 @@
     </row>
     <row r="85" ht="26" spans="1:8">
       <c r="A85" s="34" t="s">
+        <v>300</v>
+      </c>
+      <c r="B85" s="34" t="s">
+        <v>300</v>
+      </c>
+      <c r="C85" s="34" t="s">
         <v>301</v>
       </c>
-      <c r="B85" s="34" t="s">
-        <v>301</v>
-      </c>
-      <c r="C85" s="34" t="s">
+      <c r="D85" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="E85" s="34">
+        <v>0</v>
+      </c>
+      <c r="F85" s="35" t="s">
         <v>302</v>
-      </c>
-      <c r="D85" s="34" t="b">
-        <v>0</v>
-      </c>
-      <c r="E85" s="34">
-        <v>0</v>
-      </c>
-      <c r="F85" s="35" t="s">
-        <v>303</v>
       </c>
       <c r="G85" s="34" t="s">
         <v>11</v>
@@ -7687,22 +7684,22 @@
     </row>
     <row r="86" ht="65" spans="1:8">
       <c r="A86" s="32" t="s">
+        <v>342</v>
+      </c>
+      <c r="B86" s="32" t="s">
+        <v>342</v>
+      </c>
+      <c r="C86" s="32" t="s">
         <v>343</v>
       </c>
-      <c r="B86" s="32" t="s">
-        <v>343</v>
-      </c>
-      <c r="C86" s="32" t="s">
+      <c r="D86" s="32" t="b">
+        <v>0</v>
+      </c>
+      <c r="E86" s="32">
+        <v>0</v>
+      </c>
+      <c r="F86" s="33" t="s">
         <v>344</v>
-      </c>
-      <c r="D86" s="32" t="b">
-        <v>0</v>
-      </c>
-      <c r="E86" s="32">
-        <v>0</v>
-      </c>
-      <c r="F86" s="33" t="s">
-        <v>345</v>
       </c>
       <c r="G86" s="32" t="s">
         <v>11</v>
@@ -7713,13 +7710,13 @@
     </row>
     <row r="87" ht="44" customHeight="1" spans="1:8">
       <c r="A87" s="34" t="s">
+        <v>345</v>
+      </c>
+      <c r="B87" s="34" t="s">
+        <v>345</v>
+      </c>
+      <c r="C87" s="34" t="s">
         <v>346</v>
-      </c>
-      <c r="B87" s="34" t="s">
-        <v>346</v>
-      </c>
-      <c r="C87" s="34" t="s">
-        <v>347</v>
       </c>
       <c r="D87" s="34" t="b">
         <v>1</v>
@@ -7728,7 +7725,7 @@
         <v>1</v>
       </c>
       <c r="F87" s="35" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="G87" s="34" t="s">
         <v>11</v>
@@ -7739,22 +7736,22 @@
     </row>
     <row r="88" ht="40" customHeight="1" spans="1:8">
       <c r="A88" s="32" t="s">
+        <v>348</v>
+      </c>
+      <c r="B88" s="32" t="s">
+        <v>348</v>
+      </c>
+      <c r="C88" s="32" t="s">
+        <v>113</v>
+      </c>
+      <c r="D88" s="32" t="b">
+        <v>0</v>
+      </c>
+      <c r="E88" s="32">
+        <v>0</v>
+      </c>
+      <c r="F88" s="33" t="s">
         <v>349</v>
-      </c>
-      <c r="B88" s="32" t="s">
-        <v>349</v>
-      </c>
-      <c r="C88" s="32" t="s">
-        <v>114</v>
-      </c>
-      <c r="D88" s="32" t="b">
-        <v>0</v>
-      </c>
-      <c r="E88" s="32">
-        <v>0</v>
-      </c>
-      <c r="F88" s="33" t="s">
-        <v>350</v>
       </c>
       <c r="G88" s="32" t="s">
         <v>11</v>
@@ -7800,1276 +7797,1276 @@
         <v>5</v>
       </c>
       <c r="E1" s="12" t="s">
+        <v>350</v>
+      </c>
+      <c r="F1" s="13" t="s">
         <v>351</v>
       </c>
-      <c r="F1" s="13" t="s">
+      <c r="G1" s="13" t="s">
         <v>352</v>
-      </c>
-      <c r="G1" s="13" t="s">
-        <v>353</v>
       </c>
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="14" t="s">
+        <v>353</v>
+      </c>
+      <c r="B2" s="15" t="s">
+        <v>353</v>
+      </c>
+      <c r="C2" s="16" t="s">
         <v>354</v>
       </c>
-      <c r="B2" s="15" t="s">
-        <v>354</v>
-      </c>
-      <c r="C2" s="16" t="s">
+      <c r="D2" s="16" t="s">
         <v>355</v>
-      </c>
-      <c r="D2" s="16" t="s">
-        <v>356</v>
       </c>
       <c r="E2" s="16">
         <v>40</v>
       </c>
       <c r="F2" s="17" t="s">
+        <v>356</v>
+      </c>
+      <c r="G2" s="17" t="s">
         <v>357</v>
-      </c>
-      <c r="G2" s="17" t="s">
-        <v>358</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3" s="18" t="s">
+        <v>358</v>
+      </c>
+      <c r="B3" s="19" t="s">
+        <v>358</v>
+      </c>
+      <c r="C3" s="20" t="s">
         <v>359</v>
       </c>
-      <c r="B3" s="19" t="s">
-        <v>359</v>
-      </c>
-      <c r="C3" s="20" t="s">
+      <c r="D3" s="20" t="s">
         <v>360</v>
-      </c>
-      <c r="D3" s="20" t="s">
-        <v>361</v>
       </c>
       <c r="E3" s="20">
         <v>8</v>
       </c>
       <c r="F3" s="21" t="s">
+        <v>361</v>
+      </c>
+      <c r="G3" s="21" t="s">
         <v>362</v>
-      </c>
-      <c r="G3" s="21" t="s">
-        <v>363</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4" s="14" t="s">
+        <v>363</v>
+      </c>
+      <c r="B4" s="15" t="s">
+        <v>363</v>
+      </c>
+      <c r="C4" s="16" t="s">
         <v>364</v>
       </c>
-      <c r="B4" s="15" t="s">
-        <v>364</v>
-      </c>
-      <c r="C4" s="16" t="s">
+      <c r="D4" s="16" t="s">
         <v>365</v>
-      </c>
-      <c r="D4" s="16" t="s">
-        <v>366</v>
       </c>
       <c r="E4" s="16">
         <v>30</v>
       </c>
       <c r="F4" s="17" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="G4" s="17" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5" s="18" t="s">
+        <v>367</v>
+      </c>
+      <c r="B5" s="19" t="s">
+        <v>367</v>
+      </c>
+      <c r="C5" s="20" t="s">
         <v>368</v>
-      </c>
-      <c r="B5" s="19" t="s">
-        <v>368</v>
-      </c>
-      <c r="C5" s="20" t="s">
-        <v>369</v>
       </c>
       <c r="D5" s="20"/>
       <c r="E5" s="20">
         <v>3</v>
       </c>
       <c r="F5" s="21" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="G5" s="21" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6" s="18" t="s">
+        <v>370</v>
+      </c>
+      <c r="B6" s="19" t="s">
+        <v>370</v>
+      </c>
+      <c r="C6" s="20" t="s">
         <v>371</v>
       </c>
-      <c r="B6" s="19" t="s">
-        <v>371</v>
-      </c>
-      <c r="C6" s="20" t="s">
+      <c r="D6" s="20" t="s">
         <v>372</v>
-      </c>
-      <c r="D6" s="20" t="s">
-        <v>373</v>
       </c>
       <c r="E6" s="20">
         <v>10</v>
       </c>
       <c r="F6" s="21" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="G6" s="21" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7" s="14" t="s">
+        <v>374</v>
+      </c>
+      <c r="B7" s="15" t="s">
+        <v>374</v>
+      </c>
+      <c r="C7" s="16" t="s">
         <v>375</v>
       </c>
-      <c r="B7" s="15" t="s">
-        <v>375</v>
-      </c>
-      <c r="C7" s="16" t="s">
+      <c r="D7" s="16" t="s">
         <v>376</v>
-      </c>
-      <c r="D7" s="16" t="s">
-        <v>377</v>
       </c>
       <c r="E7" s="16">
         <v>25</v>
       </c>
       <c r="F7" s="17" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="G7" s="17" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8" s="18" t="s">
+        <v>378</v>
+      </c>
+      <c r="B8" s="19" t="s">
+        <v>378</v>
+      </c>
+      <c r="C8" s="20" t="s">
         <v>379</v>
       </c>
-      <c r="B8" s="19" t="s">
-        <v>379</v>
-      </c>
-      <c r="C8" s="20" t="s">
+      <c r="D8" s="20" t="s">
         <v>380</v>
-      </c>
-      <c r="D8" s="20" t="s">
-        <v>381</v>
       </c>
       <c r="E8" s="20">
         <v>35</v>
       </c>
       <c r="F8" s="21" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="G8" s="21" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9" s="22" t="s">
+        <v>382</v>
+      </c>
+      <c r="B9" s="23" t="s">
+        <v>382</v>
+      </c>
+      <c r="C9" s="24" t="s">
         <v>383</v>
       </c>
-      <c r="B9" s="23" t="s">
-        <v>383</v>
-      </c>
-      <c r="C9" s="24" t="s">
+      <c r="D9" s="24" t="s">
         <v>384</v>
-      </c>
-      <c r="D9" s="24" t="s">
-        <v>385</v>
       </c>
       <c r="E9" s="24">
         <v>50</v>
       </c>
       <c r="F9" s="25" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="G9" s="25" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10" s="26" t="s">
+        <v>386</v>
+      </c>
+      <c r="B10" s="27" t="s">
+        <v>386</v>
+      </c>
+      <c r="C10" s="28" t="s">
         <v>387</v>
       </c>
-      <c r="B10" s="27" t="s">
-        <v>387</v>
-      </c>
-      <c r="C10" s="28" t="s">
+      <c r="D10" s="28" t="s">
         <v>388</v>
-      </c>
-      <c r="D10" s="28" t="s">
-        <v>389</v>
       </c>
       <c r="E10" s="28">
         <v>55</v>
       </c>
       <c r="F10" s="29" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="G10" s="29" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11" s="22" t="s">
+        <v>390</v>
+      </c>
+      <c r="B11" s="23" t="s">
+        <v>390</v>
+      </c>
+      <c r="C11" s="24" t="s">
         <v>391</v>
       </c>
-      <c r="B11" s="23" t="s">
-        <v>391</v>
-      </c>
-      <c r="C11" s="24" t="s">
+      <c r="D11" s="24" t="s">
         <v>392</v>
-      </c>
-      <c r="D11" s="24" t="s">
-        <v>393</v>
       </c>
       <c r="E11" s="24">
         <v>35</v>
       </c>
       <c r="F11" s="25" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="G11" s="25" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12" s="26" t="s">
+        <v>394</v>
+      </c>
+      <c r="B12" s="27" t="s">
+        <v>394</v>
+      </c>
+      <c r="C12" s="28" t="s">
         <v>395</v>
       </c>
-      <c r="B12" s="27" t="s">
-        <v>395</v>
-      </c>
-      <c r="C12" s="28" t="s">
+      <c r="D12" s="28" t="s">
         <v>396</v>
-      </c>
-      <c r="D12" s="28" t="s">
-        <v>397</v>
       </c>
       <c r="E12" s="28">
         <v>30</v>
       </c>
       <c r="F12" s="29" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="G12" s="29" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13" s="22" t="s">
+        <v>398</v>
+      </c>
+      <c r="B13" s="23" t="s">
+        <v>398</v>
+      </c>
+      <c r="C13" s="24" t="s">
         <v>399</v>
       </c>
-      <c r="B13" s="23" t="s">
-        <v>399</v>
-      </c>
-      <c r="C13" s="24" t="s">
+      <c r="D13" s="24" t="s">
         <v>400</v>
-      </c>
-      <c r="D13" s="24" t="s">
-        <v>401</v>
       </c>
       <c r="E13" s="24">
         <v>40</v>
       </c>
       <c r="F13" s="25" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="G13" s="25" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14" s="26" t="s">
+        <v>402</v>
+      </c>
+      <c r="B14" s="27" t="s">
+        <v>402</v>
+      </c>
+      <c r="C14" s="28" t="s">
         <v>403</v>
       </c>
-      <c r="B14" s="27" t="s">
-        <v>403</v>
-      </c>
-      <c r="C14" s="28" t="s">
+      <c r="D14" s="28" t="s">
         <v>404</v>
-      </c>
-      <c r="D14" s="28" t="s">
-        <v>405</v>
       </c>
       <c r="E14" s="28">
         <v>4</v>
       </c>
       <c r="F14" s="29" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="G14" s="29" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15" s="22" t="s">
+        <v>406</v>
+      </c>
+      <c r="B15" s="23" t="s">
+        <v>406</v>
+      </c>
+      <c r="C15" s="24" t="s">
         <v>407</v>
       </c>
-      <c r="B15" s="23" t="s">
-        <v>407</v>
-      </c>
-      <c r="C15" s="24" t="s">
+      <c r="D15" s="24" t="s">
         <v>408</v>
-      </c>
-      <c r="D15" s="24" t="s">
-        <v>409</v>
       </c>
       <c r="E15" s="24">
         <v>30</v>
       </c>
       <c r="F15" s="25" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="G15" s="25" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
     </row>
     <row r="16" spans="1:7">
       <c r="A16" s="26" t="s">
+        <v>410</v>
+      </c>
+      <c r="B16" s="27" t="s">
+        <v>410</v>
+      </c>
+      <c r="C16" s="28" t="s">
         <v>411</v>
       </c>
-      <c r="B16" s="27" t="s">
-        <v>411</v>
-      </c>
-      <c r="C16" s="28" t="s">
+      <c r="D16" s="28" t="s">
         <v>412</v>
-      </c>
-      <c r="D16" s="28" t="s">
-        <v>413</v>
       </c>
       <c r="E16" s="28">
         <v>70</v>
       </c>
       <c r="F16" s="29" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="G16" s="29" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
     </row>
     <row r="17" spans="1:7">
       <c r="A17" s="22" t="s">
+        <v>414</v>
+      </c>
+      <c r="B17" s="23" t="s">
+        <v>414</v>
+      </c>
+      <c r="C17" s="24" t="s">
         <v>415</v>
       </c>
-      <c r="B17" s="23" t="s">
-        <v>415</v>
-      </c>
-      <c r="C17" s="24" t="s">
+      <c r="D17" s="24" t="s">
         <v>416</v>
-      </c>
-      <c r="D17" s="24" t="s">
-        <v>417</v>
       </c>
       <c r="E17" s="24">
         <v>60</v>
       </c>
       <c r="F17" s="25" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="G17" s="25" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
     </row>
     <row r="18" spans="1:7">
       <c r="A18" s="26" t="s">
+        <v>418</v>
+      </c>
+      <c r="B18" s="27" t="s">
+        <v>418</v>
+      </c>
+      <c r="C18" s="28" t="s">
         <v>419</v>
       </c>
-      <c r="B18" s="27" t="s">
-        <v>419</v>
-      </c>
-      <c r="C18" s="28" t="s">
+      <c r="D18" s="28" t="s">
         <v>420</v>
-      </c>
-      <c r="D18" s="28" t="s">
-        <v>421</v>
       </c>
       <c r="E18" s="28">
         <v>30</v>
       </c>
       <c r="F18" s="29" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="G18" s="29" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
     </row>
     <row r="19" spans="1:7">
       <c r="A19" s="22" t="s">
+        <v>422</v>
+      </c>
+      <c r="B19" s="23" t="s">
+        <v>422</v>
+      </c>
+      <c r="C19" s="24" t="s">
         <v>423</v>
       </c>
-      <c r="B19" s="23" t="s">
-        <v>423</v>
-      </c>
-      <c r="C19" s="24" t="s">
+      <c r="D19" s="24" t="s">
         <v>424</v>
-      </c>
-      <c r="D19" s="24" t="s">
-        <v>425</v>
       </c>
       <c r="E19" s="24">
         <v>30</v>
       </c>
       <c r="F19" s="25" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="G19" s="25" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
     </row>
     <row r="20" spans="1:7">
       <c r="A20" s="26" t="s">
+        <v>426</v>
+      </c>
+      <c r="B20" s="27" t="s">
+        <v>426</v>
+      </c>
+      <c r="C20" s="28" t="s">
         <v>427</v>
       </c>
-      <c r="B20" s="27" t="s">
-        <v>427</v>
-      </c>
-      <c r="C20" s="28" t="s">
+      <c r="D20" s="28" t="s">
         <v>428</v>
-      </c>
-      <c r="D20" s="28" t="s">
-        <v>429</v>
       </c>
       <c r="E20" s="28">
         <v>30</v>
       </c>
       <c r="F20" s="29" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="G20" s="29" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
     </row>
     <row r="21" spans="1:7">
       <c r="A21" s="22" t="s">
+        <v>430</v>
+      </c>
+      <c r="B21" s="23" t="s">
+        <v>430</v>
+      </c>
+      <c r="C21" s="24" t="s">
         <v>431</v>
       </c>
-      <c r="B21" s="23" t="s">
-        <v>431</v>
-      </c>
-      <c r="C21" s="24" t="s">
+      <c r="D21" s="24" t="s">
         <v>432</v>
-      </c>
-      <c r="D21" s="24" t="s">
-        <v>433</v>
       </c>
       <c r="E21" s="24">
         <v>20</v>
       </c>
       <c r="F21" s="25" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="G21" s="25" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
     </row>
     <row r="22" spans="1:7">
       <c r="A22" s="26" t="s">
+        <v>434</v>
+      </c>
+      <c r="B22" s="27" t="s">
+        <v>434</v>
+      </c>
+      <c r="C22" s="28" t="s">
         <v>435</v>
       </c>
-      <c r="B22" s="27" t="s">
-        <v>435</v>
-      </c>
-      <c r="C22" s="28" t="s">
+      <c r="D22" s="28" t="s">
         <v>436</v>
-      </c>
-      <c r="D22" s="28" t="s">
-        <v>437</v>
       </c>
       <c r="E22" s="28">
         <v>100</v>
       </c>
       <c r="F22" s="29" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="G22" s="29" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
     </row>
     <row r="23" spans="1:7">
       <c r="A23" s="22" t="s">
+        <v>438</v>
+      </c>
+      <c r="B23" s="23" t="s">
+        <v>438</v>
+      </c>
+      <c r="C23" s="24" t="s">
         <v>439</v>
       </c>
-      <c r="B23" s="23" t="s">
-        <v>439</v>
-      </c>
-      <c r="C23" s="24" t="s">
+      <c r="D23" s="24" t="s">
         <v>440</v>
-      </c>
-      <c r="D23" s="24" t="s">
-        <v>441</v>
       </c>
       <c r="E23" s="24">
         <v>10</v>
       </c>
       <c r="F23" s="25" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="G23" s="25" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
     </row>
     <row r="24" spans="1:7">
       <c r="A24" s="26" t="s">
+        <v>442</v>
+      </c>
+      <c r="B24" s="27" t="s">
+        <v>442</v>
+      </c>
+      <c r="C24" s="28" t="s">
         <v>443</v>
       </c>
-      <c r="B24" s="27" t="s">
-        <v>443</v>
-      </c>
-      <c r="C24" s="28" t="s">
+      <c r="D24" s="28" t="s">
         <v>444</v>
-      </c>
-      <c r="D24" s="28" t="s">
-        <v>445</v>
       </c>
       <c r="E24" s="28">
         <v>20</v>
       </c>
       <c r="F24" s="29" t="s">
+        <v>445</v>
+      </c>
+      <c r="G24" s="29" t="s">
         <v>446</v>
-      </c>
-      <c r="G24" s="29" t="s">
-        <v>447</v>
       </c>
     </row>
     <row r="25" spans="1:7">
       <c r="A25" s="22" t="s">
+        <v>447</v>
+      </c>
+      <c r="B25" s="23" t="s">
+        <v>447</v>
+      </c>
+      <c r="C25" s="24" t="s">
         <v>448</v>
       </c>
-      <c r="B25" s="23" t="s">
-        <v>448</v>
-      </c>
-      <c r="C25" s="24" t="s">
+      <c r="D25" s="24" t="s">
         <v>449</v>
-      </c>
-      <c r="D25" s="24" t="s">
-        <v>450</v>
       </c>
       <c r="E25" s="24">
         <v>20</v>
       </c>
       <c r="F25" s="25" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="G25" s="25" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
     </row>
     <row r="26" spans="1:7">
       <c r="A26" s="26" t="s">
+        <v>451</v>
+      </c>
+      <c r="B26" s="27" t="s">
+        <v>451</v>
+      </c>
+      <c r="C26" s="28" t="s">
         <v>452</v>
       </c>
-      <c r="B26" s="27" t="s">
-        <v>452</v>
-      </c>
-      <c r="C26" s="28" t="s">
+      <c r="D26" s="28" t="s">
         <v>453</v>
-      </c>
-      <c r="D26" s="28" t="s">
-        <v>454</v>
       </c>
       <c r="E26" s="28">
         <v>35</v>
       </c>
       <c r="F26" s="29" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="G26" s="29" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
     </row>
     <row r="27" spans="1:7">
       <c r="A27" s="22" t="s">
+        <v>455</v>
+      </c>
+      <c r="B27" s="23" t="s">
+        <v>455</v>
+      </c>
+      <c r="C27" s="24" t="s">
         <v>456</v>
       </c>
-      <c r="B27" s="23" t="s">
-        <v>456</v>
-      </c>
-      <c r="C27" s="24" t="s">
+      <c r="D27" s="24" t="s">
         <v>457</v>
-      </c>
-      <c r="D27" s="24" t="s">
-        <v>458</v>
       </c>
       <c r="E27" s="24">
         <v>50</v>
       </c>
       <c r="F27" s="25" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="G27" s="25" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
     </row>
     <row r="28" spans="1:7">
       <c r="A28" s="26" t="s">
+        <v>459</v>
+      </c>
+      <c r="B28" s="27" t="s">
+        <v>459</v>
+      </c>
+      <c r="C28" s="28" t="s">
         <v>460</v>
       </c>
-      <c r="B28" s="27" t="s">
-        <v>460</v>
-      </c>
-      <c r="C28" s="28" t="s">
+      <c r="D28" s="28" t="s">
         <v>461</v>
-      </c>
-      <c r="D28" s="28" t="s">
-        <v>462</v>
       </c>
       <c r="E28" s="28">
         <v>20</v>
       </c>
       <c r="F28" s="29" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="G28" s="29" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
     </row>
     <row r="29" spans="1:7">
       <c r="A29" s="22" t="s">
+        <v>463</v>
+      </c>
+      <c r="B29" s="23" t="s">
+        <v>463</v>
+      </c>
+      <c r="C29" s="24" t="s">
         <v>464</v>
       </c>
-      <c r="B29" s="23" t="s">
-        <v>464</v>
-      </c>
-      <c r="C29" s="24" t="s">
+      <c r="D29" s="24" t="s">
         <v>465</v>
-      </c>
-      <c r="D29" s="24" t="s">
-        <v>466</v>
       </c>
       <c r="E29" s="24">
         <v>5</v>
       </c>
       <c r="F29" s="25" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="G29" s="25" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
     </row>
     <row r="30" spans="1:7">
       <c r="A30" s="26" t="s">
+        <v>467</v>
+      </c>
+      <c r="B30" s="27" t="s">
+        <v>467</v>
+      </c>
+      <c r="C30" s="28" t="s">
         <v>468</v>
       </c>
-      <c r="B30" s="27" t="s">
-        <v>468</v>
-      </c>
-      <c r="C30" s="28" t="s">
+      <c r="D30" s="28" t="s">
         <v>469</v>
-      </c>
-      <c r="D30" s="28" t="s">
-        <v>470</v>
       </c>
       <c r="E30" s="28">
         <v>20</v>
       </c>
       <c r="F30" s="29" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="G30" s="29" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
     </row>
     <row r="31" spans="1:7">
       <c r="A31" s="22" t="s">
+        <v>471</v>
+      </c>
+      <c r="B31" s="23" t="s">
+        <v>471</v>
+      </c>
+      <c r="C31" s="24" t="s">
         <v>472</v>
       </c>
-      <c r="B31" s="23" t="s">
-        <v>472</v>
-      </c>
-      <c r="C31" s="24" t="s">
+      <c r="D31" s="24" t="s">
         <v>473</v>
-      </c>
-      <c r="D31" s="24" t="s">
-        <v>474</v>
       </c>
       <c r="E31" s="24">
         <v>15</v>
       </c>
       <c r="F31" s="25" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="G31" s="25" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
     </row>
     <row r="32" spans="1:7">
       <c r="A32" s="26" t="s">
+        <v>475</v>
+      </c>
+      <c r="B32" s="27" t="s">
+        <v>475</v>
+      </c>
+      <c r="C32" s="28" t="s">
         <v>476</v>
       </c>
-      <c r="B32" s="27" t="s">
-        <v>476</v>
-      </c>
-      <c r="C32" s="28" t="s">
+      <c r="D32" s="28" t="s">
         <v>477</v>
-      </c>
-      <c r="D32" s="28" t="s">
-        <v>478</v>
       </c>
       <c r="E32" s="28">
         <v>15</v>
       </c>
       <c r="F32" s="29" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="G32" s="29" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
     </row>
     <row r="33" spans="1:7">
       <c r="A33" s="22" t="s">
+        <v>479</v>
+      </c>
+      <c r="B33" s="23" t="s">
+        <v>479</v>
+      </c>
+      <c r="C33" s="24" t="s">
         <v>480</v>
       </c>
-      <c r="B33" s="23" t="s">
-        <v>480</v>
-      </c>
-      <c r="C33" s="24" t="s">
+      <c r="D33" s="24" t="s">
         <v>481</v>
-      </c>
-      <c r="D33" s="24" t="s">
-        <v>482</v>
       </c>
       <c r="E33" s="24">
         <v>15</v>
       </c>
       <c r="F33" s="25" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="G33" s="25" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
     </row>
     <row r="34" spans="1:7">
       <c r="A34" s="26" t="s">
+        <v>483</v>
+      </c>
+      <c r="B34" s="27" t="s">
+        <v>483</v>
+      </c>
+      <c r="C34" s="28" t="s">
         <v>484</v>
       </c>
-      <c r="B34" s="27" t="s">
-        <v>484</v>
-      </c>
-      <c r="C34" s="28" t="s">
+      <c r="D34" s="28" t="s">
         <v>485</v>
-      </c>
-      <c r="D34" s="28" t="s">
-        <v>486</v>
       </c>
       <c r="E34" s="28">
         <v>5</v>
       </c>
       <c r="F34" s="29" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="G34" s="29" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
     </row>
     <row r="35" spans="1:7">
       <c r="A35" s="22" t="s">
+        <v>487</v>
+      </c>
+      <c r="B35" s="23" t="s">
+        <v>487</v>
+      </c>
+      <c r="C35" s="24" t="s">
         <v>488</v>
       </c>
-      <c r="B35" s="23" t="s">
-        <v>488</v>
-      </c>
-      <c r="C35" s="24" t="s">
+      <c r="D35" s="24" t="s">
         <v>489</v>
-      </c>
-      <c r="D35" s="24" t="s">
-        <v>490</v>
       </c>
       <c r="E35" s="24">
         <v>25</v>
       </c>
       <c r="F35" s="25" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="G35" s="25" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
     </row>
     <row r="36" spans="1:7">
       <c r="A36" s="26" t="s">
+        <v>491</v>
+      </c>
+      <c r="B36" s="27" t="s">
+        <v>491</v>
+      </c>
+      <c r="C36" s="28" t="s">
         <v>492</v>
       </c>
-      <c r="B36" s="27" t="s">
-        <v>492</v>
-      </c>
-      <c r="C36" s="28" t="s">
+      <c r="D36" s="28" t="s">
         <v>493</v>
-      </c>
-      <c r="D36" s="28" t="s">
-        <v>494</v>
       </c>
       <c r="E36" s="28">
         <v>10</v>
       </c>
       <c r="F36" s="29" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="G36" s="29" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
     </row>
     <row r="37" spans="1:7">
       <c r="A37" s="22" t="s">
+        <v>495</v>
+      </c>
+      <c r="B37" s="23" t="s">
+        <v>495</v>
+      </c>
+      <c r="C37" s="24" t="s">
         <v>496</v>
       </c>
-      <c r="B37" s="23" t="s">
-        <v>496</v>
-      </c>
-      <c r="C37" s="24" t="s">
+      <c r="D37" s="24" t="s">
         <v>497</v>
-      </c>
-      <c r="D37" s="24" t="s">
-        <v>498</v>
       </c>
       <c r="E37" s="24">
         <v>8</v>
       </c>
       <c r="F37" s="25" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="G37" s="25" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
     </row>
     <row r="38" spans="1:7">
       <c r="A38" s="26" t="s">
+        <v>499</v>
+      </c>
+      <c r="B38" s="27" t="s">
+        <v>499</v>
+      </c>
+      <c r="C38" s="28" t="s">
         <v>500</v>
       </c>
-      <c r="B38" s="27" t="s">
-        <v>500</v>
-      </c>
-      <c r="C38" s="28" t="s">
+      <c r="D38" s="28" t="s">
         <v>501</v>
-      </c>
-      <c r="D38" s="28" t="s">
-        <v>502</v>
       </c>
       <c r="E38" s="28">
         <v>100</v>
       </c>
       <c r="F38" s="29" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="G38" s="29" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
     </row>
     <row r="39" spans="1:7">
       <c r="A39" s="22" t="s">
+        <v>503</v>
+      </c>
+      <c r="B39" s="23" t="s">
+        <v>503</v>
+      </c>
+      <c r="C39" s="24" t="s">
         <v>504</v>
       </c>
-      <c r="B39" s="23" t="s">
-        <v>504</v>
-      </c>
-      <c r="C39" s="24" t="s">
+      <c r="D39" s="24" t="s">
         <v>505</v>
-      </c>
-      <c r="D39" s="24" t="s">
-        <v>506</v>
       </c>
       <c r="E39" s="24">
         <v>20</v>
       </c>
       <c r="F39" s="25" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="G39" s="25" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
     </row>
     <row r="40" spans="1:7">
       <c r="A40" s="18" t="s">
+        <v>507</v>
+      </c>
+      <c r="B40" s="19" t="s">
+        <v>507</v>
+      </c>
+      <c r="C40" s="20" t="s">
         <v>508</v>
       </c>
-      <c r="B40" s="19" t="s">
-        <v>508</v>
-      </c>
-      <c r="C40" s="20" t="s">
+      <c r="D40" s="20" t="s">
         <v>509</v>
-      </c>
-      <c r="D40" s="20" t="s">
-        <v>510</v>
       </c>
       <c r="E40" s="20">
         <v>10</v>
       </c>
       <c r="F40" s="21" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="G40" s="21" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
     </row>
     <row r="41" spans="1:7">
       <c r="A41" s="14" t="s">
+        <v>511</v>
+      </c>
+      <c r="B41" s="15" t="s">
+        <v>511</v>
+      </c>
+      <c r="C41" s="16" t="s">
         <v>512</v>
       </c>
-      <c r="B41" s="15" t="s">
-        <v>512</v>
-      </c>
-      <c r="C41" s="16" t="s">
+      <c r="D41" s="16" t="s">
         <v>513</v>
-      </c>
-      <c r="D41" s="16" t="s">
-        <v>514</v>
       </c>
       <c r="E41" s="16">
         <v>10</v>
       </c>
       <c r="F41" s="17" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="G41" s="17" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
     </row>
     <row r="42" spans="1:7">
       <c r="A42" s="18" t="s">
+        <v>515</v>
+      </c>
+      <c r="B42" s="19" t="s">
+        <v>515</v>
+      </c>
+      <c r="C42" s="20" t="s">
         <v>516</v>
       </c>
-      <c r="B42" s="19" t="s">
-        <v>516</v>
-      </c>
-      <c r="C42" s="20" t="s">
+      <c r="D42" s="20" t="s">
         <v>517</v>
-      </c>
-      <c r="D42" s="20" t="s">
-        <v>518</v>
       </c>
       <c r="E42" s="20">
         <v>12</v>
       </c>
       <c r="F42" s="21" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="G42" s="21" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
     </row>
     <row r="43" spans="1:7">
       <c r="A43" s="14" t="s">
+        <v>519</v>
+      </c>
+      <c r="B43" s="15" t="s">
+        <v>519</v>
+      </c>
+      <c r="C43" s="16" t="s">
         <v>520</v>
       </c>
-      <c r="B43" s="15" t="s">
-        <v>520</v>
-      </c>
-      <c r="C43" s="16" t="s">
+      <c r="D43" s="16" t="s">
         <v>521</v>
-      </c>
-      <c r="D43" s="16" t="s">
-        <v>522</v>
       </c>
       <c r="E43" s="16">
         <v>15</v>
       </c>
       <c r="F43" s="17" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="G43" s="17" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
     </row>
     <row r="44" spans="1:7">
       <c r="A44" s="18" t="s">
+        <v>523</v>
+      </c>
+      <c r="B44" s="19" t="s">
+        <v>523</v>
+      </c>
+      <c r="C44" s="20" t="s">
         <v>524</v>
       </c>
-      <c r="B44" s="19" t="s">
-        <v>524</v>
-      </c>
-      <c r="C44" s="20" t="s">
-        <v>525</v>
-      </c>
       <c r="D44" s="20" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="E44" s="20">
         <v>25</v>
       </c>
       <c r="F44" s="21" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="G44" s="21" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
     </row>
     <row r="45" spans="1:7">
       <c r="A45" s="14" t="s">
+        <v>525</v>
+      </c>
+      <c r="B45" s="15" t="s">
+        <v>525</v>
+      </c>
+      <c r="C45" s="16" t="s">
         <v>526</v>
       </c>
-      <c r="B45" s="15" t="s">
-        <v>526</v>
-      </c>
-      <c r="C45" s="16" t="s">
+      <c r="D45" s="16" t="s">
         <v>527</v>
-      </c>
-      <c r="D45" s="16" t="s">
-        <v>528</v>
       </c>
       <c r="E45" s="16">
         <v>3</v>
       </c>
       <c r="F45" s="17" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="G45" s="17" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
     </row>
     <row r="46" spans="1:7">
       <c r="A46" s="18" t="s">
+        <v>529</v>
+      </c>
+      <c r="B46" s="19" t="s">
+        <v>529</v>
+      </c>
+      <c r="C46" s="20" t="s">
         <v>530</v>
       </c>
-      <c r="B46" s="19" t="s">
-        <v>530</v>
-      </c>
-      <c r="C46" s="20" t="s">
+      <c r="D46" s="20" t="s">
         <v>531</v>
-      </c>
-      <c r="D46" s="20" t="s">
-        <v>532</v>
       </c>
       <c r="E46" s="20">
         <v>2</v>
       </c>
       <c r="F46" s="21" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="G46" s="21" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
     </row>
     <row r="47" spans="1:7">
       <c r="A47" s="14" t="s">
+        <v>533</v>
+      </c>
+      <c r="B47" s="15" t="s">
+        <v>533</v>
+      </c>
+      <c r="C47" s="16" t="s">
         <v>534</v>
       </c>
-      <c r="B47" s="15" t="s">
-        <v>534</v>
-      </c>
-      <c r="C47" s="16" t="s">
+      <c r="D47" s="16" t="s">
         <v>535</v>
-      </c>
-      <c r="D47" s="16" t="s">
-        <v>536</v>
       </c>
       <c r="E47" s="16">
         <v>6</v>
       </c>
       <c r="F47" s="17" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="G47" s="17" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
     </row>
     <row r="48" spans="1:7">
       <c r="A48" s="18" t="s">
+        <v>537</v>
+      </c>
+      <c r="B48" s="19" t="s">
+        <v>537</v>
+      </c>
+      <c r="C48" s="20" t="s">
         <v>538</v>
       </c>
-      <c r="B48" s="19" t="s">
-        <v>538</v>
-      </c>
-      <c r="C48" s="20" t="s">
+      <c r="D48" s="20" t="s">
         <v>539</v>
-      </c>
-      <c r="D48" s="20" t="s">
-        <v>540</v>
       </c>
       <c r="E48" s="20">
         <v>4</v>
       </c>
       <c r="F48" s="21" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="G48" s="21" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
     </row>
     <row r="49" spans="1:7">
       <c r="A49" s="14" t="s">
+        <v>541</v>
+      </c>
+      <c r="B49" s="15" t="s">
+        <v>541</v>
+      </c>
+      <c r="C49" s="16" t="s">
         <v>542</v>
       </c>
-      <c r="B49" s="15" t="s">
-        <v>542</v>
-      </c>
-      <c r="C49" s="16" t="s">
-        <v>543</v>
-      </c>
       <c r="D49" s="16" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="E49" s="16">
         <v>3</v>
       </c>
       <c r="F49" s="17" t="s">
+        <v>361</v>
+      </c>
+      <c r="G49" s="17" t="s">
         <v>362</v>
-      </c>
-      <c r="G49" s="17" t="s">
-        <v>363</v>
       </c>
     </row>
     <row r="50" spans="1:7">
       <c r="A50" s="18" t="s">
+        <v>543</v>
+      </c>
+      <c r="B50" s="19" t="s">
+        <v>543</v>
+      </c>
+      <c r="C50" s="20" t="s">
         <v>544</v>
       </c>
-      <c r="B50" s="19" t="s">
-        <v>544</v>
-      </c>
-      <c r="C50" s="20" t="s">
+      <c r="D50" s="20" t="s">
         <v>545</v>
-      </c>
-      <c r="D50" s="20" t="s">
-        <v>546</v>
       </c>
       <c r="E50" s="20">
         <v>4</v>
       </c>
       <c r="F50" s="21" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="G50" s="21" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
     </row>
     <row r="51" spans="1:7">
       <c r="A51" s="14" t="s">
+        <v>547</v>
+      </c>
+      <c r="B51" s="15" t="s">
+        <v>547</v>
+      </c>
+      <c r="C51" s="16" t="s">
         <v>548</v>
       </c>
-      <c r="B51" s="15" t="s">
-        <v>548</v>
-      </c>
-      <c r="C51" s="16" t="s">
+      <c r="D51" s="16" t="s">
         <v>549</v>
-      </c>
-      <c r="D51" s="16" t="s">
-        <v>550</v>
       </c>
       <c r="E51" s="16">
         <v>4</v>
       </c>
       <c r="F51" s="17" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="G51" s="17" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
     </row>
     <row r="52" spans="1:7">
       <c r="A52" s="18" t="s">
+        <v>551</v>
+      </c>
+      <c r="B52" s="19" t="s">
+        <v>551</v>
+      </c>
+      <c r="C52" s="20" t="s">
         <v>552</v>
       </c>
-      <c r="B52" s="19" t="s">
-        <v>552</v>
-      </c>
-      <c r="C52" s="20" t="s">
+      <c r="D52" s="20" t="s">
         <v>553</v>
-      </c>
-      <c r="D52" s="20" t="s">
-        <v>554</v>
       </c>
       <c r="E52" s="20">
         <v>6</v>
       </c>
       <c r="F52" s="21" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="G52" s="21" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
     </row>
     <row r="53" spans="1:7">
       <c r="A53" s="14" t="s">
+        <v>555</v>
+      </c>
+      <c r="B53" s="15" t="s">
+        <v>555</v>
+      </c>
+      <c r="C53" s="16" t="s">
         <v>556</v>
       </c>
-      <c r="B53" s="15" t="s">
-        <v>556</v>
-      </c>
-      <c r="C53" s="16" t="s">
+      <c r="D53" s="16" t="s">
         <v>557</v>
-      </c>
-      <c r="D53" s="16" t="s">
-        <v>558</v>
       </c>
       <c r="E53" s="16">
         <v>2</v>
       </c>
       <c r="F53" s="17" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="G53" s="17" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
     </row>
     <row r="54" spans="1:7">
       <c r="A54" s="18" t="s">
+        <v>559</v>
+      </c>
+      <c r="B54" s="19" t="s">
+        <v>559</v>
+      </c>
+      <c r="C54" s="20" t="s">
         <v>560</v>
       </c>
-      <c r="B54" s="19" t="s">
-        <v>560</v>
-      </c>
-      <c r="C54" s="20" t="s">
+      <c r="D54" s="20" t="s">
         <v>561</v>
-      </c>
-      <c r="D54" s="20" t="s">
-        <v>562</v>
       </c>
       <c r="E54" s="20">
         <v>2</v>
       </c>
       <c r="F54" s="21" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="G54" s="21" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
     </row>
     <row r="55" spans="1:7">
       <c r="A55" s="14" t="s">
+        <v>563</v>
+      </c>
+      <c r="B55" s="15" t="s">
+        <v>563</v>
+      </c>
+      <c r="C55" s="16" t="s">
         <v>564</v>
       </c>
-      <c r="B55" s="15" t="s">
-        <v>564</v>
-      </c>
-      <c r="C55" s="16" t="s">
+      <c r="D55" s="16" t="s">
         <v>565</v>
-      </c>
-      <c r="D55" s="16" t="s">
-        <v>566</v>
       </c>
       <c r="E55" s="16">
         <v>4</v>
       </c>
       <c r="F55" s="17" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="G55" s="17" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
     </row>
     <row r="56" spans="1:7">
       <c r="A56" s="18" t="s">
+        <v>567</v>
+      </c>
+      <c r="B56" s="19" t="s">
+        <v>567</v>
+      </c>
+      <c r="C56" s="20" t="s">
         <v>568</v>
       </c>
-      <c r="B56" s="19" t="s">
-        <v>568</v>
-      </c>
-      <c r="C56" s="20" t="s">
+      <c r="D56" s="20" t="s">
         <v>569</v>
-      </c>
-      <c r="D56" s="20" t="s">
-        <v>570</v>
       </c>
       <c r="E56" s="20">
         <v>3</v>
       </c>
       <c r="F56" s="21" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="G56" s="21" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
     </row>
   </sheetData>
@@ -9108,1424 +9105,1424 @@
         <v>5</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>350</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>351</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>352</v>
       </c>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="2" t="s">
+        <v>571</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>572</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="C2" s="3" t="s">
         <v>573</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>574</v>
       </c>
       <c r="D2" s="4"/>
       <c r="E2" s="5">
         <v>25</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="6" t="s">
+        <v>575</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>575</v>
+      </c>
+      <c r="C3" s="5" t="s">
         <v>576</v>
       </c>
-      <c r="B3" s="6" t="s">
-        <v>576</v>
-      </c>
-      <c r="C3" s="5" t="s">
+      <c r="D3" s="5" t="s">
         <v>577</v>
-      </c>
-      <c r="D3" s="5" t="s">
-        <v>578</v>
       </c>
       <c r="E3" s="5">
         <v>12</v>
       </c>
       <c r="F3" s="7" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="8" t="s">
+        <v>579</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>579</v>
+      </c>
+      <c r="C4" s="9" t="s">
         <v>580</v>
-      </c>
-      <c r="B4" s="8" t="s">
-        <v>580</v>
-      </c>
-      <c r="C4" s="9" t="s">
-        <v>581</v>
       </c>
       <c r="D4" s="4"/>
       <c r="E4" s="5">
         <v>20</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="6" t="s">
+        <v>582</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>582</v>
+      </c>
+      <c r="C5" s="3" t="s">
         <v>583</v>
-      </c>
-      <c r="B5" s="6" t="s">
-        <v>583</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>584</v>
       </c>
       <c r="D5" s="4"/>
       <c r="E5" s="5">
         <v>40</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="6" t="s">
+        <v>585</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>585</v>
+      </c>
+      <c r="C6" s="5" t="s">
         <v>586</v>
       </c>
-      <c r="B6" s="6" t="s">
-        <v>586</v>
-      </c>
-      <c r="C6" s="5" t="s">
+      <c r="D6" s="5" t="s">
         <v>587</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>588</v>
       </c>
       <c r="E6" s="5">
         <v>20</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="6" t="s">
+        <v>589</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>589</v>
+      </c>
+      <c r="C7" s="5" t="s">
         <v>590</v>
       </c>
-      <c r="B7" s="6" t="s">
-        <v>590</v>
-      </c>
-      <c r="C7" s="5" t="s">
+      <c r="D7" s="5" t="s">
         <v>591</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>592</v>
       </c>
       <c r="E7" s="5">
         <v>15</v>
       </c>
       <c r="F7" s="7" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="6" t="s">
+        <v>593</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>593</v>
+      </c>
+      <c r="C8" s="5" t="s">
         <v>594</v>
       </c>
-      <c r="B8" s="6" t="s">
-        <v>594</v>
-      </c>
-      <c r="C8" s="5" t="s">
+      <c r="D8" s="5" t="s">
         <v>595</v>
-      </c>
-      <c r="D8" s="5" t="s">
-        <v>596</v>
       </c>
       <c r="E8" s="5">
         <v>40</v>
       </c>
       <c r="F8" s="7" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="6" t="s">
+        <v>597</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>597</v>
+      </c>
+      <c r="C9" s="5" t="s">
         <v>598</v>
       </c>
-      <c r="B9" s="6" t="s">
-        <v>598</v>
-      </c>
-      <c r="C9" s="5" t="s">
+      <c r="D9" s="5" t="s">
         <v>599</v>
-      </c>
-      <c r="D9" s="5" t="s">
-        <v>600</v>
       </c>
       <c r="E9" s="5">
         <v>15</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="6" t="s">
+        <v>601</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>601</v>
+      </c>
+      <c r="C10" s="5" t="s">
         <v>602</v>
       </c>
-      <c r="B10" s="6" t="s">
-        <v>602</v>
-      </c>
-      <c r="C10" s="5" t="s">
+      <c r="D10" s="5" t="s">
         <v>603</v>
-      </c>
-      <c r="D10" s="5" t="s">
-        <v>604</v>
       </c>
       <c r="E10" s="5">
         <v>15</v>
       </c>
       <c r="F10" s="7" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="6" t="s">
+        <v>605</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>605</v>
+      </c>
+      <c r="C11" s="5" t="s">
         <v>606</v>
       </c>
-      <c r="B11" s="6" t="s">
-        <v>606</v>
-      </c>
-      <c r="C11" s="5" t="s">
+      <c r="D11" s="5" t="s">
         <v>607</v>
-      </c>
-      <c r="D11" s="5" t="s">
-        <v>608</v>
       </c>
       <c r="E11" s="5">
         <v>30</v>
       </c>
       <c r="F11" s="7" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="6" t="s">
+        <v>609</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>609</v>
+      </c>
+      <c r="C12" s="5" t="s">
         <v>610</v>
       </c>
-      <c r="B12" s="6" t="s">
-        <v>610</v>
-      </c>
-      <c r="C12" s="5" t="s">
+      <c r="D12" s="5" t="s">
         <v>611</v>
-      </c>
-      <c r="D12" s="5" t="s">
-        <v>612</v>
       </c>
       <c r="E12" s="5">
         <v>15</v>
       </c>
       <c r="F12" s="7" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="6" t="s">
+        <v>613</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>613</v>
+      </c>
+      <c r="C13" s="5" t="s">
         <v>614</v>
       </c>
-      <c r="B13" s="6" t="s">
-        <v>614</v>
-      </c>
-      <c r="C13" s="5" t="s">
+      <c r="D13" s="5" t="s">
         <v>615</v>
-      </c>
-      <c r="D13" s="5" t="s">
-        <v>616</v>
       </c>
       <c r="E13" s="5">
         <v>15</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="6" t="s">
+        <v>617</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>617</v>
+      </c>
+      <c r="C14" s="5" t="s">
         <v>618</v>
       </c>
-      <c r="B14" s="6" t="s">
-        <v>618</v>
-      </c>
-      <c r="C14" s="5" t="s">
+      <c r="D14" s="5" t="s">
         <v>619</v>
-      </c>
-      <c r="D14" s="5" t="s">
-        <v>620</v>
       </c>
       <c r="E14" s="5">
         <v>20</v>
       </c>
       <c r="F14" s="7" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="6" t="s">
+        <v>621</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>621</v>
+      </c>
+      <c r="C15" s="5" t="s">
         <v>622</v>
       </c>
-      <c r="B15" s="6" t="s">
-        <v>622</v>
-      </c>
-      <c r="C15" s="5" t="s">
+      <c r="D15" s="5" t="s">
         <v>623</v>
-      </c>
-      <c r="D15" s="5" t="s">
-        <v>624</v>
       </c>
       <c r="E15" s="5">
         <v>20</v>
       </c>
       <c r="F15" s="7" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="6" t="s">
+        <v>625</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>625</v>
+      </c>
+      <c r="C16" s="5" t="s">
         <v>626</v>
       </c>
-      <c r="B16" s="6" t="s">
-        <v>626</v>
-      </c>
-      <c r="C16" s="5" t="s">
+      <c r="D16" s="5" t="s">
         <v>627</v>
-      </c>
-      <c r="D16" s="5" t="s">
-        <v>628</v>
       </c>
       <c r="E16" s="5">
         <v>15</v>
       </c>
       <c r="F16" s="7" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
     </row>
     <row r="17" spans="1:6">
       <c r="A17" s="6" t="s">
+        <v>629</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>629</v>
+      </c>
+      <c r="C17" s="5" t="s">
         <v>630</v>
       </c>
-      <c r="B17" s="6" t="s">
-        <v>630</v>
-      </c>
-      <c r="C17" s="5" t="s">
+      <c r="D17" s="5" t="s">
         <v>631</v>
-      </c>
-      <c r="D17" s="5" t="s">
-        <v>632</v>
       </c>
       <c r="E17" s="5">
         <v>20</v>
       </c>
       <c r="F17" s="7" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
     </row>
     <row r="18" spans="1:6">
       <c r="A18" s="6" t="s">
+        <v>633</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>633</v>
+      </c>
+      <c r="C18" s="5" t="s">
         <v>634</v>
       </c>
-      <c r="B18" s="6" t="s">
-        <v>634</v>
-      </c>
-      <c r="C18" s="5" t="s">
+      <c r="D18" s="5" t="s">
         <v>635</v>
-      </c>
-      <c r="D18" s="5" t="s">
-        <v>636</v>
       </c>
       <c r="E18" s="5">
         <v>12</v>
       </c>
       <c r="F18" s="7" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
     </row>
     <row r="19" spans="1:6">
       <c r="A19" s="6" t="s">
+        <v>637</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>637</v>
+      </c>
+      <c r="C19" s="5" t="s">
         <v>638</v>
       </c>
-      <c r="B19" s="6" t="s">
-        <v>638</v>
-      </c>
-      <c r="C19" s="5" t="s">
+      <c r="D19" s="5" t="s">
         <v>639</v>
-      </c>
-      <c r="D19" s="5" t="s">
-        <v>640</v>
       </c>
       <c r="E19" s="5">
         <v>15</v>
       </c>
       <c r="F19" s="7" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
     </row>
     <row r="20" spans="1:6">
       <c r="A20" s="6" t="s">
+        <v>641</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>641</v>
+      </c>
+      <c r="C20" s="5" t="s">
         <v>642</v>
       </c>
-      <c r="B20" s="6" t="s">
-        <v>642</v>
-      </c>
-      <c r="C20" s="5" t="s">
+      <c r="D20" s="5" t="s">
         <v>643</v>
-      </c>
-      <c r="D20" s="5" t="s">
-        <v>644</v>
       </c>
       <c r="E20" s="5">
         <v>12</v>
       </c>
       <c r="F20" s="7" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
     </row>
     <row r="21" spans="1:6">
       <c r="A21" s="6" t="s">
+        <v>645</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>645</v>
+      </c>
+      <c r="C21" s="5" t="s">
         <v>646</v>
       </c>
-      <c r="B21" s="6" t="s">
-        <v>646</v>
-      </c>
-      <c r="C21" s="5" t="s">
+      <c r="D21" s="5" t="s">
         <v>647</v>
-      </c>
-      <c r="D21" s="5" t="s">
-        <v>648</v>
       </c>
       <c r="E21" s="5">
         <v>20</v>
       </c>
       <c r="F21" s="7" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
     </row>
     <row r="22" spans="1:6">
       <c r="A22" s="6" t="s">
+        <v>649</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>649</v>
+      </c>
+      <c r="C22" s="5" t="s">
         <v>650</v>
       </c>
-      <c r="B22" s="6" t="s">
-        <v>650</v>
-      </c>
-      <c r="C22" s="5" t="s">
+      <c r="D22" s="5" t="s">
         <v>651</v>
-      </c>
-      <c r="D22" s="5" t="s">
-        <v>652</v>
       </c>
       <c r="E22" s="5">
         <v>15</v>
       </c>
       <c r="F22" s="7" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
     </row>
     <row r="23" spans="1:6">
       <c r="A23" s="6" t="s">
+        <v>653</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>653</v>
+      </c>
+      <c r="C23" s="5" t="s">
         <v>654</v>
       </c>
-      <c r="B23" s="6" t="s">
-        <v>654</v>
-      </c>
-      <c r="C23" s="5" t="s">
+      <c r="D23" s="5" t="s">
         <v>655</v>
-      </c>
-      <c r="D23" s="5" t="s">
-        <v>656</v>
       </c>
       <c r="E23" s="5">
         <v>15</v>
       </c>
       <c r="F23" s="7" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
     </row>
     <row r="24" spans="1:6">
       <c r="A24" s="6" t="s">
+        <v>657</v>
+      </c>
+      <c r="B24" s="6" t="s">
+        <v>657</v>
+      </c>
+      <c r="C24" s="5" t="s">
         <v>658</v>
       </c>
-      <c r="B24" s="6" t="s">
-        <v>658</v>
-      </c>
-      <c r="C24" s="5" t="s">
+      <c r="D24" s="5" t="s">
         <v>659</v>
-      </c>
-      <c r="D24" s="5" t="s">
-        <v>660</v>
       </c>
       <c r="E24" s="5">
         <v>15</v>
       </c>
       <c r="F24" s="7" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
     </row>
     <row r="25" spans="1:6">
       <c r="A25" s="6" t="s">
+        <v>661</v>
+      </c>
+      <c r="B25" s="6" t="s">
+        <v>661</v>
+      </c>
+      <c r="C25" s="5" t="s">
         <v>662</v>
       </c>
-      <c r="B25" s="6" t="s">
-        <v>662</v>
-      </c>
-      <c r="C25" s="5" t="s">
+      <c r="D25" s="5" t="s">
         <v>663</v>
-      </c>
-      <c r="D25" s="5" t="s">
-        <v>664</v>
       </c>
       <c r="E25" s="5">
         <v>15</v>
       </c>
       <c r="F25" s="7" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
     </row>
     <row r="26" spans="1:6">
       <c r="A26" s="6" t="s">
+        <v>665</v>
+      </c>
+      <c r="B26" s="6" t="s">
+        <v>665</v>
+      </c>
+      <c r="C26" s="5" t="s">
         <v>666</v>
       </c>
-      <c r="B26" s="6" t="s">
-        <v>666</v>
-      </c>
-      <c r="C26" s="5" t="s">
+      <c r="D26" s="5" t="s">
         <v>667</v>
-      </c>
-      <c r="D26" s="5" t="s">
-        <v>668</v>
       </c>
       <c r="E26" s="5">
         <v>15</v>
       </c>
       <c r="F26" s="7" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
     </row>
     <row r="27" spans="1:6">
       <c r="A27" s="6" t="s">
+        <v>669</v>
+      </c>
+      <c r="B27" s="6" t="s">
+        <v>669</v>
+      </c>
+      <c r="C27" s="5" t="s">
         <v>670</v>
       </c>
-      <c r="B27" s="6" t="s">
-        <v>670</v>
-      </c>
-      <c r="C27" s="5" t="s">
+      <c r="D27" s="5" t="s">
         <v>671</v>
-      </c>
-      <c r="D27" s="5" t="s">
-        <v>672</v>
       </c>
       <c r="E27" s="5">
         <v>15</v>
       </c>
       <c r="F27" s="7" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
     </row>
     <row r="28" spans="1:6">
       <c r="A28" s="6" t="s">
+        <v>673</v>
+      </c>
+      <c r="B28" s="6" t="s">
+        <v>673</v>
+      </c>
+      <c r="C28" s="5" t="s">
         <v>674</v>
       </c>
-      <c r="B28" s="6" t="s">
-        <v>674</v>
-      </c>
-      <c r="C28" s="5" t="s">
+      <c r="D28" s="5" t="s">
         <v>675</v>
-      </c>
-      <c r="D28" s="5" t="s">
-        <v>676</v>
       </c>
       <c r="E28" s="5">
         <v>3</v>
       </c>
       <c r="F28" s="7" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
     </row>
     <row r="29" spans="1:6">
       <c r="A29" s="6" t="s">
+        <v>676</v>
+      </c>
+      <c r="B29" s="6" t="s">
+        <v>676</v>
+      </c>
+      <c r="C29" s="5" t="s">
         <v>677</v>
       </c>
-      <c r="B29" s="6" t="s">
-        <v>677</v>
-      </c>
-      <c r="C29" s="5" t="s">
+      <c r="D29" s="5" t="s">
         <v>678</v>
-      </c>
-      <c r="D29" s="5" t="s">
-        <v>679</v>
       </c>
       <c r="E29" s="5">
         <v>18</v>
       </c>
       <c r="F29" s="7" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
     </row>
     <row r="30" spans="1:6">
       <c r="A30" s="6" t="s">
+        <v>680</v>
+      </c>
+      <c r="B30" s="6" t="s">
+        <v>680</v>
+      </c>
+      <c r="C30" s="5" t="s">
         <v>681</v>
       </c>
-      <c r="B30" s="6" t="s">
-        <v>681</v>
-      </c>
-      <c r="C30" s="5" t="s">
+      <c r="D30" s="5" t="s">
         <v>682</v>
-      </c>
-      <c r="D30" s="5" t="s">
-        <v>683</v>
       </c>
       <c r="E30" s="5">
         <v>15</v>
       </c>
       <c r="F30" s="7" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
     </row>
     <row r="31" spans="1:6">
       <c r="A31" s="6" t="s">
+        <v>684</v>
+      </c>
+      <c r="B31" s="6" t="s">
+        <v>684</v>
+      </c>
+      <c r="C31" s="5" t="s">
         <v>685</v>
       </c>
-      <c r="B31" s="6" t="s">
-        <v>685</v>
-      </c>
-      <c r="C31" s="5" t="s">
+      <c r="D31" s="5" t="s">
         <v>686</v>
-      </c>
-      <c r="D31" s="5" t="s">
-        <v>687</v>
       </c>
       <c r="E31" s="5">
         <v>15</v>
       </c>
       <c r="F31" s="7" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
     </row>
     <row r="32" spans="1:6">
       <c r="A32" s="6" t="s">
+        <v>688</v>
+      </c>
+      <c r="B32" s="6" t="s">
+        <v>688</v>
+      </c>
+      <c r="C32" s="5" t="s">
         <v>689</v>
       </c>
-      <c r="B32" s="6" t="s">
-        <v>689</v>
-      </c>
-      <c r="C32" s="5" t="s">
+      <c r="D32" s="5" t="s">
         <v>690</v>
-      </c>
-      <c r="D32" s="5" t="s">
-        <v>691</v>
       </c>
       <c r="E32" s="5">
         <v>15</v>
       </c>
       <c r="F32" s="7" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
     </row>
     <row r="33" spans="1:6">
       <c r="A33" s="6" t="s">
+        <v>692</v>
+      </c>
+      <c r="B33" s="6" t="s">
+        <v>692</v>
+      </c>
+      <c r="C33" s="5" t="s">
         <v>693</v>
       </c>
-      <c r="B33" s="6" t="s">
-        <v>693</v>
-      </c>
-      <c r="C33" s="5" t="s">
+      <c r="D33" s="5" t="s">
         <v>694</v>
-      </c>
-      <c r="D33" s="5" t="s">
-        <v>695</v>
       </c>
       <c r="E33" s="5">
         <v>18</v>
       </c>
       <c r="F33" s="7" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
     </row>
     <row r="34" spans="1:6">
       <c r="A34" s="6" t="s">
+        <v>696</v>
+      </c>
+      <c r="B34" s="6" t="s">
+        <v>696</v>
+      </c>
+      <c r="C34" s="5" t="s">
         <v>697</v>
       </c>
-      <c r="B34" s="6" t="s">
-        <v>697</v>
-      </c>
-      <c r="C34" s="5" t="s">
+      <c r="D34" s="5" t="s">
         <v>698</v>
-      </c>
-      <c r="D34" s="5" t="s">
-        <v>699</v>
       </c>
       <c r="E34" s="5">
         <v>20</v>
       </c>
       <c r="F34" s="7" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
     </row>
     <row r="35" spans="1:6">
       <c r="A35" s="6" t="s">
+        <v>700</v>
+      </c>
+      <c r="B35" s="6" t="s">
+        <v>700</v>
+      </c>
+      <c r="C35" s="5" t="s">
         <v>701</v>
       </c>
-      <c r="B35" s="6" t="s">
-        <v>701</v>
-      </c>
-      <c r="C35" s="5" t="s">
+      <c r="D35" s="5" t="s">
         <v>702</v>
-      </c>
-      <c r="D35" s="5" t="s">
-        <v>703</v>
       </c>
       <c r="E35" s="5">
         <v>15</v>
       </c>
       <c r="F35" s="7" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
     </row>
     <row r="36" spans="1:6">
       <c r="A36" s="6" t="s">
+        <v>704</v>
+      </c>
+      <c r="B36" s="6" t="s">
+        <v>704</v>
+      </c>
+      <c r="C36" s="5" t="s">
         <v>705</v>
       </c>
-      <c r="B36" s="6" t="s">
-        <v>705</v>
-      </c>
-      <c r="C36" s="5" t="s">
+      <c r="D36" s="5" t="s">
         <v>706</v>
-      </c>
-      <c r="D36" s="5" t="s">
-        <v>707</v>
       </c>
       <c r="E36" s="5">
         <v>18</v>
       </c>
       <c r="F36" s="7" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
     </row>
     <row r="37" spans="1:6">
       <c r="A37" s="6" t="s">
+        <v>708</v>
+      </c>
+      <c r="B37" s="6" t="s">
+        <v>708</v>
+      </c>
+      <c r="C37" s="5" t="s">
         <v>709</v>
       </c>
-      <c r="B37" s="6" t="s">
-        <v>709</v>
-      </c>
-      <c r="C37" s="5" t="s">
+      <c r="D37" s="5" t="s">
         <v>710</v>
-      </c>
-      <c r="D37" s="5" t="s">
-        <v>711</v>
       </c>
       <c r="E37" s="5">
         <v>15</v>
       </c>
       <c r="F37" s="7" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
     </row>
     <row r="38" spans="1:6">
       <c r="A38" s="6" t="s">
+        <v>712</v>
+      </c>
+      <c r="B38" s="6" t="s">
+        <v>712</v>
+      </c>
+      <c r="C38" s="5" t="s">
         <v>713</v>
       </c>
-      <c r="B38" s="6" t="s">
-        <v>713</v>
-      </c>
-      <c r="C38" s="5" t="s">
+      <c r="D38" s="5" t="s">
         <v>714</v>
-      </c>
-      <c r="D38" s="5" t="s">
-        <v>715</v>
       </c>
       <c r="E38" s="5">
         <v>15</v>
       </c>
       <c r="F38" s="7" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
     </row>
     <row r="39" spans="1:6">
       <c r="A39" s="6" t="s">
+        <v>716</v>
+      </c>
+      <c r="B39" s="6" t="s">
+        <v>716</v>
+      </c>
+      <c r="C39" s="5" t="s">
         <v>717</v>
       </c>
-      <c r="B39" s="6" t="s">
-        <v>717</v>
-      </c>
-      <c r="C39" s="5" t="s">
+      <c r="D39" s="5" t="s">
         <v>718</v>
-      </c>
-      <c r="D39" s="5" t="s">
-        <v>719</v>
       </c>
       <c r="E39" s="5">
         <v>15</v>
       </c>
       <c r="F39" s="7" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
     </row>
     <row r="40" spans="1:6">
       <c r="A40" s="6" t="s">
+        <v>720</v>
+      </c>
+      <c r="B40" s="6" t="s">
+        <v>720</v>
+      </c>
+      <c r="C40" s="5" t="s">
         <v>721</v>
       </c>
-      <c r="B40" s="6" t="s">
-        <v>721</v>
-      </c>
-      <c r="C40" s="5" t="s">
+      <c r="D40" s="5" t="s">
         <v>722</v>
-      </c>
-      <c r="D40" s="5" t="s">
-        <v>723</v>
       </c>
       <c r="E40" s="5">
         <v>15</v>
       </c>
       <c r="F40" s="7" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
     </row>
     <row r="41" spans="1:6">
       <c r="A41" s="6" t="s">
+        <v>724</v>
+      </c>
+      <c r="B41" s="6" t="s">
+        <v>724</v>
+      </c>
+      <c r="C41" s="5" t="s">
         <v>725</v>
       </c>
-      <c r="B41" s="6" t="s">
-        <v>725</v>
-      </c>
-      <c r="C41" s="5" t="s">
+      <c r="D41" s="5" t="s">
         <v>726</v>
-      </c>
-      <c r="D41" s="5" t="s">
-        <v>727</v>
       </c>
       <c r="E41" s="5">
         <v>15</v>
       </c>
       <c r="F41" s="7" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
     </row>
     <row r="42" spans="1:6">
       <c r="A42" s="6" t="s">
+        <v>728</v>
+      </c>
+      <c r="B42" s="6" t="s">
+        <v>728</v>
+      </c>
+      <c r="C42" s="5" t="s">
         <v>729</v>
       </c>
-      <c r="B42" s="6" t="s">
-        <v>729</v>
-      </c>
-      <c r="C42" s="5" t="s">
+      <c r="D42" s="5" t="s">
         <v>730</v>
-      </c>
-      <c r="D42" s="5" t="s">
-        <v>731</v>
       </c>
       <c r="E42" s="5">
         <v>15</v>
       </c>
       <c r="F42" s="7" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
     </row>
     <row r="43" spans="1:6">
       <c r="A43" s="6" t="s">
+        <v>732</v>
+      </c>
+      <c r="B43" s="6" t="s">
+        <v>732</v>
+      </c>
+      <c r="C43" s="5" t="s">
         <v>733</v>
       </c>
-      <c r="B43" s="6" t="s">
-        <v>733</v>
-      </c>
-      <c r="C43" s="5" t="s">
+      <c r="D43" s="5" t="s">
         <v>734</v>
-      </c>
-      <c r="D43" s="5" t="s">
-        <v>735</v>
       </c>
       <c r="E43" s="5">
         <v>18</v>
       </c>
       <c r="F43" s="7" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
     </row>
     <row r="44" spans="1:6">
       <c r="A44" s="6" t="s">
+        <v>736</v>
+      </c>
+      <c r="B44" s="6" t="s">
+        <v>736</v>
+      </c>
+      <c r="C44" s="5" t="s">
         <v>737</v>
       </c>
-      <c r="B44" s="6" t="s">
-        <v>737</v>
-      </c>
-      <c r="C44" s="5" t="s">
+      <c r="D44" s="5" t="s">
         <v>738</v>
-      </c>
-      <c r="D44" s="5" t="s">
-        <v>739</v>
       </c>
       <c r="E44" s="5">
         <v>15</v>
       </c>
       <c r="F44" s="7" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
     </row>
     <row r="45" spans="1:6">
       <c r="A45" s="6" t="s">
+        <v>740</v>
+      </c>
+      <c r="B45" s="6" t="s">
+        <v>740</v>
+      </c>
+      <c r="C45" s="5" t="s">
         <v>741</v>
       </c>
-      <c r="B45" s="6" t="s">
-        <v>741</v>
-      </c>
-      <c r="C45" s="5" t="s">
+      <c r="D45" s="5" t="s">
         <v>742</v>
-      </c>
-      <c r="D45" s="5" t="s">
-        <v>743</v>
       </c>
       <c r="E45" s="5">
         <v>10000000</v>
       </c>
       <c r="F45" s="7" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
     </row>
     <row r="46" spans="1:6">
       <c r="A46" s="6" t="s">
+        <v>744</v>
+      </c>
+      <c r="B46" s="6" t="s">
+        <v>744</v>
+      </c>
+      <c r="C46" s="5" t="s">
         <v>745</v>
       </c>
-      <c r="B46" s="6" t="s">
-        <v>745</v>
-      </c>
-      <c r="C46" s="5" t="s">
+      <c r="D46" s="5" t="s">
         <v>746</v>
-      </c>
-      <c r="D46" s="5" t="s">
-        <v>747</v>
       </c>
       <c r="E46" s="5">
         <v>15</v>
       </c>
       <c r="F46" s="7" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
     </row>
     <row r="47" spans="1:6">
       <c r="A47" s="6" t="s">
+        <v>748</v>
+      </c>
+      <c r="B47" s="6" t="s">
+        <v>748</v>
+      </c>
+      <c r="C47" s="5" t="s">
         <v>749</v>
       </c>
-      <c r="B47" s="6" t="s">
-        <v>749</v>
-      </c>
-      <c r="C47" s="5" t="s">
+      <c r="D47" s="5" t="s">
         <v>750</v>
-      </c>
-      <c r="D47" s="5" t="s">
-        <v>751</v>
       </c>
       <c r="E47" s="5">
         <v>15</v>
       </c>
       <c r="F47" s="7" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
     </row>
     <row r="48" spans="1:6">
       <c r="A48" s="6" t="s">
+        <v>752</v>
+      </c>
+      <c r="B48" s="6" t="s">
+        <v>752</v>
+      </c>
+      <c r="C48" s="5" t="s">
         <v>753</v>
       </c>
-      <c r="B48" s="6" t="s">
-        <v>753</v>
-      </c>
-      <c r="C48" s="5" t="s">
+      <c r="D48" s="5" t="s">
         <v>754</v>
-      </c>
-      <c r="D48" s="5" t="s">
-        <v>755</v>
       </c>
       <c r="E48" s="5">
         <v>12</v>
       </c>
       <c r="F48" s="7" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
     </row>
     <row r="49" spans="1:6">
       <c r="A49" s="6" t="s">
+        <v>756</v>
+      </c>
+      <c r="B49" s="6" t="s">
+        <v>756</v>
+      </c>
+      <c r="C49" s="5" t="s">
         <v>757</v>
       </c>
-      <c r="B49" s="6" t="s">
-        <v>757</v>
-      </c>
-      <c r="C49" s="5" t="s">
+      <c r="D49" s="5" t="s">
         <v>758</v>
-      </c>
-      <c r="D49" s="5" t="s">
-        <v>759</v>
       </c>
       <c r="E49" s="5">
         <v>15</v>
       </c>
       <c r="F49" s="7" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
     </row>
     <row r="50" spans="1:6">
       <c r="A50" s="6" t="s">
+        <v>760</v>
+      </c>
+      <c r="B50" s="6" t="s">
+        <v>760</v>
+      </c>
+      <c r="C50" s="5" t="s">
         <v>761</v>
       </c>
-      <c r="B50" s="6" t="s">
-        <v>761</v>
-      </c>
-      <c r="C50" s="5" t="s">
+      <c r="D50" s="5" t="s">
         <v>762</v>
-      </c>
-      <c r="D50" s="5" t="s">
-        <v>763</v>
       </c>
       <c r="E50" s="5">
         <v>40</v>
       </c>
       <c r="F50" s="7" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
     </row>
     <row r="51" spans="1:6">
       <c r="A51" s="6" t="s">
+        <v>764</v>
+      </c>
+      <c r="B51" s="6" t="s">
+        <v>764</v>
+      </c>
+      <c r="C51" s="5" t="s">
         <v>765</v>
       </c>
-      <c r="B51" s="6" t="s">
-        <v>765</v>
-      </c>
-      <c r="C51" s="5" t="s">
+      <c r="D51" s="5" t="s">
         <v>766</v>
-      </c>
-      <c r="D51" s="5" t="s">
-        <v>767</v>
       </c>
       <c r="E51" s="5">
         <v>50</v>
       </c>
       <c r="F51" s="7" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
     </row>
     <row r="52" spans="1:6">
       <c r="A52" s="6" t="s">
+        <v>768</v>
+      </c>
+      <c r="B52" s="6" t="s">
+        <v>768</v>
+      </c>
+      <c r="C52" s="5" t="s">
         <v>769</v>
       </c>
-      <c r="B52" s="6" t="s">
-        <v>769</v>
-      </c>
-      <c r="C52" s="5" t="s">
+      <c r="D52" s="5" t="s">
         <v>770</v>
-      </c>
-      <c r="D52" s="5" t="s">
-        <v>771</v>
       </c>
       <c r="E52" s="5">
         <v>18</v>
       </c>
       <c r="F52" s="7" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
     </row>
     <row r="53" spans="1:6">
       <c r="A53" s="6" t="s">
+        <v>772</v>
+      </c>
+      <c r="B53" s="6" t="s">
+        <v>772</v>
+      </c>
+      <c r="C53" s="5" t="s">
         <v>773</v>
       </c>
-      <c r="B53" s="6" t="s">
-        <v>773</v>
-      </c>
-      <c r="C53" s="5" t="s">
+      <c r="D53" s="5" t="s">
         <v>774</v>
-      </c>
-      <c r="D53" s="5" t="s">
-        <v>775</v>
       </c>
       <c r="E53" s="5">
         <v>15</v>
       </c>
       <c r="F53" s="7" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
     </row>
     <row r="54" spans="1:6">
       <c r="A54" s="6" t="s">
+        <v>776</v>
+      </c>
+      <c r="B54" s="6" t="s">
+        <v>776</v>
+      </c>
+      <c r="C54" s="5" t="s">
         <v>777</v>
       </c>
-      <c r="B54" s="6" t="s">
-        <v>777</v>
-      </c>
-      <c r="C54" s="5" t="s">
+      <c r="D54" s="5" t="s">
         <v>778</v>
-      </c>
-      <c r="D54" s="5" t="s">
-        <v>779</v>
       </c>
       <c r="E54" s="5">
         <v>20</v>
       </c>
       <c r="F54" s="7" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="55" spans="1:6">
       <c r="A55" s="6" t="s">
+        <v>780</v>
+      </c>
+      <c r="B55" s="6" t="s">
+        <v>780</v>
+      </c>
+      <c r="C55" s="5" t="s">
         <v>781</v>
       </c>
-      <c r="B55" s="6" t="s">
-        <v>781</v>
-      </c>
-      <c r="C55" s="5" t="s">
+      <c r="D55" s="5" t="s">
         <v>782</v>
-      </c>
-      <c r="D55" s="5" t="s">
-        <v>783</v>
       </c>
       <c r="E55" s="5">
         <v>12</v>
       </c>
       <c r="F55" s="7" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
     </row>
     <row r="56" spans="1:6">
       <c r="A56" s="6" t="s">
+        <v>784</v>
+      </c>
+      <c r="B56" s="6" t="s">
+        <v>784</v>
+      </c>
+      <c r="C56" s="5" t="s">
         <v>785</v>
       </c>
-      <c r="B56" s="6" t="s">
-        <v>785</v>
-      </c>
-      <c r="C56" s="5" t="s">
+      <c r="D56" s="5" t="s">
         <v>786</v>
-      </c>
-      <c r="D56" s="5" t="s">
-        <v>787</v>
       </c>
       <c r="E56" s="5">
         <v>20</v>
       </c>
       <c r="F56" s="7" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
     </row>
     <row r="57" spans="1:6">
       <c r="A57" s="6" t="s">
+        <v>788</v>
+      </c>
+      <c r="B57" s="6" t="s">
+        <v>788</v>
+      </c>
+      <c r="C57" s="5" t="s">
         <v>789</v>
       </c>
-      <c r="B57" s="6" t="s">
-        <v>789</v>
-      </c>
-      <c r="C57" s="5" t="s">
+      <c r="D57" s="5" t="s">
         <v>790</v>
-      </c>
-      <c r="D57" s="5" t="s">
-        <v>791</v>
       </c>
       <c r="E57" s="5">
         <v>20</v>
       </c>
       <c r="F57" s="7" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
     </row>
     <row r="58" spans="1:6">
       <c r="A58" s="6" t="s">
+        <v>792</v>
+      </c>
+      <c r="B58" s="6" t="s">
+        <v>792</v>
+      </c>
+      <c r="C58" s="5" t="s">
         <v>793</v>
       </c>
-      <c r="B58" s="6" t="s">
-        <v>793</v>
-      </c>
-      <c r="C58" s="5" t="s">
+      <c r="D58" s="5" t="s">
         <v>794</v>
-      </c>
-      <c r="D58" s="5" t="s">
-        <v>795</v>
       </c>
       <c r="E58" s="5">
         <v>15</v>
       </c>
       <c r="F58" s="7" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
     </row>
     <row r="59" spans="1:6">
       <c r="A59" s="6" t="s">
+        <v>796</v>
+      </c>
+      <c r="B59" s="6" t="s">
+        <v>796</v>
+      </c>
+      <c r="C59" s="5" t="s">
         <v>797</v>
       </c>
-      <c r="B59" s="6" t="s">
-        <v>797</v>
-      </c>
-      <c r="C59" s="5" t="s">
+      <c r="D59" s="5" t="s">
         <v>798</v>
-      </c>
-      <c r="D59" s="5" t="s">
-        <v>799</v>
       </c>
       <c r="E59" s="5">
         <v>15</v>
       </c>
       <c r="F59" s="7" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
     </row>
     <row r="60" spans="1:6">
       <c r="A60" s="6" t="s">
+        <v>800</v>
+      </c>
+      <c r="B60" s="6" t="s">
+        <v>800</v>
+      </c>
+      <c r="C60" s="5" t="s">
         <v>801</v>
       </c>
-      <c r="B60" s="6" t="s">
-        <v>801</v>
-      </c>
-      <c r="C60" s="5" t="s">
+      <c r="D60" s="5" t="s">
         <v>802</v>
-      </c>
-      <c r="D60" s="5" t="s">
-        <v>803</v>
       </c>
       <c r="E60" s="5">
         <v>40</v>
       </c>
       <c r="F60" s="7" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
     </row>
     <row r="61" spans="1:6">
       <c r="A61" s="6" t="s">
+        <v>804</v>
+      </c>
+      <c r="B61" s="6" t="s">
+        <v>804</v>
+      </c>
+      <c r="C61" s="5" t="s">
         <v>805</v>
       </c>
-      <c r="B61" s="6" t="s">
-        <v>805</v>
-      </c>
-      <c r="C61" s="5" t="s">
+      <c r="D61" s="5" t="s">
         <v>806</v>
-      </c>
-      <c r="D61" s="5" t="s">
-        <v>807</v>
       </c>
       <c r="E61" s="5">
         <v>15</v>
       </c>
       <c r="F61" s="7" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
     </row>
     <row r="62" spans="1:6">
       <c r="A62" s="6" t="s">
+        <v>808</v>
+      </c>
+      <c r="B62" s="6" t="s">
+        <v>808</v>
+      </c>
+      <c r="C62" s="5" t="s">
         <v>809</v>
       </c>
-      <c r="B62" s="6" t="s">
-        <v>809</v>
-      </c>
-      <c r="C62" s="5" t="s">
+      <c r="D62" s="5" t="s">
         <v>810</v>
-      </c>
-      <c r="D62" s="5" t="s">
-        <v>811</v>
       </c>
       <c r="E62" s="5">
         <v>20</v>
       </c>
       <c r="F62" s="7" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
     </row>
     <row r="63" spans="1:6">
       <c r="A63" s="6" t="s">
+        <v>812</v>
+      </c>
+      <c r="B63" s="6" t="s">
+        <v>812</v>
+      </c>
+      <c r="C63" s="5" t="s">
         <v>813</v>
       </c>
-      <c r="B63" s="6" t="s">
-        <v>813</v>
-      </c>
-      <c r="C63" s="5" t="s">
+      <c r="D63" s="5" t="s">
         <v>814</v>
-      </c>
-      <c r="D63" s="5" t="s">
-        <v>815</v>
       </c>
       <c r="E63" s="5">
         <v>20</v>
       </c>
       <c r="F63" s="7" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
     </row>
     <row r="64" ht="26" spans="1:6">
       <c r="A64" s="6" t="s">
+        <v>816</v>
+      </c>
+      <c r="B64" s="6" t="s">
+        <v>816</v>
+      </c>
+      <c r="C64" s="5" t="s">
         <v>817</v>
       </c>
-      <c r="B64" s="6" t="s">
-        <v>817</v>
-      </c>
-      <c r="C64" s="5" t="s">
+      <c r="D64" s="5" t="s">
         <v>818</v>
-      </c>
-      <c r="D64" s="5" t="s">
-        <v>819</v>
       </c>
       <c r="E64" s="5">
         <v>15</v>
       </c>
       <c r="F64" s="7" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
     </row>
     <row r="65" spans="1:6">
       <c r="A65" s="6" t="s">
+        <v>820</v>
+      </c>
+      <c r="B65" s="6" t="s">
+        <v>820</v>
+      </c>
+      <c r="C65" s="5" t="s">
         <v>821</v>
       </c>
-      <c r="B65" s="6" t="s">
-        <v>821</v>
-      </c>
-      <c r="C65" s="5" t="s">
+      <c r="D65" s="5" t="s">
         <v>822</v>
-      </c>
-      <c r="D65" s="5" t="s">
-        <v>823</v>
       </c>
       <c r="E65" s="5">
         <v>20</v>
       </c>
       <c r="F65" s="7" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
     </row>
     <row r="66" spans="1:6">
       <c r="A66" s="6" t="s">
+        <v>824</v>
+      </c>
+      <c r="B66" s="6" t="s">
+        <v>824</v>
+      </c>
+      <c r="C66" s="5" t="s">
         <v>825</v>
       </c>
-      <c r="B66" s="6" t="s">
-        <v>825</v>
-      </c>
-      <c r="C66" s="5" t="s">
+      <c r="D66" s="5" t="s">
         <v>826</v>
-      </c>
-      <c r="D66" s="5" t="s">
-        <v>827</v>
       </c>
       <c r="E66" s="5">
         <v>6</v>
       </c>
       <c r="F66" s="7" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
     </row>
     <row r="67" spans="1:6">
       <c r="A67" s="6" t="s">
+        <v>828</v>
+      </c>
+      <c r="B67" s="6" t="s">
+        <v>828</v>
+      </c>
+      <c r="C67" s="5" t="s">
         <v>829</v>
       </c>
-      <c r="B67" s="6" t="s">
-        <v>829</v>
-      </c>
-      <c r="C67" s="5" t="s">
+      <c r="D67" s="5" t="s">
         <v>830</v>
-      </c>
-      <c r="D67" s="5" t="s">
-        <v>831</v>
       </c>
       <c r="E67" s="5">
         <v>20</v>
       </c>
       <c r="F67" s="7" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
     </row>
     <row r="68" spans="1:6">
       <c r="A68" s="6" t="s">
+        <v>832</v>
+      </c>
+      <c r="B68" s="6" t="s">
+        <v>832</v>
+      </c>
+      <c r="C68" s="5" t="s">
         <v>833</v>
       </c>
-      <c r="B68" s="6" t="s">
-        <v>833</v>
-      </c>
-      <c r="C68" s="5" t="s">
+      <c r="D68" s="5" t="s">
         <v>834</v>
-      </c>
-      <c r="D68" s="5" t="s">
-        <v>835</v>
       </c>
       <c r="E68" s="5">
         <v>18</v>
       </c>
       <c r="F68" s="7" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
     </row>
     <row r="69" spans="1:6">
       <c r="A69" s="6" t="s">
+        <v>836</v>
+      </c>
+      <c r="B69" s="6" t="s">
+        <v>836</v>
+      </c>
+      <c r="C69" s="5" t="s">
         <v>837</v>
       </c>
-      <c r="B69" s="6" t="s">
-        <v>837</v>
-      </c>
-      <c r="C69" s="5" t="s">
+      <c r="D69" s="5" t="s">
         <v>838</v>
-      </c>
-      <c r="D69" s="5" t="s">
-        <v>839</v>
       </c>
       <c r="E69" s="5">
         <v>12</v>
       </c>
       <c r="F69" s="7" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
     </row>
     <row r="70" spans="1:6">
       <c r="A70" s="6" t="s">
+        <v>840</v>
+      </c>
+      <c r="B70" s="6" t="s">
+        <v>840</v>
+      </c>
+      <c r="C70" s="5" t="s">
         <v>841</v>
       </c>
-      <c r="B70" s="6" t="s">
-        <v>841</v>
-      </c>
-      <c r="C70" s="5" t="s">
+      <c r="D70" s="5" t="s">
         <v>842</v>
-      </c>
-      <c r="D70" s="5" t="s">
-        <v>843</v>
       </c>
       <c r="E70" s="5">
         <v>18</v>
       </c>
       <c r="F70" s="7" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
     </row>
     <row r="71" spans="1:6">
       <c r="A71" s="6" t="s">
+        <v>844</v>
+      </c>
+      <c r="B71" s="6" t="s">
+        <v>844</v>
+      </c>
+      <c r="C71" s="5" t="s">
         <v>845</v>
       </c>
-      <c r="B71" s="6" t="s">
-        <v>845</v>
-      </c>
-      <c r="C71" s="5" t="s">
+      <c r="D71" s="5" t="s">
         <v>846</v>
-      </c>
-      <c r="D71" s="5" t="s">
-        <v>847</v>
       </c>
       <c r="E71" s="5">
         <v>6</v>
       </c>
       <c r="F71" s="7" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
     </row>
     <row r="72" spans="1:6">
       <c r="A72" s="6" t="s">
+        <v>848</v>
+      </c>
+      <c r="B72" s="6" t="s">
+        <v>848</v>
+      </c>
+      <c r="C72" s="5" t="s">
         <v>849</v>
       </c>
-      <c r="B72" s="6" t="s">
-        <v>849</v>
-      </c>
-      <c r="C72" s="5" t="s">
+      <c r="D72" s="5" t="s">
         <v>850</v>
-      </c>
-      <c r="D72" s="5" t="s">
-        <v>851</v>
       </c>
       <c r="E72" s="5">
         <v>15</v>
       </c>
       <c r="F72" s="7" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
     </row>
     <row r="75" spans="1:6">
